--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E153FA96-0E65-411A-81D7-15A1ADC21AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622FA571-3514-4BFA-BEC7-C3FB57D8F451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
   <sheets>
     <sheet name="info_index" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="B10" t="str">
         <f ca="1">"このスクリプトは "&amp;B15&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script2 によって生成されました。</v>
+        <v>このスクリプトは C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content_scripts(変数) によって生成されました。</v>
       </c>
       <c r="E10" t="str">
         <f t="shared" si="0"/>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="B15" t="str" cm="1">
         <f t="array" aca="1" ref="B15" ca="1">CELL("filename")</f>
-        <v>C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script2</v>
+        <v>C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content_scripts(変数)</v>
       </c>
       <c r="E15" t="str">
         <f t="shared" si="0"/>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="B25" t="str">
         <f ca="1">$AC$204</f>
-        <v>//このスクリプトは C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script2 によって生成されました。
+        <v>//このスクリプトは C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content_scripts(変数) によって生成されました。
 //Foil wax reel shaft
 IF InfoType = 'axis' THEN
 	IF InfoIdx = 1 THEN
@@ -16260,7 +16260,7 @@
     <row r="204" spans="5:29" x14ac:dyDescent="0.55000000000000004">
       <c r="AC204" t="str">
         <f ca="1">IF(LENB($B$10),$B$7&amp;$B$10,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AC$2:AC$201)&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$11),CHAR(10)&amp;$B$7&amp;$B$11,"")</f>
-        <v>//このスクリプトは C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script2 によって生成されました。
+        <v>//このスクリプトは C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content_scripts(変数) によって生成されました。
 //Foil wax reel shaft
 IF InfoType = 'axis' THEN
 	IF InfoIdx = 1 THEN
@@ -16621,7 +16621,7 @@
       </c>
       <c r="B2" t="str" cm="1">
         <f t="array" aca="1" ref="B2" ca="1">CELL("filename")</f>
-        <v>C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script2</v>
+        <v>C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content_scripts(変数)</v>
       </c>
       <c r="E2" t="s">
         <v>117</v>
@@ -17013,7 +17013,7 @@
       </c>
       <c r="B4" t="str">
         <f ca="1">"このスクリプトは "&amp;B2&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script2 によって生成されました。</v>
+        <v>このスクリプトは C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content_scripts(変数) によって生成されました。</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" ref="E4:E67" si="0">E3</f>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="B12" t="str">
         <f ca="1">$AJ$204</f>
-        <v>//このスクリプトは C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script2 によって生成されました。
+        <v>//このスクリプトは C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content_scripts(変数) によって生成されました。
 //Foil wax reel shaft
 IF InfoType = 'axis' THEN
 	IF InfoIdx = 1 THEN
@@ -40214,7 +40214,7 @@
     <row r="204" spans="5:36" x14ac:dyDescent="0.55000000000000004">
       <c r="AJ204" t="str">
         <f ca="1">IF(LENB($B$4),$B$6&amp;$B$4,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AJ$2:AJ$201)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$7&amp;" 1"&amp;$B$8&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$5),CHAR(10)&amp;$B$6&amp;$B$5,"")</f>
-        <v>//このスクリプトは C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script2 によって生成されました。
+        <v>//このスクリプトは C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content_scripts(変数) によって生成されました。
 //Foil wax reel shaft
 IF InfoType = 'axis' THEN
 	IF InfoIdx = 1 THEN
@@ -40701,7 +40701,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A1:XFD1 A2:B2 C2:XFD11 A4:B8 A23:XFD24 A12:XFD14 C15:XFD22 A29:XFD1048576 C25:XFD28 A22:B28">
+  <conditionalFormatting sqref="A1:XFD1 A2:B2 C2:XFD11 A4:B8 A12:XFD14 C15:XFD22 A22:B28 A23:XFD24 C25:XFD28 A29:XFD1048576">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7B6B14-4B76-446A-8100-BEC52295446F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2241A67-169F-4B94-87FC-275C76E74537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
   <sheets>
     <sheet name="info_index" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]title_scripts(変数)</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]title_scripts(変数) によって生成されました。</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ref="E5:E68" si="0">E4</f>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AK$205</f>
-        <v>//このスクリプトは C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]title_scripts(変数) によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸
@@ -28089,7 +28089,7 @@
     <row r="205" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="AK205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AK$3:AK$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]title_scripts(変数) によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2241A67-169F-4B94-87FC-275C76E74537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19506EF2-EB96-4DDA-A01F-B3B7EEF85D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="info_script" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$N$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$P$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="257">
   <si>
     <t>RCA2-GS3NA-I-10-2-50-A6-M-K1</t>
   </si>
@@ -1120,10 +1120,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Rt</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>key2</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1254,10 +1250,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ErrCode</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>endif3</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1382,6 +1374,38 @@
   </si>
   <si>
     <t>strInfoKey</t>
+  </si>
+  <si>
+    <t>ソレノイドインデックス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソレノイド親機インデックス</t>
+    <rPh sb="5" eb="7">
+      <t>オヤキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>T-roll gluing ①</t>
+  </si>
+  <si>
+    <t>T-roll gluing ②</t>
+  </si>
+  <si>
+    <t>X-roll gluing ①</t>
+  </si>
+  <si>
+    <t>X-roll gluing ②</t>
+  </si>
+  <si>
+    <t>X-roll flat plate pressing</t>
+  </si>
+  <si>
+    <t>strRt</t>
+  </si>
+  <si>
+    <t>uiErrCode</t>
   </si>
 </sst>
 </file>
@@ -2187,7 +2211,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
-  <dimension ref="A1:N78"/>
+  <dimension ref="A1:P78"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -2196,11 +2220,11 @@
     <col min="8" max="8" width="81" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="71.08203125" customWidth="1"/>
     <col min="10" max="11" width="13.08203125" customWidth="1"/>
-    <col min="12" max="13" width="18.33203125" customWidth="1"/>
-    <col min="14" max="14" width="3.58203125" customWidth="1"/>
+    <col min="12" max="15" width="18.33203125" customWidth="1"/>
+    <col min="16" max="16" width="3.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="21" t="s">
         <v>102</v>
       </c>
@@ -2232,7 +2256,7 @@
         <v>3</v>
       </c>
       <c r="K1" s="22" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L1" s="22" t="s">
         <v>5</v>
@@ -2240,9 +2264,15 @@
       <c r="M1" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="N1" s="23"/>
+      <c r="N1" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="O1" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="P1" s="23"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="30">
         <v>38</v>
       </c>
@@ -2271,18 +2301,20 @@
         <v>21</v>
       </c>
       <c r="J2" s="31" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L2" s="31">
         <v>1</v>
       </c>
       <c r="M2" s="32"/>
-      <c r="N2" s="6"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="6"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="7">
         <v>35</v>
       </c>
@@ -2311,18 +2343,20 @@
         <v>13</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L3" s="12">
         <v>1</v>
       </c>
       <c r="M3" s="27"/>
-      <c r="N3" s="10"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="10"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="7">
         <v>37</v>
       </c>
@@ -2351,18 +2385,20 @@
         <v>13</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L4" s="12">
         <v>1</v>
       </c>
       <c r="M4" s="27"/>
-      <c r="N4" s="10"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="10"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="7">
         <v>36</v>
       </c>
@@ -2391,18 +2427,20 @@
         <v>13</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L5" s="12">
         <v>1</v>
       </c>
       <c r="M5" s="27"/>
-      <c r="N5" s="10"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="10"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="7">
         <v>19</v>
       </c>
@@ -2434,15 +2472,17 @@
         <v>2</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L6" s="8">
         <v>1</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="7">
         <v>18</v>
       </c>
@@ -2474,15 +2514,17 @@
         <v>2</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L7" s="8">
         <v>1</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="7">
         <v>20</v>
       </c>
@@ -2514,15 +2556,17 @@
         <v>2</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L8" s="8">
         <v>1</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="7">
         <v>22</v>
       </c>
@@ -2554,15 +2598,17 @@
         <v>2</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L9" s="8">
         <v>1</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="7">
         <v>23</v>
       </c>
@@ -2594,15 +2640,17 @@
         <v>2</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L10" s="8">
         <v>1</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="7">
         <v>42</v>
       </c>
@@ -2627,8 +2675,10 @@
       <c r="L11" s="8"/>
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="7">
         <v>43</v>
       </c>
@@ -2653,8 +2703,10 @@
       <c r="L12" s="8"/>
       <c r="M12" s="10"/>
       <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="7">
         <v>44</v>
       </c>
@@ -2679,8 +2731,10 @@
       <c r="L13" s="8"/>
       <c r="M13" s="10"/>
       <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="7">
         <v>32</v>
       </c>
@@ -2709,18 +2763,20 @@
         <v>32</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L14" s="8">
         <v>1</v>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="7">
         <v>33</v>
       </c>
@@ -2749,18 +2805,20 @@
         <v>32</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L15" s="8">
         <v>1</v>
       </c>
       <c r="M15" s="10"/>
       <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="7">
         <v>41</v>
       </c>
@@ -2787,8 +2845,10 @@
       <c r="L16" s="8"/>
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="7">
         <v>45</v>
       </c>
@@ -2815,8 +2875,10 @@
       <c r="L17" s="8"/>
       <c r="M17" s="10"/>
       <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="7">
         <v>1</v>
       </c>
@@ -2848,327 +2910,385 @@
         <v>4</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L18" s="8">
         <v>1</v>
       </c>
       <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
+      <c r="N18" s="10">
+        <v>0</v>
+      </c>
+      <c r="O18" s="10">
+        <v>0</v>
+      </c>
+      <c r="P18" s="10"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="7">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C19" s="7">
+        <v>5</v>
+      </c>
+      <c r="D19" s="8">
+        <v>5</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="L19" s="8">
+        <v>1</v>
+      </c>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10">
+        <v>0</v>
+      </c>
+      <c r="O19" s="10">
+        <v>1</v>
+      </c>
+      <c r="P19" s="10"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="7">
+        <v>10</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" s="7">
+        <v>11</v>
+      </c>
+      <c r="D20" s="12">
+        <v>9</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="L20" s="13">
+        <v>1</v>
+      </c>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25">
+        <v>0</v>
+      </c>
+      <c r="O20" s="25">
         <v>2</v>
       </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
+      <c r="P20" s="10"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="7">
-        <v>47</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C20" s="7">
-        <v>3</v>
-      </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="7">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C21" s="7">
+        <v>13</v>
+      </c>
+      <c r="D21" s="12">
+        <v>11</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="J21" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="8">
-        <v>2</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="L21" s="8">
+      <c r="K21" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="L21" s="13">
         <v>1</v>
       </c>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="25">
+        <v>0</v>
+      </c>
+      <c r="O21" s="25">
+        <v>3</v>
+      </c>
+      <c r="P21" s="10"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="7">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C22" s="7">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D22" s="8">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J22" s="8" t="s">
         <v>4</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="L22" s="8">
+        <v>237</v>
+      </c>
+      <c r="L22" s="11">
         <v>1</v>
       </c>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="24">
+        <v>0</v>
+      </c>
+      <c r="O22" s="24">
+        <v>4</v>
+      </c>
+      <c r="P22" s="10"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="7">
+        <v>46</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" s="7">
+        <v>2</v>
+      </c>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10">
+        <v>0</v>
+      </c>
+      <c r="O23" s="10">
+        <v>5</v>
+      </c>
+      <c r="P23" s="10"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="7">
+        <v>47</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" s="7">
         <v>3</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C23" s="7">
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10">
+        <v>0</v>
+      </c>
+      <c r="O24" s="10">
         <v>6</v>
       </c>
-      <c r="D23" s="8">
-        <v>5</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="L23" s="8">
-        <v>1</v>
-      </c>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
+      <c r="P24" s="10"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="7">
-        <v>8</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C24" s="7">
-        <v>7</v>
-      </c>
-      <c r="D24" s="8">
-        <v>6</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="L24" s="11">
-        <v>1</v>
-      </c>
-      <c r="M24" s="24"/>
-      <c r="N24" s="10"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="7">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C25" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D25" s="8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>70</v>
+        <v>63</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>4</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="L25" s="11">
+        <v>237</v>
+      </c>
+      <c r="L25" s="8">
         <v>1</v>
       </c>
-      <c r="M25" s="24"/>
-      <c r="N25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10">
+        <v>0</v>
+      </c>
+      <c r="O25" s="10">
+        <v>7</v>
+      </c>
+      <c r="P25" s="10"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C26" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D26" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="J26" s="8" t="s">
         <v>4</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="L26" s="11">
+        <v>237</v>
+      </c>
+      <c r="L26" s="8">
         <v>1</v>
       </c>
-      <c r="M26" s="24"/>
-      <c r="N26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10">
+        <v>0</v>
+      </c>
+      <c r="O26" s="10">
+        <v>8</v>
+      </c>
+      <c r="P26" s="10"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C27" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D27" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>69</v>
@@ -3180,158 +3300,182 @@
         <v>4</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L27" s="11">
         <v>1</v>
       </c>
       <c r="M27" s="24"/>
-      <c r="N27" s="10"/>
+      <c r="N27" s="24">
+        <v>0</v>
+      </c>
+      <c r="O27" s="24">
+        <v>9</v>
+      </c>
+      <c r="P27" s="10"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C28" s="7">
-        <v>11</v>
-      </c>
-      <c r="D28" s="12">
-        <v>9</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="H28" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="I28" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="8">
+        <v>7</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I28" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="J28" s="12" t="s">
+      <c r="J28" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K28" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="L28" s="13">
+      <c r="K28" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="L28" s="11">
         <v>1</v>
       </c>
-      <c r="M28" s="25"/>
-      <c r="N28" s="10"/>
+      <c r="M28" s="24"/>
+      <c r="N28" s="24">
+        <v>0</v>
+      </c>
+      <c r="O28" s="24">
+        <v>10</v>
+      </c>
+      <c r="P28" s="10"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C29" s="7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D29" s="8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J29" s="8" t="s">
         <v>4</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L29" s="11">
         <v>1</v>
       </c>
       <c r="M29" s="24"/>
-      <c r="N29" s="10"/>
+      <c r="N29" s="24">
+        <v>0</v>
+      </c>
+      <c r="O29" s="24">
+        <v>11</v>
+      </c>
+      <c r="P29" s="10"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="7">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C30" s="7">
-        <v>13</v>
-      </c>
-      <c r="D30" s="12">
-        <v>11</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="F30" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="G30" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="H30" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="I30" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="8">
+        <v>8</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I30" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="J30" s="12" t="s">
+      <c r="J30" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K30" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="L30" s="13">
+      <c r="K30" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="L30" s="11">
         <v>1</v>
       </c>
-      <c r="M30" s="25"/>
-      <c r="N30" s="10"/>
+      <c r="M30" s="24"/>
+      <c r="N30" s="24">
+        <v>0</v>
+      </c>
+      <c r="O30" s="24">
+        <v>12</v>
+      </c>
+      <c r="P30" s="10"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="7">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C31" s="7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D31" s="8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>70</v>
@@ -3340,15 +3484,21 @@
         <v>4</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L31" s="11">
         <v>1</v>
       </c>
       <c r="M31" s="24"/>
-      <c r="N31" s="10"/>
+      <c r="N31" s="24">
+        <v>0</v>
+      </c>
+      <c r="O31" s="24">
+        <v>13</v>
+      </c>
+      <c r="P31" s="10"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="7">
         <v>14</v>
       </c>
@@ -3380,15 +3530,21 @@
         <v>4</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L32" s="13">
         <v>1</v>
       </c>
       <c r="M32" s="25"/>
-      <c r="N32" s="10"/>
+      <c r="N32" s="25">
+        <v>0</v>
+      </c>
+      <c r="O32" s="25">
+        <v>14</v>
+      </c>
+      <c r="P32" s="10"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="7">
         <v>15</v>
       </c>
@@ -3420,15 +3576,21 @@
         <v>4</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L33" s="13">
         <v>1</v>
       </c>
       <c r="M33" s="25"/>
-      <c r="N33" s="10"/>
+      <c r="N33" s="25">
+        <v>0</v>
+      </c>
+      <c r="O33" s="25">
+        <v>15</v>
+      </c>
+      <c r="P33" s="10"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="7">
         <v>48</v>
       </c>
@@ -3441,9 +3603,11 @@
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
       <c r="F34" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="G34" s="8"/>
+        <v>219</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>252</v>
+      </c>
       <c r="H34" s="8" t="s">
         <v>51</v>
       </c>
@@ -3452,9 +3616,15 @@
       <c r="K34" s="8"/>
       <c r="L34" s="8"/>
       <c r="M34" s="10"/>
-      <c r="N34" s="10"/>
+      <c r="N34" s="10">
+        <v>1</v>
+      </c>
+      <c r="O34" s="10">
+        <v>0</v>
+      </c>
+      <c r="P34" s="10"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="7">
         <v>49</v>
       </c>
@@ -3467,9 +3637,11 @@
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
       <c r="F35" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="G35" s="8"/>
+        <v>220</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>253</v>
+      </c>
       <c r="H35" s="8" t="s">
         <v>51</v>
       </c>
@@ -3478,9 +3650,15 @@
       <c r="K35" s="8"/>
       <c r="L35" s="8"/>
       <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
+      <c r="N35" s="10">
+        <v>1</v>
+      </c>
+      <c r="O35" s="10">
+        <v>1</v>
+      </c>
+      <c r="P35" s="10"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="7">
         <v>50</v>
       </c>
@@ -3493,20 +3671,28 @@
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
       <c r="F36" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="G36" s="8"/>
+        <v>222</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>254</v>
+      </c>
       <c r="H36" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
       <c r="K36" s="8"/>
       <c r="L36" s="8"/>
       <c r="M36" s="10"/>
-      <c r="N36" s="10"/>
+      <c r="N36" s="10">
+        <v>1</v>
+      </c>
+      <c r="O36" s="10">
+        <v>2</v>
+      </c>
+      <c r="P36" s="10"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="29">
         <v>12</v>
       </c>
@@ -3532,7 +3718,7 @@
         <v>4</v>
       </c>
       <c r="K37" s="14" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L37" s="15">
         <v>1</v>
@@ -3540,9 +3726,11 @@
       <c r="M37" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="N37" s="10"/>
+      <c r="N37" s="26"/>
+      <c r="O37" s="26"/>
+      <c r="P37" s="10"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="29">
         <v>16</v>
       </c>
@@ -3568,7 +3756,7 @@
         <v>4</v>
       </c>
       <c r="K38" s="14" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L38" s="15">
         <v>1</v>
@@ -3576,9 +3764,11 @@
       <c r="M38" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="N38" s="10"/>
+      <c r="N38" s="26"/>
+      <c r="O38" s="26"/>
+      <c r="P38" s="10"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="29">
         <v>17</v>
       </c>
@@ -3604,7 +3794,7 @@
         <v>4</v>
       </c>
       <c r="K39" s="14" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L39" s="15">
         <v>1</v>
@@ -3612,9 +3802,11 @@
       <c r="M39" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="N39" s="10"/>
+      <c r="N39" s="26"/>
+      <c r="O39" s="26"/>
+      <c r="P39" s="10"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="7">
         <v>21</v>
       </c>
@@ -3634,7 +3826,7 @@
         <v>130</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>30</v>
@@ -3646,15 +3838,17 @@
         <v>2</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L40" s="8">
         <v>1</v>
       </c>
       <c r="M40" s="10"/>
       <c r="N40" s="10"/>
+      <c r="O40" s="10"/>
+      <c r="P40" s="10"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="7">
         <v>24</v>
       </c>
@@ -3679,18 +3873,20 @@
         <v>8</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L41" s="8">
         <v>1</v>
       </c>
       <c r="M41" s="10"/>
       <c r="N41" s="10"/>
+      <c r="O41" s="10"/>
+      <c r="P41" s="10"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="7">
         <v>25</v>
       </c>
@@ -3715,18 +3911,20 @@
         <v>9</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L42" s="8">
         <v>1</v>
       </c>
       <c r="M42" s="10"/>
       <c r="N42" s="10"/>
+      <c r="O42" s="10"/>
+      <c r="P42" s="10"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="7">
         <v>29</v>
       </c>
@@ -3749,18 +3947,20 @@
         <v>23</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L43" s="8">
         <v>3</v>
       </c>
       <c r="M43" s="10"/>
       <c r="N43" s="10"/>
+      <c r="O43" s="10"/>
+      <c r="P43" s="10"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="7">
         <v>30</v>
       </c>
@@ -3785,10 +3985,10 @@
         <v>24</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L44" s="8">
         <v>1</v>
@@ -3797,8 +3997,10 @@
         <v>57</v>
       </c>
       <c r="N44" s="10"/>
+      <c r="O44" s="10"/>
+      <c r="P44" s="10"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="7">
         <v>34</v>
       </c>
@@ -3823,10 +4025,10 @@
         <v>36</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L45" s="8">
         <v>1</v>
@@ -3835,8 +4037,10 @@
         <v>34</v>
       </c>
       <c r="N45" s="10"/>
+      <c r="O45" s="10"/>
+      <c r="P45" s="10"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="7">
         <v>26</v>
       </c>
@@ -3857,18 +4061,20 @@
         <v>59</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L46" s="8">
         <v>1</v>
       </c>
       <c r="M46" s="10"/>
       <c r="N46" s="10"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="10"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="7">
         <v>27</v>
       </c>
@@ -3889,18 +4095,20 @@
         <v>19</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L47" s="8">
         <v>1</v>
       </c>
       <c r="M47" s="10"/>
       <c r="N47" s="10"/>
+      <c r="O47" s="10"/>
+      <c r="P47" s="10"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="7">
         <v>28</v>
       </c>
@@ -3921,18 +4129,20 @@
         <v>17</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L48" s="8">
         <v>1</v>
       </c>
       <c r="M48" s="10"/>
       <c r="N48" s="10"/>
+      <c r="O48" s="10"/>
+      <c r="P48" s="10"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="7">
         <v>31</v>
       </c>
@@ -3953,10 +4163,10 @@
         <v>26</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L49" s="8">
         <v>1</v>
@@ -3965,8 +4175,10 @@
         <v>57</v>
       </c>
       <c r="N49" s="10"/>
+      <c r="O49" s="10"/>
+      <c r="P49" s="10"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="7">
         <v>39</v>
       </c>
@@ -3987,18 +4199,20 @@
         <v>26</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L50" s="8">
         <v>1</v>
       </c>
       <c r="M50" s="10"/>
       <c r="N50" s="10"/>
+      <c r="O50" s="10"/>
+      <c r="P50" s="10"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="18"/>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
@@ -4013,8 +4227,10 @@
       <c r="L51" s="19"/>
       <c r="M51" s="20"/>
       <c r="N51" s="20"/>
+      <c r="O51" s="20"/>
+      <c r="P51" s="20"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>111</v>
       </c>
@@ -4022,7 +4238,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A54">
         <f>MAX(A$2:A$51)</f>
         <v>50</v>
@@ -4032,9 +4248,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B55" t="s">
         <v>117</v>
@@ -4043,7 +4259,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A56">
         <f>ROW(A52)-ROW(A1)-1</f>
         <v>50</v>
@@ -4057,7 +4273,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" t="s">
         <v>114</v>
       </c>
@@ -4065,7 +4281,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B58">
         <f>COUNTIF(B$2:B$51,B57)</f>
         <v>22</v>
@@ -4075,18 +4291,18 @@
         <v>19</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="H61" s="2" t="s">
         <v>37</v>
       </c>
       <c r="L61">
         <v>1</v>
       </c>
-      <c r="N61" t="s">
+      <c r="P61" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="H62" t="s">
         <v>56</v>
       </c>
@@ -4099,16 +4315,16 @@
       <c r="L62">
         <v>1</v>
       </c>
-      <c r="N62" t="s">
+      <c r="P62" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="H64" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="65" spans="8:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="8:16" x14ac:dyDescent="0.55000000000000004">
       <c r="H65" t="s">
         <v>82</v>
       </c>
@@ -4121,16 +4337,16 @@
       <c r="L65">
         <v>1</v>
       </c>
-      <c r="N65" t="s">
+      <c r="P65" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="67" spans="8:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="8:16" x14ac:dyDescent="0.55000000000000004">
       <c r="H67" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="68" spans="8:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="8:16" x14ac:dyDescent="0.55000000000000004">
       <c r="H68" t="s">
         <v>83</v>
       </c>
@@ -4143,16 +4359,16 @@
       <c r="L68">
         <v>1</v>
       </c>
-      <c r="N68" t="s">
+      <c r="P68" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="70" spans="8:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="8:16" x14ac:dyDescent="0.55000000000000004">
       <c r="H70" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="71" spans="8:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="8:16" x14ac:dyDescent="0.55000000000000004">
       <c r="H71" t="s">
         <v>42</v>
       </c>
@@ -4165,11 +4381,11 @@
       <c r="L71">
         <v>1</v>
       </c>
-      <c r="N71" t="s">
+      <c r="P71" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="72" spans="8:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="8:16" x14ac:dyDescent="0.55000000000000004">
       <c r="H72" t="s">
         <v>45</v>
       </c>
@@ -4182,16 +4398,16 @@
       <c r="L72">
         <v>2</v>
       </c>
-      <c r="N72" t="s">
+      <c r="P72" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="74" spans="8:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="8:16" x14ac:dyDescent="0.55000000000000004">
       <c r="H74" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="75" spans="8:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="8:16" x14ac:dyDescent="0.55000000000000004">
       <c r="H75" t="s">
         <v>46</v>
       </c>
@@ -4204,11 +4420,11 @@
       <c r="L75">
         <v>1</v>
       </c>
-      <c r="N75" t="s">
+      <c r="P75" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="76" spans="8:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="8:16" x14ac:dyDescent="0.55000000000000004">
       <c r="H76" t="s">
         <v>50</v>
       </c>
@@ -4221,11 +4437,11 @@
       <c r="L76">
         <v>1</v>
       </c>
-      <c r="N76" t="s">
+      <c r="P76" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="77" spans="8:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="8:16" x14ac:dyDescent="0.55000000000000004">
       <c r="H77" t="s">
         <v>51</v>
       </c>
@@ -4238,11 +4454,11 @@
       <c r="L77">
         <v>2</v>
       </c>
-      <c r="N77" t="s">
+      <c r="P77" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="78" spans="8:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="8:16" x14ac:dyDescent="0.55000000000000004">
       <c r="H78" t="s">
         <v>85</v>
       </c>
@@ -4255,18 +4471,14 @@
       <c r="L78">
         <v>1</v>
       </c>
-      <c r="N78" t="s">
+      <c r="P78" t="s">
         <v>87</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N45" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N50">
-      <sortCondition ref="B1:B45"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:P50" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A2:N51">
+  <conditionalFormatting sqref="A2:P51">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>MOD(ROW(A2),2)=1</formula>
     </cfRule>
@@ -4295,19 +4507,19 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="F1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="J1" t="s">
+        <v>239</v>
+      </c>
+      <c r="L1" t="s">
+        <v>240</v>
+      </c>
+      <c r="N1" t="s">
         <v>241</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>242</v>
-      </c>
-      <c r="N1" t="s">
-        <v>243</v>
-      </c>
-      <c r="P1" t="s">
-        <v>244</v>
       </c>
       <c r="AA1" t="str">
         <f>IF(LEN(J1),J2&amp;CHAR(9)&amp;":"&amp;J1,"")</f>
@@ -4341,73 +4553,73 @@
     </row>
     <row r="2" spans="1:37" s="33" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="33" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F2" s="33" t="s">
         <v>102</v>
       </c>
       <c r="G2" s="33" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H2" s="33" t="s">
+        <v>228</v>
+      </c>
+      <c r="J2" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="L2" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="N2" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="P2" s="33" t="s">
         <v>230</v>
       </c>
-      <c r="J2" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="L2" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="N2" s="33" t="s">
+      <c r="X2" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="P2" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="X2" s="33" t="s">
-        <v>213</v>
-      </c>
       <c r="Y2" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="Z2" s="33" t="s">
         <v>204</v>
       </c>
-      <c r="Z2" s="33" t="s">
+      <c r="AA2" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="AA2" s="33" t="s">
+      <c r="AB2" s="33" t="s">
         <v>206</v>
       </c>
-      <c r="AB2" s="33" t="s">
+      <c r="AC2" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="AC2" s="33" t="s">
-        <v>208</v>
-      </c>
       <c r="AD2" s="33" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE2" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="AF2" s="33" t="s">
         <v>215</v>
       </c>
-      <c r="AF2" s="33" t="s">
-        <v>216</v>
-      </c>
       <c r="AG2" s="33" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AH2" s="33" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AI2" s="33" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AJ2" s="33" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AK2" s="33" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.55000000000000004">
@@ -4416,7 +4628,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]title_scripts(変数)</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
@@ -4488,7 +4700,7 @@
 	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウリール軸';</v>
+			strRt	:= '箔ロウリール軸';</v>
       </c>
       <c r="AC3" t="str" cm="1">
         <f t="array" aca="1" ref="AC3:AC202" ca="1">IF(LEN(AB3:AB202),AB3:AB202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;L$2&amp;"' THEN","")</f>
@@ -4497,7 +4709,7 @@
 	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウリール軸';
+			strRt	:= '箔ロウリール軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD3" t="str" cm="1">
@@ -4507,9 +4719,9 @@
 	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウリール軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis1】 箔ロウリール軸';</v>
+			strRt	:= '箔ロウリール軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 箔ロウリール軸';</v>
       </c>
       <c r="AE3" t="str" cm="1">
         <f t="array" aca="1" ref="AE3:AE202" ca="1">IF(LEN(AD3:AD202),AD3:AD202,"")&amp;IF(LEN(N3:N202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;N$2&amp;"' THEN","")</f>
@@ -4518,9 +4730,9 @@
 	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウリール軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis1】 箔ロウリール軸';
+			strRt	:= '箔ロウリール軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 箔ロウリール軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF3" t="str" cm="1">
@@ -4530,11 +4742,11 @@
 	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウリール軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis1】 箔ロウリール軸';
+			strRt	:= '箔ロウリール軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 箔ロウリール軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= '5TK20GN-CW2J+5GN180K';</v>
+			strRt	:= '5TK20GN-CW2J+5GN180K';</v>
       </c>
       <c r="AG3" t="str" cm="1">
         <f t="array" aca="1" ref="AG3:AG202" ca="1">IF(LEN(AF3:AF202),AF3:AF202,"")&amp;IF(LEN(P3:P202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;P$2&amp;"' THEN","")</f>
@@ -4543,11 +4755,11 @@
 	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウリール軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis1】 箔ロウリール軸';
+			strRt	:= '箔ロウリール軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 箔ロウリール軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= '5TK20GN-CW2J+5GN180K';
+			strRt	:= '5TK20GN-CW2J+5GN180K';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH3" t="str" cm="1">
@@ -4557,13 +4769,13 @@
 	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウリール軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis1】 箔ロウリール軸';
+			strRt	:= '箔ロウリール軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 箔ロウリール軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= '5TK20GN-CW2J+5GN180K';
+			strRt	:= '5TK20GN-CW2J+5GN180K';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';</v>
+			strRt	:= 'OrientalMotor';</v>
       </c>
       <c r="AI3" t="str" cm="1">
         <f t="array" aca="1" ref="AI3:AI202" ca="1">IF(LEN(AH3:AH202),AH3:AH202,"")&amp;IF(LEN(J3:J202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 3"&amp;$B$9&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"END_IF"&amp;$B$9,"")</f>
@@ -4572,15 +4784,15 @@
 	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウリール軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis1】 箔ロウリール軸';
+			strRt	:= '箔ロウリール軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 箔ロウリール軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= '5TK20GN-CW2J+5GN180K';
+			strRt	:= '5TK20GN-CW2J+5GN180K';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';
+			strRt	:= 'OrientalMotor';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ3" t="str" cm="1">
@@ -4590,15 +4802,15 @@
 	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウリール軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis1】 箔ロウリール軸';
+			strRt	:= '箔ロウリール軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 箔ロウリール軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= '5TK20GN-CW2J+5GN180K';
+			strRt	:= '5TK20GN-CW2J+5GN180K';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';
+			strRt	:= 'OrientalMotor';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK3" t="str" cm="1">
@@ -4608,15 +4820,15 @@
 	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウリール軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis1】 箔ロウリール軸';
+			strRt	:= '箔ロウリール軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 箔ロウリール軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= '5TK20GN-CW2J+5GN180K';
+			strRt	:= '5TK20GN-CW2J+5GN180K';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';
+			strRt	:= 'OrientalMotor';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -4691,7 +4903,7 @@
 	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板送り軸';</v>
+			strRt	:= '平板送り軸';</v>
       </c>
       <c r="AC4" t="str">
         <f ca="1"/>
@@ -4699,7 +4911,7 @@
 	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板送り軸';
+			strRt	:= '平板送り軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD4" t="str">
@@ -4708,9 +4920,9 @@
 	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis2】 平板送り軸';</v>
+			strRt	:= '平板送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 平板送り軸';</v>
       </c>
       <c r="AE4" t="str">
         <f ca="1"/>
@@ -4718,9 +4930,9 @@
 	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis2】 平板送り軸';
+			strRt	:= '平板送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 平板送り軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF4" t="str">
@@ -4729,11 +4941,11 @@
 	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis2】 平板送り軸';
+			strRt	:= '平板送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 平板送り軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';</v>
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';</v>
       </c>
       <c r="AG4" t="str">
         <f ca="1"/>
@@ -4741,11 +4953,11 @@
 	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis2】 平板送り軸';
+			strRt	:= '平板送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 平板送り軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH4" t="str">
@@ -4754,13 +4966,13 @@
 	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis2】 平板送り軸';
+			strRt	:= '平板送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 平板送り軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';</v>
+			strRt	:= 'OrientalMotor';</v>
       </c>
       <c r="AI4" t="str">
         <f ca="1"/>
@@ -4768,15 +4980,15 @@
 	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis2】 平板送り軸';
+			strRt	:= '平板送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 平板送り軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';
+			strRt	:= 'OrientalMotor';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ4" t="str">
@@ -4785,15 +4997,15 @@
 	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis2】 平板送り軸';
+			strRt	:= '平板送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 平板送り軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';
+			strRt	:= 'OrientalMotor';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK4" t="str">
@@ -4802,15 +5014,15 @@
 	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis2】 平板送り軸';
+			strRt	:= '平板送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 平板送り軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';
+			strRt	:= 'OrientalMotor';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -4820,7 +5032,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]title_scripts(変数) によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ref="E5:E68" si="0">E4</f>
@@ -4891,7 +5103,7 @@
 	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ送り軸';</v>
+			strRt	:= '箔ロウ送り軸';</v>
       </c>
       <c r="AC5" t="str">
         <f ca="1"/>
@@ -4899,7 +5111,7 @@
 	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ送り軸';
+			strRt	:= '箔ロウ送り軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD5" t="str">
@@ -4908,9 +5120,9 @@
 	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis3】 箔ロウ送り軸';</v>
+			strRt	:= '箔ロウ送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 箔ロウ送り軸';</v>
       </c>
       <c r="AE5" t="str">
         <f ca="1"/>
@@ -4918,9 +5130,9 @@
 	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis3】 箔ロウ送り軸';
+			strRt	:= '箔ロウ送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 箔ロウ送り軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF5" t="str">
@@ -4929,11 +5141,11 @@
 	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis3】 箔ロウ送り軸';
+			strRt	:= '箔ロウ送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 箔ロウ送り軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';</v>
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';</v>
       </c>
       <c r="AG5" t="str">
         <f ca="1"/>
@@ -4941,11 +5153,11 @@
 	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis3】 箔ロウ送り軸';
+			strRt	:= '箔ロウ送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 箔ロウ送り軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH5" t="str">
@@ -4954,13 +5166,13 @@
 	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis3】 箔ロウ送り軸';
+			strRt	:= '箔ロウ送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 箔ロウ送り軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';</v>
+			strRt	:= 'OrientalMotor';</v>
       </c>
       <c r="AI5" t="str">
         <f ca="1"/>
@@ -4968,15 +5180,15 @@
 	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis3】 箔ロウ送り軸';
+			strRt	:= '箔ロウ送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 箔ロウ送り軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';
+			strRt	:= 'OrientalMotor';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ5" t="str">
@@ -4985,15 +5197,15 @@
 	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis3】 箔ロウ送り軸';
+			strRt	:= '箔ロウ送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 箔ロウ送り軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';
+			strRt	:= 'OrientalMotor';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK5" t="str">
@@ -5002,15 +5214,15 @@
 	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis3】 箔ロウ送り軸';
+			strRt	:= '箔ロウ送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 箔ロウ送り軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';
+			strRt	:= 'OrientalMotor';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -5090,7 +5302,7 @@
 	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板送り';</v>
+			strRt	:= '波板送り';</v>
       </c>
       <c r="AC6" t="str">
         <f ca="1"/>
@@ -5098,7 +5310,7 @@
 	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板送り';
+			strRt	:= '波板送り';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD6" t="str">
@@ -5107,9 +5319,9 @@
 	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板送り';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis4】 波板送り';</v>
+			strRt	:= '波板送り';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 波板送り';</v>
       </c>
       <c r="AE6" t="str">
         <f ca="1"/>
@@ -5117,9 +5329,9 @@
 	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板送り';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis4】 波板送り';
+			strRt	:= '波板送り';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 波板送り';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF6" t="str">
@@ -5128,11 +5340,11 @@
 	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板送り';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis4】 波板送り';
+			strRt	:= '波板送り';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 波板送り';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';</v>
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';</v>
       </c>
       <c r="AG6" t="str">
         <f ca="1"/>
@@ -5140,11 +5352,11 @@
 	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板送り';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis4】 波板送り';
+			strRt	:= '波板送り';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 波板送り';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH6" t="str">
@@ -5153,13 +5365,13 @@
 	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板送り';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis4】 波板送り';
+			strRt	:= '波板送り';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 波板送り';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';</v>
+			strRt	:= 'OrientalMotor';</v>
       </c>
       <c r="AI6" t="str">
         <f ca="1"/>
@@ -5167,15 +5379,15 @@
 	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板送り';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis4】 波板送り';
+			strRt	:= '波板送り';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 波板送り';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';
+			strRt	:= 'OrientalMotor';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ6" t="str">
@@ -5184,15 +5396,15 @@
 	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板送り';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis4】 波板送り';
+			strRt	:= '波板送り';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 波板送り';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';
+			strRt	:= 'OrientalMotor';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK6" t="str">
@@ -5201,15 +5413,15 @@
 	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板送り';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis4】 波板送り';
+			strRt	:= '波板送り';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 波板送り';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';
+			strRt	:= 'OrientalMotor';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -5289,7 +5501,7 @@
 	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出上下軸';</v>
+			strRt	:= 'ワーク排出上下軸';</v>
       </c>
       <c r="AC7" t="str">
         <f ca="1"/>
@@ -5297,7 +5509,7 @@
 	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出上下軸';
+			strRt	:= 'ワーク排出上下軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD7" t="str">
@@ -5306,9 +5518,9 @@
 	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis5】 ワーク排出上下軸';</v>
+			strRt	:= 'ワーク排出上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 ワーク排出上下軸';</v>
       </c>
       <c r="AE7" t="str">
         <f ca="1"/>
@@ -5316,9 +5528,9 @@
 	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis5】 ワーク排出上下軸';
+			strRt	:= 'ワーク排出上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 ワーク排出上下軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF7" t="str">
@@ -5327,11 +5539,11 @@
 	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis5】 ワーク排出上下軸';
+			strRt	:= 'ワーク排出上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 ワーク排出上下軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';</v>
+			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';</v>
       </c>
       <c r="AG7" t="str">
         <f ca="1"/>
@@ -5339,11 +5551,11 @@
 	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis5】 ワーク排出上下軸';
+			strRt	:= 'ワーク排出上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 ワーク排出上下軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
+			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH7" t="str">
@@ -5352,13 +5564,13 @@
 	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis5】 ワーク排出上下軸';
+			strRt	:= 'ワーク排出上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 ワーク排出上下軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
+			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';</v>
+			strRt	:= 'IAI';</v>
       </c>
       <c r="AI7" t="str">
         <f ca="1"/>
@@ -5366,15 +5578,15 @@
 	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis5】 ワーク排出上下軸';
+			strRt	:= 'ワーク排出上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 ワーク排出上下軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
+			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ7" t="str">
@@ -5383,15 +5595,15 @@
 	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis5】 ワーク排出上下軸';
+			strRt	:= 'ワーク排出上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 ワーク排出上下軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
+			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK7" t="str">
@@ -5400,15 +5612,15 @@
 	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis5】 ワーク排出上下軸';
+			strRt	:= 'ワーク排出上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 ワーク排出上下軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
+			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -5488,7 +5700,7 @@
 	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '周長測定子上下軸';</v>
+			strRt	:= '周長測定子上下軸';</v>
       </c>
       <c r="AC8" t="str">
         <f ca="1"/>
@@ -5496,7 +5708,7 @@
 	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '周長測定子上下軸';
+			strRt	:= '周長測定子上下軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD8" t="str">
@@ -5505,9 +5717,9 @@
 	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '周長測定子上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis6】 周長測定子上下軸';</v>
+			strRt	:= '周長測定子上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 周長測定子上下軸';</v>
       </c>
       <c r="AE8" t="str">
         <f ca="1"/>
@@ -5515,9 +5727,9 @@
 	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '周長測定子上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis6】 周長測定子上下軸';
+			strRt	:= '周長測定子上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 周長測定子上下軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF8" t="str">
@@ -5526,11 +5738,11 @@
 	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '周長測定子上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis6】 周長測定子上下軸';
+			strRt	:= '周長測定子上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 周長測定子上下軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';</v>
+			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';</v>
       </c>
       <c r="AG8" t="str">
         <f ca="1"/>
@@ -5538,11 +5750,11 @@
 	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '周長測定子上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis6】 周長測定子上下軸';
+			strRt	:= '周長測定子上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 周長測定子上下軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
+			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH8" t="str">
@@ -5551,13 +5763,13 @@
 	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '周長測定子上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis6】 周長測定子上下軸';
+			strRt	:= '周長測定子上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 周長測定子上下軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
+			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';</v>
+			strRt	:= 'IAI';</v>
       </c>
       <c r="AI8" t="str">
         <f ca="1"/>
@@ -5565,15 +5777,15 @@
 	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '周長測定子上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis6】 周長測定子上下軸';
+			strRt	:= '周長測定子上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 周長測定子上下軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
+			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ8" t="str">
@@ -5582,15 +5794,15 @@
 	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '周長測定子上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis6】 周長測定子上下軸';
+			strRt	:= '周長測定子上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 周長測定子上下軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
+			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK8" t="str">
@@ -5599,15 +5811,15 @@
 	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '周長測定子上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis6】 周長測定子上下軸';
+			strRt	:= '周長測定子上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 周長測定子上下軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
+			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -5687,7 +5899,7 @@
 	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク(排出)チャック軸';</v>
+			strRt	:= 'ワーク(排出)チャック軸';</v>
       </c>
       <c r="AC9" t="str">
         <f ca="1"/>
@@ -5695,7 +5907,7 @@
 	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク(排出)チャック軸';
+			strRt	:= 'ワーク(排出)チャック軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD9" t="str">
@@ -5704,9 +5916,9 @@
 	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク(排出)チャック軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis7】 ワーク(排出)チャック軸';</v>
+			strRt	:= 'ワーク(排出)チャック軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 ワーク(排出)チャック軸';</v>
       </c>
       <c r="AE9" t="str">
         <f ca="1"/>
@@ -5714,9 +5926,9 @@
 	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク(排出)チャック軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis7】 ワーク(排出)チャック軸';
+			strRt	:= 'ワーク(排出)チャック軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 ワーク(排出)チャック軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF9" t="str">
@@ -5725,11 +5937,11 @@
 	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク(排出)チャック軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis7】 ワーク(排出)チャック軸';
+			strRt	:= 'ワーク(排出)チャック軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 ワーク(排出)チャック軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';</v>
+			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';</v>
       </c>
       <c r="AG9" t="str">
         <f ca="1"/>
@@ -5737,11 +5949,11 @@
 	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク(排出)チャック軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis7】 ワーク(排出)チャック軸';
+			strRt	:= 'ワーク(排出)チャック軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 ワーク(排出)チャック軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
+			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH9" t="str">
@@ -5750,13 +5962,13 @@
 	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク(排出)チャック軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis7】 ワーク(排出)チャック軸';
+			strRt	:= 'ワーク(排出)チャック軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 ワーク(排出)チャック軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
+			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';</v>
+			strRt	:= 'IAI';</v>
       </c>
       <c r="AI9" t="str">
         <f ca="1"/>
@@ -5764,15 +5976,15 @@
 	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク(排出)チャック軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis7】 ワーク(排出)チャック軸';
+			strRt	:= 'ワーク(排出)チャック軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 ワーク(排出)チャック軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
+			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ9" t="str">
@@ -5781,15 +5993,15 @@
 	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク(排出)チャック軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis7】 ワーク(排出)チャック軸';
+			strRt	:= 'ワーク(排出)チャック軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 ワーク(排出)チャック軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
+			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK9" t="str">
@@ -5798,15 +6010,15 @@
 	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク(排出)チャック軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis7】 ワーク(排出)チャック軸';
+			strRt	:= 'ワーク(排出)チャック軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 ワーク(排出)チャック軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
+			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -5880,7 +6092,7 @@
 	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Y軸：溶接トーチ前後';</v>
+			strRt	:= 'Y軸：溶接トーチ前後';</v>
       </c>
       <c r="AC10" t="str">
         <f ca="1"/>
@@ -5888,7 +6100,7 @@
 	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Y軸：溶接トーチ前後';
+			strRt	:= 'Y軸：溶接トーチ前後';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD10" t="str">
@@ -5897,9 +6109,9 @@
 	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Y軸：溶接トーチ前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis8】 Y軸：溶接トーチ前後';</v>
+			strRt	:= 'Y軸：溶接トーチ前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y軸：溶接トーチ前後';</v>
       </c>
       <c r="AE10" t="str">
         <f ca="1"/>
@@ -5907,9 +6119,9 @@
 	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Y軸：溶接トーチ前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis8】 Y軸：溶接トーチ前後';
+			strRt	:= 'Y軸：溶接トーチ前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF10" t="str">
@@ -5918,11 +6130,11 @@
 	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Y軸：溶接トーチ前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis8】 Y軸：溶接トーチ前後';
+			strRt	:= 'Y軸：溶接トーチ前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';</v>
+			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';</v>
       </c>
       <c r="AG10" t="str">
         <f ca="1"/>
@@ -5930,11 +6142,11 @@
 	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Y軸：溶接トーチ前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis8】 Y軸：溶接トーチ前後';
+			strRt	:= 'Y軸：溶接トーチ前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
+			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH10" t="str">
@@ -5943,13 +6155,13 @@
 	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Y軸：溶接トーチ前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis8】 Y軸：溶接トーチ前後';
+			strRt	:= 'Y軸：溶接トーチ前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
+			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';</v>
+			strRt	:= 'IAI';</v>
       </c>
       <c r="AI10" t="str">
         <f ca="1"/>
@@ -5957,15 +6169,15 @@
 	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Y軸：溶接トーチ前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis8】 Y軸：溶接トーチ前後';
+			strRt	:= 'Y軸：溶接トーチ前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
+			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ10" t="str">
@@ -5974,15 +6186,15 @@
 	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Y軸：溶接トーチ前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis8】 Y軸：溶接トーチ前後';
+			strRt	:= 'Y軸：溶接トーチ前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
+			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK10" t="str">
@@ -5991,15 +6203,15 @@
 	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Y軸：溶接トーチ前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis8】 Y軸：溶接トーチ前後';
+			strRt	:= 'Y軸：溶接トーチ前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
+			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -6073,7 +6285,7 @@
 	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Z軸：溶接トーチ上下';</v>
+			strRt	:= 'Z軸：溶接トーチ上下';</v>
       </c>
       <c r="AC11" t="str">
         <f ca="1"/>
@@ -6081,7 +6293,7 @@
 	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Z軸：溶接トーチ上下';
+			strRt	:= 'Z軸：溶接トーチ上下';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD11" t="str">
@@ -6090,9 +6302,9 @@
 	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Z軸：溶接トーチ上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis9】 Z軸：溶接トーチ上下';</v>
+			strRt	:= 'Z軸：溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z軸：溶接トーチ上下';</v>
       </c>
       <c r="AE11" t="str">
         <f ca="1"/>
@@ -6100,9 +6312,9 @@
 	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Z軸：溶接トーチ上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis9】 Z軸：溶接トーチ上下';
+			strRt	:= 'Z軸：溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF11" t="str">
@@ -6111,11 +6323,11 @@
 	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Z軸：溶接トーチ上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis9】 Z軸：溶接トーチ上下';
+			strRt	:= 'Z軸：溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';</v>
+			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';</v>
       </c>
       <c r="AG11" t="str">
         <f ca="1"/>
@@ -6123,11 +6335,11 @@
 	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Z軸：溶接トーチ上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis9】 Z軸：溶接トーチ上下';
+			strRt	:= 'Z軸：溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
+			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH11" t="str">
@@ -6136,13 +6348,13 @@
 	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Z軸：溶接トーチ上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis9】 Z軸：溶接トーチ上下';
+			strRt	:= 'Z軸：溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
+			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';</v>
+			strRt	:= 'IAI';</v>
       </c>
       <c r="AI11" t="str">
         <f ca="1"/>
@@ -6150,15 +6362,15 @@
 	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Z軸：溶接トーチ上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis9】 Z軸：溶接トーチ上下';
+			strRt	:= 'Z軸：溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
+			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ11" t="str">
@@ -6167,15 +6379,15 @@
 	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Z軸：溶接トーチ上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis9】 Z軸：溶接トーチ上下';
+			strRt	:= 'Z軸：溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
+			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK11" t="str">
@@ -6184,15 +6396,15 @@
 	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Z軸：溶接トーチ上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis9】 Z軸：溶接トーチ上下';
+			strRt	:= 'Z軸：溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
+			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -6266,7 +6478,7 @@
 	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'バインダー供給ポンプモータ';</v>
+			strRt	:= 'バインダー供給ポンプモータ';</v>
       </c>
       <c r="AC12" t="str">
         <f ca="1"/>
@@ -6274,7 +6486,7 @@
 	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'バインダー供給ポンプモータ';
+			strRt	:= 'バインダー供給ポンプモータ';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD12" t="str">
@@ -6283,9 +6495,9 @@
 	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'バインダー供給ポンプモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis10】 バインダー供給ポンプモータ';</v>
+			strRt	:= 'バインダー供給ポンプモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 バインダー供給ポンプモータ';</v>
       </c>
       <c r="AE12" t="str">
         <f ca="1"/>
@@ -6293,9 +6505,9 @@
 	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'バインダー供給ポンプモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis10】 バインダー供給ポンプモータ';
+			strRt	:= 'バインダー供給ポンプモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 バインダー供給ポンプモータ';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF12" t="str">
@@ -6304,11 +6516,11 @@
 	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'バインダー供給ポンプモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis10】 バインダー供給ポンプモータ';
+			strRt	:= 'バインダー供給ポンプモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 バインダー供給ポンプモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';</v>
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AG12" t="str">
         <f ca="1"/>
@@ -6316,11 +6528,11 @@
 	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'バインダー供給ポンプモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis10】 バインダー供給ポンプモータ';
+			strRt	:= 'バインダー供給ポンプモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 バインダー供給ポンプモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH12" t="str">
@@ -6329,13 +6541,13 @@
 	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'バインダー供給ポンプモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis10】 バインダー供給ポンプモータ';
+			strRt	:= 'バインダー供給ポンプモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 バインダー供給ポンプモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';</v>
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI12" t="str">
         <f ca="1"/>
@@ -6343,15 +6555,15 @@
 	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'バインダー供給ポンプモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis10】 バインダー供給ポンプモータ';
+			strRt	:= 'バインダー供給ポンプモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 バインダー供給ポンプモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ12" t="str">
@@ -6360,15 +6572,15 @@
 	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'バインダー供給ポンプモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis10】 バインダー供給ポンプモータ';
+			strRt	:= 'バインダー供給ポンプモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 バインダー供給ポンプモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK12" t="str">
@@ -6377,15 +6589,15 @@
 	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'バインダー供給ポンプモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis10】 バインダー供給ポンプモータ';
+			strRt	:= 'バインダー供給ポンプモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 バインダー供給ポンプモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -6395,492 +6607,492 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AK$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]title_scripts(変数) によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウリール軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis1】 箔ロウリール軸';
+			strRt	:= '箔ロウリール軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 箔ロウリール軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= '5TK20GN-CW2J+5GN180K';
+			strRt	:= '5TK20GN-CW2J+5GN180K';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';
+			strRt	:= 'OrientalMotor';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis2】 平板送り軸';
+			strRt	:= '平板送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 平板送り軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';
+			strRt	:= 'OrientalMotor';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis3】 箔ロウ送り軸';
+			strRt	:= '箔ロウ送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 箔ロウ送り軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';
+			strRt	:= 'OrientalMotor';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板送り';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis4】 波板送り';
+			strRt	:= '波板送り';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 波板送り';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';
+			strRt	:= 'OrientalMotor';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis5】 ワーク排出上下軸';
+			strRt	:= 'ワーク排出上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 ワーク排出上下軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
+			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '周長測定子上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis6】 周長測定子上下軸';
+			strRt	:= '周長測定子上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 周長測定子上下軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
+			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク(排出)チャック軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis7】 ワーク(排出)チャック軸';
+			strRt	:= 'ワーク(排出)チャック軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 ワーク(排出)チャック軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
+			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Y軸：溶接トーチ前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis8】 Y軸：溶接トーチ前後';
+			strRt	:= 'Y軸：溶接トーチ前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
+			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Z軸：溶接トーチ上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis9】 Z軸：溶接トーチ上下';
+			strRt	:= 'Z軸：溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
+			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'バインダー供給ポンプモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis10】 バインダー供給ポンプモータ';
+			strRt	:= 'バインダー供給ポンプモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 バインダー供給ポンプモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis11】 波板リールモータ';
+			strRt	:= '波板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 波板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis12】 平板リールモータ';
+			strRt	:= '平板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 平板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り主軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis13】 巻取り主軸';
+			strRt	:= '巻取り主軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 巻取り主軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'SV3-B075AK';
+			strRt	:= 'SV3-B075AK';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'KEYENCE';
+			strRt	:= 'KEYENCE';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク幅調整軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis14】 ワーク幅調整軸';
+			strRt	:= 'ワーク幅調整軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 ワーク幅調整軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'SV3-M040AK';
+			strRt	:= 'SV3-M040AK';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'KEYENCE';
+			strRt	:= 'KEYENCE';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis15】 Tロール回転軸';
+			strRt	:= 'Tロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 Tロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'M540-402';
+			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ロータユニットXロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis16】 ロータユニットXロール回転軸';
+			strRt	:= 'ロータユニットXロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 ロータユニットXロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'M540-402';
+			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	ELSE
-		ErrCode	:= 2;
+		uiErrCode	:= 2;
 	END_IF;
 //EC
 ELSIF strInfoType = 'EC' THEN
 	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出前後軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【EC1】 ワーク排出前後軸';
+			strRt	:= 'ワーク排出前後軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 ワーク排出前後軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'EC-S4HR-200-7-ML-TMD2';
+			strRt	:= 'EC-S4HR-200-7-ML-TMD2';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	ELSE
-		ErrCode	:= 2;
+		uiErrCode	:= 2;
 	END_IF;
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
 	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り軸芯前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder1】 巻取り軸芯前後';
+			strRt	:= '巻取り軸芯前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 巻取り軸芯前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2A63-200DCZ-M9BVZ';
+			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder2】 Tロール糊付け①';
+			strRt	:= 'Tロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 Tロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDAS16×10-B-R';
+			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder3】 Tロール糊付け②';
+			strRt	:= 'Tロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 Tロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDAS16×10-B-R';
+			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//平板下側補助プレート逃がし
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板下側補助プレート逃がし';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder4】 平板下側補助プレート逃がし';
+			strRt	:= '平板下側補助プレート逃がし';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 平板下側補助プレート逃がし';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
+			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック(ハンド)前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder5】 平板チャック(ハンド)前後';
+			strRt	:= '平板チャック(ハンド)前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'MXQ20-50A-M9BZ';
+			strRt	:= 'MXQ20-50A-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder6】 平板チャック開閉';
+			strRt	:= '平板チャック開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 平板チャック開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'MHF2-16D1-M9BL-X83C1';
+			strRt	:= 'MHF2-16D1-M9BL-X83C1';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= '平板押え上下①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-20DZ-M9BVM';
+			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ押え上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder8】 箔ロウ押え上下';
+			strRt	:= '箔ロウ押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 箔ロウ押え上下';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2D25-20DMZ-M9BM';
+			strRt	:= 'CDQ2D25-20DMZ-M9BM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウカット';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder9】 箔ロウカット';
+			strRt	:= '箔ロウカット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 箔ロウカット';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQSKB16-10DM-M9NWVZ';
+			strRt	:= 'CDQSKB16-10DM-M9NWVZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板押え';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder10】 波板押え';
+			strRt	:= '波板押え';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 波板押え';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-20DZ-M9BVM';
+			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder11】 平板カット刃押出し';
+			strRt	:= '平板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 平板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CD55B32-105-M9BZ';
+			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder12】 平板カット刃開閉';
+			strRt	:= '平板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 平板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-10DMZ-L-A93M';
+			strRt	:= 'CDQ2B25-10DMZ-L-A93M';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder13】 波板カット刃押出し';
+			strRt	:= '波板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 波板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CD55B32-105-M9BZ';
+			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder14】 波板カット刃開閉';
+			strRt	:= '波板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 波板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B40M-15DMZ-M9BZ';
+			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//波板カット補助R
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助R';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder15】 波板カット補助R';
+			strRt	:= '波板カット補助R';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 波板カット補助R';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CXSJM10P-10-M9BL';
+			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助L';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder16】 波板カット補助L';
+			strRt	:= '波板カット補助L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 波板カット補助L';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CXSJM10P-10-M9BL';
+			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder17】 Xロール糊付け①';
+			strRt	:= 'Xロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 Xロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDM2RA20-25Z-M9BWV';
+			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder18】 Xロール糊付け②';
+			strRt	:= 'Xロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 Xロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDM2RA20-25Z-M9BWV';
+			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール平板押付';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder19】 Xロール平板押付';
+			strRt	:= 'Xロール平板押付';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 Xロール平板押付';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= '不明';
+			strRt	:= '不明';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	ELSE
-		ErrCode	:= 2;
+		uiErrCode	:= 2;
 	END_IF;
 ELSE
-	ErrCode	:= 1;
+	uiErrCode	:= 1;
 END_IF;
 //-----ここまで生成script-----</v>
       </c>
@@ -6953,7 +7165,7 @@
 	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板リールモータ';</v>
+			strRt	:= '波板リールモータ';</v>
       </c>
       <c r="AC13" t="str">
         <f ca="1"/>
@@ -6961,7 +7173,7 @@
 	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板リールモータ';
+			strRt	:= '波板リールモータ';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD13" t="str">
@@ -6970,9 +7182,9 @@
 	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis11】 波板リールモータ';</v>
+			strRt	:= '波板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 波板リールモータ';</v>
       </c>
       <c r="AE13" t="str">
         <f ca="1"/>
@@ -6980,9 +7192,9 @@
 	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis11】 波板リールモータ';
+			strRt	:= '波板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 波板リールモータ';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF13" t="str">
@@ -6991,11 +7203,11 @@
 	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis11】 波板リールモータ';
+			strRt	:= '波板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 波板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';</v>
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AG13" t="str">
         <f ca="1"/>
@@ -7003,11 +7215,11 @@
 	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis11】 波板リールモータ';
+			strRt	:= '波板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 波板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH13" t="str">
@@ -7016,13 +7228,13 @@
 	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis11】 波板リールモータ';
+			strRt	:= '波板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 波板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';</v>
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI13" t="str">
         <f ca="1"/>
@@ -7030,15 +7242,15 @@
 	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis11】 波板リールモータ';
+			strRt	:= '波板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 波板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ13" t="str">
@@ -7047,15 +7259,15 @@
 	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis11】 波板リールモータ';
+			strRt	:= '波板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 波板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK13" t="str">
@@ -7064,21 +7276,21 @@
 	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis11】 波板リールモータ';
+			strRt	:= '波板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 波板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B14" t="str">
         <f>IF(LEN(AI1),"●"&amp;B27&amp;CHAR(10)&amp;AI1,"")</f>
@@ -7157,7 +7369,7 @@
 	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板リールモータ';</v>
+			strRt	:= '平板リールモータ';</v>
       </c>
       <c r="AC14" t="str">
         <f ca="1"/>
@@ -7165,7 +7377,7 @@
 	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板リールモータ';
+			strRt	:= '平板リールモータ';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD14" t="str">
@@ -7174,9 +7386,9 @@
 	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis12】 平板リールモータ';</v>
+			strRt	:= '平板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 平板リールモータ';</v>
       </c>
       <c r="AE14" t="str">
         <f ca="1"/>
@@ -7184,9 +7396,9 @@
 	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis12】 平板リールモータ';
+			strRt	:= '平板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 平板リールモータ';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF14" t="str">
@@ -7195,11 +7407,11 @@
 	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis12】 平板リールモータ';
+			strRt	:= '平板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 平板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';</v>
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AG14" t="str">
         <f ca="1"/>
@@ -7207,11 +7419,11 @@
 	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis12】 平板リールモータ';
+			strRt	:= '平板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 平板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH14" t="str">
@@ -7220,13 +7432,13 @@
 	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis12】 平板リールモータ';
+			strRt	:= '平板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 平板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';</v>
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI14" t="str">
         <f ca="1"/>
@@ -7234,15 +7446,15 @@
 	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis12】 平板リールモータ';
+			strRt	:= '平板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 平板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ14" t="str">
@@ -7251,15 +7463,15 @@
 	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis12】 平板リールモータ';
+			strRt	:= '平板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 平板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK14" t="str">
@@ -7268,15 +7480,15 @@
 	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis12】 平板リールモータ';
+			strRt	:= '平板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 平板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -7350,7 +7562,7 @@
 	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り主軸';</v>
+			strRt	:= '巻取り主軸';</v>
       </c>
       <c r="AC15" t="str">
         <f ca="1"/>
@@ -7358,7 +7570,7 @@
 	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り主軸';
+			strRt	:= '巻取り主軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD15" t="str">
@@ -7367,9 +7579,9 @@
 	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り主軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis13】 巻取り主軸';</v>
+			strRt	:= '巻取り主軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 巻取り主軸';</v>
       </c>
       <c r="AE15" t="str">
         <f ca="1"/>
@@ -7377,9 +7589,9 @@
 	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り主軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis13】 巻取り主軸';
+			strRt	:= '巻取り主軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 巻取り主軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF15" t="str">
@@ -7388,11 +7600,11 @@
 	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り主軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis13】 巻取り主軸';
+			strRt	:= '巻取り主軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 巻取り主軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'SV3-B075AK';</v>
+			strRt	:= 'SV3-B075AK';</v>
       </c>
       <c r="AG15" t="str">
         <f ca="1"/>
@@ -7400,11 +7612,11 @@
 	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り主軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis13】 巻取り主軸';
+			strRt	:= '巻取り主軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 巻取り主軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'SV3-B075AK';
+			strRt	:= 'SV3-B075AK';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH15" t="str">
@@ -7413,13 +7625,13 @@
 	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り主軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis13】 巻取り主軸';
+			strRt	:= '巻取り主軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 巻取り主軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'SV3-B075AK';
+			strRt	:= 'SV3-B075AK';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'KEYENCE';</v>
+			strRt	:= 'KEYENCE';</v>
       </c>
       <c r="AI15" t="str">
         <f ca="1"/>
@@ -7427,15 +7639,15 @@
 	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り主軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis13】 巻取り主軸';
+			strRt	:= '巻取り主軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 巻取り主軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'SV3-B075AK';
+			strRt	:= 'SV3-B075AK';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'KEYENCE';
+			strRt	:= 'KEYENCE';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ15" t="str">
@@ -7444,15 +7656,15 @@
 	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り主軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis13】 巻取り主軸';
+			strRt	:= '巻取り主軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 巻取り主軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'SV3-B075AK';
+			strRt	:= 'SV3-B075AK';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'KEYENCE';
+			strRt	:= 'KEYENCE';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK15" t="str">
@@ -7461,15 +7673,15 @@
 	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り主軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis13】 巻取り主軸';
+			strRt	:= '巻取り主軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 巻取り主軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'SV3-B075AK';
+			strRt	:= 'SV3-B075AK';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'KEYENCE';
+			strRt	:= 'KEYENCE';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -7543,7 +7755,7 @@
 	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク幅調整軸';</v>
+			strRt	:= 'ワーク幅調整軸';</v>
       </c>
       <c r="AC16" t="str">
         <f ca="1"/>
@@ -7551,7 +7763,7 @@
 	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク幅調整軸';
+			strRt	:= 'ワーク幅調整軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD16" t="str">
@@ -7560,9 +7772,9 @@
 	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク幅調整軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis14】 ワーク幅調整軸';</v>
+			strRt	:= 'ワーク幅調整軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 ワーク幅調整軸';</v>
       </c>
       <c r="AE16" t="str">
         <f ca="1"/>
@@ -7570,9 +7782,9 @@
 	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク幅調整軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis14】 ワーク幅調整軸';
+			strRt	:= 'ワーク幅調整軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 ワーク幅調整軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF16" t="str">
@@ -7581,11 +7793,11 @@
 	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク幅調整軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis14】 ワーク幅調整軸';
+			strRt	:= 'ワーク幅調整軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 ワーク幅調整軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'SV3-M040AK';</v>
+			strRt	:= 'SV3-M040AK';</v>
       </c>
       <c r="AG16" t="str">
         <f ca="1"/>
@@ -7593,11 +7805,11 @@
 	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク幅調整軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis14】 ワーク幅調整軸';
+			strRt	:= 'ワーク幅調整軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 ワーク幅調整軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'SV3-M040AK';
+			strRt	:= 'SV3-M040AK';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH16" t="str">
@@ -7606,13 +7818,13 @@
 	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク幅調整軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis14】 ワーク幅調整軸';
+			strRt	:= 'ワーク幅調整軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 ワーク幅調整軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'SV3-M040AK';
+			strRt	:= 'SV3-M040AK';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'KEYENCE';</v>
+			strRt	:= 'KEYENCE';</v>
       </c>
       <c r="AI16" t="str">
         <f ca="1"/>
@@ -7620,15 +7832,15 @@
 	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク幅調整軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis14】 ワーク幅調整軸';
+			strRt	:= 'ワーク幅調整軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 ワーク幅調整軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'SV3-M040AK';
+			strRt	:= 'SV3-M040AK';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'KEYENCE';
+			strRt	:= 'KEYENCE';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ16" t="str">
@@ -7637,15 +7849,15 @@
 	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク幅調整軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis14】 ワーク幅調整軸';
+			strRt	:= 'ワーク幅調整軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 ワーク幅調整軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'SV3-M040AK';
+			strRt	:= 'SV3-M040AK';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'KEYENCE';
+			strRt	:= 'KEYENCE';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK16" t="str">
@@ -7654,15 +7866,15 @@
 	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク幅調整軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis14】 ワーク幅調整軸';
+			strRt	:= 'ワーク幅調整軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 ワーク幅調整軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'SV3-M040AK';
+			strRt	:= 'SV3-M040AK';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'KEYENCE';
+			strRt	:= 'KEYENCE';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -7736,7 +7948,7 @@
 	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール回転軸';</v>
+			strRt	:= 'Tロール回転軸';</v>
       </c>
       <c r="AC17" t="str">
         <f ca="1"/>
@@ -7744,7 +7956,7 @@
 	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール回転軸';
+			strRt	:= 'Tロール回転軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD17" t="str">
@@ -7753,9 +7965,9 @@
 	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis15】 Tロール回転軸';</v>
+			strRt	:= 'Tロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 Tロール回転軸';</v>
       </c>
       <c r="AE17" t="str">
         <f ca="1"/>
@@ -7763,9 +7975,9 @@
 	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis15】 Tロール回転軸';
+			strRt	:= 'Tロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 Tロール回転軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF17" t="str">
@@ -7774,11 +7986,11 @@
 	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis15】 Tロール回転軸';
+			strRt	:= 'Tロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 Tロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'M540-402';</v>
+			strRt	:= 'M540-402';</v>
       </c>
       <c r="AG17" t="str">
         <f ca="1"/>
@@ -7786,11 +7998,11 @@
 	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis15】 Tロール回転軸';
+			strRt	:= 'Tロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 Tロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'M540-402';
+			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH17" t="str">
@@ -7799,13 +8011,13 @@
 	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis15】 Tロール回転軸';
+			strRt	:= 'Tロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 Tロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'M540-402';
+			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';</v>
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI17" t="str">
         <f ca="1"/>
@@ -7813,15 +8025,15 @@
 	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis15】 Tロール回転軸';
+			strRt	:= 'Tロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 Tロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'M540-402';
+			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ17" t="str">
@@ -7830,15 +8042,15 @@
 	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis15】 Tロール回転軸';
+			strRt	:= 'Tロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 Tロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'M540-402';
+			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK17" t="str">
@@ -7847,15 +8059,15 @@
 	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis15】 Tロール回転軸';
+			strRt	:= 'Tロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 Tロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'M540-402';
+			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -7929,7 +8141,7 @@
 	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ロータユニットXロール回転軸';</v>
+			strRt	:= 'ロータユニットXロール回転軸';</v>
       </c>
       <c r="AC18" t="str">
         <f ca="1"/>
@@ -7937,7 +8149,7 @@
 	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ロータユニットXロール回転軸';
+			strRt	:= 'ロータユニットXロール回転軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD18" t="str">
@@ -7946,9 +8158,9 @@
 	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ロータユニットXロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis16】 ロータユニットXロール回転軸';</v>
+			strRt	:= 'ロータユニットXロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 ロータユニットXロール回転軸';</v>
       </c>
       <c r="AE18" t="str">
         <f ca="1"/>
@@ -7956,9 +8168,9 @@
 	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ロータユニットXロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis16】 ロータユニットXロール回転軸';
+			strRt	:= 'ロータユニットXロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 ロータユニットXロール回転軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF18" t="str">
@@ -7967,11 +8179,11 @@
 	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ロータユニットXロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis16】 ロータユニットXロール回転軸';
+			strRt	:= 'ロータユニットXロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 ロータユニットXロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'M540-402';</v>
+			strRt	:= 'M540-402';</v>
       </c>
       <c r="AG18" t="str">
         <f ca="1"/>
@@ -7979,11 +8191,11 @@
 	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ロータユニットXロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis16】 ロータユニットXロール回転軸';
+			strRt	:= 'ロータユニットXロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 ロータユニットXロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'M540-402';
+			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH18" t="str">
@@ -7992,13 +8204,13 @@
 	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ロータユニットXロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis16】 ロータユニットXロール回転軸';
+			strRt	:= 'ロータユニットXロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 ロータユニットXロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'M540-402';
+			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';</v>
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI18" t="str">
         <f ca="1"/>
@@ -8006,15 +8218,15 @@
 	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ロータユニットXロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis16】 ロータユニットXロール回転軸';
+			strRt	:= 'ロータユニットXロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 ロータユニットXロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'M540-402';
+			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ18" t="str">
@@ -8023,15 +8235,15 @@
 	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ロータユニットXロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis16】 ロータユニットXロール回転軸';
+			strRt	:= 'ロータユニットXロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 ロータユニットXロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'M540-402';
+			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK18" t="str">
@@ -8040,15 +8252,15 @@
 	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ロータユニットXロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis16】 ロータユニットXロール回転軸';
+			strRt	:= 'ロータユニットXロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 ロータユニットXロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'M540-402';
+			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -8446,7 +8658,7 @@
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -8648,10 +8860,10 @@
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B25" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E25" t="str">
         <f t="shared" si="0"/>
@@ -8752,10 +8964,10 @@
     </row>
     <row r="26" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B26" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E26" t="str">
         <f t="shared" si="0"/>
@@ -8856,10 +9068,10 @@
     </row>
     <row r="27" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B27" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E27" t="str">
         <f t="shared" si="0"/>
@@ -8963,7 +9175,7 @@
         <v>197</v>
       </c>
       <c r="B28" t="s">
-        <v>198</v>
+        <v>255</v>
       </c>
       <c r="E28" t="str">
         <f t="shared" si="0"/>
@@ -9064,10 +9276,10 @@
     </row>
     <row r="29" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B29" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="E29" t="str">
         <f t="shared" si="0"/>
@@ -10435,14 +10647,14 @@
         <f ca="1"/>
         <v xml:space="preserve">
 	ELSE
-		ErrCode	:= 2;
+		uiErrCode	:= 2;
 	END_IF;</v>
       </c>
       <c r="AK42" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 	ELSE
-		ErrCode	:= 2;
+		uiErrCode	:= 2;
 	END_IF;</v>
       </c>
     </row>
@@ -10522,7 +10734,7 @@
 	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出前後軸';</v>
+			strRt	:= 'ワーク排出前後軸';</v>
       </c>
       <c r="AC43" t="str">
         <f ca="1"/>
@@ -10532,7 +10744,7 @@
 	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出前後軸';
+			strRt	:= 'ワーク排出前後軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD43" t="str">
@@ -10543,9 +10755,9 @@
 	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出前後軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【EC1】 ワーク排出前後軸';</v>
+			strRt	:= 'ワーク排出前後軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 ワーク排出前後軸';</v>
       </c>
       <c r="AE43" t="str">
         <f ca="1"/>
@@ -10555,9 +10767,9 @@
 	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出前後軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【EC1】 ワーク排出前後軸';
+			strRt	:= 'ワーク排出前後軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 ワーク排出前後軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF43" t="str">
@@ -10568,11 +10780,11 @@
 	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出前後軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【EC1】 ワーク排出前後軸';
+			strRt	:= 'ワーク排出前後軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 ワーク排出前後軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'EC-S4HR-200-7-ML-TMD2';</v>
+			strRt	:= 'EC-S4HR-200-7-ML-TMD2';</v>
       </c>
       <c r="AG43" t="str">
         <f ca="1"/>
@@ -10582,11 +10794,11 @@
 	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出前後軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【EC1】 ワーク排出前後軸';
+			strRt	:= 'ワーク排出前後軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 ワーク排出前後軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'EC-S4HR-200-7-ML-TMD2';
+			strRt	:= 'EC-S4HR-200-7-ML-TMD2';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH43" t="str">
@@ -10597,13 +10809,13 @@
 	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出前後軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【EC1】 ワーク排出前後軸';
+			strRt	:= 'ワーク排出前後軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 ワーク排出前後軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'EC-S4HR-200-7-ML-TMD2';
+			strRt	:= 'EC-S4HR-200-7-ML-TMD2';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';</v>
+			strRt	:= 'IAI';</v>
       </c>
       <c r="AI43" t="str">
         <f ca="1"/>
@@ -10613,15 +10825,15 @@
 	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出前後軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【EC1】 ワーク排出前後軸';
+			strRt	:= 'ワーク排出前後軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 ワーク排出前後軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'EC-S4HR-200-7-ML-TMD2';
+			strRt	:= 'EC-S4HR-200-7-ML-TMD2';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ43" t="str">
@@ -10632,15 +10844,15 @@
 	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出前後軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【EC1】 ワーク排出前後軸';
+			strRt	:= 'ワーク排出前後軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 ワーク排出前後軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'EC-S4HR-200-7-ML-TMD2';
+			strRt	:= 'EC-S4HR-200-7-ML-TMD2';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK43" t="str">
@@ -10651,15 +10863,15 @@
 	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出前後軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【EC1】 ワーク排出前後軸';
+			strRt	:= 'ワーク排出前後軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 ワーク排出前後軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'EC-S4HR-200-7-ML-TMD2';
+			strRt	:= 'EC-S4HR-200-7-ML-TMD2';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -12520,14 +12732,14 @@
         <f ca="1"/>
         <v xml:space="preserve">
 	ELSE
-		ErrCode	:= 2;
+		uiErrCode	:= 2;
 	END_IF;</v>
       </c>
       <c r="AK62" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 	ELSE
-		ErrCode	:= 2;
+		uiErrCode	:= 2;
 	END_IF;</v>
       </c>
     </row>
@@ -12607,7 +12819,7 @@
 	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り軸芯前後';</v>
+			strRt	:= '巻取り軸芯前後';</v>
       </c>
       <c r="AC63" t="str">
         <f ca="1"/>
@@ -12617,7 +12829,7 @@
 	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り軸芯前後';
+			strRt	:= '巻取り軸芯前後';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD63" t="str">
@@ -12628,9 +12840,9 @@
 	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り軸芯前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder1】 巻取り軸芯前後';</v>
+			strRt	:= '巻取り軸芯前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 巻取り軸芯前後';</v>
       </c>
       <c r="AE63" t="str">
         <f ca="1"/>
@@ -12640,9 +12852,9 @@
 	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り軸芯前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder1】 巻取り軸芯前後';
+			strRt	:= '巻取り軸芯前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 巻取り軸芯前後';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF63" t="str">
@@ -12653,11 +12865,11 @@
 	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り軸芯前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder1】 巻取り軸芯前後';
+			strRt	:= '巻取り軸芯前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 巻取り軸芯前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2A63-200DCZ-M9BVZ';</v>
+			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';</v>
       </c>
       <c r="AG63" t="str">
         <f ca="1"/>
@@ -12667,11 +12879,11 @@
 	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り軸芯前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder1】 巻取り軸芯前後';
+			strRt	:= '巻取り軸芯前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 巻取り軸芯前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2A63-200DCZ-M9BVZ';
+			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH63" t="str">
@@ -12682,13 +12894,13 @@
 	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り軸芯前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder1】 巻取り軸芯前後';
+			strRt	:= '巻取り軸芯前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 巻取り軸芯前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2A63-200DCZ-M9BVZ';
+			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';</v>
+			strRt	:= 'SMC';</v>
       </c>
       <c r="AI63" t="str">
         <f ca="1"/>
@@ -12698,15 +12910,15 @@
 	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り軸芯前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder1】 巻取り軸芯前後';
+			strRt	:= '巻取り軸芯前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 巻取り軸芯前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2A63-200DCZ-M9BVZ';
+			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ63" t="str">
@@ -12717,15 +12929,15 @@
 	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り軸芯前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder1】 巻取り軸芯前後';
+			strRt	:= '巻取り軸芯前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 巻取り軸芯前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2A63-200DCZ-M9BVZ';
+			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK63" t="str">
@@ -12736,15 +12948,15 @@
 	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り軸芯前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder1】 巻取り軸芯前後';
+			strRt	:= '巻取り軸芯前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 巻取り軸芯前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2A63-200DCZ-M9BVZ';
+			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -12761,7 +12973,7 @@
         <v/>
       </c>
       <c r="H64">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I64" t="str">
         <f ca="1"/>
@@ -12818,7 +13030,7 @@
 	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け①';</v>
+			strRt	:= 'Tロール糊付け①';</v>
       </c>
       <c r="AC64" t="str">
         <f ca="1"/>
@@ -12826,7 +13038,7 @@
 	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け①';
+			strRt	:= 'Tロール糊付け①';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD64" t="str">
@@ -12835,9 +13047,9 @@
 	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder2】 Tロール糊付け①';</v>
+			strRt	:= 'Tロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 Tロール糊付け①';</v>
       </c>
       <c r="AE64" t="str">
         <f ca="1"/>
@@ -12845,9 +13057,9 @@
 	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder2】 Tロール糊付け①';
+			strRt	:= 'Tロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 Tロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF64" t="str">
@@ -12856,11 +13068,11 @@
 	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder2】 Tロール糊付け①';
+			strRt	:= 'Tロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 Tロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDAS16×10-B-R';</v>
+			strRt	:= 'CDAS16×10-B-R';</v>
       </c>
       <c r="AG64" t="str">
         <f ca="1"/>
@@ -12868,11 +13080,11 @@
 	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder2】 Tロール糊付け①';
+			strRt	:= 'Tロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 Tロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDAS16×10-B-R';
+			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH64" t="str">
@@ -12881,13 +13093,13 @@
 	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder2】 Tロール糊付け①';
+			strRt	:= 'Tロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 Tロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDAS16×10-B-R';
+			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';</v>
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI64" t="str">
         <f ca="1"/>
@@ -12895,15 +13107,15 @@
 	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder2】 Tロール糊付け①';
+			strRt	:= 'Tロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 Tロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDAS16×10-B-R';
+			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ64" t="str">
@@ -12912,15 +13124,15 @@
 	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder2】 Tロール糊付け①';
+			strRt	:= 'Tロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 Tロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDAS16×10-B-R';
+			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK64" t="str">
@@ -12929,15 +13141,15 @@
 	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder2】 Tロール糊付け①';
+			strRt	:= 'Tロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 Tロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDAS16×10-B-R';
+			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -12954,7 +13166,7 @@
         <v/>
       </c>
       <c r="H65">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I65" t="str">
         <f ca="1"/>
@@ -13011,7 +13223,7 @@
 	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け②';</v>
+			strRt	:= 'Tロール糊付け②';</v>
       </c>
       <c r="AC65" t="str">
         <f ca="1"/>
@@ -13019,7 +13231,7 @@
 	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け②';
+			strRt	:= 'Tロール糊付け②';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD65" t="str">
@@ -13028,9 +13240,9 @@
 	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder3】 Tロール糊付け②';</v>
+			strRt	:= 'Tロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 Tロール糊付け②';</v>
       </c>
       <c r="AE65" t="str">
         <f ca="1"/>
@@ -13038,9 +13250,9 @@
 	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder3】 Tロール糊付け②';
+			strRt	:= 'Tロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 Tロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF65" t="str">
@@ -13049,11 +13261,11 @@
 	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder3】 Tロール糊付け②';
+			strRt	:= 'Tロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 Tロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDAS16×10-B-R';</v>
+			strRt	:= 'CDAS16×10-B-R';</v>
       </c>
       <c r="AG65" t="str">
         <f ca="1"/>
@@ -13061,11 +13273,11 @@
 	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder3】 Tロール糊付け②';
+			strRt	:= 'Tロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 Tロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDAS16×10-B-R';
+			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH65" t="str">
@@ -13074,13 +13286,13 @@
 	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder3】 Tロール糊付け②';
+			strRt	:= 'Tロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 Tロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDAS16×10-B-R';
+			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';</v>
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI65" t="str">
         <f ca="1"/>
@@ -13088,15 +13300,15 @@
 	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder3】 Tロール糊付け②';
+			strRt	:= 'Tロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 Tロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDAS16×10-B-R';
+			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ65" t="str">
@@ -13105,15 +13317,15 @@
 	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder3】 Tロール糊付け②';
+			strRt	:= 'Tロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 Tロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDAS16×10-B-R';
+			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK65" t="str">
@@ -13122,15 +13334,15 @@
 	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder3】 Tロール糊付け②';
+			strRt	:= 'Tロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 Tロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDAS16×10-B-R';
+			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -13147,7 +13359,7 @@
         <v/>
       </c>
       <c r="H66">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I66" t="str">
         <f ca="1"/>
@@ -13204,7 +13416,7 @@
 	//平板下側補助プレート逃がし
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板下側補助プレート逃がし';</v>
+			strRt	:= '平板下側補助プレート逃がし';</v>
       </c>
       <c r="AC66" t="str">
         <f ca="1"/>
@@ -13212,7 +13424,7 @@
 	//平板下側補助プレート逃がし
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板下側補助プレート逃がし';
+			strRt	:= '平板下側補助プレート逃がし';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD66" t="str">
@@ -13221,9 +13433,9 @@
 	//平板下側補助プレート逃がし
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板下側補助プレート逃がし';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder4】 平板下側補助プレート逃がし';</v>
+			strRt	:= '平板下側補助プレート逃がし';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 平板下側補助プレート逃がし';</v>
       </c>
       <c r="AE66" t="str">
         <f ca="1"/>
@@ -13231,9 +13443,9 @@
 	//平板下側補助プレート逃がし
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板下側補助プレート逃がし';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder4】 平板下側補助プレート逃がし';
+			strRt	:= '平板下側補助プレート逃がし';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 平板下側補助プレート逃がし';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF66" t="str">
@@ -13242,11 +13454,11 @@
 	//平板下側補助プレート逃がし
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板下側補助プレート逃がし';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder4】 平板下側補助プレート逃がし';
+			strRt	:= '平板下側補助プレート逃がし';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 平板下側補助プレート逃がし';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDJ2D16-45Z-W-M9BWZ-B';</v>
+			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';</v>
       </c>
       <c r="AG66" t="str">
         <f ca="1"/>
@@ -13254,11 +13466,11 @@
 	//平板下側補助プレート逃がし
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板下側補助プレート逃がし';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder4】 平板下側補助プレート逃がし';
+			strRt	:= '平板下側補助プレート逃がし';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 平板下側補助プレート逃がし';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
+			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH66" t="str">
@@ -13267,13 +13479,13 @@
 	//平板下側補助プレート逃がし
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板下側補助プレート逃がし';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder4】 平板下側補助プレート逃がし';
+			strRt	:= '平板下側補助プレート逃がし';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 平板下側補助プレート逃がし';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
+			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';</v>
+			strRt	:= 'SMC';</v>
       </c>
       <c r="AI66" t="str">
         <f ca="1"/>
@@ -13281,15 +13493,15 @@
 	//平板下側補助プレート逃がし
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板下側補助プレート逃がし';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder4】 平板下側補助プレート逃がし';
+			strRt	:= '平板下側補助プレート逃がし';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 平板下側補助プレート逃がし';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
+			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ66" t="str">
@@ -13298,15 +13510,15 @@
 	//平板下側補助プレート逃がし
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板下側補助プレート逃がし';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder4】 平板下側補助プレート逃がし';
+			strRt	:= '平板下側補助プレート逃がし';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 平板下側補助プレート逃がし';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
+			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK66" t="str">
@@ -13315,15 +13527,15 @@
 	//平板下側補助プレート逃がし
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板下側補助プレート逃がし';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder4】 平板下側補助プレート逃がし';
+			strRt	:= '平板下側補助プレート逃がし';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 平板下側補助プレート逃がし';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
+			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -13340,7 +13552,7 @@
         <v/>
       </c>
       <c r="H67">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I67" t="str">
         <f ca="1"/>
@@ -13397,7 +13609,7 @@
 	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック(ハンド)前後';</v>
+			strRt	:= '平板チャック(ハンド)前後';</v>
       </c>
       <c r="AC67" t="str">
         <f ca="1"/>
@@ -13405,7 +13617,7 @@
 	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック(ハンド)前後';
+			strRt	:= '平板チャック(ハンド)前後';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD67" t="str">
@@ -13414,9 +13626,9 @@
 	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック(ハンド)前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder5】 平板チャック(ハンド)前後';</v>
+			strRt	:= '平板チャック(ハンド)前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';</v>
       </c>
       <c r="AE67" t="str">
         <f ca="1"/>
@@ -13424,9 +13636,9 @@
 	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック(ハンド)前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder5】 平板チャック(ハンド)前後';
+			strRt	:= '平板チャック(ハンド)前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF67" t="str">
@@ -13435,11 +13647,11 @@
 	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック(ハンド)前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder5】 平板チャック(ハンド)前後';
+			strRt	:= '平板チャック(ハンド)前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'MXQ20-50A-M9BZ';</v>
+			strRt	:= 'MXQ20-50A-M9BZ';</v>
       </c>
       <c r="AG67" t="str">
         <f ca="1"/>
@@ -13447,11 +13659,11 @@
 	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック(ハンド)前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder5】 平板チャック(ハンド)前後';
+			strRt	:= '平板チャック(ハンド)前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'MXQ20-50A-M9BZ';
+			strRt	:= 'MXQ20-50A-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH67" t="str">
@@ -13460,13 +13672,13 @@
 	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック(ハンド)前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder5】 平板チャック(ハンド)前後';
+			strRt	:= '平板チャック(ハンド)前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'MXQ20-50A-M9BZ';
+			strRt	:= 'MXQ20-50A-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';</v>
+			strRt	:= 'SMC';</v>
       </c>
       <c r="AI67" t="str">
         <f ca="1"/>
@@ -13474,15 +13686,15 @@
 	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック(ハンド)前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder5】 平板チャック(ハンド)前後';
+			strRt	:= '平板チャック(ハンド)前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'MXQ20-50A-M9BZ';
+			strRt	:= 'MXQ20-50A-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ67" t="str">
@@ -13491,15 +13703,15 @@
 	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック(ハンド)前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder5】 平板チャック(ハンド)前後';
+			strRt	:= '平板チャック(ハンド)前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'MXQ20-50A-M9BZ';
+			strRt	:= 'MXQ20-50A-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK67" t="str">
@@ -13508,15 +13720,15 @@
 	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック(ハンド)前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder5】 平板チャック(ハンド)前後';
+			strRt	:= '平板チャック(ハンド)前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'MXQ20-50A-M9BZ';
+			strRt	:= 'MXQ20-50A-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -13533,7 +13745,7 @@
         <v/>
       </c>
       <c r="H68">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I68" t="str">
         <f ca="1"/>
@@ -13590,7 +13802,7 @@
 	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック開閉';</v>
+			strRt	:= '平板チャック開閉';</v>
       </c>
       <c r="AC68" t="str">
         <f ca="1"/>
@@ -13598,7 +13810,7 @@
 	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック開閉';
+			strRt	:= '平板チャック開閉';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD68" t="str">
@@ -13607,9 +13819,9 @@
 	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder6】 平板チャック開閉';</v>
+			strRt	:= '平板チャック開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 平板チャック開閉';</v>
       </c>
       <c r="AE68" t="str">
         <f ca="1"/>
@@ -13617,9 +13829,9 @@
 	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder6】 平板チャック開閉';
+			strRt	:= '平板チャック開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 平板チャック開閉';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF68" t="str">
@@ -13628,11 +13840,11 @@
 	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder6】 平板チャック開閉';
+			strRt	:= '平板チャック開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 平板チャック開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'MHF2-16D1-M9BL-X83C1';</v>
+			strRt	:= 'MHF2-16D1-M9BL-X83C1';</v>
       </c>
       <c r="AG68" t="str">
         <f ca="1"/>
@@ -13640,11 +13852,11 @@
 	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder6】 平板チャック開閉';
+			strRt	:= '平板チャック開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 平板チャック開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'MHF2-16D1-M9BL-X83C1';
+			strRt	:= 'MHF2-16D1-M9BL-X83C1';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH68" t="str">
@@ -13653,13 +13865,13 @@
 	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder6】 平板チャック開閉';
+			strRt	:= '平板チャック開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 平板チャック開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'MHF2-16D1-M9BL-X83C1';
+			strRt	:= 'MHF2-16D1-M9BL-X83C1';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';</v>
+			strRt	:= 'SMC';</v>
       </c>
       <c r="AI68" t="str">
         <f ca="1"/>
@@ -13667,15 +13879,15 @@
 	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder6】 平板チャック開閉';
+			strRt	:= '平板チャック開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 平板チャック開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'MHF2-16D1-M9BL-X83C1';
+			strRt	:= 'MHF2-16D1-M9BL-X83C1';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ68" t="str">
@@ -13684,15 +13896,15 @@
 	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder6】 平板チャック開閉';
+			strRt	:= '平板チャック開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 平板チャック開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'MHF2-16D1-M9BL-X83C1';
+			strRt	:= 'MHF2-16D1-M9BL-X83C1';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK68" t="str">
@@ -13701,15 +13913,15 @@
 	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder6】 平板チャック開閉';
+			strRt	:= '平板チャック開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 平板チャック開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'MHF2-16D1-M9BL-X83C1';
+			strRt	:= 'MHF2-16D1-M9BL-X83C1';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -13726,7 +13938,7 @@
         <v/>
       </c>
       <c r="H69">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I69" t="str">
         <f ca="1"/>
@@ -13783,7 +13995,7 @@
 	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板押え上下①';</v>
+			strRt	:= '平板押え上下①';</v>
       </c>
       <c r="AC69" t="str">
         <f ca="1"/>
@@ -13791,7 +14003,7 @@
 	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板押え上下①';
+			strRt	:= '平板押え上下①';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD69" t="str">
@@ -13800,9 +14012,9 @@
 	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder7】 平板押え上下①';</v>
+			strRt	:= '平板押え上下①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下①';</v>
       </c>
       <c r="AE69" t="str">
         <f ca="1"/>
@@ -13810,9 +14022,9 @@
 	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= '平板押え上下①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下①';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF69" t="str">
@@ -13821,11 +14033,11 @@
 	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= '平板押え上下①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-20DZ-M9BVM';</v>
+			strRt	:= 'CDQ2B25-20DZ-M9BVM';</v>
       </c>
       <c r="AG69" t="str">
         <f ca="1"/>
@@ -13833,11 +14045,11 @@
 	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= '平板押え上下①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-20DZ-M9BVM';
+			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH69" t="str">
@@ -13846,13 +14058,13 @@
 	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= '平板押え上下①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-20DZ-M9BVM';
+			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';</v>
+			strRt	:= 'SMC';</v>
       </c>
       <c r="AI69" t="str">
         <f ca="1"/>
@@ -13860,15 +14072,15 @@
 	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= '平板押え上下①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-20DZ-M9BVM';
+			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ69" t="str">
@@ -13877,15 +14089,15 @@
 	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= '平板押え上下①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-20DZ-M9BVM';
+			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK69" t="str">
@@ -13894,15 +14106,15 @@
 	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= '平板押え上下①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-20DZ-M9BVM';
+			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -13919,7 +14131,7 @@
         <v/>
       </c>
       <c r="H70">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I70" t="str">
         <f ca="1"/>
@@ -13976,7 +14188,7 @@
 	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ押え上下';</v>
+			strRt	:= '箔ロウ押え上下';</v>
       </c>
       <c r="AC70" t="str">
         <f ca="1"/>
@@ -13984,7 +14196,7 @@
 	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ押え上下';
+			strRt	:= '箔ロウ押え上下';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD70" t="str">
@@ -13993,9 +14205,9 @@
 	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ押え上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder8】 箔ロウ押え上下';</v>
+			strRt	:= '箔ロウ押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 箔ロウ押え上下';</v>
       </c>
       <c r="AE70" t="str">
         <f ca="1"/>
@@ -14003,9 +14215,9 @@
 	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ押え上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder8】 箔ロウ押え上下';
+			strRt	:= '箔ロウ押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 箔ロウ押え上下';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF70" t="str">
@@ -14014,11 +14226,11 @@
 	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ押え上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder8】 箔ロウ押え上下';
+			strRt	:= '箔ロウ押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 箔ロウ押え上下';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2D25-20DMZ-M9BM';</v>
+			strRt	:= 'CDQ2D25-20DMZ-M9BM';</v>
       </c>
       <c r="AG70" t="str">
         <f ca="1"/>
@@ -14026,11 +14238,11 @@
 	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ押え上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder8】 箔ロウ押え上下';
+			strRt	:= '箔ロウ押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 箔ロウ押え上下';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2D25-20DMZ-M9BM';
+			strRt	:= 'CDQ2D25-20DMZ-M9BM';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH70" t="str">
@@ -14039,13 +14251,13 @@
 	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ押え上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder8】 箔ロウ押え上下';
+			strRt	:= '箔ロウ押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 箔ロウ押え上下';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2D25-20DMZ-M9BM';
+			strRt	:= 'CDQ2D25-20DMZ-M9BM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';</v>
+			strRt	:= 'SMC';</v>
       </c>
       <c r="AI70" t="str">
         <f ca="1"/>
@@ -14053,15 +14265,15 @@
 	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ押え上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder8】 箔ロウ押え上下';
+			strRt	:= '箔ロウ押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 箔ロウ押え上下';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2D25-20DMZ-M9BM';
+			strRt	:= 'CDQ2D25-20DMZ-M9BM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ70" t="str">
@@ -14070,15 +14282,15 @@
 	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ押え上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder8】 箔ロウ押え上下';
+			strRt	:= '箔ロウ押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 箔ロウ押え上下';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2D25-20DMZ-M9BM';
+			strRt	:= 'CDQ2D25-20DMZ-M9BM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK70" t="str">
@@ -14087,15 +14299,15 @@
 	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ押え上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder8】 箔ロウ押え上下';
+			strRt	:= '箔ロウ押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 箔ロウ押え上下';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2D25-20DMZ-M9BM';
+			strRt	:= 'CDQ2D25-20DMZ-M9BM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -14112,7 +14324,7 @@
         <v/>
       </c>
       <c r="H71">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I71" t="str">
         <f ca="1"/>
@@ -14169,7 +14381,7 @@
 	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウカット';</v>
+			strRt	:= '箔ロウカット';</v>
       </c>
       <c r="AC71" t="str">
         <f ca="1"/>
@@ -14177,7 +14389,7 @@
 	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウカット';
+			strRt	:= '箔ロウカット';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD71" t="str">
@@ -14186,9 +14398,9 @@
 	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウカット';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder9】 箔ロウカット';</v>
+			strRt	:= '箔ロウカット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 箔ロウカット';</v>
       </c>
       <c r="AE71" t="str">
         <f ca="1"/>
@@ -14196,9 +14408,9 @@
 	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウカット';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder9】 箔ロウカット';
+			strRt	:= '箔ロウカット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 箔ロウカット';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF71" t="str">
@@ -14207,11 +14419,11 @@
 	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウカット';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder9】 箔ロウカット';
+			strRt	:= '箔ロウカット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 箔ロウカット';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQSKB16-10DM-M9NWVZ';</v>
+			strRt	:= 'CDQSKB16-10DM-M9NWVZ';</v>
       </c>
       <c r="AG71" t="str">
         <f ca="1"/>
@@ -14219,11 +14431,11 @@
 	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウカット';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder9】 箔ロウカット';
+			strRt	:= '箔ロウカット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 箔ロウカット';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQSKB16-10DM-M9NWVZ';
+			strRt	:= 'CDQSKB16-10DM-M9NWVZ';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH71" t="str">
@@ -14232,13 +14444,13 @@
 	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウカット';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder9】 箔ロウカット';
+			strRt	:= '箔ロウカット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 箔ロウカット';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQSKB16-10DM-M9NWVZ';
+			strRt	:= 'CDQSKB16-10DM-M9NWVZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';</v>
+			strRt	:= 'SMC';</v>
       </c>
       <c r="AI71" t="str">
         <f ca="1"/>
@@ -14246,15 +14458,15 @@
 	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウカット';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder9】 箔ロウカット';
+			strRt	:= '箔ロウカット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 箔ロウカット';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQSKB16-10DM-M9NWVZ';
+			strRt	:= 'CDQSKB16-10DM-M9NWVZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ71" t="str">
@@ -14263,15 +14475,15 @@
 	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウカット';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder9】 箔ロウカット';
+			strRt	:= '箔ロウカット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 箔ロウカット';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQSKB16-10DM-M9NWVZ';
+			strRt	:= 'CDQSKB16-10DM-M9NWVZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK71" t="str">
@@ -14280,15 +14492,15 @@
 	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウカット';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder9】 箔ロウカット';
+			strRt	:= '箔ロウカット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 箔ロウカット';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQSKB16-10DM-M9NWVZ';
+			strRt	:= 'CDQSKB16-10DM-M9NWVZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -14305,7 +14517,7 @@
         <v/>
       </c>
       <c r="H72">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I72" t="str">
         <f ca="1"/>
@@ -14362,7 +14574,7 @@
 	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板押え';</v>
+			strRt	:= '波板押え';</v>
       </c>
       <c r="AC72" t="str">
         <f ca="1"/>
@@ -14370,7 +14582,7 @@
 	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板押え';
+			strRt	:= '波板押え';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD72" t="str">
@@ -14379,9 +14591,9 @@
 	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板押え';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder10】 波板押え';</v>
+			strRt	:= '波板押え';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 波板押え';</v>
       </c>
       <c r="AE72" t="str">
         <f ca="1"/>
@@ -14389,9 +14601,9 @@
 	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板押え';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder10】 波板押え';
+			strRt	:= '波板押え';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 波板押え';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF72" t="str">
@@ -14400,11 +14612,11 @@
 	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板押え';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder10】 波板押え';
+			strRt	:= '波板押え';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 波板押え';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-20DZ-M9BVM';</v>
+			strRt	:= 'CDQ2B25-20DZ-M9BVM';</v>
       </c>
       <c r="AG72" t="str">
         <f ca="1"/>
@@ -14412,11 +14624,11 @@
 	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板押え';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder10】 波板押え';
+			strRt	:= '波板押え';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 波板押え';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-20DZ-M9BVM';
+			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH72" t="str">
@@ -14425,13 +14637,13 @@
 	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板押え';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder10】 波板押え';
+			strRt	:= '波板押え';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 波板押え';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-20DZ-M9BVM';
+			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';</v>
+			strRt	:= 'SMC';</v>
       </c>
       <c r="AI72" t="str">
         <f ca="1"/>
@@ -14439,15 +14651,15 @@
 	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板押え';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder10】 波板押え';
+			strRt	:= '波板押え';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 波板押え';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-20DZ-M9BVM';
+			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ72" t="str">
@@ -14456,15 +14668,15 @@
 	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板押え';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder10】 波板押え';
+			strRt	:= '波板押え';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 波板押え';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-20DZ-M9BVM';
+			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK72" t="str">
@@ -14473,15 +14685,15 @@
 	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板押え';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder10】 波板押え';
+			strRt	:= '波板押え';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 波板押え';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-20DZ-M9BVM';
+			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -14498,7 +14710,7 @@
         <v/>
       </c>
       <c r="H73">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I73" t="str">
         <f ca="1"/>
@@ -14555,7 +14767,7 @@
 	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃押出し';</v>
+			strRt	:= '平板カット刃押出し';</v>
       </c>
       <c r="AC73" t="str">
         <f ca="1"/>
@@ -14563,7 +14775,7 @@
 	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃押出し';
+			strRt	:= '平板カット刃押出し';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD73" t="str">
@@ -14572,9 +14784,9 @@
 	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder11】 平板カット刃押出し';</v>
+			strRt	:= '平板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 平板カット刃押出し';</v>
       </c>
       <c r="AE73" t="str">
         <f ca="1"/>
@@ -14582,9 +14794,9 @@
 	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder11】 平板カット刃押出し';
+			strRt	:= '平板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 平板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF73" t="str">
@@ -14593,11 +14805,11 @@
 	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder11】 平板カット刃押出し';
+			strRt	:= '平板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 平板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CD55B32-105-M9BZ';</v>
+			strRt	:= 'CD55B32-105-M9BZ';</v>
       </c>
       <c r="AG73" t="str">
         <f ca="1"/>
@@ -14605,11 +14817,11 @@
 	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder11】 平板カット刃押出し';
+			strRt	:= '平板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 平板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CD55B32-105-M9BZ';
+			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH73" t="str">
@@ -14618,13 +14830,13 @@
 	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder11】 平板カット刃押出し';
+			strRt	:= '平板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 平板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CD55B32-105-M9BZ';
+			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';</v>
+			strRt	:= 'SMC';</v>
       </c>
       <c r="AI73" t="str">
         <f ca="1"/>
@@ -14632,15 +14844,15 @@
 	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder11】 平板カット刃押出し';
+			strRt	:= '平板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 平板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CD55B32-105-M9BZ';
+			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ73" t="str">
@@ -14649,15 +14861,15 @@
 	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder11】 平板カット刃押出し';
+			strRt	:= '平板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 平板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CD55B32-105-M9BZ';
+			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK73" t="str">
@@ -14666,15 +14878,15 @@
 	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder11】 平板カット刃押出し';
+			strRt	:= '平板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 平板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CD55B32-105-M9BZ';
+			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -14691,7 +14903,7 @@
         <v/>
       </c>
       <c r="H74">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I74" t="str">
         <f ca="1"/>
@@ -14748,7 +14960,7 @@
 	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃開閉';</v>
+			strRt	:= '平板カット刃開閉';</v>
       </c>
       <c r="AC74" t="str">
         <f ca="1"/>
@@ -14756,7 +14968,7 @@
 	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃開閉';
+			strRt	:= '平板カット刃開閉';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD74" t="str">
@@ -14765,9 +14977,9 @@
 	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder12】 平板カット刃開閉';</v>
+			strRt	:= '平板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 平板カット刃開閉';</v>
       </c>
       <c r="AE74" t="str">
         <f ca="1"/>
@@ -14775,9 +14987,9 @@
 	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder12】 平板カット刃開閉';
+			strRt	:= '平板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 平板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF74" t="str">
@@ -14786,11 +14998,11 @@
 	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder12】 平板カット刃開閉';
+			strRt	:= '平板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 平板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-10DMZ-L-A93M';</v>
+			strRt	:= 'CDQ2B25-10DMZ-L-A93M';</v>
       </c>
       <c r="AG74" t="str">
         <f ca="1"/>
@@ -14798,11 +15010,11 @@
 	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder12】 平板カット刃開閉';
+			strRt	:= '平板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 平板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-10DMZ-L-A93M';
+			strRt	:= 'CDQ2B25-10DMZ-L-A93M';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH74" t="str">
@@ -14811,13 +15023,13 @@
 	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder12】 平板カット刃開閉';
+			strRt	:= '平板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 平板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-10DMZ-L-A93M';
+			strRt	:= 'CDQ2B25-10DMZ-L-A93M';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';</v>
+			strRt	:= 'SMC';</v>
       </c>
       <c r="AI74" t="str">
         <f ca="1"/>
@@ -14825,15 +15037,15 @@
 	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder12】 平板カット刃開閉';
+			strRt	:= '平板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 平板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-10DMZ-L-A93M';
+			strRt	:= 'CDQ2B25-10DMZ-L-A93M';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ74" t="str">
@@ -14842,15 +15054,15 @@
 	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder12】 平板カット刃開閉';
+			strRt	:= '平板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 平板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-10DMZ-L-A93M';
+			strRt	:= 'CDQ2B25-10DMZ-L-A93M';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK74" t="str">
@@ -14859,15 +15071,15 @@
 	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder12】 平板カット刃開閉';
+			strRt	:= '平板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 平板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-10DMZ-L-A93M';
+			strRt	:= 'CDQ2B25-10DMZ-L-A93M';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -14884,7 +15096,7 @@
         <v/>
       </c>
       <c r="H75">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I75" t="str">
         <f ca="1"/>
@@ -14941,7 +15153,7 @@
 	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃押出し';</v>
+			strRt	:= '波板カット刃押出し';</v>
       </c>
       <c r="AC75" t="str">
         <f ca="1"/>
@@ -14949,7 +15161,7 @@
 	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃押出し';
+			strRt	:= '波板カット刃押出し';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD75" t="str">
@@ -14958,9 +15170,9 @@
 	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder13】 波板カット刃押出し';</v>
+			strRt	:= '波板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 波板カット刃押出し';</v>
       </c>
       <c r="AE75" t="str">
         <f ca="1"/>
@@ -14968,9 +15180,9 @@
 	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder13】 波板カット刃押出し';
+			strRt	:= '波板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 波板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF75" t="str">
@@ -14979,11 +15191,11 @@
 	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder13】 波板カット刃押出し';
+			strRt	:= '波板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 波板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CD55B32-105-M9BZ';</v>
+			strRt	:= 'CD55B32-105-M9BZ';</v>
       </c>
       <c r="AG75" t="str">
         <f ca="1"/>
@@ -14991,11 +15203,11 @@
 	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder13】 波板カット刃押出し';
+			strRt	:= '波板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 波板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CD55B32-105-M9BZ';
+			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH75" t="str">
@@ -15004,13 +15216,13 @@
 	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder13】 波板カット刃押出し';
+			strRt	:= '波板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 波板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CD55B32-105-M9BZ';
+			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';</v>
+			strRt	:= 'SMC';</v>
       </c>
       <c r="AI75" t="str">
         <f ca="1"/>
@@ -15018,15 +15230,15 @@
 	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder13】 波板カット刃押出し';
+			strRt	:= '波板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 波板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CD55B32-105-M9BZ';
+			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ75" t="str">
@@ -15035,15 +15247,15 @@
 	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder13】 波板カット刃押出し';
+			strRt	:= '波板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 波板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CD55B32-105-M9BZ';
+			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK75" t="str">
@@ -15052,15 +15264,15 @@
 	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder13】 波板カット刃押出し';
+			strRt	:= '波板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 波板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CD55B32-105-M9BZ';
+			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -15077,7 +15289,7 @@
         <v/>
       </c>
       <c r="H76">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I76" t="str">
         <f ca="1"/>
@@ -15134,7 +15346,7 @@
 	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃開閉';</v>
+			strRt	:= '波板カット刃開閉';</v>
       </c>
       <c r="AC76" t="str">
         <f ca="1"/>
@@ -15142,7 +15354,7 @@
 	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃開閉';
+			strRt	:= '波板カット刃開閉';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD76" t="str">
@@ -15151,9 +15363,9 @@
 	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder14】 波板カット刃開閉';</v>
+			strRt	:= '波板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 波板カット刃開閉';</v>
       </c>
       <c r="AE76" t="str">
         <f ca="1"/>
@@ -15161,9 +15373,9 @@
 	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder14】 波板カット刃開閉';
+			strRt	:= '波板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 波板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF76" t="str">
@@ -15172,11 +15384,11 @@
 	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder14】 波板カット刃開閉';
+			strRt	:= '波板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 波板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B40M-15DMZ-M9BZ';</v>
+			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';</v>
       </c>
       <c r="AG76" t="str">
         <f ca="1"/>
@@ -15184,11 +15396,11 @@
 	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder14】 波板カット刃開閉';
+			strRt	:= '波板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 波板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B40M-15DMZ-M9BZ';
+			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH76" t="str">
@@ -15197,13 +15409,13 @@
 	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder14】 波板カット刃開閉';
+			strRt	:= '波板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 波板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B40M-15DMZ-M9BZ';
+			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';</v>
+			strRt	:= 'SMC';</v>
       </c>
       <c r="AI76" t="str">
         <f ca="1"/>
@@ -15211,15 +15423,15 @@
 	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder14】 波板カット刃開閉';
+			strRt	:= '波板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 波板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B40M-15DMZ-M9BZ';
+			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ76" t="str">
@@ -15228,15 +15440,15 @@
 	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder14】 波板カット刃開閉';
+			strRt	:= '波板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 波板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B40M-15DMZ-M9BZ';
+			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK76" t="str">
@@ -15245,15 +15457,15 @@
 	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder14】 波板カット刃開閉';
+			strRt	:= '波板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 波板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B40M-15DMZ-M9BZ';
+			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -15327,7 +15539,7 @@
 	//波板カット補助R
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助R';</v>
+			strRt	:= '波板カット補助R';</v>
       </c>
       <c r="AC77" t="str">
         <f ca="1"/>
@@ -15335,7 +15547,7 @@
 	//波板カット補助R
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助R';
+			strRt	:= '波板カット補助R';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD77" t="str">
@@ -15344,9 +15556,9 @@
 	//波板カット補助R
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助R';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder15】 波板カット補助R';</v>
+			strRt	:= '波板カット補助R';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 波板カット補助R';</v>
       </c>
       <c r="AE77" t="str">
         <f ca="1"/>
@@ -15354,9 +15566,9 @@
 	//波板カット補助R
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助R';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder15】 波板カット補助R';
+			strRt	:= '波板カット補助R';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 波板カット補助R';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF77" t="str">
@@ -15365,11 +15577,11 @@
 	//波板カット補助R
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助R';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder15】 波板カット補助R';
+			strRt	:= '波板カット補助R';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 波板カット補助R';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CXSJM10P-10-M9BL';</v>
+			strRt	:= 'CXSJM10P-10-M9BL';</v>
       </c>
       <c r="AG77" t="str">
         <f ca="1"/>
@@ -15377,11 +15589,11 @@
 	//波板カット補助R
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助R';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder15】 波板カット補助R';
+			strRt	:= '波板カット補助R';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 波板カット補助R';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CXSJM10P-10-M9BL';
+			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH77" t="str">
@@ -15390,13 +15602,13 @@
 	//波板カット補助R
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助R';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder15】 波板カット補助R';
+			strRt	:= '波板カット補助R';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 波板カット補助R';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CXSJM10P-10-M9BL';
+			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';</v>
+			strRt	:= 'SMC';</v>
       </c>
       <c r="AI77" t="str">
         <f ca="1"/>
@@ -15404,15 +15616,15 @@
 	//波板カット補助R
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助R';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder15】 波板カット補助R';
+			strRt	:= '波板カット補助R';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 波板カット補助R';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CXSJM10P-10-M9BL';
+			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ77" t="str">
@@ -15421,15 +15633,15 @@
 	//波板カット補助R
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助R';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder15】 波板カット補助R';
+			strRt	:= '波板カット補助R';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 波板カット補助R';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CXSJM10P-10-M9BL';
+			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK77" t="str">
@@ -15438,15 +15650,15 @@
 	//波板カット補助R
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助R';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder15】 波板カット補助R';
+			strRt	:= '波板カット補助R';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 波板カット補助R';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CXSJM10P-10-M9BL';
+			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -15520,7 +15732,7 @@
 	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助L';</v>
+			strRt	:= '波板カット補助L';</v>
       </c>
       <c r="AC78" t="str">
         <f ca="1"/>
@@ -15528,7 +15740,7 @@
 	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助L';
+			strRt	:= '波板カット補助L';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD78" t="str">
@@ -15537,9 +15749,9 @@
 	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助L';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder16】 波板カット補助L';</v>
+			strRt	:= '波板カット補助L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 波板カット補助L';</v>
       </c>
       <c r="AE78" t="str">
         <f ca="1"/>
@@ -15547,9 +15759,9 @@
 	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助L';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder16】 波板カット補助L';
+			strRt	:= '波板カット補助L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 波板カット補助L';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF78" t="str">
@@ -15558,11 +15770,11 @@
 	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助L';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder16】 波板カット補助L';
+			strRt	:= '波板カット補助L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 波板カット補助L';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CXSJM10P-10-M9BL';</v>
+			strRt	:= 'CXSJM10P-10-M9BL';</v>
       </c>
       <c r="AG78" t="str">
         <f ca="1"/>
@@ -15570,11 +15782,11 @@
 	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助L';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder16】 波板カット補助L';
+			strRt	:= '波板カット補助L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 波板カット補助L';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CXSJM10P-10-M9BL';
+			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH78" t="str">
@@ -15583,13 +15795,13 @@
 	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助L';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder16】 波板カット補助L';
+			strRt	:= '波板カット補助L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 波板カット補助L';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CXSJM10P-10-M9BL';
+			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';</v>
+			strRt	:= 'SMC';</v>
       </c>
       <c r="AI78" t="str">
         <f ca="1"/>
@@ -15597,15 +15809,15 @@
 	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助L';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder16】 波板カット補助L';
+			strRt	:= '波板カット補助L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 波板カット補助L';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CXSJM10P-10-M9BL';
+			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ78" t="str">
@@ -15614,15 +15826,15 @@
 	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助L';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder16】 波板カット補助L';
+			strRt	:= '波板カット補助L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 波板カット補助L';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CXSJM10P-10-M9BL';
+			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK78" t="str">
@@ -15631,15 +15843,15 @@
 	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助L';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder16】 波板カット補助L';
+			strRt	:= '波板カット補助L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 波板カット補助L';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CXSJM10P-10-M9BL';
+			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -15713,7 +15925,7 @@
 	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け①';</v>
+			strRt	:= 'Xロール糊付け①';</v>
       </c>
       <c r="AC79" t="str">
         <f ca="1"/>
@@ -15721,7 +15933,7 @@
 	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け①';
+			strRt	:= 'Xロール糊付け①';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD79" t="str">
@@ -15730,9 +15942,9 @@
 	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder17】 Xロール糊付け①';</v>
+			strRt	:= 'Xロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 Xロール糊付け①';</v>
       </c>
       <c r="AE79" t="str">
         <f ca="1"/>
@@ -15740,9 +15952,9 @@
 	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder17】 Xロール糊付け①';
+			strRt	:= 'Xロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 Xロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF79" t="str">
@@ -15751,11 +15963,11 @@
 	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder17】 Xロール糊付け①';
+			strRt	:= 'Xロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 Xロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDM2RA20-25Z-M9BWV';</v>
+			strRt	:= 'CDM2RA20-25Z-M9BWV';</v>
       </c>
       <c r="AG79" t="str">
         <f ca="1"/>
@@ -15763,11 +15975,11 @@
 	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder17】 Xロール糊付け①';
+			strRt	:= 'Xロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 Xロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDM2RA20-25Z-M9BWV';
+			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH79" t="str">
@@ -15776,13 +15988,13 @@
 	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder17】 Xロール糊付け①';
+			strRt	:= 'Xロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 Xロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDM2RA20-25Z-M9BWV';
+			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';</v>
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI79" t="str">
         <f ca="1"/>
@@ -15790,15 +16002,15 @@
 	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder17】 Xロール糊付け①';
+			strRt	:= 'Xロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 Xロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDM2RA20-25Z-M9BWV';
+			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ79" t="str">
@@ -15807,15 +16019,15 @@
 	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder17】 Xロール糊付け①';
+			strRt	:= 'Xロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 Xロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDM2RA20-25Z-M9BWV';
+			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK79" t="str">
@@ -15824,15 +16036,15 @@
 	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder17】 Xロール糊付け①';
+			strRt	:= 'Xロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 Xロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDM2RA20-25Z-M9BWV';
+			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -15906,7 +16118,7 @@
 	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け②';</v>
+			strRt	:= 'Xロール糊付け②';</v>
       </c>
       <c r="AC80" t="str">
         <f ca="1"/>
@@ -15914,7 +16126,7 @@
 	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け②';
+			strRt	:= 'Xロール糊付け②';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD80" t="str">
@@ -15923,9 +16135,9 @@
 	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder18】 Xロール糊付け②';</v>
+			strRt	:= 'Xロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 Xロール糊付け②';</v>
       </c>
       <c r="AE80" t="str">
         <f ca="1"/>
@@ -15933,9 +16145,9 @@
 	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder18】 Xロール糊付け②';
+			strRt	:= 'Xロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 Xロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF80" t="str">
@@ -15944,11 +16156,11 @@
 	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder18】 Xロール糊付け②';
+			strRt	:= 'Xロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 Xロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDM2RA20-25Z-M9BWV';</v>
+			strRt	:= 'CDM2RA20-25Z-M9BWV';</v>
       </c>
       <c r="AG80" t="str">
         <f ca="1"/>
@@ -15956,11 +16168,11 @@
 	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder18】 Xロール糊付け②';
+			strRt	:= 'Xロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 Xロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDM2RA20-25Z-M9BWV';
+			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH80" t="str">
@@ -15969,13 +16181,13 @@
 	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder18】 Xロール糊付け②';
+			strRt	:= 'Xロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 Xロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDM2RA20-25Z-M9BWV';
+			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';</v>
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI80" t="str">
         <f ca="1"/>
@@ -15983,15 +16195,15 @@
 	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder18】 Xロール糊付け②';
+			strRt	:= 'Xロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 Xロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDM2RA20-25Z-M9BWV';
+			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ80" t="str">
@@ -16000,15 +16212,15 @@
 	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder18】 Xロール糊付け②';
+			strRt	:= 'Xロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 Xロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDM2RA20-25Z-M9BWV';
+			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK80" t="str">
@@ -16017,15 +16229,15 @@
 	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder18】 Xロール糊付け②';
+			strRt	:= 'Xロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 Xロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDM2RA20-25Z-M9BWV';
+			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -16099,7 +16311,7 @@
 	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール平板押付';</v>
+			strRt	:= 'Xロール平板押付';</v>
       </c>
       <c r="AC81" t="str">
         <f ca="1"/>
@@ -16107,7 +16319,7 @@
 	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール平板押付';
+			strRt	:= 'Xロール平板押付';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD81" t="str">
@@ -16116,9 +16328,9 @@
 	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール平板押付';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder19】 Xロール平板押付';</v>
+			strRt	:= 'Xロール平板押付';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 Xロール平板押付';</v>
       </c>
       <c r="AE81" t="str">
         <f ca="1"/>
@@ -16126,9 +16338,9 @@
 	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール平板押付';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder19】 Xロール平板押付';
+			strRt	:= 'Xロール平板押付';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 Xロール平板押付';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF81" t="str">
@@ -16137,11 +16349,11 @@
 	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール平板押付';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder19】 Xロール平板押付';
+			strRt	:= 'Xロール平板押付';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 Xロール平板押付';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= '不明';</v>
+			strRt	:= '不明';</v>
       </c>
       <c r="AG81" t="str">
         <f ca="1"/>
@@ -16149,11 +16361,11 @@
 	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール平板押付';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder19】 Xロール平板押付';
+			strRt	:= 'Xロール平板押付';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 Xロール平板押付';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= '不明';
+			strRt	:= '不明';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH81" t="str">
@@ -16162,13 +16374,13 @@
 	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール平板押付';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder19】 Xロール平板押付';
+			strRt	:= 'Xロール平板押付';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 Xロール平板押付';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= '不明';
+			strRt	:= '不明';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';</v>
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI81" t="str">
         <f ca="1"/>
@@ -16176,15 +16388,15 @@
 	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール平板押付';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder19】 Xロール平板押付';
+			strRt	:= 'Xロール平板押付';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 Xロール平板押付';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= '不明';
+			strRt	:= '不明';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AJ81" t="str">
@@ -16193,15 +16405,15 @@
 	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール平板押付';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder19】 Xロール平板押付';
+			strRt	:= 'Xロール平板押付';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 Xロール平板押付';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= '不明';
+			strRt	:= '不明';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
       <c r="AK81" t="str">
@@ -16210,15 +16422,15 @@
 	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール平板押付';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder19】 Xロール平板押付';
+			strRt	:= 'Xロール平板押付';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 Xロール平板押付';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= '不明';
+			strRt	:= '不明';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
     </row>
@@ -28075,506 +28287,506 @@
         <f ca="1"/>
         <v xml:space="preserve">
 	ELSE
-		ErrCode	:= 2;
+		uiErrCode	:= 2;
 	END_IF;</v>
       </c>
       <c r="AK202" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 	ELSE
-		ErrCode	:= 2;
+		uiErrCode	:= 2;
 	END_IF;</v>
       </c>
     </row>
     <row r="205" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="AK205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AK$3:AK$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]title_scripts(変数) によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウリール軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis1】 箔ロウリール軸';
+			strRt	:= '箔ロウリール軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 箔ロウリール軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= '5TK20GN-CW2J+5GN180K';
+			strRt	:= '5TK20GN-CW2J+5GN180K';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';
+			strRt	:= 'OrientalMotor';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis2】 平板送り軸';
+			strRt	:= '平板送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 平板送り軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';
+			strRt	:= 'OrientalMotor';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis3】 箔ロウ送り軸';
+			strRt	:= '箔ロウ送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 箔ロウ送り軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';
+			strRt	:= 'OrientalMotor';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板送り';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis4】 波板送り';
+			strRt	:= '波板送り';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 波板送り';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
+			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'OrientalMotor';
+			strRt	:= 'OrientalMotor';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis5】 ワーク排出上下軸';
+			strRt	:= 'ワーク排出上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 ワーク排出上下軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
+			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '周長測定子上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis6】 周長測定子上下軸';
+			strRt	:= '周長測定子上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 周長測定子上下軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
+			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク(排出)チャック軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis7】 ワーク(排出)チャック軸';
+			strRt	:= 'ワーク(排出)チャック軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 ワーク(排出)チャック軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
+			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Y軸：溶接トーチ前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis8】 Y軸：溶接トーチ前後';
+			strRt	:= 'Y軸：溶接トーチ前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
+			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Z軸：溶接トーチ上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis9】 Z軸：溶接トーチ上下';
+			strRt	:= 'Z軸：溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
+			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'バインダー供給ポンプモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis10】 バインダー供給ポンプモータ';
+			strRt	:= 'バインダー供給ポンプモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 バインダー供給ポンプモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis11】 波板リールモータ';
+			strRt	:= '波板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 波板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis12】 平板リールモータ';
+			strRt	:= '平板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 平板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り主軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis13】 巻取り主軸';
+			strRt	:= '巻取り主軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 巻取り主軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'SV3-B075AK';
+			strRt	:= 'SV3-B075AK';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'KEYENCE';
+			strRt	:= 'KEYENCE';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク幅調整軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis14】 ワーク幅調整軸';
+			strRt	:= 'ワーク幅調整軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 ワーク幅調整軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'SV3-M040AK';
+			strRt	:= 'SV3-M040AK';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'KEYENCE';
+			strRt	:= 'KEYENCE';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis15】 Tロール回転軸';
+			strRt	:= 'Tロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 Tロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'M540-402';
+			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ロータユニットXロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【axis16】 ロータユニットXロール回転軸';
+			strRt	:= 'ロータユニットXロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 ロータユニットXロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'M540-402';
+			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	ELSE
-		ErrCode	:= 2;
+		uiErrCode	:= 2;
 	END_IF;
 //EC
 ELSIF strInfoType = 'EC' THEN
 	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'ワーク排出前後軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【EC1】 ワーク排出前後軸';
+			strRt	:= 'ワーク排出前後軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 ワーク排出前後軸';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'EC-S4HR-200-7-ML-TMD2';
+			strRt	:= 'EC-S4HR-200-7-ML-TMD2';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'IAI';
+			strRt	:= 'IAI';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	ELSE
-		ErrCode	:= 2;
+		uiErrCode	:= 2;
 	END_IF;
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
 	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '巻取り軸芯前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder1】 巻取り軸芯前後';
+			strRt	:= '巻取り軸芯前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 巻取り軸芯前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2A63-200DCZ-M9BVZ';
+			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder2】 Tロール糊付け①';
+			strRt	:= 'Tロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 Tロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDAS16×10-B-R';
+			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Tロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder3】 Tロール糊付け②';
+			strRt	:= 'Tロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 Tロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDAS16×10-B-R';
+			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//平板下側補助プレート逃がし
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板下側補助プレート逃がし';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder4】 平板下側補助プレート逃がし';
+			strRt	:= '平板下側補助プレート逃がし';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 平板下側補助プレート逃がし';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
+			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック(ハンド)前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder5】 平板チャック(ハンド)前後';
+			strRt	:= '平板チャック(ハンド)前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'MXQ20-50A-M9BZ';
+			strRt	:= 'MXQ20-50A-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板チャック開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder6】 平板チャック開閉';
+			strRt	:= '平板チャック開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 平板チャック開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'MHF2-16D1-M9BL-X83C1';
+			strRt	:= 'MHF2-16D1-M9BL-X83C1';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= '平板押え上下①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-20DZ-M9BVM';
+			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウ押え上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder8】 箔ロウ押え上下';
+			strRt	:= '箔ロウ押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 箔ロウ押え上下';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2D25-20DMZ-M9BM';
+			strRt	:= 'CDQ2D25-20DMZ-M9BM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '箔ロウカット';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder9】 箔ロウカット';
+			strRt	:= '箔ロウカット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 箔ロウカット';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQSKB16-10DM-M9NWVZ';
+			strRt	:= 'CDQSKB16-10DM-M9NWVZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板押え';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder10】 波板押え';
+			strRt	:= '波板押え';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 波板押え';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-20DZ-M9BVM';
+			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder11】 平板カット刃押出し';
+			strRt	:= '平板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 平板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CD55B32-105-M9BZ';
+			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '平板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder12】 平板カット刃開閉';
+			strRt	:= '平板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 平板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B25-10DMZ-L-A93M';
+			strRt	:= 'CDQ2B25-10DMZ-L-A93M';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder13】 波板カット刃押出し';
+			strRt	:= '波板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 波板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CD55B32-105-M9BZ';
+			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder14】 波板カット刃開閉';
+			strRt	:= '波板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 波板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDQ2B40M-15DMZ-M9BZ';
+			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//波板カット補助R
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助R';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder15】 波板カット補助R';
+			strRt	:= '波板カット補助R';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 波板カット補助R';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CXSJM10P-10-M9BL';
+			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= '波板カット補助L';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder16】 波板カット補助L';
+			strRt	:= '波板カット補助L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 波板カット補助L';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CXSJM10P-10-M9BL';
+			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'SMC';
+			strRt	:= 'SMC';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder17】 Xロール糊付け①';
+			strRt	:= 'Xロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 Xロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDM2RA20-25Z-M9BWV';
+			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder18】 Xロール糊付け②';
+			strRt	:= 'Xロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 Xロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= 'CDM2RA20-25Z-M9BWV';
+			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			Rt	:= 'Xロール平板押付';
-		ELSIF strInfoKey = 'index_name' THEN
-			Rt	:= '【cylinder19】 Xロール平板押付';
+			strRt	:= 'Xロール平板押付';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 Xロール平板押付';
 		ELSIF strInfoKey = 'model' THEN
-			Rt	:= '不明';
+			strRt	:= '不明';
 		ELSIF strInfoKey = 'mf' THEN
-			Rt	:= 'unknown';
+			strRt	:= 'unknown';
 		ELSE
-			ErrCode	:= 3;
+			uiErrCode	:= 3;
 		END_IF;
 	ELSE
-		ErrCode	:= 2;
+		uiErrCode	:= 2;
 	END_IF;
 ELSE
-	ErrCode	:= 1;
+	uiErrCode	:= 1;
 END_IF;
 //-----ここまで生成script-----</v>
       </c>

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19506EF2-EB96-4DDA-A01F-B3B7EEF85D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582438E4-114A-4731-80D4-03825A44883D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -2926,169 +2926,145 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="7">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C19" s="7">
-        <v>5</v>
-      </c>
-      <c r="D19" s="8">
-        <v>5</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>93</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
       <c r="F19" s="8" t="s">
-        <v>154</v>
+        <v>217</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>174</v>
+        <v>250</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="L19" s="8">
-        <v>1</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
       <c r="M19" s="10"/>
       <c r="N19" s="10">
         <v>0</v>
       </c>
       <c r="O19" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P19" s="10"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="7">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C20" s="7">
-        <v>11</v>
-      </c>
-      <c r="D20" s="12">
-        <v>9</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="I20" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="K20" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="L20" s="13">
-        <v>1</v>
-      </c>
-      <c r="M20" s="25"/>
-      <c r="N20" s="25">
+        <v>3</v>
+      </c>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10">
         <v>0</v>
       </c>
-      <c r="O20" s="25">
-        <v>2</v>
+      <c r="O20" s="10">
+        <v>6</v>
       </c>
       <c r="P20" s="10"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="7">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C21" s="7">
-        <v>13</v>
-      </c>
-      <c r="D21" s="12">
-        <v>11</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="G21" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="I21" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="J21" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="K21" s="12" t="s">
+      <c r="D21" s="8">
+        <v>2</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="L21" s="13">
+      <c r="L21" s="8">
         <v>1</v>
       </c>
-      <c r="M21" s="25"/>
-      <c r="N21" s="25">
+      <c r="M21" s="10"/>
+      <c r="N21" s="10">
         <v>0</v>
       </c>
-      <c r="O21" s="25">
-        <v>3</v>
+      <c r="O21" s="10">
+        <v>7</v>
       </c>
       <c r="P21" s="10"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C22" s="7">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D22" s="8">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J22" s="8" t="s">
         <v>4</v>
@@ -3096,113 +3072,137 @@
       <c r="K22" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="L22" s="11">
+      <c r="L22" s="8">
         <v>1</v>
       </c>
-      <c r="M22" s="24"/>
-      <c r="N22" s="24">
+      <c r="M22" s="10"/>
+      <c r="N22" s="10">
         <v>0</v>
       </c>
-      <c r="O22" s="24">
-        <v>4</v>
+      <c r="O22" s="10">
+        <v>1</v>
       </c>
       <c r="P22" s="10"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="7">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C23" s="7">
-        <v>2</v>
-      </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
+        <v>6</v>
+      </c>
+      <c r="D23" s="8">
+        <v>5</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>93</v>
+      </c>
       <c r="F23" s="8" t="s">
-        <v>217</v>
+        <v>153</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>250</v>
+        <v>175</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
+        <v>65</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="L23" s="8">
+        <v>1</v>
+      </c>
       <c r="M23" s="10"/>
       <c r="N23" s="10">
         <v>0</v>
       </c>
       <c r="O23" s="10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P23" s="10"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="7">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C24" s="7">
-        <v>3</v>
-      </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
+        <v>7</v>
+      </c>
+      <c r="D24" s="8">
+        <v>6</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="F24" s="8" t="s">
-        <v>218</v>
+        <v>148</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>251</v>
+        <v>176</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10">
+        <v>69</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="L24" s="11">
+        <v>1</v>
+      </c>
+      <c r="M24" s="24"/>
+      <c r="N24" s="24">
         <v>0</v>
       </c>
-      <c r="O24" s="10">
-        <v>6</v>
+      <c r="O24" s="24">
+        <v>9</v>
       </c>
       <c r="P24" s="10"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="7">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C25" s="7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D25" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>64</v>
+        <v>73</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>4</v>
@@ -3210,45 +3210,45 @@
       <c r="K25" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="11">
         <v>1</v>
       </c>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10">
+      <c r="M25" s="24"/>
+      <c r="N25" s="24">
         <v>0</v>
       </c>
-      <c r="O25" s="10">
-        <v>7</v>
+      <c r="O25" s="24">
+        <v>10</v>
       </c>
       <c r="P25" s="10"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C26" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D26" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J26" s="8" t="s">
         <v>4</v>
@@ -3256,39 +3256,39 @@
       <c r="K26" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="L26" s="8">
+      <c r="L26" s="11">
         <v>1</v>
       </c>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10">
+      <c r="M26" s="24"/>
+      <c r="N26" s="24">
         <v>0</v>
       </c>
-      <c r="O26" s="10">
-        <v>8</v>
+      <c r="O26" s="24">
+        <v>11</v>
       </c>
       <c r="P26" s="10"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C27" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D27" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>69</v>
@@ -3310,83 +3310,83 @@
         <v>0</v>
       </c>
       <c r="O27" s="24">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P27" s="10"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C28" s="7">
-        <v>8</v>
-      </c>
-      <c r="D28" s="8">
-        <v>7</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="I28" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="12">
+        <v>9</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="I28" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="J28" s="8" t="s">
+      <c r="J28" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="K28" s="8" t="s">
+      <c r="K28" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="L28" s="11">
+      <c r="L28" s="13">
         <v>1</v>
       </c>
-      <c r="M28" s="24"/>
-      <c r="N28" s="24">
+      <c r="M28" s="25"/>
+      <c r="N28" s="25">
         <v>0</v>
       </c>
-      <c r="O28" s="24">
-        <v>10</v>
+      <c r="O28" s="25">
+        <v>2</v>
       </c>
       <c r="P28" s="10"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C29" s="7">
+        <v>12</v>
+      </c>
+      <c r="D29" s="8">
         <v>9</v>
       </c>
-      <c r="D29" s="8">
-        <v>7</v>
-      </c>
       <c r="E29" s="8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J29" s="8" t="s">
         <v>4</v>
@@ -3402,80 +3402,80 @@
         <v>0</v>
       </c>
       <c r="O29" s="24">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P29" s="10"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="7">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C30" s="7">
-        <v>10</v>
-      </c>
-      <c r="D30" s="8">
-        <v>8</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I30" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="12">
+        <v>11</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="I30" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="J30" s="8" t="s">
+      <c r="J30" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="K30" s="8" t="s">
+      <c r="K30" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="L30" s="11">
+      <c r="L30" s="13">
         <v>1</v>
       </c>
-      <c r="M30" s="24"/>
-      <c r="N30" s="24">
+      <c r="M30" s="25"/>
+      <c r="N30" s="25">
         <v>0</v>
       </c>
-      <c r="O30" s="24">
-        <v>12</v>
+      <c r="O30" s="25">
+        <v>3</v>
       </c>
       <c r="P30" s="10"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="7">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C31" s="7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D31" s="8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>70</v>
@@ -3494,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="O31" s="24">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="P31" s="10"/>
     </row>
@@ -4476,7 +4476,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P50" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}"/>
+  <autoFilter ref="A1:P50" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P50">
+      <sortCondition ref="B1:B50"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A2:P51">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -12973,7 +12977,7 @@
         <v/>
       </c>
       <c r="H64">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I64" t="str">
         <f ca="1"/>
@@ -13166,7 +13170,7 @@
         <v/>
       </c>
       <c r="H65">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I65" t="str">
         <f ca="1"/>
@@ -13359,7 +13363,7 @@
         <v/>
       </c>
       <c r="H66">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I66" t="str">
         <f ca="1"/>
@@ -13552,7 +13556,7 @@
         <v/>
       </c>
       <c r="H67">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I67" t="str">
         <f ca="1"/>
@@ -13745,7 +13749,7 @@
         <v/>
       </c>
       <c r="H68">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I68" t="str">
         <f ca="1"/>
@@ -13938,7 +13942,7 @@
         <v/>
       </c>
       <c r="H69">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I69" t="str">
         <f ca="1"/>
@@ -14131,7 +14135,7 @@
         <v/>
       </c>
       <c r="H70">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I70" t="str">
         <f ca="1"/>
@@ -14324,7 +14328,7 @@
         <v/>
       </c>
       <c r="H71">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I71" t="str">
         <f ca="1"/>
@@ -14517,7 +14521,7 @@
         <v/>
       </c>
       <c r="H72">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I72" t="str">
         <f ca="1"/>
@@ -14710,7 +14714,7 @@
         <v/>
       </c>
       <c r="H73">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I73" t="str">
         <f ca="1"/>
@@ -14903,7 +14907,7 @@
         <v/>
       </c>
       <c r="H74">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I74" t="str">
         <f ca="1"/>
@@ -15096,7 +15100,7 @@
         <v/>
       </c>
       <c r="H75">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I75" t="str">
         <f ca="1"/>
@@ -15289,7 +15293,7 @@
         <v/>
       </c>
       <c r="H76">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I76" t="str">
         <f ca="1"/>

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582438E4-114A-4731-80D4-03825A44883D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C42BB7-CDAF-441E-BD89-EE65B9E88837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -952,16 +952,6 @@
     <t>箔ロウ押え上下</t>
   </si>
   <si>
-    <t>波板カット補助R</t>
-    <rPh sb="0" eb="2">
-      <t>ナミイタ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ホジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>波板カット補助L</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1071,9 +1061,6 @@
   </si>
   <si>
     <t>Corrugated sheet cutter blade open/close</t>
-  </si>
-  <si>
-    <t>Corrugated sheet cutter auxiliary R</t>
   </si>
   <si>
     <t>Corrugated sheet cutter auxiliary L</t>
@@ -1406,6 +1393,20 @@
   </si>
   <si>
     <t>uiErrCode</t>
+  </si>
+  <si>
+    <t>波板カット補助</t>
+    <rPh sb="0" eb="2">
+      <t>ナミイタ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ホジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Corrugated sheet cutter auxiliary</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -2244,7 +2245,7 @@
         <v>105</v>
       </c>
       <c r="G1" s="22" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H1" s="22" t="s">
         <v>10</v>
@@ -2256,7 +2257,7 @@
         <v>3</v>
       </c>
       <c r="K1" s="22" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L1" s="22" t="s">
         <v>5</v>
@@ -2265,10 +2266,10 @@
         <v>112</v>
       </c>
       <c r="N1" s="23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O1" s="23" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="P1" s="23"/>
     </row>
@@ -2292,7 +2293,7 @@
         <v>137</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H2" s="31" t="s">
         <v>20</v>
@@ -2301,10 +2302,10 @@
         <v>21</v>
       </c>
       <c r="J2" s="31" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L2" s="31">
         <v>1</v>
@@ -2334,7 +2335,7 @@
         <v>126</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>14</v>
@@ -2343,10 +2344,10 @@
         <v>13</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L3" s="12">
         <v>1</v>
@@ -2376,7 +2377,7 @@
         <v>125</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>14</v>
@@ -2385,10 +2386,10 @@
         <v>13</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L4" s="12">
         <v>1</v>
@@ -2418,7 +2419,7 @@
         <v>89</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>14</v>
@@ -2427,10 +2428,10 @@
         <v>13</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L5" s="12">
         <v>1</v>
@@ -2460,7 +2461,7 @@
         <v>132</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>1</v>
@@ -2472,7 +2473,7 @@
         <v>2</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L6" s="8">
         <v>1</v>
@@ -2502,7 +2503,7 @@
         <v>133</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>0</v>
@@ -2514,7 +2515,7 @@
         <v>2</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L7" s="8">
         <v>1</v>
@@ -2544,7 +2545,7 @@
         <v>131</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>28</v>
@@ -2556,7 +2557,7 @@
         <v>2</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L8" s="8">
         <v>1</v>
@@ -2586,7 +2587,7 @@
         <v>134</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>106</v>
@@ -2598,7 +2599,7 @@
         <v>2</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L9" s="8">
         <v>1</v>
@@ -2628,7 +2629,7 @@
         <v>135</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>107</v>
@@ -2640,7 +2641,7 @@
         <v>2</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L10" s="8">
         <v>1</v>
@@ -2666,7 +2667,7 @@
         <v>136</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
@@ -2694,7 +2695,7 @@
         <v>138</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
@@ -2722,7 +2723,7 @@
         <v>139</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
@@ -2754,7 +2755,7 @@
         <v>127</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>31</v>
@@ -2763,10 +2764,10 @@
         <v>32</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L14" s="8">
         <v>1</v>
@@ -2796,7 +2797,7 @@
         <v>128</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>33</v>
@@ -2805,10 +2806,10 @@
         <v>32</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L15" s="8">
         <v>1</v>
@@ -2834,7 +2835,7 @@
         <v>129</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>141</v>
@@ -2864,7 +2865,7 @@
         <v>140</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>141</v>
@@ -2898,7 +2899,7 @@
         <v>145</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>61</v>
@@ -2910,7 +2911,7 @@
         <v>4</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L18" s="8">
         <v>1</v>
@@ -2937,13 +2938,13 @@
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
@@ -2971,13 +2972,13 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I20" s="8"/>
       <c r="J20" s="8"/>
@@ -3012,7 +3013,7 @@
         <v>121</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>63</v>
@@ -3024,7 +3025,7 @@
         <v>4</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L21" s="8">
         <v>1</v>
@@ -3055,10 +3056,10 @@
         <v>93</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H22" s="8" t="s">
         <v>67</v>
@@ -3070,7 +3071,7 @@
         <v>4</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L22" s="8">
         <v>1</v>
@@ -3101,10 +3102,10 @@
         <v>93</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H23" s="8" t="s">
         <v>65</v>
@@ -3116,7 +3117,7 @@
         <v>4</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L23" s="8">
         <v>1</v>
@@ -3150,7 +3151,7 @@
         <v>148</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H24" s="8" t="s">
         <v>69</v>
@@ -3162,7 +3163,7 @@
         <v>4</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L24" s="11">
         <v>1</v>
@@ -3196,7 +3197,7 @@
         <v>150</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H25" s="8" t="s">
         <v>73</v>
@@ -3208,7 +3209,7 @@
         <v>4</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L25" s="11">
         <v>1</v>
@@ -3242,7 +3243,7 @@
         <v>122</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H26" s="8" t="s">
         <v>71</v>
@@ -3254,7 +3255,7 @@
         <v>4</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L26" s="11">
         <v>1</v>
@@ -3288,7 +3289,7 @@
         <v>149</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>69</v>
@@ -3300,7 +3301,7 @@
         <v>4</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L27" s="11">
         <v>1</v>
@@ -3334,7 +3335,7 @@
         <v>142</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H28" s="12" t="s">
         <v>75</v>
@@ -3346,7 +3347,7 @@
         <v>4</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L28" s="13">
         <v>1</v>
@@ -3380,7 +3381,7 @@
         <v>146</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>74</v>
@@ -3392,7 +3393,7 @@
         <v>4</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L29" s="11">
         <v>1</v>
@@ -3426,7 +3427,7 @@
         <v>143</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>75</v>
@@ -3438,7 +3439,7 @@
         <v>4</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L30" s="13">
         <v>1</v>
@@ -3472,7 +3473,7 @@
         <v>147</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>76</v>
@@ -3484,7 +3485,7 @@
         <v>4</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L31" s="11">
         <v>1</v>
@@ -3515,10 +3516,10 @@
         <v>96</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>151</v>
+        <v>255</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>77</v>
@@ -3530,7 +3531,7 @@
         <v>4</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L32" s="13">
         <v>1</v>
@@ -3561,10 +3562,10 @@
         <v>96</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>77</v>
@@ -3576,7 +3577,7 @@
         <v>4</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L33" s="13">
         <v>1</v>
@@ -3603,10 +3604,10 @@
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
       <c r="F34" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>51</v>
@@ -3637,10 +3638,10 @@
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
       <c r="F35" s="8" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>51</v>
@@ -3671,13 +3672,13 @@
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
       <c r="F36" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
@@ -3718,7 +3719,7 @@
         <v>4</v>
       </c>
       <c r="K37" s="14" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L37" s="15">
         <v>1</v>
@@ -3756,7 +3757,7 @@
         <v>4</v>
       </c>
       <c r="K38" s="14" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L38" s="15">
         <v>1</v>
@@ -3794,7 +3795,7 @@
         <v>4</v>
       </c>
       <c r="K39" s="14" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L39" s="15">
         <v>1</v>
@@ -3826,7 +3827,7 @@
         <v>130</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>30</v>
@@ -3838,7 +3839,7 @@
         <v>2</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L40" s="8">
         <v>1</v>
@@ -3873,10 +3874,10 @@
         <v>8</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L41" s="8">
         <v>1</v>
@@ -3911,10 +3912,10 @@
         <v>9</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L42" s="8">
         <v>1</v>
@@ -3947,10 +3948,10 @@
         <v>23</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L43" s="8">
         <v>3</v>
@@ -3985,10 +3986,10 @@
         <v>24</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L44" s="8">
         <v>1</v>
@@ -4025,10 +4026,10 @@
         <v>36</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L45" s="8">
         <v>1</v>
@@ -4061,10 +4062,10 @@
         <v>59</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L46" s="8">
         <v>1</v>
@@ -4095,10 +4096,10 @@
         <v>19</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L47" s="8">
         <v>1</v>
@@ -4129,10 +4130,10 @@
         <v>17</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L48" s="8">
         <v>1</v>
@@ -4163,10 +4164,10 @@
         <v>26</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L49" s="8">
         <v>1</v>
@@ -4199,10 +4200,10 @@
         <v>26</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L50" s="8">
         <v>1</v>
@@ -4250,7 +4251,7 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B55" t="s">
         <v>117</v>
@@ -4511,19 +4512,19 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="F1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="J1" t="s">
+        <v>237</v>
+      </c>
+      <c r="L1" t="s">
+        <v>238</v>
+      </c>
+      <c r="N1" t="s">
         <v>239</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>240</v>
-      </c>
-      <c r="N1" t="s">
-        <v>241</v>
-      </c>
-      <c r="P1" t="s">
-        <v>242</v>
       </c>
       <c r="AA1" t="str">
         <f>IF(LEN(J1),J2&amp;CHAR(9)&amp;":"&amp;J1,"")</f>
@@ -4557,82 +4558,82 @@
     </row>
     <row r="2" spans="1:37" s="33" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="33" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F2" s="33" t="s">
         <v>102</v>
       </c>
       <c r="G2" s="33" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H2" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="J2" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="L2" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="N2" s="33" t="s">
+        <v>209</v>
+      </c>
+      <c r="P2" s="33" t="s">
         <v>228</v>
       </c>
-      <c r="J2" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="L2" s="33" t="s">
+      <c r="X2" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y2" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="N2" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="P2" s="33" t="s">
-        <v>230</v>
-      </c>
-      <c r="X2" s="33" t="s">
+      <c r="Z2" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="AA2" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="AB2" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="AC2" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="AD2" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="AE2" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="Y2" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="Z2" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="AA2" s="33" t="s">
-        <v>205</v>
-      </c>
-      <c r="AB2" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="AC2" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="AD2" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="AE2" s="33" t="s">
-        <v>214</v>
-      </c>
       <c r="AF2" s="33" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG2" s="33" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AH2" s="33" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AI2" s="33" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AJ2" s="33" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AK2" s="33" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
@@ -4647,15 +4648,15 @@
       </c>
       <c r="I3" t="str" cm="1">
         <f t="array" aca="1" ref="I3:I202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(H3)),INDEX(OFFSET(info_index!$F$2:$F$51,0,$B$23),MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$51&amp;info_index!$C$2:$C$51,0)&amp;"",1),"")</f>
-        <v>箔ロウリール軸</v>
+        <v>Foil wax reel shaft</v>
       </c>
       <c r="J3" t="str" cm="1">
         <f t="array" aca="1" ref="J3:J202" ca="1">IF(LEN(_xlfn.ANCHORARRAY($H3)),IF(LEN(_xlfn.ANCHORARRAY(I3)),_xlfn.ANCHORARRAY(I3),"unknown"),"")</f>
-        <v>箔ロウリール軸</v>
+        <v>Foil wax reel shaft</v>
       </c>
       <c r="L3" t="str" cm="1">
         <f t="array" aca="1" ref="L3:L202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),"【"&amp;E3:E202&amp;F3:F202&amp;"】 "&amp;_xlfn.ANCHORARRAY(J3),"")</f>
-        <v>【axis1】 箔ロウリール軸</v>
+        <v>【axis1】 Foil wax reel shaft</v>
       </c>
       <c r="M3" t="str" cm="1">
         <f t="array" ref="M3:M202">IFERROR(INDEX(info_index!$H$2:$H$51,MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$51&amp;info_index!$C$2:$C$51,0),1)&amp;"","")</f>
@@ -4686,14 +4687,14 @@
         <f t="array" aca="1" ref="Z3:Z202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(Y3)),_xlfn.ANCHORARRAY(Y3),"")&amp;IF(LEN(J3:J202),CHAR(10)&amp;CHAR(9)&amp;$B$7&amp;_xlfn.ANCHORARRAY(J3)&amp;CHAR(10)&amp;CHAR(9)&amp;IF(F3:F202=1,"IF ","ELSIF ")&amp;$B$26&amp;" = "&amp;F3:F202&amp;" THEN","")</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//箔ロウリール軸
+	//Foil wax reel shaft
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AA3" t="str" cm="1">
         <f t="array" aca="1" ref="AA3:AA202" ca="1">IF(LEN(Z3:Z202),Z3:Z202,"")&amp;IF(LEN(J3:J202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"IF "&amp;$B$27&amp;" = '"&amp;$J$2&amp;"' THEN","")</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//箔ロウリール軸
+	//Foil wax reel shaft
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -4701,54 +4702,54 @@
         <f t="array" aca="1" ref="AB3:AB202" ca="1">IF(LEN(AA3:AA202),AA3:AA202,"")&amp;IF(LEN(J3:J202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(J3)&amp;"'"&amp;$B$9,"")</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//箔ロウリール軸
+	//Foil wax reel shaft
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウリール軸';</v>
+			strRt	:= 'Foil wax reel shaft';</v>
       </c>
       <c r="AC3" t="str" cm="1">
         <f t="array" aca="1" ref="AC3:AC202" ca="1">IF(LEN(AB3:AB202),AB3:AB202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;L$2&amp;"' THEN","")</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//箔ロウリール軸
+	//Foil wax reel shaft
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウリール軸';
+			strRt	:= 'Foil wax reel shaft';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD3" t="str" cm="1">
         <f t="array" aca="1" ref="AD3:AD202" ca="1">IF(LEN(AC3:AC202),AC3:AC202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(L3)&amp;"'"&amp;$B$9,"")</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//箔ロウリール軸
+	//Foil wax reel shaft
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウリール軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis1】 箔ロウリール軸';</v>
+			strRt	:= 'Foil wax reel shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 Foil wax reel shaft';</v>
       </c>
       <c r="AE3" t="str" cm="1">
         <f t="array" aca="1" ref="AE3:AE202" ca="1">IF(LEN(AD3:AD202),AD3:AD202,"")&amp;IF(LEN(N3:N202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;N$2&amp;"' THEN","")</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//箔ロウリール軸
+	//Foil wax reel shaft
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウリール軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis1】 箔ロウリール軸';
+			strRt	:= 'Foil wax reel shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 Foil wax reel shaft';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF3" t="str" cm="1">
         <f t="array" aca="1" ref="AF3:AF202" ca="1">IF(LEN(AE3:AE202),AE3:AE202,"")&amp;IF(LEN(N3:N202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(N3)&amp;"'"&amp;$B$9,"")</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//箔ロウリール軸
+	//Foil wax reel shaft
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウリール軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis1】 箔ロウリール軸';
+			strRt	:= 'Foil wax reel shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 Foil wax reel shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '5TK20GN-CW2J+5GN180K';</v>
       </c>
@@ -4756,12 +4757,12 @@
         <f t="array" aca="1" ref="AG3:AG202" ca="1">IF(LEN(AF3:AF202),AF3:AF202,"")&amp;IF(LEN(P3:P202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;P$2&amp;"' THEN","")</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//箔ロウリール軸
+	//Foil wax reel shaft
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウリール軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis1】 箔ロウリール軸';
+			strRt	:= 'Foil wax reel shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 Foil wax reel shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '5TK20GN-CW2J+5GN180K';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -4770,12 +4771,12 @@
         <f t="array" aca="1" ref="AH3:AH202" ca="1">IF(LEN(AG3:AG202),AG3:AG202,"")&amp;IF(LEN(P3:P202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(P3)&amp;"'"&amp;$B$9,"")</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//箔ロウリール軸
+	//Foil wax reel shaft
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウリール軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis1】 箔ロウリール軸';
+			strRt	:= 'Foil wax reel shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 Foil wax reel shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '5TK20GN-CW2J+5GN180K';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4785,12 +4786,12 @@
         <f t="array" aca="1" ref="AI3:AI202" ca="1">IF(LEN(AH3:AH202),AH3:AH202,"")&amp;IF(LEN(J3:J202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 3"&amp;$B$9&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"END_IF"&amp;$B$9,"")</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//箔ロウリール軸
+	//Foil wax reel shaft
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウリール軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis1】 箔ロウリール軸';
+			strRt	:= 'Foil wax reel shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 Foil wax reel shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '5TK20GN-CW2J+5GN180K';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4803,12 +4804,12 @@
         <f t="array" aca="1" ref="AJ3:AJ202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(AI3)),_xlfn.ANCHORARRAY(AI3),"")&amp;IF(G3:G202="●",CHAR(10)&amp;CHAR(9)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 2"&amp;$B$9&amp;CHAR(10)&amp;CHAR(9)&amp;"END_IF"&amp;$B$9,"")</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//箔ロウリール軸
+	//Foil wax reel shaft
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウリール軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis1】 箔ロウリール軸';
+			strRt	:= 'Foil wax reel shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 Foil wax reel shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '5TK20GN-CW2J+5GN180K';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4821,12 +4822,12 @@
         <f t="array" aca="1" ref="AK3:AK202" ca="1">_xlfn.ANCHORARRAY(AJ3)</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//箔ロウリール軸
+	//Foil wax reel shaft
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウリール軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis1】 箔ロウリール軸';
+			strRt	:= 'Foil wax reel shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 Foil wax reel shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '5TK20GN-CW2J+5GN180K';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4854,15 +4855,15 @@
       </c>
       <c r="I4" t="str">
         <f ca="1"/>
-        <v>平板送り軸</v>
+        <v>Flat sheet feed shaft</v>
       </c>
       <c r="J4" t="str">
         <f ca="1"/>
-        <v>平板送り軸</v>
+        <v>Flat sheet feed shaft</v>
       </c>
       <c r="L4" t="str">
         <f ca="1"/>
-        <v>【axis2】 平板送り軸</v>
+        <v>【axis2】 Flat sheet feed shaft</v>
       </c>
       <c r="M4" t="str">
         <v>AZM46AC-HP9+AZD-CEP+CC070VZR</v>
@@ -4891,75 +4892,75 @@
       <c r="Z4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板送り軸
+	//Flat sheet feed shaft
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AA4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板送り軸
+	//Flat sheet feed shaft
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板送り軸
+	//Flat sheet feed shaft
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板送り軸';</v>
+			strRt	:= 'Flat sheet feed shaft';</v>
       </c>
       <c r="AC4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板送り軸
+	//Flat sheet feed shaft
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板送り軸';
+			strRt	:= 'Flat sheet feed shaft';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板送り軸
+	//Flat sheet feed shaft
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis2】 平板送り軸';</v>
+			strRt	:= 'Flat sheet feed shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 Flat sheet feed shaft';</v>
       </c>
       <c r="AE4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板送り軸
+	//Flat sheet feed shaft
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis2】 平板送り軸';
+			strRt	:= 'Flat sheet feed shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 Flat sheet feed shaft';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板送り軸
+	//Flat sheet feed shaft
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis2】 平板送り軸';
+			strRt	:= 'Flat sheet feed shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 Flat sheet feed shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';</v>
       </c>
       <c r="AG4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板送り軸
+	//Flat sheet feed shaft
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis2】 平板送り軸';
+			strRt	:= 'Flat sheet feed shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 Flat sheet feed shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -4967,12 +4968,12 @@
       <c r="AH4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板送り軸
+	//Flat sheet feed shaft
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis2】 平板送り軸';
+			strRt	:= 'Flat sheet feed shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 Flat sheet feed shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4981,12 +4982,12 @@
       <c r="AI4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板送り軸
+	//Flat sheet feed shaft
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis2】 平板送り軸';
+			strRt	:= 'Flat sheet feed shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 Flat sheet feed shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4998,12 +4999,12 @@
       <c r="AJ4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板送り軸
+	//Flat sheet feed shaft
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis2】 平板送り軸';
+			strRt	:= 'Flat sheet feed shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 Flat sheet feed shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5015,12 +5016,12 @@
       <c r="AK4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板送り軸
+	//Flat sheet feed shaft
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis2】 平板送り軸';
+			strRt	:= 'Flat sheet feed shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 Flat sheet feed shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5032,11 +5033,11 @@
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content によって生成されました。</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ref="E5:E68" si="0">E4</f>
@@ -5054,15 +5055,15 @@
       </c>
       <c r="I5" t="str">
         <f ca="1"/>
-        <v>箔ロウ送り軸</v>
+        <v>Foil wax feed shaft</v>
       </c>
       <c r="J5" t="str">
         <f ca="1"/>
-        <v>箔ロウ送り軸</v>
+        <v>Foil wax feed shaft</v>
       </c>
       <c r="L5" t="str">
         <f ca="1"/>
-        <v>【axis3】 箔ロウ送り軸</v>
+        <v>【axis3】 Foil wax feed shaft</v>
       </c>
       <c r="M5" t="str">
         <v>AZM46AC-HP9+AZD-CEP+CC070VZR</v>
@@ -5091,75 +5092,75 @@
       <c r="Z5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ送り軸
+	//Foil wax feed shaft
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AA5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ送り軸
+	//Foil wax feed shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ送り軸
+	//Foil wax feed shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ送り軸';</v>
+			strRt	:= 'Foil wax feed shaft';</v>
       </c>
       <c r="AC5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ送り軸
+	//Foil wax feed shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ送り軸';
+			strRt	:= 'Foil wax feed shaft';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ送り軸
+	//Foil wax feed shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis3】 箔ロウ送り軸';</v>
+			strRt	:= 'Foil wax feed shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 Foil wax feed shaft';</v>
       </c>
       <c r="AE5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ送り軸
+	//Foil wax feed shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis3】 箔ロウ送り軸';
+			strRt	:= 'Foil wax feed shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 Foil wax feed shaft';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ送り軸
+	//Foil wax feed shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis3】 箔ロウ送り軸';
+			strRt	:= 'Foil wax feed shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 Foil wax feed shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';</v>
       </c>
       <c r="AG5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ送り軸
+	//Foil wax feed shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis3】 箔ロウ送り軸';
+			strRt	:= 'Foil wax feed shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 Foil wax feed shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5167,12 +5168,12 @@
       <c r="AH5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ送り軸
+	//Foil wax feed shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis3】 箔ロウ送り軸';
+			strRt	:= 'Foil wax feed shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 Foil wax feed shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5181,12 +5182,12 @@
       <c r="AI5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ送り軸
+	//Foil wax feed shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis3】 箔ロウ送り軸';
+			strRt	:= 'Foil wax feed shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 Foil wax feed shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5198,12 +5199,12 @@
       <c r="AJ5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ送り軸
+	//Foil wax feed shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis3】 箔ロウ送り軸';
+			strRt	:= 'Foil wax feed shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 Foil wax feed shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5215,12 +5216,12 @@
       <c r="AK5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ送り軸
+	//Foil wax feed shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis3】 箔ロウ送り軸';
+			strRt	:= 'Foil wax feed shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 Foil wax feed shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5232,10 +5233,10 @@
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
@@ -5253,15 +5254,15 @@
       </c>
       <c r="I6" t="str">
         <f ca="1"/>
-        <v>波板送り</v>
+        <v>Corrugated sheet feed</v>
       </c>
       <c r="J6" t="str">
         <f ca="1"/>
-        <v>波板送り</v>
+        <v>Corrugated sheet feed</v>
       </c>
       <c r="L6" t="str">
         <f ca="1"/>
-        <v>【axis4】 波板送り</v>
+        <v>【axis4】 Corrugated sheet feed</v>
       </c>
       <c r="M6" t="str">
         <v>AZM46AC-HP9+AZD-CEP+CC070VZR</v>
@@ -5290,75 +5291,75 @@
       <c r="Z6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板送り
+	//Corrugated sheet feed
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AA6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板送り
+	//Corrugated sheet feed
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板送り
+	//Corrugated sheet feed
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板送り';</v>
+			strRt	:= 'Corrugated sheet feed';</v>
       </c>
       <c r="AC6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板送り
+	//Corrugated sheet feed
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板送り';
+			strRt	:= 'Corrugated sheet feed';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板送り
+	//Corrugated sheet feed
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板送り';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis4】 波板送り';</v>
+			strRt	:= 'Corrugated sheet feed';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 Corrugated sheet feed';</v>
       </c>
       <c r="AE6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板送り
+	//Corrugated sheet feed
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板送り';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis4】 波板送り';
+			strRt	:= 'Corrugated sheet feed';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 Corrugated sheet feed';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板送り
+	//Corrugated sheet feed
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板送り';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis4】 波板送り';
+			strRt	:= 'Corrugated sheet feed';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 Corrugated sheet feed';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';</v>
       </c>
       <c r="AG6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板送り
+	//Corrugated sheet feed
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板送り';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis4】 波板送り';
+			strRt	:= 'Corrugated sheet feed';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 Corrugated sheet feed';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5366,12 +5367,12 @@
       <c r="AH6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板送り
+	//Corrugated sheet feed
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板送り';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis4】 波板送り';
+			strRt	:= 'Corrugated sheet feed';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 Corrugated sheet feed';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5380,12 +5381,12 @@
       <c r="AI6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板送り
+	//Corrugated sheet feed
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板送り';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis4】 波板送り';
+			strRt	:= 'Corrugated sheet feed';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 Corrugated sheet feed';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5397,12 +5398,12 @@
       <c r="AJ6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板送り
+	//Corrugated sheet feed
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板送り';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis4】 波板送り';
+			strRt	:= 'Corrugated sheet feed';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 Corrugated sheet feed';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5414,12 +5415,12 @@
       <c r="AK6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板送り
+	//Corrugated sheet feed
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板送り';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis4】 波板送り';
+			strRt	:= 'Corrugated sheet feed';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 Corrugated sheet feed';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5431,10 +5432,10 @@
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -5452,15 +5453,15 @@
       </c>
       <c r="I7" t="str">
         <f ca="1"/>
-        <v>ワーク排出上下軸</v>
+        <v>Workpiece discharge up/down shaft</v>
       </c>
       <c r="J7" t="str">
         <f ca="1"/>
-        <v>ワーク排出上下軸</v>
+        <v>Workpiece discharge up/down shaft</v>
       </c>
       <c r="L7" t="str">
         <f ca="1"/>
-        <v>【axis5】 ワーク排出上下軸</v>
+        <v>【axis5】 Workpiece discharge up/down shaft</v>
       </c>
       <c r="M7" t="str">
         <v>RCP6-SA7R-WA-56P-16-400-P5-S-B-MR</v>
@@ -5489,75 +5490,75 @@
       <c r="Z7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク排出上下軸
+	//Workpiece discharge up/down shaft
 	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AA7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク排出上下軸
+	//Workpiece discharge up/down shaft
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク排出上下軸
+	//Workpiece discharge up/down shaft
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出上下軸';</v>
+			strRt	:= 'Workpiece discharge up/down shaft';</v>
       </c>
       <c r="AC7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク排出上下軸
+	//Workpiece discharge up/down shaft
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出上下軸';
+			strRt	:= 'Workpiece discharge up/down shaft';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク排出上下軸
+	//Workpiece discharge up/down shaft
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis5】 ワーク排出上下軸';</v>
+			strRt	:= 'Workpiece discharge up/down shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 Workpiece discharge up/down shaft';</v>
       </c>
       <c r="AE7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク排出上下軸
+	//Workpiece discharge up/down shaft
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis5】 ワーク排出上下軸';
+			strRt	:= 'Workpiece discharge up/down shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 Workpiece discharge up/down shaft';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク排出上下軸
+	//Workpiece discharge up/down shaft
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis5】 ワーク排出上下軸';
+			strRt	:= 'Workpiece discharge up/down shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 Workpiece discharge up/down shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';</v>
       </c>
       <c r="AG7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク排出上下軸
+	//Workpiece discharge up/down shaft
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis5】 ワーク排出上下軸';
+			strRt	:= 'Workpiece discharge up/down shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 Workpiece discharge up/down shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5565,12 +5566,12 @@
       <c r="AH7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク排出上下軸
+	//Workpiece discharge up/down shaft
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis5】 ワーク排出上下軸';
+			strRt	:= 'Workpiece discharge up/down shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 Workpiece discharge up/down shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5579,12 +5580,12 @@
       <c r="AI7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク排出上下軸
+	//Workpiece discharge up/down shaft
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis5】 ワーク排出上下軸';
+			strRt	:= 'Workpiece discharge up/down shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 Workpiece discharge up/down shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5596,12 +5597,12 @@
       <c r="AJ7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク排出上下軸
+	//Workpiece discharge up/down shaft
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis5】 ワーク排出上下軸';
+			strRt	:= 'Workpiece discharge up/down shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 Workpiece discharge up/down shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5613,12 +5614,12 @@
       <c r="AK7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク排出上下軸
+	//Workpiece discharge up/down shaft
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis5】 ワーク排出上下軸';
+			strRt	:= 'Workpiece discharge up/down shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 Workpiece discharge up/down shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5630,10 +5631,10 @@
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -5651,15 +5652,15 @@
       </c>
       <c r="I8" t="str">
         <f ca="1"/>
-        <v>周長測定子上下軸</v>
+        <v>Circumference measuring probe up/down shaft</v>
       </c>
       <c r="J8" t="str">
         <f ca="1"/>
-        <v>周長測定子上下軸</v>
+        <v>Circumference measuring probe up/down shaft</v>
       </c>
       <c r="L8" t="str">
         <f ca="1"/>
-        <v>【axis6】 周長測定子上下軸</v>
+        <v>【axis6】 Circumference measuring probe up/down shaft</v>
       </c>
       <c r="M8" t="str">
         <v>RCA2-GS3NA-I-10-2-50-A6-M-K1</v>
@@ -5688,75 +5689,75 @@
       <c r="Z8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子上下軸
+	//Circumference measuring probe up/down shaft
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AA8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子上下軸
+	//Circumference measuring probe up/down shaft
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子上下軸
+	//Circumference measuring probe up/down shaft
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子上下軸';</v>
+			strRt	:= 'Circumference measuring probe up/down shaft';</v>
       </c>
       <c r="AC8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子上下軸
+	//Circumference measuring probe up/down shaft
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子上下軸';
+			strRt	:= 'Circumference measuring probe up/down shaft';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子上下軸
+	//Circumference measuring probe up/down shaft
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis6】 周長測定子上下軸';</v>
+			strRt	:= 'Circumference measuring probe up/down shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 Circumference measuring probe up/down shaft';</v>
       </c>
       <c r="AE8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子上下軸
+	//Circumference measuring probe up/down shaft
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis6】 周長測定子上下軸';
+			strRt	:= 'Circumference measuring probe up/down shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 Circumference measuring probe up/down shaft';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子上下軸
+	//Circumference measuring probe up/down shaft
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis6】 周長測定子上下軸';
+			strRt	:= 'Circumference measuring probe up/down shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 Circumference measuring probe up/down shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';</v>
       </c>
       <c r="AG8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子上下軸
+	//Circumference measuring probe up/down shaft
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis6】 周長測定子上下軸';
+			strRt	:= 'Circumference measuring probe up/down shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 Circumference measuring probe up/down shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5764,12 +5765,12 @@
       <c r="AH8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子上下軸
+	//Circumference measuring probe up/down shaft
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis6】 周長測定子上下軸';
+			strRt	:= 'Circumference measuring probe up/down shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 Circumference measuring probe up/down shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5778,12 +5779,12 @@
       <c r="AI8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子上下軸
+	//Circumference measuring probe up/down shaft
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis6】 周長測定子上下軸';
+			strRt	:= 'Circumference measuring probe up/down shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 Circumference measuring probe up/down shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5795,12 +5796,12 @@
       <c r="AJ8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子上下軸
+	//Circumference measuring probe up/down shaft
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis6】 周長測定子上下軸';
+			strRt	:= 'Circumference measuring probe up/down shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 Circumference measuring probe up/down shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5812,12 +5813,12 @@
       <c r="AK8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子上下軸
+	//Circumference measuring probe up/down shaft
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis6】 周長測定子上下軸';
+			strRt	:= 'Circumference measuring probe up/down shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 Circumference measuring probe up/down shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5829,10 +5830,10 @@
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -5850,15 +5851,15 @@
       </c>
       <c r="I9" t="str">
         <f ca="1"/>
-        <v>ワーク(排出)チャック軸</v>
+        <v>Workpiece (discharge) chuck shaft</v>
       </c>
       <c r="J9" t="str">
         <f ca="1"/>
-        <v>ワーク(排出)チャック軸</v>
+        <v>Workpiece (discharge) chuck shaft</v>
       </c>
       <c r="L9" t="str">
         <f ca="1"/>
-        <v>【axis7】 ワーク(排出)チャック軸</v>
+        <v>【axis7】 Workpiece (discharge) chuck shaft</v>
       </c>
       <c r="M9" t="str">
         <v>RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM</v>
@@ -5887,75 +5888,75 @@
       <c r="Z9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク(排出)チャック軸
+	//Workpiece (discharge) chuck shaft
 	ELSIF uiInfoIdx = 7 THEN</v>
       </c>
       <c r="AA9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク(排出)チャック軸
+	//Workpiece (discharge) chuck shaft
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク(排出)チャック軸
+	//Workpiece (discharge) chuck shaft
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク(排出)チャック軸';</v>
+			strRt	:= 'Workpiece (discharge) chuck shaft';</v>
       </c>
       <c r="AC9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク(排出)チャック軸
+	//Workpiece (discharge) chuck shaft
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク(排出)チャック軸';
+			strRt	:= 'Workpiece (discharge) chuck shaft';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク(排出)チャック軸
+	//Workpiece (discharge) chuck shaft
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク(排出)チャック軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis7】 ワーク(排出)チャック軸';</v>
+			strRt	:= 'Workpiece (discharge) chuck shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 Workpiece (discharge) chuck shaft';</v>
       </c>
       <c r="AE9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク(排出)チャック軸
+	//Workpiece (discharge) chuck shaft
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク(排出)チャック軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis7】 ワーク(排出)チャック軸';
+			strRt	:= 'Workpiece (discharge) chuck shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 Workpiece (discharge) chuck shaft';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク(排出)チャック軸
+	//Workpiece (discharge) chuck shaft
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク(排出)チャック軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis7】 ワーク(排出)チャック軸';
+			strRt	:= 'Workpiece (discharge) chuck shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 Workpiece (discharge) chuck shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';</v>
       </c>
       <c r="AG9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク(排出)チャック軸
+	//Workpiece (discharge) chuck shaft
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク(排出)チャック軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis7】 ワーク(排出)チャック軸';
+			strRt	:= 'Workpiece (discharge) chuck shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 Workpiece (discharge) chuck shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5963,12 +5964,12 @@
       <c r="AH9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク(排出)チャック軸
+	//Workpiece (discharge) chuck shaft
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク(排出)チャック軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis7】 ワーク(排出)チャック軸';
+			strRt	:= 'Workpiece (discharge) chuck shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 Workpiece (discharge) chuck shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5977,12 +5978,12 @@
       <c r="AI9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク(排出)チャック軸
+	//Workpiece (discharge) chuck shaft
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク(排出)チャック軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis7】 ワーク(排出)チャック軸';
+			strRt	:= 'Workpiece (discharge) chuck shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 Workpiece (discharge) chuck shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5994,12 +5995,12 @@
       <c r="AJ9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク(排出)チャック軸
+	//Workpiece (discharge) chuck shaft
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク(排出)チャック軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis7】 ワーク(排出)チャック軸';
+			strRt	:= 'Workpiece (discharge) chuck shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 Workpiece (discharge) chuck shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6011,12 +6012,12 @@
       <c r="AK9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク(排出)チャック軸
+	//Workpiece (discharge) chuck shaft
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク(排出)チャック軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis7】 ワーク(排出)チャック軸';
+			strRt	:= 'Workpiece (discharge) chuck shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 Workpiece (discharge) chuck shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6043,15 +6044,15 @@
       </c>
       <c r="I10" t="str">
         <f ca="1"/>
-        <v>Y軸：溶接トーチ前後</v>
+        <v>Y-axis: Welding torch forward/backward</v>
       </c>
       <c r="J10" t="str">
         <f ca="1"/>
-        <v>Y軸：溶接トーチ前後</v>
+        <v>Y-axis: Welding torch forward/backward</v>
       </c>
       <c r="L10" t="str">
         <f ca="1"/>
-        <v>【axis8】 Y軸：溶接トーチ前後</v>
+        <v>【axis8】 Y-axis: Welding torch forward/backward</v>
       </c>
       <c r="M10" t="str">
         <v>ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③</v>
@@ -6080,75 +6081,75 @@
       <c r="Z10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y軸：溶接トーチ前後
+	//Y-axis: Welding torch forward/backward
 	ELSIF uiInfoIdx = 8 THEN</v>
       </c>
       <c r="AA10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y軸：溶接トーチ前後
+	//Y-axis: Welding torch forward/backward
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y軸：溶接トーチ前後
+	//Y-axis: Welding torch forward/backward
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y軸：溶接トーチ前後';</v>
+			strRt	:= 'Y-axis: Welding torch forward/backward';</v>
       </c>
       <c r="AC10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y軸：溶接トーチ前後
+	//Y-axis: Welding torch forward/backward
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y軸：溶接トーチ前後';
+			strRt	:= 'Y-axis: Welding torch forward/backward';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y軸：溶接トーチ前後
+	//Y-axis: Welding torch forward/backward
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y軸：溶接トーチ前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis8】 Y軸：溶接トーチ前後';</v>
+			strRt	:= 'Y-axis: Welding torch forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y-axis: Welding torch forward/backward';</v>
       </c>
       <c r="AE10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y軸：溶接トーチ前後
+	//Y-axis: Welding torch forward/backward
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y軸：溶接トーチ前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
+			strRt	:= 'Y-axis: Welding torch forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y-axis: Welding torch forward/backward';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y軸：溶接トーチ前後
+	//Y-axis: Welding torch forward/backward
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y軸：溶接トーチ前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
+			strRt	:= 'Y-axis: Welding torch forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y-axis: Welding torch forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';</v>
       </c>
       <c r="AG10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y軸：溶接トーチ前後
+	//Y-axis: Welding torch forward/backward
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y軸：溶接トーチ前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
+			strRt	:= 'Y-axis: Welding torch forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y-axis: Welding torch forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -6156,12 +6157,12 @@
       <c r="AH10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y軸：溶接トーチ前後
+	//Y-axis: Welding torch forward/backward
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y軸：溶接トーチ前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
+			strRt	:= 'Y-axis: Welding torch forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y-axis: Welding torch forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6170,12 +6171,12 @@
       <c r="AI10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y軸：溶接トーチ前後
+	//Y-axis: Welding torch forward/backward
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y軸：溶接トーチ前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
+			strRt	:= 'Y-axis: Welding torch forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y-axis: Welding torch forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6187,12 +6188,12 @@
       <c r="AJ10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y軸：溶接トーチ前後
+	//Y-axis: Welding torch forward/backward
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y軸：溶接トーチ前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
+			strRt	:= 'Y-axis: Welding torch forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y-axis: Welding torch forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6204,12 +6205,12 @@
       <c r="AK10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y軸：溶接トーチ前後
+	//Y-axis: Welding torch forward/backward
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y軸：溶接トーチ前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
+			strRt	:= 'Y-axis: Welding torch forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y-axis: Welding torch forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6236,15 +6237,15 @@
       </c>
       <c r="I11" t="str">
         <f ca="1"/>
-        <v>Z軸：溶接トーチ上下</v>
+        <v>Z-axis: Welding torch up/down</v>
       </c>
       <c r="J11" t="str">
         <f ca="1"/>
-        <v>Z軸：溶接トーチ上下</v>
+        <v>Z-axis: Welding torch up/down</v>
       </c>
       <c r="L11" t="str">
         <f ca="1"/>
-        <v>【axis9】 Z軸：溶接トーチ上下</v>
+        <v>【axis9】 Z-axis: Welding torch up/down</v>
       </c>
       <c r="M11" t="str">
         <v>ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤</v>
@@ -6273,75 +6274,75 @@
       <c r="Z11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z軸：溶接トーチ上下
+	//Z-axis: Welding torch up/down
 	ELSIF uiInfoIdx = 9 THEN</v>
       </c>
       <c r="AA11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z軸：溶接トーチ上下
+	//Z-axis: Welding torch up/down
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z軸：溶接トーチ上下
+	//Z-axis: Welding torch up/down
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z軸：溶接トーチ上下';</v>
+			strRt	:= 'Z-axis: Welding torch up/down';</v>
       </c>
       <c r="AC11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z軸：溶接トーチ上下
+	//Z-axis: Welding torch up/down
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z軸：溶接トーチ上下';
+			strRt	:= 'Z-axis: Welding torch up/down';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z軸：溶接トーチ上下
+	//Z-axis: Welding torch up/down
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z軸：溶接トーチ上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis9】 Z軸：溶接トーチ上下';</v>
+			strRt	:= 'Z-axis: Welding torch up/down';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z-axis: Welding torch up/down';</v>
       </c>
       <c r="AE11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z軸：溶接トーチ上下
+	//Z-axis: Welding torch up/down
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z軸：溶接トーチ上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
+			strRt	:= 'Z-axis: Welding torch up/down';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z-axis: Welding torch up/down';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z軸：溶接トーチ上下
+	//Z-axis: Welding torch up/down
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z軸：溶接トーチ上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
+			strRt	:= 'Z-axis: Welding torch up/down';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z-axis: Welding torch up/down';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';</v>
       </c>
       <c r="AG11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z軸：溶接トーチ上下
+	//Z-axis: Welding torch up/down
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z軸：溶接トーチ上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
+			strRt	:= 'Z-axis: Welding torch up/down';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z-axis: Welding torch up/down';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -6349,12 +6350,12 @@
       <c r="AH11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z軸：溶接トーチ上下
+	//Z-axis: Welding torch up/down
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z軸：溶接トーチ上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
+			strRt	:= 'Z-axis: Welding torch up/down';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z-axis: Welding torch up/down';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6363,12 +6364,12 @@
       <c r="AI11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z軸：溶接トーチ上下
+	//Z-axis: Welding torch up/down
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z軸：溶接トーチ上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
+			strRt	:= 'Z-axis: Welding torch up/down';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z-axis: Welding torch up/down';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6380,12 +6381,12 @@
       <c r="AJ11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z軸：溶接トーチ上下
+	//Z-axis: Welding torch up/down
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z軸：溶接トーチ上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
+			strRt	:= 'Z-axis: Welding torch up/down';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z-axis: Welding torch up/down';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6397,12 +6398,12 @@
       <c r="AK11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z軸：溶接トーチ上下
+	//Z-axis: Welding torch up/down
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z軸：溶接トーチ上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
+			strRt	:= 'Z-axis: Welding torch up/down';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z-axis: Welding torch up/down';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6429,15 +6430,15 @@
       </c>
       <c r="I12" t="str">
         <f ca="1"/>
-        <v>バインダー供給ポンプモータ</v>
+        <v>Binder supply pump motor</v>
       </c>
       <c r="J12" t="str">
         <f ca="1"/>
-        <v>バインダー供給ポンプモータ</v>
+        <v>Binder supply pump motor</v>
       </c>
       <c r="L12" t="str">
         <f ca="1"/>
-        <v>【axis10】 バインダー供給ポンプモータ</v>
+        <v>【axis10】 Binder supply pump motor</v>
       </c>
       <c r="M12" t="str">
         <v/>
@@ -6466,75 +6467,75 @@
       <c r="Z12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//バインダー供給ポンプモータ
+	//Binder supply pump motor
 	ELSIF uiInfoIdx = 10 THEN</v>
       </c>
       <c r="AA12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//バインダー供給ポンプモータ
+	//Binder supply pump motor
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//バインダー供給ポンプモータ
+	//Binder supply pump motor
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'バインダー供給ポンプモータ';</v>
+			strRt	:= 'Binder supply pump motor';</v>
       </c>
       <c r="AC12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//バインダー供給ポンプモータ
+	//Binder supply pump motor
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'バインダー供給ポンプモータ';
+			strRt	:= 'Binder supply pump motor';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//バインダー供給ポンプモータ
+	//Binder supply pump motor
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'バインダー供給ポンプモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis10】 バインダー供給ポンプモータ';</v>
+			strRt	:= 'Binder supply pump motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 Binder supply pump motor';</v>
       </c>
       <c r="AE12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//バインダー供給ポンプモータ
+	//Binder supply pump motor
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'バインダー供給ポンプモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis10】 バインダー供給ポンプモータ';
+			strRt	:= 'Binder supply pump motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 Binder supply pump motor';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//バインダー供給ポンプモータ
+	//Binder supply pump motor
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'バインダー供給ポンプモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis10】 バインダー供給ポンプモータ';
+			strRt	:= 'Binder supply pump motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 Binder supply pump motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AG12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//バインダー供給ポンプモータ
+	//Binder supply pump motor
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'バインダー供給ポンプモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis10】 バインダー供給ポンプモータ';
+			strRt	:= 'Binder supply pump motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 Binder supply pump motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -6542,12 +6543,12 @@
       <c r="AH12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//バインダー供給ポンプモータ
+	//Binder supply pump motor
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'バインダー供給ポンプモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis10】 バインダー供給ポンプモータ';
+			strRt	:= 'Binder supply pump motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 Binder supply pump motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6556,12 +6557,12 @@
       <c r="AI12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//バインダー供給ポンプモータ
+	//Binder supply pump motor
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'バインダー供給ポンプモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis10】 バインダー供給ポンプモータ';
+			strRt	:= 'Binder supply pump motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 Binder supply pump motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6573,12 +6574,12 @@
       <c r="AJ12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//バインダー供給ポンプモータ
+	//Binder supply pump motor
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'バインダー供給ポンプモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis10】 バインダー供給ポンプモータ';
+			strRt	:= 'Binder supply pump motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 Binder supply pump motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6590,12 +6591,12 @@
       <c r="AK12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//バインダー供給ポンプモータ
+	//Binder supply pump motor
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'バインダー供給ポンプモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis10】 バインダー供給ポンプモータ';
+			strRt	:= 'Binder supply pump motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 Binder supply pump motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6607,19 +6608,19 @@
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B13" t="str">
         <f ca="1">$AK$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
-	//箔ロウリール軸
+	//Foil wax reel shaft
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウリール軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis1】 箔ロウリール軸';
+			strRt	:= 'Foil wax reel shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 Foil wax reel shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '5TK20GN-CW2J+5GN180K';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6627,12 +6628,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//平板送り軸
+	//Flat sheet feed shaft
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis2】 平板送り軸';
+			strRt	:= 'Flat sheet feed shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 Flat sheet feed shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6640,12 +6641,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//箔ロウ送り軸
+	//Foil wax feed shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis3】 箔ロウ送り軸';
+			strRt	:= 'Foil wax feed shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 Foil wax feed shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6653,12 +6654,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//波板送り
+	//Corrugated sheet feed
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板送り';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis4】 波板送り';
+			strRt	:= 'Corrugated sheet feed';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 Corrugated sheet feed';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6666,12 +6667,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//ワーク排出上下軸
+	//Workpiece discharge up/down shaft
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis5】 ワーク排出上下軸';
+			strRt	:= 'Workpiece discharge up/down shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 Workpiece discharge up/down shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6679,12 +6680,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定子上下軸
+	//Circumference measuring probe up/down shaft
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis6】 周長測定子上下軸';
+			strRt	:= 'Circumference measuring probe up/down shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 Circumference measuring probe up/down shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6692,12 +6693,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//ワーク(排出)チャック軸
+	//Workpiece (discharge) chuck shaft
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク(排出)チャック軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis7】 ワーク(排出)チャック軸';
+			strRt	:= 'Workpiece (discharge) chuck shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 Workpiece (discharge) chuck shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6705,12 +6706,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Y軸：溶接トーチ前後
+	//Y-axis: Welding torch forward/backward
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y軸：溶接トーチ前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
+			strRt	:= 'Y-axis: Welding torch forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y-axis: Welding torch forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6718,12 +6719,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Z軸：溶接トーチ上下
+	//Z-axis: Welding torch up/down
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z軸：溶接トーチ上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
+			strRt	:= 'Z-axis: Welding torch up/down';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z-axis: Welding torch up/down';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6731,12 +6732,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//バインダー供給ポンプモータ
+	//Binder supply pump motor
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'バインダー供給ポンプモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis10】 バインダー供給ポンプモータ';
+			strRt	:= 'Binder supply pump motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 Binder supply pump motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6744,12 +6745,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//波板リールモータ
+	//Corrugated sheet reel motor
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis11】 波板リールモータ';
+			strRt	:= 'Corrugated sheet reel motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 Corrugated sheet reel motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6757,12 +6758,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//平板リールモータ
+	//Flat sheet reel motor
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis12】 平板リールモータ';
+			strRt	:= 'Flat sheet reel motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 Flat sheet reel motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6770,12 +6771,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻取り主軸
+	//Winding main shaft
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り主軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis13】 巻取り主軸';
+			strRt	:= 'Winding main shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 Winding main shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-B075AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6783,12 +6784,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//ワーク幅調整軸
+	//Workpiece width adjustment shaft
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク幅調整軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis14】 ワーク幅調整軸';
+			strRt	:= 'Workpiece width adjustment shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 Workpiece width adjustment shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-M040AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6796,12 +6797,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Tロール回転軸
+	//T-roll rotation shaft
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 Tロール回転軸';
+			strRt	:= 'T-roll rotation shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 T-roll rotation shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6809,12 +6810,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//ロータユニットXロール回転軸
+	//Rotor unit X-roll rotation shaft
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ロータユニットXロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis16】 ロータユニットXロール回転軸';
+			strRt	:= 'Rotor unit X-roll rotation shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 Rotor unit X-roll rotation shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6827,12 +6828,12 @@
 	END_IF;
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//ワーク排出前後軸
+	//Workpiece discharge front and rear axis
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出前後軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【EC1】 ワーク排出前後軸';
+			strRt	:= 'Workpiece discharge front and rear axis';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 Workpiece discharge front and rear axis';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'EC-S4HR-200-7-ML-TMD2';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6845,12 +6846,12 @@
 	END_IF;
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//巻取り軸芯前後
+	//Winding shaft center forward/backward
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り軸芯前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder1】 巻取り軸芯前後';
+			strRt	:= 'Winding shaft center forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 Winding shaft center forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6858,12 +6859,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Tロール糊付け①
+	//T-roll gluing ①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder2】 Tロール糊付け①';
+			strRt	:= 'T-roll gluing ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 T-roll gluing ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6871,12 +6872,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Tロール糊付け②
+	//T-roll gluing ②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder3】 Tロール糊付け②';
+			strRt	:= 'T-roll gluing ②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 T-roll gluing ②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6884,12 +6885,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//平板下側補助プレート逃がし
+	//Flat sheet lower auxiliary plate release
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板下側補助プレート逃がし';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder4】 平板下側補助プレート逃がし';
+			strRt	:= 'Flat sheet lower auxiliary plate release';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 Flat sheet lower auxiliary plate release';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6897,12 +6898,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//平板チャック(ハンド)前後
+	//Flat sheet chuck (hand) forward/backward
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック(ハンド)前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
+			strRt	:= 'Flat sheet chuck (hand) forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 Flat sheet chuck (hand) forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MXQ20-50A-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6910,12 +6911,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//平板チャック開閉
+	//Flat sheet chuck open/close
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder6】 平板チャック開閉';
+			strRt	:= 'Flat sheet chuck open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 Flat sheet chuck open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MHF2-16D1-M9BL-X83C1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6923,12 +6924,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//平板押え上下①
+	//Flat sheet clamp up/down ①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= 'Flat sheet clamp up/down ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 Flat sheet clamp up/down ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6936,12 +6937,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//箔ロウ押え上下
+	//Foil wax clamp up/down
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ押え上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder8】 箔ロウ押え上下';
+			strRt	:= 'Foil wax clamp up/down';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 Foil wax clamp up/down';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2D25-20DMZ-M9BM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6949,12 +6950,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//箔ロウカット
+	//Foil wax cut
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウカット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder9】 箔ロウカット';
+			strRt	:= 'Foil wax cut';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 Foil wax cut';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQSKB16-10DM-M9NWVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6962,12 +6963,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//波板押え
+	//Corrugated sheet clamp
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板押え';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder10】 波板押え';
+			strRt	:= 'Corrugated sheet clamp';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 Corrugated sheet clamp';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6975,12 +6976,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//平板カット刃押出し
+	//Flat sheet cutter blade push-out
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder11】 平板カット刃押出し';
+			strRt	:= 'Flat sheet cutter blade push-out';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 Flat sheet cutter blade push-out';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6988,12 +6989,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//平板カット刃開閉
+	//Flat sheet cutter blade open/close
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder12】 平板カット刃開閉';
+			strRt	:= 'Flat sheet cutter blade open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 Flat sheet cutter blade open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-10DMZ-L-A93M';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7001,12 +7002,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//波板カット刃押出し
+	//Corrugated sheet cutter blade push-out
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder13】 波板カット刃押出し';
+			strRt	:= 'Corrugated sheet cutter blade push-out';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 Corrugated sheet cutter blade push-out';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7014,12 +7015,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//波板カット刃開閉
+	//Corrugated sheet cutter blade open/close
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder14】 波板カット刃開閉';
+			strRt	:= 'Corrugated sheet cutter blade open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 Corrugated sheet cutter blade open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7027,12 +7028,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//波板カット補助R
+	//Corrugated sheet cutter auxiliary
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助R';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder15】 波板カット補助R';
+			strRt	:= 'Corrugated sheet cutter auxiliary';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 Corrugated sheet cutter auxiliary';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7040,12 +7041,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//波板カット補助L
+	//Corrugated sheet cutter auxiliary L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助L';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder16】 波板カット補助L';
+			strRt	:= 'Corrugated sheet cutter auxiliary L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 Corrugated sheet cutter auxiliary L';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7053,12 +7054,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Xロール糊付け①
+	//X-roll gluing ①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder17】 Xロール糊付け①';
+			strRt	:= 'X-roll gluing ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 X-roll gluing ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7066,12 +7067,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Xロール糊付け②
+	//X-roll gluing ②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder18】 Xロール糊付け②';
+			strRt	:= 'X-roll gluing ②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 X-roll gluing ②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7079,12 +7080,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Xロール平板押付
+	//X-roll flat plate pressing
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール平板押付';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder19】 Xロール平板押付';
+			strRt	:= 'X-roll flat plate pressing';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 X-roll flat plate pressing';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '不明';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7116,15 +7117,15 @@
       </c>
       <c r="I13" t="str">
         <f ca="1"/>
-        <v>波板リールモータ</v>
+        <v>Corrugated sheet reel motor</v>
       </c>
       <c r="J13" t="str">
         <f ca="1"/>
-        <v>波板リールモータ</v>
+        <v>Corrugated sheet reel motor</v>
       </c>
       <c r="L13" t="str">
         <f ca="1"/>
-        <v>【axis11】 波板リールモータ</v>
+        <v>【axis11】 Corrugated sheet reel motor</v>
       </c>
       <c r="M13" t="str">
         <v/>
@@ -7153,75 +7154,75 @@
       <c r="Z13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板リールモータ
+	//Corrugated sheet reel motor
 	ELSIF uiInfoIdx = 11 THEN</v>
       </c>
       <c r="AA13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板リールモータ
+	//Corrugated sheet reel motor
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板リールモータ
+	//Corrugated sheet reel motor
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板リールモータ';</v>
+			strRt	:= 'Corrugated sheet reel motor';</v>
       </c>
       <c r="AC13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板リールモータ
+	//Corrugated sheet reel motor
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板リールモータ';
+			strRt	:= 'Corrugated sheet reel motor';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板リールモータ
+	//Corrugated sheet reel motor
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis11】 波板リールモータ';</v>
+			strRt	:= 'Corrugated sheet reel motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 Corrugated sheet reel motor';</v>
       </c>
       <c r="AE13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板リールモータ
+	//Corrugated sheet reel motor
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis11】 波板リールモータ';
+			strRt	:= 'Corrugated sheet reel motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 Corrugated sheet reel motor';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板リールモータ
+	//Corrugated sheet reel motor
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis11】 波板リールモータ';
+			strRt	:= 'Corrugated sheet reel motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 Corrugated sheet reel motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AG13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板リールモータ
+	//Corrugated sheet reel motor
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis11】 波板リールモータ';
+			strRt	:= 'Corrugated sheet reel motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 Corrugated sheet reel motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7229,12 +7230,12 @@
       <c r="AH13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板リールモータ
+	//Corrugated sheet reel motor
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis11】 波板リールモータ';
+			strRt	:= 'Corrugated sheet reel motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 Corrugated sheet reel motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7243,12 +7244,12 @@
       <c r="AI13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板リールモータ
+	//Corrugated sheet reel motor
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis11】 波板リールモータ';
+			strRt	:= 'Corrugated sheet reel motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 Corrugated sheet reel motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7260,12 +7261,12 @@
       <c r="AJ13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板リールモータ
+	//Corrugated sheet reel motor
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis11】 波板リールモータ';
+			strRt	:= 'Corrugated sheet reel motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 Corrugated sheet reel motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7277,12 +7278,12 @@
       <c r="AK13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板リールモータ
+	//Corrugated sheet reel motor
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis11】 波板リールモータ';
+			strRt	:= 'Corrugated sheet reel motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 Corrugated sheet reel motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7294,7 +7295,7 @@
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B14" t="str">
         <f>IF(LEN(AI1),"●"&amp;B27&amp;CHAR(10)&amp;AI1,"")</f>
@@ -7320,15 +7321,15 @@
       </c>
       <c r="I14" t="str">
         <f ca="1"/>
-        <v>平板リールモータ</v>
+        <v>Flat sheet reel motor</v>
       </c>
       <c r="J14" t="str">
         <f ca="1"/>
-        <v>平板リールモータ</v>
+        <v>Flat sheet reel motor</v>
       </c>
       <c r="L14" t="str">
         <f ca="1"/>
-        <v>【axis12】 平板リールモータ</v>
+        <v>【axis12】 Flat sheet reel motor</v>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -7357,75 +7358,75 @@
       <c r="Z14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板リールモータ
+	//Flat sheet reel motor
 	ELSIF uiInfoIdx = 12 THEN</v>
       </c>
       <c r="AA14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板リールモータ
+	//Flat sheet reel motor
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板リールモータ
+	//Flat sheet reel motor
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板リールモータ';</v>
+			strRt	:= 'Flat sheet reel motor';</v>
       </c>
       <c r="AC14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板リールモータ
+	//Flat sheet reel motor
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板リールモータ';
+			strRt	:= 'Flat sheet reel motor';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板リールモータ
+	//Flat sheet reel motor
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis12】 平板リールモータ';</v>
+			strRt	:= 'Flat sheet reel motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 Flat sheet reel motor';</v>
       </c>
       <c r="AE14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板リールモータ
+	//Flat sheet reel motor
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis12】 平板リールモータ';
+			strRt	:= 'Flat sheet reel motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 Flat sheet reel motor';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板リールモータ
+	//Flat sheet reel motor
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis12】 平板リールモータ';
+			strRt	:= 'Flat sheet reel motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 Flat sheet reel motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AG14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板リールモータ
+	//Flat sheet reel motor
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis12】 平板リールモータ';
+			strRt	:= 'Flat sheet reel motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 Flat sheet reel motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7433,12 +7434,12 @@
       <c r="AH14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板リールモータ
+	//Flat sheet reel motor
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis12】 平板リールモータ';
+			strRt	:= 'Flat sheet reel motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 Flat sheet reel motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7447,12 +7448,12 @@
       <c r="AI14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板リールモータ
+	//Flat sheet reel motor
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis12】 平板リールモータ';
+			strRt	:= 'Flat sheet reel motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 Flat sheet reel motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7464,12 +7465,12 @@
       <c r="AJ14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板リールモータ
+	//Flat sheet reel motor
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis12】 平板リールモータ';
+			strRt	:= 'Flat sheet reel motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 Flat sheet reel motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7481,12 +7482,12 @@
       <c r="AK14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板リールモータ
+	//Flat sheet reel motor
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis12】 平板リールモータ';
+			strRt	:= 'Flat sheet reel motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 Flat sheet reel motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7513,15 +7514,15 @@
       </c>
       <c r="I15" t="str">
         <f ca="1"/>
-        <v>巻取り主軸</v>
+        <v>Winding main shaft</v>
       </c>
       <c r="J15" t="str">
         <f ca="1"/>
-        <v>巻取り主軸</v>
+        <v>Winding main shaft</v>
       </c>
       <c r="L15" t="str">
         <f ca="1"/>
-        <v>【axis13】 巻取り主軸</v>
+        <v>【axis13】 Winding main shaft</v>
       </c>
       <c r="M15" t="str">
         <v>SV3-B075AK</v>
@@ -7550,75 +7551,75 @@
       <c r="Z15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り主軸
+	//Winding main shaft
 	ELSIF uiInfoIdx = 13 THEN</v>
       </c>
       <c r="AA15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り主軸
+	//Winding main shaft
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り主軸
+	//Winding main shaft
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り主軸';</v>
+			strRt	:= 'Winding main shaft';</v>
       </c>
       <c r="AC15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り主軸
+	//Winding main shaft
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り主軸';
+			strRt	:= 'Winding main shaft';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り主軸
+	//Winding main shaft
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り主軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis13】 巻取り主軸';</v>
+			strRt	:= 'Winding main shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 Winding main shaft';</v>
       </c>
       <c r="AE15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り主軸
+	//Winding main shaft
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り主軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis13】 巻取り主軸';
+			strRt	:= 'Winding main shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 Winding main shaft';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り主軸
+	//Winding main shaft
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り主軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis13】 巻取り主軸';
+			strRt	:= 'Winding main shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 Winding main shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-B075AK';</v>
       </c>
       <c r="AG15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り主軸
+	//Winding main shaft
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り主軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis13】 巻取り主軸';
+			strRt	:= 'Winding main shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 Winding main shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-B075AK';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7626,12 +7627,12 @@
       <c r="AH15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り主軸
+	//Winding main shaft
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り主軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis13】 巻取り主軸';
+			strRt	:= 'Winding main shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 Winding main shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-B075AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7640,12 +7641,12 @@
       <c r="AI15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り主軸
+	//Winding main shaft
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り主軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis13】 巻取り主軸';
+			strRt	:= 'Winding main shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 Winding main shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-B075AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7657,12 +7658,12 @@
       <c r="AJ15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り主軸
+	//Winding main shaft
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り主軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis13】 巻取り主軸';
+			strRt	:= 'Winding main shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 Winding main shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-B075AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7674,12 +7675,12 @@
       <c r="AK15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り主軸
+	//Winding main shaft
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り主軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis13】 巻取り主軸';
+			strRt	:= 'Winding main shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 Winding main shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-B075AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7706,15 +7707,15 @@
       </c>
       <c r="I16" t="str">
         <f ca="1"/>
-        <v>ワーク幅調整軸</v>
+        <v>Workpiece width adjustment shaft</v>
       </c>
       <c r="J16" t="str">
         <f ca="1"/>
-        <v>ワーク幅調整軸</v>
+        <v>Workpiece width adjustment shaft</v>
       </c>
       <c r="L16" t="str">
         <f ca="1"/>
-        <v>【axis14】 ワーク幅調整軸</v>
+        <v>【axis14】 Workpiece width adjustment shaft</v>
       </c>
       <c r="M16" t="str">
         <v>SV3-M040AK</v>
@@ -7743,75 +7744,75 @@
       <c r="Z16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク幅調整軸
+	//Workpiece width adjustment shaft
 	ELSIF uiInfoIdx = 14 THEN</v>
       </c>
       <c r="AA16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク幅調整軸
+	//Workpiece width adjustment shaft
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク幅調整軸
+	//Workpiece width adjustment shaft
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク幅調整軸';</v>
+			strRt	:= 'Workpiece width adjustment shaft';</v>
       </c>
       <c r="AC16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク幅調整軸
+	//Workpiece width adjustment shaft
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク幅調整軸';
+			strRt	:= 'Workpiece width adjustment shaft';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク幅調整軸
+	//Workpiece width adjustment shaft
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク幅調整軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis14】 ワーク幅調整軸';</v>
+			strRt	:= 'Workpiece width adjustment shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 Workpiece width adjustment shaft';</v>
       </c>
       <c r="AE16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク幅調整軸
+	//Workpiece width adjustment shaft
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク幅調整軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis14】 ワーク幅調整軸';
+			strRt	:= 'Workpiece width adjustment shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 Workpiece width adjustment shaft';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク幅調整軸
+	//Workpiece width adjustment shaft
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク幅調整軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis14】 ワーク幅調整軸';
+			strRt	:= 'Workpiece width adjustment shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 Workpiece width adjustment shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-M040AK';</v>
       </c>
       <c r="AG16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク幅調整軸
+	//Workpiece width adjustment shaft
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク幅調整軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis14】 ワーク幅調整軸';
+			strRt	:= 'Workpiece width adjustment shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 Workpiece width adjustment shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-M040AK';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7819,12 +7820,12 @@
       <c r="AH16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク幅調整軸
+	//Workpiece width adjustment shaft
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク幅調整軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis14】 ワーク幅調整軸';
+			strRt	:= 'Workpiece width adjustment shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 Workpiece width adjustment shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-M040AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7833,12 +7834,12 @@
       <c r="AI16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク幅調整軸
+	//Workpiece width adjustment shaft
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク幅調整軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis14】 ワーク幅調整軸';
+			strRt	:= 'Workpiece width adjustment shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 Workpiece width adjustment shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-M040AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7850,12 +7851,12 @@
       <c r="AJ16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク幅調整軸
+	//Workpiece width adjustment shaft
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク幅調整軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis14】 ワーク幅調整軸';
+			strRt	:= 'Workpiece width adjustment shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 Workpiece width adjustment shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-M040AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7867,12 +7868,12 @@
       <c r="AK16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ワーク幅調整軸
+	//Workpiece width adjustment shaft
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク幅調整軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis14】 ワーク幅調整軸';
+			strRt	:= 'Workpiece width adjustment shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 Workpiece width adjustment shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-M040AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7899,15 +7900,15 @@
       </c>
       <c r="I17" t="str">
         <f ca="1"/>
-        <v>Tロール回転軸</v>
+        <v>T-roll rotation shaft</v>
       </c>
       <c r="J17" t="str">
         <f ca="1"/>
-        <v>Tロール回転軸</v>
+        <v>T-roll rotation shaft</v>
       </c>
       <c r="L17" t="str">
         <f ca="1"/>
-        <v>【axis15】 Tロール回転軸</v>
+        <v>【axis15】 T-roll rotation shaft</v>
       </c>
       <c r="M17" t="str">
         <v>M540-402</v>
@@ -7936,75 +7937,75 @@
       <c r="Z17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//T-roll rotation shaft
 	ELSIF uiInfoIdx = 15 THEN</v>
       </c>
       <c r="AA17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//T-roll rotation shaft
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//T-roll rotation shaft
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';</v>
+			strRt	:= 'T-roll rotation shaft';</v>
       </c>
       <c r="AC17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//T-roll rotation shaft
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';
+			strRt	:= 'T-roll rotation shaft';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//T-roll rotation shaft
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 Tロール回転軸';</v>
+			strRt	:= 'T-roll rotation shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 T-roll rotation shaft';</v>
       </c>
       <c r="AE17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//T-roll rotation shaft
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 Tロール回転軸';
+			strRt	:= 'T-roll rotation shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 T-roll rotation shaft';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//T-roll rotation shaft
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 Tロール回転軸';
+			strRt	:= 'T-roll rotation shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 T-roll rotation shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';</v>
       </c>
       <c r="AG17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//T-roll rotation shaft
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 Tロール回転軸';
+			strRt	:= 'T-roll rotation shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 T-roll rotation shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8012,12 +8013,12 @@
       <c r="AH17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//T-roll rotation shaft
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 Tロール回転軸';
+			strRt	:= 'T-roll rotation shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 T-roll rotation shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8026,12 +8027,12 @@
       <c r="AI17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//T-roll rotation shaft
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 Tロール回転軸';
+			strRt	:= 'T-roll rotation shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 T-roll rotation shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8043,12 +8044,12 @@
       <c r="AJ17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//T-roll rotation shaft
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 Tロール回転軸';
+			strRt	:= 'T-roll rotation shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 T-roll rotation shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8060,12 +8061,12 @@
       <c r="AK17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//T-roll rotation shaft
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 Tロール回転軸';
+			strRt	:= 'T-roll rotation shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 T-roll rotation shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8092,15 +8093,15 @@
       </c>
       <c r="I18" t="str">
         <f ca="1"/>
-        <v>ロータユニットXロール回転軸</v>
+        <v>Rotor unit X-roll rotation shaft</v>
       </c>
       <c r="J18" t="str">
         <f ca="1"/>
-        <v>ロータユニットXロール回転軸</v>
+        <v>Rotor unit X-roll rotation shaft</v>
       </c>
       <c r="L18" t="str">
         <f ca="1"/>
-        <v>【axis16】 ロータユニットXロール回転軸</v>
+        <v>【axis16】 Rotor unit X-roll rotation shaft</v>
       </c>
       <c r="M18" t="str">
         <v>M540-402</v>
@@ -8129,75 +8130,75 @@
       <c r="Z18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ロータユニットXロール回転軸
+	//Rotor unit X-roll rotation shaft
 	ELSIF uiInfoIdx = 16 THEN</v>
       </c>
       <c r="AA18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ロータユニットXロール回転軸
+	//Rotor unit X-roll rotation shaft
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ロータユニットXロール回転軸
+	//Rotor unit X-roll rotation shaft
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ロータユニットXロール回転軸';</v>
+			strRt	:= 'Rotor unit X-roll rotation shaft';</v>
       </c>
       <c r="AC18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ロータユニットXロール回転軸
+	//Rotor unit X-roll rotation shaft
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ロータユニットXロール回転軸';
+			strRt	:= 'Rotor unit X-roll rotation shaft';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ロータユニットXロール回転軸
+	//Rotor unit X-roll rotation shaft
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ロータユニットXロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis16】 ロータユニットXロール回転軸';</v>
+			strRt	:= 'Rotor unit X-roll rotation shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 Rotor unit X-roll rotation shaft';</v>
       </c>
       <c r="AE18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ロータユニットXロール回転軸
+	//Rotor unit X-roll rotation shaft
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ロータユニットXロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis16】 ロータユニットXロール回転軸';
+			strRt	:= 'Rotor unit X-roll rotation shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 Rotor unit X-roll rotation shaft';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ロータユニットXロール回転軸
+	//Rotor unit X-roll rotation shaft
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ロータユニットXロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis16】 ロータユニットXロール回転軸';
+			strRt	:= 'Rotor unit X-roll rotation shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 Rotor unit X-roll rotation shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';</v>
       </c>
       <c r="AG18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ロータユニットXロール回転軸
+	//Rotor unit X-roll rotation shaft
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ロータユニットXロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis16】 ロータユニットXロール回転軸';
+			strRt	:= 'Rotor unit X-roll rotation shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 Rotor unit X-roll rotation shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8205,12 +8206,12 @@
       <c r="AH18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ロータユニットXロール回転軸
+	//Rotor unit X-roll rotation shaft
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ロータユニットXロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis16】 ロータユニットXロール回転軸';
+			strRt	:= 'Rotor unit X-roll rotation shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 Rotor unit X-roll rotation shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8219,12 +8220,12 @@
       <c r="AI18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ロータユニットXロール回転軸
+	//Rotor unit X-roll rotation shaft
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ロータユニットXロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis16】 ロータユニットXロール回転軸';
+			strRt	:= 'Rotor unit X-roll rotation shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 Rotor unit X-roll rotation shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8236,12 +8237,12 @@
       <c r="AJ18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ロータユニットXロール回転軸
+	//Rotor unit X-roll rotation shaft
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ロータユニットXロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis16】 ロータユニットXロール回転軸';
+			strRt	:= 'Rotor unit X-roll rotation shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 Rotor unit X-roll rotation shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8253,12 +8254,12 @@
       <c r="AK18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//ロータユニットXロール回転軸
+	//Rotor unit X-roll rotation shaft
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ロータユニットXロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis16】 ロータユニットXロール回転軸';
+			strRt	:= 'Rotor unit X-roll rotation shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 Rotor unit X-roll rotation shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8662,10 +8663,10 @@
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="str">
         <f t="shared" si="0"/>
@@ -8864,10 +8865,10 @@
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B25" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E25" t="str">
         <f t="shared" si="0"/>
@@ -8968,10 +8969,10 @@
     </row>
     <row r="26" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B26" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E26" t="str">
         <f t="shared" si="0"/>
@@ -9072,10 +9073,10 @@
     </row>
     <row r="27" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E27" t="str">
         <f t="shared" si="0"/>
@@ -9176,10 +9177,10 @@
     </row>
     <row r="28" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B28" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E28" t="str">
         <f t="shared" si="0"/>
@@ -9280,10 +9281,10 @@
     </row>
     <row r="29" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B29" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E29" t="str">
         <f t="shared" si="0"/>
@@ -10678,15 +10679,15 @@
       </c>
       <c r="I43" t="str">
         <f ca="1"/>
-        <v>ワーク排出前後軸</v>
+        <v>Workpiece discharge front and rear axis</v>
       </c>
       <c r="J43" t="str">
         <f ca="1"/>
-        <v>ワーク排出前後軸</v>
+        <v>Workpiece discharge front and rear axis</v>
       </c>
       <c r="L43" t="str">
         <f ca="1"/>
-        <v>【EC1】 ワーク排出前後軸</v>
+        <v>【EC1】 Workpiece discharge front and rear axis</v>
       </c>
       <c r="M43" t="str">
         <v>EC-S4HR-200-7-ML-TMD2</v>
@@ -10718,7 +10719,7 @@
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//ワーク排出前後軸
+	//Workpiece discharge front and rear axis
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AA43" t="str">
@@ -10726,7 +10727,7 @@
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//ワーク排出前後軸
+	//Workpiece discharge front and rear axis
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -10735,20 +10736,20 @@
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//ワーク排出前後軸
+	//Workpiece discharge front and rear axis
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出前後軸';</v>
+			strRt	:= 'Workpiece discharge front and rear axis';</v>
       </c>
       <c r="AC43" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//ワーク排出前後軸
+	//Workpiece discharge front and rear axis
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出前後軸';
+			strRt	:= 'Workpiece discharge front and rear axis';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD43" t="str">
@@ -10756,24 +10757,24 @@
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//ワーク排出前後軸
+	//Workpiece discharge front and rear axis
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出前後軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【EC1】 ワーク排出前後軸';</v>
+			strRt	:= 'Workpiece discharge front and rear axis';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 Workpiece discharge front and rear axis';</v>
       </c>
       <c r="AE43" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//ワーク排出前後軸
+	//Workpiece discharge front and rear axis
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出前後軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【EC1】 ワーク排出前後軸';
+			strRt	:= 'Workpiece discharge front and rear axis';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 Workpiece discharge front and rear axis';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF43" t="str">
@@ -10781,12 +10782,12 @@
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//ワーク排出前後軸
+	//Workpiece discharge front and rear axis
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出前後軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【EC1】 ワーク排出前後軸';
+			strRt	:= 'Workpiece discharge front and rear axis';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 Workpiece discharge front and rear axis';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'EC-S4HR-200-7-ML-TMD2';</v>
       </c>
@@ -10795,12 +10796,12 @@
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//ワーク排出前後軸
+	//Workpiece discharge front and rear axis
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出前後軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【EC1】 ワーク排出前後軸';
+			strRt	:= 'Workpiece discharge front and rear axis';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 Workpiece discharge front and rear axis';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'EC-S4HR-200-7-ML-TMD2';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10810,12 +10811,12 @@
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//ワーク排出前後軸
+	//Workpiece discharge front and rear axis
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出前後軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【EC1】 ワーク排出前後軸';
+			strRt	:= 'Workpiece discharge front and rear axis';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 Workpiece discharge front and rear axis';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'EC-S4HR-200-7-ML-TMD2';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10826,12 +10827,12 @@
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//ワーク排出前後軸
+	//Workpiece discharge front and rear axis
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出前後軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【EC1】 ワーク排出前後軸';
+			strRt	:= 'Workpiece discharge front and rear axis';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 Workpiece discharge front and rear axis';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'EC-S4HR-200-7-ML-TMD2';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10845,12 +10846,12 @@
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//ワーク排出前後軸
+	//Workpiece discharge front and rear axis
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出前後軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【EC1】 ワーク排出前後軸';
+			strRt	:= 'Workpiece discharge front and rear axis';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 Workpiece discharge front and rear axis';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'EC-S4HR-200-7-ML-TMD2';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10864,12 +10865,12 @@
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//ワーク排出前後軸
+	//Workpiece discharge front and rear axis
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出前後軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【EC1】 ワーク排出前後軸';
+			strRt	:= 'Workpiece discharge front and rear axis';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 Workpiece discharge front and rear axis';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'EC-S4HR-200-7-ML-TMD2';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12763,15 +12764,15 @@
       </c>
       <c r="I63" t="str">
         <f ca="1"/>
-        <v>巻取り軸芯前後</v>
+        <v>Winding shaft center forward/backward</v>
       </c>
       <c r="J63" t="str">
         <f ca="1"/>
-        <v>巻取り軸芯前後</v>
+        <v>Winding shaft center forward/backward</v>
       </c>
       <c r="L63" t="str">
         <f ca="1"/>
-        <v>【cylinder1】 巻取り軸芯前後</v>
+        <v>【cylinder1】 Winding shaft center forward/backward</v>
       </c>
       <c r="M63" t="str">
         <v>CDQ2A63-200DCZ-M9BVZ</v>
@@ -12803,7 +12804,7 @@
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//巻取り軸芯前後
+	//Winding shaft center forward/backward
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AA63" t="str">
@@ -12811,7 +12812,7 @@
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//巻取り軸芯前後
+	//Winding shaft center forward/backward
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -12820,20 +12821,20 @@
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//巻取り軸芯前後
+	//Winding shaft center forward/backward
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り軸芯前後';</v>
+			strRt	:= 'Winding shaft center forward/backward';</v>
       </c>
       <c r="AC63" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//巻取り軸芯前後
+	//Winding shaft center forward/backward
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り軸芯前後';
+			strRt	:= 'Winding shaft center forward/backward';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD63" t="str">
@@ -12841,24 +12842,24 @@
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//巻取り軸芯前後
+	//Winding shaft center forward/backward
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り軸芯前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder1】 巻取り軸芯前後';</v>
+			strRt	:= 'Winding shaft center forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 Winding shaft center forward/backward';</v>
       </c>
       <c r="AE63" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//巻取り軸芯前後
+	//Winding shaft center forward/backward
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り軸芯前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder1】 巻取り軸芯前後';
+			strRt	:= 'Winding shaft center forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 Winding shaft center forward/backward';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF63" t="str">
@@ -12866,12 +12867,12 @@
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//巻取り軸芯前後
+	//Winding shaft center forward/backward
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り軸芯前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder1】 巻取り軸芯前後';
+			strRt	:= 'Winding shaft center forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 Winding shaft center forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';</v>
       </c>
@@ -12880,12 +12881,12 @@
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//巻取り軸芯前後
+	//Winding shaft center forward/backward
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り軸芯前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder1】 巻取り軸芯前後';
+			strRt	:= 'Winding shaft center forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 Winding shaft center forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12895,12 +12896,12 @@
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//巻取り軸芯前後
+	//Winding shaft center forward/backward
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り軸芯前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder1】 巻取り軸芯前後';
+			strRt	:= 'Winding shaft center forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 Winding shaft center forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12911,12 +12912,12 @@
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//巻取り軸芯前後
+	//Winding shaft center forward/backward
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り軸芯前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder1】 巻取り軸芯前後';
+			strRt	:= 'Winding shaft center forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 Winding shaft center forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12930,12 +12931,12 @@
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//巻取り軸芯前後
+	//Winding shaft center forward/backward
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り軸芯前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder1】 巻取り軸芯前後';
+			strRt	:= 'Winding shaft center forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 Winding shaft center forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12949,12 +12950,12 @@
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//巻取り軸芯前後
+	//Winding shaft center forward/backward
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り軸芯前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder1】 巻取り軸芯前後';
+			strRt	:= 'Winding shaft center forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 Winding shaft center forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12981,15 +12982,15 @@
       </c>
       <c r="I64" t="str">
         <f ca="1"/>
-        <v>Tロール糊付け①</v>
+        <v>T-roll gluing ①</v>
       </c>
       <c r="J64" t="str">
         <f ca="1"/>
-        <v>Tロール糊付け①</v>
+        <v>T-roll gluing ①</v>
       </c>
       <c r="L64" t="str">
         <f ca="1"/>
-        <v>【cylinder2】 Tロール糊付け①</v>
+        <v>【cylinder2】 T-roll gluing ①</v>
       </c>
       <c r="M64" t="str">
         <v>CDAS16×10-B-R</v>
@@ -13018,75 +13019,75 @@
       <c r="Z64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け①
+	//T-roll gluing ①
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AA64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け①
+	//T-roll gluing ①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け①
+	//T-roll gluing ①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け①';</v>
+			strRt	:= 'T-roll gluing ①';</v>
       </c>
       <c r="AC64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け①
+	//T-roll gluing ①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け①';
+			strRt	:= 'T-roll gluing ①';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け①
+	//T-roll gluing ①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder2】 Tロール糊付け①';</v>
+			strRt	:= 'T-roll gluing ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 T-roll gluing ①';</v>
       </c>
       <c r="AE64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け①
+	//T-roll gluing ①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder2】 Tロール糊付け①';
+			strRt	:= 'T-roll gluing ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 T-roll gluing ①';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け①
+	//T-roll gluing ①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder2】 Tロール糊付け①';
+			strRt	:= 'T-roll gluing ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 T-roll gluing ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';</v>
       </c>
       <c r="AG64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け①
+	//T-roll gluing ①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder2】 Tロール糊付け①';
+			strRt	:= 'T-roll gluing ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 T-roll gluing ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13094,12 +13095,12 @@
       <c r="AH64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け①
+	//T-roll gluing ①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder2】 Tロール糊付け①';
+			strRt	:= 'T-roll gluing ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 T-roll gluing ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13108,12 +13109,12 @@
       <c r="AI64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け①
+	//T-roll gluing ①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder2】 Tロール糊付け①';
+			strRt	:= 'T-roll gluing ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 T-roll gluing ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13125,12 +13126,12 @@
       <c r="AJ64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け①
+	//T-roll gluing ①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder2】 Tロール糊付け①';
+			strRt	:= 'T-roll gluing ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 T-roll gluing ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13142,12 +13143,12 @@
       <c r="AK64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け①
+	//T-roll gluing ①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder2】 Tロール糊付け①';
+			strRt	:= 'T-roll gluing ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 T-roll gluing ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13174,15 +13175,15 @@
       </c>
       <c r="I65" t="str">
         <f ca="1"/>
-        <v>Tロール糊付け②</v>
+        <v>T-roll gluing ②</v>
       </c>
       <c r="J65" t="str">
         <f ca="1"/>
-        <v>Tロール糊付け②</v>
+        <v>T-roll gluing ②</v>
       </c>
       <c r="L65" t="str">
         <f ca="1"/>
-        <v>【cylinder3】 Tロール糊付け②</v>
+        <v>【cylinder3】 T-roll gluing ②</v>
       </c>
       <c r="M65" t="str">
         <v>CDAS16×10-B-R</v>
@@ -13211,75 +13212,75 @@
       <c r="Z65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け②
+	//T-roll gluing ②
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AA65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け②
+	//T-roll gluing ②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け②
+	//T-roll gluing ②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け②';</v>
+			strRt	:= 'T-roll gluing ②';</v>
       </c>
       <c r="AC65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け②
+	//T-roll gluing ②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け②';
+			strRt	:= 'T-roll gluing ②';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け②
+	//T-roll gluing ②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder3】 Tロール糊付け②';</v>
+			strRt	:= 'T-roll gluing ②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 T-roll gluing ②';</v>
       </c>
       <c r="AE65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け②
+	//T-roll gluing ②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder3】 Tロール糊付け②';
+			strRt	:= 'T-roll gluing ②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 T-roll gluing ②';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け②
+	//T-roll gluing ②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder3】 Tロール糊付け②';
+			strRt	:= 'T-roll gluing ②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 T-roll gluing ②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';</v>
       </c>
       <c r="AG65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け②
+	//T-roll gluing ②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder3】 Tロール糊付け②';
+			strRt	:= 'T-roll gluing ②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 T-roll gluing ②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13287,12 +13288,12 @@
       <c r="AH65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け②
+	//T-roll gluing ②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder3】 Tロール糊付け②';
+			strRt	:= 'T-roll gluing ②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 T-roll gluing ②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13301,12 +13302,12 @@
       <c r="AI65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け②
+	//T-roll gluing ②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder3】 Tロール糊付け②';
+			strRt	:= 'T-roll gluing ②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 T-roll gluing ②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13318,12 +13319,12 @@
       <c r="AJ65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け②
+	//T-roll gluing ②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder3】 Tロール糊付け②';
+			strRt	:= 'T-roll gluing ②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 T-roll gluing ②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13335,12 +13336,12 @@
       <c r="AK65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール糊付け②
+	//T-roll gluing ②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder3】 Tロール糊付け②';
+			strRt	:= 'T-roll gluing ②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 T-roll gluing ②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13367,15 +13368,15 @@
       </c>
       <c r="I66" t="str">
         <f ca="1"/>
-        <v>平板下側補助プレート逃がし</v>
+        <v>Flat sheet lower auxiliary plate release</v>
       </c>
       <c r="J66" t="str">
         <f ca="1"/>
-        <v>平板下側補助プレート逃がし</v>
+        <v>Flat sheet lower auxiliary plate release</v>
       </c>
       <c r="L66" t="str">
         <f ca="1"/>
-        <v>【cylinder4】 平板下側補助プレート逃がし</v>
+        <v>【cylinder4】 Flat sheet lower auxiliary plate release</v>
       </c>
       <c r="M66" t="str">
         <v>CDJ2D16-45Z-W-M9BWZ-B</v>
@@ -13404,75 +13405,75 @@
       <c r="Z66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板下側補助プレート逃がし
+	//Flat sheet lower auxiliary plate release
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AA66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板下側補助プレート逃がし
+	//Flat sheet lower auxiliary plate release
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板下側補助プレート逃がし
+	//Flat sheet lower auxiliary plate release
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板下側補助プレート逃がし';</v>
+			strRt	:= 'Flat sheet lower auxiliary plate release';</v>
       </c>
       <c r="AC66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板下側補助プレート逃がし
+	//Flat sheet lower auxiliary plate release
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板下側補助プレート逃がし';
+			strRt	:= 'Flat sheet lower auxiliary plate release';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板下側補助プレート逃がし
+	//Flat sheet lower auxiliary plate release
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板下側補助プレート逃がし';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder4】 平板下側補助プレート逃がし';</v>
+			strRt	:= 'Flat sheet lower auxiliary plate release';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 Flat sheet lower auxiliary plate release';</v>
       </c>
       <c r="AE66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板下側補助プレート逃がし
+	//Flat sheet lower auxiliary plate release
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板下側補助プレート逃がし';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder4】 平板下側補助プレート逃がし';
+			strRt	:= 'Flat sheet lower auxiliary plate release';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 Flat sheet lower auxiliary plate release';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板下側補助プレート逃がし
+	//Flat sheet lower auxiliary plate release
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板下側補助プレート逃がし';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder4】 平板下側補助プレート逃がし';
+			strRt	:= 'Flat sheet lower auxiliary plate release';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 Flat sheet lower auxiliary plate release';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';</v>
       </c>
       <c r="AG66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板下側補助プレート逃がし
+	//Flat sheet lower auxiliary plate release
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板下側補助プレート逃がし';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder4】 平板下側補助プレート逃がし';
+			strRt	:= 'Flat sheet lower auxiliary plate release';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 Flat sheet lower auxiliary plate release';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13480,12 +13481,12 @@
       <c r="AH66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板下側補助プレート逃がし
+	//Flat sheet lower auxiliary plate release
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板下側補助プレート逃がし';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder4】 平板下側補助プレート逃がし';
+			strRt	:= 'Flat sheet lower auxiliary plate release';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 Flat sheet lower auxiliary plate release';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13494,12 +13495,12 @@
       <c r="AI66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板下側補助プレート逃がし
+	//Flat sheet lower auxiliary plate release
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板下側補助プレート逃がし';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder4】 平板下側補助プレート逃がし';
+			strRt	:= 'Flat sheet lower auxiliary plate release';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 Flat sheet lower auxiliary plate release';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13511,12 +13512,12 @@
       <c r="AJ66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板下側補助プレート逃がし
+	//Flat sheet lower auxiliary plate release
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板下側補助プレート逃がし';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder4】 平板下側補助プレート逃がし';
+			strRt	:= 'Flat sheet lower auxiliary plate release';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 Flat sheet lower auxiliary plate release';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13528,12 +13529,12 @@
       <c r="AK66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板下側補助プレート逃がし
+	//Flat sheet lower auxiliary plate release
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板下側補助プレート逃がし';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder4】 平板下側補助プレート逃がし';
+			strRt	:= 'Flat sheet lower auxiliary plate release';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 Flat sheet lower auxiliary plate release';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13560,15 +13561,15 @@
       </c>
       <c r="I67" t="str">
         <f ca="1"/>
-        <v>平板チャック(ハンド)前後</v>
+        <v>Flat sheet chuck (hand) forward/backward</v>
       </c>
       <c r="J67" t="str">
         <f ca="1"/>
-        <v>平板チャック(ハンド)前後</v>
+        <v>Flat sheet chuck (hand) forward/backward</v>
       </c>
       <c r="L67" t="str">
         <f ca="1"/>
-        <v>【cylinder5】 平板チャック(ハンド)前後</v>
+        <v>【cylinder5】 Flat sheet chuck (hand) forward/backward</v>
       </c>
       <c r="M67" t="str">
         <v>MXQ20-50A-M9BZ</v>
@@ -13597,75 +13598,75 @@
       <c r="Z67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック(ハンド)前後
+	//Flat sheet chuck (hand) forward/backward
 	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AA67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック(ハンド)前後
+	//Flat sheet chuck (hand) forward/backward
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック(ハンド)前後
+	//Flat sheet chuck (hand) forward/backward
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック(ハンド)前後';</v>
+			strRt	:= 'Flat sheet chuck (hand) forward/backward';</v>
       </c>
       <c r="AC67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック(ハンド)前後
+	//Flat sheet chuck (hand) forward/backward
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック(ハンド)前後';
+			strRt	:= 'Flat sheet chuck (hand) forward/backward';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック(ハンド)前後
+	//Flat sheet chuck (hand) forward/backward
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック(ハンド)前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';</v>
+			strRt	:= 'Flat sheet chuck (hand) forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 Flat sheet chuck (hand) forward/backward';</v>
       </c>
       <c r="AE67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック(ハンド)前後
+	//Flat sheet chuck (hand) forward/backward
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック(ハンド)前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
+			strRt	:= 'Flat sheet chuck (hand) forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 Flat sheet chuck (hand) forward/backward';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック(ハンド)前後
+	//Flat sheet chuck (hand) forward/backward
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック(ハンド)前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
+			strRt	:= 'Flat sheet chuck (hand) forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 Flat sheet chuck (hand) forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MXQ20-50A-M9BZ';</v>
       </c>
       <c r="AG67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック(ハンド)前後
+	//Flat sheet chuck (hand) forward/backward
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック(ハンド)前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
+			strRt	:= 'Flat sheet chuck (hand) forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 Flat sheet chuck (hand) forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MXQ20-50A-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13673,12 +13674,12 @@
       <c r="AH67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック(ハンド)前後
+	//Flat sheet chuck (hand) forward/backward
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック(ハンド)前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
+			strRt	:= 'Flat sheet chuck (hand) forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 Flat sheet chuck (hand) forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MXQ20-50A-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13687,12 +13688,12 @@
       <c r="AI67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック(ハンド)前後
+	//Flat sheet chuck (hand) forward/backward
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック(ハンド)前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
+			strRt	:= 'Flat sheet chuck (hand) forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 Flat sheet chuck (hand) forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MXQ20-50A-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13704,12 +13705,12 @@
       <c r="AJ67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック(ハンド)前後
+	//Flat sheet chuck (hand) forward/backward
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック(ハンド)前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
+			strRt	:= 'Flat sheet chuck (hand) forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 Flat sheet chuck (hand) forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MXQ20-50A-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13721,12 +13722,12 @@
       <c r="AK67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック(ハンド)前後
+	//Flat sheet chuck (hand) forward/backward
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック(ハンド)前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
+			strRt	:= 'Flat sheet chuck (hand) forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 Flat sheet chuck (hand) forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MXQ20-50A-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13753,15 +13754,15 @@
       </c>
       <c r="I68" t="str">
         <f ca="1"/>
-        <v>平板チャック開閉</v>
+        <v>Flat sheet chuck open/close</v>
       </c>
       <c r="J68" t="str">
         <f ca="1"/>
-        <v>平板チャック開閉</v>
+        <v>Flat sheet chuck open/close</v>
       </c>
       <c r="L68" t="str">
         <f ca="1"/>
-        <v>【cylinder6】 平板チャック開閉</v>
+        <v>【cylinder6】 Flat sheet chuck open/close</v>
       </c>
       <c r="M68" t="str">
         <v>MHF2-16D1-M9BL-X83C1</v>
@@ -13790,75 +13791,75 @@
       <c r="Z68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック開閉
+	//Flat sheet chuck open/close
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AA68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック開閉
+	//Flat sheet chuck open/close
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック開閉
+	//Flat sheet chuck open/close
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック開閉';</v>
+			strRt	:= 'Flat sheet chuck open/close';</v>
       </c>
       <c r="AC68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック開閉
+	//Flat sheet chuck open/close
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック開閉';
+			strRt	:= 'Flat sheet chuck open/close';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック開閉
+	//Flat sheet chuck open/close
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder6】 平板チャック開閉';</v>
+			strRt	:= 'Flat sheet chuck open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 Flat sheet chuck open/close';</v>
       </c>
       <c r="AE68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック開閉
+	//Flat sheet chuck open/close
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder6】 平板チャック開閉';
+			strRt	:= 'Flat sheet chuck open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 Flat sheet chuck open/close';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック開閉
+	//Flat sheet chuck open/close
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder6】 平板チャック開閉';
+			strRt	:= 'Flat sheet chuck open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 Flat sheet chuck open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MHF2-16D1-M9BL-X83C1';</v>
       </c>
       <c r="AG68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック開閉
+	//Flat sheet chuck open/close
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder6】 平板チャック開閉';
+			strRt	:= 'Flat sheet chuck open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 Flat sheet chuck open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MHF2-16D1-M9BL-X83C1';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13866,12 +13867,12 @@
       <c r="AH68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック開閉
+	//Flat sheet chuck open/close
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder6】 平板チャック開閉';
+			strRt	:= 'Flat sheet chuck open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 Flat sheet chuck open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MHF2-16D1-M9BL-X83C1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13880,12 +13881,12 @@
       <c r="AI68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック開閉
+	//Flat sheet chuck open/close
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder6】 平板チャック開閉';
+			strRt	:= 'Flat sheet chuck open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 Flat sheet chuck open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MHF2-16D1-M9BL-X83C1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13897,12 +13898,12 @@
       <c r="AJ68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック開閉
+	//Flat sheet chuck open/close
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder6】 平板チャック開閉';
+			strRt	:= 'Flat sheet chuck open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 Flat sheet chuck open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MHF2-16D1-M9BL-X83C1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13914,12 +13915,12 @@
       <c r="AK68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板チャック開閉
+	//Flat sheet chuck open/close
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder6】 平板チャック開閉';
+			strRt	:= 'Flat sheet chuck open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 Flat sheet chuck open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MHF2-16D1-M9BL-X83C1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13946,15 +13947,15 @@
       </c>
       <c r="I69" t="str">
         <f ca="1"/>
-        <v>平板押え上下①</v>
+        <v>Flat sheet clamp up/down ①</v>
       </c>
       <c r="J69" t="str">
         <f ca="1"/>
-        <v>平板押え上下①</v>
+        <v>Flat sheet clamp up/down ①</v>
       </c>
       <c r="L69" t="str">
         <f ca="1"/>
-        <v>【cylinder7】 平板押え上下①</v>
+        <v>【cylinder7】 Flat sheet clamp up/down ①</v>
       </c>
       <c r="M69" t="str">
         <v>CDQ2B25-20DZ-M9BVM</v>
@@ -13983,75 +13984,75 @@
       <c r="Z69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//Flat sheet clamp up/down ①
 	ELSIF uiInfoIdx = 7 THEN</v>
       </c>
       <c r="AA69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//Flat sheet clamp up/down ①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//Flat sheet clamp up/down ①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';</v>
+			strRt	:= 'Flat sheet clamp up/down ①';</v>
       </c>
       <c r="AC69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//Flat sheet clamp up/down ①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';
+			strRt	:= 'Flat sheet clamp up/down ①';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//Flat sheet clamp up/down ①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 平板押え上下①';</v>
+			strRt	:= 'Flat sheet clamp up/down ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 Flat sheet clamp up/down ①';</v>
       </c>
       <c r="AE69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//Flat sheet clamp up/down ①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= 'Flat sheet clamp up/down ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 Flat sheet clamp up/down ①';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//Flat sheet clamp up/down ①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= 'Flat sheet clamp up/down ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 Flat sheet clamp up/down ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';</v>
       </c>
       <c r="AG69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//Flat sheet clamp up/down ①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= 'Flat sheet clamp up/down ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 Flat sheet clamp up/down ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14059,12 +14060,12 @@
       <c r="AH69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//Flat sheet clamp up/down ①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= 'Flat sheet clamp up/down ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 Flat sheet clamp up/down ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14073,12 +14074,12 @@
       <c r="AI69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//Flat sheet clamp up/down ①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= 'Flat sheet clamp up/down ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 Flat sheet clamp up/down ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14090,12 +14091,12 @@
       <c r="AJ69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//Flat sheet clamp up/down ①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= 'Flat sheet clamp up/down ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 Flat sheet clamp up/down ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14107,12 +14108,12 @@
       <c r="AK69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//Flat sheet clamp up/down ①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= 'Flat sheet clamp up/down ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 Flat sheet clamp up/down ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14139,15 +14140,15 @@
       </c>
       <c r="I70" t="str">
         <f ca="1"/>
-        <v>箔ロウ押え上下</v>
+        <v>Foil wax clamp up/down</v>
       </c>
       <c r="J70" t="str">
         <f ca="1"/>
-        <v>箔ロウ押え上下</v>
+        <v>Foil wax clamp up/down</v>
       </c>
       <c r="L70" t="str">
         <f ca="1"/>
-        <v>【cylinder8】 箔ロウ押え上下</v>
+        <v>【cylinder8】 Foil wax clamp up/down</v>
       </c>
       <c r="M70" t="str">
         <v>CDQ2D25-20DMZ-M9BM</v>
@@ -14176,75 +14177,75 @@
       <c r="Z70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ押え上下
+	//Foil wax clamp up/down
 	ELSIF uiInfoIdx = 8 THEN</v>
       </c>
       <c r="AA70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ押え上下
+	//Foil wax clamp up/down
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ押え上下
+	//Foil wax clamp up/down
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ押え上下';</v>
+			strRt	:= 'Foil wax clamp up/down';</v>
       </c>
       <c r="AC70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ押え上下
+	//Foil wax clamp up/down
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ押え上下';
+			strRt	:= 'Foil wax clamp up/down';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ押え上下
+	//Foil wax clamp up/down
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ押え上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder8】 箔ロウ押え上下';</v>
+			strRt	:= 'Foil wax clamp up/down';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 Foil wax clamp up/down';</v>
       </c>
       <c r="AE70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ押え上下
+	//Foil wax clamp up/down
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ押え上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder8】 箔ロウ押え上下';
+			strRt	:= 'Foil wax clamp up/down';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 Foil wax clamp up/down';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ押え上下
+	//Foil wax clamp up/down
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ押え上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder8】 箔ロウ押え上下';
+			strRt	:= 'Foil wax clamp up/down';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 Foil wax clamp up/down';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2D25-20DMZ-M9BM';</v>
       </c>
       <c r="AG70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ押え上下
+	//Foil wax clamp up/down
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ押え上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder8】 箔ロウ押え上下';
+			strRt	:= 'Foil wax clamp up/down';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 Foil wax clamp up/down';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2D25-20DMZ-M9BM';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14252,12 +14253,12 @@
       <c r="AH70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ押え上下
+	//Foil wax clamp up/down
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ押え上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder8】 箔ロウ押え上下';
+			strRt	:= 'Foil wax clamp up/down';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 Foil wax clamp up/down';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2D25-20DMZ-M9BM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14266,12 +14267,12 @@
       <c r="AI70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ押え上下
+	//Foil wax clamp up/down
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ押え上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder8】 箔ロウ押え上下';
+			strRt	:= 'Foil wax clamp up/down';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 Foil wax clamp up/down';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2D25-20DMZ-M9BM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14283,12 +14284,12 @@
       <c r="AJ70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ押え上下
+	//Foil wax clamp up/down
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ押え上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder8】 箔ロウ押え上下';
+			strRt	:= 'Foil wax clamp up/down';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 Foil wax clamp up/down';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2D25-20DMZ-M9BM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14300,12 +14301,12 @@
       <c r="AK70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ押え上下
+	//Foil wax clamp up/down
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ押え上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder8】 箔ロウ押え上下';
+			strRt	:= 'Foil wax clamp up/down';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 Foil wax clamp up/down';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2D25-20DMZ-M9BM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14332,15 +14333,15 @@
       </c>
       <c r="I71" t="str">
         <f ca="1"/>
-        <v>箔ロウカット</v>
+        <v>Foil wax cut</v>
       </c>
       <c r="J71" t="str">
         <f ca="1"/>
-        <v>箔ロウカット</v>
+        <v>Foil wax cut</v>
       </c>
       <c r="L71" t="str">
         <f ca="1"/>
-        <v>【cylinder9】 箔ロウカット</v>
+        <v>【cylinder9】 Foil wax cut</v>
       </c>
       <c r="M71" t="str">
         <v>CDQSKB16-10DM-M9NWVZ</v>
@@ -14369,75 +14370,75 @@
       <c r="Z71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウカット
+	//Foil wax cut
 	ELSIF uiInfoIdx = 9 THEN</v>
       </c>
       <c r="AA71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウカット
+	//Foil wax cut
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウカット
+	//Foil wax cut
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウカット';</v>
+			strRt	:= 'Foil wax cut';</v>
       </c>
       <c r="AC71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウカット
+	//Foil wax cut
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウカット';
+			strRt	:= 'Foil wax cut';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウカット
+	//Foil wax cut
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウカット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder9】 箔ロウカット';</v>
+			strRt	:= 'Foil wax cut';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 Foil wax cut';</v>
       </c>
       <c r="AE71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウカット
+	//Foil wax cut
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウカット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder9】 箔ロウカット';
+			strRt	:= 'Foil wax cut';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 Foil wax cut';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウカット
+	//Foil wax cut
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウカット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder9】 箔ロウカット';
+			strRt	:= 'Foil wax cut';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 Foil wax cut';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQSKB16-10DM-M9NWVZ';</v>
       </c>
       <c r="AG71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウカット
+	//Foil wax cut
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウカット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder9】 箔ロウカット';
+			strRt	:= 'Foil wax cut';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 Foil wax cut';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQSKB16-10DM-M9NWVZ';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14445,12 +14446,12 @@
       <c r="AH71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウカット
+	//Foil wax cut
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウカット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder9】 箔ロウカット';
+			strRt	:= 'Foil wax cut';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 Foil wax cut';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQSKB16-10DM-M9NWVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14459,12 +14460,12 @@
       <c r="AI71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウカット
+	//Foil wax cut
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウカット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder9】 箔ロウカット';
+			strRt	:= 'Foil wax cut';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 Foil wax cut';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQSKB16-10DM-M9NWVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14476,12 +14477,12 @@
       <c r="AJ71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウカット
+	//Foil wax cut
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウカット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder9】 箔ロウカット';
+			strRt	:= 'Foil wax cut';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 Foil wax cut';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQSKB16-10DM-M9NWVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14493,12 +14494,12 @@
       <c r="AK71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウカット
+	//Foil wax cut
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウカット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder9】 箔ロウカット';
+			strRt	:= 'Foil wax cut';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 Foil wax cut';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQSKB16-10DM-M9NWVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14525,15 +14526,15 @@
       </c>
       <c r="I72" t="str">
         <f ca="1"/>
-        <v>波板押え</v>
+        <v>Corrugated sheet clamp</v>
       </c>
       <c r="J72" t="str">
         <f ca="1"/>
-        <v>波板押え</v>
+        <v>Corrugated sheet clamp</v>
       </c>
       <c r="L72" t="str">
         <f ca="1"/>
-        <v>【cylinder10】 波板押え</v>
+        <v>【cylinder10】 Corrugated sheet clamp</v>
       </c>
       <c r="M72" t="str">
         <v>CDQ2B25-20DZ-M9BVM</v>
@@ -14562,75 +14563,75 @@
       <c r="Z72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板押え
+	//Corrugated sheet clamp
 	ELSIF uiInfoIdx = 10 THEN</v>
       </c>
       <c r="AA72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板押え
+	//Corrugated sheet clamp
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板押え
+	//Corrugated sheet clamp
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板押え';</v>
+			strRt	:= 'Corrugated sheet clamp';</v>
       </c>
       <c r="AC72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板押え
+	//Corrugated sheet clamp
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板押え';
+			strRt	:= 'Corrugated sheet clamp';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板押え
+	//Corrugated sheet clamp
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板押え';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder10】 波板押え';</v>
+			strRt	:= 'Corrugated sheet clamp';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 Corrugated sheet clamp';</v>
       </c>
       <c r="AE72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板押え
+	//Corrugated sheet clamp
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板押え';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder10】 波板押え';
+			strRt	:= 'Corrugated sheet clamp';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 Corrugated sheet clamp';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板押え
+	//Corrugated sheet clamp
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板押え';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder10】 波板押え';
+			strRt	:= 'Corrugated sheet clamp';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 Corrugated sheet clamp';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';</v>
       </c>
       <c r="AG72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板押え
+	//Corrugated sheet clamp
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板押え';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder10】 波板押え';
+			strRt	:= 'Corrugated sheet clamp';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 Corrugated sheet clamp';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14638,12 +14639,12 @@
       <c r="AH72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板押え
+	//Corrugated sheet clamp
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板押え';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder10】 波板押え';
+			strRt	:= 'Corrugated sheet clamp';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 Corrugated sheet clamp';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14652,12 +14653,12 @@
       <c r="AI72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板押え
+	//Corrugated sheet clamp
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板押え';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder10】 波板押え';
+			strRt	:= 'Corrugated sheet clamp';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 Corrugated sheet clamp';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14669,12 +14670,12 @@
       <c r="AJ72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板押え
+	//Corrugated sheet clamp
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板押え';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder10】 波板押え';
+			strRt	:= 'Corrugated sheet clamp';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 Corrugated sheet clamp';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14686,12 +14687,12 @@
       <c r="AK72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板押え
+	//Corrugated sheet clamp
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板押え';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder10】 波板押え';
+			strRt	:= 'Corrugated sheet clamp';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 Corrugated sheet clamp';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14718,15 +14719,15 @@
       </c>
       <c r="I73" t="str">
         <f ca="1"/>
-        <v>平板カット刃押出し</v>
+        <v>Flat sheet cutter blade push-out</v>
       </c>
       <c r="J73" t="str">
         <f ca="1"/>
-        <v>平板カット刃押出し</v>
+        <v>Flat sheet cutter blade push-out</v>
       </c>
       <c r="L73" t="str">
         <f ca="1"/>
-        <v>【cylinder11】 平板カット刃押出し</v>
+        <v>【cylinder11】 Flat sheet cutter blade push-out</v>
       </c>
       <c r="M73" t="str">
         <v>CD55B32-105-M9BZ</v>
@@ -14755,75 +14756,75 @@
       <c r="Z73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃押出し
+	//Flat sheet cutter blade push-out
 	ELSIF uiInfoIdx = 11 THEN</v>
       </c>
       <c r="AA73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃押出し
+	//Flat sheet cutter blade push-out
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃押出し
+	//Flat sheet cutter blade push-out
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃押出し';</v>
+			strRt	:= 'Flat sheet cutter blade push-out';</v>
       </c>
       <c r="AC73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃押出し
+	//Flat sheet cutter blade push-out
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃押出し';
+			strRt	:= 'Flat sheet cutter blade push-out';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃押出し
+	//Flat sheet cutter blade push-out
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder11】 平板カット刃押出し';</v>
+			strRt	:= 'Flat sheet cutter blade push-out';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 Flat sheet cutter blade push-out';</v>
       </c>
       <c r="AE73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃押出し
+	//Flat sheet cutter blade push-out
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder11】 平板カット刃押出し';
+			strRt	:= 'Flat sheet cutter blade push-out';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 Flat sheet cutter blade push-out';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃押出し
+	//Flat sheet cutter blade push-out
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder11】 平板カット刃押出し';
+			strRt	:= 'Flat sheet cutter blade push-out';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 Flat sheet cutter blade push-out';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';</v>
       </c>
       <c r="AG73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃押出し
+	//Flat sheet cutter blade push-out
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder11】 平板カット刃押出し';
+			strRt	:= 'Flat sheet cutter blade push-out';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 Flat sheet cutter blade push-out';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14831,12 +14832,12 @@
       <c r="AH73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃押出し
+	//Flat sheet cutter blade push-out
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder11】 平板カット刃押出し';
+			strRt	:= 'Flat sheet cutter blade push-out';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 Flat sheet cutter blade push-out';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14845,12 +14846,12 @@
       <c r="AI73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃押出し
+	//Flat sheet cutter blade push-out
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder11】 平板カット刃押出し';
+			strRt	:= 'Flat sheet cutter blade push-out';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 Flat sheet cutter blade push-out';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14862,12 +14863,12 @@
       <c r="AJ73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃押出し
+	//Flat sheet cutter blade push-out
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder11】 平板カット刃押出し';
+			strRt	:= 'Flat sheet cutter blade push-out';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 Flat sheet cutter blade push-out';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14879,12 +14880,12 @@
       <c r="AK73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃押出し
+	//Flat sheet cutter blade push-out
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder11】 平板カット刃押出し';
+			strRt	:= 'Flat sheet cutter blade push-out';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 Flat sheet cutter blade push-out';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14911,15 +14912,15 @@
       </c>
       <c r="I74" t="str">
         <f ca="1"/>
-        <v>平板カット刃開閉</v>
+        <v>Flat sheet cutter blade open/close</v>
       </c>
       <c r="J74" t="str">
         <f ca="1"/>
-        <v>平板カット刃開閉</v>
+        <v>Flat sheet cutter blade open/close</v>
       </c>
       <c r="L74" t="str">
         <f ca="1"/>
-        <v>【cylinder12】 平板カット刃開閉</v>
+        <v>【cylinder12】 Flat sheet cutter blade open/close</v>
       </c>
       <c r="M74" t="str">
         <v>CDQ2B25-10DMZ-L-A93M</v>
@@ -14948,75 +14949,75 @@
       <c r="Z74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃開閉
+	//Flat sheet cutter blade open/close
 	ELSIF uiInfoIdx = 12 THEN</v>
       </c>
       <c r="AA74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃開閉
+	//Flat sheet cutter blade open/close
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃開閉
+	//Flat sheet cutter blade open/close
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃開閉';</v>
+			strRt	:= 'Flat sheet cutter blade open/close';</v>
       </c>
       <c r="AC74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃開閉
+	//Flat sheet cutter blade open/close
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃開閉';
+			strRt	:= 'Flat sheet cutter blade open/close';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃開閉
+	//Flat sheet cutter blade open/close
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder12】 平板カット刃開閉';</v>
+			strRt	:= 'Flat sheet cutter blade open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 Flat sheet cutter blade open/close';</v>
       </c>
       <c r="AE74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃開閉
+	//Flat sheet cutter blade open/close
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder12】 平板カット刃開閉';
+			strRt	:= 'Flat sheet cutter blade open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 Flat sheet cutter blade open/close';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃開閉
+	//Flat sheet cutter blade open/close
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder12】 平板カット刃開閉';
+			strRt	:= 'Flat sheet cutter blade open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 Flat sheet cutter blade open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-10DMZ-L-A93M';</v>
       </c>
       <c r="AG74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃開閉
+	//Flat sheet cutter blade open/close
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder12】 平板カット刃開閉';
+			strRt	:= 'Flat sheet cutter blade open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 Flat sheet cutter blade open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-10DMZ-L-A93M';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -15024,12 +15025,12 @@
       <c r="AH74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃開閉
+	//Flat sheet cutter blade open/close
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder12】 平板カット刃開閉';
+			strRt	:= 'Flat sheet cutter blade open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 Flat sheet cutter blade open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-10DMZ-L-A93M';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15038,12 +15039,12 @@
       <c r="AI74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃開閉
+	//Flat sheet cutter blade open/close
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder12】 平板カット刃開閉';
+			strRt	:= 'Flat sheet cutter blade open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 Flat sheet cutter blade open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-10DMZ-L-A93M';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15055,12 +15056,12 @@
       <c r="AJ74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃開閉
+	//Flat sheet cutter blade open/close
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder12】 平板カット刃開閉';
+			strRt	:= 'Flat sheet cutter blade open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 Flat sheet cutter blade open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-10DMZ-L-A93M';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15072,12 +15073,12 @@
       <c r="AK74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板カット刃開閉
+	//Flat sheet cutter blade open/close
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder12】 平板カット刃開閉';
+			strRt	:= 'Flat sheet cutter blade open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 Flat sheet cutter blade open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-10DMZ-L-A93M';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15104,15 +15105,15 @@
       </c>
       <c r="I75" t="str">
         <f ca="1"/>
-        <v>波板カット刃押出し</v>
+        <v>Corrugated sheet cutter blade push-out</v>
       </c>
       <c r="J75" t="str">
         <f ca="1"/>
-        <v>波板カット刃押出し</v>
+        <v>Corrugated sheet cutter blade push-out</v>
       </c>
       <c r="L75" t="str">
         <f ca="1"/>
-        <v>【cylinder13】 波板カット刃押出し</v>
+        <v>【cylinder13】 Corrugated sheet cutter blade push-out</v>
       </c>
       <c r="M75" t="str">
         <v>CD55B32-105-M9BZ</v>
@@ -15141,75 +15142,75 @@
       <c r="Z75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃押出し
+	//Corrugated sheet cutter blade push-out
 	ELSIF uiInfoIdx = 13 THEN</v>
       </c>
       <c r="AA75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃押出し
+	//Corrugated sheet cutter blade push-out
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃押出し
+	//Corrugated sheet cutter blade push-out
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃押出し';</v>
+			strRt	:= 'Corrugated sheet cutter blade push-out';</v>
       </c>
       <c r="AC75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃押出し
+	//Corrugated sheet cutter blade push-out
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃押出し';
+			strRt	:= 'Corrugated sheet cutter blade push-out';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃押出し
+	//Corrugated sheet cutter blade push-out
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder13】 波板カット刃押出し';</v>
+			strRt	:= 'Corrugated sheet cutter blade push-out';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 Corrugated sheet cutter blade push-out';</v>
       </c>
       <c r="AE75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃押出し
+	//Corrugated sheet cutter blade push-out
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder13】 波板カット刃押出し';
+			strRt	:= 'Corrugated sheet cutter blade push-out';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 Corrugated sheet cutter blade push-out';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃押出し
+	//Corrugated sheet cutter blade push-out
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder13】 波板カット刃押出し';
+			strRt	:= 'Corrugated sheet cutter blade push-out';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 Corrugated sheet cutter blade push-out';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';</v>
       </c>
       <c r="AG75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃押出し
+	//Corrugated sheet cutter blade push-out
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder13】 波板カット刃押出し';
+			strRt	:= 'Corrugated sheet cutter blade push-out';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 Corrugated sheet cutter blade push-out';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -15217,12 +15218,12 @@
       <c r="AH75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃押出し
+	//Corrugated sheet cutter blade push-out
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder13】 波板カット刃押出し';
+			strRt	:= 'Corrugated sheet cutter blade push-out';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 Corrugated sheet cutter blade push-out';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15231,12 +15232,12 @@
       <c r="AI75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃押出し
+	//Corrugated sheet cutter blade push-out
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder13】 波板カット刃押出し';
+			strRt	:= 'Corrugated sheet cutter blade push-out';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 Corrugated sheet cutter blade push-out';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15248,12 +15249,12 @@
       <c r="AJ75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃押出し
+	//Corrugated sheet cutter blade push-out
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder13】 波板カット刃押出し';
+			strRt	:= 'Corrugated sheet cutter blade push-out';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 Corrugated sheet cutter blade push-out';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15265,12 +15266,12 @@
       <c r="AK75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃押出し
+	//Corrugated sheet cutter blade push-out
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder13】 波板カット刃押出し';
+			strRt	:= 'Corrugated sheet cutter blade push-out';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 Corrugated sheet cutter blade push-out';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15297,15 +15298,15 @@
       </c>
       <c r="I76" t="str">
         <f ca="1"/>
-        <v>波板カット刃開閉</v>
+        <v>Corrugated sheet cutter blade open/close</v>
       </c>
       <c r="J76" t="str">
         <f ca="1"/>
-        <v>波板カット刃開閉</v>
+        <v>Corrugated sheet cutter blade open/close</v>
       </c>
       <c r="L76" t="str">
         <f ca="1"/>
-        <v>【cylinder14】 波板カット刃開閉</v>
+        <v>【cylinder14】 Corrugated sheet cutter blade open/close</v>
       </c>
       <c r="M76" t="str">
         <v>CDQ2B40M-15DMZ-M9BZ</v>
@@ -15334,75 +15335,75 @@
       <c r="Z76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃開閉
+	//Corrugated sheet cutter blade open/close
 	ELSIF uiInfoIdx = 14 THEN</v>
       </c>
       <c r="AA76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃開閉
+	//Corrugated sheet cutter blade open/close
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃開閉
+	//Corrugated sheet cutter blade open/close
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃開閉';</v>
+			strRt	:= 'Corrugated sheet cutter blade open/close';</v>
       </c>
       <c r="AC76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃開閉
+	//Corrugated sheet cutter blade open/close
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃開閉';
+			strRt	:= 'Corrugated sheet cutter blade open/close';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃開閉
+	//Corrugated sheet cutter blade open/close
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder14】 波板カット刃開閉';</v>
+			strRt	:= 'Corrugated sheet cutter blade open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 Corrugated sheet cutter blade open/close';</v>
       </c>
       <c r="AE76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃開閉
+	//Corrugated sheet cutter blade open/close
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder14】 波板カット刃開閉';
+			strRt	:= 'Corrugated sheet cutter blade open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 Corrugated sheet cutter blade open/close';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃開閉
+	//Corrugated sheet cutter blade open/close
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder14】 波板カット刃開閉';
+			strRt	:= 'Corrugated sheet cutter blade open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 Corrugated sheet cutter blade open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';</v>
       </c>
       <c r="AG76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃開閉
+	//Corrugated sheet cutter blade open/close
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder14】 波板カット刃開閉';
+			strRt	:= 'Corrugated sheet cutter blade open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 Corrugated sheet cutter blade open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -15410,12 +15411,12 @@
       <c r="AH76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃開閉
+	//Corrugated sheet cutter blade open/close
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder14】 波板カット刃開閉';
+			strRt	:= 'Corrugated sheet cutter blade open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 Corrugated sheet cutter blade open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15424,12 +15425,12 @@
       <c r="AI76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃開閉
+	//Corrugated sheet cutter blade open/close
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder14】 波板カット刃開閉';
+			strRt	:= 'Corrugated sheet cutter blade open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 Corrugated sheet cutter blade open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15441,12 +15442,12 @@
       <c r="AJ76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃開閉
+	//Corrugated sheet cutter blade open/close
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder14】 波板カット刃開閉';
+			strRt	:= 'Corrugated sheet cutter blade open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 Corrugated sheet cutter blade open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15458,12 +15459,12 @@
       <c r="AK76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット刃開閉
+	//Corrugated sheet cutter blade open/close
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder14】 波板カット刃開閉';
+			strRt	:= 'Corrugated sheet cutter blade open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 Corrugated sheet cutter blade open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15490,15 +15491,15 @@
       </c>
       <c r="I77" t="str">
         <f ca="1"/>
-        <v>波板カット補助R</v>
+        <v>Corrugated sheet cutter auxiliary</v>
       </c>
       <c r="J77" t="str">
         <f ca="1"/>
-        <v>波板カット補助R</v>
+        <v>Corrugated sheet cutter auxiliary</v>
       </c>
       <c r="L77" t="str">
         <f ca="1"/>
-        <v>【cylinder15】 波板カット補助R</v>
+        <v>【cylinder15】 Corrugated sheet cutter auxiliary</v>
       </c>
       <c r="M77" t="str">
         <v>CXSJM10P-10-M9BL</v>
@@ -15527,75 +15528,75 @@
       <c r="Z77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助R
+	//Corrugated sheet cutter auxiliary
 	ELSIF uiInfoIdx = 15 THEN</v>
       </c>
       <c r="AA77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助R
+	//Corrugated sheet cutter auxiliary
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助R
+	//Corrugated sheet cutter auxiliary
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助R';</v>
+			strRt	:= 'Corrugated sheet cutter auxiliary';</v>
       </c>
       <c r="AC77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助R
+	//Corrugated sheet cutter auxiliary
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助R';
+			strRt	:= 'Corrugated sheet cutter auxiliary';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助R
+	//Corrugated sheet cutter auxiliary
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助R';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder15】 波板カット補助R';</v>
+			strRt	:= 'Corrugated sheet cutter auxiliary';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 Corrugated sheet cutter auxiliary';</v>
       </c>
       <c r="AE77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助R
+	//Corrugated sheet cutter auxiliary
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助R';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder15】 波板カット補助R';
+			strRt	:= 'Corrugated sheet cutter auxiliary';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 Corrugated sheet cutter auxiliary';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助R
+	//Corrugated sheet cutter auxiliary
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助R';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder15】 波板カット補助R';
+			strRt	:= 'Corrugated sheet cutter auxiliary';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 Corrugated sheet cutter auxiliary';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';</v>
       </c>
       <c r="AG77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助R
+	//Corrugated sheet cutter auxiliary
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助R';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder15】 波板カット補助R';
+			strRt	:= 'Corrugated sheet cutter auxiliary';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 Corrugated sheet cutter auxiliary';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -15603,12 +15604,12 @@
       <c r="AH77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助R
+	//Corrugated sheet cutter auxiliary
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助R';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder15】 波板カット補助R';
+			strRt	:= 'Corrugated sheet cutter auxiliary';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 Corrugated sheet cutter auxiliary';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15617,12 +15618,12 @@
       <c r="AI77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助R
+	//Corrugated sheet cutter auxiliary
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助R';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder15】 波板カット補助R';
+			strRt	:= 'Corrugated sheet cutter auxiliary';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 Corrugated sheet cutter auxiliary';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15634,12 +15635,12 @@
       <c r="AJ77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助R
+	//Corrugated sheet cutter auxiliary
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助R';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder15】 波板カット補助R';
+			strRt	:= 'Corrugated sheet cutter auxiliary';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 Corrugated sheet cutter auxiliary';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15651,12 +15652,12 @@
       <c r="AK77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助R
+	//Corrugated sheet cutter auxiliary
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助R';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder15】 波板カット補助R';
+			strRt	:= 'Corrugated sheet cutter auxiliary';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 Corrugated sheet cutter auxiliary';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15683,15 +15684,15 @@
       </c>
       <c r="I78" t="str">
         <f ca="1"/>
-        <v>波板カット補助L</v>
+        <v>Corrugated sheet cutter auxiliary L</v>
       </c>
       <c r="J78" t="str">
         <f ca="1"/>
-        <v>波板カット補助L</v>
+        <v>Corrugated sheet cutter auxiliary L</v>
       </c>
       <c r="L78" t="str">
         <f ca="1"/>
-        <v>【cylinder16】 波板カット補助L</v>
+        <v>【cylinder16】 Corrugated sheet cutter auxiliary L</v>
       </c>
       <c r="M78" t="str">
         <v>CXSJM10P-10-M9BL</v>
@@ -15720,75 +15721,75 @@
       <c r="Z78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助L
+	//Corrugated sheet cutter auxiliary L
 	ELSIF uiInfoIdx = 16 THEN</v>
       </c>
       <c r="AA78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助L
+	//Corrugated sheet cutter auxiliary L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助L
+	//Corrugated sheet cutter auxiliary L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助L';</v>
+			strRt	:= 'Corrugated sheet cutter auxiliary L';</v>
       </c>
       <c r="AC78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助L
+	//Corrugated sheet cutter auxiliary L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助L';
+			strRt	:= 'Corrugated sheet cutter auxiliary L';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助L
+	//Corrugated sheet cutter auxiliary L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助L';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder16】 波板カット補助L';</v>
+			strRt	:= 'Corrugated sheet cutter auxiliary L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 Corrugated sheet cutter auxiliary L';</v>
       </c>
       <c r="AE78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助L
+	//Corrugated sheet cutter auxiliary L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助L';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder16】 波板カット補助L';
+			strRt	:= 'Corrugated sheet cutter auxiliary L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 Corrugated sheet cutter auxiliary L';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助L
+	//Corrugated sheet cutter auxiliary L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助L';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder16】 波板カット補助L';
+			strRt	:= 'Corrugated sheet cutter auxiliary L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 Corrugated sheet cutter auxiliary L';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';</v>
       </c>
       <c r="AG78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助L
+	//Corrugated sheet cutter auxiliary L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助L';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder16】 波板カット補助L';
+			strRt	:= 'Corrugated sheet cutter auxiliary L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 Corrugated sheet cutter auxiliary L';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -15796,12 +15797,12 @@
       <c r="AH78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助L
+	//Corrugated sheet cutter auxiliary L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助L';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder16】 波板カット補助L';
+			strRt	:= 'Corrugated sheet cutter auxiliary L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 Corrugated sheet cutter auxiliary L';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15810,12 +15811,12 @@
       <c r="AI78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助L
+	//Corrugated sheet cutter auxiliary L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助L';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder16】 波板カット補助L';
+			strRt	:= 'Corrugated sheet cutter auxiliary L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 Corrugated sheet cutter auxiliary L';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15827,12 +15828,12 @@
       <c r="AJ78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助L
+	//Corrugated sheet cutter auxiliary L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助L';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder16】 波板カット補助L';
+			strRt	:= 'Corrugated sheet cutter auxiliary L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 Corrugated sheet cutter auxiliary L';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15844,12 +15845,12 @@
       <c r="AK78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//波板カット補助L
+	//Corrugated sheet cutter auxiliary L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助L';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder16】 波板カット補助L';
+			strRt	:= 'Corrugated sheet cutter auxiliary L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 Corrugated sheet cutter auxiliary L';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15876,15 +15877,15 @@
       </c>
       <c r="I79" t="str">
         <f ca="1"/>
-        <v>Xロール糊付け①</v>
+        <v>X-roll gluing ①</v>
       </c>
       <c r="J79" t="str">
         <f ca="1"/>
-        <v>Xロール糊付け①</v>
+        <v>X-roll gluing ①</v>
       </c>
       <c r="L79" t="str">
         <f ca="1"/>
-        <v>【cylinder17】 Xロール糊付け①</v>
+        <v>【cylinder17】 X-roll gluing ①</v>
       </c>
       <c r="M79" t="str">
         <v>CDM2RA20-25Z-M9BWV</v>
@@ -15913,75 +15914,75 @@
       <c r="Z79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け①
+	//X-roll gluing ①
 	ELSIF uiInfoIdx = 17 THEN</v>
       </c>
       <c r="AA79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け①
+	//X-roll gluing ①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け①
+	//X-roll gluing ①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け①';</v>
+			strRt	:= 'X-roll gluing ①';</v>
       </c>
       <c r="AC79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け①
+	//X-roll gluing ①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け①';
+			strRt	:= 'X-roll gluing ①';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け①
+	//X-roll gluing ①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder17】 Xロール糊付け①';</v>
+			strRt	:= 'X-roll gluing ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 X-roll gluing ①';</v>
       </c>
       <c r="AE79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け①
+	//X-roll gluing ①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder17】 Xロール糊付け①';
+			strRt	:= 'X-roll gluing ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 X-roll gluing ①';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け①
+	//X-roll gluing ①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder17】 Xロール糊付け①';
+			strRt	:= 'X-roll gluing ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 X-roll gluing ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';</v>
       </c>
       <c r="AG79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け①
+	//X-roll gluing ①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder17】 Xロール糊付け①';
+			strRt	:= 'X-roll gluing ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 X-roll gluing ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -15989,12 +15990,12 @@
       <c r="AH79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け①
+	//X-roll gluing ①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder17】 Xロール糊付け①';
+			strRt	:= 'X-roll gluing ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 X-roll gluing ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16003,12 +16004,12 @@
       <c r="AI79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け①
+	//X-roll gluing ①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder17】 Xロール糊付け①';
+			strRt	:= 'X-roll gluing ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 X-roll gluing ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16020,12 +16021,12 @@
       <c r="AJ79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け①
+	//X-roll gluing ①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder17】 Xロール糊付け①';
+			strRt	:= 'X-roll gluing ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 X-roll gluing ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16037,12 +16038,12 @@
       <c r="AK79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け①
+	//X-roll gluing ①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder17】 Xロール糊付け①';
+			strRt	:= 'X-roll gluing ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 X-roll gluing ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16069,15 +16070,15 @@
       </c>
       <c r="I80" t="str">
         <f ca="1"/>
-        <v>Xロール糊付け②</v>
+        <v>X-roll gluing ②</v>
       </c>
       <c r="J80" t="str">
         <f ca="1"/>
-        <v>Xロール糊付け②</v>
+        <v>X-roll gluing ②</v>
       </c>
       <c r="L80" t="str">
         <f ca="1"/>
-        <v>【cylinder18】 Xロール糊付け②</v>
+        <v>【cylinder18】 X-roll gluing ②</v>
       </c>
       <c r="M80" t="str">
         <v>CDM2RA20-25Z-M9BWV</v>
@@ -16106,75 +16107,75 @@
       <c r="Z80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け②
+	//X-roll gluing ②
 	ELSIF uiInfoIdx = 18 THEN</v>
       </c>
       <c r="AA80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け②
+	//X-roll gluing ②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け②
+	//X-roll gluing ②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け②';</v>
+			strRt	:= 'X-roll gluing ②';</v>
       </c>
       <c r="AC80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け②
+	//X-roll gluing ②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け②';
+			strRt	:= 'X-roll gluing ②';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け②
+	//X-roll gluing ②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder18】 Xロール糊付け②';</v>
+			strRt	:= 'X-roll gluing ②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 X-roll gluing ②';</v>
       </c>
       <c r="AE80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け②
+	//X-roll gluing ②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder18】 Xロール糊付け②';
+			strRt	:= 'X-roll gluing ②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 X-roll gluing ②';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け②
+	//X-roll gluing ②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder18】 Xロール糊付け②';
+			strRt	:= 'X-roll gluing ②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 X-roll gluing ②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';</v>
       </c>
       <c r="AG80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け②
+	//X-roll gluing ②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder18】 Xロール糊付け②';
+			strRt	:= 'X-roll gluing ②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 X-roll gluing ②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -16182,12 +16183,12 @@
       <c r="AH80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け②
+	//X-roll gluing ②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder18】 Xロール糊付け②';
+			strRt	:= 'X-roll gluing ②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 X-roll gluing ②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16196,12 +16197,12 @@
       <c r="AI80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け②
+	//X-roll gluing ②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder18】 Xロール糊付け②';
+			strRt	:= 'X-roll gluing ②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 X-roll gluing ②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16213,12 +16214,12 @@
       <c r="AJ80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け②
+	//X-roll gluing ②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder18】 Xロール糊付け②';
+			strRt	:= 'X-roll gluing ②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 X-roll gluing ②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16230,12 +16231,12 @@
       <c r="AK80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール糊付け②
+	//X-roll gluing ②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder18】 Xロール糊付け②';
+			strRt	:= 'X-roll gluing ②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 X-roll gluing ②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16262,15 +16263,15 @@
       </c>
       <c r="I81" t="str">
         <f ca="1"/>
-        <v>Xロール平板押付</v>
+        <v>X-roll flat plate pressing</v>
       </c>
       <c r="J81" t="str">
         <f ca="1"/>
-        <v>Xロール平板押付</v>
+        <v>X-roll flat plate pressing</v>
       </c>
       <c r="L81" t="str">
         <f ca="1"/>
-        <v>【cylinder19】 Xロール平板押付</v>
+        <v>【cylinder19】 X-roll flat plate pressing</v>
       </c>
       <c r="M81" t="str">
         <v>不明</v>
@@ -16299,75 +16300,75 @@
       <c r="Z81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール平板押付
+	//X-roll flat plate pressing
 	ELSIF uiInfoIdx = 19 THEN</v>
       </c>
       <c r="AA81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール平板押付
+	//X-roll flat plate pressing
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール平板押付
+	//X-roll flat plate pressing
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール平板押付';</v>
+			strRt	:= 'X-roll flat plate pressing';</v>
       </c>
       <c r="AC81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール平板押付
+	//X-roll flat plate pressing
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール平板押付';
+			strRt	:= 'X-roll flat plate pressing';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール平板押付
+	//X-roll flat plate pressing
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール平板押付';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder19】 Xロール平板押付';</v>
+			strRt	:= 'X-roll flat plate pressing';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 X-roll flat plate pressing';</v>
       </c>
       <c r="AE81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール平板押付
+	//X-roll flat plate pressing
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール平板押付';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder19】 Xロール平板押付';
+			strRt	:= 'X-roll flat plate pressing';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 X-roll flat plate pressing';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール平板押付
+	//X-roll flat plate pressing
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール平板押付';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder19】 Xロール平板押付';
+			strRt	:= 'X-roll flat plate pressing';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 X-roll flat plate pressing';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '不明';</v>
       </c>
       <c r="AG81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール平板押付
+	//X-roll flat plate pressing
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール平板押付';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder19】 Xロール平板押付';
+			strRt	:= 'X-roll flat plate pressing';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 X-roll flat plate pressing';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '不明';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -16375,12 +16376,12 @@
       <c r="AH81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール平板押付
+	//X-roll flat plate pressing
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール平板押付';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder19】 Xロール平板押付';
+			strRt	:= 'X-roll flat plate pressing';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 X-roll flat plate pressing';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '不明';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16389,12 +16390,12 @@
       <c r="AI81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール平板押付
+	//X-roll flat plate pressing
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール平板押付';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder19】 Xロール平板押付';
+			strRt	:= 'X-roll flat plate pressing';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 X-roll flat plate pressing';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '不明';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16406,12 +16407,12 @@
       <c r="AJ81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール平板押付
+	//X-roll flat plate pressing
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール平板押付';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder19】 Xロール平板押付';
+			strRt	:= 'X-roll flat plate pressing';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 X-roll flat plate pressing';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '不明';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16423,12 +16424,12 @@
       <c r="AK81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Xロール平板押付
+	//X-roll flat plate pressing
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール平板押付';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder19】 Xロール平板押付';
+			strRt	:= 'X-roll flat plate pressing';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 X-roll flat plate pressing';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '不明';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28305,15 +28306,15 @@
     <row r="205" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="AK205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AK$3:AK$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
-	//箔ロウリール軸
+	//Foil wax reel shaft
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウリール軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis1】 箔ロウリール軸';
+			strRt	:= 'Foil wax reel shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 Foil wax reel shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '5TK20GN-CW2J+5GN180K';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28321,12 +28322,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//平板送り軸
+	//Flat sheet feed shaft
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis2】 平板送り軸';
+			strRt	:= 'Flat sheet feed shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 Flat sheet feed shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28334,12 +28335,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//箔ロウ送り軸
+	//Foil wax feed shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ送り軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis3】 箔ロウ送り軸';
+			strRt	:= 'Foil wax feed shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 Foil wax feed shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28347,12 +28348,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//波板送り
+	//Corrugated sheet feed
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板送り';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis4】 波板送り';
+			strRt	:= 'Corrugated sheet feed';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 Corrugated sheet feed';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28360,12 +28361,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//ワーク排出上下軸
+	//Workpiece discharge up/down shaft
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis5】 ワーク排出上下軸';
+			strRt	:= 'Workpiece discharge up/down shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 Workpiece discharge up/down shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28373,12 +28374,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定子上下軸
+	//Circumference measuring probe up/down shaft
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子上下軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis6】 周長測定子上下軸';
+			strRt	:= 'Circumference measuring probe up/down shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 Circumference measuring probe up/down shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28386,12 +28387,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//ワーク(排出)チャック軸
+	//Workpiece (discharge) chuck shaft
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク(排出)チャック軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis7】 ワーク(排出)チャック軸';
+			strRt	:= 'Workpiece (discharge) chuck shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 Workpiece (discharge) chuck shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28399,12 +28400,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Y軸：溶接トーチ前後
+	//Y-axis: Welding torch forward/backward
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y軸：溶接トーチ前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
+			strRt	:= 'Y-axis: Welding torch forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y-axis: Welding torch forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28412,12 +28413,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Z軸：溶接トーチ上下
+	//Z-axis: Welding torch up/down
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z軸：溶接トーチ上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
+			strRt	:= 'Z-axis: Welding torch up/down';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z-axis: Welding torch up/down';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28425,12 +28426,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//バインダー供給ポンプモータ
+	//Binder supply pump motor
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'バインダー供給ポンプモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis10】 バインダー供給ポンプモータ';
+			strRt	:= 'Binder supply pump motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 Binder supply pump motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28438,12 +28439,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//波板リールモータ
+	//Corrugated sheet reel motor
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis11】 波板リールモータ';
+			strRt	:= 'Corrugated sheet reel motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 Corrugated sheet reel motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28451,12 +28452,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//平板リールモータ
+	//Flat sheet reel motor
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板リールモータ';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis12】 平板リールモータ';
+			strRt	:= 'Flat sheet reel motor';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 Flat sheet reel motor';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28464,12 +28465,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻取り主軸
+	//Winding main shaft
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り主軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis13】 巻取り主軸';
+			strRt	:= 'Winding main shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 Winding main shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-B075AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28477,12 +28478,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//ワーク幅調整軸
+	//Workpiece width adjustment shaft
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク幅調整軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis14】 ワーク幅調整軸';
+			strRt	:= 'Workpiece width adjustment shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 Workpiece width adjustment shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-M040AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28490,12 +28491,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Tロール回転軸
+	//T-roll rotation shaft
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 Tロール回転軸';
+			strRt	:= 'T-roll rotation shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 T-roll rotation shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28503,12 +28504,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//ロータユニットXロール回転軸
+	//Rotor unit X-roll rotation shaft
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ロータユニットXロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis16】 ロータユニットXロール回転軸';
+			strRt	:= 'Rotor unit X-roll rotation shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 Rotor unit X-roll rotation shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28521,12 +28522,12 @@
 	END_IF;
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//ワーク排出前後軸
+	//Workpiece discharge front and rear axis
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'ワーク排出前後軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【EC1】 ワーク排出前後軸';
+			strRt	:= 'Workpiece discharge front and rear axis';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 Workpiece discharge front and rear axis';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'EC-S4HR-200-7-ML-TMD2';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28539,12 +28540,12 @@
 	END_IF;
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//巻取り軸芯前後
+	//Winding shaft center forward/backward
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り軸芯前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder1】 巻取り軸芯前後';
+			strRt	:= 'Winding shaft center forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 Winding shaft center forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28552,12 +28553,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Tロール糊付け①
+	//T-roll gluing ①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder2】 Tロール糊付け①';
+			strRt	:= 'T-roll gluing ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 T-roll gluing ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28565,12 +28566,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Tロール糊付け②
+	//T-roll gluing ②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder3】 Tロール糊付け②';
+			strRt	:= 'T-roll gluing ②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 T-roll gluing ②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28578,12 +28579,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//平板下側補助プレート逃がし
+	//Flat sheet lower auxiliary plate release
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板下側補助プレート逃がし';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder4】 平板下側補助プレート逃がし';
+			strRt	:= 'Flat sheet lower auxiliary plate release';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 Flat sheet lower auxiliary plate release';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28591,12 +28592,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//平板チャック(ハンド)前後
+	//Flat sheet chuck (hand) forward/backward
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック(ハンド)前後';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
+			strRt	:= 'Flat sheet chuck (hand) forward/backward';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 Flat sheet chuck (hand) forward/backward';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MXQ20-50A-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28604,12 +28605,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//平板チャック開閉
+	//Flat sheet chuck open/close
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板チャック開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder6】 平板チャック開閉';
+			strRt	:= 'Flat sheet chuck open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 Flat sheet chuck open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MHF2-16D1-M9BL-X83C1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28617,12 +28618,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//平板押え上下①
+	//Flat sheet clamp up/down ①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= 'Flat sheet clamp up/down ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 Flat sheet clamp up/down ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28630,12 +28631,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//箔ロウ押え上下
+	//Foil wax clamp up/down
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ押え上下';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder8】 箔ロウ押え上下';
+			strRt	:= 'Foil wax clamp up/down';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 Foil wax clamp up/down';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2D25-20DMZ-M9BM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28643,12 +28644,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//箔ロウカット
+	//Foil wax cut
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウカット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder9】 箔ロウカット';
+			strRt	:= 'Foil wax cut';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 Foil wax cut';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQSKB16-10DM-M9NWVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28656,12 +28657,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//波板押え
+	//Corrugated sheet clamp
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板押え';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder10】 波板押え';
+			strRt	:= 'Corrugated sheet clamp';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 Corrugated sheet clamp';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28669,12 +28670,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//平板カット刃押出し
+	//Flat sheet cutter blade push-out
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder11】 平板カット刃押出し';
+			strRt	:= 'Flat sheet cutter blade push-out';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 Flat sheet cutter blade push-out';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28682,12 +28683,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//平板カット刃開閉
+	//Flat sheet cutter blade open/close
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder12】 平板カット刃開閉';
+			strRt	:= 'Flat sheet cutter blade open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 Flat sheet cutter blade open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-10DMZ-L-A93M';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28695,12 +28696,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//波板カット刃押出し
+	//Corrugated sheet cutter blade push-out
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃押出し';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder13】 波板カット刃押出し';
+			strRt	:= 'Corrugated sheet cutter blade push-out';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 Corrugated sheet cutter blade push-out';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28708,12 +28709,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//波板カット刃開閉
+	//Corrugated sheet cutter blade open/close
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット刃開閉';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder14】 波板カット刃開閉';
+			strRt	:= 'Corrugated sheet cutter blade open/close';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 Corrugated sheet cutter blade open/close';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28721,12 +28722,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//波板カット補助R
+	//Corrugated sheet cutter auxiliary
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助R';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder15】 波板カット補助R';
+			strRt	:= 'Corrugated sheet cutter auxiliary';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 Corrugated sheet cutter auxiliary';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28734,12 +28735,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//波板カット補助L
+	//Corrugated sheet cutter auxiliary L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '波板カット補助L';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder16】 波板カット補助L';
+			strRt	:= 'Corrugated sheet cutter auxiliary L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 Corrugated sheet cutter auxiliary L';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28747,12 +28748,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Xロール糊付け①
+	//X-roll gluing ①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder17】 Xロール糊付け①';
+			strRt	:= 'X-roll gluing ①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 X-roll gluing ①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28760,12 +28761,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Xロール糊付け②
+	//X-roll gluing ②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール糊付け②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder18】 Xロール糊付け②';
+			strRt	:= 'X-roll gluing ②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 X-roll gluing ②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28773,12 +28774,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Xロール平板押付
+	//X-roll flat plate pressing
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Xロール平板押付';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder19】 Xロール平板押付';
+			strRt	:= 'X-roll flat plate pressing';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 X-roll flat plate pressing';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '不明';
 		ELSIF strInfoKey = 'mf' THEN

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C42BB7-CDAF-441E-BD89-EE65B9E88837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489407AC-0D2C-4791-8814-D0019DA7AD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -982,9 +982,6 @@
     <t>Foil wax reel shaft</t>
   </si>
   <si>
-    <t>Flat sheet feed shaft</t>
-  </si>
-  <si>
     <t>Foil wax feed shaft</t>
   </si>
   <si>
@@ -1406,6 +1403,10 @@
   </si>
   <si>
     <t>Corrugated sheet cutter auxiliary</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Flat sheet feed shaft</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2257,7 +2258,7 @@
         <v>3</v>
       </c>
       <c r="K1" s="22" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L1" s="22" t="s">
         <v>5</v>
@@ -2266,10 +2267,10 @@
         <v>112</v>
       </c>
       <c r="N1" s="23" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O1" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P1" s="23"/>
     </row>
@@ -2302,10 +2303,10 @@
         <v>21</v>
       </c>
       <c r="J2" s="31" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L2" s="31">
         <v>1</v>
@@ -2335,7 +2336,7 @@
         <v>126</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>156</v>
+        <v>256</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>14</v>
@@ -2344,10 +2345,10 @@
         <v>13</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L3" s="12">
         <v>1</v>
@@ -2377,7 +2378,7 @@
         <v>125</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>14</v>
@@ -2386,10 +2387,10 @@
         <v>13</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L4" s="12">
         <v>1</v>
@@ -2419,7 +2420,7 @@
         <v>89</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>14</v>
@@ -2428,10 +2429,10 @@
         <v>13</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L5" s="12">
         <v>1</v>
@@ -2461,7 +2462,7 @@
         <v>132</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>1</v>
@@ -2473,7 +2474,7 @@
         <v>2</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L6" s="8">
         <v>1</v>
@@ -2503,7 +2504,7 @@
         <v>133</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>0</v>
@@ -2515,7 +2516,7 @@
         <v>2</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L7" s="8">
         <v>1</v>
@@ -2545,7 +2546,7 @@
         <v>131</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>28</v>
@@ -2557,7 +2558,7 @@
         <v>2</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L8" s="8">
         <v>1</v>
@@ -2587,7 +2588,7 @@
         <v>134</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>106</v>
@@ -2599,7 +2600,7 @@
         <v>2</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L9" s="8">
         <v>1</v>
@@ -2629,7 +2630,7 @@
         <v>135</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>107</v>
@@ -2641,7 +2642,7 @@
         <v>2</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L10" s="8">
         <v>1</v>
@@ -2667,7 +2668,7 @@
         <v>136</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
@@ -2695,7 +2696,7 @@
         <v>138</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
@@ -2723,7 +2724,7 @@
         <v>139</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
@@ -2755,7 +2756,7 @@
         <v>127</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>31</v>
@@ -2764,10 +2765,10 @@
         <v>32</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L14" s="8">
         <v>1</v>
@@ -2797,7 +2798,7 @@
         <v>128</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>33</v>
@@ -2806,10 +2807,10 @@
         <v>32</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L15" s="8">
         <v>1</v>
@@ -2835,7 +2836,7 @@
         <v>129</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>141</v>
@@ -2865,7 +2866,7 @@
         <v>140</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>141</v>
@@ -2899,7 +2900,7 @@
         <v>145</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>61</v>
@@ -2911,7 +2912,7 @@
         <v>4</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L18" s="8">
         <v>1</v>
@@ -2938,13 +2939,13 @@
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
@@ -2972,13 +2973,13 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I20" s="8"/>
       <c r="J20" s="8"/>
@@ -3013,7 +3014,7 @@
         <v>121</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>63</v>
@@ -3025,7 +3026,7 @@
         <v>4</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L21" s="8">
         <v>1</v>
@@ -3059,7 +3060,7 @@
         <v>153</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H22" s="8" t="s">
         <v>67</v>
@@ -3071,7 +3072,7 @@
         <v>4</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L22" s="8">
         <v>1</v>
@@ -3105,7 +3106,7 @@
         <v>152</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H23" s="8" t="s">
         <v>65</v>
@@ -3117,7 +3118,7 @@
         <v>4</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L23" s="8">
         <v>1</v>
@@ -3151,7 +3152,7 @@
         <v>148</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H24" s="8" t="s">
         <v>69</v>
@@ -3163,7 +3164,7 @@
         <v>4</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L24" s="11">
         <v>1</v>
@@ -3197,7 +3198,7 @@
         <v>150</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H25" s="8" t="s">
         <v>73</v>
@@ -3209,7 +3210,7 @@
         <v>4</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L25" s="11">
         <v>1</v>
@@ -3243,7 +3244,7 @@
         <v>122</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H26" s="8" t="s">
         <v>71</v>
@@ -3255,7 +3256,7 @@
         <v>4</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L26" s="11">
         <v>1</v>
@@ -3289,7 +3290,7 @@
         <v>149</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>69</v>
@@ -3301,7 +3302,7 @@
         <v>4</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L27" s="11">
         <v>1</v>
@@ -3335,7 +3336,7 @@
         <v>142</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H28" s="12" t="s">
         <v>75</v>
@@ -3347,7 +3348,7 @@
         <v>4</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L28" s="13">
         <v>1</v>
@@ -3381,7 +3382,7 @@
         <v>146</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>74</v>
@@ -3393,7 +3394,7 @@
         <v>4</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L29" s="11">
         <v>1</v>
@@ -3427,7 +3428,7 @@
         <v>143</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>75</v>
@@ -3439,7 +3440,7 @@
         <v>4</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L30" s="13">
         <v>1</v>
@@ -3473,7 +3474,7 @@
         <v>147</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>76</v>
@@ -3485,7 +3486,7 @@
         <v>4</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L31" s="11">
         <v>1</v>
@@ -3516,10 +3517,10 @@
         <v>96</v>
       </c>
       <c r="F32" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="G32" s="12" t="s">
         <v>255</v>
-      </c>
-      <c r="G32" s="12" t="s">
-        <v>256</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>77</v>
@@ -3531,7 +3532,7 @@
         <v>4</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L32" s="13">
         <v>1</v>
@@ -3565,7 +3566,7 @@
         <v>151</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>77</v>
@@ -3577,7 +3578,7 @@
         <v>4</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L33" s="13">
         <v>1</v>
@@ -3604,10 +3605,10 @@
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
       <c r="F34" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>51</v>
@@ -3638,10 +3639,10 @@
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
       <c r="F35" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>51</v>
@@ -3672,13 +3673,13 @@
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
       <c r="F36" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
@@ -3719,7 +3720,7 @@
         <v>4</v>
       </c>
       <c r="K37" s="14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L37" s="15">
         <v>1</v>
@@ -3757,7 +3758,7 @@
         <v>4</v>
       </c>
       <c r="K38" s="14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L38" s="15">
         <v>1</v>
@@ -3795,7 +3796,7 @@
         <v>4</v>
       </c>
       <c r="K39" s="14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L39" s="15">
         <v>1</v>
@@ -3827,7 +3828,7 @@
         <v>130</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>30</v>
@@ -3839,7 +3840,7 @@
         <v>2</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L40" s="8">
         <v>1</v>
@@ -3874,10 +3875,10 @@
         <v>8</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L41" s="8">
         <v>1</v>
@@ -3912,10 +3913,10 @@
         <v>9</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L42" s="8">
         <v>1</v>
@@ -3948,10 +3949,10 @@
         <v>23</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L43" s="8">
         <v>3</v>
@@ -3986,10 +3987,10 @@
         <v>24</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L44" s="8">
         <v>1</v>
@@ -4026,10 +4027,10 @@
         <v>36</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L45" s="8">
         <v>1</v>
@@ -4062,10 +4063,10 @@
         <v>59</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L46" s="8">
         <v>1</v>
@@ -4096,10 +4097,10 @@
         <v>19</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L47" s="8">
         <v>1</v>
@@ -4130,10 +4131,10 @@
         <v>17</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L48" s="8">
         <v>1</v>
@@ -4164,10 +4165,10 @@
         <v>26</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L49" s="8">
         <v>1</v>
@@ -4200,10 +4201,10 @@
         <v>26</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L50" s="8">
         <v>1</v>
@@ -4251,7 +4252,7 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B55" t="s">
         <v>117</v>
@@ -4512,19 +4513,19 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="F1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1" t="s">
         <v>237</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>238</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>239</v>
-      </c>
-      <c r="P1" t="s">
-        <v>240</v>
       </c>
       <c r="AA1" t="str">
         <f>IF(LEN(J1),J2&amp;CHAR(9)&amp;":"&amp;J1,"")</f>
@@ -4558,82 +4559,82 @@
     </row>
     <row r="2" spans="1:37" s="33" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="33" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F2" s="33" t="s">
         <v>102</v>
       </c>
       <c r="G2" s="33" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H2" s="33" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J2" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="L2" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="L2" s="33" t="s">
-        <v>199</v>
-      </c>
       <c r="N2" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="P2" s="33" t="s">
+        <v>227</v>
+      </c>
+      <c r="X2" s="33" t="s">
         <v>209</v>
       </c>
-      <c r="P2" s="33" t="s">
-        <v>228</v>
-      </c>
-      <c r="X2" s="33" t="s">
-        <v>210</v>
-      </c>
       <c r="Y2" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="Z2" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="Z2" s="33" t="s">
+      <c r="AA2" s="33" t="s">
         <v>202</v>
       </c>
-      <c r="AA2" s="33" t="s">
+      <c r="AB2" s="33" t="s">
         <v>203</v>
       </c>
-      <c r="AB2" s="33" t="s">
+      <c r="AC2" s="33" t="s">
         <v>204</v>
       </c>
-      <c r="AC2" s="33" t="s">
-        <v>205</v>
-      </c>
       <c r="AD2" s="33" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AE2" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="AF2" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="AF2" s="33" t="s">
-        <v>213</v>
-      </c>
       <c r="AG2" s="33" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AH2" s="33" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AI2" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="AJ2" s="33" t="s">
         <v>224</v>
       </c>
-      <c r="AJ2" s="33" t="s">
-        <v>225</v>
-      </c>
       <c r="AK2" s="33" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
@@ -5033,11 +5034,11 @@
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ref="E5:E68" si="0">E4</f>
@@ -5233,10 +5234,10 @@
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" t="s">
         <v>191</v>
-      </c>
-      <c r="B6" t="s">
-        <v>192</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
@@ -5432,10 +5433,10 @@
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B7" t="s">
         <v>184</v>
-      </c>
-      <c r="B7" t="s">
-        <v>185</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -5631,10 +5632,10 @@
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B8" t="s">
         <v>186</v>
-      </c>
-      <c r="B8" t="s">
-        <v>187</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -5830,10 +5831,10 @@
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>187</v>
+      </c>
+      <c r="B9" t="s">
         <v>188</v>
-      </c>
-      <c r="B9" t="s">
-        <v>189</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -6608,11 +6609,11 @@
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B13" t="str">
         <f ca="1">$AK$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//Foil wax reel shaft
@@ -7295,7 +7296,7 @@
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B14" t="str">
         <f>IF(LEN(AI1),"●"&amp;B27&amp;CHAR(10)&amp;AI1,"")</f>
@@ -8663,7 +8664,7 @@
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -8865,10 +8866,10 @@
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B25" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E25" t="str">
         <f t="shared" si="0"/>
@@ -8969,10 +8970,10 @@
     </row>
     <row r="26" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B26" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E26" t="str">
         <f t="shared" si="0"/>
@@ -9073,10 +9074,10 @@
     </row>
     <row r="27" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B27" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E27" t="str">
         <f t="shared" si="0"/>
@@ -9177,10 +9178,10 @@
     </row>
     <row r="28" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B28" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E28" t="str">
         <f t="shared" si="0"/>
@@ -9281,10 +9282,10 @@
     </row>
     <row r="29" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B29" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E29" t="str">
         <f t="shared" si="0"/>
@@ -28306,7 +28307,7 @@
     <row r="205" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="AK205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AK$3:AK$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//Foil wax reel shaft

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489407AC-0D2C-4791-8814-D0019DA7AD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1EA097-E7EF-494F-9C70-ED39C5AB79A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -2213,6 +2213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:P78"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -4496,6 +4497,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFB68130-827D-4D3B-BD9D-BF7AF7772D03}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK205"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -4634,7 +4636,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_sv3_error.xlsm]config</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
@@ -5038,7 +5040,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_sv3_error.xlsm]config によって生成されました。</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ref="E5:E68" si="0">E4</f>
@@ -6613,7 +6615,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AK$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_sv3_error.xlsm]config によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//Foil wax reel shaft
@@ -28307,7 +28309,7 @@
     <row r="205" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="AK205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AK$3:AK$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_sv3_error.xlsm]config によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//Foil wax reel shaft

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1EA097-E7EF-494F-9C70-ED39C5AB79A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E11EA6-2B13-4D68-B8E9-DAB85ACF4239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
   <sheets>
     <sheet name="info_index" sheetId="1" r:id="rId1"/>
@@ -720,22 +720,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>平板下側補助プレート逃がし</t>
-    <rPh sb="0" eb="2">
-      <t>ヒライタ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>シタガワ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ホジョ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ニ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>箔ロウカット</t>
     <rPh sb="0" eb="1">
       <t>ハク</t>
@@ -1025,9 +1009,6 @@
   </si>
   <si>
     <t>Winding shaft center forward/backward</t>
-  </si>
-  <si>
-    <t>Flat sheet lower auxiliary plate release</t>
   </si>
   <si>
     <t>Flat sheet chuck (hand) forward/backward</t>
@@ -1408,6 +1389,19 @@
   <si>
     <t>Flat sheet feed shaft</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>平板補助プレート</t>
+    <rPh sb="0" eb="2">
+      <t>ヒライタ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Flat auxiliary plate</t>
   </si>
 </sst>
 </file>
@@ -2247,7 +2241,7 @@
         <v>105</v>
       </c>
       <c r="G1" s="22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H1" s="22" t="s">
         <v>10</v>
@@ -2259,7 +2253,7 @@
         <v>3</v>
       </c>
       <c r="K1" s="22" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L1" s="22" t="s">
         <v>5</v>
@@ -2268,10 +2262,10 @@
         <v>112</v>
       </c>
       <c r="N1" s="23" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O1" s="23" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="P1" s="23"/>
     </row>
@@ -2292,10 +2286,10 @@
         <v>91</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H2" s="31" t="s">
         <v>20</v>
@@ -2304,10 +2298,10 @@
         <v>21</v>
       </c>
       <c r="J2" s="31" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L2" s="31">
         <v>1</v>
@@ -2334,10 +2328,10 @@
         <v>98</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>14</v>
@@ -2346,10 +2340,10 @@
         <v>13</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L3" s="12">
         <v>1</v>
@@ -2376,10 +2370,10 @@
         <v>92</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>14</v>
@@ -2388,10 +2382,10 @@
         <v>13</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L4" s="12">
         <v>1</v>
@@ -2421,7 +2415,7 @@
         <v>89</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>14</v>
@@ -2430,10 +2424,10 @@
         <v>13</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L5" s="12">
         <v>1</v>
@@ -2460,10 +2454,10 @@
         <v>94</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>1</v>
@@ -2475,7 +2469,7 @@
         <v>2</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L6" s="8">
         <v>1</v>
@@ -2502,10 +2496,10 @@
         <v>94</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>0</v>
@@ -2517,7 +2511,7 @@
         <v>2</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L7" s="8">
         <v>1</v>
@@ -2544,10 +2538,10 @@
         <v>99</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>28</v>
@@ -2559,7 +2553,7 @@
         <v>2</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L8" s="8">
         <v>1</v>
@@ -2586,10 +2580,10 @@
         <v>101</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>106</v>
@@ -2601,7 +2595,7 @@
         <v>2</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L9" s="8">
         <v>1</v>
@@ -2628,10 +2622,10 @@
         <v>101</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>107</v>
@@ -2643,7 +2637,7 @@
         <v>2</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L10" s="8">
         <v>1</v>
@@ -2666,10 +2660,10 @@
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
@@ -2694,10 +2688,10 @@
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
@@ -2722,10 +2716,10 @@
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
@@ -2754,10 +2748,10 @@
         <v>99</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>31</v>
@@ -2766,10 +2760,10 @@
         <v>32</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L14" s="8">
         <v>1</v>
@@ -2796,10 +2790,10 @@
         <v>99</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>33</v>
@@ -2808,10 +2802,10 @@
         <v>32</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L15" s="8">
         <v>1</v>
@@ -2826,7 +2820,7 @@
         <v>41</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C16" s="7">
         <v>15</v>
@@ -2834,13 +2828,13 @@
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I16" s="8"/>
       <c r="J16" s="8"/>
@@ -2856,7 +2850,7 @@
         <v>45</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C17" s="7">
         <v>16</v>
@@ -2864,13 +2858,13 @@
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
       <c r="F17" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="H17" s="8" t="s">
         <v>140</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>141</v>
       </c>
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
@@ -2898,10 +2892,10 @@
         <v>99</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>61</v>
@@ -2913,7 +2907,7 @@
         <v>4</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L18" s="8">
         <v>1</v>
@@ -2940,13 +2934,13 @@
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
@@ -2974,13 +2968,13 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I20" s="8"/>
       <c r="J20" s="8"/>
@@ -3009,13 +3003,13 @@
         <v>2</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>121</v>
+        <v>255</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>171</v>
+        <v>256</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>63</v>
@@ -3027,7 +3021,7 @@
         <v>4</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L21" s="8">
         <v>1</v>
@@ -3058,10 +3052,10 @@
         <v>93</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H22" s="8" t="s">
         <v>67</v>
@@ -3073,7 +3067,7 @@
         <v>4</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L22" s="8">
         <v>1</v>
@@ -3104,10 +3098,10 @@
         <v>93</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H23" s="8" t="s">
         <v>65</v>
@@ -3119,7 +3113,7 @@
         <v>4</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L23" s="8">
         <v>1</v>
@@ -3150,10 +3144,10 @@
         <v>98</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H24" s="8" t="s">
         <v>69</v>
@@ -3165,7 +3159,7 @@
         <v>4</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L24" s="11">
         <v>1</v>
@@ -3196,10 +3190,10 @@
         <v>92</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H25" s="8" t="s">
         <v>73</v>
@@ -3211,7 +3205,7 @@
         <v>4</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L25" s="11">
         <v>1</v>
@@ -3242,10 +3236,10 @@
         <v>92</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H26" s="8" t="s">
         <v>71</v>
@@ -3257,7 +3251,7 @@
         <v>4</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L26" s="11">
         <v>1</v>
@@ -3288,10 +3282,10 @@
         <v>100</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>69</v>
@@ -3303,7 +3297,7 @@
         <v>4</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L27" s="11">
         <v>1</v>
@@ -3334,10 +3328,10 @@
         <v>95</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H28" s="12" t="s">
         <v>75</v>
@@ -3349,7 +3343,7 @@
         <v>4</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L28" s="13">
         <v>1</v>
@@ -3380,10 +3374,10 @@
         <v>95</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>74</v>
@@ -3395,7 +3389,7 @@
         <v>4</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L29" s="11">
         <v>1</v>
@@ -3426,10 +3420,10 @@
         <v>97</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>75</v>
@@ -3441,7 +3435,7 @@
         <v>4</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L30" s="13">
         <v>1</v>
@@ -3472,10 +3466,10 @@
         <v>97</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>76</v>
@@ -3487,7 +3481,7 @@
         <v>4</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L31" s="11">
         <v>1</v>
@@ -3518,10 +3512,10 @@
         <v>96</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>77</v>
@@ -3533,7 +3527,7 @@
         <v>4</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L32" s="13">
         <v>1</v>
@@ -3564,10 +3558,10 @@
         <v>96</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>77</v>
@@ -3579,7 +3573,7 @@
         <v>4</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L33" s="13">
         <v>1</v>
@@ -3606,10 +3600,10 @@
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
       <c r="F34" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>51</v>
@@ -3640,10 +3634,10 @@
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
       <c r="F35" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>51</v>
@@ -3674,13 +3668,13 @@
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
       <c r="F36" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
@@ -3721,7 +3715,7 @@
         <v>4</v>
       </c>
       <c r="K37" s="14" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L37" s="15">
         <v>1</v>
@@ -3759,7 +3753,7 @@
         <v>4</v>
       </c>
       <c r="K38" s="14" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L38" s="15">
         <v>1</v>
@@ -3797,7 +3791,7 @@
         <v>4</v>
       </c>
       <c r="K39" s="14" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L39" s="15">
         <v>1</v>
@@ -3814,7 +3808,7 @@
         <v>21</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C40" s="7">
         <v>1</v>
@@ -3826,10 +3820,10 @@
         <v>99</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>30</v>
@@ -3841,7 +3835,7 @@
         <v>2</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L40" s="8">
         <v>1</v>
@@ -3876,10 +3870,10 @@
         <v>8</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L41" s="8">
         <v>1</v>
@@ -3914,10 +3908,10 @@
         <v>9</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L42" s="8">
         <v>1</v>
@@ -3950,10 +3944,10 @@
         <v>23</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L43" s="8">
         <v>3</v>
@@ -3988,10 +3982,10 @@
         <v>24</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L44" s="8">
         <v>1</v>
@@ -4028,10 +4022,10 @@
         <v>36</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L45" s="8">
         <v>1</v>
@@ -4064,10 +4058,10 @@
         <v>59</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L46" s="8">
         <v>1</v>
@@ -4098,10 +4092,10 @@
         <v>19</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L47" s="8">
         <v>1</v>
@@ -4132,10 +4126,10 @@
         <v>17</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L48" s="8">
         <v>1</v>
@@ -4166,10 +4160,10 @@
         <v>26</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L49" s="8">
         <v>1</v>
@@ -4202,10 +4196,10 @@
         <v>26</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L50" s="8">
         <v>1</v>
@@ -4253,7 +4247,7 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B55" t="s">
         <v>117</v>
@@ -4515,19 +4509,19 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="F1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="J1" t="s">
+        <v>234</v>
+      </c>
+      <c r="L1" t="s">
+        <v>235</v>
+      </c>
+      <c r="N1" t="s">
         <v>236</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>237</v>
-      </c>
-      <c r="N1" t="s">
-        <v>238</v>
-      </c>
-      <c r="P1" t="s">
-        <v>239</v>
       </c>
       <c r="AA1" t="str">
         <f>IF(LEN(J1),J2&amp;CHAR(9)&amp;":"&amp;J1,"")</f>
@@ -4561,82 +4555,82 @@
     </row>
     <row r="2" spans="1:37" s="33" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="33" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F2" s="33" t="s">
         <v>102</v>
       </c>
       <c r="G2" s="33" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H2" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="J2" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="L2" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="N2" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="P2" s="33" t="s">
         <v>225</v>
       </c>
-      <c r="J2" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="L2" s="33" t="s">
+      <c r="X2" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y2" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="N2" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="P2" s="33" t="s">
-        <v>227</v>
-      </c>
-      <c r="X2" s="33" t="s">
+      <c r="Z2" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="AA2" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="AB2" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="AC2" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="AD2" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="AE2" s="33" t="s">
         <v>209</v>
       </c>
-      <c r="Y2" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="Z2" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="AA2" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="AB2" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="AC2" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="AD2" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="AE2" s="33" t="s">
-        <v>211</v>
-      </c>
       <c r="AF2" s="33" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AG2" s="33" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AH2" s="33" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AI2" s="33" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AJ2" s="33" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AK2" s="33" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_sv3_error.xlsm]config</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
@@ -4651,15 +4645,15 @@
       </c>
       <c r="I3" t="str" cm="1">
         <f t="array" aca="1" ref="I3:I202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(H3)),INDEX(OFFSET(info_index!$F$2:$F$51,0,$B$23),MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$51&amp;info_index!$C$2:$C$51,0)&amp;"",1),"")</f>
-        <v>Foil wax reel shaft</v>
+        <v>箔ロウリール軸</v>
       </c>
       <c r="J3" t="str" cm="1">
         <f t="array" aca="1" ref="J3:J202" ca="1">IF(LEN(_xlfn.ANCHORARRAY($H3)),IF(LEN(_xlfn.ANCHORARRAY(I3)),_xlfn.ANCHORARRAY(I3),"unknown"),"")</f>
-        <v>Foil wax reel shaft</v>
+        <v>箔ロウリール軸</v>
       </c>
       <c r="L3" t="str" cm="1">
         <f t="array" aca="1" ref="L3:L202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),"【"&amp;E3:E202&amp;F3:F202&amp;"】 "&amp;_xlfn.ANCHORARRAY(J3),"")</f>
-        <v>【axis1】 Foil wax reel shaft</v>
+        <v>【axis1】 箔ロウリール軸</v>
       </c>
       <c r="M3" t="str" cm="1">
         <f t="array" ref="M3:M202">IFERROR(INDEX(info_index!$H$2:$H$51,MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$51&amp;info_index!$C$2:$C$51,0),1)&amp;"","")</f>
@@ -4690,14 +4684,14 @@
         <f t="array" aca="1" ref="Z3:Z202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(Y3)),_xlfn.ANCHORARRAY(Y3),"")&amp;IF(LEN(J3:J202),CHAR(10)&amp;CHAR(9)&amp;$B$7&amp;_xlfn.ANCHORARRAY(J3)&amp;CHAR(10)&amp;CHAR(9)&amp;IF(F3:F202=1,"IF ","ELSIF ")&amp;$B$26&amp;" = "&amp;F3:F202&amp;" THEN","")</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//Foil wax reel shaft
+	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AA3" t="str" cm="1">
         <f t="array" aca="1" ref="AA3:AA202" ca="1">IF(LEN(Z3:Z202),Z3:Z202,"")&amp;IF(LEN(J3:J202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"IF "&amp;$B$27&amp;" = '"&amp;$J$2&amp;"' THEN","")</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//Foil wax reel shaft
+	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -4705,54 +4699,54 @@
         <f t="array" aca="1" ref="AB3:AB202" ca="1">IF(LEN(AA3:AA202),AA3:AA202,"")&amp;IF(LEN(J3:J202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(J3)&amp;"'"&amp;$B$9,"")</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//Foil wax reel shaft
+	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax reel shaft';</v>
+			strRt	:= '箔ロウリール軸';</v>
       </c>
       <c r="AC3" t="str" cm="1">
         <f t="array" aca="1" ref="AC3:AC202" ca="1">IF(LEN(AB3:AB202),AB3:AB202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;L$2&amp;"' THEN","")</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//Foil wax reel shaft
+	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax reel shaft';
+			strRt	:= '箔ロウリール軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD3" t="str" cm="1">
         <f t="array" aca="1" ref="AD3:AD202" ca="1">IF(LEN(AC3:AC202),AC3:AC202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(L3)&amp;"'"&amp;$B$9,"")</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//Foil wax reel shaft
+	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax reel shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis1】 Foil wax reel shaft';</v>
+			strRt	:= '箔ロウリール軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 箔ロウリール軸';</v>
       </c>
       <c r="AE3" t="str" cm="1">
         <f t="array" aca="1" ref="AE3:AE202" ca="1">IF(LEN(AD3:AD202),AD3:AD202,"")&amp;IF(LEN(N3:N202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;N$2&amp;"' THEN","")</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//Foil wax reel shaft
+	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax reel shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis1】 Foil wax reel shaft';
+			strRt	:= '箔ロウリール軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 箔ロウリール軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF3" t="str" cm="1">
         <f t="array" aca="1" ref="AF3:AF202" ca="1">IF(LEN(AE3:AE202),AE3:AE202,"")&amp;IF(LEN(N3:N202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(N3)&amp;"'"&amp;$B$9,"")</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//Foil wax reel shaft
+	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax reel shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis1】 Foil wax reel shaft';
+			strRt	:= '箔ロウリール軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 箔ロウリール軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '5TK20GN-CW2J+5GN180K';</v>
       </c>
@@ -4760,12 +4754,12 @@
         <f t="array" aca="1" ref="AG3:AG202" ca="1">IF(LEN(AF3:AF202),AF3:AF202,"")&amp;IF(LEN(P3:P202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;P$2&amp;"' THEN","")</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//Foil wax reel shaft
+	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax reel shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis1】 Foil wax reel shaft';
+			strRt	:= '箔ロウリール軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 箔ロウリール軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '5TK20GN-CW2J+5GN180K';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -4774,12 +4768,12 @@
         <f t="array" aca="1" ref="AH3:AH202" ca="1">IF(LEN(AG3:AG202),AG3:AG202,"")&amp;IF(LEN(P3:P202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(P3)&amp;"'"&amp;$B$9,"")</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//Foil wax reel shaft
+	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax reel shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis1】 Foil wax reel shaft';
+			strRt	:= '箔ロウリール軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 箔ロウリール軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '5TK20GN-CW2J+5GN180K';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4789,12 +4783,12 @@
         <f t="array" aca="1" ref="AI3:AI202" ca="1">IF(LEN(AH3:AH202),AH3:AH202,"")&amp;IF(LEN(J3:J202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 3"&amp;$B$9&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"END_IF"&amp;$B$9,"")</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//Foil wax reel shaft
+	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax reel shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis1】 Foil wax reel shaft';
+			strRt	:= '箔ロウリール軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 箔ロウリール軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '5TK20GN-CW2J+5GN180K';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4807,12 +4801,12 @@
         <f t="array" aca="1" ref="AJ3:AJ202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(AI3)),_xlfn.ANCHORARRAY(AI3),"")&amp;IF(G3:G202="●",CHAR(10)&amp;CHAR(9)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 2"&amp;$B$9&amp;CHAR(10)&amp;CHAR(9)&amp;"END_IF"&amp;$B$9,"")</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//Foil wax reel shaft
+	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax reel shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis1】 Foil wax reel shaft';
+			strRt	:= '箔ロウリール軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 箔ロウリール軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '5TK20GN-CW2J+5GN180K';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4825,12 +4819,12 @@
         <f t="array" aca="1" ref="AK3:AK202" ca="1">_xlfn.ANCHORARRAY(AJ3)</f>
         <v>//axis
 IF strInfoType = 'axis' THEN
-	//Foil wax reel shaft
+	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax reel shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis1】 Foil wax reel shaft';
+			strRt	:= '箔ロウリール軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 箔ロウリール軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '5TK20GN-CW2J+5GN180K';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4858,15 +4852,15 @@
       </c>
       <c r="I4" t="str">
         <f ca="1"/>
-        <v>Flat sheet feed shaft</v>
+        <v>平板送り軸</v>
       </c>
       <c r="J4" t="str">
         <f ca="1"/>
-        <v>Flat sheet feed shaft</v>
+        <v>平板送り軸</v>
       </c>
       <c r="L4" t="str">
         <f ca="1"/>
-        <v>【axis2】 Flat sheet feed shaft</v>
+        <v>【axis2】 平板送り軸</v>
       </c>
       <c r="M4" t="str">
         <v>AZM46AC-HP9+AZD-CEP+CC070VZR</v>
@@ -4895,75 +4889,75 @@
       <c r="Z4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet feed shaft
+	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AA4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet feed shaft
+	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet feed shaft
+	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet feed shaft';</v>
+			strRt	:= '平板送り軸';</v>
       </c>
       <c r="AC4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet feed shaft
+	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet feed shaft';
+			strRt	:= '平板送り軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet feed shaft
+	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet feed shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis2】 Flat sheet feed shaft';</v>
+			strRt	:= '平板送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 平板送り軸';</v>
       </c>
       <c r="AE4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet feed shaft
+	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet feed shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis2】 Flat sheet feed shaft';
+			strRt	:= '平板送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 平板送り軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet feed shaft
+	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet feed shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis2】 Flat sheet feed shaft';
+			strRt	:= '平板送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 平板送り軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';</v>
       </c>
       <c r="AG4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet feed shaft
+	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet feed shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis2】 Flat sheet feed shaft';
+			strRt	:= '平板送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 平板送り軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -4971,12 +4965,12 @@
       <c r="AH4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet feed shaft
+	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet feed shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis2】 Flat sheet feed shaft';
+			strRt	:= '平板送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 平板送り軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4985,12 +4979,12 @@
       <c r="AI4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet feed shaft
+	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet feed shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis2】 Flat sheet feed shaft';
+			strRt	:= '平板送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 平板送り軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5002,12 +4996,12 @@
       <c r="AJ4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet feed shaft
+	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet feed shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis2】 Flat sheet feed shaft';
+			strRt	:= '平板送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 平板送り軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5019,12 +5013,12 @@
       <c r="AK4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet feed shaft
+	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet feed shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis2】 Flat sheet feed shaft';
+			strRt	:= '平板送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 平板送り軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5036,11 +5030,11 @@
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_sv3_error.xlsm]config によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ref="E5:E68" si="0">E4</f>
@@ -5058,15 +5052,15 @@
       </c>
       <c r="I5" t="str">
         <f ca="1"/>
-        <v>Foil wax feed shaft</v>
+        <v>箔ロウ送り軸</v>
       </c>
       <c r="J5" t="str">
         <f ca="1"/>
-        <v>Foil wax feed shaft</v>
+        <v>箔ロウ送り軸</v>
       </c>
       <c r="L5" t="str">
         <f ca="1"/>
-        <v>【axis3】 Foil wax feed shaft</v>
+        <v>【axis3】 箔ロウ送り軸</v>
       </c>
       <c r="M5" t="str">
         <v>AZM46AC-HP9+AZD-CEP+CC070VZR</v>
@@ -5095,75 +5089,75 @@
       <c r="Z5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax feed shaft
+	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AA5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax feed shaft
+	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax feed shaft
+	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax feed shaft';</v>
+			strRt	:= '箔ロウ送り軸';</v>
       </c>
       <c r="AC5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax feed shaft
+	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax feed shaft';
+			strRt	:= '箔ロウ送り軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax feed shaft
+	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax feed shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis3】 Foil wax feed shaft';</v>
+			strRt	:= '箔ロウ送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 箔ロウ送り軸';</v>
       </c>
       <c r="AE5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax feed shaft
+	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax feed shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis3】 Foil wax feed shaft';
+			strRt	:= '箔ロウ送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 箔ロウ送り軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax feed shaft
+	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax feed shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis3】 Foil wax feed shaft';
+			strRt	:= '箔ロウ送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 箔ロウ送り軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';</v>
       </c>
       <c r="AG5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax feed shaft
+	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax feed shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis3】 Foil wax feed shaft';
+			strRt	:= '箔ロウ送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 箔ロウ送り軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5171,12 +5165,12 @@
       <c r="AH5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax feed shaft
+	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax feed shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis3】 Foil wax feed shaft';
+			strRt	:= '箔ロウ送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 箔ロウ送り軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5185,12 +5179,12 @@
       <c r="AI5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax feed shaft
+	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax feed shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis3】 Foil wax feed shaft';
+			strRt	:= '箔ロウ送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 箔ロウ送り軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5202,12 +5196,12 @@
       <c r="AJ5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax feed shaft
+	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax feed shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis3】 Foil wax feed shaft';
+			strRt	:= '箔ロウ送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 箔ロウ送り軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5219,12 +5213,12 @@
       <c r="AK5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax feed shaft
+	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax feed shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis3】 Foil wax feed shaft';
+			strRt	:= '箔ロウ送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 箔ロウ送り軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5236,10 +5230,10 @@
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
@@ -5257,15 +5251,15 @@
       </c>
       <c r="I6" t="str">
         <f ca="1"/>
-        <v>Corrugated sheet feed</v>
+        <v>波板送り</v>
       </c>
       <c r="J6" t="str">
         <f ca="1"/>
-        <v>Corrugated sheet feed</v>
+        <v>波板送り</v>
       </c>
       <c r="L6" t="str">
         <f ca="1"/>
-        <v>【axis4】 Corrugated sheet feed</v>
+        <v>【axis4】 波板送り</v>
       </c>
       <c r="M6" t="str">
         <v>AZM46AC-HP9+AZD-CEP+CC070VZR</v>
@@ -5294,75 +5288,75 @@
       <c r="Z6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet feed
+	//波板送り
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AA6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet feed
+	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet feed
+	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet feed';</v>
+			strRt	:= '波板送り';</v>
       </c>
       <c r="AC6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet feed
+	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet feed';
+			strRt	:= '波板送り';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet feed
+	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet feed';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis4】 Corrugated sheet feed';</v>
+			strRt	:= '波板送り';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 波板送り';</v>
       </c>
       <c r="AE6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet feed
+	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet feed';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis4】 Corrugated sheet feed';
+			strRt	:= '波板送り';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 波板送り';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet feed
+	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet feed';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis4】 Corrugated sheet feed';
+			strRt	:= '波板送り';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 波板送り';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';</v>
       </c>
       <c r="AG6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet feed
+	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet feed';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis4】 Corrugated sheet feed';
+			strRt	:= '波板送り';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 波板送り';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5370,12 +5364,12 @@
       <c r="AH6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet feed
+	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet feed';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis4】 Corrugated sheet feed';
+			strRt	:= '波板送り';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 波板送り';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5384,12 +5378,12 @@
       <c r="AI6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet feed
+	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet feed';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis4】 Corrugated sheet feed';
+			strRt	:= '波板送り';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 波板送り';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5401,12 +5395,12 @@
       <c r="AJ6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet feed
+	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet feed';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis4】 Corrugated sheet feed';
+			strRt	:= '波板送り';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 波板送り';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5418,12 +5412,12 @@
       <c r="AK6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet feed
+	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet feed';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis4】 Corrugated sheet feed';
+			strRt	:= '波板送り';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 波板送り';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5435,10 +5429,10 @@
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -5456,15 +5450,15 @@
       </c>
       <c r="I7" t="str">
         <f ca="1"/>
-        <v>Workpiece discharge up/down shaft</v>
+        <v>ワーク排出上下軸</v>
       </c>
       <c r="J7" t="str">
         <f ca="1"/>
-        <v>Workpiece discharge up/down shaft</v>
+        <v>ワーク排出上下軸</v>
       </c>
       <c r="L7" t="str">
         <f ca="1"/>
-        <v>【axis5】 Workpiece discharge up/down shaft</v>
+        <v>【axis5】 ワーク排出上下軸</v>
       </c>
       <c r="M7" t="str">
         <v>RCP6-SA7R-WA-56P-16-400-P5-S-B-MR</v>
@@ -5493,75 +5487,75 @@
       <c r="Z7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece discharge up/down shaft
+	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AA7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece discharge up/down shaft
+	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece discharge up/down shaft
+	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge up/down shaft';</v>
+			strRt	:= 'ワーク排出上下軸';</v>
       </c>
       <c r="AC7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece discharge up/down shaft
+	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge up/down shaft';
+			strRt	:= 'ワーク排出上下軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece discharge up/down shaft
+	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge up/down shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis5】 Workpiece discharge up/down shaft';</v>
+			strRt	:= 'ワーク排出上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 ワーク排出上下軸';</v>
       </c>
       <c r="AE7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece discharge up/down shaft
+	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge up/down shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis5】 Workpiece discharge up/down shaft';
+			strRt	:= 'ワーク排出上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 ワーク排出上下軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece discharge up/down shaft
+	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge up/down shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis5】 Workpiece discharge up/down shaft';
+			strRt	:= 'ワーク排出上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 ワーク排出上下軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';</v>
       </c>
       <c r="AG7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece discharge up/down shaft
+	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge up/down shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis5】 Workpiece discharge up/down shaft';
+			strRt	:= 'ワーク排出上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 ワーク排出上下軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5569,12 +5563,12 @@
       <c r="AH7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece discharge up/down shaft
+	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge up/down shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis5】 Workpiece discharge up/down shaft';
+			strRt	:= 'ワーク排出上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 ワーク排出上下軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5583,12 +5577,12 @@
       <c r="AI7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece discharge up/down shaft
+	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge up/down shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis5】 Workpiece discharge up/down shaft';
+			strRt	:= 'ワーク排出上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 ワーク排出上下軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5600,12 +5594,12 @@
       <c r="AJ7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece discharge up/down shaft
+	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge up/down shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis5】 Workpiece discharge up/down shaft';
+			strRt	:= 'ワーク排出上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 ワーク排出上下軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5617,12 +5611,12 @@
       <c r="AK7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece discharge up/down shaft
+	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge up/down shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis5】 Workpiece discharge up/down shaft';
+			strRt	:= 'ワーク排出上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 ワーク排出上下軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5634,10 +5628,10 @@
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -5655,15 +5649,15 @@
       </c>
       <c r="I8" t="str">
         <f ca="1"/>
-        <v>Circumference measuring probe up/down shaft</v>
+        <v>周長測定子上下軸</v>
       </c>
       <c r="J8" t="str">
         <f ca="1"/>
-        <v>Circumference measuring probe up/down shaft</v>
+        <v>周長測定子上下軸</v>
       </c>
       <c r="L8" t="str">
         <f ca="1"/>
-        <v>【axis6】 Circumference measuring probe up/down shaft</v>
+        <v>【axis6】 周長測定子上下軸</v>
       </c>
       <c r="M8" t="str">
         <v>RCA2-GS3NA-I-10-2-50-A6-M-K1</v>
@@ -5692,75 +5686,75 @@
       <c r="Z8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measuring probe up/down shaft
+	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AA8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measuring probe up/down shaft
+	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measuring probe up/down shaft
+	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measuring probe up/down shaft';</v>
+			strRt	:= '周長測定子上下軸';</v>
       </c>
       <c r="AC8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measuring probe up/down shaft
+	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measuring probe up/down shaft';
+			strRt	:= '周長測定子上下軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measuring probe up/down shaft
+	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measuring probe up/down shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis6】 Circumference measuring probe up/down shaft';</v>
+			strRt	:= '周長測定子上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 周長測定子上下軸';</v>
       </c>
       <c r="AE8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measuring probe up/down shaft
+	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measuring probe up/down shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis6】 Circumference measuring probe up/down shaft';
+			strRt	:= '周長測定子上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 周長測定子上下軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measuring probe up/down shaft
+	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measuring probe up/down shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis6】 Circumference measuring probe up/down shaft';
+			strRt	:= '周長測定子上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 周長測定子上下軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';</v>
       </c>
       <c r="AG8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measuring probe up/down shaft
+	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measuring probe up/down shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis6】 Circumference measuring probe up/down shaft';
+			strRt	:= '周長測定子上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 周長測定子上下軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5768,12 +5762,12 @@
       <c r="AH8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measuring probe up/down shaft
+	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measuring probe up/down shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis6】 Circumference measuring probe up/down shaft';
+			strRt	:= '周長測定子上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 周長測定子上下軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5782,12 +5776,12 @@
       <c r="AI8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measuring probe up/down shaft
+	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measuring probe up/down shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis6】 Circumference measuring probe up/down shaft';
+			strRt	:= '周長測定子上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 周長測定子上下軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5799,12 +5793,12 @@
       <c r="AJ8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measuring probe up/down shaft
+	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measuring probe up/down shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis6】 Circumference measuring probe up/down shaft';
+			strRt	:= '周長測定子上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 周長測定子上下軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5816,12 +5810,12 @@
       <c r="AK8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measuring probe up/down shaft
+	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measuring probe up/down shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis6】 Circumference measuring probe up/down shaft';
+			strRt	:= '周長測定子上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 周長測定子上下軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5833,10 +5827,10 @@
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -5854,15 +5848,15 @@
       </c>
       <c r="I9" t="str">
         <f ca="1"/>
-        <v>Workpiece (discharge) chuck shaft</v>
+        <v>ワーク(排出)チャック軸</v>
       </c>
       <c r="J9" t="str">
         <f ca="1"/>
-        <v>Workpiece (discharge) chuck shaft</v>
+        <v>ワーク(排出)チャック軸</v>
       </c>
       <c r="L9" t="str">
         <f ca="1"/>
-        <v>【axis7】 Workpiece (discharge) chuck shaft</v>
+        <v>【axis7】 ワーク(排出)チャック軸</v>
       </c>
       <c r="M9" t="str">
         <v>RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM</v>
@@ -5891,75 +5885,75 @@
       <c r="Z9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece (discharge) chuck shaft
+	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN</v>
       </c>
       <c r="AA9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece (discharge) chuck shaft
+	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece (discharge) chuck shaft
+	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece (discharge) chuck shaft';</v>
+			strRt	:= 'ワーク(排出)チャック軸';</v>
       </c>
       <c r="AC9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece (discharge) chuck shaft
+	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece (discharge) chuck shaft';
+			strRt	:= 'ワーク(排出)チャック軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece (discharge) chuck shaft
+	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece (discharge) chuck shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis7】 Workpiece (discharge) chuck shaft';</v>
+			strRt	:= 'ワーク(排出)チャック軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 ワーク(排出)チャック軸';</v>
       </c>
       <c r="AE9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece (discharge) chuck shaft
+	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece (discharge) chuck shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis7】 Workpiece (discharge) chuck shaft';
+			strRt	:= 'ワーク(排出)チャック軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 ワーク(排出)チャック軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece (discharge) chuck shaft
+	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece (discharge) chuck shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis7】 Workpiece (discharge) chuck shaft';
+			strRt	:= 'ワーク(排出)チャック軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 ワーク(排出)チャック軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';</v>
       </c>
       <c r="AG9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece (discharge) chuck shaft
+	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece (discharge) chuck shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis7】 Workpiece (discharge) chuck shaft';
+			strRt	:= 'ワーク(排出)チャック軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 ワーク(排出)チャック軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5967,12 +5961,12 @@
       <c r="AH9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece (discharge) chuck shaft
+	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece (discharge) chuck shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis7】 Workpiece (discharge) chuck shaft';
+			strRt	:= 'ワーク(排出)チャック軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 ワーク(排出)チャック軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5981,12 +5975,12 @@
       <c r="AI9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece (discharge) chuck shaft
+	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece (discharge) chuck shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis7】 Workpiece (discharge) chuck shaft';
+			strRt	:= 'ワーク(排出)チャック軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 ワーク(排出)チャック軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5998,12 +5992,12 @@
       <c r="AJ9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece (discharge) chuck shaft
+	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece (discharge) chuck shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis7】 Workpiece (discharge) chuck shaft';
+			strRt	:= 'ワーク(排出)チャック軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 ワーク(排出)チャック軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6015,12 +6009,12 @@
       <c r="AK9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece (discharge) chuck shaft
+	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece (discharge) chuck shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis7】 Workpiece (discharge) chuck shaft';
+			strRt	:= 'ワーク(排出)チャック軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 ワーク(排出)チャック軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6047,15 +6041,15 @@
       </c>
       <c r="I10" t="str">
         <f ca="1"/>
-        <v>Y-axis: Welding torch forward/backward</v>
+        <v>Y軸：溶接トーチ前後</v>
       </c>
       <c r="J10" t="str">
         <f ca="1"/>
-        <v>Y-axis: Welding torch forward/backward</v>
+        <v>Y軸：溶接トーチ前後</v>
       </c>
       <c r="L10" t="str">
         <f ca="1"/>
-        <v>【axis8】 Y-axis: Welding torch forward/backward</v>
+        <v>【axis8】 Y軸：溶接トーチ前後</v>
       </c>
       <c r="M10" t="str">
         <v>ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③</v>
@@ -6084,75 +6078,75 @@
       <c r="Z10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y-axis: Welding torch forward/backward
+	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN</v>
       </c>
       <c r="AA10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y-axis: Welding torch forward/backward
+	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y-axis: Welding torch forward/backward
+	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y-axis: Welding torch forward/backward';</v>
+			strRt	:= 'Y軸：溶接トーチ前後';</v>
       </c>
       <c r="AC10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y-axis: Welding torch forward/backward
+	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y-axis: Welding torch forward/backward';
+			strRt	:= 'Y軸：溶接トーチ前後';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y-axis: Welding torch forward/backward
+	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y-axis: Welding torch forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis8】 Y-axis: Welding torch forward/backward';</v>
+			strRt	:= 'Y軸：溶接トーチ前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y軸：溶接トーチ前後';</v>
       </c>
       <c r="AE10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y-axis: Welding torch forward/backward
+	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y-axis: Welding torch forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis8】 Y-axis: Welding torch forward/backward';
+			strRt	:= 'Y軸：溶接トーチ前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y-axis: Welding torch forward/backward
+	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y-axis: Welding torch forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis8】 Y-axis: Welding torch forward/backward';
+			strRt	:= 'Y軸：溶接トーチ前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';</v>
       </c>
       <c r="AG10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y-axis: Welding torch forward/backward
+	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y-axis: Welding torch forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis8】 Y-axis: Welding torch forward/backward';
+			strRt	:= 'Y軸：溶接トーチ前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -6160,12 +6154,12 @@
       <c r="AH10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y-axis: Welding torch forward/backward
+	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y-axis: Welding torch forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis8】 Y-axis: Welding torch forward/backward';
+			strRt	:= 'Y軸：溶接トーチ前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6174,12 +6168,12 @@
       <c r="AI10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y-axis: Welding torch forward/backward
+	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y-axis: Welding torch forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis8】 Y-axis: Welding torch forward/backward';
+			strRt	:= 'Y軸：溶接トーチ前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6191,12 +6185,12 @@
       <c r="AJ10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y-axis: Welding torch forward/backward
+	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y-axis: Welding torch forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis8】 Y-axis: Welding torch forward/backward';
+			strRt	:= 'Y軸：溶接トーチ前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6208,12 +6202,12 @@
       <c r="AK10" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Y-axis: Welding torch forward/backward
+	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y-axis: Welding torch forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis8】 Y-axis: Welding torch forward/backward';
+			strRt	:= 'Y軸：溶接トーチ前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6240,15 +6234,15 @@
       </c>
       <c r="I11" t="str">
         <f ca="1"/>
-        <v>Z-axis: Welding torch up/down</v>
+        <v>Z軸：溶接トーチ上下</v>
       </c>
       <c r="J11" t="str">
         <f ca="1"/>
-        <v>Z-axis: Welding torch up/down</v>
+        <v>Z軸：溶接トーチ上下</v>
       </c>
       <c r="L11" t="str">
         <f ca="1"/>
-        <v>【axis9】 Z-axis: Welding torch up/down</v>
+        <v>【axis9】 Z軸：溶接トーチ上下</v>
       </c>
       <c r="M11" t="str">
         <v>ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤</v>
@@ -6277,75 +6271,75 @@
       <c r="Z11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z-axis: Welding torch up/down
+	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN</v>
       </c>
       <c r="AA11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z-axis: Welding torch up/down
+	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z-axis: Welding torch up/down
+	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z-axis: Welding torch up/down';</v>
+			strRt	:= 'Z軸：溶接トーチ上下';</v>
       </c>
       <c r="AC11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z-axis: Welding torch up/down
+	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z-axis: Welding torch up/down';
+			strRt	:= 'Z軸：溶接トーチ上下';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z-axis: Welding torch up/down
+	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z-axis: Welding torch up/down';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis9】 Z-axis: Welding torch up/down';</v>
+			strRt	:= 'Z軸：溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z軸：溶接トーチ上下';</v>
       </c>
       <c r="AE11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z-axis: Welding torch up/down
+	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z-axis: Welding torch up/down';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis9】 Z-axis: Welding torch up/down';
+			strRt	:= 'Z軸：溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z-axis: Welding torch up/down
+	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z-axis: Welding torch up/down';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis9】 Z-axis: Welding torch up/down';
+			strRt	:= 'Z軸：溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';</v>
       </c>
       <c r="AG11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z-axis: Welding torch up/down
+	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z-axis: Welding torch up/down';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis9】 Z-axis: Welding torch up/down';
+			strRt	:= 'Z軸：溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -6353,12 +6347,12 @@
       <c r="AH11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z-axis: Welding torch up/down
+	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z-axis: Welding torch up/down';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis9】 Z-axis: Welding torch up/down';
+			strRt	:= 'Z軸：溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6367,12 +6361,12 @@
       <c r="AI11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z-axis: Welding torch up/down
+	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z-axis: Welding torch up/down';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis9】 Z-axis: Welding torch up/down';
+			strRt	:= 'Z軸：溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6384,12 +6378,12 @@
       <c r="AJ11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z-axis: Welding torch up/down
+	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z-axis: Welding torch up/down';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis9】 Z-axis: Welding torch up/down';
+			strRt	:= 'Z軸：溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6401,12 +6395,12 @@
       <c r="AK11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Z-axis: Welding torch up/down
+	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z-axis: Welding torch up/down';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis9】 Z-axis: Welding torch up/down';
+			strRt	:= 'Z軸：溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6433,15 +6427,15 @@
       </c>
       <c r="I12" t="str">
         <f ca="1"/>
-        <v>Binder supply pump motor</v>
+        <v>バインダー供給ポンプモータ</v>
       </c>
       <c r="J12" t="str">
         <f ca="1"/>
-        <v>Binder supply pump motor</v>
+        <v>バインダー供給ポンプモータ</v>
       </c>
       <c r="L12" t="str">
         <f ca="1"/>
-        <v>【axis10】 Binder supply pump motor</v>
+        <v>【axis10】 バインダー供給ポンプモータ</v>
       </c>
       <c r="M12" t="str">
         <v/>
@@ -6470,75 +6464,75 @@
       <c r="Z12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Binder supply pump motor
+	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN</v>
       </c>
       <c r="AA12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Binder supply pump motor
+	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Binder supply pump motor
+	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Binder supply pump motor';</v>
+			strRt	:= 'バインダー供給ポンプモータ';</v>
       </c>
       <c r="AC12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Binder supply pump motor
+	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Binder supply pump motor';
+			strRt	:= 'バインダー供給ポンプモータ';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Binder supply pump motor
+	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Binder supply pump motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis10】 Binder supply pump motor';</v>
+			strRt	:= 'バインダー供給ポンプモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 バインダー供給ポンプモータ';</v>
       </c>
       <c r="AE12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Binder supply pump motor
+	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Binder supply pump motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis10】 Binder supply pump motor';
+			strRt	:= 'バインダー供給ポンプモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 バインダー供給ポンプモータ';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Binder supply pump motor
+	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Binder supply pump motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis10】 Binder supply pump motor';
+			strRt	:= 'バインダー供給ポンプモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 バインダー供給ポンプモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AG12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Binder supply pump motor
+	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Binder supply pump motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis10】 Binder supply pump motor';
+			strRt	:= 'バインダー供給ポンプモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 バインダー供給ポンプモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -6546,12 +6540,12 @@
       <c r="AH12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Binder supply pump motor
+	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Binder supply pump motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis10】 Binder supply pump motor';
+			strRt	:= 'バインダー供給ポンプモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 バインダー供給ポンプモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6560,12 +6554,12 @@
       <c r="AI12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Binder supply pump motor
+	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Binder supply pump motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis10】 Binder supply pump motor';
+			strRt	:= 'バインダー供給ポンプモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 バインダー供給ポンプモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6577,12 +6571,12 @@
       <c r="AJ12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Binder supply pump motor
+	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Binder supply pump motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis10】 Binder supply pump motor';
+			strRt	:= 'バインダー供給ポンプモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 バインダー供給ポンプモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6594,12 +6588,12 @@
       <c r="AK12" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Binder supply pump motor
+	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Binder supply pump motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis10】 Binder supply pump motor';
+			strRt	:= 'バインダー供給ポンプモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 バインダー供給ポンプモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6611,19 +6605,19 @@
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B13" t="str">
         <f ca="1">$AK$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_sv3_error.xlsm]config によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
-	//Foil wax reel shaft
+	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax reel shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis1】 Foil wax reel shaft';
+			strRt	:= '箔ロウリール軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 箔ロウリール軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '5TK20GN-CW2J+5GN180K';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6631,12 +6625,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Flat sheet feed shaft
+	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet feed shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis2】 Flat sheet feed shaft';
+			strRt	:= '平板送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 平板送り軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6644,12 +6638,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Foil wax feed shaft
+	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax feed shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis3】 Foil wax feed shaft';
+			strRt	:= '箔ロウ送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 箔ロウ送り軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6657,12 +6651,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Corrugated sheet feed
+	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet feed';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis4】 Corrugated sheet feed';
+			strRt	:= '波板送り';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 波板送り';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6670,12 +6664,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Workpiece discharge up/down shaft
+	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge up/down shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis5】 Workpiece discharge up/down shaft';
+			strRt	:= 'ワーク排出上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 ワーク排出上下軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6683,12 +6677,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Circumference measuring probe up/down shaft
+	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measuring probe up/down shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis6】 Circumference measuring probe up/down shaft';
+			strRt	:= '周長測定子上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 周長測定子上下軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6696,12 +6690,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Workpiece (discharge) chuck shaft
+	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece (discharge) chuck shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis7】 Workpiece (discharge) chuck shaft';
+			strRt	:= 'ワーク(排出)チャック軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 ワーク(排出)チャック軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6709,12 +6703,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Y-axis: Welding torch forward/backward
+	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y-axis: Welding torch forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis8】 Y-axis: Welding torch forward/backward';
+			strRt	:= 'Y軸：溶接トーチ前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6722,12 +6716,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Z-axis: Welding torch up/down
+	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z-axis: Welding torch up/down';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis9】 Z-axis: Welding torch up/down';
+			strRt	:= 'Z軸：溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6735,12 +6729,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Binder supply pump motor
+	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Binder supply pump motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis10】 Binder supply pump motor';
+			strRt	:= 'バインダー供給ポンプモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 バインダー供給ポンプモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6748,12 +6742,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Corrugated sheet reel motor
+	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet reel motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis11】 Corrugated sheet reel motor';
+			strRt	:= '波板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 波板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6761,12 +6755,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Flat sheet reel motor
+	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet reel motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis12】 Flat sheet reel motor';
+			strRt	:= '平板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 平板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6774,12 +6768,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding main shaft
+	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding main shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis13】 Winding main shaft';
+			strRt	:= '巻取り主軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 巻取り主軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-B075AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6787,12 +6781,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Workpiece width adjustment shaft
+	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece width adjustment shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis14】 Workpiece width adjustment shaft';
+			strRt	:= 'ワーク幅調整軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 ワーク幅調整軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-M040AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6800,12 +6794,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//T-roll rotation shaft
+	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll rotation shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 T-roll rotation shaft';
+			strRt	:= 'Tロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 Tロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6813,12 +6807,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Rotor unit X-roll rotation shaft
+	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Rotor unit X-roll rotation shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis16】 Rotor unit X-roll rotation shaft';
+			strRt	:= 'ロータユニットXロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 ロータユニットXロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6831,12 +6825,12 @@
 	END_IF;
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//Workpiece discharge front and rear axis
+	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge front and rear axis';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【EC1】 Workpiece discharge front and rear axis';
+			strRt	:= 'ワーク排出前後軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 ワーク排出前後軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'EC-S4HR-200-7-ML-TMD2';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6849,12 +6843,12 @@
 	END_IF;
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//Winding shaft center forward/backward
+	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding shaft center forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder1】 Winding shaft center forward/backward';
+			strRt	:= '巻取り軸芯前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 巻取り軸芯前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6862,12 +6856,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//T-roll gluing ①
+	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder2】 T-roll gluing ①';
+			strRt	:= 'Tロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 Tロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6875,12 +6869,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//T-roll gluing ②
+	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder3】 T-roll gluing ②';
+			strRt	:= 'Tロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 Tロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6888,12 +6882,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Flat sheet lower auxiliary plate release
+	//平板補助プレート
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet lower auxiliary plate release';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder4】 Flat sheet lower auxiliary plate release';
+			strRt	:= '平板補助プレート';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 平板補助プレート';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6901,12 +6895,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Flat sheet chuck (hand) forward/backward
+	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck (hand) forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder5】 Flat sheet chuck (hand) forward/backward';
+			strRt	:= '平板チャック(ハンド)前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MXQ20-50A-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6914,12 +6908,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Flat sheet chuck open/close
+	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder6】 Flat sheet chuck open/close';
+			strRt	:= '平板チャック開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 平板チャック開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MHF2-16D1-M9BL-X83C1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6927,12 +6921,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Flat sheet clamp up/down ①
+	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet clamp up/down ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 Flat sheet clamp up/down ①';
+			strRt	:= '平板押え上下①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6940,12 +6934,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Foil wax clamp up/down
+	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax clamp up/down';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder8】 Foil wax clamp up/down';
+			strRt	:= '箔ロウ押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 箔ロウ押え上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2D25-20DMZ-M9BM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6953,12 +6947,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Foil wax cut
+	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax cut';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder9】 Foil wax cut';
+			strRt	:= '箔ロウカット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 箔ロウカット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQSKB16-10DM-M9NWVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6966,12 +6960,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Corrugated sheet clamp
+	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet clamp';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder10】 Corrugated sheet clamp';
+			strRt	:= '波板押え';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 波板押え';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6979,12 +6973,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Flat sheet cutter blade push-out
+	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade push-out';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder11】 Flat sheet cutter blade push-out';
+			strRt	:= '平板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 平板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6992,12 +6986,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Flat sheet cutter blade open/close
+	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder12】 Flat sheet cutter blade open/close';
+			strRt	:= '平板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 平板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-10DMZ-L-A93M';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7005,12 +6999,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Corrugated sheet cutter blade push-out
+	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade push-out';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder13】 Corrugated sheet cutter blade push-out';
+			strRt	:= '波板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 波板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7018,12 +7012,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Corrugated sheet cutter blade open/close
+	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder14】 Corrugated sheet cutter blade open/close';
+			strRt	:= '波板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 波板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7031,12 +7025,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Corrugated sheet cutter auxiliary
+	//波板カット補助
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder15】 Corrugated sheet cutter auxiliary';
+			strRt	:= '波板カット補助';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 波板カット補助';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7044,12 +7038,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Corrugated sheet cutter auxiliary L
+	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary L';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder16】 Corrugated sheet cutter auxiliary L';
+			strRt	:= '波板カット補助L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 波板カット補助L';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7057,12 +7051,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//X-roll gluing ①
+	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder17】 X-roll gluing ①';
+			strRt	:= 'Xロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 Xロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7070,12 +7064,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//X-roll gluing ②
+	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder18】 X-roll gluing ②';
+			strRt	:= 'Xロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 Xロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7083,12 +7077,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//X-roll flat plate pressing
+	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll flat plate pressing';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder19】 X-roll flat plate pressing';
+			strRt	:= 'Xロール平板押付';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 Xロール平板押付';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '不明';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7120,15 +7114,15 @@
       </c>
       <c r="I13" t="str">
         <f ca="1"/>
-        <v>Corrugated sheet reel motor</v>
+        <v>波板リールモータ</v>
       </c>
       <c r="J13" t="str">
         <f ca="1"/>
-        <v>Corrugated sheet reel motor</v>
+        <v>波板リールモータ</v>
       </c>
       <c r="L13" t="str">
         <f ca="1"/>
-        <v>【axis11】 Corrugated sheet reel motor</v>
+        <v>【axis11】 波板リールモータ</v>
       </c>
       <c r="M13" t="str">
         <v/>
@@ -7157,75 +7151,75 @@
       <c r="Z13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet reel motor
+	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN</v>
       </c>
       <c r="AA13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet reel motor
+	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet reel motor
+	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet reel motor';</v>
+			strRt	:= '波板リールモータ';</v>
       </c>
       <c r="AC13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet reel motor
+	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet reel motor';
+			strRt	:= '波板リールモータ';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet reel motor
+	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet reel motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis11】 Corrugated sheet reel motor';</v>
+			strRt	:= '波板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 波板リールモータ';</v>
       </c>
       <c r="AE13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet reel motor
+	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet reel motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis11】 Corrugated sheet reel motor';
+			strRt	:= '波板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 波板リールモータ';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet reel motor
+	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet reel motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis11】 Corrugated sheet reel motor';
+			strRt	:= '波板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 波板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AG13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet reel motor
+	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet reel motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis11】 Corrugated sheet reel motor';
+			strRt	:= '波板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 波板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7233,12 +7227,12 @@
       <c r="AH13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet reel motor
+	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet reel motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis11】 Corrugated sheet reel motor';
+			strRt	:= '波板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 波板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7247,12 +7241,12 @@
       <c r="AI13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet reel motor
+	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet reel motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis11】 Corrugated sheet reel motor';
+			strRt	:= '波板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 波板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7264,12 +7258,12 @@
       <c r="AJ13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet reel motor
+	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet reel motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis11】 Corrugated sheet reel motor';
+			strRt	:= '波板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 波板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7281,12 +7275,12 @@
       <c r="AK13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet reel motor
+	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet reel motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis11】 Corrugated sheet reel motor';
+			strRt	:= '波板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 波板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7298,7 +7292,7 @@
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B14" t="str">
         <f>IF(LEN(AI1),"●"&amp;B27&amp;CHAR(10)&amp;AI1,"")</f>
@@ -7324,15 +7318,15 @@
       </c>
       <c r="I14" t="str">
         <f ca="1"/>
-        <v>Flat sheet reel motor</v>
+        <v>平板リールモータ</v>
       </c>
       <c r="J14" t="str">
         <f ca="1"/>
-        <v>Flat sheet reel motor</v>
+        <v>平板リールモータ</v>
       </c>
       <c r="L14" t="str">
         <f ca="1"/>
-        <v>【axis12】 Flat sheet reel motor</v>
+        <v>【axis12】 平板リールモータ</v>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -7361,75 +7355,75 @@
       <c r="Z14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet reel motor
+	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN</v>
       </c>
       <c r="AA14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet reel motor
+	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet reel motor
+	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet reel motor';</v>
+			strRt	:= '平板リールモータ';</v>
       </c>
       <c r="AC14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet reel motor
+	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet reel motor';
+			strRt	:= '平板リールモータ';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet reel motor
+	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet reel motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis12】 Flat sheet reel motor';</v>
+			strRt	:= '平板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 平板リールモータ';</v>
       </c>
       <c r="AE14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet reel motor
+	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet reel motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis12】 Flat sheet reel motor';
+			strRt	:= '平板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 平板リールモータ';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet reel motor
+	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet reel motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis12】 Flat sheet reel motor';
+			strRt	:= '平板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 平板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AG14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet reel motor
+	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet reel motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis12】 Flat sheet reel motor';
+			strRt	:= '平板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 平板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7437,12 +7431,12 @@
       <c r="AH14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet reel motor
+	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet reel motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis12】 Flat sheet reel motor';
+			strRt	:= '平板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 平板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7451,12 +7445,12 @@
       <c r="AI14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet reel motor
+	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet reel motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis12】 Flat sheet reel motor';
+			strRt	:= '平板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 平板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7468,12 +7462,12 @@
       <c r="AJ14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet reel motor
+	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet reel motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis12】 Flat sheet reel motor';
+			strRt	:= '平板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 平板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7485,12 +7479,12 @@
       <c r="AK14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet reel motor
+	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet reel motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis12】 Flat sheet reel motor';
+			strRt	:= '平板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 平板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7517,15 +7511,15 @@
       </c>
       <c r="I15" t="str">
         <f ca="1"/>
-        <v>Winding main shaft</v>
+        <v>巻取り主軸</v>
       </c>
       <c r="J15" t="str">
         <f ca="1"/>
-        <v>Winding main shaft</v>
+        <v>巻取り主軸</v>
       </c>
       <c r="L15" t="str">
         <f ca="1"/>
-        <v>【axis13】 Winding main shaft</v>
+        <v>【axis13】 巻取り主軸</v>
       </c>
       <c r="M15" t="str">
         <v>SV3-B075AK</v>
@@ -7554,75 +7548,75 @@
       <c r="Z15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding main shaft
+	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN</v>
       </c>
       <c r="AA15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding main shaft
+	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding main shaft
+	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding main shaft';</v>
+			strRt	:= '巻取り主軸';</v>
       </c>
       <c r="AC15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding main shaft
+	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding main shaft';
+			strRt	:= '巻取り主軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding main shaft
+	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding main shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis13】 Winding main shaft';</v>
+			strRt	:= '巻取り主軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 巻取り主軸';</v>
       </c>
       <c r="AE15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding main shaft
+	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding main shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis13】 Winding main shaft';
+			strRt	:= '巻取り主軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 巻取り主軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding main shaft
+	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding main shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis13】 Winding main shaft';
+			strRt	:= '巻取り主軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 巻取り主軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-B075AK';</v>
       </c>
       <c r="AG15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding main shaft
+	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding main shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis13】 Winding main shaft';
+			strRt	:= '巻取り主軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 巻取り主軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-B075AK';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7630,12 +7624,12 @@
       <c r="AH15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding main shaft
+	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding main shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis13】 Winding main shaft';
+			strRt	:= '巻取り主軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 巻取り主軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-B075AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7644,12 +7638,12 @@
       <c r="AI15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding main shaft
+	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding main shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis13】 Winding main shaft';
+			strRt	:= '巻取り主軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 巻取り主軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-B075AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7661,12 +7655,12 @@
       <c r="AJ15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding main shaft
+	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding main shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis13】 Winding main shaft';
+			strRt	:= '巻取り主軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 巻取り主軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-B075AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7678,12 +7672,12 @@
       <c r="AK15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding main shaft
+	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding main shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis13】 Winding main shaft';
+			strRt	:= '巻取り主軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 巻取り主軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-B075AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7710,15 +7704,15 @@
       </c>
       <c r="I16" t="str">
         <f ca="1"/>
-        <v>Workpiece width adjustment shaft</v>
+        <v>ワーク幅調整軸</v>
       </c>
       <c r="J16" t="str">
         <f ca="1"/>
-        <v>Workpiece width adjustment shaft</v>
+        <v>ワーク幅調整軸</v>
       </c>
       <c r="L16" t="str">
         <f ca="1"/>
-        <v>【axis14】 Workpiece width adjustment shaft</v>
+        <v>【axis14】 ワーク幅調整軸</v>
       </c>
       <c r="M16" t="str">
         <v>SV3-M040AK</v>
@@ -7747,75 +7741,75 @@
       <c r="Z16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece width adjustment shaft
+	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN</v>
       </c>
       <c r="AA16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece width adjustment shaft
+	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece width adjustment shaft
+	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece width adjustment shaft';</v>
+			strRt	:= 'ワーク幅調整軸';</v>
       </c>
       <c r="AC16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece width adjustment shaft
+	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece width adjustment shaft';
+			strRt	:= 'ワーク幅調整軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece width adjustment shaft
+	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece width adjustment shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis14】 Workpiece width adjustment shaft';</v>
+			strRt	:= 'ワーク幅調整軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 ワーク幅調整軸';</v>
       </c>
       <c r="AE16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece width adjustment shaft
+	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece width adjustment shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis14】 Workpiece width adjustment shaft';
+			strRt	:= 'ワーク幅調整軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 ワーク幅調整軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece width adjustment shaft
+	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece width adjustment shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis14】 Workpiece width adjustment shaft';
+			strRt	:= 'ワーク幅調整軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 ワーク幅調整軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-M040AK';</v>
       </c>
       <c r="AG16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece width adjustment shaft
+	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece width adjustment shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis14】 Workpiece width adjustment shaft';
+			strRt	:= 'ワーク幅調整軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 ワーク幅調整軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-M040AK';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7823,12 +7817,12 @@
       <c r="AH16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece width adjustment shaft
+	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece width adjustment shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis14】 Workpiece width adjustment shaft';
+			strRt	:= 'ワーク幅調整軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 ワーク幅調整軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-M040AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7837,12 +7831,12 @@
       <c r="AI16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece width adjustment shaft
+	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece width adjustment shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis14】 Workpiece width adjustment shaft';
+			strRt	:= 'ワーク幅調整軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 ワーク幅調整軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-M040AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7854,12 +7848,12 @@
       <c r="AJ16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece width adjustment shaft
+	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece width adjustment shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis14】 Workpiece width adjustment shaft';
+			strRt	:= 'ワーク幅調整軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 ワーク幅調整軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-M040AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7871,12 +7865,12 @@
       <c r="AK16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Workpiece width adjustment shaft
+	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece width adjustment shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis14】 Workpiece width adjustment shaft';
+			strRt	:= 'ワーク幅調整軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 ワーク幅調整軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-M040AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7903,15 +7897,15 @@
       </c>
       <c r="I17" t="str">
         <f ca="1"/>
-        <v>T-roll rotation shaft</v>
+        <v>Tロール回転軸</v>
       </c>
       <c r="J17" t="str">
         <f ca="1"/>
-        <v>T-roll rotation shaft</v>
+        <v>Tロール回転軸</v>
       </c>
       <c r="L17" t="str">
         <f ca="1"/>
-        <v>【axis15】 T-roll rotation shaft</v>
+        <v>【axis15】 Tロール回転軸</v>
       </c>
       <c r="M17" t="str">
         <v>M540-402</v>
@@ -7940,75 +7934,75 @@
       <c r="Z17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll rotation shaft
+	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN</v>
       </c>
       <c r="AA17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll rotation shaft
+	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll rotation shaft
+	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll rotation shaft';</v>
+			strRt	:= 'Tロール回転軸';</v>
       </c>
       <c r="AC17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll rotation shaft
+	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll rotation shaft';
+			strRt	:= 'Tロール回転軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll rotation shaft
+	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll rotation shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 T-roll rotation shaft';</v>
+			strRt	:= 'Tロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 Tロール回転軸';</v>
       </c>
       <c r="AE17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll rotation shaft
+	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll rotation shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 T-roll rotation shaft';
+			strRt	:= 'Tロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 Tロール回転軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll rotation shaft
+	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll rotation shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 T-roll rotation shaft';
+			strRt	:= 'Tロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 Tロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';</v>
       </c>
       <c r="AG17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll rotation shaft
+	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll rotation shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 T-roll rotation shaft';
+			strRt	:= 'Tロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 Tロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8016,12 +8010,12 @@
       <c r="AH17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll rotation shaft
+	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll rotation shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 T-roll rotation shaft';
+			strRt	:= 'Tロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 Tロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8030,12 +8024,12 @@
       <c r="AI17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll rotation shaft
+	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll rotation shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 T-roll rotation shaft';
+			strRt	:= 'Tロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 Tロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8047,12 +8041,12 @@
       <c r="AJ17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll rotation shaft
+	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll rotation shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 T-roll rotation shaft';
+			strRt	:= 'Tロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 Tロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8064,12 +8058,12 @@
       <c r="AK17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll rotation shaft
+	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll rotation shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 T-roll rotation shaft';
+			strRt	:= 'Tロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 Tロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8096,15 +8090,15 @@
       </c>
       <c r="I18" t="str">
         <f ca="1"/>
-        <v>Rotor unit X-roll rotation shaft</v>
+        <v>ロータユニットXロール回転軸</v>
       </c>
       <c r="J18" t="str">
         <f ca="1"/>
-        <v>Rotor unit X-roll rotation shaft</v>
+        <v>ロータユニットXロール回転軸</v>
       </c>
       <c r="L18" t="str">
         <f ca="1"/>
-        <v>【axis16】 Rotor unit X-roll rotation shaft</v>
+        <v>【axis16】 ロータユニットXロール回転軸</v>
       </c>
       <c r="M18" t="str">
         <v>M540-402</v>
@@ -8133,75 +8127,75 @@
       <c r="Z18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Rotor unit X-roll rotation shaft
+	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN</v>
       </c>
       <c r="AA18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Rotor unit X-roll rotation shaft
+	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Rotor unit X-roll rotation shaft
+	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Rotor unit X-roll rotation shaft';</v>
+			strRt	:= 'ロータユニットXロール回転軸';</v>
       </c>
       <c r="AC18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Rotor unit X-roll rotation shaft
+	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Rotor unit X-roll rotation shaft';
+			strRt	:= 'ロータユニットXロール回転軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Rotor unit X-roll rotation shaft
+	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Rotor unit X-roll rotation shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis16】 Rotor unit X-roll rotation shaft';</v>
+			strRt	:= 'ロータユニットXロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 ロータユニットXロール回転軸';</v>
       </c>
       <c r="AE18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Rotor unit X-roll rotation shaft
+	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Rotor unit X-roll rotation shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis16】 Rotor unit X-roll rotation shaft';
+			strRt	:= 'ロータユニットXロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 ロータユニットXロール回転軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Rotor unit X-roll rotation shaft
+	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Rotor unit X-roll rotation shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis16】 Rotor unit X-roll rotation shaft';
+			strRt	:= 'ロータユニットXロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 ロータユニットXロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';</v>
       </c>
       <c r="AG18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Rotor unit X-roll rotation shaft
+	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Rotor unit X-roll rotation shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis16】 Rotor unit X-roll rotation shaft';
+			strRt	:= 'ロータユニットXロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 ロータユニットXロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8209,12 +8203,12 @@
       <c r="AH18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Rotor unit X-roll rotation shaft
+	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Rotor unit X-roll rotation shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis16】 Rotor unit X-roll rotation shaft';
+			strRt	:= 'ロータユニットXロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 ロータユニットXロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8223,12 +8217,12 @@
       <c r="AI18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Rotor unit X-roll rotation shaft
+	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Rotor unit X-roll rotation shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis16】 Rotor unit X-roll rotation shaft';
+			strRt	:= 'ロータユニットXロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 ロータユニットXロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8240,12 +8234,12 @@
       <c r="AJ18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Rotor unit X-roll rotation shaft
+	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Rotor unit X-roll rotation shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis16】 Rotor unit X-roll rotation shaft';
+			strRt	:= 'ロータユニットXロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 ロータユニットXロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8257,12 +8251,12 @@
       <c r="AK18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Rotor unit X-roll rotation shaft
+	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Rotor unit X-roll rotation shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis16】 Rotor unit X-roll rotation shaft';
+			strRt	:= 'ロータユニットXロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 ロータユニットXロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8666,10 +8660,10 @@
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="str">
         <f t="shared" si="0"/>
@@ -8868,10 +8862,10 @@
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B25" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E25" t="str">
         <f t="shared" si="0"/>
@@ -8972,10 +8966,10 @@
     </row>
     <row r="26" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B26" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E26" t="str">
         <f t="shared" si="0"/>
@@ -9076,10 +9070,10 @@
     </row>
     <row r="27" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B27" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E27" t="str">
         <f t="shared" si="0"/>
@@ -9180,10 +9174,10 @@
     </row>
     <row r="28" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B28" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E28" t="str">
         <f t="shared" si="0"/>
@@ -9284,10 +9278,10 @@
     </row>
     <row r="29" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B29" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E29" t="str">
         <f t="shared" si="0"/>
@@ -10668,7 +10662,7 @@
     </row>
     <row r="43" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E43" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F43">
         <f>COUNTIF(E$3:E43,E43)</f>
@@ -10682,15 +10676,15 @@
       </c>
       <c r="I43" t="str">
         <f ca="1"/>
-        <v>Workpiece discharge front and rear axis</v>
+        <v>ワーク排出前後軸</v>
       </c>
       <c r="J43" t="str">
         <f ca="1"/>
-        <v>Workpiece discharge front and rear axis</v>
+        <v>ワーク排出前後軸</v>
       </c>
       <c r="L43" t="str">
         <f ca="1"/>
-        <v>【EC1】 Workpiece discharge front and rear axis</v>
+        <v>【EC1】 ワーク排出前後軸</v>
       </c>
       <c r="M43" t="str">
         <v>EC-S4HR-200-7-ML-TMD2</v>
@@ -10722,7 +10716,7 @@
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//Workpiece discharge front and rear axis
+	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AA43" t="str">
@@ -10730,7 +10724,7 @@
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//Workpiece discharge front and rear axis
+	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -10739,20 +10733,20 @@
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//Workpiece discharge front and rear axis
+	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge front and rear axis';</v>
+			strRt	:= 'ワーク排出前後軸';</v>
       </c>
       <c r="AC43" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//Workpiece discharge front and rear axis
+	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge front and rear axis';
+			strRt	:= 'ワーク排出前後軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD43" t="str">
@@ -10760,24 +10754,24 @@
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//Workpiece discharge front and rear axis
+	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge front and rear axis';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【EC1】 Workpiece discharge front and rear axis';</v>
+			strRt	:= 'ワーク排出前後軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 ワーク排出前後軸';</v>
       </c>
       <c r="AE43" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//Workpiece discharge front and rear axis
+	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge front and rear axis';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【EC1】 Workpiece discharge front and rear axis';
+			strRt	:= 'ワーク排出前後軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 ワーク排出前後軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF43" t="str">
@@ -10785,12 +10779,12 @@
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//Workpiece discharge front and rear axis
+	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge front and rear axis';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【EC1】 Workpiece discharge front and rear axis';
+			strRt	:= 'ワーク排出前後軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 ワーク排出前後軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'EC-S4HR-200-7-ML-TMD2';</v>
       </c>
@@ -10799,12 +10793,12 @@
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//Workpiece discharge front and rear axis
+	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge front and rear axis';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【EC1】 Workpiece discharge front and rear axis';
+			strRt	:= 'ワーク排出前後軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 ワーク排出前後軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'EC-S4HR-200-7-ML-TMD2';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10814,12 +10808,12 @@
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//Workpiece discharge front and rear axis
+	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge front and rear axis';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【EC1】 Workpiece discharge front and rear axis';
+			strRt	:= 'ワーク排出前後軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 ワーク排出前後軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'EC-S4HR-200-7-ML-TMD2';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10830,12 +10824,12 @@
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//Workpiece discharge front and rear axis
+	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge front and rear axis';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【EC1】 Workpiece discharge front and rear axis';
+			strRt	:= 'ワーク排出前後軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 ワーク排出前後軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'EC-S4HR-200-7-ML-TMD2';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10849,12 +10843,12 @@
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//Workpiece discharge front and rear axis
+	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge front and rear axis';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【EC1】 Workpiece discharge front and rear axis';
+			strRt	:= 'ワーク排出前後軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 ワーク排出前後軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'EC-S4HR-200-7-ML-TMD2';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10868,12 +10862,12 @@
         <v xml:space="preserve">
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//Workpiece discharge front and rear axis
+	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge front and rear axis';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【EC1】 Workpiece discharge front and rear axis';
+			strRt	:= 'ワーク排出前後軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 ワーク排出前後軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'EC-S4HR-200-7-ML-TMD2';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12767,15 +12761,15 @@
       </c>
       <c r="I63" t="str">
         <f ca="1"/>
-        <v>Winding shaft center forward/backward</v>
+        <v>巻取り軸芯前後</v>
       </c>
       <c r="J63" t="str">
         <f ca="1"/>
-        <v>Winding shaft center forward/backward</v>
+        <v>巻取り軸芯前後</v>
       </c>
       <c r="L63" t="str">
         <f ca="1"/>
-        <v>【cylinder1】 Winding shaft center forward/backward</v>
+        <v>【cylinder1】 巻取り軸芯前後</v>
       </c>
       <c r="M63" t="str">
         <v>CDQ2A63-200DCZ-M9BVZ</v>
@@ -12807,7 +12801,7 @@
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//Winding shaft center forward/backward
+	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AA63" t="str">
@@ -12815,7 +12809,7 @@
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//Winding shaft center forward/backward
+	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -12824,20 +12818,20 @@
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//Winding shaft center forward/backward
+	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding shaft center forward/backward';</v>
+			strRt	:= '巻取り軸芯前後';</v>
       </c>
       <c r="AC63" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//Winding shaft center forward/backward
+	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding shaft center forward/backward';
+			strRt	:= '巻取り軸芯前後';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD63" t="str">
@@ -12845,24 +12839,24 @@
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//Winding shaft center forward/backward
+	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding shaft center forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder1】 Winding shaft center forward/backward';</v>
+			strRt	:= '巻取り軸芯前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 巻取り軸芯前後';</v>
       </c>
       <c r="AE63" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//Winding shaft center forward/backward
+	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding shaft center forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder1】 Winding shaft center forward/backward';
+			strRt	:= '巻取り軸芯前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 巻取り軸芯前後';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF63" t="str">
@@ -12870,12 +12864,12 @@
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//Winding shaft center forward/backward
+	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding shaft center forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder1】 Winding shaft center forward/backward';
+			strRt	:= '巻取り軸芯前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 巻取り軸芯前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';</v>
       </c>
@@ -12884,12 +12878,12 @@
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//Winding shaft center forward/backward
+	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding shaft center forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder1】 Winding shaft center forward/backward';
+			strRt	:= '巻取り軸芯前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 巻取り軸芯前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12899,12 +12893,12 @@
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//Winding shaft center forward/backward
+	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding shaft center forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder1】 Winding shaft center forward/backward';
+			strRt	:= '巻取り軸芯前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 巻取り軸芯前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12915,12 +12909,12 @@
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//Winding shaft center forward/backward
+	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding shaft center forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder1】 Winding shaft center forward/backward';
+			strRt	:= '巻取り軸芯前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 巻取り軸芯前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12934,12 +12928,12 @@
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//Winding shaft center forward/backward
+	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding shaft center forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder1】 Winding shaft center forward/backward';
+			strRt	:= '巻取り軸芯前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 巻取り軸芯前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12953,12 +12947,12 @@
         <v xml:space="preserve">
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//Winding shaft center forward/backward
+	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding shaft center forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder1】 Winding shaft center forward/backward';
+			strRt	:= '巻取り軸芯前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 巻取り軸芯前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12985,15 +12979,15 @@
       </c>
       <c r="I64" t="str">
         <f ca="1"/>
-        <v>T-roll gluing ①</v>
+        <v>Tロール糊付け①</v>
       </c>
       <c r="J64" t="str">
         <f ca="1"/>
-        <v>T-roll gluing ①</v>
+        <v>Tロール糊付け①</v>
       </c>
       <c r="L64" t="str">
         <f ca="1"/>
-        <v>【cylinder2】 T-roll gluing ①</v>
+        <v>【cylinder2】 Tロール糊付け①</v>
       </c>
       <c r="M64" t="str">
         <v>CDAS16×10-B-R</v>
@@ -13022,75 +13016,75 @@
       <c r="Z64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ①
+	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AA64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ①
+	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ①
+	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ①';</v>
+			strRt	:= 'Tロール糊付け①';</v>
       </c>
       <c r="AC64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ①
+	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ①';
+			strRt	:= 'Tロール糊付け①';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ①
+	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder2】 T-roll gluing ①';</v>
+			strRt	:= 'Tロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 Tロール糊付け①';</v>
       </c>
       <c r="AE64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ①
+	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder2】 T-roll gluing ①';
+			strRt	:= 'Tロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 Tロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ①
+	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder2】 T-roll gluing ①';
+			strRt	:= 'Tロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 Tロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';</v>
       </c>
       <c r="AG64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ①
+	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder2】 T-roll gluing ①';
+			strRt	:= 'Tロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 Tロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13098,12 +13092,12 @@
       <c r="AH64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ①
+	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder2】 T-roll gluing ①';
+			strRt	:= 'Tロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 Tロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13112,12 +13106,12 @@
       <c r="AI64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ①
+	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder2】 T-roll gluing ①';
+			strRt	:= 'Tロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 Tロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13129,12 +13123,12 @@
       <c r="AJ64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ①
+	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder2】 T-roll gluing ①';
+			strRt	:= 'Tロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 Tロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13146,12 +13140,12 @@
       <c r="AK64" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ①
+	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder2】 T-roll gluing ①';
+			strRt	:= 'Tロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 Tロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13178,15 +13172,15 @@
       </c>
       <c r="I65" t="str">
         <f ca="1"/>
-        <v>T-roll gluing ②</v>
+        <v>Tロール糊付け②</v>
       </c>
       <c r="J65" t="str">
         <f ca="1"/>
-        <v>T-roll gluing ②</v>
+        <v>Tロール糊付け②</v>
       </c>
       <c r="L65" t="str">
         <f ca="1"/>
-        <v>【cylinder3】 T-roll gluing ②</v>
+        <v>【cylinder3】 Tロール糊付け②</v>
       </c>
       <c r="M65" t="str">
         <v>CDAS16×10-B-R</v>
@@ -13215,75 +13209,75 @@
       <c r="Z65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ②
+	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AA65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ②
+	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ②
+	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ②';</v>
+			strRt	:= 'Tロール糊付け②';</v>
       </c>
       <c r="AC65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ②
+	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ②';
+			strRt	:= 'Tロール糊付け②';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ②
+	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder3】 T-roll gluing ②';</v>
+			strRt	:= 'Tロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 Tロール糊付け②';</v>
       </c>
       <c r="AE65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ②
+	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder3】 T-roll gluing ②';
+			strRt	:= 'Tロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 Tロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ②
+	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder3】 T-roll gluing ②';
+			strRt	:= 'Tロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 Tロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';</v>
       </c>
       <c r="AG65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ②
+	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder3】 T-roll gluing ②';
+			strRt	:= 'Tロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 Tロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13291,12 +13285,12 @@
       <c r="AH65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ②
+	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder3】 T-roll gluing ②';
+			strRt	:= 'Tロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 Tロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13305,12 +13299,12 @@
       <c r="AI65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ②
+	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder3】 T-roll gluing ②';
+			strRt	:= 'Tロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 Tロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13322,12 +13316,12 @@
       <c r="AJ65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ②
+	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder3】 T-roll gluing ②';
+			strRt	:= 'Tロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 Tロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13339,12 +13333,12 @@
       <c r="AK65" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//T-roll gluing ②
+	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder3】 T-roll gluing ②';
+			strRt	:= 'Tロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 Tロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13371,15 +13365,15 @@
       </c>
       <c r="I66" t="str">
         <f ca="1"/>
-        <v>Flat sheet lower auxiliary plate release</v>
+        <v>平板補助プレート</v>
       </c>
       <c r="J66" t="str">
         <f ca="1"/>
-        <v>Flat sheet lower auxiliary plate release</v>
+        <v>平板補助プレート</v>
       </c>
       <c r="L66" t="str">
         <f ca="1"/>
-        <v>【cylinder4】 Flat sheet lower auxiliary plate release</v>
+        <v>【cylinder4】 平板補助プレート</v>
       </c>
       <c r="M66" t="str">
         <v>CDJ2D16-45Z-W-M9BWZ-B</v>
@@ -13408,75 +13402,75 @@
       <c r="Z66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet lower auxiliary plate release
+	//平板補助プレート
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AA66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet lower auxiliary plate release
+	//平板補助プレート
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet lower auxiliary plate release
+	//平板補助プレート
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet lower auxiliary plate release';</v>
+			strRt	:= '平板補助プレート';</v>
       </c>
       <c r="AC66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet lower auxiliary plate release
+	//平板補助プレート
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet lower auxiliary plate release';
+			strRt	:= '平板補助プレート';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet lower auxiliary plate release
+	//平板補助プレート
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet lower auxiliary plate release';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder4】 Flat sheet lower auxiliary plate release';</v>
+			strRt	:= '平板補助プレート';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 平板補助プレート';</v>
       </c>
       <c r="AE66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet lower auxiliary plate release
+	//平板補助プレート
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet lower auxiliary plate release';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder4】 Flat sheet lower auxiliary plate release';
+			strRt	:= '平板補助プレート';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 平板補助プレート';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet lower auxiliary plate release
+	//平板補助プレート
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet lower auxiliary plate release';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder4】 Flat sheet lower auxiliary plate release';
+			strRt	:= '平板補助プレート';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 平板補助プレート';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';</v>
       </c>
       <c r="AG66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet lower auxiliary plate release
+	//平板補助プレート
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet lower auxiliary plate release';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder4】 Flat sheet lower auxiliary plate release';
+			strRt	:= '平板補助プレート';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 平板補助プレート';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13484,12 +13478,12 @@
       <c r="AH66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet lower auxiliary plate release
+	//平板補助プレート
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet lower auxiliary plate release';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder4】 Flat sheet lower auxiliary plate release';
+			strRt	:= '平板補助プレート';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 平板補助プレート';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13498,12 +13492,12 @@
       <c r="AI66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet lower auxiliary plate release
+	//平板補助プレート
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet lower auxiliary plate release';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder4】 Flat sheet lower auxiliary plate release';
+			strRt	:= '平板補助プレート';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 平板補助プレート';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13515,12 +13509,12 @@
       <c r="AJ66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet lower auxiliary plate release
+	//平板補助プレート
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet lower auxiliary plate release';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder4】 Flat sheet lower auxiliary plate release';
+			strRt	:= '平板補助プレート';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 平板補助プレート';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13532,12 +13526,12 @@
       <c r="AK66" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet lower auxiliary plate release
+	//平板補助プレート
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet lower auxiliary plate release';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder4】 Flat sheet lower auxiliary plate release';
+			strRt	:= '平板補助プレート';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 平板補助プレート';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13564,15 +13558,15 @@
       </c>
       <c r="I67" t="str">
         <f ca="1"/>
-        <v>Flat sheet chuck (hand) forward/backward</v>
+        <v>平板チャック(ハンド)前後</v>
       </c>
       <c r="J67" t="str">
         <f ca="1"/>
-        <v>Flat sheet chuck (hand) forward/backward</v>
+        <v>平板チャック(ハンド)前後</v>
       </c>
       <c r="L67" t="str">
         <f ca="1"/>
-        <v>【cylinder5】 Flat sheet chuck (hand) forward/backward</v>
+        <v>【cylinder5】 平板チャック(ハンド)前後</v>
       </c>
       <c r="M67" t="str">
         <v>MXQ20-50A-M9BZ</v>
@@ -13601,75 +13595,75 @@
       <c r="Z67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck (hand) forward/backward
+	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AA67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck (hand) forward/backward
+	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck (hand) forward/backward
+	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck (hand) forward/backward';</v>
+			strRt	:= '平板チャック(ハンド)前後';</v>
       </c>
       <c r="AC67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck (hand) forward/backward
+	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck (hand) forward/backward';
+			strRt	:= '平板チャック(ハンド)前後';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck (hand) forward/backward
+	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck (hand) forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder5】 Flat sheet chuck (hand) forward/backward';</v>
+			strRt	:= '平板チャック(ハンド)前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';</v>
       </c>
       <c r="AE67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck (hand) forward/backward
+	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck (hand) forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder5】 Flat sheet chuck (hand) forward/backward';
+			strRt	:= '平板チャック(ハンド)前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck (hand) forward/backward
+	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck (hand) forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder5】 Flat sheet chuck (hand) forward/backward';
+			strRt	:= '平板チャック(ハンド)前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MXQ20-50A-M9BZ';</v>
       </c>
       <c r="AG67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck (hand) forward/backward
+	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck (hand) forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder5】 Flat sheet chuck (hand) forward/backward';
+			strRt	:= '平板チャック(ハンド)前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MXQ20-50A-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13677,12 +13671,12 @@
       <c r="AH67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck (hand) forward/backward
+	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck (hand) forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder5】 Flat sheet chuck (hand) forward/backward';
+			strRt	:= '平板チャック(ハンド)前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MXQ20-50A-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13691,12 +13685,12 @@
       <c r="AI67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck (hand) forward/backward
+	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck (hand) forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder5】 Flat sheet chuck (hand) forward/backward';
+			strRt	:= '平板チャック(ハンド)前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MXQ20-50A-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13708,12 +13702,12 @@
       <c r="AJ67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck (hand) forward/backward
+	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck (hand) forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder5】 Flat sheet chuck (hand) forward/backward';
+			strRt	:= '平板チャック(ハンド)前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MXQ20-50A-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13725,12 +13719,12 @@
       <c r="AK67" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck (hand) forward/backward
+	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck (hand) forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder5】 Flat sheet chuck (hand) forward/backward';
+			strRt	:= '平板チャック(ハンド)前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MXQ20-50A-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13757,15 +13751,15 @@
       </c>
       <c r="I68" t="str">
         <f ca="1"/>
-        <v>Flat sheet chuck open/close</v>
+        <v>平板チャック開閉</v>
       </c>
       <c r="J68" t="str">
         <f ca="1"/>
-        <v>Flat sheet chuck open/close</v>
+        <v>平板チャック開閉</v>
       </c>
       <c r="L68" t="str">
         <f ca="1"/>
-        <v>【cylinder6】 Flat sheet chuck open/close</v>
+        <v>【cylinder6】 平板チャック開閉</v>
       </c>
       <c r="M68" t="str">
         <v>MHF2-16D1-M9BL-X83C1</v>
@@ -13794,75 +13788,75 @@
       <c r="Z68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck open/close
+	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AA68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck open/close
+	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck open/close
+	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck open/close';</v>
+			strRt	:= '平板チャック開閉';</v>
       </c>
       <c r="AC68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck open/close
+	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck open/close';
+			strRt	:= '平板チャック開閉';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck open/close
+	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder6】 Flat sheet chuck open/close';</v>
+			strRt	:= '平板チャック開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 平板チャック開閉';</v>
       </c>
       <c r="AE68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck open/close
+	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder6】 Flat sheet chuck open/close';
+			strRt	:= '平板チャック開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 平板チャック開閉';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck open/close
+	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder6】 Flat sheet chuck open/close';
+			strRt	:= '平板チャック開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 平板チャック開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MHF2-16D1-M9BL-X83C1';</v>
       </c>
       <c r="AG68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck open/close
+	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder6】 Flat sheet chuck open/close';
+			strRt	:= '平板チャック開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 平板チャック開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MHF2-16D1-M9BL-X83C1';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13870,12 +13864,12 @@
       <c r="AH68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck open/close
+	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder6】 Flat sheet chuck open/close';
+			strRt	:= '平板チャック開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 平板チャック開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MHF2-16D1-M9BL-X83C1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13884,12 +13878,12 @@
       <c r="AI68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck open/close
+	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder6】 Flat sheet chuck open/close';
+			strRt	:= '平板チャック開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 平板チャック開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MHF2-16D1-M9BL-X83C1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13901,12 +13895,12 @@
       <c r="AJ68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck open/close
+	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder6】 Flat sheet chuck open/close';
+			strRt	:= '平板チャック開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 平板チャック開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MHF2-16D1-M9BL-X83C1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13918,12 +13912,12 @@
       <c r="AK68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet chuck open/close
+	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder6】 Flat sheet chuck open/close';
+			strRt	:= '平板チャック開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 平板チャック開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MHF2-16D1-M9BL-X83C1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13950,15 +13944,15 @@
       </c>
       <c r="I69" t="str">
         <f ca="1"/>
-        <v>Flat sheet clamp up/down ①</v>
+        <v>平板押え上下①</v>
       </c>
       <c r="J69" t="str">
         <f ca="1"/>
-        <v>Flat sheet clamp up/down ①</v>
+        <v>平板押え上下①</v>
       </c>
       <c r="L69" t="str">
         <f ca="1"/>
-        <v>【cylinder7】 Flat sheet clamp up/down ①</v>
+        <v>【cylinder7】 平板押え上下①</v>
       </c>
       <c r="M69" t="str">
         <v>CDQ2B25-20DZ-M9BVM</v>
@@ -13987,75 +13981,75 @@
       <c r="Z69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet clamp up/down ①
+	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN</v>
       </c>
       <c r="AA69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet clamp up/down ①
+	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet clamp up/down ①
+	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet clamp up/down ①';</v>
+			strRt	:= '平板押え上下①';</v>
       </c>
       <c r="AC69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet clamp up/down ①
+	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet clamp up/down ①';
+			strRt	:= '平板押え上下①';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet clamp up/down ①
+	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet clamp up/down ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 Flat sheet clamp up/down ①';</v>
+			strRt	:= '平板押え上下①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下①';</v>
       </c>
       <c r="AE69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet clamp up/down ①
+	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet clamp up/down ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 Flat sheet clamp up/down ①';
+			strRt	:= '平板押え上下①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下①';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet clamp up/down ①
+	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet clamp up/down ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 Flat sheet clamp up/down ①';
+			strRt	:= '平板押え上下①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';</v>
       </c>
       <c r="AG69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet clamp up/down ①
+	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet clamp up/down ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 Flat sheet clamp up/down ①';
+			strRt	:= '平板押え上下①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14063,12 +14057,12 @@
       <c r="AH69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet clamp up/down ①
+	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet clamp up/down ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 Flat sheet clamp up/down ①';
+			strRt	:= '平板押え上下①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14077,12 +14071,12 @@
       <c r="AI69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet clamp up/down ①
+	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet clamp up/down ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 Flat sheet clamp up/down ①';
+			strRt	:= '平板押え上下①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14094,12 +14088,12 @@
       <c r="AJ69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet clamp up/down ①
+	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet clamp up/down ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 Flat sheet clamp up/down ①';
+			strRt	:= '平板押え上下①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14111,12 +14105,12 @@
       <c r="AK69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet clamp up/down ①
+	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet clamp up/down ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 Flat sheet clamp up/down ①';
+			strRt	:= '平板押え上下①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14143,15 +14137,15 @@
       </c>
       <c r="I70" t="str">
         <f ca="1"/>
-        <v>Foil wax clamp up/down</v>
+        <v>箔ロウ押え上下</v>
       </c>
       <c r="J70" t="str">
         <f ca="1"/>
-        <v>Foil wax clamp up/down</v>
+        <v>箔ロウ押え上下</v>
       </c>
       <c r="L70" t="str">
         <f ca="1"/>
-        <v>【cylinder8】 Foil wax clamp up/down</v>
+        <v>【cylinder8】 箔ロウ押え上下</v>
       </c>
       <c r="M70" t="str">
         <v>CDQ2D25-20DMZ-M9BM</v>
@@ -14180,75 +14174,75 @@
       <c r="Z70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax clamp up/down
+	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN</v>
       </c>
       <c r="AA70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax clamp up/down
+	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax clamp up/down
+	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax clamp up/down';</v>
+			strRt	:= '箔ロウ押え上下';</v>
       </c>
       <c r="AC70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax clamp up/down
+	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax clamp up/down';
+			strRt	:= '箔ロウ押え上下';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax clamp up/down
+	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax clamp up/down';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder8】 Foil wax clamp up/down';</v>
+			strRt	:= '箔ロウ押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 箔ロウ押え上下';</v>
       </c>
       <c r="AE70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax clamp up/down
+	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax clamp up/down';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder8】 Foil wax clamp up/down';
+			strRt	:= '箔ロウ押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 箔ロウ押え上下';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax clamp up/down
+	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax clamp up/down';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder8】 Foil wax clamp up/down';
+			strRt	:= '箔ロウ押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 箔ロウ押え上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2D25-20DMZ-M9BM';</v>
       </c>
       <c r="AG70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax clamp up/down
+	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax clamp up/down';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder8】 Foil wax clamp up/down';
+			strRt	:= '箔ロウ押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 箔ロウ押え上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2D25-20DMZ-M9BM';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14256,12 +14250,12 @@
       <c r="AH70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax clamp up/down
+	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax clamp up/down';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder8】 Foil wax clamp up/down';
+			strRt	:= '箔ロウ押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 箔ロウ押え上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2D25-20DMZ-M9BM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14270,12 +14264,12 @@
       <c r="AI70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax clamp up/down
+	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax clamp up/down';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder8】 Foil wax clamp up/down';
+			strRt	:= '箔ロウ押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 箔ロウ押え上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2D25-20DMZ-M9BM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14287,12 +14281,12 @@
       <c r="AJ70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax clamp up/down
+	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax clamp up/down';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder8】 Foil wax clamp up/down';
+			strRt	:= '箔ロウ押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 箔ロウ押え上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2D25-20DMZ-M9BM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14304,12 +14298,12 @@
       <c r="AK70" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax clamp up/down
+	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax clamp up/down';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder8】 Foil wax clamp up/down';
+			strRt	:= '箔ロウ押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 箔ロウ押え上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2D25-20DMZ-M9BM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14336,15 +14330,15 @@
       </c>
       <c r="I71" t="str">
         <f ca="1"/>
-        <v>Foil wax cut</v>
+        <v>箔ロウカット</v>
       </c>
       <c r="J71" t="str">
         <f ca="1"/>
-        <v>Foil wax cut</v>
+        <v>箔ロウカット</v>
       </c>
       <c r="L71" t="str">
         <f ca="1"/>
-        <v>【cylinder9】 Foil wax cut</v>
+        <v>【cylinder9】 箔ロウカット</v>
       </c>
       <c r="M71" t="str">
         <v>CDQSKB16-10DM-M9NWVZ</v>
@@ -14373,75 +14367,75 @@
       <c r="Z71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax cut
+	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN</v>
       </c>
       <c r="AA71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax cut
+	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax cut
+	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax cut';</v>
+			strRt	:= '箔ロウカット';</v>
       </c>
       <c r="AC71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax cut
+	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax cut';
+			strRt	:= '箔ロウカット';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax cut
+	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax cut';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder9】 Foil wax cut';</v>
+			strRt	:= '箔ロウカット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 箔ロウカット';</v>
       </c>
       <c r="AE71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax cut
+	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax cut';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder9】 Foil wax cut';
+			strRt	:= '箔ロウカット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 箔ロウカット';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax cut
+	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax cut';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder9】 Foil wax cut';
+			strRt	:= '箔ロウカット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 箔ロウカット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQSKB16-10DM-M9NWVZ';</v>
       </c>
       <c r="AG71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax cut
+	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax cut';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder9】 Foil wax cut';
+			strRt	:= '箔ロウカット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 箔ロウカット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQSKB16-10DM-M9NWVZ';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14449,12 +14443,12 @@
       <c r="AH71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax cut
+	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax cut';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder9】 Foil wax cut';
+			strRt	:= '箔ロウカット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 箔ロウカット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQSKB16-10DM-M9NWVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14463,12 +14457,12 @@
       <c r="AI71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax cut
+	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax cut';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder9】 Foil wax cut';
+			strRt	:= '箔ロウカット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 箔ロウカット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQSKB16-10DM-M9NWVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14480,12 +14474,12 @@
       <c r="AJ71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax cut
+	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax cut';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder9】 Foil wax cut';
+			strRt	:= '箔ロウカット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 箔ロウカット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQSKB16-10DM-M9NWVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14497,12 +14491,12 @@
       <c r="AK71" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax cut
+	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax cut';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder9】 Foil wax cut';
+			strRt	:= '箔ロウカット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 箔ロウカット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQSKB16-10DM-M9NWVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14529,15 +14523,15 @@
       </c>
       <c r="I72" t="str">
         <f ca="1"/>
-        <v>Corrugated sheet clamp</v>
+        <v>波板押え</v>
       </c>
       <c r="J72" t="str">
         <f ca="1"/>
-        <v>Corrugated sheet clamp</v>
+        <v>波板押え</v>
       </c>
       <c r="L72" t="str">
         <f ca="1"/>
-        <v>【cylinder10】 Corrugated sheet clamp</v>
+        <v>【cylinder10】 波板押え</v>
       </c>
       <c r="M72" t="str">
         <v>CDQ2B25-20DZ-M9BVM</v>
@@ -14566,75 +14560,75 @@
       <c r="Z72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet clamp
+	//波板押え
 	ELSIF uiInfoIdx = 10 THEN</v>
       </c>
       <c r="AA72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet clamp
+	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet clamp
+	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet clamp';</v>
+			strRt	:= '波板押え';</v>
       </c>
       <c r="AC72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet clamp
+	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet clamp';
+			strRt	:= '波板押え';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet clamp
+	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet clamp';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder10】 Corrugated sheet clamp';</v>
+			strRt	:= '波板押え';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 波板押え';</v>
       </c>
       <c r="AE72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet clamp
+	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet clamp';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder10】 Corrugated sheet clamp';
+			strRt	:= '波板押え';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 波板押え';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet clamp
+	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet clamp';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder10】 Corrugated sheet clamp';
+			strRt	:= '波板押え';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 波板押え';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';</v>
       </c>
       <c r="AG72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet clamp
+	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet clamp';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder10】 Corrugated sheet clamp';
+			strRt	:= '波板押え';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 波板押え';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14642,12 +14636,12 @@
       <c r="AH72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet clamp
+	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet clamp';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder10】 Corrugated sheet clamp';
+			strRt	:= '波板押え';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 波板押え';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14656,12 +14650,12 @@
       <c r="AI72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet clamp
+	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet clamp';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder10】 Corrugated sheet clamp';
+			strRt	:= '波板押え';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 波板押え';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14673,12 +14667,12 @@
       <c r="AJ72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet clamp
+	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet clamp';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder10】 Corrugated sheet clamp';
+			strRt	:= '波板押え';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 波板押え';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14690,12 +14684,12 @@
       <c r="AK72" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet clamp
+	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet clamp';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder10】 Corrugated sheet clamp';
+			strRt	:= '波板押え';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 波板押え';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14722,15 +14716,15 @@
       </c>
       <c r="I73" t="str">
         <f ca="1"/>
-        <v>Flat sheet cutter blade push-out</v>
+        <v>平板カット刃押出し</v>
       </c>
       <c r="J73" t="str">
         <f ca="1"/>
-        <v>Flat sheet cutter blade push-out</v>
+        <v>平板カット刃押出し</v>
       </c>
       <c r="L73" t="str">
         <f ca="1"/>
-        <v>【cylinder11】 Flat sheet cutter blade push-out</v>
+        <v>【cylinder11】 平板カット刃押出し</v>
       </c>
       <c r="M73" t="str">
         <v>CD55B32-105-M9BZ</v>
@@ -14759,75 +14753,75 @@
       <c r="Z73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade push-out
+	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN</v>
       </c>
       <c r="AA73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade push-out
+	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade push-out
+	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade push-out';</v>
+			strRt	:= '平板カット刃押出し';</v>
       </c>
       <c r="AC73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade push-out
+	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade push-out';
+			strRt	:= '平板カット刃押出し';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade push-out
+	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade push-out';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder11】 Flat sheet cutter blade push-out';</v>
+			strRt	:= '平板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 平板カット刃押出し';</v>
       </c>
       <c r="AE73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade push-out
+	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade push-out';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder11】 Flat sheet cutter blade push-out';
+			strRt	:= '平板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 平板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade push-out
+	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade push-out';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder11】 Flat sheet cutter blade push-out';
+			strRt	:= '平板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 平板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';</v>
       </c>
       <c r="AG73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade push-out
+	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade push-out';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder11】 Flat sheet cutter blade push-out';
+			strRt	:= '平板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 平板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14835,12 +14829,12 @@
       <c r="AH73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade push-out
+	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade push-out';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder11】 Flat sheet cutter blade push-out';
+			strRt	:= '平板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 平板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14849,12 +14843,12 @@
       <c r="AI73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade push-out
+	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade push-out';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder11】 Flat sheet cutter blade push-out';
+			strRt	:= '平板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 平板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14866,12 +14860,12 @@
       <c r="AJ73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade push-out
+	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade push-out';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder11】 Flat sheet cutter blade push-out';
+			strRt	:= '平板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 平板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14883,12 +14877,12 @@
       <c r="AK73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade push-out
+	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade push-out';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder11】 Flat sheet cutter blade push-out';
+			strRt	:= '平板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 平板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14915,15 +14909,15 @@
       </c>
       <c r="I74" t="str">
         <f ca="1"/>
-        <v>Flat sheet cutter blade open/close</v>
+        <v>平板カット刃開閉</v>
       </c>
       <c r="J74" t="str">
         <f ca="1"/>
-        <v>Flat sheet cutter blade open/close</v>
+        <v>平板カット刃開閉</v>
       </c>
       <c r="L74" t="str">
         <f ca="1"/>
-        <v>【cylinder12】 Flat sheet cutter blade open/close</v>
+        <v>【cylinder12】 平板カット刃開閉</v>
       </c>
       <c r="M74" t="str">
         <v>CDQ2B25-10DMZ-L-A93M</v>
@@ -14952,75 +14946,75 @@
       <c r="Z74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade open/close
+	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN</v>
       </c>
       <c r="AA74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade open/close
+	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade open/close
+	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade open/close';</v>
+			strRt	:= '平板カット刃開閉';</v>
       </c>
       <c r="AC74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade open/close
+	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade open/close';
+			strRt	:= '平板カット刃開閉';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade open/close
+	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder12】 Flat sheet cutter blade open/close';</v>
+			strRt	:= '平板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 平板カット刃開閉';</v>
       </c>
       <c r="AE74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade open/close
+	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder12】 Flat sheet cutter blade open/close';
+			strRt	:= '平板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 平板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade open/close
+	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder12】 Flat sheet cutter blade open/close';
+			strRt	:= '平板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 平板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-10DMZ-L-A93M';</v>
       </c>
       <c r="AG74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade open/close
+	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder12】 Flat sheet cutter blade open/close';
+			strRt	:= '平板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 平板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-10DMZ-L-A93M';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -15028,12 +15022,12 @@
       <c r="AH74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade open/close
+	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder12】 Flat sheet cutter blade open/close';
+			strRt	:= '平板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 平板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-10DMZ-L-A93M';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15042,12 +15036,12 @@
       <c r="AI74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade open/close
+	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder12】 Flat sheet cutter blade open/close';
+			strRt	:= '平板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 平板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-10DMZ-L-A93M';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15059,12 +15053,12 @@
       <c r="AJ74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade open/close
+	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder12】 Flat sheet cutter blade open/close';
+			strRt	:= '平板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 平板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-10DMZ-L-A93M';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15076,12 +15070,12 @@
       <c r="AK74" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Flat sheet cutter blade open/close
+	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder12】 Flat sheet cutter blade open/close';
+			strRt	:= '平板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 平板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-10DMZ-L-A93M';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15108,15 +15102,15 @@
       </c>
       <c r="I75" t="str">
         <f ca="1"/>
-        <v>Corrugated sheet cutter blade push-out</v>
+        <v>波板カット刃押出し</v>
       </c>
       <c r="J75" t="str">
         <f ca="1"/>
-        <v>Corrugated sheet cutter blade push-out</v>
+        <v>波板カット刃押出し</v>
       </c>
       <c r="L75" t="str">
         <f ca="1"/>
-        <v>【cylinder13】 Corrugated sheet cutter blade push-out</v>
+        <v>【cylinder13】 波板カット刃押出し</v>
       </c>
       <c r="M75" t="str">
         <v>CD55B32-105-M9BZ</v>
@@ -15145,75 +15139,75 @@
       <c r="Z75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade push-out
+	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN</v>
       </c>
       <c r="AA75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade push-out
+	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade push-out
+	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade push-out';</v>
+			strRt	:= '波板カット刃押出し';</v>
       </c>
       <c r="AC75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade push-out
+	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade push-out';
+			strRt	:= '波板カット刃押出し';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade push-out
+	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade push-out';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder13】 Corrugated sheet cutter blade push-out';</v>
+			strRt	:= '波板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 波板カット刃押出し';</v>
       </c>
       <c r="AE75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade push-out
+	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade push-out';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder13】 Corrugated sheet cutter blade push-out';
+			strRt	:= '波板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 波板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade push-out
+	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade push-out';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder13】 Corrugated sheet cutter blade push-out';
+			strRt	:= '波板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 波板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';</v>
       </c>
       <c r="AG75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade push-out
+	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade push-out';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder13】 Corrugated sheet cutter blade push-out';
+			strRt	:= '波板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 波板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -15221,12 +15215,12 @@
       <c r="AH75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade push-out
+	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade push-out';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder13】 Corrugated sheet cutter blade push-out';
+			strRt	:= '波板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 波板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15235,12 +15229,12 @@
       <c r="AI75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade push-out
+	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade push-out';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder13】 Corrugated sheet cutter blade push-out';
+			strRt	:= '波板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 波板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15252,12 +15246,12 @@
       <c r="AJ75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade push-out
+	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade push-out';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder13】 Corrugated sheet cutter blade push-out';
+			strRt	:= '波板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 波板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15269,12 +15263,12 @@
       <c r="AK75" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade push-out
+	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade push-out';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder13】 Corrugated sheet cutter blade push-out';
+			strRt	:= '波板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 波板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15301,15 +15295,15 @@
       </c>
       <c r="I76" t="str">
         <f ca="1"/>
-        <v>Corrugated sheet cutter blade open/close</v>
+        <v>波板カット刃開閉</v>
       </c>
       <c r="J76" t="str">
         <f ca="1"/>
-        <v>Corrugated sheet cutter blade open/close</v>
+        <v>波板カット刃開閉</v>
       </c>
       <c r="L76" t="str">
         <f ca="1"/>
-        <v>【cylinder14】 Corrugated sheet cutter blade open/close</v>
+        <v>【cylinder14】 波板カット刃開閉</v>
       </c>
       <c r="M76" t="str">
         <v>CDQ2B40M-15DMZ-M9BZ</v>
@@ -15338,75 +15332,75 @@
       <c r="Z76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade open/close
+	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN</v>
       </c>
       <c r="AA76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade open/close
+	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade open/close
+	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade open/close';</v>
+			strRt	:= '波板カット刃開閉';</v>
       </c>
       <c r="AC76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade open/close
+	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade open/close';
+			strRt	:= '波板カット刃開閉';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade open/close
+	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder14】 Corrugated sheet cutter blade open/close';</v>
+			strRt	:= '波板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 波板カット刃開閉';</v>
       </c>
       <c r="AE76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade open/close
+	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder14】 Corrugated sheet cutter blade open/close';
+			strRt	:= '波板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 波板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade open/close
+	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder14】 Corrugated sheet cutter blade open/close';
+			strRt	:= '波板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 波板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';</v>
       </c>
       <c r="AG76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade open/close
+	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder14】 Corrugated sheet cutter blade open/close';
+			strRt	:= '波板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 波板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -15414,12 +15408,12 @@
       <c r="AH76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade open/close
+	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder14】 Corrugated sheet cutter blade open/close';
+			strRt	:= '波板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 波板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15428,12 +15422,12 @@
       <c r="AI76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade open/close
+	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder14】 Corrugated sheet cutter blade open/close';
+			strRt	:= '波板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 波板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15445,12 +15439,12 @@
       <c r="AJ76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade open/close
+	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder14】 Corrugated sheet cutter blade open/close';
+			strRt	:= '波板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 波板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15462,12 +15456,12 @@
       <c r="AK76" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter blade open/close
+	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder14】 Corrugated sheet cutter blade open/close';
+			strRt	:= '波板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 波板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15494,15 +15488,15 @@
       </c>
       <c r="I77" t="str">
         <f ca="1"/>
-        <v>Corrugated sheet cutter auxiliary</v>
+        <v>波板カット補助</v>
       </c>
       <c r="J77" t="str">
         <f ca="1"/>
-        <v>Corrugated sheet cutter auxiliary</v>
+        <v>波板カット補助</v>
       </c>
       <c r="L77" t="str">
         <f ca="1"/>
-        <v>【cylinder15】 Corrugated sheet cutter auxiliary</v>
+        <v>【cylinder15】 波板カット補助</v>
       </c>
       <c r="M77" t="str">
         <v>CXSJM10P-10-M9BL</v>
@@ -15531,75 +15525,75 @@
       <c r="Z77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary
+	//波板カット補助
 	ELSIF uiInfoIdx = 15 THEN</v>
       </c>
       <c r="AA77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary
+	//波板カット補助
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary
+	//波板カット補助
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary';</v>
+			strRt	:= '波板カット補助';</v>
       </c>
       <c r="AC77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary
+	//波板カット補助
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary';
+			strRt	:= '波板カット補助';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary
+	//波板カット補助
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder15】 Corrugated sheet cutter auxiliary';</v>
+			strRt	:= '波板カット補助';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 波板カット補助';</v>
       </c>
       <c r="AE77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary
+	//波板カット補助
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder15】 Corrugated sheet cutter auxiliary';
+			strRt	:= '波板カット補助';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 波板カット補助';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary
+	//波板カット補助
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder15】 Corrugated sheet cutter auxiliary';
+			strRt	:= '波板カット補助';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 波板カット補助';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';</v>
       </c>
       <c r="AG77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary
+	//波板カット補助
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder15】 Corrugated sheet cutter auxiliary';
+			strRt	:= '波板カット補助';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 波板カット補助';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -15607,12 +15601,12 @@
       <c r="AH77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary
+	//波板カット補助
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder15】 Corrugated sheet cutter auxiliary';
+			strRt	:= '波板カット補助';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 波板カット補助';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15621,12 +15615,12 @@
       <c r="AI77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary
+	//波板カット補助
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder15】 Corrugated sheet cutter auxiliary';
+			strRt	:= '波板カット補助';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 波板カット補助';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15638,12 +15632,12 @@
       <c r="AJ77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary
+	//波板カット補助
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder15】 Corrugated sheet cutter auxiliary';
+			strRt	:= '波板カット補助';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 波板カット補助';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15655,12 +15649,12 @@
       <c r="AK77" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary
+	//波板カット補助
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder15】 Corrugated sheet cutter auxiliary';
+			strRt	:= '波板カット補助';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 波板カット補助';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15687,15 +15681,15 @@
       </c>
       <c r="I78" t="str">
         <f ca="1"/>
-        <v>Corrugated sheet cutter auxiliary L</v>
+        <v>波板カット補助L</v>
       </c>
       <c r="J78" t="str">
         <f ca="1"/>
-        <v>Corrugated sheet cutter auxiliary L</v>
+        <v>波板カット補助L</v>
       </c>
       <c r="L78" t="str">
         <f ca="1"/>
-        <v>【cylinder16】 Corrugated sheet cutter auxiliary L</v>
+        <v>【cylinder16】 波板カット補助L</v>
       </c>
       <c r="M78" t="str">
         <v>CXSJM10P-10-M9BL</v>
@@ -15724,75 +15718,75 @@
       <c r="Z78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary L
+	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN</v>
       </c>
       <c r="AA78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary L
+	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary L
+	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary L';</v>
+			strRt	:= '波板カット補助L';</v>
       </c>
       <c r="AC78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary L
+	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary L';
+			strRt	:= '波板カット補助L';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary L
+	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary L';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder16】 Corrugated sheet cutter auxiliary L';</v>
+			strRt	:= '波板カット補助L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 波板カット補助L';</v>
       </c>
       <c r="AE78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary L
+	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary L';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder16】 Corrugated sheet cutter auxiliary L';
+			strRt	:= '波板カット補助L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 波板カット補助L';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary L
+	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary L';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder16】 Corrugated sheet cutter auxiliary L';
+			strRt	:= '波板カット補助L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 波板カット補助L';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';</v>
       </c>
       <c r="AG78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary L
+	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary L';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder16】 Corrugated sheet cutter auxiliary L';
+			strRt	:= '波板カット補助L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 波板カット補助L';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -15800,12 +15794,12 @@
       <c r="AH78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary L
+	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary L';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder16】 Corrugated sheet cutter auxiliary L';
+			strRt	:= '波板カット補助L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 波板カット補助L';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15814,12 +15808,12 @@
       <c r="AI78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary L
+	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary L';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder16】 Corrugated sheet cutter auxiliary L';
+			strRt	:= '波板カット補助L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 波板カット補助L';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15831,12 +15825,12 @@
       <c r="AJ78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary L
+	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary L';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder16】 Corrugated sheet cutter auxiliary L';
+			strRt	:= '波板カット補助L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 波板カット補助L';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15848,12 +15842,12 @@
       <c r="AK78" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Corrugated sheet cutter auxiliary L
+	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary L';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder16】 Corrugated sheet cutter auxiliary L';
+			strRt	:= '波板カット補助L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 波板カット補助L';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15880,15 +15874,15 @@
       </c>
       <c r="I79" t="str">
         <f ca="1"/>
-        <v>X-roll gluing ①</v>
+        <v>Xロール糊付け①</v>
       </c>
       <c r="J79" t="str">
         <f ca="1"/>
-        <v>X-roll gluing ①</v>
+        <v>Xロール糊付け①</v>
       </c>
       <c r="L79" t="str">
         <f ca="1"/>
-        <v>【cylinder17】 X-roll gluing ①</v>
+        <v>【cylinder17】 Xロール糊付け①</v>
       </c>
       <c r="M79" t="str">
         <v>CDM2RA20-25Z-M9BWV</v>
@@ -15917,75 +15911,75 @@
       <c r="Z79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ①
+	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN</v>
       </c>
       <c r="AA79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ①
+	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ①
+	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ①';</v>
+			strRt	:= 'Xロール糊付け①';</v>
       </c>
       <c r="AC79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ①
+	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ①';
+			strRt	:= 'Xロール糊付け①';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ①
+	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder17】 X-roll gluing ①';</v>
+			strRt	:= 'Xロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 Xロール糊付け①';</v>
       </c>
       <c r="AE79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ①
+	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder17】 X-roll gluing ①';
+			strRt	:= 'Xロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 Xロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ①
+	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder17】 X-roll gluing ①';
+			strRt	:= 'Xロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 Xロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';</v>
       </c>
       <c r="AG79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ①
+	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder17】 X-roll gluing ①';
+			strRt	:= 'Xロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 Xロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -15993,12 +15987,12 @@
       <c r="AH79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ①
+	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder17】 X-roll gluing ①';
+			strRt	:= 'Xロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 Xロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16007,12 +16001,12 @@
       <c r="AI79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ①
+	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder17】 X-roll gluing ①';
+			strRt	:= 'Xロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 Xロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16024,12 +16018,12 @@
       <c r="AJ79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ①
+	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder17】 X-roll gluing ①';
+			strRt	:= 'Xロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 Xロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16041,12 +16035,12 @@
       <c r="AK79" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ①
+	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder17】 X-roll gluing ①';
+			strRt	:= 'Xロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 Xロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16073,15 +16067,15 @@
       </c>
       <c r="I80" t="str">
         <f ca="1"/>
-        <v>X-roll gluing ②</v>
+        <v>Xロール糊付け②</v>
       </c>
       <c r="J80" t="str">
         <f ca="1"/>
-        <v>X-roll gluing ②</v>
+        <v>Xロール糊付け②</v>
       </c>
       <c r="L80" t="str">
         <f ca="1"/>
-        <v>【cylinder18】 X-roll gluing ②</v>
+        <v>【cylinder18】 Xロール糊付け②</v>
       </c>
       <c r="M80" t="str">
         <v>CDM2RA20-25Z-M9BWV</v>
@@ -16110,75 +16104,75 @@
       <c r="Z80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ②
+	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN</v>
       </c>
       <c r="AA80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ②
+	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ②
+	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ②';</v>
+			strRt	:= 'Xロール糊付け②';</v>
       </c>
       <c r="AC80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ②
+	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ②';
+			strRt	:= 'Xロール糊付け②';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ②
+	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder18】 X-roll gluing ②';</v>
+			strRt	:= 'Xロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 Xロール糊付け②';</v>
       </c>
       <c r="AE80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ②
+	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder18】 X-roll gluing ②';
+			strRt	:= 'Xロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 Xロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ②
+	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder18】 X-roll gluing ②';
+			strRt	:= 'Xロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 Xロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';</v>
       </c>
       <c r="AG80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ②
+	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder18】 X-roll gluing ②';
+			strRt	:= 'Xロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 Xロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -16186,12 +16180,12 @@
       <c r="AH80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ②
+	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder18】 X-roll gluing ②';
+			strRt	:= 'Xロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 Xロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16200,12 +16194,12 @@
       <c r="AI80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ②
+	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder18】 X-roll gluing ②';
+			strRt	:= 'Xロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 Xロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16217,12 +16211,12 @@
       <c r="AJ80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ②
+	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder18】 X-roll gluing ②';
+			strRt	:= 'Xロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 Xロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16234,12 +16228,12 @@
       <c r="AK80" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll gluing ②
+	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder18】 X-roll gluing ②';
+			strRt	:= 'Xロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 Xロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16266,15 +16260,15 @@
       </c>
       <c r="I81" t="str">
         <f ca="1"/>
-        <v>X-roll flat plate pressing</v>
+        <v>Xロール平板押付</v>
       </c>
       <c r="J81" t="str">
         <f ca="1"/>
-        <v>X-roll flat plate pressing</v>
+        <v>Xロール平板押付</v>
       </c>
       <c r="L81" t="str">
         <f ca="1"/>
-        <v>【cylinder19】 X-roll flat plate pressing</v>
+        <v>【cylinder19】 Xロール平板押付</v>
       </c>
       <c r="M81" t="str">
         <v>不明</v>
@@ -16303,75 +16297,75 @@
       <c r="Z81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll flat plate pressing
+	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN</v>
       </c>
       <c r="AA81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll flat plate pressing
+	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll flat plate pressing
+	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll flat plate pressing';</v>
+			strRt	:= 'Xロール平板押付';</v>
       </c>
       <c r="AC81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll flat plate pressing
+	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll flat plate pressing';
+			strRt	:= 'Xロール平板押付';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll flat plate pressing
+	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll flat plate pressing';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder19】 X-roll flat plate pressing';</v>
+			strRt	:= 'Xロール平板押付';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 Xロール平板押付';</v>
       </c>
       <c r="AE81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll flat plate pressing
+	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll flat plate pressing';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder19】 X-roll flat plate pressing';
+			strRt	:= 'Xロール平板押付';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 Xロール平板押付';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll flat plate pressing
+	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll flat plate pressing';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder19】 X-roll flat plate pressing';
+			strRt	:= 'Xロール平板押付';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 Xロール平板押付';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '不明';</v>
       </c>
       <c r="AG81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll flat plate pressing
+	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll flat plate pressing';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder19】 X-roll flat plate pressing';
+			strRt	:= 'Xロール平板押付';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 Xロール平板押付';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '不明';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -16379,12 +16373,12 @@
       <c r="AH81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll flat plate pressing
+	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll flat plate pressing';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder19】 X-roll flat plate pressing';
+			strRt	:= 'Xロール平板押付';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 Xロール平板押付';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '不明';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16393,12 +16387,12 @@
       <c r="AI81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll flat plate pressing
+	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll flat plate pressing';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder19】 X-roll flat plate pressing';
+			strRt	:= 'Xロール平板押付';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 Xロール平板押付';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '不明';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16410,12 +16404,12 @@
       <c r="AJ81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll flat plate pressing
+	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll flat plate pressing';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder19】 X-roll flat plate pressing';
+			strRt	:= 'Xロール平板押付';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 Xロール平板押付';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '不明';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16427,12 +16421,12 @@
       <c r="AK81" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-roll flat plate pressing
+	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll flat plate pressing';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder19】 X-roll flat plate pressing';
+			strRt	:= 'Xロール平板押付';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 Xロール平板押付';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '不明';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28309,15 +28303,15 @@
     <row r="205" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="AK205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AK$3:AK$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_sv3_error.xlsm]config によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
-	//Foil wax reel shaft
+	//箔ロウリール軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax reel shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis1】 Foil wax reel shaft';
+			strRt	:= '箔ロウリール軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis1】 箔ロウリール軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '5TK20GN-CW2J+5GN180K';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28325,12 +28319,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Flat sheet feed shaft
+	//平板送り軸
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet feed shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis2】 Flat sheet feed shaft';
+			strRt	:= '平板送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis2】 平板送り軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28338,12 +28332,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Foil wax feed shaft
+	//箔ロウ送り軸
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax feed shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis3】 Foil wax feed shaft';
+			strRt	:= '箔ロウ送り軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis3】 箔ロウ送り軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28351,12 +28345,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Corrugated sheet feed
+	//波板送り
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet feed';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis4】 Corrugated sheet feed';
+			strRt	:= '波板送り';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis4】 波板送り';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'AZM46AC-HP9+AZD-CEP+CC070VZR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28364,12 +28358,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Workpiece discharge up/down shaft
+	//ワーク排出上下軸
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge up/down shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis5】 Workpiece discharge up/down shaft';
+			strRt	:= 'ワーク排出上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis5】 ワーク排出上下軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA7R-WA-56P-16-400-P5-S-B-MR';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28377,12 +28371,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Circumference measuring probe up/down shaft
+	//周長測定子上下軸
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measuring probe up/down shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis6】 Circumference measuring probe up/down shaft';
+			strRt	:= '周長測定子上下軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis6】 周長測定子上下軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCA2-GS3NA-I-10-2-50-A6-M-K1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28390,12 +28384,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Workpiece (discharge) chuck shaft
+	//ワーク(排出)チャック軸
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece (discharge) chuck shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis7】 Workpiece (discharge) chuck shaft';
+			strRt	:= 'ワーク(排出)チャック軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis7】 ワーク(排出)チャック軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'RCP6-SA4R-WA-35P-16-150-P5-X07-MR-NM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28403,12 +28397,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Y-axis: Welding torch forward/backward
+	//Y軸：溶接トーチ前後
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Y-axis: Welding torch forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis8】 Y-axis: Welding torch forward/backward';
+			strRt	:= 'Y軸：溶接トーチ前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis8】 Y軸：溶接トーチ前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-8-②-T4-⑧-③';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28416,12 +28410,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Z-axis: Welding torch up/down
+	//Z軸：溶接トーチ上下
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Z-axis: Welding torch up/down';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis9】 Z-axis: Welding torch up/down';
+			strRt	:= 'Z軸：溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis9】 Z軸：溶接トーチ上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'ICSB2-YSA2M-WA-20AQ-20AQBNM-T4-5L-SC/ISB【ISPB】-SXM-WA-60-4-④-T4-⑧-⑤';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28429,12 +28423,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Binder supply pump motor
+	//バインダー供給ポンプモータ
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Binder supply pump motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis10】 Binder supply pump motor';
+			strRt	:= 'バインダー供給ポンプモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis10】 バインダー供給ポンプモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28442,12 +28436,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Corrugated sheet reel motor
+	//波板リールモータ
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet reel motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis11】 Corrugated sheet reel motor';
+			strRt	:= '波板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis11】 波板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28455,12 +28449,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Flat sheet reel motor
+	//平板リールモータ
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet reel motor';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis12】 Flat sheet reel motor';
+			strRt	:= '平板リールモータ';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis12】 平板リールモータ';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28468,12 +28462,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding main shaft
+	//巻取り主軸
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding main shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis13】 Winding main shaft';
+			strRt	:= '巻取り主軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis13】 巻取り主軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-B075AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28481,12 +28475,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Workpiece width adjustment shaft
+	//ワーク幅調整軸
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece width adjustment shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis14】 Workpiece width adjustment shaft';
+			strRt	:= 'ワーク幅調整軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis14】 ワーク幅調整軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'SV3-M040AK';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28494,12 +28488,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//T-roll rotation shaft
+	//Tロール回転軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll rotation shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 T-roll rotation shaft';
+			strRt	:= 'Tロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 Tロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28507,12 +28501,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Rotor unit X-roll rotation shaft
+	//ロータユニットXロール回転軸
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Rotor unit X-roll rotation shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis16】 Rotor unit X-roll rotation shaft';
+			strRt	:= 'ロータユニットXロール回転軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis16】 ロータユニットXロール回転軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'M540-402';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28525,12 +28519,12 @@
 	END_IF;
 //EC
 ELSIF strInfoType = 'EC' THEN
-	//Workpiece discharge front and rear axis
+	//ワーク排出前後軸
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Workpiece discharge front and rear axis';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【EC1】 Workpiece discharge front and rear axis';
+			strRt	:= 'ワーク排出前後軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【EC1】 ワーク排出前後軸';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'EC-S4HR-200-7-ML-TMD2';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28543,12 +28537,12 @@
 	END_IF;
 //cylinder
 ELSIF strInfoType = 'cylinder' THEN
-	//Winding shaft center forward/backward
+	//巻取り軸芯前後
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding shaft center forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder1】 Winding shaft center forward/backward';
+			strRt	:= '巻取り軸芯前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder1】 巻取り軸芯前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2A63-200DCZ-M9BVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28556,12 +28550,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//T-roll gluing ①
+	//Tロール糊付け①
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder2】 T-roll gluing ①';
+			strRt	:= 'Tロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder2】 Tロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28569,12 +28563,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//T-roll gluing ②
+	//Tロール糊付け②
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'T-roll gluing ②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder3】 T-roll gluing ②';
+			strRt	:= 'Tロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder3】 Tロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDAS16×10-B-R';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28582,12 +28576,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Flat sheet lower auxiliary plate release
+	//平板補助プレート
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet lower auxiliary plate release';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder4】 Flat sheet lower auxiliary plate release';
+			strRt	:= '平板補助プレート';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder4】 平板補助プレート';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDJ2D16-45Z-W-M9BWZ-B';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28595,12 +28589,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Flat sheet chuck (hand) forward/backward
+	//平板チャック(ハンド)前後
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck (hand) forward/backward';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder5】 Flat sheet chuck (hand) forward/backward';
+			strRt	:= '平板チャック(ハンド)前後';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder5】 平板チャック(ハンド)前後';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MXQ20-50A-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28608,12 +28602,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Flat sheet chuck open/close
+	//平板チャック開閉
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet chuck open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder6】 Flat sheet chuck open/close';
+			strRt	:= '平板チャック開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder6】 平板チャック開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'MHF2-16D1-M9BL-X83C1';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28621,12 +28615,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Flat sheet clamp up/down ①
+	//平板押え上下①
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet clamp up/down ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 Flat sheet clamp up/down ①';
+			strRt	:= '平板押え上下①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28634,12 +28628,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Foil wax clamp up/down
+	//箔ロウ押え上下
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax clamp up/down';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder8】 Foil wax clamp up/down';
+			strRt	:= '箔ロウ押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder8】 箔ロウ押え上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2D25-20DMZ-M9BM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28647,12 +28641,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Foil wax cut
+	//箔ロウカット
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax cut';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder9】 Foil wax cut';
+			strRt	:= '箔ロウカット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder9】 箔ロウカット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQSKB16-10DM-M9NWVZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28660,12 +28654,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Corrugated sheet clamp
+	//波板押え
 	ELSIF uiInfoIdx = 10 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet clamp';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder10】 Corrugated sheet clamp';
+			strRt	:= '波板押え';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder10】 波板押え';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28673,12 +28667,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Flat sheet cutter blade push-out
+	//平板カット刃押出し
 	ELSIF uiInfoIdx = 11 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade push-out';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder11】 Flat sheet cutter blade push-out';
+			strRt	:= '平板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder11】 平板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28686,12 +28680,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Flat sheet cutter blade open/close
+	//平板カット刃開閉
 	ELSIF uiInfoIdx = 12 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat sheet cutter blade open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder12】 Flat sheet cutter blade open/close';
+			strRt	:= '平板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder12】 平板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-10DMZ-L-A93M';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28699,12 +28693,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Corrugated sheet cutter blade push-out
+	//波板カット刃押出し
 	ELSIF uiInfoIdx = 13 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade push-out';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder13】 Corrugated sheet cutter blade push-out';
+			strRt	:= '波板カット刃押出し';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder13】 波板カット刃押出し';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CD55B32-105-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28712,12 +28706,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Corrugated sheet cutter blade open/close
+	//波板カット刃開閉
 	ELSIF uiInfoIdx = 14 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter blade open/close';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder14】 Corrugated sheet cutter blade open/close';
+			strRt	:= '波板カット刃開閉';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder14】 波板カット刃開閉';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B40M-15DMZ-M9BZ';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28725,12 +28719,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Corrugated sheet cutter auxiliary
+	//波板カット補助
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder15】 Corrugated sheet cutter auxiliary';
+			strRt	:= '波板カット補助';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder15】 波板カット補助';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28738,12 +28732,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Corrugated sheet cutter auxiliary L
+	//波板カット補助L
 	ELSIF uiInfoIdx = 16 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated sheet cutter auxiliary L';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder16】 Corrugated sheet cutter auxiliary L';
+			strRt	:= '波板カット補助L';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder16】 波板カット補助L';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CXSJM10P-10-M9BL';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28751,12 +28745,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//X-roll gluing ①
+	//Xロール糊付け①
 	ELSIF uiInfoIdx = 17 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder17】 X-roll gluing ①';
+			strRt	:= 'Xロール糊付け①';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder17】 Xロール糊付け①';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28764,12 +28758,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//X-roll gluing ②
+	//Xロール糊付け②
 	ELSIF uiInfoIdx = 18 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll gluing ②';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder18】 X-roll gluing ②';
+			strRt	:= 'Xロール糊付け②';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder18】 Xロール糊付け②';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDM2RA20-25Z-M9BWV';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28777,12 +28771,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//X-roll flat plate pressing
+	//Xロール平板押付
 	ELSIF uiInfoIdx = 19 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll flat plate pressing';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder19】 X-roll flat plate pressing';
+			strRt	:= 'Xロール平板押付';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder19】 Xロール平板押付';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= '不明';
 		ELSIF strInfoKey = 'mf' THEN

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E11EA6-2B13-4D68-B8E9-DAB85ACF4239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C12ABC1-AED6-4BC7-8E02-480734D4EEC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
   <sheets>
     <sheet name="info_index" sheetId="1" r:id="rId1"/>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ref="E5:E68" si="0">E4</f>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AK$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸
@@ -28303,7 +28303,7 @@
     <row r="205" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="AK205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AK$3:AK$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C12ABC1-AED6-4BC7-8E02-480734D4EEC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B076AF1-3E30-476E-A97C-60913BD27EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -811,9 +811,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ワーク排出上下軸</t>
-  </si>
-  <si>
     <t>周長測定子上下軸</t>
     <rPh sb="0" eb="2">
       <t>シュウチョウ</t>
@@ -1402,6 +1399,10 @@
   </si>
   <si>
     <t>Flat auxiliary plate</t>
+  </si>
+  <si>
+    <t>ワーク排出上下軸</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -2241,7 +2242,7 @@
         <v>105</v>
       </c>
       <c r="G1" s="22" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H1" s="22" t="s">
         <v>10</v>
@@ -2253,7 +2254,7 @@
         <v>3</v>
       </c>
       <c r="K1" s="22" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L1" s="22" t="s">
         <v>5</v>
@@ -2262,10 +2263,10 @@
         <v>112</v>
       </c>
       <c r="N1" s="23" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O1" s="23" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P1" s="23"/>
     </row>
@@ -2286,10 +2287,10 @@
         <v>91</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H2" s="31" t="s">
         <v>20</v>
@@ -2298,10 +2299,10 @@
         <v>21</v>
       </c>
       <c r="J2" s="31" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L2" s="31">
         <v>1</v>
@@ -2331,7 +2332,7 @@
         <v>125</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>14</v>
@@ -2340,10 +2341,10 @@
         <v>13</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L3" s="12">
         <v>1</v>
@@ -2373,7 +2374,7 @@
         <v>124</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>14</v>
@@ -2382,10 +2383,10 @@
         <v>13</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L4" s="12">
         <v>1</v>
@@ -2415,7 +2416,7 @@
         <v>89</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>14</v>
@@ -2424,10 +2425,10 @@
         <v>13</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L5" s="12">
         <v>1</v>
@@ -2454,10 +2455,10 @@
         <v>94</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>131</v>
+        <v>256</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>1</v>
@@ -2469,7 +2470,7 @@
         <v>2</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L6" s="8">
         <v>1</v>
@@ -2496,10 +2497,10 @@
         <v>94</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>0</v>
@@ -2511,7 +2512,7 @@
         <v>2</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L7" s="8">
         <v>1</v>
@@ -2541,7 +2542,7 @@
         <v>130</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>28</v>
@@ -2553,7 +2554,7 @@
         <v>2</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L8" s="8">
         <v>1</v>
@@ -2580,10 +2581,10 @@
         <v>101</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>106</v>
@@ -2595,7 +2596,7 @@
         <v>2</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L9" s="8">
         <v>1</v>
@@ -2622,10 +2623,10 @@
         <v>101</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>107</v>
@@ -2637,7 +2638,7 @@
         <v>2</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L10" s="8">
         <v>1</v>
@@ -2660,10 +2661,10 @@
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
@@ -2688,10 +2689,10 @@
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
@@ -2716,10 +2717,10 @@
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
@@ -2751,7 +2752,7 @@
         <v>126</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>31</v>
@@ -2760,10 +2761,10 @@
         <v>32</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L14" s="8">
         <v>1</v>
@@ -2793,7 +2794,7 @@
         <v>127</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>33</v>
@@ -2802,10 +2803,10 @@
         <v>32</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L15" s="8">
         <v>1</v>
@@ -2831,10 +2832,10 @@
         <v>128</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I16" s="8"/>
       <c r="J16" s="8"/>
@@ -2858,13 +2859,13 @@
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
       <c r="F17" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="H17" s="8" t="s">
         <v>139</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>140</v>
       </c>
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
@@ -2892,10 +2893,10 @@
         <v>99</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>61</v>
@@ -2907,7 +2908,7 @@
         <v>4</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L18" s="8">
         <v>1</v>
@@ -2934,13 +2935,13 @@
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
@@ -2968,13 +2969,13 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I20" s="8"/>
       <c r="J20" s="8"/>
@@ -3003,13 +3004,13 @@
         <v>2</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F21" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="G21" s="8" t="s">
         <v>255</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>256</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>63</v>
@@ -3021,7 +3022,7 @@
         <v>4</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L21" s="8">
         <v>1</v>
@@ -3052,10 +3053,10 @@
         <v>93</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H22" s="8" t="s">
         <v>67</v>
@@ -3067,7 +3068,7 @@
         <v>4</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L22" s="8">
         <v>1</v>
@@ -3098,10 +3099,10 @@
         <v>93</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H23" s="8" t="s">
         <v>65</v>
@@ -3113,7 +3114,7 @@
         <v>4</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L23" s="8">
         <v>1</v>
@@ -3144,10 +3145,10 @@
         <v>98</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H24" s="8" t="s">
         <v>69</v>
@@ -3159,7 +3160,7 @@
         <v>4</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L24" s="11">
         <v>1</v>
@@ -3190,10 +3191,10 @@
         <v>92</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H25" s="8" t="s">
         <v>73</v>
@@ -3205,7 +3206,7 @@
         <v>4</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L25" s="11">
         <v>1</v>
@@ -3239,7 +3240,7 @@
         <v>121</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H26" s="8" t="s">
         <v>71</v>
@@ -3251,7 +3252,7 @@
         <v>4</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L26" s="11">
         <v>1</v>
@@ -3282,10 +3283,10 @@
         <v>100</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>69</v>
@@ -3297,7 +3298,7 @@
         <v>4</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L27" s="11">
         <v>1</v>
@@ -3328,10 +3329,10 @@
         <v>95</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H28" s="12" t="s">
         <v>75</v>
@@ -3343,7 +3344,7 @@
         <v>4</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L28" s="13">
         <v>1</v>
@@ -3374,10 +3375,10 @@
         <v>95</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>74</v>
@@ -3389,7 +3390,7 @@
         <v>4</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L29" s="11">
         <v>1</v>
@@ -3420,10 +3421,10 @@
         <v>97</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>75</v>
@@ -3435,7 +3436,7 @@
         <v>4</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L30" s="13">
         <v>1</v>
@@ -3466,10 +3467,10 @@
         <v>97</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>76</v>
@@ -3481,7 +3482,7 @@
         <v>4</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L31" s="11">
         <v>1</v>
@@ -3512,10 +3513,10 @@
         <v>96</v>
       </c>
       <c r="F32" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="G32" s="12" t="s">
         <v>252</v>
-      </c>
-      <c r="G32" s="12" t="s">
-        <v>253</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>77</v>
@@ -3527,7 +3528,7 @@
         <v>4</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L32" s="13">
         <v>1</v>
@@ -3558,10 +3559,10 @@
         <v>96</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>77</v>
@@ -3573,7 +3574,7 @@
         <v>4</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L33" s="13">
         <v>1</v>
@@ -3600,10 +3601,10 @@
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
       <c r="F34" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>51</v>
@@ -3634,10 +3635,10 @@
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
       <c r="F35" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>51</v>
@@ -3668,13 +3669,13 @@
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
       <c r="F36" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
@@ -3715,7 +3716,7 @@
         <v>4</v>
       </c>
       <c r="K37" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L37" s="15">
         <v>1</v>
@@ -3753,7 +3754,7 @@
         <v>4</v>
       </c>
       <c r="K38" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L38" s="15">
         <v>1</v>
@@ -3791,7 +3792,7 @@
         <v>4</v>
       </c>
       <c r="K39" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L39" s="15">
         <v>1</v>
@@ -3823,7 +3824,7 @@
         <v>129</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>30</v>
@@ -3835,7 +3836,7 @@
         <v>2</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L40" s="8">
         <v>1</v>
@@ -3870,10 +3871,10 @@
         <v>8</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L41" s="8">
         <v>1</v>
@@ -3908,10 +3909,10 @@
         <v>9</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L42" s="8">
         <v>1</v>
@@ -3944,10 +3945,10 @@
         <v>23</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L43" s="8">
         <v>3</v>
@@ -3982,10 +3983,10 @@
         <v>24</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L44" s="8">
         <v>1</v>
@@ -4022,10 +4023,10 @@
         <v>36</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L45" s="8">
         <v>1</v>
@@ -4058,10 +4059,10 @@
         <v>59</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L46" s="8">
         <v>1</v>
@@ -4092,10 +4093,10 @@
         <v>19</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L47" s="8">
         <v>1</v>
@@ -4126,10 +4127,10 @@
         <v>17</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L48" s="8">
         <v>1</v>
@@ -4160,10 +4161,10 @@
         <v>26</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L49" s="8">
         <v>1</v>
@@ -4196,10 +4197,10 @@
         <v>26</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L50" s="8">
         <v>1</v>
@@ -4247,7 +4248,7 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B55" t="s">
         <v>117</v>
@@ -4509,19 +4510,19 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="F1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J1" t="s">
+        <v>233</v>
+      </c>
+      <c r="L1" t="s">
         <v>234</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>235</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>236</v>
-      </c>
-      <c r="P1" t="s">
-        <v>237</v>
       </c>
       <c r="AA1" t="str">
         <f>IF(LEN(J1),J2&amp;CHAR(9)&amp;":"&amp;J1,"")</f>
@@ -4555,78 +4556,78 @@
     </row>
     <row r="2" spans="1:37" s="33" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F2" s="33" t="s">
         <v>102</v>
       </c>
       <c r="G2" s="33" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H2" s="33" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J2" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="L2" s="33" t="s">
         <v>195</v>
       </c>
-      <c r="L2" s="33" t="s">
-        <v>196</v>
-      </c>
       <c r="N2" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="P2" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="X2" s="33" t="s">
         <v>206</v>
       </c>
-      <c r="P2" s="33" t="s">
-        <v>225</v>
-      </c>
-      <c r="X2" s="33" t="s">
-        <v>207</v>
-      </c>
       <c r="Y2" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="Z2" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="Z2" s="33" t="s">
+      <c r="AA2" s="33" t="s">
         <v>199</v>
       </c>
-      <c r="AA2" s="33" t="s">
+      <c r="AB2" s="33" t="s">
         <v>200</v>
       </c>
-      <c r="AB2" s="33" t="s">
+      <c r="AC2" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="AC2" s="33" t="s">
-        <v>202</v>
-      </c>
       <c r="AD2" s="33" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AE2" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="AF2" s="33" t="s">
         <v>209</v>
       </c>
-      <c r="AF2" s="33" t="s">
-        <v>210</v>
-      </c>
       <c r="AG2" s="33" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AH2" s="33" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AI2" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="AJ2" s="33" t="s">
         <v>221</v>
       </c>
-      <c r="AJ2" s="33" t="s">
-        <v>222</v>
-      </c>
       <c r="AK2" s="33" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
@@ -5030,7 +5031,7 @@
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
@@ -5230,10 +5231,10 @@
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" t="s">
         <v>188</v>
-      </c>
-      <c r="B6" t="s">
-        <v>189</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
@@ -5429,10 +5430,10 @@
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
+        <v>180</v>
+      </c>
+      <c r="B7" t="s">
         <v>181</v>
-      </c>
-      <c r="B7" t="s">
-        <v>182</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -5628,10 +5629,10 @@
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B8" t="s">
         <v>183</v>
-      </c>
-      <c r="B8" t="s">
-        <v>184</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -5827,10 +5828,10 @@
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B9" t="s">
         <v>185</v>
-      </c>
-      <c r="B9" t="s">
-        <v>186</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -6605,7 +6606,7 @@
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B13" t="str">
         <f ca="1">$AK$205</f>
@@ -7292,7 +7293,7 @@
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B14" t="str">
         <f>IF(LEN(AI1),"●"&amp;B27&amp;CHAR(10)&amp;AI1,"")</f>
@@ -8660,7 +8661,7 @@
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -8862,10 +8863,10 @@
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B25" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E25" t="str">
         <f t="shared" si="0"/>
@@ -8966,10 +8967,10 @@
     </row>
     <row r="26" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B26" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E26" t="str">
         <f t="shared" si="0"/>
@@ -9070,10 +9071,10 @@
     </row>
     <row r="27" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B27" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E27" t="str">
         <f t="shared" si="0"/>
@@ -9174,10 +9175,10 @@
     </row>
     <row r="28" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B28" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E28" t="str">
         <f t="shared" si="0"/>
@@ -9278,10 +9279,10 @@
     </row>
     <row r="29" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B29" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E29" t="str">
         <f t="shared" si="0"/>

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B076AF1-3E30-476E-A97C-60913BD27EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C422E4D7-DDA9-4B19-88AA-E2DE1AB47390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="271">
   <si>
     <t>RCA2-GS3NA-I-10-2-50-A6-M-K1</t>
   </si>
@@ -1404,6 +1404,50 @@
     <t>ワーク排出上下軸</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>平板供給部</t>
+  </si>
+  <si>
+    <t>波板供給部</t>
+  </si>
+  <si>
+    <t>箔ロウ供給部</t>
+  </si>
+  <si>
+    <t>巻取り軸部</t>
+  </si>
+  <si>
+    <t>溶接部</t>
+  </si>
+  <si>
+    <t>排出部</t>
+  </si>
+  <si>
+    <t>Flat Sheet Supply</t>
+  </si>
+  <si>
+    <t>Corrugated Sheet Supply</t>
+  </si>
+  <si>
+    <t>Foil Wax Supply</t>
+  </si>
+  <si>
+    <t>Winding Shaft</t>
+  </si>
+  <si>
+    <t>Welding</t>
+  </si>
+  <si>
+    <t>Discharge</t>
+  </si>
+  <si>
+    <t>unit</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>unit</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -1840,7 +1884,7 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$A$54">
+    <xdr:sp macro="" textlink="$A$62">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="正方形/長方形 1">
           <a:extLst>
@@ -1900,7 +1944,7 @@
               <a:ea typeface="游ゴシック"/>
             </a:rPr>
             <a:pPr algn="l"/>
-            <a:t>50</a:t>
+            <a:t>56</a:t>
           </a:fld>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="600"/>
         </a:p>
@@ -2209,7 +2253,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:P78"/>
+  <dimension ref="A1:P86"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -4211,265 +4255,469 @@
       <c r="P50" s="10"/>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="18"/>
-      <c r="B51" s="18"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="19"/>
-      <c r="I51" s="19"/>
-      <c r="J51" s="19"/>
-      <c r="K51" s="19"/>
-      <c r="L51" s="19"/>
-      <c r="M51" s="20"/>
-      <c r="N51" s="20"/>
-      <c r="O51" s="20"/>
-      <c r="P51" s="20"/>
+      <c r="A51" s="7">
+        <v>51</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C51" s="7">
+        <v>1</v>
+      </c>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="10"/>
+      <c r="P51" s="10"/>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="7">
+        <v>52</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C52" s="7">
+        <v>2</v>
+      </c>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="10"/>
+      <c r="P52" s="10"/>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" t="s">
-        <v>111</v>
-      </c>
-      <c r="D53" t="s">
-        <v>110</v>
-      </c>
+      <c r="A53" s="7">
+        <v>53</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C53" s="7">
+        <v>3</v>
+      </c>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="10"/>
+      <c r="P53" s="10"/>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54">
-        <f>MAX(A$2:A$51)</f>
-        <v>50</v>
-      </c>
-      <c r="D54">
-        <f>MAX(D$2:D$51)</f>
-        <v>11</v>
-      </c>
+      <c r="A54" s="7">
+        <v>54</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C54" s="7">
+        <v>4</v>
+      </c>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="H54" s="8"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="10"/>
+      <c r="P54" s="10"/>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" t="s">
-        <v>203</v>
-      </c>
-      <c r="B55" t="s">
-        <v>117</v>
-      </c>
-      <c r="C55" t="s">
-        <v>116</v>
-      </c>
+      <c r="A55" s="7">
+        <v>55</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C55" s="7">
+        <v>5</v>
+      </c>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="H55" s="8"/>
+      <c r="I55" s="8"/>
+      <c r="J55" s="8"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="8"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="10"/>
+      <c r="O55" s="10"/>
+      <c r="P55" s="10"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56">
-        <f>ROW(A52)-ROW(A1)-1</f>
-        <v>50</v>
-      </c>
-      <c r="B56">
-        <f>COUNTIF(B$2:B$51,B55)</f>
-        <v>16</v>
-      </c>
-      <c r="C56" s="28">
-        <f>_xlfn.MAXIFS(C$2:C$51,$B$2:$B$51,C55)</f>
-        <v>16</v>
-      </c>
+      <c r="A56" s="7">
+        <v>56</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C56" s="7">
+        <v>6</v>
+      </c>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="H56" s="8"/>
+      <c r="I56" s="8"/>
+      <c r="J56" s="8"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="8"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="10"/>
+      <c r="P56" s="10"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" t="s">
-        <v>114</v>
-      </c>
-      <c r="C57" t="s">
-        <v>114</v>
-      </c>
+      <c r="A57" s="7"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="8"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="8"/>
+      <c r="I57" s="8"/>
+      <c r="J57" s="8"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="8"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="10"/>
+      <c r="O57" s="10"/>
+      <c r="P57" s="10"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58">
-        <f>COUNTIF(B$2:B$51,B57)</f>
-        <v>22</v>
-      </c>
-      <c r="C58" s="28">
-        <f>_xlfn.MAXIFS(C$2:C$51,$B$2:$B$51,C57)</f>
-        <v>19</v>
-      </c>
+      <c r="A58" s="7"/>
+      <c r="B58" s="7"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8"/>
+      <c r="I58" s="8"/>
+      <c r="J58" s="8"/>
+      <c r="K58" s="8"/>
+      <c r="L58" s="8"/>
+      <c r="M58" s="10"/>
+      <c r="N58" s="10"/>
+      <c r="O58" s="10"/>
+      <c r="P58" s="10"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="18"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="19"/>
+      <c r="H59" s="19"/>
+      <c r="I59" s="19"/>
+      <c r="J59" s="19"/>
+      <c r="K59" s="19"/>
+      <c r="L59" s="19"/>
+      <c r="M59" s="20"/>
+      <c r="N59" s="20"/>
+      <c r="O59" s="20"/>
+      <c r="P59" s="20"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H61" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L61">
-        <v>1</v>
-      </c>
-      <c r="P61" t="s">
-        <v>79</v>
+      <c r="A61" t="s">
+        <v>111</v>
+      </c>
+      <c r="D61" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H62" t="s">
+      <c r="A62">
+        <f>MAX(A$2:A$59)</f>
         <v>56</v>
       </c>
-      <c r="I62" t="s">
-        <v>53</v>
-      </c>
-      <c r="J62" t="s">
-        <v>52</v>
-      </c>
-      <c r="L62">
-        <v>1</v>
-      </c>
-      <c r="P62" t="s">
-        <v>79</v>
+      <c r="D62">
+        <f>MAX(D$2:D$59)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" t="s">
+        <v>203</v>
+      </c>
+      <c r="B63" t="s">
+        <v>117</v>
+      </c>
+      <c r="C63" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H64" s="2" t="s">
+      <c r="A64">
+        <f>ROW(A60)-ROW(A1)-1</f>
+        <v>58</v>
+      </c>
+      <c r="B64">
+        <f>COUNTIF(B$2:B$59,B63)</f>
+        <v>16</v>
+      </c>
+      <c r="C64" s="28">
+        <f>_xlfn.MAXIFS(C$2:C$59,$B$2:$B$59,C63)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" t="s">
+        <v>114</v>
+      </c>
+      <c r="C65" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66">
+        <f>COUNTIF(B$2:B$59,B65)</f>
+        <v>22</v>
+      </c>
+      <c r="C66" s="28">
+        <f>_xlfn.MAXIFS(C$2:C$59,$B$2:$B$59,C65)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H69" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L69">
+        <v>1</v>
+      </c>
+      <c r="P69" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H70" t="s">
+        <v>56</v>
+      </c>
+      <c r="I70" t="s">
+        <v>53</v>
+      </c>
+      <c r="J70" t="s">
+        <v>52</v>
+      </c>
+      <c r="L70">
+        <v>1</v>
+      </c>
+      <c r="P70" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H72" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="65" spans="8:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H65" t="s">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H73" t="s">
         <v>82</v>
       </c>
-      <c r="I65" t="s">
+      <c r="I73" t="s">
         <v>84</v>
       </c>
-      <c r="J65" t="s">
+      <c r="J73" t="s">
         <v>80</v>
       </c>
-      <c r="L65">
+      <c r="L73">
         <v>1</v>
       </c>
-      <c r="P65" t="s">
+      <c r="P73" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="67" spans="8:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H67" s="2" t="s">
+    <row r="75" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H75" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="68" spans="8:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H68" t="s">
+    <row r="76" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H76" t="s">
         <v>83</v>
       </c>
-      <c r="I68" t="s">
+      <c r="I76" t="s">
         <v>84</v>
       </c>
-      <c r="J68" t="s">
+      <c r="J76" t="s">
         <v>81</v>
-      </c>
-      <c r="L68">
-        <v>1</v>
-      </c>
-      <c r="P68" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70" spans="8:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H70" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="71" spans="8:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H71" t="s">
-        <v>42</v>
-      </c>
-      <c r="I71" t="s">
-        <v>43</v>
-      </c>
-      <c r="J71" t="s">
-        <v>12</v>
-      </c>
-      <c r="L71">
-        <v>1</v>
-      </c>
-      <c r="P71" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="72" spans="8:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H72" t="s">
-        <v>45</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J72" t="s">
-        <v>44</v>
-      </c>
-      <c r="L72">
-        <v>2</v>
-      </c>
-      <c r="P72" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="74" spans="8:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H74" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="75" spans="8:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H75" t="s">
-        <v>46</v>
-      </c>
-      <c r="I75" t="s">
-        <v>47</v>
-      </c>
-      <c r="J75" t="s">
-        <v>12</v>
-      </c>
-      <c r="L75">
-        <v>1</v>
-      </c>
-      <c r="P75" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="76" spans="8:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H76" t="s">
-        <v>50</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J76" t="s">
-        <v>49</v>
       </c>
       <c r="L76">
         <v>1</v>
       </c>
       <c r="P76" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="78" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H78" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H79" t="s">
+        <v>42</v>
+      </c>
+      <c r="I79" t="s">
+        <v>43</v>
+      </c>
+      <c r="J79" t="s">
+        <v>12</v>
+      </c>
+      <c r="L79">
+        <v>1</v>
+      </c>
+      <c r="P79" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="77" spans="8:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H77" t="s">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H80" t="s">
+        <v>45</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J80" t="s">
+        <v>44</v>
+      </c>
+      <c r="L80">
+        <v>2</v>
+      </c>
+      <c r="P80" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="82" spans="8:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H82" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="83" spans="8:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H83" t="s">
+        <v>46</v>
+      </c>
+      <c r="I83" t="s">
+        <v>47</v>
+      </c>
+      <c r="J83" t="s">
+        <v>12</v>
+      </c>
+      <c r="L83">
+        <v>1</v>
+      </c>
+      <c r="P83" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="84" spans="8:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H84" t="s">
+        <v>50</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J84" t="s">
+        <v>49</v>
+      </c>
+      <c r="L84">
+        <v>1</v>
+      </c>
+      <c r="P84" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="85" spans="8:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H85" t="s">
         <v>51</v>
       </c>
-      <c r="I77" t="s">
+      <c r="I85" t="s">
         <v>55</v>
       </c>
-      <c r="J77" t="s">
+      <c r="J85" t="s">
         <v>4</v>
       </c>
-      <c r="L77">
+      <c r="L85">
         <v>2</v>
       </c>
-      <c r="P77" t="s">
+      <c r="P85" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="78" spans="8:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H78" t="s">
+    <row r="86" spans="8:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H86" t="s">
         <v>85</v>
       </c>
-      <c r="I78" t="s">
+      <c r="I86" t="s">
         <v>86</v>
       </c>
-      <c r="J78" t="s">
+      <c r="J86" t="s">
         <v>88</v>
       </c>
-      <c r="L78">
+      <c r="L86">
         <v>1</v>
       </c>
-      <c r="P78" t="s">
+      <c r="P86" t="s">
         <v>87</v>
       </c>
     </row>
@@ -4480,7 +4728,7 @@
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A2:P51">
+  <conditionalFormatting sqref="A2:P59">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>MOD(ROW(A2),2)=1</formula>
     </cfRule>
@@ -4631,7 +4879,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
@@ -4641,11 +4889,11 @@
         <v>1</v>
       </c>
       <c r="H3" cm="1">
-        <f t="array" ref="H3:H202">IFERROR(MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$51&amp;info_index!$C$2:$C$51,0),"")</f>
+        <f t="array" ref="H3:H202">IFERROR(MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$59&amp;info_index!$C$2:$C$59,0),"")</f>
         <v>1</v>
       </c>
       <c r="I3" t="str" cm="1">
-        <f t="array" aca="1" ref="I3:I202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(H3)),INDEX(OFFSET(info_index!$F$2:$F$51,0,$B$23),MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$51&amp;info_index!$C$2:$C$51,0)&amp;"",1),"")</f>
+        <f t="array" aca="1" ref="I3:I202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(H3)),INDEX(OFFSET(info_index!$F$2:$F$59,0,$B$23),MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$59&amp;info_index!$C$2:$C$59,0)&amp;"",1),"")</f>
         <v>箔ロウリール軸</v>
       </c>
       <c r="J3" t="str" cm="1">
@@ -4657,7 +4905,7 @@
         <v>【axis1】 箔ロウリール軸</v>
       </c>
       <c r="M3" t="str" cm="1">
-        <f t="array" ref="M3:M202">IFERROR(INDEX(info_index!$H$2:$H$51,MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$51&amp;info_index!$C$2:$C$51,0),1)&amp;"","")</f>
+        <f t="array" ref="M3:M202">IFERROR(INDEX(info_index!$H$2:$H$59,MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$59&amp;info_index!$C$2:$C$59,0),1)&amp;"","")</f>
         <v>5TK20GN-CW2J+5GN180K</v>
       </c>
       <c r="N3" t="str" cm="1">
@@ -4665,7 +4913,7 @@
         <v>5TK20GN-CW2J+5GN180K</v>
       </c>
       <c r="O3" t="str" cm="1">
-        <f t="array" aca="1" ref="O3:O202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(H3)),INDEX(OFFSET(info_index!$J$2:$J$51,0,$B$23),MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$51&amp;info_index!$C$2:$C$51,0),1)&amp;"","")</f>
+        <f t="array" aca="1" ref="O3:O202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(H3)),INDEX(OFFSET(info_index!$J$2:$J$59,0,$B$23),MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$59&amp;info_index!$C$2:$C$59,0),1)&amp;"","")</f>
         <v>OrientalMotor</v>
       </c>
       <c r="P3" t="str" cm="1">
@@ -5035,7 +5283,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ref="E5:E68" si="0">E4</f>
@@ -6610,7 +6858,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AK$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸
@@ -7094,6 +7342,89 @@
 	ELSE
 		uiErrCode	:= 2;
 	END_IF;
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//平板供給部
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit1】 平板供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//波板供給部
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '波板供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit2】 波板供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//箔ロウ供給部
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウ供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit3】 箔ロウ供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//巻取り軸部
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '巻取り軸部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit4】 巻取り軸部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//溶接部
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit5】 溶接部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//排出部
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit6】 排出部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	ELSE
+		uiErrCode	:= 2;
+	END_IF;
 ELSE
 	uiErrCode	:= 1;
 END_IF;
@@ -17329,7 +17660,7 @@
         <v>29</v>
       </c>
       <c r="G91" t="str">
-        <v/>
+        <v>●</v>
       </c>
       <c r="H91" t="str">
         <v/>
@@ -17410,45 +17741,50 @@
       </c>
       <c r="AJ91" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	ELSE
+		uiErrCode	:= 2;
+	END_IF;</v>
       </c>
       <c r="AK91" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	ELSE
+		uiErrCode	:= 2;
+	END_IF;</v>
       </c>
     </row>
     <row r="92" spans="5:37" x14ac:dyDescent="0.55000000000000004">
-      <c r="E92" t="str">
-        <f t="shared" si="1"/>
-        <v>cylinder</v>
+      <c r="E92" t="s">
+        <v>269</v>
       </c>
       <c r="F92">
         <f>COUNTIF(E$3:E92,E92)</f>
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
-      <c r="H92" t="str">
-        <v/>
+      <c r="H92">
+        <v>50</v>
       </c>
       <c r="I92" t="str">
         <f ca="1"/>
-        <v/>
+        <v>平板供給部</v>
       </c>
       <c r="J92" t="str">
         <f ca="1"/>
-        <v/>
+        <v>平板供給部</v>
       </c>
       <c r="L92" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【unit1】 平板供給部</v>
       </c>
       <c r="M92" t="str">
         <v/>
       </c>
       <c r="N92" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="O92" t="str">
         <f ca="1"/>
@@ -17456,97 +17792,217 @@
       </c>
       <c r="P92" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="X92" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//unit</v>
       </c>
       <c r="Y92" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN</v>
       </c>
       <c r="Z92" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//平板供給部
+	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AA92" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//平板供給部
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB92" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//平板供給部
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板供給部';</v>
       </c>
       <c r="AC92" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//平板供給部
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板供給部';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD92" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//平板供給部
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit1】 平板供給部';</v>
       </c>
       <c r="AE92" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//平板供給部
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit1】 平板供給部';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF92" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//平板供給部
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit1】 平板供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AG92" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//平板供給部
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit1】 平板供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH92" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//平板供給部
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit1】 平板供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI92" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//平板供給部
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit1】 平板供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AJ92" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//平板供給部
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit1】 平板供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AK92" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//平板供給部
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit1】 平板供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="93" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E93" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F93">
         <f>COUNTIF(E$3:E93,E93)</f>
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
-      <c r="H93" t="str">
-        <v/>
+      <c r="H93">
+        <v>51</v>
       </c>
       <c r="I93" t="str">
         <f ca="1"/>
-        <v/>
+        <v>波板供給部</v>
       </c>
       <c r="J93" t="str">
         <f ca="1"/>
-        <v/>
+        <v>波板供給部</v>
       </c>
       <c r="L93" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【unit2】 波板供給部</v>
       </c>
       <c r="M93" t="str">
         <v/>
       </c>
       <c r="N93" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="O93" t="str">
         <f ca="1"/>
@@ -17554,97 +18010,192 @@
       </c>
       <c r="P93" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="X93" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Y93" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Z93" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//波板供給部
+	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AA93" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//波板供給部
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB93" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//波板供給部
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '波板供給部';</v>
       </c>
       <c r="AC93" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//波板供給部
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '波板供給部';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD93" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//波板供給部
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '波板供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit2】 波板供給部';</v>
       </c>
       <c r="AE93" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//波板供給部
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '波板供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit2】 波板供給部';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF93" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//波板供給部
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '波板供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit2】 波板供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AG93" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//波板供給部
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '波板供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit2】 波板供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH93" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//波板供給部
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '波板供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit2】 波板供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI93" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//波板供給部
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '波板供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit2】 波板供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AJ93" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//波板供給部
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '波板供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit2】 波板供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AK93" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//波板供給部
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '波板供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit2】 波板供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="94" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E94" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F94">
         <f>COUNTIF(E$3:E94,E94)</f>
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
-      <c r="H94" t="str">
-        <v/>
+      <c r="H94">
+        <v>52</v>
       </c>
       <c r="I94" t="str">
         <f ca="1"/>
-        <v/>
+        <v>箔ロウ供給部</v>
       </c>
       <c r="J94" t="str">
         <f ca="1"/>
-        <v/>
+        <v>箔ロウ供給部</v>
       </c>
       <c r="L94" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【unit3】 箔ロウ供給部</v>
       </c>
       <c r="M94" t="str">
         <v/>
       </c>
       <c r="N94" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="O94" t="str">
         <f ca="1"/>
@@ -17652,97 +18203,192 @@
       </c>
       <c r="P94" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="X94" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Y94" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Z94" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウ供給部
+	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AA94" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウ供給部
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB94" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウ供給部
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウ供給部';</v>
       </c>
       <c r="AC94" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウ供給部
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウ供給部';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD94" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウ供給部
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウ供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit3】 箔ロウ供給部';</v>
       </c>
       <c r="AE94" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウ供給部
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウ供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit3】 箔ロウ供給部';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF94" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウ供給部
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウ供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit3】 箔ロウ供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AG94" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウ供給部
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウ供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit3】 箔ロウ供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH94" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウ供給部
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウ供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit3】 箔ロウ供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI94" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウ供給部
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウ供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit3】 箔ロウ供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AJ94" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウ供給部
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウ供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit3】 箔ロウ供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AK94" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウ供給部
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウ供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit3】 箔ロウ供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="95" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E95" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F95">
         <f>COUNTIF(E$3:E95,E95)</f>
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
-      <c r="H95" t="str">
-        <v/>
+      <c r="H95">
+        <v>53</v>
       </c>
       <c r="I95" t="str">
         <f ca="1"/>
-        <v/>
+        <v>巻取り軸部</v>
       </c>
       <c r="J95" t="str">
         <f ca="1"/>
-        <v/>
+        <v>巻取り軸部</v>
       </c>
       <c r="L95" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【unit4】 巻取り軸部</v>
       </c>
       <c r="M95" t="str">
         <v/>
       </c>
       <c r="N95" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="O95" t="str">
         <f ca="1"/>
@@ -17750,97 +18396,192 @@
       </c>
       <c r="P95" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="X95" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Y95" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Z95" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//巻取り軸部
+	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AA95" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//巻取り軸部
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB95" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//巻取り軸部
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '巻取り軸部';</v>
       </c>
       <c r="AC95" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//巻取り軸部
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '巻取り軸部';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD95" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//巻取り軸部
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '巻取り軸部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit4】 巻取り軸部';</v>
       </c>
       <c r="AE95" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//巻取り軸部
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '巻取り軸部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit4】 巻取り軸部';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF95" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//巻取り軸部
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '巻取り軸部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit4】 巻取り軸部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AG95" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//巻取り軸部
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '巻取り軸部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit4】 巻取り軸部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH95" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//巻取り軸部
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '巻取り軸部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit4】 巻取り軸部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI95" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//巻取り軸部
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '巻取り軸部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit4】 巻取り軸部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AJ95" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//巻取り軸部
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '巻取り軸部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit4】 巻取り軸部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AK95" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//巻取り軸部
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '巻取り軸部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit4】 巻取り軸部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="96" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E96" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F96">
         <f>COUNTIF(E$3:E96,E96)</f>
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
-      <c r="H96" t="str">
-        <v/>
+      <c r="H96">
+        <v>54</v>
       </c>
       <c r="I96" t="str">
         <f ca="1"/>
-        <v/>
+        <v>溶接部</v>
       </c>
       <c r="J96" t="str">
         <f ca="1"/>
-        <v/>
+        <v>溶接部</v>
       </c>
       <c r="L96" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【unit5】 溶接部</v>
       </c>
       <c r="M96" t="str">
         <v/>
       </c>
       <c r="N96" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="O96" t="str">
         <f ca="1"/>
@@ -17848,97 +18589,192 @@
       </c>
       <c r="P96" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="X96" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Y96" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Z96" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接部
+	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AA96" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接部
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB96" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接部
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接部';</v>
       </c>
       <c r="AC96" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接部
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接部';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD96" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接部
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit5】 溶接部';</v>
       </c>
       <c r="AE96" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接部
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit5】 溶接部';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF96" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接部
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit5】 溶接部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AG96" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接部
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit5】 溶接部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH96" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接部
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit5】 溶接部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI96" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接部
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit5】 溶接部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AJ96" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接部
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit5】 溶接部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AK96" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接部
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit5】 溶接部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="97" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E97" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F97">
         <f>COUNTIF(E$3:E97,E97)</f>
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
-      <c r="H97" t="str">
-        <v/>
+      <c r="H97">
+        <v>55</v>
       </c>
       <c r="I97" t="str">
         <f ca="1"/>
-        <v/>
+        <v>排出部</v>
       </c>
       <c r="J97" t="str">
         <f ca="1"/>
-        <v/>
+        <v>排出部</v>
       </c>
       <c r="L97" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【unit6】 排出部</v>
       </c>
       <c r="M97" t="str">
         <v/>
       </c>
       <c r="N97" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="O97" t="str">
         <f ca="1"/>
@@ -17946,73 +18782,168 @@
       </c>
       <c r="P97" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="X97" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Y97" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Z97" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出部
+	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AA97" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出部
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB97" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出部
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出部';</v>
       </c>
       <c r="AC97" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出部
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出部';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD97" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出部
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit6】 排出部';</v>
       </c>
       <c r="AE97" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出部
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit6】 排出部';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF97" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出部
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit6】 排出部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AG97" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出部
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit6】 排出部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH97" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出部
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit6】 排出部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI97" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出部
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit6】 排出部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AJ97" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出部
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit6】 排出部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AK97" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出部
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit6】 排出部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="98" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E98" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F98">
         <f>COUNTIF(E$3:E98,E98)</f>
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -18106,11 +19037,11 @@
     <row r="99" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E99" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F99">
         <f>COUNTIF(E$3:E99,E99)</f>
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -18204,11 +19135,11 @@
     <row r="100" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E100" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F100">
         <f>COUNTIF(E$3:E100,E100)</f>
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -18302,11 +19233,11 @@
     <row r="101" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E101" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F101">
         <f>COUNTIF(E$3:E101,E101)</f>
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -18400,11 +19331,11 @@
     <row r="102" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E102" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F102">
         <f>COUNTIF(E$3:E102,E102)</f>
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="G102" t="str">
         <v/>
@@ -18498,11 +19429,11 @@
     <row r="103" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E103" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F103">
         <f>COUNTIF(E$3:E103,E103)</f>
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="G103" t="str">
         <v/>
@@ -18596,11 +19527,11 @@
     <row r="104" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E104" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F104">
         <f>COUNTIF(E$3:E104,E104)</f>
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="G104" t="str">
         <v/>
@@ -18694,11 +19625,11 @@
     <row r="105" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E105" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F105">
         <f>COUNTIF(E$3:E105,E105)</f>
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="G105" t="str">
         <v/>
@@ -18792,11 +19723,11 @@
     <row r="106" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E106" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F106">
         <f>COUNTIF(E$3:E106,E106)</f>
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="G106" t="str">
         <v/>
@@ -18890,11 +19821,11 @@
     <row r="107" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E107" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F107">
         <f>COUNTIF(E$3:E107,E107)</f>
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="G107" t="str">
         <v/>
@@ -18988,11 +19919,11 @@
     <row r="108" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E108" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F108">
         <f>COUNTIF(E$3:E108,E108)</f>
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="G108" t="str">
         <v/>
@@ -19086,11 +20017,11 @@
     <row r="109" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E109" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F109">
         <f>COUNTIF(E$3:E109,E109)</f>
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="G109" t="str">
         <v/>
@@ -19184,11 +20115,11 @@
     <row r="110" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E110" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F110">
         <f>COUNTIF(E$3:E110,E110)</f>
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="G110" t="str">
         <v/>
@@ -19282,11 +20213,11 @@
     <row r="111" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E111" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F111">
         <f>COUNTIF(E$3:E111,E111)</f>
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="G111" t="str">
         <v/>
@@ -19380,11 +20311,11 @@
     <row r="112" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E112" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F112">
         <f>COUNTIF(E$3:E112,E112)</f>
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="G112" t="str">
         <v/>
@@ -19478,11 +20409,11 @@
     <row r="113" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E113" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F113">
         <f>COUNTIF(E$3:E113,E113)</f>
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="G113" t="str">
         <v/>
@@ -19576,11 +20507,11 @@
     <row r="114" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E114" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F114">
         <f>COUNTIF(E$3:E114,E114)</f>
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="G114" t="str">
         <v/>
@@ -19674,11 +20605,11 @@
     <row r="115" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E115" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F115">
         <f>COUNTIF(E$3:E115,E115)</f>
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="G115" t="str">
         <v/>
@@ -19772,11 +20703,11 @@
     <row r="116" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E116" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F116">
         <f>COUNTIF(E$3:E116,E116)</f>
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="G116" t="str">
         <v/>
@@ -19870,11 +20801,11 @@
     <row r="117" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E117" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F117">
         <f>COUNTIF(E$3:E117,E117)</f>
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="G117" t="str">
         <v/>
@@ -19968,11 +20899,11 @@
     <row r="118" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E118" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F118">
         <f>COUNTIF(E$3:E118,E118)</f>
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="G118" t="str">
         <v/>
@@ -20066,11 +20997,11 @@
     <row r="119" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E119" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F119">
         <f>COUNTIF(E$3:E119,E119)</f>
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="G119" t="str">
         <v/>
@@ -20164,11 +21095,11 @@
     <row r="120" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E120" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F120">
         <f>COUNTIF(E$3:E120,E120)</f>
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="G120" t="str">
         <v/>
@@ -20262,11 +21193,11 @@
     <row r="121" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E121" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F121">
         <f>COUNTIF(E$3:E121,E121)</f>
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="G121" t="str">
         <v/>
@@ -20360,11 +21291,11 @@
     <row r="122" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E122" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F122">
         <f>COUNTIF(E$3:E122,E122)</f>
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="G122" t="str">
         <v/>
@@ -20458,11 +21389,11 @@
     <row r="123" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E123" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F123">
         <f>COUNTIF(E$3:E123,E123)</f>
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="G123" t="str">
         <v/>
@@ -20556,11 +21487,11 @@
     <row r="124" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E124" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F124">
         <f>COUNTIF(E$3:E124,E124)</f>
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="G124" t="str">
         <v/>
@@ -20654,11 +21585,11 @@
     <row r="125" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E125" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F125">
         <f>COUNTIF(E$3:E125,E125)</f>
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="G125" t="str">
         <v/>
@@ -20752,11 +21683,11 @@
     <row r="126" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E126" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F126">
         <f>COUNTIF(E$3:E126,E126)</f>
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="G126" t="str">
         <v/>
@@ -20850,11 +21781,11 @@
     <row r="127" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E127" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F127">
         <f>COUNTIF(E$3:E127,E127)</f>
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="G127" t="str">
         <v/>
@@ -20948,11 +21879,11 @@
     <row r="128" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E128" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F128">
         <f>COUNTIF(E$3:E128,E128)</f>
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="G128" t="str">
         <v/>
@@ -21046,11 +21977,11 @@
     <row r="129" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E129" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F129">
         <f>COUNTIF(E$3:E129,E129)</f>
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="G129" t="str">
         <v/>
@@ -21144,11 +22075,11 @@
     <row r="130" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E130" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F130">
         <f>COUNTIF(E$3:E130,E130)</f>
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="G130" t="str">
         <v/>
@@ -21242,11 +22173,11 @@
     <row r="131" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E131" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F131">
         <f>COUNTIF(E$3:E131,E131)</f>
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="G131" t="str">
         <v/>
@@ -21340,11 +22271,11 @@
     <row r="132" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E132" t="str">
         <f t="shared" si="1"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F132">
         <f>COUNTIF(E$3:E132,E132)</f>
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="G132" t="str">
         <v/>
@@ -21438,11 +22369,11 @@
     <row r="133" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E133" t="str">
         <f t="shared" ref="E133:E196" si="2">E132</f>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F133">
         <f>COUNTIF(E$3:E133,E133)</f>
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="G133" t="str">
         <v/>
@@ -21536,11 +22467,11 @@
     <row r="134" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E134" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F134">
         <f>COUNTIF(E$3:E134,E134)</f>
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G134" t="str">
         <v/>
@@ -21634,11 +22565,11 @@
     <row r="135" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E135" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F135">
         <f>COUNTIF(E$3:E135,E135)</f>
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="G135" t="str">
         <v/>
@@ -21732,11 +22663,11 @@
     <row r="136" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E136" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F136">
         <f>COUNTIF(E$3:E136,E136)</f>
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="G136" t="str">
         <v/>
@@ -21830,11 +22761,11 @@
     <row r="137" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E137" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F137">
         <f>COUNTIF(E$3:E137,E137)</f>
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G137" t="str">
         <v/>
@@ -21928,11 +22859,11 @@
     <row r="138" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E138" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F138">
         <f>COUNTIF(E$3:E138,E138)</f>
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="G138" t="str">
         <v/>
@@ -22026,11 +22957,11 @@
     <row r="139" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E139" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F139">
         <f>COUNTIF(E$3:E139,E139)</f>
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="G139" t="str">
         <v/>
@@ -22124,11 +23055,11 @@
     <row r="140" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E140" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F140">
         <f>COUNTIF(E$3:E140,E140)</f>
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="G140" t="str">
         <v/>
@@ -22222,11 +23153,11 @@
     <row r="141" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E141" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F141">
         <f>COUNTIF(E$3:E141,E141)</f>
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="G141" t="str">
         <v/>
@@ -22320,11 +23251,11 @@
     <row r="142" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E142" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F142">
         <f>COUNTIF(E$3:E142,E142)</f>
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="G142" t="str">
         <v/>
@@ -22418,11 +23349,11 @@
     <row r="143" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E143" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F143">
         <f>COUNTIF(E$3:E143,E143)</f>
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="G143" t="str">
         <v/>
@@ -22516,11 +23447,11 @@
     <row r="144" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E144" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F144">
         <f>COUNTIF(E$3:E144,E144)</f>
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="G144" t="str">
         <v/>
@@ -22614,11 +23545,11 @@
     <row r="145" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E145" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F145">
         <f>COUNTIF(E$3:E145,E145)</f>
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="G145" t="str">
         <v/>
@@ -22712,11 +23643,11 @@
     <row r="146" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E146" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F146">
         <f>COUNTIF(E$3:E146,E146)</f>
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="G146" t="str">
         <v/>
@@ -22810,11 +23741,11 @@
     <row r="147" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E147" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F147">
         <f>COUNTIF(E$3:E147,E147)</f>
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="G147" t="str">
         <v/>
@@ -22908,11 +23839,11 @@
     <row r="148" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E148" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F148">
         <f>COUNTIF(E$3:E148,E148)</f>
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="G148" t="str">
         <v/>
@@ -23006,11 +23937,11 @@
     <row r="149" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E149" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F149">
         <f>COUNTIF(E$3:E149,E149)</f>
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="G149" t="str">
         <v/>
@@ -23104,11 +24035,11 @@
     <row r="150" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E150" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F150">
         <f>COUNTIF(E$3:E150,E150)</f>
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="G150" t="str">
         <v/>
@@ -23202,11 +24133,11 @@
     <row r="151" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E151" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F151">
         <f>COUNTIF(E$3:E151,E151)</f>
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="G151" t="str">
         <v/>
@@ -23300,11 +24231,11 @@
     <row r="152" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E152" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F152">
         <f>COUNTIF(E$3:E152,E152)</f>
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="G152" t="str">
         <v/>
@@ -23398,11 +24329,11 @@
     <row r="153" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E153" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F153">
         <f>COUNTIF(E$3:E153,E153)</f>
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="G153" t="str">
         <v/>
@@ -23496,11 +24427,11 @@
     <row r="154" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E154" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F154">
         <f>COUNTIF(E$3:E154,E154)</f>
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="G154" t="str">
         <v/>
@@ -23594,11 +24525,11 @@
     <row r="155" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E155" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F155">
         <f>COUNTIF(E$3:E155,E155)</f>
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="G155" t="str">
         <v/>
@@ -23692,11 +24623,11 @@
     <row r="156" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E156" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F156">
         <f>COUNTIF(E$3:E156,E156)</f>
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="G156" t="str">
         <v/>
@@ -23790,11 +24721,11 @@
     <row r="157" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E157" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F157">
         <f>COUNTIF(E$3:E157,E157)</f>
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="G157" t="str">
         <v/>
@@ -23888,11 +24819,11 @@
     <row r="158" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E158" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F158">
         <f>COUNTIF(E$3:E158,E158)</f>
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="G158" t="str">
         <v/>
@@ -23986,11 +24917,11 @@
     <row r="159" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E159" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F159">
         <f>COUNTIF(E$3:E159,E159)</f>
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="G159" t="str">
         <v/>
@@ -24084,11 +25015,11 @@
     <row r="160" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E160" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F160">
         <f>COUNTIF(E$3:E160,E160)</f>
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="G160" t="str">
         <v/>
@@ -24182,11 +25113,11 @@
     <row r="161" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E161" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F161">
         <f>COUNTIF(E$3:E161,E161)</f>
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="G161" t="str">
         <v/>
@@ -24280,11 +25211,11 @@
     <row r="162" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E162" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F162">
         <f>COUNTIF(E$3:E162,E162)</f>
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="G162" t="str">
         <v/>
@@ -24378,11 +25309,11 @@
     <row r="163" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E163" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F163">
         <f>COUNTIF(E$3:E163,E163)</f>
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="G163" t="str">
         <v/>
@@ -24476,11 +25407,11 @@
     <row r="164" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E164" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F164">
         <f>COUNTIF(E$3:E164,E164)</f>
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="G164" t="str">
         <v/>
@@ -24574,11 +25505,11 @@
     <row r="165" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E165" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F165">
         <f>COUNTIF(E$3:E165,E165)</f>
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="G165" t="str">
         <v/>
@@ -24672,11 +25603,11 @@
     <row r="166" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E166" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F166">
         <f>COUNTIF(E$3:E166,E166)</f>
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="G166" t="str">
         <v/>
@@ -24770,11 +25701,11 @@
     <row r="167" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E167" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F167">
         <f>COUNTIF(E$3:E167,E167)</f>
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="G167" t="str">
         <v/>
@@ -24868,11 +25799,11 @@
     <row r="168" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E168" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F168">
         <f>COUNTIF(E$3:E168,E168)</f>
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="G168" t="str">
         <v/>
@@ -24966,11 +25897,11 @@
     <row r="169" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E169" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F169">
         <f>COUNTIF(E$3:E169,E169)</f>
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="G169" t="str">
         <v/>
@@ -25064,11 +25995,11 @@
     <row r="170" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E170" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F170">
         <f>COUNTIF(E$3:E170,E170)</f>
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="G170" t="str">
         <v/>
@@ -25162,11 +26093,11 @@
     <row r="171" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E171" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F171">
         <f>COUNTIF(E$3:E171,E171)</f>
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="G171" t="str">
         <v/>
@@ -25260,11 +26191,11 @@
     <row r="172" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E172" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F172">
         <f>COUNTIF(E$3:E172,E172)</f>
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="G172" t="str">
         <v/>
@@ -25358,11 +26289,11 @@
     <row r="173" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E173" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F173">
         <f>COUNTIF(E$3:E173,E173)</f>
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="G173" t="str">
         <v/>
@@ -25456,11 +26387,11 @@
     <row r="174" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E174" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F174">
         <f>COUNTIF(E$3:E174,E174)</f>
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="G174" t="str">
         <v/>
@@ -25554,11 +26485,11 @@
     <row r="175" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E175" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F175">
         <f>COUNTIF(E$3:E175,E175)</f>
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="G175" t="str">
         <v/>
@@ -25652,11 +26583,11 @@
     <row r="176" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E176" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F176">
         <f>COUNTIF(E$3:E176,E176)</f>
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="G176" t="str">
         <v/>
@@ -25750,11 +26681,11 @@
     <row r="177" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E177" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F177">
         <f>COUNTIF(E$3:E177,E177)</f>
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="G177" t="str">
         <v/>
@@ -25848,11 +26779,11 @@
     <row r="178" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E178" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F178">
         <f>COUNTIF(E$3:E178,E178)</f>
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="G178" t="str">
         <v/>
@@ -25946,11 +26877,11 @@
     <row r="179" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E179" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F179">
         <f>COUNTIF(E$3:E179,E179)</f>
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="G179" t="str">
         <v/>
@@ -26044,11 +26975,11 @@
     <row r="180" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E180" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F180">
         <f>COUNTIF(E$3:E180,E180)</f>
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="G180" t="str">
         <v/>
@@ -26142,11 +27073,11 @@
     <row r="181" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E181" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F181">
         <f>COUNTIF(E$3:E181,E181)</f>
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="G181" t="str">
         <v/>
@@ -26240,11 +27171,11 @@
     <row r="182" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E182" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F182">
         <f>COUNTIF(E$3:E182,E182)</f>
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="G182" t="str">
         <v/>
@@ -26338,11 +27269,11 @@
     <row r="183" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E183" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F183">
         <f>COUNTIF(E$3:E183,E183)</f>
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="G183" t="str">
         <v/>
@@ -26436,11 +27367,11 @@
     <row r="184" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E184" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F184">
         <f>COUNTIF(E$3:E184,E184)</f>
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="G184" t="str">
         <v/>
@@ -26534,11 +27465,11 @@
     <row r="185" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E185" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F185">
         <f>COUNTIF(E$3:E185,E185)</f>
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="G185" t="str">
         <v/>
@@ -26632,11 +27563,11 @@
     <row r="186" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E186" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F186">
         <f>COUNTIF(E$3:E186,E186)</f>
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="G186" t="str">
         <v/>
@@ -26730,11 +27661,11 @@
     <row r="187" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E187" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F187">
         <f>COUNTIF(E$3:E187,E187)</f>
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="G187" t="str">
         <v/>
@@ -26828,11 +27759,11 @@
     <row r="188" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E188" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F188">
         <f>COUNTIF(E$3:E188,E188)</f>
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="G188" t="str">
         <v/>
@@ -26926,11 +27857,11 @@
     <row r="189" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E189" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F189">
         <f>COUNTIF(E$3:E189,E189)</f>
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="G189" t="str">
         <v/>
@@ -27024,11 +27955,11 @@
     <row r="190" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E190" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F190">
         <f>COUNTIF(E$3:E190,E190)</f>
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="G190" t="str">
         <v/>
@@ -27122,11 +28053,11 @@
     <row r="191" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E191" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F191">
         <f>COUNTIF(E$3:E191,E191)</f>
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="G191" t="str">
         <v/>
@@ -27220,11 +28151,11 @@
     <row r="192" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E192" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F192">
         <f>COUNTIF(E$3:E192,E192)</f>
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="G192" t="str">
         <v/>
@@ -27318,11 +28249,11 @@
     <row r="193" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E193" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F193">
         <f>COUNTIF(E$3:E193,E193)</f>
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="G193" t="str">
         <v/>
@@ -27416,11 +28347,11 @@
     <row r="194" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E194" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F194">
         <f>COUNTIF(E$3:E194,E194)</f>
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="G194" t="str">
         <v/>
@@ -27514,11 +28445,11 @@
     <row r="195" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E195" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F195">
         <f>COUNTIF(E$3:E195,E195)</f>
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="G195" t="str">
         <v/>
@@ -27612,11 +28543,11 @@
     <row r="196" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E196" t="str">
         <f t="shared" si="2"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F196">
         <f>COUNTIF(E$3:E196,E196)</f>
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="G196" t="str">
         <v/>
@@ -27710,11 +28641,11 @@
     <row r="197" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E197" t="str">
         <f t="shared" ref="E197:E202" si="3">E196</f>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F197">
         <f>COUNTIF(E$3:E197,E197)</f>
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="G197" t="str">
         <v/>
@@ -27808,11 +28739,11 @@
     <row r="198" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E198" t="str">
         <f t="shared" si="3"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F198">
         <f>COUNTIF(E$3:E198,E198)</f>
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="G198" t="str">
         <v/>
@@ -27906,11 +28837,11 @@
     <row r="199" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E199" t="str">
         <f t="shared" si="3"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F199">
         <f>COUNTIF(E$3:E199,E199)</f>
-        <v>137</v>
+        <v>108</v>
       </c>
       <c r="G199" t="str">
         <v/>
@@ -28004,11 +28935,11 @@
     <row r="200" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E200" t="str">
         <f t="shared" si="3"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F200">
         <f>COUNTIF(E$3:E200,E200)</f>
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="G200" t="str">
         <v/>
@@ -28102,11 +29033,11 @@
     <row r="201" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E201" t="str">
         <f t="shared" si="3"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F201">
         <f>COUNTIF(E$3:E201,E201)</f>
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="G201" t="str">
         <v/>
@@ -28200,11 +29131,11 @@
     <row r="202" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E202" t="str">
         <f t="shared" si="3"/>
-        <v>cylinder</v>
+        <v>unit</v>
       </c>
       <c r="F202">
         <f>COUNTIF(E$3:E202,E202)</f>
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="G202" t="str">
         <v>●</v>
@@ -28304,7 +29235,7 @@
     <row r="205" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="AK205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AK$3:AK$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸
@@ -28788,6 +29719,89 @@
 	ELSE
 		uiErrCode	:= 2;
 	END_IF;
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//平板供給部
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit1】 平板供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//波板供給部
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '波板供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit2】 波板供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//箔ロウ供給部
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウ供給部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit3】 箔ロウ供給部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//巻取り軸部
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '巻取り軸部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit4】 巻取り軸部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//溶接部
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit5】 溶接部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//排出部
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出部';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit6】 排出部';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	ELSE
+		uiErrCode	:= 2;
+	END_IF;
 ELSE
 	uiErrCode	:= 1;
 END_IF;

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D663CF54-BC0E-4CA2-AA3F-39FF6BEA1136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB28470-3E18-484C-8FB2-CDE4B94CD573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="info_script" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$P$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$P$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="280">
   <si>
     <t>RCA2-GS3NA-I-10-2-50-A6-M-K1</t>
   </si>
@@ -1463,6 +1463,30 @@
     <t>WLD</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>箔ロウリール固定</t>
+    <rPh sb="0" eb="1">
+      <t>ハク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MGPM12-20Z-M9BL</t>
+  </si>
+  <si>
+    <t>Foil wax reel fixing</t>
+  </si>
+  <si>
+    <t>MISUMI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ガイド付薄形シリンダ MGPシリーズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -1854,15 +1878,15 @@
   <dxfs count="2">
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <patternFill patternType="lightUp">
+          <fgColor rgb="FF33CCCC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="lightUp">
-          <fgColor rgb="FF33CCCC"/>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1899,7 +1923,7 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$A$62">
+    <xdr:sp macro="" textlink="$A$63">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="正方形/長方形 1">
           <a:extLst>
@@ -1959,7 +1983,7 @@
               <a:ea typeface="游ゴシック"/>
             </a:rPr>
             <a:pPr algn="l"/>
-            <a:t>57</a:t>
+            <a:t>58</a:t>
           </a:fld>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="600"/>
         </a:p>
@@ -2268,7 +2292,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:P86"/>
+  <dimension ref="A1:P87"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -3750,46 +3774,48 @@
       <c r="P36" s="10"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="29">
-        <v>12</v>
-      </c>
-      <c r="B37" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="C37" s="29"/>
-      <c r="D37" s="14">
-        <v>11</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="I37" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J37" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="K37" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="L37" s="15">
-        <v>1</v>
-      </c>
-      <c r="M37" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="N37" s="26"/>
-      <c r="O37" s="26"/>
+      <c r="A37" s="7">
+        <v>58</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C37" s="7">
+        <v>20</v>
+      </c>
+      <c r="D37" s="8">
+        <v>7</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="L37" s="8"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
       <c r="P37" s="10"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="29">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B38" s="29" t="s">
         <v>115</v>
@@ -3799,15 +3825,15 @@
         <v>11</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F38" s="14"/>
       <c r="G38" s="14"/>
       <c r="H38" s="14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="J38" s="14" t="s">
         <v>4</v>
@@ -3827,7 +3853,7 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="29">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B39" s="29" t="s">
         <v>115</v>
@@ -3864,76 +3890,76 @@
       <c r="P39" s="10"/>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="7">
-        <v>21</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C40" s="7">
+      <c r="A40" s="29">
+        <v>17</v>
+      </c>
+      <c r="B40" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="C40" s="29"/>
+      <c r="D40" s="14">
+        <v>11</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I40" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="L40" s="15">
         <v>1</v>
       </c>
-      <c r="D40" s="8">
-        <v>1</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I40" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="J40" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="K40" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="L40" s="8">
-        <v>1</v>
-      </c>
-      <c r="M40" s="10"/>
-      <c r="N40" s="10"/>
-      <c r="O40" s="10"/>
+      <c r="M40" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="N40" s="26"/>
+      <c r="O40" s="26"/>
       <c r="P40" s="10"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="7">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C41" s="7"/>
+        <v>122</v>
+      </c>
+      <c r="C41" s="7">
+        <v>1</v>
+      </c>
       <c r="D41" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G41" s="8"/>
+        <v>129</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>203</v>
+      </c>
       <c r="H41" s="8" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>225</v>
+        <v>2</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L41" s="8">
         <v>1</v>
@@ -3945,7 +3971,7 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>119</v>
@@ -3962,10 +3988,10 @@
       </c>
       <c r="G42" s="8"/>
       <c r="H42" s="8" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J42" s="8" t="s">
         <v>225</v>
@@ -3983,25 +4009,27 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="7">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>119</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="8">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="F43" s="8"/>
+        <v>94</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>90</v>
+      </c>
       <c r="G43" s="8"/>
       <c r="H43" s="8" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J43" s="8" t="s">
         <v>225</v>
@@ -4010,7 +4038,7 @@
         <v>224</v>
       </c>
       <c r="L43" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M43" s="10"/>
       <c r="N43" s="10"/>
@@ -4019,27 +4047,25 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>119</v>
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="8">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>108</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="F44" s="8"/>
       <c r="G44" s="8"/>
       <c r="H44" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J44" s="8" t="s">
         <v>225</v>
@@ -4048,18 +4074,16 @@
         <v>224</v>
       </c>
       <c r="L44" s="8">
-        <v>1</v>
-      </c>
-      <c r="M44" s="10" t="s">
-        <v>57</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M44" s="10"/>
       <c r="N44" s="10"/>
       <c r="O44" s="10"/>
       <c r="P44" s="10"/>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="7">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>119</v>
@@ -4072,14 +4096,14 @@
         <v>99</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G45" s="8"/>
       <c r="H45" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I45" s="16" t="s">
-        <v>36</v>
+        <v>25</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="J45" s="8" t="s">
         <v>225</v>
@@ -4091,7 +4115,7 @@
         <v>1</v>
       </c>
       <c r="M45" s="10" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="N45" s="10"/>
       <c r="O45" s="10"/>
@@ -4099,9 +4123,11 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="7">
-        <v>26</v>
-      </c>
-      <c r="B46" s="7"/>
+        <v>34</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>119</v>
+      </c>
       <c r="C46" s="7"/>
       <c r="D46" s="8">
         <v>1</v>
@@ -4109,13 +4135,15 @@
       <c r="E46" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="F46" s="8"/>
+      <c r="F46" s="8" t="s">
+        <v>109</v>
+      </c>
       <c r="G46" s="8"/>
       <c r="H46" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>59</v>
+        <v>35</v>
+      </c>
+      <c r="I46" s="16" t="s">
+        <v>36</v>
       </c>
       <c r="J46" s="8" t="s">
         <v>225</v>
@@ -4126,30 +4154,32 @@
       <c r="L46" s="8">
         <v>1</v>
       </c>
-      <c r="M46" s="10"/>
+      <c r="M46" s="10" t="s">
+        <v>34</v>
+      </c>
       <c r="N46" s="10"/>
       <c r="O46" s="10"/>
       <c r="P46" s="10"/>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
       <c r="H47" s="8" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J47" s="8" t="s">
         <v>225</v>
@@ -4167,7 +4197,7 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -4180,10 +4210,10 @@
       <c r="F48" s="8"/>
       <c r="G48" s="8"/>
       <c r="H48" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J48" s="8" t="s">
         <v>225</v>
@@ -4201,23 +4231,23 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="7">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
       <c r="H49" s="8" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J49" s="8" t="s">
         <v>225</v>
@@ -4228,24 +4258,22 @@
       <c r="L49" s="8">
         <v>1</v>
       </c>
-      <c r="M49" s="10" t="s">
-        <v>57</v>
-      </c>
+      <c r="M49" s="10"/>
       <c r="N49" s="10"/>
       <c r="O49" s="10"/>
       <c r="P49" s="10"/>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="7">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="8">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F50" s="8"/>
       <c r="G50" s="8"/>
@@ -4264,34 +4292,42 @@
       <c r="L50" s="8">
         <v>1</v>
       </c>
-      <c r="M50" s="10"/>
+      <c r="M50" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="N50" s="10"/>
       <c r="O50" s="10"/>
       <c r="P50" s="10"/>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="7">
-        <v>51</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="C51" s="7">
+        <v>39</v>
+      </c>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="8">
+        <v>7</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="K51" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="L51" s="8">
         <v>1</v>
       </c>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="G51" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="H51" s="8"/>
-      <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="8"/>
       <c r="M51" s="10"/>
       <c r="N51" s="10"/>
       <c r="O51" s="10"/>
@@ -4299,21 +4335,21 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="7">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>266</v>
       </c>
       <c r="C52" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H52" s="8"/>
       <c r="I52" s="8"/>
@@ -4327,21 +4363,21 @@
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="7">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>266</v>
       </c>
       <c r="C53" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
@@ -4355,21 +4391,21 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="7">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>266</v>
       </c>
       <c r="C54" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
       <c r="F54" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H54" s="8"/>
       <c r="I54" s="8"/>
@@ -4383,21 +4419,21 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>266</v>
       </c>
       <c r="C55" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
       <c r="F55" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
@@ -4411,21 +4447,21 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="7">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>266</v>
       </c>
       <c r="C56" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
@@ -4439,21 +4475,21 @@
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="7">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C57" s="7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
       <c r="F57" s="8" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
@@ -4466,13 +4502,23 @@
       <c r="P57" s="10"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="7"/>
-      <c r="B58" s="7"/>
-      <c r="C58" s="7"/>
+      <c r="A58" s="7">
+        <v>57</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="C58" s="7">
+        <v>1</v>
+      </c>
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
+      <c r="F58" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>273</v>
+      </c>
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
       <c r="J58" s="8"/>
@@ -4484,104 +4530,105 @@
       <c r="P58" s="10"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="18"/>
-      <c r="B59" s="18"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="19"/>
-      <c r="F59" s="19"/>
-      <c r="G59" s="19"/>
-      <c r="H59" s="19"/>
-      <c r="I59" s="19"/>
-      <c r="J59" s="19"/>
-      <c r="K59" s="19"/>
-      <c r="L59" s="19"/>
-      <c r="M59" s="20"/>
-      <c r="N59" s="20"/>
-      <c r="O59" s="20"/>
-      <c r="P59" s="20"/>
+      <c r="A59" s="7"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="8"/>
+      <c r="J59" s="8"/>
+      <c r="K59" s="8"/>
+      <c r="L59" s="8"/>
+      <c r="M59" s="10"/>
+      <c r="N59" s="10"/>
+      <c r="O59" s="10"/>
+      <c r="P59" s="10"/>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" t="s">
-        <v>111</v>
-      </c>
-      <c r="D61" t="s">
-        <v>110</v>
-      </c>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="18"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="19"/>
+      <c r="F60" s="19"/>
+      <c r="G60" s="19"/>
+      <c r="H60" s="19"/>
+      <c r="I60" s="19"/>
+      <c r="J60" s="19"/>
+      <c r="K60" s="19"/>
+      <c r="L60" s="19"/>
+      <c r="M60" s="20"/>
+      <c r="N60" s="20"/>
+      <c r="O60" s="20"/>
+      <c r="P60" s="20"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62">
-        <f>MAX(A$2:A$59)</f>
-        <v>57</v>
-      </c>
-      <c r="D62">
-        <f>MAX(D$2:D$59)</f>
-        <v>11</v>
+      <c r="A62" t="s">
+        <v>111</v>
+      </c>
+      <c r="D62" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" t="s">
-        <v>199</v>
-      </c>
-      <c r="B63" t="s">
-        <v>117</v>
-      </c>
-      <c r="C63" t="s">
-        <v>116</v>
+      <c r="A63">
+        <f>MAX(A$2:A$60)</f>
+        <v>58</v>
+      </c>
+      <c r="D63">
+        <f>MAX(D$2:D$60)</f>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64">
-        <f>ROW(A60)-ROW(A1)-1</f>
-        <v>58</v>
-      </c>
-      <c r="B64">
-        <f>COUNTIF(B$2:B$59,B63)</f>
+      <c r="A64" t="s">
+        <v>199</v>
+      </c>
+      <c r="B64" t="s">
+        <v>117</v>
+      </c>
+      <c r="C64" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65">
+        <f>ROW(A61)-ROW(A1)-1</f>
+        <v>59</v>
+      </c>
+      <c r="B65">
+        <f>COUNTIF(B$2:B$60,B64)</f>
         <v>16</v>
       </c>
-      <c r="C64" s="28">
-        <f>_xlfn.MAXIFS(C$2:C$59,$B$2:$B$59,C63)</f>
+      <c r="C65" s="28">
+        <f>_xlfn.MAXIFS(C$2:C$60,$B$2:$B$60,C64)</f>
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" t="s">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" t="s">
         <v>114</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C66" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66">
-        <f>COUNTIF(B$2:B$59,B65)</f>
-        <v>22</v>
-      </c>
-      <c r="C66" s="28">
-        <f>_xlfn.MAXIFS(C$2:C$59,$B$2:$B$59,C65)</f>
-        <v>19</v>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67">
+        <f>COUNTIF(B$2:B$60,B66)</f>
+        <v>23</v>
+      </c>
+      <c r="C67" s="28">
+        <f>_xlfn.MAXIFS(C$2:C$60,$B$2:$B$60,C66)</f>
+        <v>20</v>
       </c>
     </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H69" s="2" t="s">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H70" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="L69">
-        <v>1</v>
-      </c>
-      <c r="P69" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H70" t="s">
-        <v>56</v>
-      </c>
-      <c r="I70" t="s">
-        <v>53</v>
-      </c>
-      <c r="J70" t="s">
-        <v>52</v>
       </c>
       <c r="L70">
         <v>1</v>
@@ -4590,120 +4637,120 @@
         <v>79</v>
       </c>
     </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H72" s="2" t="s">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H71" t="s">
+        <v>56</v>
+      </c>
+      <c r="I71" t="s">
+        <v>53</v>
+      </c>
+      <c r="J71" t="s">
+        <v>52</v>
+      </c>
+      <c r="L71">
+        <v>1</v>
+      </c>
+      <c r="P71" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H73" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H73" t="s">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H74" t="s">
         <v>82</v>
       </c>
-      <c r="I73" t="s">
+      <c r="I74" t="s">
         <v>84</v>
       </c>
-      <c r="J73" t="s">
+      <c r="J74" t="s">
         <v>80</v>
       </c>
-      <c r="L73">
+      <c r="L74">
         <v>1</v>
       </c>
-      <c r="P73" t="s">
+      <c r="P74" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H75" s="2" t="s">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H76" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H76" t="s">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H77" t="s">
         <v>83</v>
       </c>
-      <c r="I76" t="s">
+      <c r="I77" t="s">
         <v>84</v>
       </c>
-      <c r="J76" t="s">
+      <c r="J77" t="s">
         <v>81</v>
       </c>
-      <c r="L76">
+      <c r="L77">
         <v>1</v>
       </c>
-      <c r="P76" t="s">
+      <c r="P77" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="78" spans="2:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H78" s="2" t="s">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H79" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H79" t="s">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H80" t="s">
         <v>42</v>
       </c>
-      <c r="I79" t="s">
+      <c r="I80" t="s">
         <v>43</v>
       </c>
-      <c r="J79" t="s">
+      <c r="J80" t="s">
         <v>12</v>
       </c>
-      <c r="L79">
+      <c r="L80">
         <v>1</v>
-      </c>
-      <c r="P79" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H80" t="s">
-        <v>45</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J80" t="s">
-        <v>44</v>
-      </c>
-      <c r="L80">
-        <v>2</v>
       </c>
       <c r="P80" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="82" spans="8:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H82" s="2" t="s">
-        <v>41</v>
+    <row r="81" spans="8:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H81" t="s">
+        <v>45</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J81" t="s">
+        <v>44</v>
+      </c>
+      <c r="L81">
+        <v>2</v>
+      </c>
+      <c r="P81" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="83" spans="8:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="H83" t="s">
-        <v>46</v>
-      </c>
-      <c r="I83" t="s">
-        <v>47</v>
-      </c>
-      <c r="J83" t="s">
-        <v>12</v>
-      </c>
-      <c r="L83">
-        <v>1</v>
-      </c>
-      <c r="P83" t="s">
-        <v>87</v>
+      <c r="H83" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="84" spans="8:16" x14ac:dyDescent="0.55000000000000004">
       <c r="H84" t="s">
-        <v>50</v>
-      </c>
-      <c r="I84" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
+      </c>
+      <c r="I84" t="s">
+        <v>47</v>
       </c>
       <c r="J84" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="L84">
         <v>1</v>
@@ -4714,16 +4761,16 @@
     </row>
     <row r="85" spans="8:16" x14ac:dyDescent="0.55000000000000004">
       <c r="H85" t="s">
-        <v>51</v>
-      </c>
-      <c r="I85" t="s">
-        <v>55</v>
+        <v>50</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="J85" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="L85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P85" t="s">
         <v>87</v>
@@ -4731,30 +4778,47 @@
     </row>
     <row r="86" spans="8:16" x14ac:dyDescent="0.55000000000000004">
       <c r="H86" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="I86" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="J86" t="s">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="L86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P86" t="s">
         <v>87</v>
       </c>
     </row>
+    <row r="87" spans="8:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="H87" t="s">
+        <v>85</v>
+      </c>
+      <c r="I87" t="s">
+        <v>86</v>
+      </c>
+      <c r="J87" t="s">
+        <v>88</v>
+      </c>
+      <c r="L87">
+        <v>1</v>
+      </c>
+      <c r="P87" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P50" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P50">
-      <sortCondition ref="B1:B50"/>
+  <autoFilter ref="A1:P51" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P51">
+      <sortCondition ref="B1:B51"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A2:P59">
-    <cfRule type="expression" dxfId="0" priority="1">
+  <conditionalFormatting sqref="A2:P60">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>MOD(ROW(A2),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4904,7 +4968,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]info_index</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
@@ -4914,11 +4978,11 @@
         <v>1</v>
       </c>
       <c r="H3" cm="1">
-        <f t="array" ref="H3:H202">IFERROR(MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$59&amp;info_index!$C$2:$C$59,0),"")</f>
+        <f t="array" ref="H3:H202">IFERROR(MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$60&amp;info_index!$C$2:$C$60,0),"")</f>
         <v>1</v>
       </c>
       <c r="I3" t="str" cm="1">
-        <f t="array" aca="1" ref="I3:I202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(H3)),INDEX(OFFSET(info_index!$F$2:$F$59,0,$B$23),MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$59&amp;info_index!$C$2:$C$59,0)&amp;"",1),"")</f>
+        <f t="array" aca="1" ref="I3:I202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(H3)),INDEX(OFFSET(info_index!$F$2:$F$60,0,$B$23),MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$60&amp;info_index!$C$2:$C$60,0)&amp;"",1),"")</f>
         <v>箔ロウリール軸</v>
       </c>
       <c r="J3" t="str" cm="1">
@@ -4930,7 +4994,7 @@
         <v>【axis1】 箔ロウリール軸</v>
       </c>
       <c r="M3" t="str" cm="1">
-        <f t="array" ref="M3:M202">IFERROR(INDEX(info_index!$H$2:$H$59,MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$59&amp;info_index!$C$2:$C$59,0),1)&amp;"","")</f>
+        <f t="array" ref="M3:M202">IFERROR(INDEX(info_index!$H$2:$H$60,MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$60&amp;info_index!$C$2:$C$60,0),1)&amp;"","")</f>
         <v>5TK20GN-CW2J+5GN180K</v>
       </c>
       <c r="N3" t="str" cm="1">
@@ -4938,7 +5002,7 @@
         <v>5TK20GN-CW2J+5GN180K</v>
       </c>
       <c r="O3" t="str" cm="1">
-        <f t="array" aca="1" ref="O3:O202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(H3)),INDEX(OFFSET(info_index!$J$2:$J$59,0,$B$23),MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$59&amp;info_index!$C$2:$C$59,0),1)&amp;"","")</f>
+        <f t="array" aca="1" ref="O3:O202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(H3)),INDEX(OFFSET(info_index!$J$2:$J$60,0,$B$23),MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$60&amp;info_index!$C$2:$C$60,0),1)&amp;"","")</f>
         <v>OrientalMotor</v>
       </c>
       <c r="P3" t="str" cm="1">
@@ -5308,7 +5372,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]info_index によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ref="E5:E68" si="0">E4</f>
@@ -6883,7 +6947,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AK$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]info_index によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸
@@ -7364,6 +7428,19 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
+	//箔ロウリール固定
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウリール固定';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder20】 箔ロウリール固定';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'MGPM12-20Z-M9BL';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'MISUMI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
 	ELSE
 		uiErrCode	:= 2;
 	END_IF;
@@ -11047,7 +11124,7 @@
         <v/>
       </c>
       <c r="H43">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I43" t="str">
         <f ca="1"/>
@@ -16823,90 +16900,185 @@
       <c r="G82" t="str">
         <v/>
       </c>
-      <c r="H82" t="str">
-        <v/>
+      <c r="H82">
+        <v>36</v>
       </c>
       <c r="I82" t="str">
         <f ca="1"/>
-        <v/>
+        <v>箔ロウリール固定</v>
       </c>
       <c r="J82" t="str">
         <f ca="1"/>
-        <v/>
+        <v>箔ロウリール固定</v>
       </c>
       <c r="L82" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【cylinder20】 箔ロウリール固定</v>
       </c>
       <c r="M82" t="str">
-        <v/>
+        <v>MGPM12-20Z-M9BL</v>
       </c>
       <c r="N82" t="str">
-        <v/>
+        <v>MGPM12-20Z-M9BL</v>
       </c>
       <c r="O82" t="str">
         <f ca="1"/>
-        <v/>
+        <v>MISUMI</v>
       </c>
       <c r="P82" t="str">
         <f ca="1"/>
-        <v/>
+        <v>MISUMI</v>
       </c>
       <c r="X82" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Y82" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Z82" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウリール固定
+	ELSIF uiInfoIdx = 20 THEN</v>
       </c>
       <c r="AA82" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウリール固定
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB82" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウリール固定
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウリール固定';</v>
       </c>
       <c r="AC82" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウリール固定
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウリール固定';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD82" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウリール固定
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウリール固定';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder20】 箔ロウリール固定';</v>
       </c>
       <c r="AE82" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウリール固定
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウリール固定';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder20】 箔ロウリール固定';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF82" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウリール固定
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウリール固定';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder20】 箔ロウリール固定';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'MGPM12-20Z-M9BL';</v>
       </c>
       <c r="AG82" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウリール固定
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウリール固定';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder20】 箔ロウリール固定';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'MGPM12-20Z-M9BL';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH82" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウリール固定
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウリール固定';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder20】 箔ロウリール固定';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'MGPM12-20Z-M9BL';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'MISUMI';</v>
       </c>
       <c r="AI82" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウリール固定
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウリール固定';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder20】 箔ロウリール固定';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'MGPM12-20Z-M9BL';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'MISUMI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AJ82" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウリール固定
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウリール固定';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder20】 箔ロウリール固定';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'MGPM12-20Z-M9BL';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'MISUMI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AK82" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//箔ロウリール固定
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウリール固定';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder20】 箔ロウリール固定';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'MGPM12-20Z-M9BL';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'MISUMI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="83" spans="5:37" x14ac:dyDescent="0.55000000000000004">
@@ -17221,7 +17393,7 @@
         <v/>
       </c>
       <c r="H86">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I86" t="str">
         <f ca="1"/>
@@ -17934,7 +18106,7 @@
         <v/>
       </c>
       <c r="H92">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I92" t="str">
         <f ca="1"/>
@@ -18152,7 +18324,7 @@
         <v/>
       </c>
       <c r="H93">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I93" t="str">
         <f ca="1"/>
@@ -18345,7 +18517,7 @@
         <v/>
       </c>
       <c r="H94">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I94" t="str">
         <f ca="1"/>
@@ -18538,7 +18710,7 @@
         <v/>
       </c>
       <c r="H95">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I95" t="str">
         <f ca="1"/>
@@ -18731,7 +18903,7 @@
         <v/>
       </c>
       <c r="H96">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I96" t="str">
         <f ca="1"/>
@@ -18924,7 +19096,7 @@
         <v/>
       </c>
       <c r="H97">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I97" t="str">
         <f ca="1"/>
@@ -29403,7 +29575,7 @@
     <row r="205" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="AK205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AK$3:AK$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]info_index によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸
@@ -29884,6 +30056,19 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
+	//箔ロウリール固定
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '箔ロウリール固定';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder20】 箔ロウリール固定';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'MGPM12-20Z-M9BL';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'MISUMI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
 	ELSE
 		uiErrCode	:= 2;
 	END_IF;
@@ -29997,7 +30182,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB28470-3E18-484C-8FB2-CDE4B94CD573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6895B56-CE5A-4B49-9B23-BBAB2232FAA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script</v>
+        <v>C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]warning</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]warning によって生成されました。</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ref="E5:E68" si="0">E4</f>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AK$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]warning によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸
@@ -29575,7 +29575,7 @@
     <row r="205" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="AK205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AK$3:AK$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]warning によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸
@@ -30187,5 +30187,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82E0D91-B357-4B4C-AEBF-CCE5B4E56764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AA000C7-9B06-45FC-9E55-F6EC213211E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_exe_errno.xlsm]info_script</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_exe_errno.xlsm]info_script によって生成されました。</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ref="E5:E68" si="0">E4</f>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AK$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_exe_errno.xlsm]info_script によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//Foil wax reel shaft
@@ -30451,7 +30451,7 @@
     <row r="205" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="AK205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AK$3:AK$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_exe_errno.xlsm]info_script によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//Foil wax reel shaft

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AA000C7-9B06-45FC-9E55-F6EC213211E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6146265-6009-4E09-92AC-61447823CBA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="297">
   <si>
     <t>RCA2-GS3NA-I-10-2-50-A6-M-K1</t>
   </si>
@@ -1558,6 +1558,37 @@
   <si>
     <t>X-roll electromagnetic clutch</t>
   </si>
+  <si>
+    <t>OTHC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tロール糊付け軸</t>
+    <rPh sb="4" eb="6">
+      <t>ノリヅ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>T-roll gluing shaft</t>
+  </si>
+  <si>
+    <t>OTHC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(未割付け)</t>
+    <rPh sb="1" eb="4">
+      <t>ミワリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(Unassigned)</t>
+  </si>
 </sst>
 </file>
 
@@ -2030,7 +2061,7 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$A$65">
+    <xdr:sp macro="" textlink="$A$68">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="正方形/長方形 1">
           <a:extLst>
@@ -2090,7 +2121,7 @@
               <a:ea typeface="游ゴシック"/>
             </a:rPr>
             <a:pPr algn="l"/>
-            <a:t>61</a:t>
+            <a:t>64</a:t>
           </a:fld>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="600"/>
         </a:p>
@@ -2399,7 +2430,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R89"/>
+  <dimension ref="A1:R92"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -5098,128 +5129,208 @@
       <c r="R61" s="10"/>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="18"/>
-      <c r="B62" s="18"/>
-      <c r="C62" s="18"/>
-      <c r="D62" s="19"/>
-      <c r="E62" s="19"/>
-      <c r="F62" s="19"/>
-      <c r="G62" s="19"/>
-      <c r="H62" s="19"/>
-      <c r="I62" s="19"/>
-      <c r="J62" s="19"/>
-      <c r="K62" s="19"/>
-      <c r="L62" s="19"/>
-      <c r="M62" s="20"/>
-      <c r="N62" s="20"/>
-      <c r="O62" s="20"/>
-      <c r="P62" s="37"/>
-      <c r="Q62" s="37"/>
-      <c r="R62" s="20"/>
+      <c r="A62" s="7">
+        <v>62</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="C62" s="7">
+        <v>1</v>
+      </c>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="H62" s="8"/>
+      <c r="I62" s="8"/>
+      <c r="J62" s="8"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="8"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="10"/>
+      <c r="O62" s="10"/>
+      <c r="P62" s="34">
+        <v>46083.387499999997</v>
+      </c>
+      <c r="Q62" s="34">
+        <v>46083.387499999997</v>
+      </c>
+      <c r="R62" s="10"/>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="7">
+        <v>63</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="C63" s="7">
+        <v>2</v>
+      </c>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="H63" s="8"/>
+      <c r="I63" s="8"/>
+      <c r="J63" s="8"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="8"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="10"/>
+      <c r="O63" s="10"/>
+      <c r="P63" s="34">
+        <v>46083.387499999997</v>
+      </c>
+      <c r="Q63" s="34">
+        <v>46083.387499999997</v>
+      </c>
+      <c r="R63" s="10"/>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" t="s">
-        <v>111</v>
-      </c>
-      <c r="D64" t="s">
-        <v>110</v>
-      </c>
+      <c r="A64" s="7">
+        <v>64</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="C64" s="7">
+        <v>3</v>
+      </c>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="H64" s="8"/>
+      <c r="I64" s="8"/>
+      <c r="J64" s="8"/>
+      <c r="K64" s="8"/>
+      <c r="L64" s="8"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="10"/>
+      <c r="O64" s="10"/>
+      <c r="P64" s="34">
+        <v>46083.363888888889</v>
+      </c>
+      <c r="Q64" s="34">
+        <v>46083.363888888889</v>
+      </c>
+      <c r="R64" s="10"/>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65">
-        <f>MAX(A$2:A$62)</f>
-        <v>61</v>
-      </c>
-      <c r="D65">
-        <f>MAX(D$2:D$62)</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" t="s">
-        <v>199</v>
-      </c>
-      <c r="B66" t="s">
-        <v>117</v>
-      </c>
-      <c r="C66" t="s">
-        <v>116</v>
-      </c>
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="19"/>
+      <c r="K65" s="19"/>
+      <c r="L65" s="19"/>
+      <c r="M65" s="20"/>
+      <c r="N65" s="20"/>
+      <c r="O65" s="20"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="37"/>
+      <c r="R65" s="20"/>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67">
-        <f>ROW(A63)-ROW(A1)-1</f>
-        <v>61</v>
-      </c>
-      <c r="B67">
-        <f>COUNTIF(B$2:B$62,B66)</f>
-        <v>17</v>
-      </c>
-      <c r="C67" s="25">
-        <f>_xlfn.MAXIFS(C$2:C$62,$B$2:$B$62,C66)</f>
-        <v>17</v>
+      <c r="A67" t="s">
+        <v>111</v>
+      </c>
+      <c r="D67" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" t="s">
-        <v>114</v>
-      </c>
-      <c r="C68" t="s">
-        <v>114</v>
+      <c r="A68">
+        <f>MAX(A$2:A$65)</f>
+        <v>64</v>
+      </c>
+      <c r="D68">
+        <f>MAX(D$2:D$65)</f>
+        <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69">
-        <f>COUNTIF(B$2:B$62,B68)</f>
-        <v>23</v>
-      </c>
-      <c r="C69" s="25">
-        <f>_xlfn.MAXIFS(C$2:C$62,$B$2:$B$62,C68)</f>
-        <v>20</v>
+      <c r="A69" t="s">
+        <v>199</v>
+      </c>
+      <c r="B69" t="s">
+        <v>117</v>
+      </c>
+      <c r="C69" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70">
+        <f>ROW(A66)-ROW(A1)-1</f>
+        <v>64</v>
+      </c>
+      <c r="B70">
+        <f>COUNTIF(B$2:B$65,B69)</f>
+        <v>17</v>
+      </c>
+      <c r="C70" s="25">
+        <f>_xlfn.MAXIFS(C$2:C$65,$B$2:$B$65,C69)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B71" t="s">
+        <v>114</v>
+      </c>
+      <c r="C71" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H72" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L72">
-        <v>1</v>
-      </c>
-      <c r="R72" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H73" t="s">
-        <v>56</v>
-      </c>
-      <c r="I73" t="s">
-        <v>53</v>
-      </c>
-      <c r="J73" t="s">
-        <v>52</v>
-      </c>
-      <c r="L73">
-        <v>1</v>
-      </c>
-      <c r="R73" t="s">
-        <v>79</v>
+      <c r="B72">
+        <f>COUNTIF(B$2:B$65,B71)</f>
+        <v>23</v>
+      </c>
+      <c r="C72" s="25">
+        <f>_xlfn.MAXIFS(C$2:C$65,$B$2:$B$65,C71)</f>
+        <v>20</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="H75" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
+      </c>
+      <c r="L75">
+        <v>1</v>
+      </c>
+      <c r="R75" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="H76" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="I76" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="J76" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="L76">
         <v>1</v>
@@ -5230,18 +5341,18 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="H78" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="H79" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I79" t="s">
         <v>84</v>
       </c>
       <c r="J79" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L79">
         <v>1</v>
@@ -5252,113 +5363,135 @@
     </row>
     <row r="81" spans="8:18" x14ac:dyDescent="0.55000000000000004">
       <c r="H81" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="82" spans="8:18" x14ac:dyDescent="0.55000000000000004">
       <c r="H82" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="I82" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="J82" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="L82">
         <v>1</v>
       </c>
       <c r="R82" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="83" spans="8:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H83" t="s">
-        <v>45</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J83" t="s">
-        <v>44</v>
-      </c>
-      <c r="L83">
-        <v>2</v>
-      </c>
-      <c r="R83" t="s">
-        <v>87</v>
+    <row r="84" spans="8:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="H84" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="85" spans="8:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H85" s="2" t="s">
-        <v>41</v>
+      <c r="H85" t="s">
+        <v>42</v>
+      </c>
+      <c r="I85" t="s">
+        <v>43</v>
+      </c>
+      <c r="J85" t="s">
+        <v>12</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="R85" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="86" spans="8:18" x14ac:dyDescent="0.55000000000000004">
       <c r="H86" t="s">
-        <v>46</v>
-      </c>
-      <c r="I86" t="s">
-        <v>47</v>
+        <v>45</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="J86" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="L86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R86" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="87" spans="8:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H87" t="s">
-        <v>50</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J87" t="s">
-        <v>49</v>
-      </c>
-      <c r="L87">
-        <v>1</v>
-      </c>
-      <c r="R87" t="s">
-        <v>87</v>
-      </c>
-    </row>
     <row r="88" spans="8:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H88" t="s">
-        <v>51</v>
-      </c>
-      <c r="I88" t="s">
-        <v>55</v>
-      </c>
-      <c r="J88" t="s">
-        <v>4</v>
-      </c>
-      <c r="L88">
-        <v>2</v>
-      </c>
-      <c r="R88" t="s">
-        <v>87</v>
+      <c r="H88" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="89" spans="8:18" x14ac:dyDescent="0.55000000000000004">
       <c r="H89" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="I89" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="J89" t="s">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="L89">
         <v>1</v>
       </c>
       <c r="R89" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="90" spans="8:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="H90" t="s">
+        <v>50</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J90" t="s">
+        <v>49</v>
+      </c>
+      <c r="L90">
+        <v>1</v>
+      </c>
+      <c r="R90" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="91" spans="8:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="H91" t="s">
+        <v>51</v>
+      </c>
+      <c r="I91" t="s">
+        <v>55</v>
+      </c>
+      <c r="J91" t="s">
+        <v>4</v>
+      </c>
+      <c r="L91">
+        <v>2</v>
+      </c>
+      <c r="R91" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="92" spans="8:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="H92" t="s">
+        <v>85</v>
+      </c>
+      <c r="I92" t="s">
+        <v>86</v>
+      </c>
+      <c r="J92" t="s">
+        <v>88</v>
+      </c>
+      <c r="L92">
+        <v>1</v>
+      </c>
+      <c r="R92" t="s">
         <v>87</v>
       </c>
     </row>
@@ -5369,7 +5502,7 @@
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A2:R17 A18:G18 I18:R18 A19:R62">
+  <conditionalFormatting sqref="A2:R17 A18:G18 I18:R18 A19:R65">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>MOD(ROW(A2),2)=1</formula>
     </cfRule>
@@ -5520,7 +5653,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_exe_errno.xlsm]info_script</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
@@ -5530,11 +5663,11 @@
         <v>1</v>
       </c>
       <c r="H3" cm="1">
-        <f t="array" ref="H3:H202">IFERROR(MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$62&amp;info_index!$C$2:$C$62,0),"")</f>
+        <f t="array" ref="H3:H202">IFERROR(MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$65&amp;info_index!$C$2:$C$65,0),"")</f>
         <v>1</v>
       </c>
       <c r="I3" t="str" cm="1">
-        <f t="array" aca="1" ref="I3:I202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(H3)),INDEX(OFFSET(info_index!$F$2:$F$62,0,$B$23),MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$62&amp;info_index!$C$2:$C$62,0)&amp;"",1),"")</f>
+        <f t="array" aca="1" ref="I3:I202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(H3)),INDEX(OFFSET(info_index!$F$2:$F$65,0,$B$23),MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$65&amp;info_index!$C$2:$C$65,0)&amp;"",1),"")</f>
         <v>Foil wax reel shaft</v>
       </c>
       <c r="J3" t="str" cm="1">
@@ -5546,7 +5679,7 @@
         <v>【axis1】 Foil wax reel shaft</v>
       </c>
       <c r="M3" t="str" cm="1">
-        <f t="array" ref="M3:M202">IFERROR(INDEX(info_index!$H$2:$H$62,MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$62&amp;info_index!$C$2:$C$62,0),1)&amp;"","")</f>
+        <f t="array" ref="M3:M202">IFERROR(INDEX(info_index!$H$2:$H$65,MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$65&amp;info_index!$C$2:$C$65,0),1)&amp;"","")</f>
         <v>5TK20GN-CW2J+5GN180K</v>
       </c>
       <c r="N3" t="str" cm="1">
@@ -5554,7 +5687,7 @@
         <v>5TK20GN-CW2J+5GN180K</v>
       </c>
       <c r="O3" t="str" cm="1">
-        <f t="array" aca="1" ref="O3:O202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(H3)),INDEX(OFFSET(info_index!$J$2:$J$62,0,$B$23),MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$62&amp;info_index!$C$2:$C$62,0),1)&amp;"","")</f>
+        <f t="array" aca="1" ref="O3:O202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(H3)),INDEX(OFFSET(info_index!$J$2:$J$65,0,$B$23),MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$65&amp;info_index!$C$2:$C$65,0),1)&amp;"","")</f>
         <v>OrientalMotor</v>
       </c>
       <c r="P3" t="str" cm="1">
@@ -5924,7 +6057,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_exe_errno.xlsm]info_script によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content によって生成されました。</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ref="E5:E68" si="0">E4</f>
@@ -7499,7 +7632,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AK$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_exe_errno.xlsm]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//Foil wax reel shaft
@@ -8040,6 +8173,50 @@
 	ELSE
 		uiErrCode	:= 2;
 	END_IF;
+//OTHC
+ELSIF strInfoType = 'OTHC' THEN
+	//(Unassigned)
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '(Unassigned)';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC1】 (Unassigned)';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//(Unassigned)
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '(Unassigned)';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC2】 (Unassigned)';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//T-roll gluing shaft
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'T-roll gluing shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC3】 T-roll gluing shaft';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	ELSE
+		uiErrCode	:= 2;
+	END_IF;
 //unit
 ELSIF strInfoType = 'unit' THEN
 	//Flat Sheet Supply
@@ -18781,93 +18958,485 @@
         <v>6</v>
       </c>
       <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+      <c r="I91" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="J91" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="L91" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="M91" t="str">
+        <v/>
+      </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="P91" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="X91" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Y91" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Z91" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AA91" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AB91" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AC91" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AD91" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AE91" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AF91" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AG91" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AH91" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AI91" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AJ91" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AK91" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="5:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="E92" t="str">
+        <f t="shared" si="1"/>
+        <v>OTH</v>
+      </c>
+      <c r="F92">
+        <f>COUNTIF(E$3:E92,E92)</f>
+        <v>7</v>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+      <c r="I92" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="J92" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="L92" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="M92" t="str">
+        <v/>
+      </c>
+      <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="P92" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="X92" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Y92" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Z92" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AA92" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AB92" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AC92" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AD92" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AE92" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AF92" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AG92" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AH92" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AI92" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AJ92" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AK92" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="5:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="E93" t="str">
+        <f t="shared" si="1"/>
+        <v>OTH</v>
+      </c>
+      <c r="F93">
+        <f>COUNTIF(E$3:E93,E93)</f>
+        <v>8</v>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v/>
+      </c>
+      <c r="I93" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="J93" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="L93" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="M93" t="str">
+        <v/>
+      </c>
+      <c r="N93" t="str">
+        <v/>
+      </c>
+      <c r="O93" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="P93" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="X93" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Y93" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Z93" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AA93" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AB93" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AC93" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AD93" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AE93" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AF93" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AG93" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AH93" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AI93" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AJ93" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AK93" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="5:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="E94" t="str">
+        <f t="shared" si="1"/>
+        <v>OTH</v>
+      </c>
+      <c r="F94">
+        <f>COUNTIF(E$3:E94,E94)</f>
+        <v>9</v>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+      <c r="I94" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="J94" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="L94" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="M94" t="str">
+        <v/>
+      </c>
+      <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="P94" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="X94" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Y94" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Z94" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AA94" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AB94" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AC94" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AD94" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AE94" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AF94" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AG94" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AH94" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AI94" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AJ94" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AK94" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="5:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="E95" t="str">
+        <f t="shared" si="1"/>
+        <v>OTH</v>
+      </c>
+      <c r="F95">
+        <f>COUNTIF(E$3:E95,E95)</f>
+        <v>10</v>
+      </c>
+      <c r="G95" t="str">
         <v>●</v>
       </c>
-      <c r="H91" t="str">
-        <v/>
-      </c>
-      <c r="I91" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="J91" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="L91" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="M91" t="str">
-        <v/>
-      </c>
-      <c r="N91" t="str">
-        <v/>
-      </c>
-      <c r="O91" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="P91" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="X91" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Y91" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Z91" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AA91" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AB91" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AC91" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AD91" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AE91" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AF91" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AG91" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AH91" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AI91" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AJ91" t="str">
+      <c r="H95" t="str">
+        <v/>
+      </c>
+      <c r="I95" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="J95" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="L95" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="M95" t="str">
+        <v/>
+      </c>
+      <c r="N95" t="str">
+        <v/>
+      </c>
+      <c r="O95" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="P95" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="X95" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Y95" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Z95" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AA95" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AB95" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AC95" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AD95" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AE95" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AF95" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AG95" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AH95" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AI95" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AJ95" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 	ELSE
 		uiErrCode	:= 2;
 	END_IF;</v>
       </c>
-      <c r="AK91" t="str">
+      <c r="AK95" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 	ELSE
@@ -18875,176 +19444,176 @@
 	END_IF;</v>
       </c>
     </row>
-    <row r="92" spans="5:37" x14ac:dyDescent="0.55000000000000004">
-      <c r="E92" t="s">
-        <v>261</v>
-      </c>
-      <c r="F92">
-        <f>COUNTIF(E$3:E92,E92)</f>
+    <row r="96" spans="5:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="E96" t="s">
+        <v>294</v>
+      </c>
+      <c r="F96">
+        <f>COUNTIF(E$3:E96,E96)</f>
         <v>1</v>
       </c>
-      <c r="G92" t="str">
-        <v/>
-      </c>
-      <c r="H92">
-        <v>52</v>
-      </c>
-      <c r="I92" t="str">
-        <f ca="1"/>
-        <v>Flat Sheet Supply</v>
-      </c>
-      <c r="J92" t="str">
-        <f ca="1"/>
-        <v>Flat Sheet Supply</v>
-      </c>
-      <c r="L92" t="str">
-        <f ca="1"/>
-        <v>【unit1】 Flat Sheet Supply</v>
-      </c>
-      <c r="M92" t="str">
-        <v/>
-      </c>
-      <c r="N92" t="str">
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96">
+        <v>61</v>
+      </c>
+      <c r="I96" t="str">
+        <f ca="1"/>
+        <v>(Unassigned)</v>
+      </c>
+      <c r="J96" t="str">
+        <f ca="1"/>
+        <v>(Unassigned)</v>
+      </c>
+      <c r="L96" t="str">
+        <f ca="1"/>
+        <v>【OTHC1】 (Unassigned)</v>
+      </c>
+      <c r="M96" t="str">
+        <v/>
+      </c>
+      <c r="N96" t="str">
         <v>unknown</v>
       </c>
-      <c r="O92" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="P92" t="str">
+      <c r="O96" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="P96" t="str">
         <f ca="1"/>
         <v>unknown</v>
       </c>
-      <c r="X92" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-//unit</v>
-      </c>
-      <c r="Y92" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-//unit
-ELSIF strInfoType = 'unit' THEN</v>
-      </c>
-      <c r="Z92" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-//unit
-ELSIF strInfoType = 'unit' THEN
-	//Flat Sheet Supply
+      <c r="X96" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//OTHC</v>
+      </c>
+      <c r="Y96" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//OTHC
+ELSIF strInfoType = 'OTHC' THEN</v>
+      </c>
+      <c r="Z96" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//OTHC
+ELSIF strInfoType = 'OTHC' THEN
+	//(Unassigned)
 	IF uiInfoIdx = 1 THEN</v>
       </c>
-      <c r="AA92" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-//unit
-ELSIF strInfoType = 'unit' THEN
-	//Flat Sheet Supply
+      <c r="AA96" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//OTHC
+ELSIF strInfoType = 'OTHC' THEN
+	//(Unassigned)
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
-      <c r="AB92" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-//unit
-ELSIF strInfoType = 'unit' THEN
-	//Flat Sheet Supply
+      <c r="AB96" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//OTHC
+ELSIF strInfoType = 'OTHC' THEN
+	//(Unassigned)
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat Sheet Supply';</v>
-      </c>
-      <c r="AC92" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-//unit
-ELSIF strInfoType = 'unit' THEN
-	//Flat Sheet Supply
+			strRt	:= '(Unassigned)';</v>
+      </c>
+      <c r="AC96" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//OTHC
+ELSIF strInfoType = 'OTHC' THEN
+	//(Unassigned)
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat Sheet Supply';
+			strRt	:= '(Unassigned)';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
-      <c r="AD92" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-//unit
-ELSIF strInfoType = 'unit' THEN
-	//Flat Sheet Supply
+      <c r="AD96" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//OTHC
+ELSIF strInfoType = 'OTHC' THEN
+	//(Unassigned)
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat Sheet Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit1】 Flat Sheet Supply';</v>
-      </c>
-      <c r="AE92" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-//unit
-ELSIF strInfoType = 'unit' THEN
-	//Flat Sheet Supply
+			strRt	:= '(Unassigned)';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC1】 (Unassigned)';</v>
+      </c>
+      <c r="AE96" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//OTHC
+ELSIF strInfoType = 'OTHC' THEN
+	//(Unassigned)
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat Sheet Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit1】 Flat Sheet Supply';
+			strRt	:= '(Unassigned)';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC1】 (Unassigned)';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
-      <c r="AF92" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-//unit
-ELSIF strInfoType = 'unit' THEN
-	//Flat Sheet Supply
+      <c r="AF96" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//OTHC
+ELSIF strInfoType = 'OTHC' THEN
+	//(Unassigned)
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat Sheet Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit1】 Flat Sheet Supply';
+			strRt	:= '(Unassigned)';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC1】 (Unassigned)';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
-      <c r="AG92" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-//unit
-ELSIF strInfoType = 'unit' THEN
-	//Flat Sheet Supply
+      <c r="AG96" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//OTHC
+ELSIF strInfoType = 'OTHC' THEN
+	//(Unassigned)
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat Sheet Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit1】 Flat Sheet Supply';
+			strRt	:= '(Unassigned)';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC1】 (Unassigned)';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
-      <c r="AH92" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-//unit
-ELSIF strInfoType = 'unit' THEN
-	//Flat Sheet Supply
+      <c r="AH96" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//OTHC
+ELSIF strInfoType = 'OTHC' THEN
+	//(Unassigned)
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat Sheet Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit1】 Flat Sheet Supply';
+			strRt	:= '(Unassigned)';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC1】 (Unassigned)';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
 			strRt	:= 'unknown';</v>
       </c>
-      <c r="AI92" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-//unit
-ELSIF strInfoType = 'unit' THEN
-	//Flat Sheet Supply
+      <c r="AI96" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//OTHC
+ELSIF strInfoType = 'OTHC' THEN
+	//(Unassigned)
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat Sheet Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit1】 Flat Sheet Supply';
+			strRt	:= '(Unassigned)';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC1】 (Unassigned)';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -19053,17 +19622,17 @@
 			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
-      <c r="AJ92" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-//unit
-ELSIF strInfoType = 'unit' THEN
-	//Flat Sheet Supply
+      <c r="AJ96" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//OTHC
+ELSIF strInfoType = 'OTHC' THEN
+	//(Unassigned)
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat Sheet Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit1】 Flat Sheet Supply';
+			strRt	:= '(Unassigned)';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC1】 (Unassigned)';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -19072,17 +19641,17 @@
 			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
-      <c r="AK92" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-//unit
-ELSIF strInfoType = 'unit' THEN
-	//Flat Sheet Supply
+      <c r="AK96" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//OTHC
+ELSIF strInfoType = 'OTHC' THEN
+	//(Unassigned)
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Flat Sheet Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit1】 Flat Sheet Supply';
+			strRt	:= '(Unassigned)';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC1】 (Unassigned)';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -19092,156 +19661,156 @@
 		END_IF;</v>
       </c>
     </row>
-    <row r="93" spans="5:37" x14ac:dyDescent="0.55000000000000004">
-      <c r="E93" t="str">
+    <row r="97" spans="5:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="E97" t="str">
         <f t="shared" si="1"/>
-        <v>unit</v>
-      </c>
-      <c r="F93">
-        <f>COUNTIF(E$3:E93,E93)</f>
+        <v>OTHC</v>
+      </c>
+      <c r="F97">
+        <f>COUNTIF(E$3:E97,E97)</f>
         <v>2</v>
       </c>
-      <c r="G93" t="str">
-        <v/>
-      </c>
-      <c r="H93">
-        <v>53</v>
-      </c>
-      <c r="I93" t="str">
-        <f ca="1"/>
-        <v>Corrugated Sheet Supply</v>
-      </c>
-      <c r="J93" t="str">
-        <f ca="1"/>
-        <v>Corrugated Sheet Supply</v>
-      </c>
-      <c r="L93" t="str">
-        <f ca="1"/>
-        <v>【unit2】 Corrugated Sheet Supply</v>
-      </c>
-      <c r="M93" t="str">
-        <v/>
-      </c>
-      <c r="N93" t="str">
+      <c r="G97" t="str">
+        <v/>
+      </c>
+      <c r="H97">
+        <v>62</v>
+      </c>
+      <c r="I97" t="str">
+        <f ca="1"/>
+        <v>(Unassigned)</v>
+      </c>
+      <c r="J97" t="str">
+        <f ca="1"/>
+        <v>(Unassigned)</v>
+      </c>
+      <c r="L97" t="str">
+        <f ca="1"/>
+        <v>【OTHC2】 (Unassigned)</v>
+      </c>
+      <c r="M97" t="str">
+        <v/>
+      </c>
+      <c r="N97" t="str">
         <v>unknown</v>
       </c>
-      <c r="O93" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="P93" t="str">
+      <c r="O97" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="P97" t="str">
         <f ca="1"/>
         <v>unknown</v>
       </c>
-      <c r="X93" t="str">
+      <c r="X97" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 </v>
       </c>
-      <c r="Y93" t="str">
+      <c r="Y97" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 </v>
       </c>
-      <c r="Z93" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Corrugated Sheet Supply
+      <c r="Z97" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//(Unassigned)
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
-      <c r="AA93" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Corrugated Sheet Supply
+      <c r="AA97" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//(Unassigned)
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
-      <c r="AB93" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Corrugated Sheet Supply
+      <c r="AB97" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//(Unassigned)
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated Sheet Supply';</v>
-      </c>
-      <c r="AC93" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Corrugated Sheet Supply
+			strRt	:= '(Unassigned)';</v>
+      </c>
+      <c r="AC97" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//(Unassigned)
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated Sheet Supply';
+			strRt	:= '(Unassigned)';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
-      <c r="AD93" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Corrugated Sheet Supply
+      <c r="AD97" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//(Unassigned)
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated Sheet Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit2】 Corrugated Sheet Supply';</v>
-      </c>
-      <c r="AE93" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Corrugated Sheet Supply
+			strRt	:= '(Unassigned)';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC2】 (Unassigned)';</v>
+      </c>
+      <c r="AE97" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//(Unassigned)
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated Sheet Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit2】 Corrugated Sheet Supply';
+			strRt	:= '(Unassigned)';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC2】 (Unassigned)';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
-      <c r="AF93" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Corrugated Sheet Supply
+      <c r="AF97" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//(Unassigned)
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated Sheet Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit2】 Corrugated Sheet Supply';
+			strRt	:= '(Unassigned)';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC2】 (Unassigned)';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
-      <c r="AG93" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Corrugated Sheet Supply
+      <c r="AG97" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//(Unassigned)
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated Sheet Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit2】 Corrugated Sheet Supply';
+			strRt	:= '(Unassigned)';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC2】 (Unassigned)';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
-      <c r="AH93" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Corrugated Sheet Supply
+      <c r="AH97" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//(Unassigned)
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated Sheet Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit2】 Corrugated Sheet Supply';
+			strRt	:= '(Unassigned)';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC2】 (Unassigned)';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
 			strRt	:= 'unknown';</v>
       </c>
-      <c r="AI93" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Corrugated Sheet Supply
+      <c r="AI97" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//(Unassigned)
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated Sheet Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit2】 Corrugated Sheet Supply';
+			strRt	:= '(Unassigned)';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC2】 (Unassigned)';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -19250,15 +19819,15 @@
 			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
-      <c r="AJ93" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Corrugated Sheet Supply
+      <c r="AJ97" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//(Unassigned)
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated Sheet Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit2】 Corrugated Sheet Supply';
+			strRt	:= '(Unassigned)';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC2】 (Unassigned)';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -19267,15 +19836,15 @@
 			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
-      <c r="AK93" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Corrugated Sheet Supply
+      <c r="AK97" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//(Unassigned)
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Corrugated Sheet Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit2】 Corrugated Sheet Supply';
+			strRt	:= '(Unassigned)';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC2】 (Unassigned)';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -19285,156 +19854,156 @@
 		END_IF;</v>
       </c>
     </row>
-    <row r="94" spans="5:37" x14ac:dyDescent="0.55000000000000004">
-      <c r="E94" t="str">
+    <row r="98" spans="5:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="E98" t="str">
         <f t="shared" si="1"/>
-        <v>unit</v>
-      </c>
-      <c r="F94">
-        <f>COUNTIF(E$3:E94,E94)</f>
+        <v>OTHC</v>
+      </c>
+      <c r="F98">
+        <f>COUNTIF(E$3:E98,E98)</f>
         <v>3</v>
       </c>
-      <c r="G94" t="str">
-        <v/>
-      </c>
-      <c r="H94">
-        <v>54</v>
-      </c>
-      <c r="I94" t="str">
-        <f ca="1"/>
-        <v>Foil Wax Supply</v>
-      </c>
-      <c r="J94" t="str">
-        <f ca="1"/>
-        <v>Foil Wax Supply</v>
-      </c>
-      <c r="L94" t="str">
-        <f ca="1"/>
-        <v>【unit3】 Foil Wax Supply</v>
-      </c>
-      <c r="M94" t="str">
-        <v/>
-      </c>
-      <c r="N94" t="str">
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98">
+        <v>63</v>
+      </c>
+      <c r="I98" t="str">
+        <f ca="1"/>
+        <v>T-roll gluing shaft</v>
+      </c>
+      <c r="J98" t="str">
+        <f ca="1"/>
+        <v>T-roll gluing shaft</v>
+      </c>
+      <c r="L98" t="str">
+        <f ca="1"/>
+        <v>【OTHC3】 T-roll gluing shaft</v>
+      </c>
+      <c r="M98" t="str">
+        <v/>
+      </c>
+      <c r="N98" t="str">
         <v>unknown</v>
       </c>
-      <c r="O94" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="P94" t="str">
+      <c r="O98" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="P98" t="str">
         <f ca="1"/>
         <v>unknown</v>
       </c>
-      <c r="X94" t="str">
+      <c r="X98" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 </v>
       </c>
-      <c r="Y94" t="str">
+      <c r="Y98" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 </v>
       </c>
-      <c r="Z94" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Foil Wax Supply
+      <c r="Z98" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//T-roll gluing shaft
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
-      <c r="AA94" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Foil Wax Supply
+      <c r="AA98" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//T-roll gluing shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
-      <c r="AB94" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Foil Wax Supply
+      <c r="AB98" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//T-roll gluing shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil Wax Supply';</v>
-      </c>
-      <c r="AC94" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Foil Wax Supply
+			strRt	:= 'T-roll gluing shaft';</v>
+      </c>
+      <c r="AC98" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//T-roll gluing shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil Wax Supply';
+			strRt	:= 'T-roll gluing shaft';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
-      <c r="AD94" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Foil Wax Supply
+      <c r="AD98" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//T-roll gluing shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil Wax Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit3】 Foil Wax Supply';</v>
-      </c>
-      <c r="AE94" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Foil Wax Supply
+			strRt	:= 'T-roll gluing shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC3】 T-roll gluing shaft';</v>
+      </c>
+      <c r="AE98" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//T-roll gluing shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil Wax Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit3】 Foil Wax Supply';
+			strRt	:= 'T-roll gluing shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC3】 T-roll gluing shaft';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
-      <c r="AF94" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Foil Wax Supply
+      <c r="AF98" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//T-roll gluing shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil Wax Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit3】 Foil Wax Supply';
+			strRt	:= 'T-roll gluing shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC3】 T-roll gluing shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
-      <c r="AG94" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Foil Wax Supply
+      <c r="AG98" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//T-roll gluing shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil Wax Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit3】 Foil Wax Supply';
+			strRt	:= 'T-roll gluing shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC3】 T-roll gluing shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
-      <c r="AH94" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Foil Wax Supply
+      <c r="AH98" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//T-roll gluing shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil Wax Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit3】 Foil Wax Supply';
+			strRt	:= 'T-roll gluing shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC3】 T-roll gluing shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
 			strRt	:= 'unknown';</v>
       </c>
-      <c r="AI94" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Foil Wax Supply
+      <c r="AI98" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//T-roll gluing shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil Wax Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit3】 Foil Wax Supply';
+			strRt	:= 'T-roll gluing shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC3】 T-roll gluing shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -19443,15 +20012,15 @@
 			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
-      <c r="AJ94" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Foil Wax Supply
+      <c r="AJ98" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//T-roll gluing shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil Wax Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit3】 Foil Wax Supply';
+			strRt	:= 'T-roll gluing shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC3】 T-roll gluing shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -19460,15 +20029,15 @@
 			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
-      <c r="AK94" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Foil Wax Supply
+      <c r="AK98" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//T-roll gluing shaft
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil Wax Supply';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit3】 Foil Wax Supply';
+			strRt	:= 'T-roll gluing shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC3】 T-roll gluing shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -19478,156 +20047,868 @@
 		END_IF;</v>
       </c>
     </row>
-    <row r="95" spans="5:37" x14ac:dyDescent="0.55000000000000004">
-      <c r="E95" t="str">
+    <row r="99" spans="5:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="E99" t="str">
         <f t="shared" si="1"/>
-        <v>unit</v>
-      </c>
-      <c r="F95">
-        <f>COUNTIF(E$3:E95,E95)</f>
+        <v>OTHC</v>
+      </c>
+      <c r="F99">
+        <f>COUNTIF(E$3:E99,E99)</f>
         <v>4</v>
       </c>
-      <c r="G95" t="str">
-        <v/>
-      </c>
-      <c r="H95">
-        <v>55</v>
-      </c>
-      <c r="I95" t="str">
-        <f ca="1"/>
-        <v>Winding Shaft</v>
-      </c>
-      <c r="J95" t="str">
-        <f ca="1"/>
-        <v>Winding Shaft</v>
-      </c>
-      <c r="L95" t="str">
-        <f ca="1"/>
-        <v>【unit4】 Winding Shaft</v>
-      </c>
-      <c r="M95" t="str">
-        <v/>
-      </c>
-      <c r="N95" t="str">
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
+        <v/>
+      </c>
+      <c r="I99" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="J99" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="L99" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="M99" t="str">
+        <v/>
+      </c>
+      <c r="N99" t="str">
+        <v/>
+      </c>
+      <c r="O99" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="P99" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="X99" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Y99" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Z99" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AA99" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AB99" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AC99" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AD99" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AE99" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AF99" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AG99" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AH99" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AI99" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AJ99" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AK99" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="5:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="E100" t="str">
+        <f t="shared" si="1"/>
+        <v>OTHC</v>
+      </c>
+      <c r="F100">
+        <f>COUNTIF(E$3:E100,E100)</f>
+        <v>5</v>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
+        <v/>
+      </c>
+      <c r="I100" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="J100" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="L100" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="M100" t="str">
+        <v/>
+      </c>
+      <c r="N100" t="str">
+        <v/>
+      </c>
+      <c r="O100" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="P100" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="X100" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Y100" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Z100" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AA100" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AB100" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AC100" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AD100" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AE100" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AF100" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AG100" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AH100" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AI100" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AJ100" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AK100" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="5:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="E101" t="str">
+        <f t="shared" si="1"/>
+        <v>OTHC</v>
+      </c>
+      <c r="F101">
+        <f>COUNTIF(E$3:E101,E101)</f>
+        <v>6</v>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+      <c r="H101" t="str">
+        <v/>
+      </c>
+      <c r="I101" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="J101" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="L101" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="M101" t="str">
+        <v/>
+      </c>
+      <c r="N101" t="str">
+        <v/>
+      </c>
+      <c r="O101" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="P101" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="X101" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Y101" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Z101" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AA101" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AB101" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AC101" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AD101" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AE101" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AF101" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AG101" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AH101" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AI101" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AJ101" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AK101" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="5:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="E102" t="str">
+        <f t="shared" si="1"/>
+        <v>OTHC</v>
+      </c>
+      <c r="F102">
+        <f>COUNTIF(E$3:E102,E102)</f>
+        <v>7</v>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="J102" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="L102" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="M102" t="str">
+        <v/>
+      </c>
+      <c r="N102" t="str">
+        <v/>
+      </c>
+      <c r="O102" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="P102" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="X102" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Y102" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Z102" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AA102" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AB102" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AC102" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AD102" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AE102" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AF102" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AG102" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AH102" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AI102" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AJ102" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AK102" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="103" spans="5:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="E103" t="str">
+        <f t="shared" si="1"/>
+        <v>OTHC</v>
+      </c>
+      <c r="F103">
+        <f>COUNTIF(E$3:E103,E103)</f>
+        <v>8</v>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+      <c r="I103" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="J103" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="L103" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="M103" t="str">
+        <v/>
+      </c>
+      <c r="N103" t="str">
+        <v/>
+      </c>
+      <c r="O103" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="P103" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="X103" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Y103" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Z103" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AA103" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AB103" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AC103" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AD103" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AE103" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AF103" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AG103" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AH103" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AI103" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AJ103" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AK103" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="5:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="E104" t="str">
+        <f t="shared" si="1"/>
+        <v>OTHC</v>
+      </c>
+      <c r="F104">
+        <f>COUNTIF(E$3:E104,E104)</f>
+        <v>9</v>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+      <c r="I104" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="J104" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="L104" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="M104" t="str">
+        <v/>
+      </c>
+      <c r="N104" t="str">
+        <v/>
+      </c>
+      <c r="O104" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="P104" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="X104" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Y104" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Z104" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AA104" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AB104" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AC104" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AD104" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AE104" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AF104" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AG104" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AH104" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AI104" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AJ104" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AK104" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="105" spans="5:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="E105" t="str">
+        <f t="shared" si="1"/>
+        <v>OTHC</v>
+      </c>
+      <c r="F105">
+        <f>COUNTIF(E$3:E105,E105)</f>
+        <v>10</v>
+      </c>
+      <c r="G105" t="str">
+        <v>●</v>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+      <c r="I105" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="J105" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="L105" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="M105" t="str">
+        <v/>
+      </c>
+      <c r="N105" t="str">
+        <v/>
+      </c>
+      <c r="O105" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="P105" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="X105" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Y105" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Z105" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AA105" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AB105" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AC105" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AD105" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AE105" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AF105" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AG105" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AH105" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AI105" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AJ105" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	ELSE
+		uiErrCode	:= 2;
+	END_IF;</v>
+      </c>
+      <c r="AK105" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	ELSE
+		uiErrCode	:= 2;
+	END_IF;</v>
+      </c>
+    </row>
+    <row r="106" spans="5:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="E106" t="s">
+        <v>261</v>
+      </c>
+      <c r="F106">
+        <f>COUNTIF(E$3:E106,E106)</f>
+        <v>1</v>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106">
+        <v>52</v>
+      </c>
+      <c r="I106" t="str">
+        <f ca="1"/>
+        <v>Flat Sheet Supply</v>
+      </c>
+      <c r="J106" t="str">
+        <f ca="1"/>
+        <v>Flat Sheet Supply</v>
+      </c>
+      <c r="L106" t="str">
+        <f ca="1"/>
+        <v>【unit1】 Flat Sheet Supply</v>
+      </c>
+      <c r="M106" t="str">
+        <v/>
+      </c>
+      <c r="N106" t="str">
         <v>unknown</v>
       </c>
-      <c r="O95" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="P95" t="str">
+      <c r="O106" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="P106" t="str">
         <f ca="1"/>
         <v>unknown</v>
       </c>
-      <c r="X95" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-</v>
-      </c>
-      <c r="Y95" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-</v>
-      </c>
-      <c r="Z95" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Winding Shaft
-	ELSIF uiInfoIdx = 4 THEN</v>
-      </c>
-      <c r="AA95" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Winding Shaft
-	ELSIF uiInfoIdx = 4 THEN
+      <c r="X106" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//unit</v>
+      </c>
+      <c r="Y106" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN</v>
+      </c>
+      <c r="Z106" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//Flat Sheet Supply
+	IF uiInfoIdx = 1 THEN</v>
+      </c>
+      <c r="AA106" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//Flat Sheet Supply
+	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
-      <c r="AB95" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Winding Shaft
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding Shaft';</v>
-      </c>
-      <c r="AC95" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Winding Shaft
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding Shaft';
+      <c r="AB106" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//Flat Sheet Supply
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Flat Sheet Supply';</v>
+      </c>
+      <c r="AC106" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//Flat Sheet Supply
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Flat Sheet Supply';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
-      <c r="AD95" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Winding Shaft
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding Shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit4】 Winding Shaft';</v>
-      </c>
-      <c r="AE95" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Winding Shaft
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding Shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit4】 Winding Shaft';
+      <c r="AD106" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//Flat Sheet Supply
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Flat Sheet Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit1】 Flat Sheet Supply';</v>
+      </c>
+      <c r="AE106" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//Flat Sheet Supply
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Flat Sheet Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit1】 Flat Sheet Supply';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
-      <c r="AF95" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Winding Shaft
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding Shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit4】 Winding Shaft';
+      <c r="AF106" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//Flat Sheet Supply
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Flat Sheet Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit1】 Flat Sheet Supply';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
-      <c r="AG95" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Winding Shaft
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding Shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit4】 Winding Shaft';
+      <c r="AG106" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//Flat Sheet Supply
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Flat Sheet Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit1】 Flat Sheet Supply';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
-      <c r="AH95" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Winding Shaft
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding Shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit4】 Winding Shaft';
+      <c r="AH106" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//Flat Sheet Supply
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Flat Sheet Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit1】 Flat Sheet Supply';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
 			strRt	:= 'unknown';</v>
       </c>
-      <c r="AI95" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Winding Shaft
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding Shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit4】 Winding Shaft';
+      <c r="AI106" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//Flat Sheet Supply
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Flat Sheet Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit1】 Flat Sheet Supply';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -19636,15 +20917,17 @@
 			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
-      <c r="AJ95" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Winding Shaft
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding Shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit4】 Winding Shaft';
+      <c r="AJ106" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//Flat Sheet Supply
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Flat Sheet Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit1】 Flat Sheet Supply';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -19653,15 +20936,17 @@
 			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
-      <c r="AK95" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Winding Shaft
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding Shaft';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit4】 Winding Shaft';
+      <c r="AK106" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+//unit
+ELSIF strInfoType = 'unit' THEN
+	//Flat Sheet Supply
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Flat Sheet Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit1】 Flat Sheet Supply';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -19671,156 +20956,156 @@
 		END_IF;</v>
       </c>
     </row>
-    <row r="96" spans="5:37" x14ac:dyDescent="0.55000000000000004">
-      <c r="E96" t="str">
+    <row r="107" spans="5:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="E107" t="str">
         <f t="shared" si="1"/>
         <v>unit</v>
       </c>
-      <c r="F96">
-        <f>COUNTIF(E$3:E96,E96)</f>
-        <v>5</v>
-      </c>
-      <c r="G96" t="str">
-        <v/>
-      </c>
-      <c r="H96">
-        <v>56</v>
-      </c>
-      <c r="I96" t="str">
-        <f ca="1"/>
-        <v>Welding</v>
-      </c>
-      <c r="J96" t="str">
-        <f ca="1"/>
-        <v>Welding</v>
-      </c>
-      <c r="L96" t="str">
-        <f ca="1"/>
-        <v>【unit5】 Welding</v>
-      </c>
-      <c r="M96" t="str">
-        <v/>
-      </c>
-      <c r="N96" t="str">
+      <c r="F107">
+        <f>COUNTIF(E$3:E107,E107)</f>
+        <v>2</v>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+      <c r="H107">
+        <v>53</v>
+      </c>
+      <c r="I107" t="str">
+        <f ca="1"/>
+        <v>Corrugated Sheet Supply</v>
+      </c>
+      <c r="J107" t="str">
+        <f ca="1"/>
+        <v>Corrugated Sheet Supply</v>
+      </c>
+      <c r="L107" t="str">
+        <f ca="1"/>
+        <v>【unit2】 Corrugated Sheet Supply</v>
+      </c>
+      <c r="M107" t="str">
+        <v/>
+      </c>
+      <c r="N107" t="str">
         <v>unknown</v>
       </c>
-      <c r="O96" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="P96" t="str">
+      <c r="O107" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="P107" t="str">
         <f ca="1"/>
         <v>unknown</v>
       </c>
-      <c r="X96" t="str">
+      <c r="X107" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 </v>
       </c>
-      <c r="Y96" t="str">
+      <c r="Y107" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 </v>
       </c>
-      <c r="Z96" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Welding
-	ELSIF uiInfoIdx = 5 THEN</v>
-      </c>
-      <c r="AA96" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Welding
-	ELSIF uiInfoIdx = 5 THEN
+      <c r="Z107" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Corrugated Sheet Supply
+	ELSIF uiInfoIdx = 2 THEN</v>
+      </c>
+      <c r="AA107" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Corrugated Sheet Supply
+	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
-      <c r="AB96" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Welding
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Welding';</v>
-      </c>
-      <c r="AC96" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Welding
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Welding';
+      <c r="AB107" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Corrugated Sheet Supply
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Corrugated Sheet Supply';</v>
+      </c>
+      <c r="AC107" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Corrugated Sheet Supply
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Corrugated Sheet Supply';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
-      <c r="AD96" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Welding
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Welding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit5】 Welding';</v>
-      </c>
-      <c r="AE96" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Welding
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Welding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit5】 Welding';
+      <c r="AD107" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Corrugated Sheet Supply
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Corrugated Sheet Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit2】 Corrugated Sheet Supply';</v>
+      </c>
+      <c r="AE107" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Corrugated Sheet Supply
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Corrugated Sheet Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit2】 Corrugated Sheet Supply';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
-      <c r="AF96" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Welding
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Welding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit5】 Welding';
+      <c r="AF107" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Corrugated Sheet Supply
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Corrugated Sheet Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit2】 Corrugated Sheet Supply';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
-      <c r="AG96" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Welding
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Welding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit5】 Welding';
+      <c r="AG107" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Corrugated Sheet Supply
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Corrugated Sheet Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit2】 Corrugated Sheet Supply';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
-      <c r="AH96" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Welding
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Welding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit5】 Welding';
+      <c r="AH107" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Corrugated Sheet Supply
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Corrugated Sheet Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit2】 Corrugated Sheet Supply';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
 			strRt	:= 'unknown';</v>
       </c>
-      <c r="AI96" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Welding
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Welding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit5】 Welding';
+      <c r="AI107" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Corrugated Sheet Supply
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Corrugated Sheet Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit2】 Corrugated Sheet Supply';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -19829,15 +21114,15 @@
 			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
-      <c r="AJ96" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Welding
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Welding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit5】 Welding';
+      <c r="AJ107" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Corrugated Sheet Supply
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Corrugated Sheet Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit2】 Corrugated Sheet Supply';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -19846,15 +21131,15 @@
 			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
-      <c r="AK96" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Welding
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Welding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit5】 Welding';
+      <c r="AK107" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Corrugated Sheet Supply
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Corrugated Sheet Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit2】 Corrugated Sheet Supply';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -19864,156 +21149,156 @@
 		END_IF;</v>
       </c>
     </row>
-    <row r="97" spans="5:37" x14ac:dyDescent="0.55000000000000004">
-      <c r="E97" t="str">
+    <row r="108" spans="5:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="E108" t="str">
         <f t="shared" si="1"/>
         <v>unit</v>
       </c>
-      <c r="F97">
-        <f>COUNTIF(E$3:E97,E97)</f>
-        <v>6</v>
-      </c>
-      <c r="G97" t="str">
-        <v/>
-      </c>
-      <c r="H97">
-        <v>57</v>
-      </c>
-      <c r="I97" t="str">
-        <f ca="1"/>
-        <v>Discharge</v>
-      </c>
-      <c r="J97" t="str">
-        <f ca="1"/>
-        <v>Discharge</v>
-      </c>
-      <c r="L97" t="str">
-        <f ca="1"/>
-        <v>【unit6】 Discharge</v>
-      </c>
-      <c r="M97" t="str">
-        <v/>
-      </c>
-      <c r="N97" t="str">
+      <c r="F108">
+        <f>COUNTIF(E$3:E108,E108)</f>
+        <v>3</v>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108">
+        <v>54</v>
+      </c>
+      <c r="I108" t="str">
+        <f ca="1"/>
+        <v>Foil Wax Supply</v>
+      </c>
+      <c r="J108" t="str">
+        <f ca="1"/>
+        <v>Foil Wax Supply</v>
+      </c>
+      <c r="L108" t="str">
+        <f ca="1"/>
+        <v>【unit3】 Foil Wax Supply</v>
+      </c>
+      <c r="M108" t="str">
+        <v/>
+      </c>
+      <c r="N108" t="str">
         <v>unknown</v>
       </c>
-      <c r="O97" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="P97" t="str">
+      <c r="O108" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="P108" t="str">
         <f ca="1"/>
         <v>unknown</v>
       </c>
-      <c r="X97" t="str">
+      <c r="X108" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 </v>
       </c>
-      <c r="Y97" t="str">
+      <c r="Y108" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 </v>
       </c>
-      <c r="Z97" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge
-	ELSIF uiInfoIdx = 6 THEN</v>
-      </c>
-      <c r="AA97" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge
-	ELSIF uiInfoIdx = 6 THEN
+      <c r="Z108" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Foil Wax Supply
+	ELSIF uiInfoIdx = 3 THEN</v>
+      </c>
+      <c r="AA108" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Foil Wax Supply
+	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
-      <c r="AB97" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge
-	ELSIF uiInfoIdx = 6 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge';</v>
-      </c>
-      <c r="AC97" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge
-	ELSIF uiInfoIdx = 6 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge';
+      <c r="AB108" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Foil Wax Supply
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Foil Wax Supply';</v>
+      </c>
+      <c r="AC108" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Foil Wax Supply
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Foil Wax Supply';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
-      <c r="AD97" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge
-	ELSIF uiInfoIdx = 6 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit6】 Discharge';</v>
-      </c>
-      <c r="AE97" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge
-	ELSIF uiInfoIdx = 6 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit6】 Discharge';
+      <c r="AD108" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Foil Wax Supply
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Foil Wax Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit3】 Foil Wax Supply';</v>
+      </c>
+      <c r="AE108" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Foil Wax Supply
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Foil Wax Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit3】 Foil Wax Supply';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
-      <c r="AF97" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge
-	ELSIF uiInfoIdx = 6 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit6】 Discharge';
+      <c r="AF108" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Foil Wax Supply
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Foil Wax Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit3】 Foil Wax Supply';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
-      <c r="AG97" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge
-	ELSIF uiInfoIdx = 6 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit6】 Discharge';
+      <c r="AG108" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Foil Wax Supply
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Foil Wax Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit3】 Foil Wax Supply';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
-      <c r="AH97" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge
-	ELSIF uiInfoIdx = 6 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit6】 Discharge';
+      <c r="AH108" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Foil Wax Supply
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Foil Wax Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit3】 Foil Wax Supply';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
 			strRt	:= 'unknown';</v>
       </c>
-      <c r="AI97" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge
-	ELSIF uiInfoIdx = 6 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit6】 Discharge';
+      <c r="AI108" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Foil Wax Supply
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Foil Wax Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit3】 Foil Wax Supply';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -20022,15 +21307,15 @@
 			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
-      <c r="AJ97" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge
-	ELSIF uiInfoIdx = 6 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit6】 Discharge';
+      <c r="AJ108" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Foil Wax Supply
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Foil Wax Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit3】 Foil Wax Supply';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -20039,15 +21324,15 @@
 			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
-      <c r="AK97" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge
-	ELSIF uiInfoIdx = 6 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit6】 Discharge';
+      <c r="AK108" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Foil Wax Supply
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Foil Wax Supply';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit3】 Foil Wax Supply';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -20057,156 +21342,156 @@
 		END_IF;</v>
       </c>
     </row>
-    <row r="98" spans="5:37" x14ac:dyDescent="0.55000000000000004">
-      <c r="E98" t="str">
+    <row r="109" spans="5:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="E109" t="str">
         <f t="shared" si="1"/>
         <v>unit</v>
       </c>
-      <c r="F98">
-        <f>COUNTIF(E$3:E98,E98)</f>
-        <v>7</v>
-      </c>
-      <c r="G98" t="str">
-        <v/>
-      </c>
-      <c r="H98">
-        <v>58</v>
-      </c>
-      <c r="I98" t="str">
-        <f ca="1"/>
-        <v>X-roll section</v>
-      </c>
-      <c r="J98" t="str">
-        <f ca="1"/>
-        <v>X-roll section</v>
-      </c>
-      <c r="L98" t="str">
-        <f ca="1"/>
-        <v>【unit7】 X-roll section</v>
-      </c>
-      <c r="M98" t="str">
-        <v/>
-      </c>
-      <c r="N98" t="str">
+      <c r="F109">
+        <f>COUNTIF(E$3:E109,E109)</f>
+        <v>4</v>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+      <c r="H109">
+        <v>55</v>
+      </c>
+      <c r="I109" t="str">
+        <f ca="1"/>
+        <v>Winding Shaft</v>
+      </c>
+      <c r="J109" t="str">
+        <f ca="1"/>
+        <v>Winding Shaft</v>
+      </c>
+      <c r="L109" t="str">
+        <f ca="1"/>
+        <v>【unit4】 Winding Shaft</v>
+      </c>
+      <c r="M109" t="str">
+        <v/>
+      </c>
+      <c r="N109" t="str">
         <v>unknown</v>
       </c>
-      <c r="O98" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="P98" t="str">
+      <c r="O109" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="P109" t="str">
         <f ca="1"/>
         <v>unknown</v>
       </c>
-      <c r="X98" t="str">
+      <c r="X109" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 </v>
       </c>
-      <c r="Y98" t="str">
+      <c r="Y109" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 </v>
       </c>
-      <c r="Z98" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//X-roll section
-	ELSIF uiInfoIdx = 7 THEN</v>
-      </c>
-      <c r="AA98" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//X-roll section
-	ELSIF uiInfoIdx = 7 THEN
+      <c r="Z109" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Winding Shaft
+	ELSIF uiInfoIdx = 4 THEN</v>
+      </c>
+      <c r="AA109" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Winding Shaft
+	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
-      <c r="AB98" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//X-roll section
-	ELSIF uiInfoIdx = 7 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll section';</v>
-      </c>
-      <c r="AC98" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//X-roll section
-	ELSIF uiInfoIdx = 7 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll section';
+      <c r="AB109" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Winding Shaft
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Winding Shaft';</v>
+      </c>
+      <c r="AC109" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Winding Shaft
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Winding Shaft';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
-      <c r="AD98" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//X-roll section
-	ELSIF uiInfoIdx = 7 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll section';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit7】 X-roll section';</v>
-      </c>
-      <c r="AE98" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//X-roll section
-	ELSIF uiInfoIdx = 7 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll section';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit7】 X-roll section';
+      <c r="AD109" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Winding Shaft
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Winding Shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit4】 Winding Shaft';</v>
+      </c>
+      <c r="AE109" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Winding Shaft
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Winding Shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit4】 Winding Shaft';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
-      <c r="AF98" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//X-roll section
-	ELSIF uiInfoIdx = 7 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll section';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit7】 X-roll section';
+      <c r="AF109" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Winding Shaft
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Winding Shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit4】 Winding Shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
-      <c r="AG98" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//X-roll section
-	ELSIF uiInfoIdx = 7 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll section';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit7】 X-roll section';
+      <c r="AG109" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Winding Shaft
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Winding Shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit4】 Winding Shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
-      <c r="AH98" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//X-roll section
-	ELSIF uiInfoIdx = 7 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll section';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit7】 X-roll section';
+      <c r="AH109" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Winding Shaft
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Winding Shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit4】 Winding Shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
 			strRt	:= 'unknown';</v>
       </c>
-      <c r="AI98" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//X-roll section
-	ELSIF uiInfoIdx = 7 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll section';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit7】 X-roll section';
+      <c r="AI109" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Winding Shaft
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Winding Shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit4】 Winding Shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -20215,15 +21500,15 @@
 			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
-      <c r="AJ98" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//X-roll section
-	ELSIF uiInfoIdx = 7 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll section';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit7】 X-roll section';
+      <c r="AJ109" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Winding Shaft
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Winding Shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit4】 Winding Shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -20232,15 +21517,15 @@
 			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
-      <c r="AK98" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//X-roll section
-	ELSIF uiInfoIdx = 7 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-roll section';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit7】 X-roll section';
+      <c r="AK109" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Winding Shaft
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Winding Shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit4】 Winding Shaft';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -20250,1084 +21535,6 @@
 		END_IF;</v>
       </c>
     </row>
-    <row r="99" spans="5:37" x14ac:dyDescent="0.55000000000000004">
-      <c r="E99" t="str">
-        <f t="shared" si="1"/>
-        <v>unit</v>
-      </c>
-      <c r="F99">
-        <f>COUNTIF(E$3:E99,E99)</f>
-        <v>8</v>
-      </c>
-      <c r="G99" t="str">
-        <v/>
-      </c>
-      <c r="H99" t="str">
-        <v/>
-      </c>
-      <c r="I99" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="J99" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="L99" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="M99" t="str">
-        <v/>
-      </c>
-      <c r="N99" t="str">
-        <v/>
-      </c>
-      <c r="O99" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="P99" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="X99" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Y99" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Z99" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AA99" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AB99" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AC99" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AD99" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AE99" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AF99" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AG99" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AH99" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AI99" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AJ99" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AK99" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="100" spans="5:37" x14ac:dyDescent="0.55000000000000004">
-      <c r="E100" t="str">
-        <f t="shared" si="1"/>
-        <v>unit</v>
-      </c>
-      <c r="F100">
-        <f>COUNTIF(E$3:E100,E100)</f>
-        <v>9</v>
-      </c>
-      <c r="G100" t="str">
-        <v/>
-      </c>
-      <c r="H100" t="str">
-        <v/>
-      </c>
-      <c r="I100" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="J100" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="L100" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="M100" t="str">
-        <v/>
-      </c>
-      <c r="N100" t="str">
-        <v/>
-      </c>
-      <c r="O100" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="P100" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="X100" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Y100" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Z100" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AA100" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AB100" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AC100" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AD100" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AE100" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AF100" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AG100" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AH100" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AI100" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AJ100" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AK100" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="101" spans="5:37" x14ac:dyDescent="0.55000000000000004">
-      <c r="E101" t="str">
-        <f t="shared" si="1"/>
-        <v>unit</v>
-      </c>
-      <c r="F101">
-        <f>COUNTIF(E$3:E101,E101)</f>
-        <v>10</v>
-      </c>
-      <c r="G101" t="str">
-        <v/>
-      </c>
-      <c r="H101" t="str">
-        <v/>
-      </c>
-      <c r="I101" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="J101" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="L101" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="M101" t="str">
-        <v/>
-      </c>
-      <c r="N101" t="str">
-        <v/>
-      </c>
-      <c r="O101" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="P101" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="X101" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Y101" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Z101" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AA101" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AB101" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AC101" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AD101" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AE101" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AF101" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AG101" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AH101" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AI101" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AJ101" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AK101" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="5:37" x14ac:dyDescent="0.55000000000000004">
-      <c r="E102" t="str">
-        <f t="shared" si="1"/>
-        <v>unit</v>
-      </c>
-      <c r="F102">
-        <f>COUNTIF(E$3:E102,E102)</f>
-        <v>11</v>
-      </c>
-      <c r="G102" t="str">
-        <v/>
-      </c>
-      <c r="H102" t="str">
-        <v/>
-      </c>
-      <c r="I102" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="J102" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="L102" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="M102" t="str">
-        <v/>
-      </c>
-      <c r="N102" t="str">
-        <v/>
-      </c>
-      <c r="O102" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="P102" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="X102" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Y102" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Z102" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AA102" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AB102" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AC102" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AD102" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AE102" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AF102" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AG102" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AH102" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AI102" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AJ102" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AK102" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="103" spans="5:37" x14ac:dyDescent="0.55000000000000004">
-      <c r="E103" t="str">
-        <f t="shared" si="1"/>
-        <v>unit</v>
-      </c>
-      <c r="F103">
-        <f>COUNTIF(E$3:E103,E103)</f>
-        <v>12</v>
-      </c>
-      <c r="G103" t="str">
-        <v/>
-      </c>
-      <c r="H103" t="str">
-        <v/>
-      </c>
-      <c r="I103" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="J103" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="L103" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="M103" t="str">
-        <v/>
-      </c>
-      <c r="N103" t="str">
-        <v/>
-      </c>
-      <c r="O103" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="P103" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="X103" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Y103" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Z103" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AA103" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AB103" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AC103" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AD103" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AE103" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AF103" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AG103" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AH103" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AI103" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AJ103" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AK103" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="5:37" x14ac:dyDescent="0.55000000000000004">
-      <c r="E104" t="str">
-        <f t="shared" si="1"/>
-        <v>unit</v>
-      </c>
-      <c r="F104">
-        <f>COUNTIF(E$3:E104,E104)</f>
-        <v>13</v>
-      </c>
-      <c r="G104" t="str">
-        <v/>
-      </c>
-      <c r="H104" t="str">
-        <v/>
-      </c>
-      <c r="I104" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="J104" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="L104" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="M104" t="str">
-        <v/>
-      </c>
-      <c r="N104" t="str">
-        <v/>
-      </c>
-      <c r="O104" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="P104" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="X104" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Y104" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Z104" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AA104" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AB104" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AC104" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AD104" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AE104" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AF104" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AG104" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AH104" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AI104" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AJ104" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AK104" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="105" spans="5:37" x14ac:dyDescent="0.55000000000000004">
-      <c r="E105" t="str">
-        <f t="shared" si="1"/>
-        <v>unit</v>
-      </c>
-      <c r="F105">
-        <f>COUNTIF(E$3:E105,E105)</f>
-        <v>14</v>
-      </c>
-      <c r="G105" t="str">
-        <v/>
-      </c>
-      <c r="H105" t="str">
-        <v/>
-      </c>
-      <c r="I105" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="J105" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="L105" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="M105" t="str">
-        <v/>
-      </c>
-      <c r="N105" t="str">
-        <v/>
-      </c>
-      <c r="O105" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="P105" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="X105" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Y105" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Z105" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AA105" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AB105" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AC105" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AD105" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AE105" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AF105" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AG105" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AH105" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AI105" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AJ105" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AK105" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="106" spans="5:37" x14ac:dyDescent="0.55000000000000004">
-      <c r="E106" t="str">
-        <f t="shared" si="1"/>
-        <v>unit</v>
-      </c>
-      <c r="F106">
-        <f>COUNTIF(E$3:E106,E106)</f>
-        <v>15</v>
-      </c>
-      <c r="G106" t="str">
-        <v/>
-      </c>
-      <c r="H106" t="str">
-        <v/>
-      </c>
-      <c r="I106" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="J106" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="L106" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="M106" t="str">
-        <v/>
-      </c>
-      <c r="N106" t="str">
-        <v/>
-      </c>
-      <c r="O106" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="P106" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="X106" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Y106" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Z106" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AA106" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AB106" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AC106" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AD106" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AE106" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AF106" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AG106" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AH106" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AI106" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AJ106" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AK106" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="107" spans="5:37" x14ac:dyDescent="0.55000000000000004">
-      <c r="E107" t="str">
-        <f t="shared" si="1"/>
-        <v>unit</v>
-      </c>
-      <c r="F107">
-        <f>COUNTIF(E$3:E107,E107)</f>
-        <v>16</v>
-      </c>
-      <c r="G107" t="str">
-        <v/>
-      </c>
-      <c r="H107" t="str">
-        <v/>
-      </c>
-      <c r="I107" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="J107" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="L107" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="M107" t="str">
-        <v/>
-      </c>
-      <c r="N107" t="str">
-        <v/>
-      </c>
-      <c r="O107" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="P107" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="X107" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Y107" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Z107" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AA107" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AB107" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AC107" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AD107" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AE107" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AF107" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AG107" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AH107" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AI107" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AJ107" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AK107" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="108" spans="5:37" x14ac:dyDescent="0.55000000000000004">
-      <c r="E108" t="str">
-        <f t="shared" si="1"/>
-        <v>unit</v>
-      </c>
-      <c r="F108">
-        <f>COUNTIF(E$3:E108,E108)</f>
-        <v>17</v>
-      </c>
-      <c r="G108" t="str">
-        <v/>
-      </c>
-      <c r="H108" t="str">
-        <v/>
-      </c>
-      <c r="I108" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="J108" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="L108" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="M108" t="str">
-        <v/>
-      </c>
-      <c r="N108" t="str">
-        <v/>
-      </c>
-      <c r="O108" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="P108" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="X108" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Y108" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Z108" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AA108" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AB108" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AC108" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AD108" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AE108" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AF108" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AG108" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AH108" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AI108" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AJ108" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AK108" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="109" spans="5:37" x14ac:dyDescent="0.55000000000000004">
-      <c r="E109" t="str">
-        <f t="shared" si="1"/>
-        <v>unit</v>
-      </c>
-      <c r="F109">
-        <f>COUNTIF(E$3:E109,E109)</f>
-        <v>18</v>
-      </c>
-      <c r="G109" t="str">
-        <v/>
-      </c>
-      <c r="H109" t="str">
-        <v/>
-      </c>
-      <c r="I109" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="J109" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="L109" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="M109" t="str">
-        <v/>
-      </c>
-      <c r="N109" t="str">
-        <v/>
-      </c>
-      <c r="O109" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="P109" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="X109" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Y109" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Z109" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AA109" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AB109" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AC109" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AD109" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AE109" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AF109" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AG109" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AH109" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AI109" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AJ109" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AK109" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-    </row>
     <row r="110" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E110" t="str">
         <f t="shared" si="1"/>
@@ -21335,31 +21542,31 @@
       </c>
       <c r="F110">
         <f>COUNTIF(E$3:E110,E110)</f>
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G110" t="str">
         <v/>
       </c>
-      <c r="H110" t="str">
-        <v/>
+      <c r="H110">
+        <v>56</v>
       </c>
       <c r="I110" t="str">
         <f ca="1"/>
-        <v/>
+        <v>Welding</v>
       </c>
       <c r="J110" t="str">
         <f ca="1"/>
-        <v/>
+        <v>Welding</v>
       </c>
       <c r="L110" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【unit5】 Welding</v>
       </c>
       <c r="M110" t="str">
         <v/>
       </c>
       <c r="N110" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="O110" t="str">
         <f ca="1"/>
@@ -21367,63 +21574,158 @@
       </c>
       <c r="P110" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="X110" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Y110" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Z110" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Welding
+	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AA110" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Welding
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB110" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Welding
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Welding';</v>
       </c>
       <c r="AC110" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Welding
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Welding';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD110" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Welding
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Welding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit5】 Welding';</v>
       </c>
       <c r="AE110" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Welding
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Welding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit5】 Welding';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF110" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Welding
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Welding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit5】 Welding';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AG110" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Welding
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Welding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit5】 Welding';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH110" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Welding
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Welding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit5】 Welding';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI110" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Welding
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Welding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit5】 Welding';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AJ110" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Welding
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Welding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit5】 Welding';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AK110" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Welding
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Welding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit5】 Welding';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="111" spans="5:37" x14ac:dyDescent="0.55000000000000004">
@@ -21433,31 +21735,31 @@
       </c>
       <c r="F111">
         <f>COUNTIF(E$3:E111,E111)</f>
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G111" t="str">
         <v/>
       </c>
-      <c r="H111" t="str">
-        <v/>
+      <c r="H111">
+        <v>57</v>
       </c>
       <c r="I111" t="str">
         <f ca="1"/>
-        <v/>
+        <v>Discharge</v>
       </c>
       <c r="J111" t="str">
         <f ca="1"/>
-        <v/>
+        <v>Discharge</v>
       </c>
       <c r="L111" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【unit6】 Discharge</v>
       </c>
       <c r="M111" t="str">
         <v/>
       </c>
       <c r="N111" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="O111" t="str">
         <f ca="1"/>
@@ -21465,63 +21767,158 @@
       </c>
       <c r="P111" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="X111" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Y111" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Z111" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Discharge
+	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AA111" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Discharge
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB111" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Discharge
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Discharge';</v>
       </c>
       <c r="AC111" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Discharge
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Discharge';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD111" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Discharge
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Discharge';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit6】 Discharge';</v>
       </c>
       <c r="AE111" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Discharge
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Discharge';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit6】 Discharge';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF111" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Discharge
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Discharge';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit6】 Discharge';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AG111" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Discharge
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Discharge';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit6】 Discharge';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH111" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Discharge
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Discharge';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit6】 Discharge';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI111" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Discharge
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Discharge';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit6】 Discharge';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AJ111" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Discharge
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Discharge';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit6】 Discharge';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AK111" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Discharge
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Discharge';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit6】 Discharge';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="112" spans="5:37" x14ac:dyDescent="0.55000000000000004">
@@ -21531,31 +21928,31 @@
       </c>
       <c r="F112">
         <f>COUNTIF(E$3:E112,E112)</f>
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G112" t="str">
         <v/>
       </c>
-      <c r="H112" t="str">
-        <v/>
+      <c r="H112">
+        <v>58</v>
       </c>
       <c r="I112" t="str">
         <f ca="1"/>
-        <v/>
+        <v>X-roll section</v>
       </c>
       <c r="J112" t="str">
         <f ca="1"/>
-        <v/>
+        <v>X-roll section</v>
       </c>
       <c r="L112" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【unit7】 X-roll section</v>
       </c>
       <c r="M112" t="str">
         <v/>
       </c>
       <c r="N112" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="O112" t="str">
         <f ca="1"/>
@@ -21563,63 +21960,158 @@
       </c>
       <c r="P112" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="X112" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Y112" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Z112" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//X-roll section
+	ELSIF uiInfoIdx = 7 THEN</v>
       </c>
       <c r="AA112" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//X-roll section
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB112" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//X-roll section
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'X-roll section';</v>
       </c>
       <c r="AC112" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//X-roll section
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'X-roll section';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD112" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//X-roll section
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'X-roll section';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit7】 X-roll section';</v>
       </c>
       <c r="AE112" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//X-roll section
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'X-roll section';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit7】 X-roll section';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF112" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//X-roll section
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'X-roll section';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit7】 X-roll section';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AG112" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//X-roll section
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'X-roll section';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit7】 X-roll section';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH112" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//X-roll section
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'X-roll section';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit7】 X-roll section';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI112" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//X-roll section
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'X-roll section';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit7】 X-roll section';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AJ112" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//X-roll section
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'X-roll section';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit7】 X-roll section';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AK112" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//X-roll section
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'X-roll section';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit7】 X-roll section';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="113" spans="5:37" x14ac:dyDescent="0.55000000000000004">
@@ -21629,7 +22121,7 @@
       </c>
       <c r="F113">
         <f>COUNTIF(E$3:E113,E113)</f>
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="G113" t="str">
         <v/>
@@ -21727,7 +22219,7 @@
       </c>
       <c r="F114">
         <f>COUNTIF(E$3:E114,E114)</f>
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="G114" t="str">
         <v/>
@@ -21825,7 +22317,7 @@
       </c>
       <c r="F115">
         <f>COUNTIF(E$3:E115,E115)</f>
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G115" t="str">
         <v/>
@@ -21923,7 +22415,7 @@
       </c>
       <c r="F116">
         <f>COUNTIF(E$3:E116,E116)</f>
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G116" t="str">
         <v/>
@@ -22021,7 +22513,7 @@
       </c>
       <c r="F117">
         <f>COUNTIF(E$3:E117,E117)</f>
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G117" t="str">
         <v/>
@@ -22119,7 +22611,7 @@
       </c>
       <c r="F118">
         <f>COUNTIF(E$3:E118,E118)</f>
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G118" t="str">
         <v/>
@@ -22217,7 +22709,7 @@
       </c>
       <c r="F119">
         <f>COUNTIF(E$3:E119,E119)</f>
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="G119" t="str">
         <v/>
@@ -22315,7 +22807,7 @@
       </c>
       <c r="F120">
         <f>COUNTIF(E$3:E120,E120)</f>
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G120" t="str">
         <v/>
@@ -22413,7 +22905,7 @@
       </c>
       <c r="F121">
         <f>COUNTIF(E$3:E121,E121)</f>
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G121" t="str">
         <v/>
@@ -22511,7 +23003,7 @@
       </c>
       <c r="F122">
         <f>COUNTIF(E$3:E122,E122)</f>
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G122" t="str">
         <v/>
@@ -22609,7 +23101,7 @@
       </c>
       <c r="F123">
         <f>COUNTIF(E$3:E123,E123)</f>
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="G123" t="str">
         <v/>
@@ -22707,7 +23199,7 @@
       </c>
       <c r="F124">
         <f>COUNTIF(E$3:E124,E124)</f>
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G124" t="str">
         <v/>
@@ -22805,7 +23297,7 @@
       </c>
       <c r="F125">
         <f>COUNTIF(E$3:E125,E125)</f>
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="G125" t="str">
         <v/>
@@ -22903,7 +23395,7 @@
       </c>
       <c r="F126">
         <f>COUNTIF(E$3:E126,E126)</f>
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G126" t="str">
         <v/>
@@ -23001,7 +23493,7 @@
       </c>
       <c r="F127">
         <f>COUNTIF(E$3:E127,E127)</f>
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="G127" t="str">
         <v/>
@@ -23099,7 +23591,7 @@
       </c>
       <c r="F128">
         <f>COUNTIF(E$3:E128,E128)</f>
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="G128" t="str">
         <v/>
@@ -23197,7 +23689,7 @@
       </c>
       <c r="F129">
         <f>COUNTIF(E$3:E129,E129)</f>
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G129" t="str">
         <v/>
@@ -23295,7 +23787,7 @@
       </c>
       <c r="F130">
         <f>COUNTIF(E$3:E130,E130)</f>
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G130" t="str">
         <v/>
@@ -23393,7 +23885,7 @@
       </c>
       <c r="F131">
         <f>COUNTIF(E$3:E131,E131)</f>
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="G131" t="str">
         <v/>
@@ -23491,7 +23983,7 @@
       </c>
       <c r="F132">
         <f>COUNTIF(E$3:E132,E132)</f>
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G132" t="str">
         <v/>
@@ -23589,7 +24081,7 @@
       </c>
       <c r="F133">
         <f>COUNTIF(E$3:E133,E133)</f>
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G133" t="str">
         <v/>
@@ -23687,7 +24179,7 @@
       </c>
       <c r="F134">
         <f>COUNTIF(E$3:E134,E134)</f>
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="G134" t="str">
         <v/>
@@ -23785,7 +24277,7 @@
       </c>
       <c r="F135">
         <f>COUNTIF(E$3:E135,E135)</f>
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G135" t="str">
         <v/>
@@ -23883,7 +24375,7 @@
       </c>
       <c r="F136">
         <f>COUNTIF(E$3:E136,E136)</f>
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="G136" t="str">
         <v/>
@@ -23981,7 +24473,7 @@
       </c>
       <c r="F137">
         <f>COUNTIF(E$3:E137,E137)</f>
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="G137" t="str">
         <v/>
@@ -24079,7 +24571,7 @@
       </c>
       <c r="F138">
         <f>COUNTIF(E$3:E138,E138)</f>
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="G138" t="str">
         <v/>
@@ -24177,7 +24669,7 @@
       </c>
       <c r="F139">
         <f>COUNTIF(E$3:E139,E139)</f>
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="G139" t="str">
         <v/>
@@ -24275,7 +24767,7 @@
       </c>
       <c r="F140">
         <f>COUNTIF(E$3:E140,E140)</f>
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G140" t="str">
         <v/>
@@ -24373,7 +24865,7 @@
       </c>
       <c r="F141">
         <f>COUNTIF(E$3:E141,E141)</f>
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="G141" t="str">
         <v/>
@@ -24471,7 +24963,7 @@
       </c>
       <c r="F142">
         <f>COUNTIF(E$3:E142,E142)</f>
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="G142" t="str">
         <v/>
@@ -24569,7 +25061,7 @@
       </c>
       <c r="F143">
         <f>COUNTIF(E$3:E143,E143)</f>
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G143" t="str">
         <v/>
@@ -24667,7 +25159,7 @@
       </c>
       <c r="F144">
         <f>COUNTIF(E$3:E144,E144)</f>
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="G144" t="str">
         <v/>
@@ -24765,7 +25257,7 @@
       </c>
       <c r="F145">
         <f>COUNTIF(E$3:E145,E145)</f>
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G145" t="str">
         <v/>
@@ -24863,7 +25355,7 @@
       </c>
       <c r="F146">
         <f>COUNTIF(E$3:E146,E146)</f>
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="G146" t="str">
         <v/>
@@ -24961,7 +25453,7 @@
       </c>
       <c r="F147">
         <f>COUNTIF(E$3:E147,E147)</f>
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="G147" t="str">
         <v/>
@@ -25059,7 +25551,7 @@
       </c>
       <c r="F148">
         <f>COUNTIF(E$3:E148,E148)</f>
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="G148" t="str">
         <v/>
@@ -25157,7 +25649,7 @@
       </c>
       <c r="F149">
         <f>COUNTIF(E$3:E149,E149)</f>
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="G149" t="str">
         <v/>
@@ -25255,7 +25747,7 @@
       </c>
       <c r="F150">
         <f>COUNTIF(E$3:E150,E150)</f>
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="G150" t="str">
         <v/>
@@ -25353,7 +25845,7 @@
       </c>
       <c r="F151">
         <f>COUNTIF(E$3:E151,E151)</f>
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="G151" t="str">
         <v/>
@@ -25451,7 +25943,7 @@
       </c>
       <c r="F152">
         <f>COUNTIF(E$3:E152,E152)</f>
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="G152" t="str">
         <v/>
@@ -25549,7 +26041,7 @@
       </c>
       <c r="F153">
         <f>COUNTIF(E$3:E153,E153)</f>
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="G153" t="str">
         <v/>
@@ -25647,7 +26139,7 @@
       </c>
       <c r="F154">
         <f>COUNTIF(E$3:E154,E154)</f>
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="G154" t="str">
         <v/>
@@ -25745,7 +26237,7 @@
       </c>
       <c r="F155">
         <f>COUNTIF(E$3:E155,E155)</f>
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G155" t="str">
         <v/>
@@ -25843,7 +26335,7 @@
       </c>
       <c r="F156">
         <f>COUNTIF(E$3:E156,E156)</f>
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="G156" t="str">
         <v/>
@@ -25941,7 +26433,7 @@
       </c>
       <c r="F157">
         <f>COUNTIF(E$3:E157,E157)</f>
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G157" t="str">
         <v/>
@@ -26039,7 +26531,7 @@
       </c>
       <c r="F158">
         <f>COUNTIF(E$3:E158,E158)</f>
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="G158" t="str">
         <v/>
@@ -26137,7 +26629,7 @@
       </c>
       <c r="F159">
         <f>COUNTIF(E$3:E159,E159)</f>
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="G159" t="str">
         <v/>
@@ -26235,7 +26727,7 @@
       </c>
       <c r="F160">
         <f>COUNTIF(E$3:E160,E160)</f>
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="G160" t="str">
         <v/>
@@ -26333,7 +26825,7 @@
       </c>
       <c r="F161">
         <f>COUNTIF(E$3:E161,E161)</f>
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="G161" t="str">
         <v/>
@@ -26431,7 +26923,7 @@
       </c>
       <c r="F162">
         <f>COUNTIF(E$3:E162,E162)</f>
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="G162" t="str">
         <v/>
@@ -26529,7 +27021,7 @@
       </c>
       <c r="F163">
         <f>COUNTIF(E$3:E163,E163)</f>
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="G163" t="str">
         <v/>
@@ -26627,7 +27119,7 @@
       </c>
       <c r="F164">
         <f>COUNTIF(E$3:E164,E164)</f>
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="G164" t="str">
         <v/>
@@ -26725,7 +27217,7 @@
       </c>
       <c r="F165">
         <f>COUNTIF(E$3:E165,E165)</f>
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="G165" t="str">
         <v/>
@@ -26823,7 +27315,7 @@
       </c>
       <c r="F166">
         <f>COUNTIF(E$3:E166,E166)</f>
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G166" t="str">
         <v/>
@@ -26921,7 +27413,7 @@
       </c>
       <c r="F167">
         <f>COUNTIF(E$3:E167,E167)</f>
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="G167" t="str">
         <v/>
@@ -27019,7 +27511,7 @@
       </c>
       <c r="F168">
         <f>COUNTIF(E$3:E168,E168)</f>
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="G168" t="str">
         <v/>
@@ -27117,7 +27609,7 @@
       </c>
       <c r="F169">
         <f>COUNTIF(E$3:E169,E169)</f>
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="G169" t="str">
         <v/>
@@ -27215,7 +27707,7 @@
       </c>
       <c r="F170">
         <f>COUNTIF(E$3:E170,E170)</f>
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="G170" t="str">
         <v/>
@@ -27313,7 +27805,7 @@
       </c>
       <c r="F171">
         <f>COUNTIF(E$3:E171,E171)</f>
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="G171" t="str">
         <v/>
@@ -27411,7 +27903,7 @@
       </c>
       <c r="F172">
         <f>COUNTIF(E$3:E172,E172)</f>
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="G172" t="str">
         <v/>
@@ -27509,7 +28001,7 @@
       </c>
       <c r="F173">
         <f>COUNTIF(E$3:E173,E173)</f>
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G173" t="str">
         <v/>
@@ -27607,7 +28099,7 @@
       </c>
       <c r="F174">
         <f>COUNTIF(E$3:E174,E174)</f>
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G174" t="str">
         <v/>
@@ -27705,7 +28197,7 @@
       </c>
       <c r="F175">
         <f>COUNTIF(E$3:E175,E175)</f>
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="G175" t="str">
         <v/>
@@ -27803,7 +28295,7 @@
       </c>
       <c r="F176">
         <f>COUNTIF(E$3:E176,E176)</f>
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="G176" t="str">
         <v/>
@@ -27901,7 +28393,7 @@
       </c>
       <c r="F177">
         <f>COUNTIF(E$3:E177,E177)</f>
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="G177" t="str">
         <v/>
@@ -27999,7 +28491,7 @@
       </c>
       <c r="F178">
         <f>COUNTIF(E$3:E178,E178)</f>
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="G178" t="str">
         <v/>
@@ -28097,7 +28589,7 @@
       </c>
       <c r="F179">
         <f>COUNTIF(E$3:E179,E179)</f>
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G179" t="str">
         <v/>
@@ -28195,7 +28687,7 @@
       </c>
       <c r="F180">
         <f>COUNTIF(E$3:E180,E180)</f>
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="G180" t="str">
         <v/>
@@ -28293,7 +28785,7 @@
       </c>
       <c r="F181">
         <f>COUNTIF(E$3:E181,E181)</f>
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="G181" t="str">
         <v/>
@@ -28391,7 +28883,7 @@
       </c>
       <c r="F182">
         <f>COUNTIF(E$3:E182,E182)</f>
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="G182" t="str">
         <v/>
@@ -28489,7 +28981,7 @@
       </c>
       <c r="F183">
         <f>COUNTIF(E$3:E183,E183)</f>
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="G183" t="str">
         <v/>
@@ -28587,7 +29079,7 @@
       </c>
       <c r="F184">
         <f>COUNTIF(E$3:E184,E184)</f>
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="G184" t="str">
         <v/>
@@ -28685,7 +29177,7 @@
       </c>
       <c r="F185">
         <f>COUNTIF(E$3:E185,E185)</f>
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="G185" t="str">
         <v/>
@@ -28783,7 +29275,7 @@
       </c>
       <c r="F186">
         <f>COUNTIF(E$3:E186,E186)</f>
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="G186" t="str">
         <v/>
@@ -28881,7 +29373,7 @@
       </c>
       <c r="F187">
         <f>COUNTIF(E$3:E187,E187)</f>
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="G187" t="str">
         <v/>
@@ -28979,7 +29471,7 @@
       </c>
       <c r="F188">
         <f>COUNTIF(E$3:E188,E188)</f>
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G188" t="str">
         <v/>
@@ -29077,7 +29569,7 @@
       </c>
       <c r="F189">
         <f>COUNTIF(E$3:E189,E189)</f>
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="G189" t="str">
         <v/>
@@ -29175,7 +29667,7 @@
       </c>
       <c r="F190">
         <f>COUNTIF(E$3:E190,E190)</f>
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="G190" t="str">
         <v/>
@@ -29273,7 +29765,7 @@
       </c>
       <c r="F191">
         <f>COUNTIF(E$3:E191,E191)</f>
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="G191" t="str">
         <v/>
@@ -29371,7 +29863,7 @@
       </c>
       <c r="F192">
         <f>COUNTIF(E$3:E192,E192)</f>
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="G192" t="str">
         <v/>
@@ -29469,7 +29961,7 @@
       </c>
       <c r="F193">
         <f>COUNTIF(E$3:E193,E193)</f>
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="G193" t="str">
         <v/>
@@ -29567,7 +30059,7 @@
       </c>
       <c r="F194">
         <f>COUNTIF(E$3:E194,E194)</f>
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G194" t="str">
         <v/>
@@ -29665,7 +30157,7 @@
       </c>
       <c r="F195">
         <f>COUNTIF(E$3:E195,E195)</f>
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G195" t="str">
         <v/>
@@ -29763,7 +30255,7 @@
       </c>
       <c r="F196">
         <f>COUNTIF(E$3:E196,E196)</f>
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="G196" t="str">
         <v/>
@@ -29861,7 +30353,7 @@
       </c>
       <c r="F197">
         <f>COUNTIF(E$3:E197,E197)</f>
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="G197" t="str">
         <v/>
@@ -29959,7 +30451,7 @@
       </c>
       <c r="F198">
         <f>COUNTIF(E$3:E198,E198)</f>
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="G198" t="str">
         <v/>
@@ -30057,7 +30549,7 @@
       </c>
       <c r="F199">
         <f>COUNTIF(E$3:E199,E199)</f>
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="G199" t="str">
         <v/>
@@ -30155,7 +30647,7 @@
       </c>
       <c r="F200">
         <f>COUNTIF(E$3:E200,E200)</f>
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="G200" t="str">
         <v/>
@@ -30253,7 +30745,7 @@
       </c>
       <c r="F201">
         <f>COUNTIF(E$3:E201,E201)</f>
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="G201" t="str">
         <v/>
@@ -30351,7 +30843,7 @@
       </c>
       <c r="F202">
         <f>COUNTIF(E$3:E202,E202)</f>
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="G202" t="str">
         <v>●</v>
@@ -30451,7 +30943,7 @@
     <row r="205" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="AK205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AK$3:AK$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_exe_errno.xlsm]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]content によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//Foil wax reel shaft
@@ -30992,6 +31484,50 @@
 	ELSE
 		uiErrCode	:= 2;
 	END_IF;
+//OTHC
+ELSIF strInfoType = 'OTHC' THEN
+	//(Unassigned)
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '(Unassigned)';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC1】 (Unassigned)';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//(Unassigned)
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '(Unassigned)';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC2】 (Unassigned)';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//T-roll gluing shaft
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'T-roll gluing shaft';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【OTHC3】 T-roll gluing shaft';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	ELSE
+		uiErrCode	:= 2;
+	END_IF;
 //unit
 ELSIF strInfoType = 'unit' THEN
 	//Flat Sheet Supply

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF6C41D-253E-463C-89A4-C87352BE0DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0172E844-5E59-4CF7-AD6C-D5C0BF8458CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -882,9 +882,6 @@
     <t>平板フラップ開閉</t>
   </si>
   <si>
-    <t>巻取り軸芯前後</t>
-  </si>
-  <si>
     <t>平板カット刃開閉</t>
   </si>
   <si>
@@ -1601,6 +1598,10 @@
   </si>
   <si>
     <t>Foil wax reel section</t>
+  </si>
+  <si>
+    <t>巻取り軸芯前後</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -2477,7 +2478,7 @@
         <v>105</v>
       </c>
       <c r="G1" s="39" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H1" s="39" t="s">
         <v>10</v>
@@ -2489,7 +2490,7 @@
         <v>3</v>
       </c>
       <c r="K1" s="39" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L1" s="39" t="s">
         <v>5</v>
@@ -2498,16 +2499,16 @@
         <v>112</v>
       </c>
       <c r="N1" s="40" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O1" s="40" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P1" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q1" s="41" t="s">
         <v>277</v>
-      </c>
-      <c r="Q1" s="41" t="s">
-        <v>278</v>
       </c>
       <c r="R1" s="40"/>
     </row>
@@ -2531,7 +2532,7 @@
         <v>133</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H2" s="28" t="s">
         <v>20</v>
@@ -2540,10 +2541,10 @@
         <v>21</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L2" s="28">
         <v>1</v>
@@ -2579,7 +2580,7 @@
         <v>125</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>14</v>
@@ -2588,10 +2589,10 @@
         <v>13</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L3" s="12">
         <v>1</v>
@@ -2627,7 +2628,7 @@
         <v>124</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>14</v>
@@ -2636,10 +2637,10 @@
         <v>13</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L4" s="12">
         <v>1</v>
@@ -2675,7 +2676,7 @@
         <v>89</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>14</v>
@@ -2684,10 +2685,10 @@
         <v>13</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L5" s="12">
         <v>1</v>
@@ -2720,10 +2721,10 @@
         <v>94</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>1</v>
@@ -2735,7 +2736,7 @@
         <v>2</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L6" s="8">
         <v>1</v>
@@ -2771,7 +2772,7 @@
         <v>131</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>0</v>
@@ -2783,7 +2784,7 @@
         <v>2</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L7" s="8">
         <v>1</v>
@@ -2819,7 +2820,7 @@
         <v>130</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>28</v>
@@ -2831,7 +2832,7 @@
         <v>2</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L8" s="8">
         <v>1</v>
@@ -2864,10 +2865,10 @@
         <v>101</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>106</v>
@@ -2879,7 +2880,7 @@
         <v>2</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L9" s="8">
         <v>1</v>
@@ -2912,10 +2913,10 @@
         <v>101</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>107</v>
@@ -2927,7 +2928,7 @@
         <v>2</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L10" s="8">
         <v>1</v>
@@ -2959,7 +2960,7 @@
         <v>132</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
@@ -2993,7 +2994,7 @@
         <v>134</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
@@ -3027,7 +3028,7 @@
         <v>135</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
@@ -3065,7 +3066,7 @@
         <v>126</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>31</v>
@@ -3074,10 +3075,10 @@
         <v>32</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L14" s="8">
         <v>1</v>
@@ -3113,7 +3114,7 @@
         <v>127</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>33</v>
@@ -3122,10 +3123,10 @@
         <v>32</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L15" s="8">
         <v>1</v>
@@ -3157,7 +3158,7 @@
         <v>128</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>137</v>
@@ -3193,7 +3194,7 @@
         <v>136</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>137</v>
@@ -3227,23 +3228,23 @@
         <v>10</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F18" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="G18" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="H18" s="42" t="s">
         <v>275</v>
-      </c>
-      <c r="H18" s="42" t="s">
-        <v>276</v>
       </c>
       <c r="I18" s="8"/>
       <c r="J18" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L18" s="8"/>
       <c r="M18" s="10"/>
@@ -3274,10 +3275,10 @@
         <v>99</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>141</v>
+        <v>298</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>61</v>
@@ -3289,7 +3290,7 @@
         <v>4</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L19" s="8">
         <v>1</v>
@@ -3322,13 +3323,13 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I20" s="8"/>
       <c r="J20" s="8"/>
@@ -3362,13 +3363,13 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
@@ -3406,10 +3407,10 @@
         <v>140</v>
       </c>
       <c r="F22" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="G22" s="8" t="s">
         <v>246</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>247</v>
       </c>
       <c r="H22" s="8" t="s">
         <v>63</v>
@@ -3421,7 +3422,7 @@
         <v>4</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L22" s="8">
         <v>1</v>
@@ -3458,10 +3459,10 @@
         <v>93</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H23" s="8" t="s">
         <v>67</v>
@@ -3473,7 +3474,7 @@
         <v>4</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L23" s="8">
         <v>1</v>
@@ -3510,10 +3511,10 @@
         <v>93</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H24" s="8" t="s">
         <v>65</v>
@@ -3525,7 +3526,7 @@
         <v>4</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L24" s="8">
         <v>1</v>
@@ -3562,10 +3563,10 @@
         <v>98</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H25" s="8" t="s">
         <v>69</v>
@@ -3577,7 +3578,7 @@
         <v>4</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L25" s="11">
         <v>1</v>
@@ -3614,10 +3615,10 @@
         <v>92</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H26" s="8" t="s">
         <v>73</v>
@@ -3629,7 +3630,7 @@
         <v>4</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L26" s="11">
         <v>1</v>
@@ -3669,7 +3670,7 @@
         <v>121</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>71</v>
@@ -3681,7 +3682,7 @@
         <v>4</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L27" s="11">
         <v>1</v>
@@ -3718,10 +3719,10 @@
         <v>100</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H28" s="8" t="s">
         <v>69</v>
@@ -3733,7 +3734,7 @@
         <v>4</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L28" s="11">
         <v>1</v>
@@ -3773,7 +3774,7 @@
         <v>138</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H29" s="12" t="s">
         <v>75</v>
@@ -3785,7 +3786,7 @@
         <v>4</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L29" s="13">
         <v>1</v>
@@ -3822,10 +3823,10 @@
         <v>95</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H30" s="8" t="s">
         <v>74</v>
@@ -3837,7 +3838,7 @@
         <v>4</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L30" s="11">
         <v>1</v>
@@ -3877,7 +3878,7 @@
         <v>139</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H31" s="12" t="s">
         <v>75</v>
@@ -3889,7 +3890,7 @@
         <v>4</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L31" s="13">
         <v>1</v>
@@ -3926,10 +3927,10 @@
         <v>97</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>76</v>
@@ -3941,7 +3942,7 @@
         <v>4</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L32" s="11">
         <v>1</v>
@@ -3978,10 +3979,10 @@
         <v>96</v>
       </c>
       <c r="F33" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="G33" s="12" t="s">
         <v>243</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>244</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>77</v>
@@ -3993,7 +3994,7 @@
         <v>4</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L33" s="13">
         <v>1</v>
@@ -4030,10 +4031,10 @@
         <v>96</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H34" s="12" t="s">
         <v>77</v>
@@ -4045,7 +4046,7 @@
         <v>4</v>
       </c>
       <c r="K34" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L34" s="13">
         <v>1</v>
@@ -4078,10 +4079,10 @@
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
       <c r="F35" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>51</v>
@@ -4118,10 +4119,10 @@
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
       <c r="F36" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H36" s="8" t="s">
         <v>51</v>
@@ -4158,13 +4159,13 @@
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
       <c r="F37" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I37" s="8"/>
       <c r="J37" s="8"/>
@@ -4202,22 +4203,22 @@
         <v>92</v>
       </c>
       <c r="F38" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="H38" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="G38" s="8" t="s">
+      <c r="I38" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="J38" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="H38" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="J38" s="8" t="s">
-        <v>272</v>
-      </c>
       <c r="K38" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L38" s="8"/>
       <c r="M38" s="10"/>
@@ -4257,7 +4258,7 @@
         <v>4</v>
       </c>
       <c r="K39" s="14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L39" s="15">
         <v>1</v>
@@ -4301,7 +4302,7 @@
         <v>4</v>
       </c>
       <c r="K40" s="14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L40" s="15">
         <v>1</v>
@@ -4345,7 +4346,7 @@
         <v>4</v>
       </c>
       <c r="K41" s="14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L41" s="15">
         <v>1</v>
@@ -4383,7 +4384,7 @@
         <v>129</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H42" s="8" t="s">
         <v>30</v>
@@ -4395,7 +4396,7 @@
         <v>2</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L42" s="8">
         <v>1</v>
@@ -4436,10 +4437,10 @@
         <v>8</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L43" s="8">
         <v>1</v>
@@ -4480,10 +4481,10 @@
         <v>9</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L44" s="8">
         <v>1</v>
@@ -4522,10 +4523,10 @@
         <v>23</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L45" s="8">
         <v>3</v>
@@ -4566,10 +4567,10 @@
         <v>24</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L46" s="8">
         <v>1</v>
@@ -4612,10 +4613,10 @@
         <v>36</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L47" s="8">
         <v>1</v>
@@ -4654,10 +4655,10 @@
         <v>59</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L48" s="8">
         <v>1</v>
@@ -4694,10 +4695,10 @@
         <v>19</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L49" s="8">
         <v>1</v>
@@ -4734,10 +4735,10 @@
         <v>17</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L50" s="8">
         <v>1</v>
@@ -4774,10 +4775,10 @@
         <v>26</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L51" s="8">
         <v>1</v>
@@ -4816,10 +4817,10 @@
         <v>26</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L52" s="8">
         <v>1</v>
@@ -4840,7 +4841,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C53" s="7">
         <v>1</v>
@@ -4848,10 +4849,10 @@
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
@@ -4874,7 +4875,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C54" s="7">
         <v>2</v>
@@ -4882,10 +4883,10 @@
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
       <c r="F54" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H54" s="8"/>
       <c r="I54" s="8"/>
@@ -4908,7 +4909,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C55" s="7">
         <v>3</v>
@@ -4916,10 +4917,10 @@
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
       <c r="F55" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
@@ -4942,7 +4943,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C56" s="7">
         <v>4</v>
@@ -4950,10 +4951,10 @@
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
@@ -4976,7 +4977,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C57" s="7">
         <v>5</v>
@@ -4984,10 +4985,10 @@
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
       <c r="F57" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
@@ -5010,7 +5011,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C58" s="7">
         <v>6</v>
@@ -5018,10 +5019,10 @@
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
       <c r="F58" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
@@ -5044,7 +5045,7 @@
         <v>60</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C59" s="7">
         <v>7</v>
@@ -5052,10 +5053,10 @@
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
       <c r="F59" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="G59" s="8" t="s">
         <v>281</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>282</v>
       </c>
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
@@ -5078,7 +5079,7 @@
         <v>65</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C60" s="7">
         <v>8</v>
@@ -5086,10 +5087,10 @@
       <c r="D60" s="8"/>
       <c r="E60" s="8"/>
       <c r="F60" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="G60" s="8" t="s">
         <v>297</v>
-      </c>
-      <c r="G60" s="8" t="s">
-        <v>298</v>
       </c>
       <c r="H60" s="8"/>
       <c r="I60" s="8"/>
@@ -5112,7 +5113,7 @@
         <v>57</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C61" s="7">
         <v>1</v>
@@ -5120,10 +5121,10 @@
       <c r="D61" s="8"/>
       <c r="E61" s="8"/>
       <c r="F61" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G61" s="8" t="s">
         <v>267</v>
-      </c>
-      <c r="G61" s="8" t="s">
-        <v>268</v>
       </c>
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
@@ -5146,7 +5147,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C62" s="7">
         <v>2</v>
@@ -5154,10 +5155,10 @@
       <c r="D62" s="8"/>
       <c r="E62" s="8"/>
       <c r="F62" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="G62" s="8" t="s">
         <v>289</v>
-      </c>
-      <c r="G62" s="8" t="s">
-        <v>290</v>
       </c>
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
@@ -5180,7 +5181,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C63" s="7">
         <v>1</v>
@@ -5188,10 +5189,10 @@
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
       <c r="F63" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="G63" s="8" t="s">
         <v>295</v>
-      </c>
-      <c r="G63" s="8" t="s">
-        <v>296</v>
       </c>
       <c r="H63" s="8"/>
       <c r="I63" s="8"/>
@@ -5214,7 +5215,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C64" s="7">
         <v>2</v>
@@ -5222,10 +5223,10 @@
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
       <c r="F64" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="G64" s="8" t="s">
         <v>295</v>
-      </c>
-      <c r="G64" s="8" t="s">
-        <v>296</v>
       </c>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
@@ -5248,7 +5249,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C65" s="7">
         <v>3</v>
@@ -5256,10 +5257,10 @@
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
       <c r="F65" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="G65" s="8" t="s">
         <v>292</v>
-      </c>
-      <c r="G65" s="8" t="s">
-        <v>293</v>
       </c>
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
@@ -5317,7 +5318,7 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B70" t="s">
         <v>117</v>
@@ -5579,19 +5580,19 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="F1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J1" t="s">
+        <v>226</v>
+      </c>
+      <c r="L1" t="s">
         <v>227</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>228</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>229</v>
-      </c>
-      <c r="P1" t="s">
-        <v>230</v>
       </c>
       <c r="AA1" t="str">
         <f>IF(LEN(J1),J2&amp;CHAR(9)&amp;":"&amp;J1,"")</f>
@@ -5625,82 +5626,82 @@
     </row>
     <row r="2" spans="1:37" s="30" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="30" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E2" s="30" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F2" s="30" t="s">
         <v>102</v>
       </c>
       <c r="G2" s="30" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H2" s="30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J2" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="L2" s="30" t="s">
         <v>190</v>
       </c>
-      <c r="L2" s="30" t="s">
-        <v>191</v>
-      </c>
       <c r="N2" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="P2" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="X2" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="P2" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="X2" s="30" t="s">
-        <v>202</v>
-      </c>
       <c r="Y2" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="Z2" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="Z2" s="30" t="s">
+      <c r="AA2" s="30" t="s">
         <v>194</v>
       </c>
-      <c r="AA2" s="30" t="s">
+      <c r="AB2" s="30" t="s">
         <v>195</v>
       </c>
-      <c r="AB2" s="30" t="s">
+      <c r="AC2" s="30" t="s">
         <v>196</v>
       </c>
-      <c r="AC2" s="30" t="s">
-        <v>197</v>
-      </c>
       <c r="AD2" s="30" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AE2" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="AF2" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="AF2" s="30" t="s">
-        <v>205</v>
-      </c>
       <c r="AG2" s="30" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AH2" s="30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AI2" s="30" t="s">
+        <v>213</v>
+      </c>
+      <c r="AJ2" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="AJ2" s="30" t="s">
-        <v>215</v>
-      </c>
       <c r="AK2" s="30" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]err</v>
+        <v>C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]mess</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
@@ -6100,11 +6101,11 @@
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]err によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]mess によって生成されました。</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ref="E5:E68" si="0">E4</f>
@@ -6300,10 +6301,10 @@
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" t="s">
         <v>183</v>
-      </c>
-      <c r="B6" t="s">
-        <v>184</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
@@ -6499,10 +6500,10 @@
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
+        <v>175</v>
+      </c>
+      <c r="B7" t="s">
         <v>176</v>
-      </c>
-      <c r="B7" t="s">
-        <v>177</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -6698,10 +6699,10 @@
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B8" t="s">
         <v>178</v>
-      </c>
-      <c r="B8" t="s">
-        <v>179</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -6897,10 +6898,10 @@
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>179</v>
+      </c>
+      <c r="B9" t="s">
         <v>180</v>
-      </c>
-      <c r="B9" t="s">
-        <v>181</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -7675,11 +7676,11 @@
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B13" t="str">
         <f ca="1">$AK$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]err によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]mess によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸
@@ -8572,7 +8573,7 @@
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B14" t="str">
         <f>IF(LEN(AI1),"●"&amp;B27&amp;CHAR(10)&amp;AI1,"")</f>
@@ -10035,7 +10036,7 @@
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -10237,10 +10238,10 @@
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B25" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E25" t="str">
         <f t="shared" si="0"/>
@@ -10341,10 +10342,10 @@
     </row>
     <row r="26" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E26" t="str">
         <f t="shared" si="0"/>
@@ -10445,10 +10446,10 @@
     </row>
     <row r="27" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B27" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E27" t="str">
         <f t="shared" si="0"/>
@@ -10549,10 +10550,10 @@
     </row>
     <row r="28" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B28" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E28" t="str">
         <f t="shared" si="0"/>
@@ -10653,10 +10654,10 @@
     </row>
     <row r="29" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B29" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E29" t="str">
         <f t="shared" si="0"/>
@@ -18306,7 +18307,7 @@
     </row>
     <row r="86" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E86" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F86">
         <f>COUNTIF(E$3:E86,E86)</f>
@@ -19506,7 +19507,7 @@
     </row>
     <row r="96" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E96" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F96">
         <f>COUNTIF(E$3:E96,E96)</f>
@@ -20801,7 +20802,7 @@
     </row>
     <row r="106" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E106" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F106">
         <f>COUNTIF(E$3:E106,E106)</f>
@@ -31098,7 +31099,7 @@
     <row r="205" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="AK205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AK$3:AK$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]err によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]mess によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0172E844-5E59-4CF7-AD6C-D5C0BF8458CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE41862-4429-4E55-BFA5-A12C7F12E5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]mess</v>
+        <v>C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]err</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]mess によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]err によって生成されました。</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ref="E5:E68" si="0">E4</f>
@@ -7680,7 +7680,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AK$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]mess によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]err によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸
@@ -31099,7 +31099,7 @@
     <row r="205" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="AK205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AK$3:AK$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]mess によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]err によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE41862-4429-4E55-BFA5-A12C7F12E5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E13A8FEB-01A9-40E3-B9D2-36B1D94D9209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]err</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]err によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ref="E5:E68" si="0">E4</f>
@@ -7680,7 +7680,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AK$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]err によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸
@@ -31099,7 +31099,7 @@
     <row r="205" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="AK205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AK$3:AK$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]err によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E13A8FEB-01A9-40E3-B9D2-36B1D94D9209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A85237-4148-42F6-8951-876904885AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="info_script" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$R$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$R$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="326">
   <si>
     <t>RCA2-GS3NA-I-10-2-50-A6-M-K1</t>
   </si>
@@ -1603,6 +1603,99 @@
     <t>巻取り軸芯前後</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>Workpiece transportation Z-shaft</t>
+  </si>
+  <si>
+    <t>RCP6S-SA7R-WA-56P-16-150-SE-S-B-MR　</t>
+  </si>
+  <si>
+    <t>ロボシリンダー</t>
+  </si>
+  <si>
+    <t>Workpiece transportation X-shaft</t>
+  </si>
+  <si>
+    <t>RCP6S-SA4R-WA-35P-5-500-SE-S-ML</t>
+  </si>
+  <si>
+    <t>Workpiece transportation Y-shaft</t>
+  </si>
+  <si>
+    <t>RCP6S-SA4R-WA-35P-5-150-SE-S-MR</t>
+  </si>
+  <si>
+    <t>Workpiece  rotation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCS2-RTC12L-A-150-30-360-T2-S-L </t>
+  </si>
+  <si>
+    <t>ロボシリンダー(ロータリ)</t>
+  </si>
+  <si>
+    <t>ワークチャック</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workpiece  chuck </t>
+  </si>
+  <si>
+    <t>RCP2-GRHB-I-42P-2-40-P1-S</t>
+  </si>
+  <si>
+    <t>ロボシリンダー(グリッパ)</t>
+  </si>
+  <si>
+    <t>Welding support up/down</t>
+  </si>
+  <si>
+    <t>Welding torch up/down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCP6S-SA6C-WA-42P-3-50-SE-S-B </t>
+  </si>
+  <si>
+    <t>ワーク搬送Z軸</t>
+  </si>
+  <si>
+    <t>ワーク搬送X軸</t>
+  </si>
+  <si>
+    <t>ワーク搬送Y軸</t>
+  </si>
+  <si>
+    <t>ワーク回転</t>
+  </si>
+  <si>
+    <t>溶接補助</t>
+  </si>
+  <si>
+    <t>溶接トーチ上下</t>
+  </si>
+  <si>
+    <t>平板張力軸</t>
+    <rPh sb="0" eb="2">
+      <t>ヒライタ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>チョウリョク</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Flat tension axis</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SV3-M040AK</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サーボモータ</t>
+  </si>
 </sst>
 </file>
 
@@ -2027,11 +2120,18 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill patternType="lightUp">
           <fgColor rgb="FF33CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2075,7 +2175,7 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$A$69">
+    <xdr:sp macro="" textlink="$A$77">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="正方形/長方形 1">
           <a:extLst>
@@ -2135,7 +2235,7 @@
               <a:ea typeface="游ゴシック"/>
             </a:rPr>
             <a:pPr algn="l"/>
-            <a:t>65</a:t>
+            <a:t>73</a:t>
           </a:fld>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="600"/>
         </a:p>
@@ -2444,7 +2544,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R93"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -3260,423 +3360,381 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="7">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C19" s="7">
-        <v>1</v>
-      </c>
-      <c r="D19" s="8">
-        <v>1</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>99</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
       <c r="F19" s="8" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>61</v>
+        <v>299</v>
+      </c>
+      <c r="H19" s="42" t="s">
+        <v>300</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>62</v>
+        <v>301</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>4</v>
+        <v>223</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L19" s="8">
         <v>1</v>
       </c>
       <c r="M19" s="10"/>
-      <c r="N19" s="10">
-        <v>0</v>
-      </c>
-      <c r="O19" s="10">
-        <v>0</v>
-      </c>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
       <c r="P19" s="34">
-        <v>46069.554861111108</v>
+        <v>46139</v>
       </c>
       <c r="Q19" s="34">
-        <v>46069.554861111108</v>
+        <v>46139</v>
       </c>
       <c r="R19" s="10"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="7">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C20" s="7">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8" t="s">
-        <v>282</v>
+        <v>317</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
+        <v>302</v>
+      </c>
+      <c r="H20" s="42" t="s">
+        <v>303</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="L20" s="8">
+        <v>1</v>
+      </c>
       <c r="M20" s="10"/>
-      <c r="N20" s="10">
-        <v>0</v>
-      </c>
-      <c r="O20" s="10">
-        <v>5</v>
-      </c>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
       <c r="P20" s="34">
-        <v>46069.554861111108</v>
+        <v>46139</v>
       </c>
       <c r="Q20" s="34">
-        <v>46069.554861111108</v>
+        <v>46139</v>
       </c>
       <c r="R20" s="10"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="7">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C21" s="7">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8" t="s">
-        <v>283</v>
+        <v>318</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
+        <v>304</v>
+      </c>
+      <c r="H21" s="42" t="s">
+        <v>305</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="L21" s="8">
+        <v>1</v>
+      </c>
       <c r="M21" s="10"/>
-      <c r="N21" s="10">
-        <v>0</v>
-      </c>
-      <c r="O21" s="10">
-        <v>6</v>
-      </c>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
       <c r="P21" s="34">
-        <v>46069.554861111108</v>
+        <v>46139</v>
       </c>
       <c r="Q21" s="34">
-        <v>46069.554861111108</v>
+        <v>46139</v>
       </c>
       <c r="R21" s="10"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="7">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C22" s="7">
-        <v>4</v>
-      </c>
-      <c r="D22" s="8">
-        <v>2</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>140</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
       <c r="F22" s="8" t="s">
-        <v>245</v>
+        <v>319</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>64</v>
+        <v>306</v>
+      </c>
+      <c r="H22" s="42" t="s">
+        <v>307</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>308</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>4</v>
+        <v>223</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L22" s="8">
         <v>1</v>
       </c>
       <c r="M22" s="10"/>
-      <c r="N22" s="10">
-        <v>0</v>
-      </c>
-      <c r="O22" s="10">
-        <v>7</v>
-      </c>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
       <c r="P22" s="34">
-        <v>46069.554861111108</v>
+        <v>46139</v>
       </c>
       <c r="Q22" s="34">
-        <v>46069.554861111108</v>
+        <v>46139</v>
       </c>
       <c r="R22" s="10"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="7">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C23" s="7">
-        <v>5</v>
-      </c>
-      <c r="D23" s="8">
-        <v>5</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>93</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
       <c r="F23" s="8" t="s">
-        <v>148</v>
+        <v>309</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>67</v>
+        <v>310</v>
+      </c>
+      <c r="H23" s="42" t="s">
+        <v>311</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>68</v>
+        <v>312</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>4</v>
+        <v>223</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L23" s="8">
         <v>1</v>
       </c>
       <c r="M23" s="10"/>
-      <c r="N23" s="10">
-        <v>0</v>
-      </c>
-      <c r="O23" s="10">
-        <v>1</v>
-      </c>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
       <c r="P23" s="34">
-        <v>46069.554861111108</v>
+        <v>46139</v>
       </c>
       <c r="Q23" s="34">
-        <v>46069.554861111108</v>
+        <v>46139</v>
       </c>
       <c r="R23" s="10"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="7">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C24" s="7">
-        <v>6</v>
-      </c>
-      <c r="D24" s="8">
-        <v>5</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>93</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
       <c r="F24" s="8" t="s">
-        <v>147</v>
+        <v>320</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>65</v>
+        <v>313</v>
+      </c>
+      <c r="H24" s="42" t="s">
+        <v>300</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>66</v>
+        <v>301</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>4</v>
+        <v>223</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L24" s="8">
         <v>1</v>
       </c>
       <c r="M24" s="10"/>
-      <c r="N24" s="10">
-        <v>0</v>
-      </c>
-      <c r="O24" s="10">
-        <v>8</v>
-      </c>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
       <c r="P24" s="34">
-        <v>46069.554861111108</v>
+        <v>46139</v>
       </c>
       <c r="Q24" s="34">
-        <v>46069.554861111108</v>
+        <v>46139</v>
       </c>
       <c r="R24" s="10"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="7">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C25" s="7">
-        <v>7</v>
-      </c>
-      <c r="D25" s="8">
-        <v>6</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>98</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
       <c r="F25" s="8" t="s">
-        <v>143</v>
+        <v>321</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>69</v>
+        <v>314</v>
+      </c>
+      <c r="H25" s="42" t="s">
+        <v>315</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>70</v>
+        <v>301</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>4</v>
+        <v>223</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="L25" s="11">
+        <v>223</v>
+      </c>
+      <c r="L25" s="8">
         <v>1</v>
       </c>
-      <c r="M25" s="21"/>
-      <c r="N25" s="21">
-        <v>0</v>
-      </c>
-      <c r="O25" s="21">
-        <v>9</v>
-      </c>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
       <c r="P25" s="34">
-        <v>46069.554861111108</v>
+        <v>46139</v>
       </c>
       <c r="Q25" s="34">
-        <v>46069.554861111108</v>
+        <v>46139</v>
       </c>
       <c r="R25" s="10"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="7">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C26" s="7">
-        <v>8</v>
-      </c>
-      <c r="D26" s="8">
-        <v>7</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>92</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
       <c r="F26" s="8" t="s">
-        <v>145</v>
+        <v>322</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>73</v>
+        <v>323</v>
+      </c>
+      <c r="H26" s="42" t="s">
+        <v>324</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>70</v>
+        <v>325</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>4</v>
+        <v>221</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="L26" s="11">
-        <v>1</v>
-      </c>
-      <c r="M26" s="21"/>
-      <c r="N26" s="21">
-        <v>0</v>
-      </c>
-      <c r="O26" s="21">
-        <v>10</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="L26" s="8"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
       <c r="P26" s="34">
-        <v>46069.554861111108</v>
+        <v>46143.497916666667</v>
       </c>
       <c r="Q26" s="34">
-        <v>46069.554861111108</v>
+        <v>46143.497916666667</v>
       </c>
       <c r="R26" s="10"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C27" s="7">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D27" s="8">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>121</v>
+        <v>298</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="J27" s="8" t="s">
         <v>4</v>
@@ -3684,15 +3742,15 @@
       <c r="K27" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="L27" s="11">
+      <c r="L27" s="8">
         <v>1</v>
       </c>
-      <c r="M27" s="21"/>
-      <c r="N27" s="21">
+      <c r="M27" s="10"/>
+      <c r="N27" s="10">
         <v>0</v>
       </c>
-      <c r="O27" s="21">
-        <v>11</v>
+      <c r="O27" s="10">
+        <v>0</v>
       </c>
       <c r="P27" s="34">
         <v>46069.554861111108</v>
@@ -3704,47 +3762,35 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="7">
+        <v>46</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C28" s="7">
+        <v>2</v>
+      </c>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10">
+        <v>0</v>
+      </c>
+      <c r="O28" s="10">
         <v>5</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C28" s="7">
-        <v>10</v>
-      </c>
-      <c r="D28" s="8">
-        <v>8</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="L28" s="11">
-        <v>1</v>
-      </c>
-      <c r="M28" s="21"/>
-      <c r="N28" s="21">
-        <v>0</v>
-      </c>
-      <c r="O28" s="21">
-        <v>12</v>
       </c>
       <c r="P28" s="34">
         <v>46069.554861111108</v>
@@ -3756,83 +3802,71 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="7">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C29" s="7">
-        <v>11</v>
-      </c>
-      <c r="D29" s="12">
-        <v>9</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="G29" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="H29" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="I29" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="J29" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="K29" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="L29" s="13">
-        <v>1</v>
-      </c>
-      <c r="M29" s="22"/>
-      <c r="N29" s="22">
+        <v>3</v>
+      </c>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10">
         <v>0</v>
       </c>
-      <c r="O29" s="22">
-        <v>2</v>
-      </c>
-      <c r="P29" s="35">
+      <c r="O29" s="10">
+        <v>6</v>
+      </c>
+      <c r="P29" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q29" s="35">
+      <c r="Q29" s="34">
         <v>46069.554861111108</v>
       </c>
       <c r="R29" s="10"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="7">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C30" s="7">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D30" s="8">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>141</v>
+        <v>245</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>171</v>
+        <v>246</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>70</v>
+        <v>63</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="J30" s="8" t="s">
         <v>4</v>
@@ -3840,15 +3874,15 @@
       <c r="K30" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="L30" s="11">
+      <c r="L30" s="8">
         <v>1</v>
       </c>
-      <c r="M30" s="21"/>
-      <c r="N30" s="21">
+      <c r="M30" s="10"/>
+      <c r="N30" s="10">
         <v>0</v>
       </c>
-      <c r="O30" s="21">
-        <v>13</v>
+      <c r="O30" s="10">
+        <v>7</v>
       </c>
       <c r="P30" s="34">
         <v>46069.554861111108</v>
@@ -3860,83 +3894,83 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="7">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C31" s="7">
-        <v>13</v>
-      </c>
-      <c r="D31" s="12">
-        <v>11</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="H31" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="I31" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="J31" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="8">
+        <v>5</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="J31" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K31" s="12" t="s">
+      <c r="K31" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="L31" s="13">
+      <c r="L31" s="8">
         <v>1</v>
       </c>
-      <c r="M31" s="22"/>
-      <c r="N31" s="22">
+      <c r="M31" s="10"/>
+      <c r="N31" s="10">
         <v>0</v>
       </c>
-      <c r="O31" s="22">
-        <v>3</v>
-      </c>
-      <c r="P31" s="35">
+      <c r="O31" s="10">
+        <v>1</v>
+      </c>
+      <c r="P31" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q31" s="35">
+      <c r="Q31" s="34">
         <v>46069.554861111108</v>
       </c>
       <c r="R31" s="10"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="7">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C32" s="7">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D32" s="8">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J32" s="8" t="s">
         <v>4</v>
@@ -3944,15 +3978,15 @@
       <c r="K32" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="L32" s="11">
+      <c r="L32" s="8">
         <v>1</v>
       </c>
-      <c r="M32" s="21"/>
-      <c r="N32" s="21">
+      <c r="M32" s="10"/>
+      <c r="N32" s="10">
         <v>0</v>
       </c>
-      <c r="O32" s="21">
-        <v>4</v>
+      <c r="O32" s="10">
+        <v>8</v>
       </c>
       <c r="P32" s="34">
         <v>46069.554861111108</v>
@@ -3964,139 +3998,151 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="7">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C33" s="7">
-        <v>15</v>
-      </c>
-      <c r="D33" s="12">
-        <v>11</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="H33" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I33" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="J33" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="8">
+        <v>6</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="J33" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K33" s="12" t="s">
+      <c r="K33" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="L33" s="13">
+      <c r="L33" s="11">
         <v>1</v>
       </c>
-      <c r="M33" s="22"/>
-      <c r="N33" s="22">
+      <c r="M33" s="21"/>
+      <c r="N33" s="21">
         <v>0</v>
       </c>
-      <c r="O33" s="22">
-        <v>14</v>
-      </c>
-      <c r="P33" s="35">
+      <c r="O33" s="21">
+        <v>9</v>
+      </c>
+      <c r="P33" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q33" s="35">
+      <c r="Q33" s="34">
         <v>46069.554861111108</v>
       </c>
       <c r="R33" s="10"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="7">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C34" s="7">
-        <v>16</v>
-      </c>
-      <c r="D34" s="12">
-        <v>11</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="G34" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="H34" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I34" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="J34" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="8">
+        <v>7</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="J34" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K34" s="12" t="s">
+      <c r="K34" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="L34" s="13">
+      <c r="L34" s="11">
         <v>1</v>
       </c>
-      <c r="M34" s="22"/>
-      <c r="N34" s="22">
+      <c r="M34" s="21"/>
+      <c r="N34" s="21">
         <v>0</v>
       </c>
-      <c r="O34" s="22">
-        <v>15</v>
-      </c>
-      <c r="P34" s="35">
+      <c r="O34" s="21">
+        <v>10</v>
+      </c>
+      <c r="P34" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q34" s="35">
+      <c r="Q34" s="34">
         <v>46069.554861111108</v>
       </c>
       <c r="R34" s="10"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="7">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C35" s="7">
-        <v>17</v>
-      </c>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
+        <v>9</v>
+      </c>
+      <c r="D35" s="8">
+        <v>7</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>92</v>
+      </c>
       <c r="F35" s="8" t="s">
-        <v>206</v>
+        <v>121</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>237</v>
+        <v>168</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10">
+        <v>71</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="L35" s="11">
         <v>1</v>
       </c>
-      <c r="O35" s="10">
+      <c r="M35" s="21"/>
+      <c r="N35" s="21">
         <v>0</v>
+      </c>
+      <c r="O35" s="21">
+        <v>11</v>
       </c>
       <c r="P35" s="34">
         <v>46069.554861111108</v>
@@ -4108,35 +4154,47 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="7">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C36" s="7">
-        <v>18</v>
-      </c>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
+        <v>10</v>
+      </c>
+      <c r="D36" s="8">
+        <v>8</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>100</v>
+      </c>
       <c r="F36" s="8" t="s">
-        <v>207</v>
+        <v>144</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>238</v>
+        <v>169</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="10"/>
-      <c r="N36" s="10">
+        <v>69</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="L36" s="11">
         <v>1</v>
       </c>
-      <c r="O36" s="10">
-        <v>1</v>
+      <c r="M36" s="21"/>
+      <c r="N36" s="21">
+        <v>0</v>
+      </c>
+      <c r="O36" s="21">
+        <v>12</v>
       </c>
       <c r="P36" s="34">
         <v>46069.554861111108</v>
@@ -4148,82 +4206,100 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="7">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C37" s="7">
-        <v>19</v>
-      </c>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10">
+        <v>11</v>
+      </c>
+      <c r="D37" s="12">
+        <v>9</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="K37" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="L37" s="13">
         <v>1</v>
       </c>
-      <c r="O37" s="10">
+      <c r="M37" s="22"/>
+      <c r="N37" s="22">
+        <v>0</v>
+      </c>
+      <c r="O37" s="22">
         <v>2</v>
       </c>
-      <c r="P37" s="34">
+      <c r="P37" s="35">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q37" s="34">
+      <c r="Q37" s="35">
         <v>46069.554861111108</v>
       </c>
       <c r="R37" s="10"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="7">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C38" s="7">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D38" s="8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>268</v>
+        <v>141</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>270</v>
+        <v>171</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>269</v>
+        <v>74</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>272</v>
+        <v>70</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>271</v>
+        <v>4</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="L38" s="8"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="10"/>
-      <c r="O38" s="10"/>
+        <v>224</v>
+      </c>
+      <c r="L38" s="11">
+        <v>1</v>
+      </c>
+      <c r="M38" s="21"/>
+      <c r="N38" s="21">
+        <v>0</v>
+      </c>
+      <c r="O38" s="21">
+        <v>13</v>
+      </c>
       <c r="P38" s="34">
         <v>46069.554861111108</v>
       </c>
@@ -4233,221 +4309,245 @@
       <c r="R38" s="10"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="26">
-        <v>12</v>
-      </c>
-      <c r="B39" s="26" t="s">
+      <c r="A39" s="7">
+        <v>11</v>
+      </c>
+      <c r="B39" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C39" s="26"/>
-      <c r="D39" s="14">
+      <c r="C39" s="7">
+        <v>13</v>
+      </c>
+      <c r="D39" s="12">
         <v>11</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14" t="s">
+      <c r="F39" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="H39" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="I39" s="14" t="s">
+      <c r="I39" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="J39" s="14" t="s">
+      <c r="J39" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="K39" s="14" t="s">
+      <c r="K39" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="L39" s="15">
+      <c r="L39" s="13">
         <v>1</v>
       </c>
-      <c r="M39" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="N39" s="23"/>
-      <c r="O39" s="23"/>
-      <c r="P39" s="36">
+      <c r="M39" s="22"/>
+      <c r="N39" s="22">
+        <v>0</v>
+      </c>
+      <c r="O39" s="22">
+        <v>3</v>
+      </c>
+      <c r="P39" s="35">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q39" s="36">
+      <c r="Q39" s="35">
         <v>46069.554861111108</v>
       </c>
       <c r="R39" s="10"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="26">
-        <v>16</v>
-      </c>
-      <c r="B40" s="26" t="s">
+      <c r="A40" s="7">
+        <v>13</v>
+      </c>
+      <c r="B40" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C40" s="26"/>
-      <c r="D40" s="14">
+      <c r="C40" s="7">
+        <v>14</v>
+      </c>
+      <c r="D40" s="8">
         <v>11</v>
       </c>
-      <c r="E40" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="I40" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="J40" s="14" t="s">
+      <c r="E40" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="J40" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K40" s="14" t="s">
+      <c r="K40" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="L40" s="15">
+      <c r="L40" s="11">
         <v>1</v>
       </c>
-      <c r="M40" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="N40" s="23"/>
-      <c r="O40" s="23"/>
-      <c r="P40" s="36">
+      <c r="M40" s="21"/>
+      <c r="N40" s="21">
+        <v>0</v>
+      </c>
+      <c r="O40" s="21">
+        <v>4</v>
+      </c>
+      <c r="P40" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q40" s="36">
+      <c r="Q40" s="34">
         <v>46069.554861111108</v>
       </c>
       <c r="R40" s="10"/>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="26">
-        <v>17</v>
-      </c>
-      <c r="B41" s="26" t="s">
+      <c r="A41" s="7">
+        <v>14</v>
+      </c>
+      <c r="B41" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C41" s="26"/>
-      <c r="D41" s="14">
+      <c r="C41" s="7">
+        <v>15</v>
+      </c>
+      <c r="D41" s="12">
         <v>11</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E41" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14" t="s">
+      <c r="F41" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="H41" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="I41" s="14" t="s">
+      <c r="I41" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="J41" s="14" t="s">
+      <c r="J41" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="K41" s="14" t="s">
+      <c r="K41" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="L41" s="15">
+      <c r="L41" s="13">
         <v>1</v>
       </c>
-      <c r="M41" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="N41" s="23"/>
-      <c r="O41" s="23"/>
-      <c r="P41" s="36">
+      <c r="M41" s="22"/>
+      <c r="N41" s="22">
+        <v>0</v>
+      </c>
+      <c r="O41" s="22">
+        <v>14</v>
+      </c>
+      <c r="P41" s="35">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q41" s="36">
+      <c r="Q41" s="35">
         <v>46069.554861111108</v>
       </c>
       <c r="R41" s="10"/>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="7">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C42" s="7">
+        <v>16</v>
+      </c>
+      <c r="D42" s="12">
+        <v>11</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="J42" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="K42" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="L42" s="13">
         <v>1</v>
       </c>
-      <c r="D42" s="8">
-        <v>1</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I42" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="J42" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="K42" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="L42" s="8">
-        <v>1</v>
-      </c>
-      <c r="M42" s="10"/>
-      <c r="N42" s="10"/>
-      <c r="O42" s="10"/>
-      <c r="P42" s="34">
+      <c r="M42" s="22"/>
+      <c r="N42" s="22">
+        <v>0</v>
+      </c>
+      <c r="O42" s="22">
+        <v>15</v>
+      </c>
+      <c r="P42" s="35">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q42" s="34">
+      <c r="Q42" s="35">
         <v>46069.554861111108</v>
       </c>
       <c r="R42" s="10"/>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="7">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8">
-        <v>3</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>94</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="C43" s="7">
+        <v>17</v>
+      </c>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
       <c r="F43" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G43" s="8"/>
+        <v>206</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>237</v>
+      </c>
       <c r="H43" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I43" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J43" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="K43" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="L43" s="8">
+        <v>51</v>
+      </c>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="10">
         <v>1</v>
       </c>
-      <c r="M43" s="10"/>
-      <c r="N43" s="10"/>
-      <c r="O43" s="10"/>
+      <c r="O43" s="10">
+        <v>0</v>
+      </c>
       <c r="P43" s="34">
         <v>46069.554861111108</v>
       </c>
@@ -4458,40 +4558,36 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="7">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8">
-        <v>3</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>94</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="C44" s="7">
+        <v>18</v>
+      </c>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
       <c r="F44" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G44" s="8"/>
+        <v>207</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>238</v>
+      </c>
       <c r="H44" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I44" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="J44" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="K44" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="L44" s="8">
+        <v>51</v>
+      </c>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="10">
         <v>1</v>
       </c>
-      <c r="M44" s="10"/>
-      <c r="N44" s="10"/>
-      <c r="O44" s="10"/>
+      <c r="O44" s="10">
+        <v>1</v>
+      </c>
       <c r="P44" s="34">
         <v>46069.554861111108</v>
       </c>
@@ -4502,38 +4598,36 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="7">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8">
-        <v>7</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
+        <v>114</v>
+      </c>
+      <c r="C45" s="7">
+        <v>19</v>
+      </c>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>239</v>
+      </c>
       <c r="H45" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I45" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="J45" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="K45" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="L45" s="8">
-        <v>3</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
       <c r="M45" s="10"/>
-      <c r="N45" s="10"/>
-      <c r="O45" s="10"/>
+      <c r="N45" s="10">
+        <v>1</v>
+      </c>
+      <c r="O45" s="10">
+        <v>2</v>
+      </c>
       <c r="P45" s="34">
         <v>46069.554861111108</v>
       </c>
@@ -4544,40 +4638,40 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="7">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C46" s="7"/>
+        <v>114</v>
+      </c>
+      <c r="C46" s="7">
+        <v>20</v>
+      </c>
       <c r="D46" s="8">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="G46" s="8"/>
+        <v>268</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>270</v>
+      </c>
       <c r="H46" s="8" t="s">
-        <v>25</v>
+        <v>269</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>24</v>
+        <v>272</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>222</v>
+        <v>271</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="L46" s="8">
-        <v>1</v>
-      </c>
-      <c r="M46" s="10" t="s">
-        <v>57</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="L46" s="8"/>
+      <c r="M46" s="10"/>
       <c r="N46" s="10"/>
       <c r="O46" s="10"/>
       <c r="P46" s="34">
@@ -4589,156 +4683,170 @@
       <c r="R46" s="10"/>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="7">
-        <v>34</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8">
+      <c r="A47" s="26">
+        <v>12</v>
+      </c>
+      <c r="B47" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="C47" s="26"/>
+      <c r="D47" s="14">
+        <v>11</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J47" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="K47" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="L47" s="15">
         <v>1</v>
       </c>
-      <c r="E47" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I47" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="J47" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="K47" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="L47" s="8">
-        <v>1</v>
-      </c>
-      <c r="M47" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="N47" s="10"/>
-      <c r="O47" s="10"/>
-      <c r="P47" s="34">
+      <c r="M47" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="N47" s="23"/>
+      <c r="O47" s="23"/>
+      <c r="P47" s="36">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q47" s="34">
+      <c r="Q47" s="36">
         <v>46069.554861111108</v>
       </c>
       <c r="R47" s="10"/>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="7">
-        <v>26</v>
-      </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8">
+      <c r="A48" s="26">
+        <v>16</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48" s="26"/>
+      <c r="D48" s="14">
+        <v>11</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J48" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="K48" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="L48" s="15">
         <v>1</v>
       </c>
-      <c r="E48" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I48" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="J48" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="K48" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="L48" s="8">
-        <v>1</v>
-      </c>
-      <c r="M48" s="10"/>
-      <c r="N48" s="10"/>
-      <c r="O48" s="10"/>
-      <c r="P48" s="34">
+      <c r="M48" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="N48" s="23"/>
+      <c r="O48" s="23"/>
+      <c r="P48" s="36">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q48" s="34">
+      <c r="Q48" s="36">
         <v>46069.554861111108</v>
       </c>
       <c r="R48" s="10"/>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="7">
-        <v>27</v>
-      </c>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="8">
-        <v>5</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="I49" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J49" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="K49" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="L49" s="8">
+      <c r="A49" s="26">
+        <v>17</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="C49" s="26"/>
+      <c r="D49" s="14">
+        <v>11</v>
+      </c>
+      <c r="E49" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I49" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J49" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="K49" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="L49" s="15">
         <v>1</v>
       </c>
-      <c r="M49" s="10"/>
-      <c r="N49" s="10"/>
-      <c r="O49" s="10"/>
-      <c r="P49" s="34">
+      <c r="M49" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="N49" s="23"/>
+      <c r="O49" s="23"/>
+      <c r="P49" s="36">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q49" s="34">
+      <c r="Q49" s="36">
         <v>46069.554861111108</v>
       </c>
       <c r="R49" s="10"/>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="7">
-        <v>28</v>
-      </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
+        <v>21</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C50" s="7">
+        <v>1</v>
+      </c>
       <c r="D50" s="8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
+        <v>99</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>202</v>
+      </c>
       <c r="H50" s="8" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>222</v>
+        <v>2</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L50" s="8">
         <v>1</v>
@@ -4756,9 +4864,11 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="7">
-        <v>31</v>
-      </c>
-      <c r="B51" s="7"/>
+        <v>24</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>119</v>
+      </c>
       <c r="C51" s="7"/>
       <c r="D51" s="8">
         <v>3</v>
@@ -4766,13 +4876,15 @@
       <c r="E51" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="F51" s="8"/>
+      <c r="F51" s="8" t="s">
+        <v>90</v>
+      </c>
       <c r="G51" s="8"/>
       <c r="H51" s="8" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J51" s="8" t="s">
         <v>222</v>
@@ -4783,9 +4895,7 @@
       <c r="L51" s="8">
         <v>1</v>
       </c>
-      <c r="M51" s="10" t="s">
-        <v>57</v>
-      </c>
+      <c r="M51" s="10"/>
       <c r="N51" s="10"/>
       <c r="O51" s="10"/>
       <c r="P51" s="34">
@@ -4798,23 +4908,27 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="7">
-        <v>39</v>
-      </c>
-      <c r="B52" s="7"/>
+        <v>25</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>119</v>
+      </c>
       <c r="C52" s="7"/>
       <c r="D52" s="8">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="F52" s="8"/>
+        <v>94</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>90</v>
+      </c>
       <c r="G52" s="8"/>
       <c r="H52" s="8" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J52" s="8" t="s">
         <v>222</v>
@@ -4838,27 +4952,35 @@
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="7">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="C53" s="7">
-        <v>1</v>
-      </c>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="G53" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="H53" s="8"/>
-      <c r="I53" s="8"/>
-      <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
-      <c r="L53" s="8"/>
+        <v>119</v>
+      </c>
+      <c r="C53" s="7"/>
+      <c r="D53" s="8">
+        <v>7</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J53" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="K53" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="L53" s="8">
+        <v>3</v>
+      </c>
       <c r="M53" s="10"/>
       <c r="N53" s="10"/>
       <c r="O53" s="10"/>
@@ -4872,28 +4994,40 @@
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="7">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="C54" s="7">
-        <v>2</v>
-      </c>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
+        <v>119</v>
+      </c>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8">
+        <v>1</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>99</v>
+      </c>
       <c r="F54" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="H54" s="8"/>
-      <c r="I54" s="8"/>
-      <c r="J54" s="8"/>
-      <c r="K54" s="8"/>
-      <c r="L54" s="8"/>
-      <c r="M54" s="10"/>
+        <v>108</v>
+      </c>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="L54" s="8">
+        <v>1</v>
+      </c>
+      <c r="M54" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="N54" s="10"/>
       <c r="O54" s="10"/>
       <c r="P54" s="34">
@@ -4906,28 +5040,40 @@
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="7">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="C55" s="7">
-        <v>3</v>
-      </c>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
+        <v>119</v>
+      </c>
+      <c r="C55" s="7"/>
+      <c r="D55" s="8">
+        <v>1</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>99</v>
+      </c>
       <c r="F55" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="G55" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="H55" s="8"/>
-      <c r="I55" s="8"/>
-      <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
-      <c r="L55" s="8"/>
-      <c r="M55" s="10"/>
+        <v>109</v>
+      </c>
+      <c r="G55" s="8"/>
+      <c r="H55" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I55" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="K55" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="L55" s="8">
+        <v>1</v>
+      </c>
+      <c r="M55" s="10" t="s">
+        <v>34</v>
+      </c>
       <c r="N55" s="10"/>
       <c r="O55" s="10"/>
       <c r="P55" s="34">
@@ -4940,27 +5086,33 @@
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="7">
-        <v>54</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="C56" s="7">
-        <v>4</v>
-      </c>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="G56" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="H56" s="8"/>
-      <c r="I56" s="8"/>
-      <c r="J56" s="8"/>
-      <c r="K56" s="8"/>
-      <c r="L56" s="8"/>
+        <v>26</v>
+      </c>
+      <c r="B56" s="7"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="8">
+        <v>1</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F56" s="8"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="K56" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="L56" s="8">
+        <v>1</v>
+      </c>
       <c r="M56" s="10"/>
       <c r="N56" s="10"/>
       <c r="O56" s="10"/>
@@ -4974,27 +5126,33 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="7">
-        <v>55</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="C57" s="7">
+        <v>27</v>
+      </c>
+      <c r="B57" s="7"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="8">
         <v>5</v>
       </c>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="G57" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="H57" s="8"/>
-      <c r="I57" s="8"/>
-      <c r="J57" s="8"/>
-      <c r="K57" s="8"/>
-      <c r="L57" s="8"/>
+      <c r="E57" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F57" s="8"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="K57" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="L57" s="8">
+        <v>1</v>
+      </c>
       <c r="M57" s="10"/>
       <c r="N57" s="10"/>
       <c r="O57" s="10"/>
@@ -5008,27 +5166,33 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="7">
-        <v>56</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="C58" s="7">
-        <v>6</v>
-      </c>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="G58" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="H58" s="8"/>
-      <c r="I58" s="8"/>
-      <c r="J58" s="8"/>
-      <c r="K58" s="8"/>
-      <c r="L58" s="8"/>
+        <v>28</v>
+      </c>
+      <c r="B58" s="7"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8">
+        <v>5</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F58" s="8"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="K58" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="L58" s="8">
+        <v>1</v>
+      </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10"/>
       <c r="O58" s="10"/>
@@ -5042,78 +5206,92 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="7">
-        <v>60</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="C59" s="7">
-        <v>7</v>
-      </c>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="H59" s="8"/>
-      <c r="I59" s="8"/>
-      <c r="J59" s="8"/>
-      <c r="K59" s="8"/>
-      <c r="L59" s="8"/>
-      <c r="M59" s="10"/>
+        <v>31</v>
+      </c>
+      <c r="B59" s="7"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="8">
+        <v>3</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J59" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="K59" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="L59" s="8">
+        <v>1</v>
+      </c>
+      <c r="M59" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="N59" s="10"/>
       <c r="O59" s="10"/>
       <c r="P59" s="34">
-        <v>46069.809027777781</v>
+        <v>46069.554861111108</v>
       </c>
       <c r="Q59" s="34">
-        <v>46069.809027777781</v>
+        <v>46069.554861111108</v>
       </c>
       <c r="R59" s="10"/>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="7">
-        <v>65</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="C60" s="7">
-        <v>8</v>
-      </c>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="G60" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="H60" s="8"/>
-      <c r="I60" s="8"/>
-      <c r="J60" s="8"/>
-      <c r="K60" s="8"/>
-      <c r="L60" s="8"/>
+        <v>39</v>
+      </c>
+      <c r="B60" s="7"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="8">
+        <v>7</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F60" s="8"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J60" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="K60" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="L60" s="8">
+        <v>1</v>
+      </c>
       <c r="M60" s="10"/>
       <c r="N60" s="10"/>
       <c r="O60" s="10"/>
       <c r="P60" s="34">
-        <v>46085.347222222219</v>
+        <v>46069.554861111108</v>
       </c>
       <c r="Q60" s="34">
-        <v>46085.347222222219</v>
+        <v>46069.554861111108</v>
       </c>
       <c r="R60" s="10"/>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="7">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>286</v>
+        <v>261</v>
       </c>
       <c r="C61" s="7">
         <v>1</v>
@@ -5121,10 +5299,10 @@
       <c r="D61" s="8"/>
       <c r="E61" s="8"/>
       <c r="F61" s="8" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
@@ -5138,16 +5316,16 @@
         <v>46069.554861111108</v>
       </c>
       <c r="Q61" s="34">
-        <v>46077.372916666667</v>
+        <v>46069.554861111108</v>
       </c>
       <c r="R61" s="10"/>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="7">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="C62" s="7">
         <v>2</v>
@@ -5155,10 +5333,10 @@
       <c r="D62" s="8"/>
       <c r="E62" s="8"/>
       <c r="F62" s="8" t="s">
-        <v>288</v>
+        <v>249</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>289</v>
+        <v>255</v>
       </c>
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
@@ -5169,30 +5347,30 @@
       <c r="N62" s="10"/>
       <c r="O62" s="10"/>
       <c r="P62" s="34">
-        <v>46077.372916666667</v>
+        <v>46069.554861111108</v>
       </c>
       <c r="Q62" s="34">
-        <v>46077.372916666667</v>
+        <v>46069.554861111108</v>
       </c>
       <c r="R62" s="10"/>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="7">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>290</v>
+        <v>261</v>
       </c>
       <c r="C63" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
       <c r="F63" s="8" t="s">
-        <v>294</v>
+        <v>250</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>295</v>
+        <v>256</v>
       </c>
       <c r="H63" s="8"/>
       <c r="I63" s="8"/>
@@ -5203,30 +5381,30 @@
       <c r="N63" s="10"/>
       <c r="O63" s="10"/>
       <c r="P63" s="34">
-        <v>46083.387499999997</v>
+        <v>46069.554861111108</v>
       </c>
       <c r="Q63" s="34">
-        <v>46083.387499999997</v>
+        <v>46069.554861111108</v>
       </c>
       <c r="R63" s="10"/>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="7">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>290</v>
+        <v>261</v>
       </c>
       <c r="C64" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
       <c r="F64" s="8" t="s">
-        <v>294</v>
+        <v>251</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>295</v>
+        <v>257</v>
       </c>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
@@ -5237,30 +5415,30 @@
       <c r="N64" s="10"/>
       <c r="O64" s="10"/>
       <c r="P64" s="34">
-        <v>46083.387499999997</v>
+        <v>46069.554861111108</v>
       </c>
       <c r="Q64" s="34">
-        <v>46083.387499999997</v>
+        <v>46069.554861111108</v>
       </c>
       <c r="R64" s="10"/>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="7">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>290</v>
+        <v>261</v>
       </c>
       <c r="C65" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
       <c r="F65" s="8" t="s">
-        <v>291</v>
+        <v>252</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>292</v>
+        <v>258</v>
       </c>
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
@@ -5271,286 +5449,558 @@
       <c r="N65" s="10"/>
       <c r="O65" s="10"/>
       <c r="P65" s="34">
-        <v>46083.363888888889</v>
+        <v>46069.554861111108</v>
       </c>
       <c r="Q65" s="34">
-        <v>46083.363888888889</v>
+        <v>46069.554861111108</v>
       </c>
       <c r="R65" s="10"/>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="18"/>
-      <c r="B66" s="18"/>
-      <c r="C66" s="18"/>
-      <c r="D66" s="19"/>
-      <c r="E66" s="19"/>
-      <c r="F66" s="19"/>
-      <c r="G66" s="19"/>
-      <c r="H66" s="19"/>
-      <c r="I66" s="19"/>
-      <c r="J66" s="19"/>
-      <c r="K66" s="19"/>
-      <c r="L66" s="19"/>
-      <c r="M66" s="20"/>
-      <c r="N66" s="20"/>
-      <c r="O66" s="20"/>
-      <c r="P66" s="37"/>
-      <c r="Q66" s="37"/>
-      <c r="R66" s="20"/>
+      <c r="A66" s="7">
+        <v>56</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C66" s="7">
+        <v>6</v>
+      </c>
+      <c r="D66" s="8"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="H66" s="8"/>
+      <c r="I66" s="8"/>
+      <c r="J66" s="8"/>
+      <c r="K66" s="8"/>
+      <c r="L66" s="8"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="10"/>
+      <c r="O66" s="10"/>
+      <c r="P66" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="Q66" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="R66" s="10"/>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="7">
+        <v>60</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="C67" s="7">
+        <v>7</v>
+      </c>
+      <c r="D67" s="8"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="H67" s="8"/>
+      <c r="I67" s="8"/>
+      <c r="J67" s="8"/>
+      <c r="K67" s="8"/>
+      <c r="L67" s="8"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="10"/>
+      <c r="O67" s="10"/>
+      <c r="P67" s="34">
+        <v>46069.809027777781</v>
+      </c>
+      <c r="Q67" s="34">
+        <v>46069.809027777781</v>
+      </c>
+      <c r="R67" s="10"/>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" t="s">
-        <v>111</v>
-      </c>
-      <c r="D68" t="s">
-        <v>110</v>
-      </c>
+      <c r="A68" s="7">
+        <v>65</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="C68" s="7">
+        <v>8</v>
+      </c>
+      <c r="D68" s="8"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="H68" s="8"/>
+      <c r="I68" s="8"/>
+      <c r="J68" s="8"/>
+      <c r="K68" s="8"/>
+      <c r="L68" s="8"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="10"/>
+      <c r="O68" s="10"/>
+      <c r="P68" s="34">
+        <v>46085.347222222219</v>
+      </c>
+      <c r="Q68" s="34">
+        <v>46085.347222222219</v>
+      </c>
+      <c r="R68" s="10"/>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69">
-        <f>MAX(A$2:A$66)</f>
-        <v>65</v>
-      </c>
-      <c r="D69">
-        <f>MAX(D$2:D$66)</f>
-        <v>11</v>
-      </c>
+      <c r="A69" s="7">
+        <v>57</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="C69" s="7">
+        <v>1</v>
+      </c>
+      <c r="D69" s="8"/>
+      <c r="E69" s="8"/>
+      <c r="F69" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="H69" s="8"/>
+      <c r="I69" s="8"/>
+      <c r="J69" s="8"/>
+      <c r="K69" s="8"/>
+      <c r="L69" s="8"/>
+      <c r="M69" s="10"/>
+      <c r="N69" s="10"/>
+      <c r="O69" s="10"/>
+      <c r="P69" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="Q69" s="34">
+        <v>46077.372916666667</v>
+      </c>
+      <c r="R69" s="10"/>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" t="s">
-        <v>198</v>
-      </c>
-      <c r="B70" t="s">
-        <v>117</v>
-      </c>
-      <c r="C70" t="s">
-        <v>116</v>
-      </c>
+      <c r="A70" s="7">
+        <v>61</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="C70" s="7">
+        <v>2</v>
+      </c>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="H70" s="8"/>
+      <c r="I70" s="8"/>
+      <c r="J70" s="8"/>
+      <c r="K70" s="8"/>
+      <c r="L70" s="8"/>
+      <c r="M70" s="10"/>
+      <c r="N70" s="10"/>
+      <c r="O70" s="10"/>
+      <c r="P70" s="34">
+        <v>46077.372916666667</v>
+      </c>
+      <c r="Q70" s="34">
+        <v>46077.372916666667</v>
+      </c>
+      <c r="R70" s="10"/>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71">
-        <f>ROW(A67)-ROW(A1)-1</f>
-        <v>65</v>
-      </c>
-      <c r="B71">
-        <f>COUNTIF(B$2:B$66,B70)</f>
-        <v>17</v>
-      </c>
-      <c r="C71" s="25">
-        <f>_xlfn.MAXIFS(C$2:C$66,$B$2:$B$66,C70)</f>
-        <v>17</v>
-      </c>
+      <c r="A71" s="7">
+        <v>62</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="C71" s="7">
+        <v>1</v>
+      </c>
+      <c r="D71" s="8"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="H71" s="8"/>
+      <c r="I71" s="8"/>
+      <c r="J71" s="8"/>
+      <c r="K71" s="8"/>
+      <c r="L71" s="8"/>
+      <c r="M71" s="10"/>
+      <c r="N71" s="10"/>
+      <c r="O71" s="10"/>
+      <c r="P71" s="34">
+        <v>46083.387499999997</v>
+      </c>
+      <c r="Q71" s="34">
+        <v>46083.387499999997</v>
+      </c>
+      <c r="R71" s="10"/>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" t="s">
-        <v>114</v>
-      </c>
-      <c r="C72" t="s">
-        <v>114</v>
-      </c>
+      <c r="A72" s="7">
+        <v>63</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="C72" s="7">
+        <v>2</v>
+      </c>
+      <c r="D72" s="8"/>
+      <c r="E72" s="8"/>
+      <c r="F72" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="H72" s="8"/>
+      <c r="I72" s="8"/>
+      <c r="J72" s="8"/>
+      <c r="K72" s="8"/>
+      <c r="L72" s="8"/>
+      <c r="M72" s="10"/>
+      <c r="N72" s="10"/>
+      <c r="O72" s="10"/>
+      <c r="P72" s="34">
+        <v>46083.387499999997</v>
+      </c>
+      <c r="Q72" s="34">
+        <v>46083.387499999997</v>
+      </c>
+      <c r="R72" s="10"/>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73">
-        <f>COUNTIF(B$2:B$66,B72)</f>
-        <v>23</v>
-      </c>
-      <c r="C73" s="25">
-        <f>_xlfn.MAXIFS(C$2:C$66,$B$2:$B$66,C72)</f>
-        <v>20</v>
-      </c>
+      <c r="A73" s="7">
+        <v>64</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="C73" s="7">
+        <v>3</v>
+      </c>
+      <c r="D73" s="8"/>
+      <c r="E73" s="8"/>
+      <c r="F73" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="H73" s="8"/>
+      <c r="I73" s="8"/>
+      <c r="J73" s="8"/>
+      <c r="K73" s="8"/>
+      <c r="L73" s="8"/>
+      <c r="M73" s="10"/>
+      <c r="N73" s="10"/>
+      <c r="O73" s="10"/>
+      <c r="P73" s="34">
+        <v>46083.363888888889</v>
+      </c>
+      <c r="Q73" s="34">
+        <v>46083.363888888889</v>
+      </c>
+      <c r="R73" s="10"/>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="18"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="19"/>
+      <c r="E74" s="19"/>
+      <c r="F74" s="19"/>
+      <c r="G74" s="19"/>
+      <c r="H74" s="19"/>
+      <c r="I74" s="19"/>
+      <c r="J74" s="19"/>
+      <c r="K74" s="19"/>
+      <c r="L74" s="19"/>
+      <c r="M74" s="20"/>
+      <c r="N74" s="20"/>
+      <c r="O74" s="20"/>
+      <c r="P74" s="37"/>
+      <c r="Q74" s="37"/>
+      <c r="R74" s="20"/>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H76" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L76">
-        <v>1</v>
-      </c>
-      <c r="R76" t="s">
-        <v>79</v>
+      <c r="A76" t="s">
+        <v>111</v>
+      </c>
+      <c r="D76" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H77" t="s">
-        <v>56</v>
-      </c>
-      <c r="I77" t="s">
-        <v>53</v>
-      </c>
-      <c r="J77" t="s">
-        <v>52</v>
-      </c>
-      <c r="L77">
-        <v>1</v>
-      </c>
-      <c r="R77" t="s">
-        <v>79</v>
+      <c r="A77">
+        <f>MAX(A$2:A$74)</f>
+        <v>73</v>
+      </c>
+      <c r="D77">
+        <f>MAX(D$2:D$74)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" t="s">
+        <v>198</v>
+      </c>
+      <c r="B78" t="s">
+        <v>117</v>
+      </c>
+      <c r="C78" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H79" s="2" t="s">
-        <v>38</v>
+      <c r="A79">
+        <f>ROW(A75)-ROW(A1)-1</f>
+        <v>73</v>
+      </c>
+      <c r="B79">
+        <f>COUNTIF(B$2:B$74,B78)</f>
+        <v>25</v>
+      </c>
+      <c r="C79" s="25">
+        <f>_xlfn.MAXIFS(C$2:C$74,$B$2:$B$74,C78)</f>
+        <v>25</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H80" t="s">
+      <c r="B80" t="s">
+        <v>114</v>
+      </c>
+      <c r="C80" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="81" spans="2:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B81">
+        <f>COUNTIF(B$2:B$74,B80)</f>
+        <v>23</v>
+      </c>
+      <c r="C81" s="25">
+        <f>_xlfn.MAXIFS(C$2:C$74,$B$2:$B$74,C80)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84" spans="2:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="H84" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L84">
+        <v>1</v>
+      </c>
+      <c r="R84" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="85" spans="2:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="H85" t="s">
+        <v>56</v>
+      </c>
+      <c r="I85" t="s">
+        <v>53</v>
+      </c>
+      <c r="J85" t="s">
+        <v>52</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="R85" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="87" spans="2:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="H87" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="88" spans="2:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="H88" t="s">
         <v>82</v>
       </c>
-      <c r="I80" t="s">
+      <c r="I88" t="s">
         <v>84</v>
       </c>
-      <c r="J80" t="s">
+      <c r="J88" t="s">
         <v>80</v>
       </c>
-      <c r="L80">
+      <c r="L88">
         <v>1</v>
       </c>
-      <c r="R80" t="s">
+      <c r="R88" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="82" spans="8:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H82" s="2" t="s">
+    <row r="90" spans="2:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="H90" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="83" spans="8:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H83" t="s">
+    <row r="91" spans="2:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="H91" t="s">
         <v>83</v>
       </c>
-      <c r="I83" t="s">
+      <c r="I91" t="s">
         <v>84</v>
       </c>
-      <c r="J83" t="s">
+      <c r="J91" t="s">
         <v>81</v>
-      </c>
-      <c r="L83">
-        <v>1</v>
-      </c>
-      <c r="R83" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="85" spans="8:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H85" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="86" spans="8:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H86" t="s">
-        <v>42</v>
-      </c>
-      <c r="I86" t="s">
-        <v>43</v>
-      </c>
-      <c r="J86" t="s">
-        <v>12</v>
-      </c>
-      <c r="L86">
-        <v>1</v>
-      </c>
-      <c r="R86" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="87" spans="8:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H87" t="s">
-        <v>45</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J87" t="s">
-        <v>44</v>
-      </c>
-      <c r="L87">
-        <v>2</v>
-      </c>
-      <c r="R87" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="89" spans="8:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H89" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="90" spans="8:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H90" t="s">
-        <v>46</v>
-      </c>
-      <c r="I90" t="s">
-        <v>47</v>
-      </c>
-      <c r="J90" t="s">
-        <v>12</v>
-      </c>
-      <c r="L90">
-        <v>1</v>
-      </c>
-      <c r="R90" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="91" spans="8:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H91" t="s">
-        <v>50</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J91" t="s">
-        <v>49</v>
       </c>
       <c r="L91">
         <v>1</v>
       </c>
       <c r="R91" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="93" spans="2:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="H93" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="94" spans="2:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="H94" t="s">
+        <v>42</v>
+      </c>
+      <c r="I94" t="s">
+        <v>43</v>
+      </c>
+      <c r="J94" t="s">
+        <v>12</v>
+      </c>
+      <c r="L94">
+        <v>1</v>
+      </c>
+      <c r="R94" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="92" spans="8:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H92" t="s">
+    <row r="95" spans="2:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="H95" t="s">
+        <v>45</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J95" t="s">
+        <v>44</v>
+      </c>
+      <c r="L95">
+        <v>2</v>
+      </c>
+      <c r="R95" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="97" spans="8:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="H97" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="98" spans="8:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="H98" t="s">
+        <v>46</v>
+      </c>
+      <c r="I98" t="s">
+        <v>47</v>
+      </c>
+      <c r="J98" t="s">
+        <v>12</v>
+      </c>
+      <c r="L98">
+        <v>1</v>
+      </c>
+      <c r="R98" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="99" spans="8:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="H99" t="s">
+        <v>50</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J99" t="s">
+        <v>49</v>
+      </c>
+      <c r="L99">
+        <v>1</v>
+      </c>
+      <c r="R99" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="100" spans="8:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="H100" t="s">
         <v>51</v>
       </c>
-      <c r="I92" t="s">
+      <c r="I100" t="s">
         <v>55</v>
       </c>
-      <c r="J92" t="s">
+      <c r="J100" t="s">
         <v>4</v>
       </c>
-      <c r="L92">
+      <c r="L100">
         <v>2</v>
       </c>
-      <c r="R92" t="s">
+      <c r="R100" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="93" spans="8:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H93" t="s">
+    <row r="101" spans="8:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="H101" t="s">
         <v>85</v>
       </c>
-      <c r="I93" t="s">
+      <c r="I101" t="s">
         <v>86</v>
       </c>
-      <c r="J93" t="s">
+      <c r="J101" t="s">
         <v>88</v>
       </c>
-      <c r="L93">
+      <c r="L101">
         <v>1</v>
       </c>
-      <c r="R93" t="s">
+      <c r="R101" t="s">
         <v>87</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R52" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R52">
-      <sortCondition ref="B1:B52"/>
+  <autoFilter ref="A1:R60" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R60">
+      <sortCondition ref="B1:B60"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A2:R17 A18:G18 I18:R18 A19:R66">
+  <conditionalFormatting sqref="A2:R74">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>MOD(ROW(A2),2)=1</formula>
     </cfRule>
@@ -5701,7 +6151,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index</v>
+        <v>C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_index</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
@@ -5711,11 +6161,11 @@
         <v>1</v>
       </c>
       <c r="H3" cm="1">
-        <f t="array" ref="H3:H202">IFERROR(MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$66&amp;info_index!$C$2:$C$66,0),"")</f>
+        <f t="array" ref="H3:H202">IFERROR(MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$74&amp;info_index!$C$2:$C$74,0),"")</f>
         <v>1</v>
       </c>
       <c r="I3" t="str" cm="1">
-        <f t="array" aca="1" ref="I3:I202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(H3)),INDEX(OFFSET(info_index!$F$2:$F$66,0,$B$23),MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$66&amp;info_index!$C$2:$C$66,0)&amp;"",1),"")</f>
+        <f t="array" aca="1" ref="I3:I202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(H3)),INDEX(OFFSET(info_index!$F$2:$F$74,0,$B$23),MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$74&amp;info_index!$C$2:$C$74,0)&amp;"",1),"")</f>
         <v>箔ロウリール軸</v>
       </c>
       <c r="J3" t="str" cm="1">
@@ -5727,7 +6177,7 @@
         <v>【axis1】 箔ロウリール軸</v>
       </c>
       <c r="M3" t="str" cm="1">
-        <f t="array" ref="M3:M202">IFERROR(INDEX(info_index!$H$2:$H$66,MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$66&amp;info_index!$C$2:$C$66,0),1)&amp;"","")</f>
+        <f t="array" ref="M3:M202">IFERROR(INDEX(info_index!$H$2:$H$74,MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$74&amp;info_index!$C$2:$C$74,0),1)&amp;"","")</f>
         <v>5TK20GN-CW2J+5GN180K</v>
       </c>
       <c r="N3" t="str" cm="1">
@@ -5735,7 +6185,7 @@
         <v>5TK20GN-CW2J+5GN180K</v>
       </c>
       <c r="O3" t="str" cm="1">
-        <f t="array" aca="1" ref="O3:O202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(H3)),INDEX(OFFSET(info_index!$J$2:$J$66,0,$B$23),MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$66&amp;info_index!$C$2:$C$66,0),1)&amp;"","")</f>
+        <f t="array" aca="1" ref="O3:O202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(H3)),INDEX(OFFSET(info_index!$J$2:$J$74,0,$B$23),MATCH($E$3:$E$202&amp;$F$3:$F$202,info_index!$B$2:$B$74&amp;info_index!$C$2:$C$74,0),1)&amp;"","")</f>
         <v>OrientalMotor</v>
       </c>
       <c r="P3" t="str" cm="1">
@@ -6105,7 +6555,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ref="E5:E68" si="0">E4</f>
@@ -7680,7 +8130,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AK$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸
@@ -7901,6 +8351,110 @@
 			strRt	:= 'AZM15AK';
 		ELSIF strInfoKey = 'mf' THEN
 			strRt	:= 'OrientalMotor';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//ワーク搬送Z軸
+	ELSIF uiInfoIdx = 18 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Z軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis18】 ワーク搬送Z軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA7R-WA-56P-16-150-SE-S-B-MR　';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//ワーク搬送X軸
+	ELSIF uiInfoIdx = 19 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送X軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis19】 ワーク搬送X軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA4R-WA-35P-5-500-SE-S-ML';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//ワーク搬送Y軸
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Y軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis20】 ワーク搬送Y軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA4R-WA-35P-5-150-SE-S-MR';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//ワーク回転
+	ELSIF uiInfoIdx = 21 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク回転';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis21】 ワーク回転';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCS2-RTC12L-A-150-30-360-T2-S-L ';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//ワークチャック
+	ELSIF uiInfoIdx = 22 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワークチャック';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis22】 ワークチャック';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP2-GRHB-I-42P-2-40-P1-S';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//溶接補助
+	ELSIF uiInfoIdx = 23 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接補助';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis23】 溶接補助';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA7R-WA-56P-16-150-SE-S-B-MR　';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//溶接トーチ上下
+	ELSIF uiInfoIdx = 24 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis24】 溶接トーチ上下';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA6C-WA-42P-3-50-SE-S-B ';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//平板張力軸
+	ELSIF uiInfoIdx = 25 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板張力軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis25】 平板張力軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'SV3-M040AK';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'KEYENCE';
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
@@ -9752,90 +10306,185 @@
       <c r="G20" t="str">
         <v/>
       </c>
-      <c r="H20" t="str">
-        <v/>
+      <c r="H20">
+        <v>18</v>
       </c>
       <c r="I20" t="str">
         <f ca="1"/>
-        <v/>
+        <v>ワーク搬送Z軸</v>
       </c>
       <c r="J20" t="str">
         <f ca="1"/>
-        <v/>
+        <v>ワーク搬送Z軸</v>
       </c>
       <c r="L20" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【axis18】 ワーク搬送Z軸</v>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>RCP6S-SA7R-WA-56P-16-150-SE-S-B-MR　</v>
       </c>
       <c r="N20" t="str">
-        <v/>
+        <v>RCP6S-SA7R-WA-56P-16-150-SE-S-B-MR　</v>
       </c>
       <c r="O20" t="str">
         <f ca="1"/>
-        <v/>
+        <v>IAI</v>
       </c>
       <c r="P20" t="str">
         <f ca="1"/>
-        <v/>
+        <v>IAI</v>
       </c>
       <c r="X20" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Y20" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Z20" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Z軸
+	ELSIF uiInfoIdx = 18 THEN</v>
       </c>
       <c r="AA20" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Z軸
+	ELSIF uiInfoIdx = 18 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB20" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Z軸
+	ELSIF uiInfoIdx = 18 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Z軸';</v>
       </c>
       <c r="AC20" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Z軸
+	ELSIF uiInfoIdx = 18 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Z軸';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD20" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Z軸
+	ELSIF uiInfoIdx = 18 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Z軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis18】 ワーク搬送Z軸';</v>
       </c>
       <c r="AE20" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Z軸
+	ELSIF uiInfoIdx = 18 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Z軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis18】 ワーク搬送Z軸';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF20" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Z軸
+	ELSIF uiInfoIdx = 18 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Z軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis18】 ワーク搬送Z軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA7R-WA-56P-16-150-SE-S-B-MR　';</v>
       </c>
       <c r="AG20" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Z軸
+	ELSIF uiInfoIdx = 18 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Z軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis18】 ワーク搬送Z軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA7R-WA-56P-16-150-SE-S-B-MR　';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH20" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Z軸
+	ELSIF uiInfoIdx = 18 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Z軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis18】 ワーク搬送Z軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA7R-WA-56P-16-150-SE-S-B-MR　';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';</v>
       </c>
       <c r="AI20" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Z軸
+	ELSIF uiInfoIdx = 18 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Z軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis18】 ワーク搬送Z軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA7R-WA-56P-16-150-SE-S-B-MR　';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AJ20" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Z軸
+	ELSIF uiInfoIdx = 18 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Z軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis18】 ワーク搬送Z軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA7R-WA-56P-16-150-SE-S-B-MR　';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AK20" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Z軸
+	ELSIF uiInfoIdx = 18 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Z軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis18】 ワーク搬送Z軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA7R-WA-56P-16-150-SE-S-B-MR　';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.55000000000000004">
@@ -9850,90 +10499,185 @@
       <c r="G21" t="str">
         <v/>
       </c>
-      <c r="H21" t="str">
-        <v/>
+      <c r="H21">
+        <v>19</v>
       </c>
       <c r="I21" t="str">
         <f ca="1"/>
-        <v/>
+        <v>ワーク搬送X軸</v>
       </c>
       <c r="J21" t="str">
         <f ca="1"/>
-        <v/>
+        <v>ワーク搬送X軸</v>
       </c>
       <c r="L21" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【axis19】 ワーク搬送X軸</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>RCP6S-SA4R-WA-35P-5-500-SE-S-ML</v>
       </c>
       <c r="N21" t="str">
-        <v/>
+        <v>RCP6S-SA4R-WA-35P-5-500-SE-S-ML</v>
       </c>
       <c r="O21" t="str">
         <f ca="1"/>
-        <v/>
+        <v>IAI</v>
       </c>
       <c r="P21" t="str">
         <f ca="1"/>
-        <v/>
+        <v>IAI</v>
       </c>
       <c r="X21" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Y21" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Z21" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送X軸
+	ELSIF uiInfoIdx = 19 THEN</v>
       </c>
       <c r="AA21" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送X軸
+	ELSIF uiInfoIdx = 19 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB21" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送X軸
+	ELSIF uiInfoIdx = 19 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送X軸';</v>
       </c>
       <c r="AC21" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送X軸
+	ELSIF uiInfoIdx = 19 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送X軸';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD21" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送X軸
+	ELSIF uiInfoIdx = 19 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送X軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis19】 ワーク搬送X軸';</v>
       </c>
       <c r="AE21" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送X軸
+	ELSIF uiInfoIdx = 19 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送X軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis19】 ワーク搬送X軸';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF21" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送X軸
+	ELSIF uiInfoIdx = 19 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送X軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis19】 ワーク搬送X軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA4R-WA-35P-5-500-SE-S-ML';</v>
       </c>
       <c r="AG21" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送X軸
+	ELSIF uiInfoIdx = 19 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送X軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis19】 ワーク搬送X軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA4R-WA-35P-5-500-SE-S-ML';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH21" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送X軸
+	ELSIF uiInfoIdx = 19 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送X軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis19】 ワーク搬送X軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA4R-WA-35P-5-500-SE-S-ML';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';</v>
       </c>
       <c r="AI21" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送X軸
+	ELSIF uiInfoIdx = 19 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送X軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis19】 ワーク搬送X軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA4R-WA-35P-5-500-SE-S-ML';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AJ21" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送X軸
+	ELSIF uiInfoIdx = 19 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送X軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis19】 ワーク搬送X軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA4R-WA-35P-5-500-SE-S-ML';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AK21" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送X軸
+	ELSIF uiInfoIdx = 19 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送X軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis19】 ワーク搬送X軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA4R-WA-35P-5-500-SE-S-ML';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="22" spans="1:37" x14ac:dyDescent="0.55000000000000004">
@@ -9948,90 +10692,185 @@
       <c r="G22" t="str">
         <v/>
       </c>
-      <c r="H22" t="str">
-        <v/>
+      <c r="H22">
+        <v>20</v>
       </c>
       <c r="I22" t="str">
         <f ca="1"/>
-        <v/>
+        <v>ワーク搬送Y軸</v>
       </c>
       <c r="J22" t="str">
         <f ca="1"/>
-        <v/>
+        <v>ワーク搬送Y軸</v>
       </c>
       <c r="L22" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【axis20】 ワーク搬送Y軸</v>
       </c>
       <c r="M22" t="str">
-        <v/>
+        <v>RCP6S-SA4R-WA-35P-5-150-SE-S-MR</v>
       </c>
       <c r="N22" t="str">
-        <v/>
+        <v>RCP6S-SA4R-WA-35P-5-150-SE-S-MR</v>
       </c>
       <c r="O22" t="str">
         <f ca="1"/>
-        <v/>
+        <v>IAI</v>
       </c>
       <c r="P22" t="str">
         <f ca="1"/>
-        <v/>
+        <v>IAI</v>
       </c>
       <c r="X22" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Y22" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Z22" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Y軸
+	ELSIF uiInfoIdx = 20 THEN</v>
       </c>
       <c r="AA22" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Y軸
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB22" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Y軸
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Y軸';</v>
       </c>
       <c r="AC22" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Y軸
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Y軸';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD22" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Y軸
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Y軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis20】 ワーク搬送Y軸';</v>
       </c>
       <c r="AE22" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Y軸
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Y軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis20】 ワーク搬送Y軸';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF22" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Y軸
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Y軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis20】 ワーク搬送Y軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA4R-WA-35P-5-150-SE-S-MR';</v>
       </c>
       <c r="AG22" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Y軸
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Y軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis20】 ワーク搬送Y軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA4R-WA-35P-5-150-SE-S-MR';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH22" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Y軸
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Y軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis20】 ワーク搬送Y軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA4R-WA-35P-5-150-SE-S-MR';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';</v>
       </c>
       <c r="AI22" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Y軸
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Y軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis20】 ワーク搬送Y軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA4R-WA-35P-5-150-SE-S-MR';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AJ22" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Y軸
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Y軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis20】 ワーク搬送Y軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA4R-WA-35P-5-150-SE-S-MR';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AK22" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク搬送Y軸
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Y軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis20】 ワーク搬送Y軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA4R-WA-35P-5-150-SE-S-MR';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.55000000000000004">
@@ -10052,90 +10891,185 @@
       <c r="G23" t="str">
         <v/>
       </c>
-      <c r="H23" t="str">
-        <v/>
+      <c r="H23">
+        <v>21</v>
       </c>
       <c r="I23" t="str">
         <f ca="1"/>
-        <v/>
+        <v>ワーク回転</v>
       </c>
       <c r="J23" t="str">
         <f ca="1"/>
-        <v/>
+        <v>ワーク回転</v>
       </c>
       <c r="L23" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【axis21】 ワーク回転</v>
       </c>
       <c r="M23" t="str">
-        <v/>
+        <v xml:space="preserve">RCS2-RTC12L-A-150-30-360-T2-S-L </v>
       </c>
       <c r="N23" t="str">
-        <v/>
+        <v xml:space="preserve">RCS2-RTC12L-A-150-30-360-T2-S-L </v>
       </c>
       <c r="O23" t="str">
         <f ca="1"/>
-        <v/>
+        <v>IAI</v>
       </c>
       <c r="P23" t="str">
         <f ca="1"/>
-        <v/>
+        <v>IAI</v>
       </c>
       <c r="X23" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Y23" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Z23" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク回転
+	ELSIF uiInfoIdx = 21 THEN</v>
       </c>
       <c r="AA23" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク回転
+	ELSIF uiInfoIdx = 21 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB23" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク回転
+	ELSIF uiInfoIdx = 21 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク回転';</v>
       </c>
       <c r="AC23" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク回転
+	ELSIF uiInfoIdx = 21 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク回転';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD23" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク回転
+	ELSIF uiInfoIdx = 21 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク回転';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis21】 ワーク回転';</v>
       </c>
       <c r="AE23" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク回転
+	ELSIF uiInfoIdx = 21 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク回転';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis21】 ワーク回転';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF23" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク回転
+	ELSIF uiInfoIdx = 21 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク回転';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis21】 ワーク回転';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCS2-RTC12L-A-150-30-360-T2-S-L ';</v>
       </c>
       <c r="AG23" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク回転
+	ELSIF uiInfoIdx = 21 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク回転';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis21】 ワーク回転';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCS2-RTC12L-A-150-30-360-T2-S-L ';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH23" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク回転
+	ELSIF uiInfoIdx = 21 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク回転';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis21】 ワーク回転';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCS2-RTC12L-A-150-30-360-T2-S-L ';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';</v>
       </c>
       <c r="AI23" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク回転
+	ELSIF uiInfoIdx = 21 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク回転';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis21】 ワーク回転';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCS2-RTC12L-A-150-30-360-T2-S-L ';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AJ23" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク回転
+	ELSIF uiInfoIdx = 21 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク回転';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis21】 ワーク回転';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCS2-RTC12L-A-150-30-360-T2-S-L ';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AK23" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワーク回転
+	ELSIF uiInfoIdx = 21 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク回転';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis21】 ワーク回転';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCS2-RTC12L-A-150-30-360-T2-S-L ';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.55000000000000004">
@@ -10150,90 +11084,185 @@
       <c r="G24" t="str">
         <v/>
       </c>
-      <c r="H24" t="str">
-        <v/>
+      <c r="H24">
+        <v>22</v>
       </c>
       <c r="I24" t="str">
         <f ca="1"/>
-        <v/>
+        <v>ワークチャック</v>
       </c>
       <c r="J24" t="str">
         <f ca="1"/>
-        <v/>
+        <v>ワークチャック</v>
       </c>
       <c r="L24" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【axis22】 ワークチャック</v>
       </c>
       <c r="M24" t="str">
-        <v/>
+        <v>RCP2-GRHB-I-42P-2-40-P1-S</v>
       </c>
       <c r="N24" t="str">
-        <v/>
+        <v>RCP2-GRHB-I-42P-2-40-P1-S</v>
       </c>
       <c r="O24" t="str">
         <f ca="1"/>
-        <v/>
+        <v>IAI</v>
       </c>
       <c r="P24" t="str">
         <f ca="1"/>
-        <v/>
+        <v>IAI</v>
       </c>
       <c r="X24" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Y24" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Z24" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワークチャック
+	ELSIF uiInfoIdx = 22 THEN</v>
       </c>
       <c r="AA24" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワークチャック
+	ELSIF uiInfoIdx = 22 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB24" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワークチャック
+	ELSIF uiInfoIdx = 22 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワークチャック';</v>
       </c>
       <c r="AC24" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワークチャック
+	ELSIF uiInfoIdx = 22 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワークチャック';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD24" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワークチャック
+	ELSIF uiInfoIdx = 22 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワークチャック';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis22】 ワークチャック';</v>
       </c>
       <c r="AE24" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワークチャック
+	ELSIF uiInfoIdx = 22 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワークチャック';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis22】 ワークチャック';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF24" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワークチャック
+	ELSIF uiInfoIdx = 22 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワークチャック';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis22】 ワークチャック';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP2-GRHB-I-42P-2-40-P1-S';</v>
       </c>
       <c r="AG24" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワークチャック
+	ELSIF uiInfoIdx = 22 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワークチャック';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis22】 ワークチャック';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP2-GRHB-I-42P-2-40-P1-S';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH24" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワークチャック
+	ELSIF uiInfoIdx = 22 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワークチャック';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis22】 ワークチャック';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP2-GRHB-I-42P-2-40-P1-S';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';</v>
       </c>
       <c r="AI24" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワークチャック
+	ELSIF uiInfoIdx = 22 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワークチャック';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis22】 ワークチャック';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP2-GRHB-I-42P-2-40-P1-S';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AJ24" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワークチャック
+	ELSIF uiInfoIdx = 22 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワークチャック';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis22】 ワークチャック';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP2-GRHB-I-42P-2-40-P1-S';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AK24" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//ワークチャック
+	ELSIF uiInfoIdx = 22 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワークチャック';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis22】 ワークチャック';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP2-GRHB-I-42P-2-40-P1-S';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.55000000000000004">
@@ -10254,90 +11283,185 @@
       <c r="G25" t="str">
         <v/>
       </c>
-      <c r="H25" t="str">
-        <v/>
+      <c r="H25">
+        <v>23</v>
       </c>
       <c r="I25" t="str">
         <f ca="1"/>
-        <v/>
+        <v>溶接補助</v>
       </c>
       <c r="J25" t="str">
         <f ca="1"/>
-        <v/>
+        <v>溶接補助</v>
       </c>
       <c r="L25" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【axis23】 溶接補助</v>
       </c>
       <c r="M25" t="str">
-        <v/>
+        <v>RCP6S-SA7R-WA-56P-16-150-SE-S-B-MR　</v>
       </c>
       <c r="N25" t="str">
-        <v/>
+        <v>RCP6S-SA7R-WA-56P-16-150-SE-S-B-MR　</v>
       </c>
       <c r="O25" t="str">
         <f ca="1"/>
-        <v/>
+        <v>IAI</v>
       </c>
       <c r="P25" t="str">
         <f ca="1"/>
-        <v/>
+        <v>IAI</v>
       </c>
       <c r="X25" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Y25" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Z25" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接補助
+	ELSIF uiInfoIdx = 23 THEN</v>
       </c>
       <c r="AA25" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接補助
+	ELSIF uiInfoIdx = 23 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB25" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接補助
+	ELSIF uiInfoIdx = 23 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接補助';</v>
       </c>
       <c r="AC25" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接補助
+	ELSIF uiInfoIdx = 23 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接補助';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD25" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接補助
+	ELSIF uiInfoIdx = 23 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接補助';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis23】 溶接補助';</v>
       </c>
       <c r="AE25" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接補助
+	ELSIF uiInfoIdx = 23 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接補助';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis23】 溶接補助';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF25" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接補助
+	ELSIF uiInfoIdx = 23 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接補助';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis23】 溶接補助';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA7R-WA-56P-16-150-SE-S-B-MR　';</v>
       </c>
       <c r="AG25" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接補助
+	ELSIF uiInfoIdx = 23 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接補助';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis23】 溶接補助';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA7R-WA-56P-16-150-SE-S-B-MR　';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH25" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接補助
+	ELSIF uiInfoIdx = 23 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接補助';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis23】 溶接補助';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA7R-WA-56P-16-150-SE-S-B-MR　';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';</v>
       </c>
       <c r="AI25" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接補助
+	ELSIF uiInfoIdx = 23 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接補助';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis23】 溶接補助';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA7R-WA-56P-16-150-SE-S-B-MR　';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AJ25" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接補助
+	ELSIF uiInfoIdx = 23 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接補助';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis23】 溶接補助';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA7R-WA-56P-16-150-SE-S-B-MR　';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AK25" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接補助
+	ELSIF uiInfoIdx = 23 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接補助';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis23】 溶接補助';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA7R-WA-56P-16-150-SE-S-B-MR　';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="26" spans="1:37" x14ac:dyDescent="0.55000000000000004">
@@ -10358,90 +11482,185 @@
       <c r="G26" t="str">
         <v/>
       </c>
-      <c r="H26" t="str">
-        <v/>
+      <c r="H26">
+        <v>24</v>
       </c>
       <c r="I26" t="str">
         <f ca="1"/>
-        <v/>
+        <v>溶接トーチ上下</v>
       </c>
       <c r="J26" t="str">
         <f ca="1"/>
-        <v/>
+        <v>溶接トーチ上下</v>
       </c>
       <c r="L26" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【axis24】 溶接トーチ上下</v>
       </c>
       <c r="M26" t="str">
-        <v/>
+        <v xml:space="preserve">RCP6S-SA6C-WA-42P-3-50-SE-S-B </v>
       </c>
       <c r="N26" t="str">
-        <v/>
+        <v xml:space="preserve">RCP6S-SA6C-WA-42P-3-50-SE-S-B </v>
       </c>
       <c r="O26" t="str">
         <f ca="1"/>
-        <v/>
+        <v>IAI</v>
       </c>
       <c r="P26" t="str">
         <f ca="1"/>
-        <v/>
+        <v>IAI</v>
       </c>
       <c r="X26" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Y26" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Z26" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接トーチ上下
+	ELSIF uiInfoIdx = 24 THEN</v>
       </c>
       <c r="AA26" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接トーチ上下
+	ELSIF uiInfoIdx = 24 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB26" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接トーチ上下
+	ELSIF uiInfoIdx = 24 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接トーチ上下';</v>
       </c>
       <c r="AC26" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接トーチ上下
+	ELSIF uiInfoIdx = 24 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD26" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接トーチ上下
+	ELSIF uiInfoIdx = 24 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis24】 溶接トーチ上下';</v>
       </c>
       <c r="AE26" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接トーチ上下
+	ELSIF uiInfoIdx = 24 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis24】 溶接トーチ上下';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF26" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接トーチ上下
+	ELSIF uiInfoIdx = 24 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis24】 溶接トーチ上下';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA6C-WA-42P-3-50-SE-S-B ';</v>
       </c>
       <c r="AG26" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接トーチ上下
+	ELSIF uiInfoIdx = 24 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis24】 溶接トーチ上下';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA6C-WA-42P-3-50-SE-S-B ';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH26" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接トーチ上下
+	ELSIF uiInfoIdx = 24 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis24】 溶接トーチ上下';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA6C-WA-42P-3-50-SE-S-B ';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';</v>
       </c>
       <c r="AI26" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接トーチ上下
+	ELSIF uiInfoIdx = 24 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis24】 溶接トーチ上下';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA6C-WA-42P-3-50-SE-S-B ';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AJ26" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接トーチ上下
+	ELSIF uiInfoIdx = 24 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis24】 溶接トーチ上下';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA6C-WA-42P-3-50-SE-S-B ';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AK26" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//溶接トーチ上下
+	ELSIF uiInfoIdx = 24 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis24】 溶接トーチ上下';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA6C-WA-42P-3-50-SE-S-B ';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="27" spans="1:37" x14ac:dyDescent="0.55000000000000004">
@@ -10462,90 +11681,185 @@
       <c r="G27" t="str">
         <v/>
       </c>
-      <c r="H27" t="str">
-        <v/>
+      <c r="H27">
+        <v>25</v>
       </c>
       <c r="I27" t="str">
         <f ca="1"/>
-        <v/>
+        <v>平板張力軸</v>
       </c>
       <c r="J27" t="str">
         <f ca="1"/>
-        <v/>
+        <v>平板張力軸</v>
       </c>
       <c r="L27" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【axis25】 平板張力軸</v>
       </c>
       <c r="M27" t="str">
-        <v/>
+        <v>SV3-M040AK</v>
       </c>
       <c r="N27" t="str">
-        <v/>
+        <v>SV3-M040AK</v>
       </c>
       <c r="O27" t="str">
         <f ca="1"/>
-        <v/>
+        <v>KEYENCE</v>
       </c>
       <c r="P27" t="str">
         <f ca="1"/>
-        <v/>
+        <v>KEYENCE</v>
       </c>
       <c r="X27" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Y27" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="Z27" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//平板張力軸
+	ELSIF uiInfoIdx = 25 THEN</v>
       </c>
       <c r="AA27" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//平板張力軸
+	ELSIF uiInfoIdx = 25 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB27" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//平板張力軸
+	ELSIF uiInfoIdx = 25 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板張力軸';</v>
       </c>
       <c r="AC27" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//平板張力軸
+	ELSIF uiInfoIdx = 25 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板張力軸';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD27" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//平板張力軸
+	ELSIF uiInfoIdx = 25 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板張力軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis25】 平板張力軸';</v>
       </c>
       <c r="AE27" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//平板張力軸
+	ELSIF uiInfoIdx = 25 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板張力軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis25】 平板張力軸';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF27" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//平板張力軸
+	ELSIF uiInfoIdx = 25 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板張力軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis25】 平板張力軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'SV3-M040AK';</v>
       </c>
       <c r="AG27" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//平板張力軸
+	ELSIF uiInfoIdx = 25 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板張力軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis25】 平板張力軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'SV3-M040AK';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH27" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//平板張力軸
+	ELSIF uiInfoIdx = 25 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板張力軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis25】 平板張力軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'SV3-M040AK';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'KEYENCE';</v>
       </c>
       <c r="AI27" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//平板張力軸
+	ELSIF uiInfoIdx = 25 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板張力軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis25】 平板張力軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'SV3-M040AK';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'KEYENCE';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AJ27" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//平板張力軸
+	ELSIF uiInfoIdx = 25 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板張力軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis25】 平板張力軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'SV3-M040AK';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'KEYENCE';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AK27" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//平板張力軸
+	ELSIF uiInfoIdx = 25 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板張力軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis25】 平板張力軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'SV3-M040AK';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'KEYENCE';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="28" spans="1:37" x14ac:dyDescent="0.55000000000000004">
@@ -12048,7 +13362,7 @@
         <v/>
       </c>
       <c r="H43">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="I43" t="str">
         <f ca="1"/>
@@ -14133,7 +15447,7 @@
         <v/>
       </c>
       <c r="H63">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I63" t="str">
         <f ca="1"/>
@@ -14351,7 +15665,7 @@
         <v/>
       </c>
       <c r="H64">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I64" t="str">
         <f ca="1"/>
@@ -14544,7 +15858,7 @@
         <v/>
       </c>
       <c r="H65">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I65" t="str">
         <f ca="1"/>
@@ -14737,7 +16051,7 @@
         <v/>
       </c>
       <c r="H66">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I66" t="str">
         <f ca="1"/>
@@ -14930,7 +16244,7 @@
         <v/>
       </c>
       <c r="H67">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="I67" t="str">
         <f ca="1"/>
@@ -15123,7 +16437,7 @@
         <v/>
       </c>
       <c r="H68">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="I68" t="str">
         <f ca="1"/>
@@ -15316,7 +16630,7 @@
         <v/>
       </c>
       <c r="H69">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I69" t="str">
         <f ca="1"/>
@@ -15509,7 +16823,7 @@
         <v/>
       </c>
       <c r="H70">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I70" t="str">
         <f ca="1"/>
@@ -15702,7 +17016,7 @@
         <v/>
       </c>
       <c r="H71">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="I71" t="str">
         <f ca="1"/>
@@ -15895,7 +17209,7 @@
         <v/>
       </c>
       <c r="H72">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="I72" t="str">
         <f ca="1"/>
@@ -16088,7 +17402,7 @@
         <v/>
       </c>
       <c r="H73">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I73" t="str">
         <f ca="1"/>
@@ -16281,7 +17595,7 @@
         <v/>
       </c>
       <c r="H74">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="I74" t="str">
         <f ca="1"/>
@@ -16474,7 +17788,7 @@
         <v/>
       </c>
       <c r="H75">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I75" t="str">
         <f ca="1"/>
@@ -16667,7 +17981,7 @@
         <v/>
       </c>
       <c r="H76">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="I76" t="str">
         <f ca="1"/>
@@ -16860,7 +18174,7 @@
         <v/>
       </c>
       <c r="H77">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I77" t="str">
         <f ca="1"/>
@@ -17053,7 +18367,7 @@
         <v/>
       </c>
       <c r="H78">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="I78" t="str">
         <f ca="1"/>
@@ -17246,7 +18560,7 @@
         <v/>
       </c>
       <c r="H79">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="I79" t="str">
         <f ca="1"/>
@@ -17439,7 +18753,7 @@
         <v/>
       </c>
       <c r="H80">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I80" t="str">
         <f ca="1"/>
@@ -17632,7 +18946,7 @@
         <v/>
       </c>
       <c r="H81">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I81" t="str">
         <f ca="1"/>
@@ -17825,7 +19139,7 @@
         <v/>
       </c>
       <c r="H82">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="I82" t="str">
         <f ca="1"/>
@@ -18317,7 +19631,7 @@
         <v/>
       </c>
       <c r="H86">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="I86" t="str">
         <f ca="1"/>
@@ -18535,7 +19849,7 @@
         <v/>
       </c>
       <c r="H87">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="I87" t="str">
         <f ca="1"/>
@@ -19517,7 +20831,7 @@
         <v/>
       </c>
       <c r="H96">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="I96" t="str">
         <f ca="1"/>
@@ -19735,7 +21049,7 @@
         <v/>
       </c>
       <c r="H97">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="I97" t="str">
         <f ca="1"/>
@@ -19928,7 +21242,7 @@
         <v/>
       </c>
       <c r="H98">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="I98" t="str">
         <f ca="1"/>
@@ -20812,7 +22126,7 @@
         <v/>
       </c>
       <c r="H106">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="I106" t="str">
         <f ca="1"/>
@@ -21030,7 +22344,7 @@
         <v/>
       </c>
       <c r="H107">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I107" t="str">
         <f ca="1"/>
@@ -21223,7 +22537,7 @@
         <v/>
       </c>
       <c r="H108">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="I108" t="str">
         <f ca="1"/>
@@ -21416,7 +22730,7 @@
         <v/>
       </c>
       <c r="H109">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="I109" t="str">
         <f ca="1"/>
@@ -21609,7 +22923,7 @@
         <v/>
       </c>
       <c r="H110">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="I110" t="str">
         <f ca="1"/>
@@ -21802,7 +23116,7 @@
         <v/>
       </c>
       <c r="H111">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="I111" t="str">
         <f ca="1"/>
@@ -21995,7 +23309,7 @@
         <v/>
       </c>
       <c r="H112">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="I112" t="str">
         <f ca="1"/>
@@ -22188,7 +23502,7 @@
         <v/>
       </c>
       <c r="H113">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="I113" t="str">
         <f ca="1"/>
@@ -31099,7 +32413,7 @@
     <row r="205" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="AK205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AK$3:AK$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸
@@ -31320,6 +32634,110 @@
 			strRt	:= 'AZM15AK';
 		ELSIF strInfoKey = 'mf' THEN
 			strRt	:= 'OrientalMotor';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//ワーク搬送Z軸
+	ELSIF uiInfoIdx = 18 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Z軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis18】 ワーク搬送Z軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA7R-WA-56P-16-150-SE-S-B-MR　';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//ワーク搬送X軸
+	ELSIF uiInfoIdx = 19 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送X軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis19】 ワーク搬送X軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA4R-WA-35P-5-500-SE-S-ML';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//ワーク搬送Y軸
+	ELSIF uiInfoIdx = 20 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク搬送Y軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis20】 ワーク搬送Y軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA4R-WA-35P-5-150-SE-S-MR';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//ワーク回転
+	ELSIF uiInfoIdx = 21 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワーク回転';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis21】 ワーク回転';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCS2-RTC12L-A-150-30-360-T2-S-L ';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//ワークチャック
+	ELSIF uiInfoIdx = 22 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'ワークチャック';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis22】 ワークチャック';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP2-GRHB-I-42P-2-40-P1-S';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//溶接補助
+	ELSIF uiInfoIdx = 23 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接補助';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis23】 溶接補助';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA7R-WA-56P-16-150-SE-S-B-MR　';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//溶接トーチ上下
+	ELSIF uiInfoIdx = 24 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '溶接トーチ上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis24】 溶接トーチ上下';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'RCP6S-SA6C-WA-42P-3-50-SE-S-B ';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'IAI';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//平板張力軸
+	ELSIF uiInfoIdx = 25 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '平板張力軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis25】 平板張力軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'SV3-M040AK';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'KEYENCE';
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A85237-4148-42F6-8951-876904885AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95151F3-38FC-44D1-896E-B5D655AABA87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="324">
   <si>
     <t>RCA2-GS3NA-I-10-2-50-A6-M-K1</t>
   </si>
@@ -784,10 +784,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Tロール回転軸</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ワーク排出前後軸</t>
     <rPh sb="3" eb="5">
       <t>ハイシュツ</t>
@@ -962,9 +958,6 @@
   </si>
   <si>
     <t>Workpiece width adjustment shaft</t>
-  </si>
-  <si>
-    <t>T-roll rotation shaft</t>
   </si>
   <si>
     <t>Rotor unit X-roll rotation shaft</t>
@@ -2120,18 +2113,11 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="lightUp">
           <fgColor rgb="FF33CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2578,7 +2564,7 @@
         <v>105</v>
       </c>
       <c r="G1" s="39" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H1" s="39" t="s">
         <v>10</v>
@@ -2590,7 +2576,7 @@
         <v>3</v>
       </c>
       <c r="K1" s="39" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L1" s="39" t="s">
         <v>5</v>
@@ -2599,16 +2585,16 @@
         <v>112</v>
       </c>
       <c r="N1" s="40" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="O1" s="40" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="P1" s="41" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="Q1" s="41" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="R1" s="40"/>
     </row>
@@ -2629,10 +2615,10 @@
         <v>91</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H2" s="28" t="s">
         <v>20</v>
@@ -2641,10 +2627,10 @@
         <v>21</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L2" s="28">
         <v>1</v>
@@ -2680,7 +2666,7 @@
         <v>125</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>14</v>
@@ -2689,10 +2675,10 @@
         <v>13</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L3" s="12">
         <v>1</v>
@@ -2728,7 +2714,7 @@
         <v>124</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>14</v>
@@ -2737,10 +2723,10 @@
         <v>13</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L4" s="12">
         <v>1</v>
@@ -2776,7 +2762,7 @@
         <v>89</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>14</v>
@@ -2785,10 +2771,10 @@
         <v>13</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L5" s="12">
         <v>1</v>
@@ -2821,10 +2807,10 @@
         <v>94</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>1</v>
@@ -2836,7 +2822,7 @@
         <v>2</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L6" s="8">
         <v>1</v>
@@ -2869,10 +2855,10 @@
         <v>94</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>0</v>
@@ -2884,7 +2870,7 @@
         <v>2</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L7" s="8">
         <v>1</v>
@@ -2917,10 +2903,10 @@
         <v>99</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>28</v>
@@ -2932,7 +2918,7 @@
         <v>2</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L8" s="8">
         <v>1</v>
@@ -2965,10 +2951,10 @@
         <v>101</v>
       </c>
       <c r="F9" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>262</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>264</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>106</v>
@@ -2980,7 +2966,7 @@
         <v>2</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L9" s="8">
         <v>1</v>
@@ -3013,10 +2999,10 @@
         <v>101</v>
       </c>
       <c r="F10" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>263</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>265</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>107</v>
@@ -3028,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L10" s="8">
         <v>1</v>
@@ -3057,10 +3043,10 @@
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
@@ -3091,10 +3077,10 @@
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
@@ -3125,10 +3111,10 @@
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
@@ -3166,7 +3152,7 @@
         <v>126</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>31</v>
@@ -3175,10 +3161,10 @@
         <v>32</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L14" s="8">
         <v>1</v>
@@ -3214,7 +3200,7 @@
         <v>127</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>33</v>
@@ -3223,10 +3209,10 @@
         <v>32</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L15" s="8">
         <v>1</v>
@@ -3252,20 +3238,28 @@
       <c r="C16" s="7">
         <v>15</v>
       </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
+      <c r="D16" s="8">
+        <v>10</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>276</v>
+      </c>
       <c r="F16" s="8" t="s">
-        <v>128</v>
+        <v>271</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>161</v>
+        <v>272</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>137</v>
+        <v>273</v>
       </c>
       <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
+      <c r="J16" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>217</v>
+      </c>
       <c r="L16" s="8"/>
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
@@ -3291,13 +3285,13 @@
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
       <c r="F17" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="H17" s="8" t="s">
         <v>136</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>137</v>
       </c>
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
@@ -3328,23 +3322,23 @@
         <v>10</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F18" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="H18" s="42" t="s">
         <v>273</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="H18" s="42" t="s">
-        <v>275</v>
       </c>
       <c r="I18" s="8"/>
       <c r="J18" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L18" s="8"/>
       <c r="M18" s="10"/>
@@ -3371,22 +3365,22 @@
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G19" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="H19" s="42" t="s">
+        <v>298</v>
+      </c>
+      <c r="I19" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="H19" s="42" t="s">
-        <v>300</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>301</v>
-      </c>
       <c r="J19" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L19" s="8">
         <v>1</v>
@@ -3415,22 +3409,22 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H20" s="42" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L20" s="8">
         <v>1</v>
@@ -3459,22 +3453,22 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H21" s="42" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L21" s="8">
         <v>1</v>
@@ -3503,22 +3497,22 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G22" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="H22" s="42" t="s">
+        <v>305</v>
+      </c>
+      <c r="I22" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="H22" s="42" t="s">
-        <v>307</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>308</v>
-      </c>
       <c r="J22" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L22" s="8">
         <v>1</v>
@@ -3547,22 +3541,22 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="H23" s="42" t="s">
         <v>309</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="I23" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="H23" s="42" t="s">
-        <v>311</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>312</v>
-      </c>
       <c r="J23" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L23" s="8">
         <v>1</v>
@@ -3591,22 +3585,22 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H24" s="42" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L24" s="8">
         <v>1</v>
@@ -3635,22 +3629,22 @@
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H25" s="42" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L25" s="8">
         <v>1</v>
@@ -3679,22 +3673,22 @@
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="H26" s="42" t="s">
         <v>322</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="I26" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="H26" s="42" t="s">
-        <v>324</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>325</v>
-      </c>
       <c r="J26" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L26" s="8"/>
       <c r="M26" s="10"/>
@@ -3725,10 +3719,10 @@
         <v>99</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>61</v>
@@ -3740,7 +3734,7 @@
         <v>4</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L27" s="8">
         <v>1</v>
@@ -3773,13 +3767,13 @@
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="G28" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="G28" s="8" t="s">
-        <v>284</v>
-      </c>
       <c r="H28" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I28" s="8"/>
       <c r="J28" s="8"/>
@@ -3813,13 +3807,13 @@
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="G29" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="G29" s="8" t="s">
-        <v>285</v>
-      </c>
       <c r="H29" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I29" s="8"/>
       <c r="J29" s="8"/>
@@ -3854,13 +3848,13 @@
         <v>2</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H30" s="8" t="s">
         <v>63</v>
@@ -3872,7 +3866,7 @@
         <v>4</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L30" s="8">
         <v>1</v>
@@ -3909,10 +3903,10 @@
         <v>93</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>67</v>
@@ -3924,7 +3918,7 @@
         <v>4</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L31" s="8">
         <v>1</v>
@@ -3961,10 +3955,10 @@
         <v>93</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>65</v>
@@ -3976,7 +3970,7 @@
         <v>4</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L32" s="8">
         <v>1</v>
@@ -4013,10 +4007,10 @@
         <v>98</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>69</v>
@@ -4028,7 +4022,7 @@
         <v>4</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L33" s="11">
         <v>1</v>
@@ -4065,10 +4059,10 @@
         <v>92</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>73</v>
@@ -4080,7 +4074,7 @@
         <v>4</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L34" s="11">
         <v>1</v>
@@ -4120,7 +4114,7 @@
         <v>121</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>71</v>
@@ -4132,7 +4126,7 @@
         <v>4</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L35" s="11">
         <v>1</v>
@@ -4169,10 +4163,10 @@
         <v>100</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H36" s="8" t="s">
         <v>69</v>
@@ -4184,7 +4178,7 @@
         <v>4</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L36" s="11">
         <v>1</v>
@@ -4221,10 +4215,10 @@
         <v>95</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H37" s="12" t="s">
         <v>75</v>
@@ -4236,7 +4230,7 @@
         <v>4</v>
       </c>
       <c r="K37" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L37" s="13">
         <v>1</v>
@@ -4273,10 +4267,10 @@
         <v>95</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H38" s="8" t="s">
         <v>74</v>
@@ -4288,7 +4282,7 @@
         <v>4</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L38" s="11">
         <v>1</v>
@@ -4325,10 +4319,10 @@
         <v>97</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H39" s="12" t="s">
         <v>75</v>
@@ -4340,7 +4334,7 @@
         <v>4</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L39" s="13">
         <v>1</v>
@@ -4377,10 +4371,10 @@
         <v>97</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>76</v>
@@ -4392,7 +4386,7 @@
         <v>4</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L40" s="11">
         <v>1</v>
@@ -4429,10 +4423,10 @@
         <v>96</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H41" s="12" t="s">
         <v>77</v>
@@ -4444,7 +4438,7 @@
         <v>4</v>
       </c>
       <c r="K41" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L41" s="13">
         <v>1</v>
@@ -4481,10 +4475,10 @@
         <v>96</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H42" s="12" t="s">
         <v>77</v>
@@ -4496,7 +4490,7 @@
         <v>4</v>
       </c>
       <c r="K42" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L42" s="13">
         <v>1</v>
@@ -4529,10 +4523,10 @@
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
       <c r="F43" s="8" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H43" s="8" t="s">
         <v>51</v>
@@ -4569,10 +4563,10 @@
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
       <c r="F44" s="8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H44" s="8" t="s">
         <v>51</v>
@@ -4609,13 +4603,13 @@
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
       <c r="F45" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
@@ -4653,22 +4647,22 @@
         <v>92</v>
       </c>
       <c r="F46" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G46" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="G46" s="8" t="s">
+      <c r="H46" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="I46" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="H46" s="8" t="s">
+      <c r="J46" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="I46" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="J46" s="8" t="s">
-        <v>271</v>
-      </c>
       <c r="K46" s="8" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="L46" s="8"/>
       <c r="M46" s="10"/>
@@ -4708,7 +4702,7 @@
         <v>4</v>
       </c>
       <c r="K47" s="14" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L47" s="15">
         <v>1</v>
@@ -4752,7 +4746,7 @@
         <v>4</v>
       </c>
       <c r="K48" s="14" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L48" s="15">
         <v>1</v>
@@ -4796,7 +4790,7 @@
         <v>4</v>
       </c>
       <c r="K49" s="14" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L49" s="15">
         <v>1</v>
@@ -4831,10 +4825,10 @@
         <v>99</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H50" s="8" t="s">
         <v>30</v>
@@ -4846,7 +4840,7 @@
         <v>2</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L50" s="8">
         <v>1</v>
@@ -4887,10 +4881,10 @@
         <v>8</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L51" s="8">
         <v>1</v>
@@ -4931,10 +4925,10 @@
         <v>9</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L52" s="8">
         <v>1</v>
@@ -4973,10 +4967,10 @@
         <v>23</v>
       </c>
       <c r="J53" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K53" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L53" s="8">
         <v>3</v>
@@ -5017,10 +5011,10 @@
         <v>24</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K54" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L54" s="8">
         <v>1</v>
@@ -5063,10 +5057,10 @@
         <v>36</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L55" s="8">
         <v>1</v>
@@ -5105,10 +5099,10 @@
         <v>59</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K56" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L56" s="8">
         <v>1</v>
@@ -5145,10 +5139,10 @@
         <v>19</v>
       </c>
       <c r="J57" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K57" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L57" s="8">
         <v>1</v>
@@ -5185,10 +5179,10 @@
         <v>17</v>
       </c>
       <c r="J58" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K58" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L58" s="8">
         <v>1</v>
@@ -5225,10 +5219,10 @@
         <v>26</v>
       </c>
       <c r="J59" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K59" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L59" s="8">
         <v>1</v>
@@ -5267,10 +5261,10 @@
         <v>26</v>
       </c>
       <c r="J60" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K60" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L60" s="8">
         <v>1</v>
@@ -5291,7 +5285,7 @@
         <v>51</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C61" s="7">
         <v>1</v>
@@ -5299,10 +5293,10 @@
       <c r="D61" s="8"/>
       <c r="E61" s="8"/>
       <c r="F61" s="8" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
@@ -5325,7 +5319,7 @@
         <v>52</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C62" s="7">
         <v>2</v>
@@ -5333,10 +5327,10 @@
       <c r="D62" s="8"/>
       <c r="E62" s="8"/>
       <c r="F62" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
@@ -5359,7 +5353,7 @@
         <v>53</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C63" s="7">
         <v>3</v>
@@ -5367,10 +5361,10 @@
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
       <c r="F63" s="8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H63" s="8"/>
       <c r="I63" s="8"/>
@@ -5393,7 +5387,7 @@
         <v>54</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C64" s="7">
         <v>4</v>
@@ -5401,10 +5395,10 @@
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
       <c r="F64" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
@@ -5427,7 +5421,7 @@
         <v>55</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C65" s="7">
         <v>5</v>
@@ -5435,10 +5429,10 @@
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
       <c r="F65" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
@@ -5461,7 +5455,7 @@
         <v>56</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C66" s="7">
         <v>6</v>
@@ -5469,10 +5463,10 @@
       <c r="D66" s="8"/>
       <c r="E66" s="8"/>
       <c r="F66" s="8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
@@ -5495,7 +5489,7 @@
         <v>60</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C67" s="7">
         <v>7</v>
@@ -5503,10 +5497,10 @@
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
       <c r="F67" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
@@ -5529,7 +5523,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C68" s="7">
         <v>8</v>
@@ -5537,10 +5531,10 @@
       <c r="D68" s="8"/>
       <c r="E68" s="8"/>
       <c r="F68" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
@@ -5563,7 +5557,7 @@
         <v>57</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C69" s="7">
         <v>1</v>
@@ -5571,10 +5565,10 @@
       <c r="D69" s="8"/>
       <c r="E69" s="8"/>
       <c r="F69" s="8" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
@@ -5597,7 +5591,7 @@
         <v>61</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C70" s="7">
         <v>2</v>
@@ -5605,10 +5599,10 @@
       <c r="D70" s="8"/>
       <c r="E70" s="8"/>
       <c r="F70" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
@@ -5631,7 +5625,7 @@
         <v>62</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C71" s="7">
         <v>1</v>
@@ -5639,10 +5633,10 @@
       <c r="D71" s="8"/>
       <c r="E71" s="8"/>
       <c r="F71" s="8" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H71" s="8"/>
       <c r="I71" s="8"/>
@@ -5665,7 +5659,7 @@
         <v>63</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C72" s="7">
         <v>2</v>
@@ -5673,10 +5667,10 @@
       <c r="D72" s="8"/>
       <c r="E72" s="8"/>
       <c r="F72" s="8" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
@@ -5699,7 +5693,7 @@
         <v>64</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C73" s="7">
         <v>3</v>
@@ -5707,10 +5701,10 @@
       <c r="D73" s="8"/>
       <c r="E73" s="8"/>
       <c r="F73" s="8" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H73" s="8"/>
       <c r="I73" s="8"/>
@@ -5768,7 +5762,7 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B78" t="s">
         <v>117</v>
@@ -6030,19 +6024,19 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="F1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J1" t="s">
+        <v>224</v>
+      </c>
+      <c r="L1" t="s">
+        <v>225</v>
+      </c>
+      <c r="N1" t="s">
         <v>226</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>227</v>
-      </c>
-      <c r="N1" t="s">
-        <v>228</v>
-      </c>
-      <c r="P1" t="s">
-        <v>229</v>
       </c>
       <c r="AA1" t="str">
         <f>IF(LEN(J1),J2&amp;CHAR(9)&amp;":"&amp;J1,"")</f>
@@ -6076,78 +6070,78 @@
     </row>
     <row r="2" spans="1:37" s="30" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="30" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E2" s="30" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F2" s="30" t="s">
         <v>102</v>
       </c>
       <c r="G2" s="30" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H2" s="30" t="s">
+        <v>213</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="L2" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="N2" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="P2" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="J2" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="L2" s="30" t="s">
+      <c r="X2" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="Y2" s="30" t="s">
         <v>190</v>
       </c>
-      <c r="N2" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="P2" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="X2" s="30" t="s">
+      <c r="Z2" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA2" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="AB2" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="AC2" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="AD2" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="AE2" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="Y2" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="Z2" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="AA2" s="30" t="s">
-        <v>194</v>
-      </c>
-      <c r="AB2" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="AC2" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="AD2" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="AE2" s="30" t="s">
-        <v>203</v>
-      </c>
       <c r="AF2" s="30" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG2" s="30" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AH2" s="30" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AI2" s="30" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AJ2" s="30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AK2" s="30" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
@@ -6551,7 +6545,7 @@
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
@@ -6751,10 +6745,10 @@
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
@@ -6950,10 +6944,10 @@
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -7149,10 +7143,10 @@
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -7348,10 +7342,10 @@
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -8126,7 +8120,7 @@
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B13" t="str">
         <f ca="1">$AK$205</f>
@@ -8315,16 +8309,16 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Tロール回転軸
+	//波板補助軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 Tロール回転軸';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'M540-402';
-		ELSIF strInfoKey = 'mf' THEN
-			strRt	:= 'unknown';
+			strRt	:= '波板補助軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 波板補助軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'AZM15AK';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'OrientalMotor';
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
@@ -9127,7 +9121,7 @@
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B14" t="str">
         <f>IF(LEN(AI1),"●"&amp;B27&amp;CHAR(10)&amp;AI1,"")</f>
@@ -9732,29 +9726,29 @@
       </c>
       <c r="I17" t="str">
         <f ca="1"/>
-        <v>Tロール回転軸</v>
+        <v>波板補助軸</v>
       </c>
       <c r="J17" t="str">
         <f ca="1"/>
-        <v>Tロール回転軸</v>
+        <v>波板補助軸</v>
       </c>
       <c r="L17" t="str">
         <f ca="1"/>
-        <v>【axis15】 Tロール回転軸</v>
+        <v>【axis15】 波板補助軸</v>
       </c>
       <c r="M17" t="str">
-        <v>M540-402</v>
+        <v>AZM15AK</v>
       </c>
       <c r="N17" t="str">
-        <v>M540-402</v>
+        <v>AZM15AK</v>
       </c>
       <c r="O17" t="str">
         <f ca="1"/>
-        <v/>
+        <v>OrientalMotor</v>
       </c>
       <c r="P17" t="str">
         <f ca="1"/>
-        <v>unknown</v>
+        <v>OrientalMotor</v>
       </c>
       <c r="X17" t="str">
         <f ca="1"/>
@@ -9769,106 +9763,106 @@
       <c r="Z17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//波板補助軸
 	ELSIF uiInfoIdx = 15 THEN</v>
       </c>
       <c r="AA17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//波板補助軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//波板補助軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';</v>
+			strRt	:= '波板補助軸';</v>
       </c>
       <c r="AC17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//波板補助軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';
+			strRt	:= '波板補助軸';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//波板補助軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 Tロール回転軸';</v>
+			strRt	:= '波板補助軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 波板補助軸';</v>
       </c>
       <c r="AE17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//波板補助軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 Tロール回転軸';
+			strRt	:= '波板補助軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 波板補助軸';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//波板補助軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 Tロール回転軸';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'M540-402';</v>
+			strRt	:= '波板補助軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 波板補助軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'AZM15AK';</v>
       </c>
       <c r="AG17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//波板補助軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 Tロール回転軸';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'M540-402';
+			strRt	:= '波板補助軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 波板補助軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'AZM15AK';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AH17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//波板補助軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 Tロール回転軸';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'M540-402';
-		ELSIF strInfoKey = 'mf' THEN
-			strRt	:= 'unknown';</v>
+			strRt	:= '波板補助軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 波板補助軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'AZM15AK';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'OrientalMotor';</v>
       </c>
       <c r="AI17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//波板補助軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 Tロール回転軸';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'M540-402';
-		ELSIF strInfoKey = 'mf' THEN
-			strRt	:= 'unknown';
+			strRt	:= '波板補助軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 波板補助軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'AZM15AK';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'OrientalMotor';
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;</v>
@@ -9876,16 +9870,16 @@
       <c r="AJ17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//波板補助軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 Tロール回転軸';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'M540-402';
-		ELSIF strInfoKey = 'mf' THEN
-			strRt	:= 'unknown';
+			strRt	:= '波板補助軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 波板補助軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'AZM15AK';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'OrientalMotor';
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;</v>
@@ -9893,16 +9887,16 @@
       <c r="AK17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Tロール回転軸
+	//波板補助軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 Tロール回転軸';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'M540-402';
-		ELSIF strInfoKey = 'mf' THEN
-			strRt	:= 'unknown';
+			strRt	:= '波板補助軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 波板補助軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'AZM15AK';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'OrientalMotor';
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;</v>
@@ -10875,7 +10869,7 @@
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -11267,10 +11261,10 @@
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B25" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E25" t="str">
         <f t="shared" si="0"/>
@@ -11466,10 +11460,10 @@
     </row>
     <row r="26" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B26" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E26" t="str">
         <f t="shared" si="0"/>
@@ -11665,10 +11659,10 @@
     </row>
     <row r="27" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B27" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E27" t="str">
         <f t="shared" si="0"/>
@@ -11864,10 +11858,10 @@
     </row>
     <row r="28" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B28" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E28" t="str">
         <f t="shared" si="0"/>
@@ -11968,10 +11962,10 @@
     </row>
     <row r="29" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B29" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E29" t="str">
         <f t="shared" si="0"/>
@@ -19621,7 +19615,7 @@
     </row>
     <row r="86" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E86" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F86">
         <f>COUNTIF(E$3:E86,E86)</f>
@@ -20821,7 +20815,7 @@
     </row>
     <row r="96" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E96" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F96">
         <f>COUNTIF(E$3:E96,E96)</f>
@@ -22116,7 +22110,7 @@
     </row>
     <row r="106" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E106" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F106">
         <f>COUNTIF(E$3:E106,E106)</f>
@@ -32598,16 +32592,16 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Tロール回転軸
+	//波板補助軸
 	ELSIF uiInfoIdx = 15 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Tロール回転軸';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【axis15】 Tロール回転軸';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'M540-402';
-		ELSIF strInfoKey = 'mf' THEN
-			strRt	:= 'unknown';
+			strRt	:= '波板補助軸';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【axis15】 波板補助軸';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'AZM15AK';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'OrientalMotor';
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A7C67D-B9EE-4CDA-A145-6E53355D1400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F143E3B-9B9F-45E6-85C8-DC091DD1B453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -1674,9 +1674,6 @@
     <t>サーボモータ</t>
   </si>
   <si>
-    <t>Flat tension axis</t>
-  </si>
-  <si>
     <t>平板チャック軸</t>
     <rPh sb="0" eb="2">
       <t>ヒライタ</t>
@@ -1700,9 +1697,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Flat plate chuck shaft</t>
-  </si>
-  <si>
     <t>Flat plate chuck front and rear shafts</t>
   </si>
   <si>
@@ -1711,6 +1705,14 @@
   </si>
   <si>
     <t>RCP6-TA6C-WA-42P-12-125-P3-X07-CJB-1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Flat plate chuck shaft</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Flat tension axis</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2003,7 +2005,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2131,9 +2133,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3315,7 +3314,7 @@
         <v>315</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>33</v>
@@ -3354,13 +3353,13 @@
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G18" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="H18" s="8" t="s">
         <v>322</v>
-      </c>
-      <c r="H18" s="43" t="s">
-        <v>324</v>
       </c>
       <c r="I18" s="8"/>
       <c r="J18" s="8" t="s">
@@ -3394,13 +3393,13 @@
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="G19" s="8" t="s">
         <v>321</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="H19" s="8" t="s">
         <v>323</v>
-      </c>
-      <c r="H19" s="43" t="s">
-        <v>325</v>
       </c>
       <c r="I19" s="8"/>
       <c r="J19" s="8" t="s">
@@ -6170,7 +6169,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_script</v>
+        <v>C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_index</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
@@ -6574,7 +6573,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ref="E5:E68" si="0">E4</f>
@@ -8149,7 +8148,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AK$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//Foil wax reel shaft
@@ -32432,7 +32431,7 @@
     <row r="205" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="AK205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AK$3:AK$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//Foil wax reel shaft

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8571AFB4-186B-457B-A93A-EEA5971D4B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4C8DC8-3F2F-4AAF-AAFC-E3089BACE9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
   <sheets>
     <sheet name="info_index" sheetId="1" r:id="rId1"/>
@@ -877,9 +877,6 @@
     <t>波板カット刃開閉</t>
   </si>
   <si>
-    <t>平板押え上下①</t>
-  </si>
-  <si>
     <t>波板押え</t>
     <rPh sb="0" eb="2">
       <t>ナミイタ</t>
@@ -960,9 +957,6 @@
   </si>
   <si>
     <t>Flat sheet chuck open/close</t>
-  </si>
-  <si>
-    <t>Flat sheet clamp up/down ①</t>
   </si>
   <si>
     <t>Foil wax clamp up/down</t>
@@ -1721,6 +1715,14 @@
   </si>
   <si>
     <t>Corrugated sheet tensioning shaft</t>
+  </si>
+  <si>
+    <t>平板押え上下</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Flat sheet clamp up/down</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -2597,7 +2599,7 @@
         <v>105</v>
       </c>
       <c r="G1" s="39" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H1" s="39" t="s">
         <v>10</v>
@@ -2609,7 +2611,7 @@
         <v>3</v>
       </c>
       <c r="K1" s="39" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L1" s="39" t="s">
         <v>5</v>
@@ -2618,16 +2620,16 @@
         <v>112</v>
       </c>
       <c r="N1" s="40" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O1" s="40" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="P1" s="41" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="Q1" s="41" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="R1" s="40"/>
     </row>
@@ -2651,7 +2653,7 @@
         <v>132</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H2" s="28" t="s">
         <v>20</v>
@@ -2660,10 +2662,10 @@
         <v>21</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L2" s="28">
         <v>1</v>
@@ -2699,7 +2701,7 @@
         <v>125</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>14</v>
@@ -2708,10 +2710,10 @@
         <v>13</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L3" s="12">
         <v>1</v>
@@ -2747,7 +2749,7 @@
         <v>124</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>14</v>
@@ -2756,10 +2758,10 @@
         <v>13</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L4" s="12">
         <v>1</v>
@@ -2795,7 +2797,7 @@
         <v>89</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>14</v>
@@ -2804,10 +2806,10 @@
         <v>13</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L5" s="12">
         <v>1</v>
@@ -2840,10 +2842,10 @@
         <v>94</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>1</v>
@@ -2855,7 +2857,7 @@
         <v>2</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L6" s="8">
         <v>1</v>
@@ -2891,7 +2893,7 @@
         <v>130</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>0</v>
@@ -2903,7 +2905,7 @@
         <v>2</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L7" s="8">
         <v>1</v>
@@ -2939,7 +2941,7 @@
         <v>129</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>28</v>
@@ -2951,7 +2953,7 @@
         <v>2</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L8" s="8">
         <v>1</v>
@@ -2984,10 +2986,10 @@
         <v>101</v>
       </c>
       <c r="F9" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>257</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>259</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>106</v>
@@ -2999,7 +3001,7 @@
         <v>2</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L9" s="8">
         <v>1</v>
@@ -3032,10 +3034,10 @@
         <v>101</v>
       </c>
       <c r="F10" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>258</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>260</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>107</v>
@@ -3047,7 +3049,7 @@
         <v>2</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L10" s="8">
         <v>1</v>
@@ -3079,7 +3081,7 @@
         <v>131</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
@@ -3113,7 +3115,7 @@
         <v>133</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
@@ -3147,7 +3149,7 @@
         <v>134</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
@@ -3185,7 +3187,7 @@
         <v>126</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>31</v>
@@ -3194,10 +3196,10 @@
         <v>32</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L14" s="8">
         <v>1</v>
@@ -3233,7 +3235,7 @@
         <v>127</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>33</v>
@@ -3242,10 +3244,10 @@
         <v>32</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L15" s="8">
         <v>1</v>
@@ -3275,23 +3277,23 @@
         <v>10</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F16" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="H16" s="8" t="s">
         <v>268</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>270</v>
       </c>
       <c r="I16" s="8"/>
       <c r="J16" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L16" s="8"/>
       <c r="M16" s="10"/>
@@ -3318,22 +3320,22 @@
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
       <c r="F17" s="8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>33</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L17" s="8"/>
       <c r="M17" s="10"/>
@@ -3360,20 +3362,20 @@
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="I18" s="8"/>
       <c r="J18" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L18" s="8"/>
       <c r="M18" s="10"/>
@@ -3400,20 +3402,20 @@
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G19" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="H19" s="8" t="s">
         <v>318</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>320</v>
       </c>
       <c r="I19" s="8"/>
       <c r="J19" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L19" s="8"/>
       <c r="M19" s="10"/>
@@ -3440,22 +3442,22 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H20" s="42" t="s">
         <v>33</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L20" s="8">
         <v>1</v>
@@ -3484,22 +3486,22 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="H21" s="42" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L21" s="8">
         <v>1</v>
@@ -3528,22 +3530,22 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G22" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="H22" s="42" t="s">
+        <v>297</v>
+      </c>
+      <c r="I22" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="H22" s="42" t="s">
-        <v>299</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>300</v>
-      </c>
       <c r="J22" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L22" s="8">
         <v>1</v>
@@ -3572,22 +3574,22 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="H23" s="42" t="s">
         <v>301</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="I23" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="H23" s="42" t="s">
-        <v>303</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>304</v>
-      </c>
       <c r="J23" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L23" s="8">
         <v>1</v>
@@ -3616,22 +3618,22 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="8" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H24" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L24" s="8">
         <v>1</v>
@@ -3660,22 +3662,22 @@
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H25" s="42" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L25" s="8">
         <v>1</v>
@@ -3704,22 +3706,22 @@
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="H26" s="42" t="s">
         <v>312</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="I26" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="H26" s="42" t="s">
-        <v>314</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>315</v>
-      </c>
       <c r="J26" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L26" s="8"/>
       <c r="M26" s="10"/>
@@ -3750,10 +3752,10 @@
         <v>99</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>61</v>
@@ -3765,7 +3767,7 @@
         <v>4</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L27" s="8">
         <v>1</v>
@@ -3798,13 +3800,13 @@
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="G28" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="G28" s="8" t="s">
-        <v>279</v>
-      </c>
       <c r="H28" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I28" s="8"/>
       <c r="J28" s="8"/>
@@ -3838,13 +3840,13 @@
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="G29" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="G29" s="8" t="s">
-        <v>280</v>
-      </c>
       <c r="H29" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I29" s="8"/>
       <c r="J29" s="8"/>
@@ -3882,10 +3884,10 @@
         <v>137</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="H30" s="8" t="s">
         <v>63</v>
@@ -3897,7 +3899,7 @@
         <v>4</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L30" s="8">
         <v>1</v>
@@ -3934,10 +3936,10 @@
         <v>93</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>67</v>
@@ -3949,7 +3951,7 @@
         <v>4</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L31" s="8">
         <v>1</v>
@@ -3986,10 +3988,10 @@
         <v>93</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>65</v>
@@ -4001,7 +4003,7 @@
         <v>4</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L32" s="8">
         <v>1</v>
@@ -4038,10 +4040,10 @@
         <v>98</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>140</v>
+        <v>323</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>161</v>
+        <v>324</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>69</v>
@@ -4053,7 +4055,7 @@
         <v>4</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L33" s="11">
         <v>1</v>
@@ -4090,10 +4092,10 @@
         <v>92</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>73</v>
@@ -4105,7 +4107,7 @@
         <v>4</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L34" s="11">
         <v>1</v>
@@ -4145,7 +4147,7 @@
         <v>121</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>71</v>
@@ -4157,7 +4159,7 @@
         <v>4</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L35" s="11">
         <v>1</v>
@@ -4194,10 +4196,10 @@
         <v>100</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H36" s="8" t="s">
         <v>69</v>
@@ -4209,7 +4211,7 @@
         <v>4</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L36" s="11">
         <v>1</v>
@@ -4249,7 +4251,7 @@
         <v>135</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H37" s="12" t="s">
         <v>75</v>
@@ -4261,7 +4263,7 @@
         <v>4</v>
       </c>
       <c r="K37" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L37" s="13">
         <v>1</v>
@@ -4301,7 +4303,7 @@
         <v>138</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H38" s="8" t="s">
         <v>74</v>
@@ -4313,7 +4315,7 @@
         <v>4</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L38" s="11">
         <v>1</v>
@@ -4353,7 +4355,7 @@
         <v>136</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H39" s="12" t="s">
         <v>75</v>
@@ -4365,7 +4367,7 @@
         <v>4</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L39" s="13">
         <v>1</v>
@@ -4405,7 +4407,7 @@
         <v>139</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>76</v>
@@ -4417,7 +4419,7 @@
         <v>4</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L40" s="11">
         <v>1</v>
@@ -4454,10 +4456,10 @@
         <v>96</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H41" s="12" t="s">
         <v>77</v>
@@ -4469,7 +4471,7 @@
         <v>4</v>
       </c>
       <c r="K41" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L41" s="13">
         <v>1</v>
@@ -4506,10 +4508,10 @@
         <v>96</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H42" s="12" t="s">
         <v>77</v>
@@ -4521,7 +4523,7 @@
         <v>4</v>
       </c>
       <c r="K42" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L42" s="13">
         <v>1</v>
@@ -4554,10 +4556,10 @@
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
       <c r="F43" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H43" s="8" t="s">
         <v>51</v>
@@ -4594,10 +4596,10 @@
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
       <c r="F44" s="8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H44" s="8" t="s">
         <v>51</v>
@@ -4634,13 +4636,13 @@
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
       <c r="F45" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
@@ -4678,22 +4680,22 @@
         <v>92</v>
       </c>
       <c r="F46" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="G46" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="G46" s="8" t="s">
+      <c r="H46" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="I46" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="H46" s="8" t="s">
+      <c r="J46" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="I46" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="J46" s="8" t="s">
-        <v>266</v>
-      </c>
       <c r="K46" s="8" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="L46" s="8"/>
       <c r="M46" s="10"/>
@@ -4733,7 +4735,7 @@
         <v>4</v>
       </c>
       <c r="K47" s="14" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L47" s="15">
         <v>1</v>
@@ -4777,7 +4779,7 @@
         <v>4</v>
       </c>
       <c r="K48" s="14" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L48" s="15">
         <v>1</v>
@@ -4821,7 +4823,7 @@
         <v>4</v>
       </c>
       <c r="K49" s="14" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L49" s="15">
         <v>1</v>
@@ -4859,7 +4861,7 @@
         <v>128</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H50" s="8" t="s">
         <v>30</v>
@@ -4871,7 +4873,7 @@
         <v>2</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L50" s="8">
         <v>1</v>
@@ -4912,10 +4914,10 @@
         <v>8</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L51" s="8">
         <v>1</v>
@@ -4956,10 +4958,10 @@
         <v>9</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L52" s="8">
         <v>1</v>
@@ -4998,10 +5000,10 @@
         <v>23</v>
       </c>
       <c r="J53" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K53" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L53" s="8">
         <v>3</v>
@@ -5042,10 +5044,10 @@
         <v>24</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K54" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L54" s="8">
         <v>1</v>
@@ -5088,10 +5090,10 @@
         <v>36</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L55" s="8">
         <v>1</v>
@@ -5130,10 +5132,10 @@
         <v>59</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K56" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L56" s="8">
         <v>1</v>
@@ -5170,10 +5172,10 @@
         <v>19</v>
       </c>
       <c r="J57" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K57" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L57" s="8">
         <v>1</v>
@@ -5210,10 +5212,10 @@
         <v>17</v>
       </c>
       <c r="J58" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K58" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L58" s="8">
         <v>1</v>
@@ -5250,10 +5252,10 @@
         <v>26</v>
       </c>
       <c r="J59" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K59" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L59" s="8">
         <v>1</v>
@@ -5292,10 +5294,10 @@
         <v>26</v>
       </c>
       <c r="J60" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K60" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L60" s="8">
         <v>1</v>
@@ -5316,7 +5318,7 @@
         <v>51</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C61" s="7">
         <v>1</v>
@@ -5324,10 +5326,10 @@
       <c r="D61" s="8"/>
       <c r="E61" s="8"/>
       <c r="F61" s="8" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
@@ -5350,7 +5352,7 @@
         <v>52</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C62" s="7">
         <v>2</v>
@@ -5358,10 +5360,10 @@
       <c r="D62" s="8"/>
       <c r="E62" s="8"/>
       <c r="F62" s="8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
@@ -5384,7 +5386,7 @@
         <v>53</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C63" s="7">
         <v>3</v>
@@ -5392,10 +5394,10 @@
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
       <c r="F63" s="8" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H63" s="8"/>
       <c r="I63" s="8"/>
@@ -5418,7 +5420,7 @@
         <v>54</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C64" s="7">
         <v>4</v>
@@ -5426,10 +5428,10 @@
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
       <c r="F64" s="8" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
@@ -5452,7 +5454,7 @@
         <v>55</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C65" s="7">
         <v>5</v>
@@ -5460,10 +5462,10 @@
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
       <c r="F65" s="8" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
@@ -5486,7 +5488,7 @@
         <v>56</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C66" s="7">
         <v>6</v>
@@ -5494,10 +5496,10 @@
       <c r="D66" s="8"/>
       <c r="E66" s="8"/>
       <c r="F66" s="8" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
@@ -5520,7 +5522,7 @@
         <v>60</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C67" s="7">
         <v>7</v>
@@ -5528,10 +5530,10 @@
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
       <c r="F67" s="8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
@@ -5554,7 +5556,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C68" s="7">
         <v>8</v>
@@ -5562,10 +5564,10 @@
       <c r="D68" s="8"/>
       <c r="E68" s="8"/>
       <c r="F68" s="8" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
@@ -5588,7 +5590,7 @@
         <v>57</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C69" s="7">
         <v>1</v>
@@ -5596,10 +5598,10 @@
       <c r="D69" s="8"/>
       <c r="E69" s="8"/>
       <c r="F69" s="8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
@@ -5622,7 +5624,7 @@
         <v>61</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C70" s="7">
         <v>2</v>
@@ -5630,10 +5632,10 @@
       <c r="D70" s="8"/>
       <c r="E70" s="8"/>
       <c r="F70" s="8" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
@@ -5656,7 +5658,7 @@
         <v>62</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C71" s="7">
         <v>1</v>
@@ -5664,10 +5666,10 @@
       <c r="D71" s="8"/>
       <c r="E71" s="8"/>
       <c r="F71" s="8" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H71" s="8"/>
       <c r="I71" s="8"/>
@@ -5690,7 +5692,7 @@
         <v>63</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C72" s="7">
         <v>2</v>
@@ -5698,10 +5700,10 @@
       <c r="D72" s="8"/>
       <c r="E72" s="8"/>
       <c r="F72" s="8" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
@@ -5724,7 +5726,7 @@
         <v>64</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C73" s="7">
         <v>3</v>
@@ -5732,10 +5734,10 @@
       <c r="D73" s="8"/>
       <c r="E73" s="8"/>
       <c r="F73" s="8" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H73" s="8"/>
       <c r="I73" s="8"/>
@@ -5793,7 +5795,7 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B78" t="s">
         <v>117</v>
@@ -6055,19 +6057,19 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="F1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J1" t="s">
+        <v>219</v>
+      </c>
+      <c r="L1" t="s">
+        <v>220</v>
+      </c>
+      <c r="N1" t="s">
         <v>221</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>222</v>
-      </c>
-      <c r="N1" t="s">
-        <v>223</v>
-      </c>
-      <c r="P1" t="s">
-        <v>224</v>
       </c>
       <c r="AA1" t="str">
         <f>IF(LEN(J1),J2&amp;CHAR(9)&amp;":"&amp;J1,"")</f>
@@ -6101,82 +6103,82 @@
     </row>
     <row r="2" spans="1:37" s="30" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="30" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E2" s="30" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F2" s="30" t="s">
         <v>102</v>
       </c>
       <c r="G2" s="30" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H2" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="L2" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="N2" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="P2" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="J2" s="30" t="s">
-        <v>184</v>
-      </c>
-      <c r="L2" s="30" t="s">
+      <c r="X2" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="Y2" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="N2" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="P2" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="X2" s="30" t="s">
+      <c r="Z2" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="AA2" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="AB2" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="AC2" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="AD2" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="AE2" s="30" t="s">
         <v>196</v>
       </c>
-      <c r="Y2" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="Z2" s="30" t="s">
-        <v>188</v>
-      </c>
-      <c r="AA2" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="AB2" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="AC2" s="30" t="s">
-        <v>191</v>
-      </c>
-      <c r="AD2" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="AE2" s="30" t="s">
-        <v>198</v>
-      </c>
       <c r="AF2" s="30" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG2" s="30" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AH2" s="30" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AI2" s="30" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AJ2" s="30" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AK2" s="30" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_script</v>
+        <v>C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_index</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
@@ -6576,11 +6578,11 @@
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ref="E5:E68" si="0">E4</f>
@@ -6776,10 +6778,10 @@
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
@@ -6975,10 +6977,10 @@
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -7174,10 +7176,10 @@
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -7373,10 +7375,10 @@
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -8151,11 +8153,11 @@
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B13" t="str">
         <f ca="1">$AK$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸
@@ -8584,12 +8586,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//平板押え上下①
+	//平板押え上下
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= '平板押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9152,7 +9154,7 @@
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B14" t="str">
         <f>IF(LEN(AI1),"●"&amp;B27&amp;CHAR(10)&amp;AI1,"")</f>
@@ -10900,7 +10902,7 @@
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -11292,10 +11294,10 @@
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B25" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E25" t="str">
         <f t="shared" si="0"/>
@@ -11491,10 +11493,10 @@
     </row>
     <row r="26" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B26" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E26" t="str">
         <f t="shared" si="0"/>
@@ -11690,10 +11692,10 @@
     </row>
     <row r="27" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B27" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E27" t="str">
         <f t="shared" si="0"/>
@@ -11889,10 +11891,10 @@
     </row>
     <row r="28" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B28" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E28" t="str">
         <f t="shared" si="0"/>
@@ -11993,10 +11995,10 @@
     </row>
     <row r="29" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B29" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E29" t="str">
         <f t="shared" si="0"/>
@@ -16659,15 +16661,15 @@
       </c>
       <c r="I69" t="str">
         <f ca="1"/>
-        <v>平板押え上下①</v>
+        <v>平板押え上下</v>
       </c>
       <c r="J69" t="str">
         <f ca="1"/>
-        <v>平板押え上下①</v>
+        <v>平板押え上下</v>
       </c>
       <c r="L69" t="str">
         <f ca="1"/>
-        <v>【cylinder7】 平板押え上下①</v>
+        <v>【cylinder7】 平板押え上下</v>
       </c>
       <c r="M69" t="str">
         <v>CDQ2B25-20DZ-M9BVM</v>
@@ -16696,75 +16698,75 @@
       <c r="Z69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//平板押え上下
 	ELSIF uiInfoIdx = 7 THEN</v>
       </c>
       <c r="AA69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//平板押え上下
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//平板押え上下
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';</v>
+			strRt	:= '平板押え上下';</v>
       </c>
       <c r="AC69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//平板押え上下
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';
+			strRt	:= '平板押え上下';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//平板押え上下
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 平板押え上下①';</v>
+			strRt	:= '平板押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下';</v>
       </c>
       <c r="AE69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//平板押え上下
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= '平板押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//平板押え上下
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= '平板押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';</v>
       </c>
       <c r="AG69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//平板押え上下
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= '平板押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -16772,12 +16774,12 @@
       <c r="AH69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//平板押え上下
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= '平板押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16786,12 +16788,12 @@
       <c r="AI69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//平板押え上下
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= '平板押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16803,12 +16805,12 @@
       <c r="AJ69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//平板押え上下
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= '平板押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -16820,12 +16822,12 @@
       <c r="AK69" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//平板押え上下①
+	//平板押え上下
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= '平板押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN
@@ -19646,7 +19648,7 @@
     </row>
     <row r="86" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E86" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F86">
         <f>COUNTIF(E$3:E86,E86)</f>
@@ -20846,7 +20848,7 @@
     </row>
     <row r="96" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E96" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F96">
         <f>COUNTIF(E$3:E96,E96)</f>
@@ -22141,7 +22143,7 @@
     </row>
     <row r="106" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E106" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F106">
         <f>COUNTIF(E$3:E106,E106)</f>
@@ -32438,7 +32440,7 @@
     <row r="205" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="AK205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AK$3:AK$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸
@@ -32867,12 +32869,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//平板押え上下①
+	//平板押え上下
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '平板押え上下①';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【cylinder7】 平板押え上下①';
+			strRt	:= '平板押え上下';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【cylinder7】 平板押え上下';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'CDQ2B25-20DZ-M9BVM';
 		ELSIF strInfoKey = 'mf' THEN

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA94DD3-DA99-450E-BEF0-1CCB7A47C698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E397C62-F638-4CAC-BFDC-18B41EE6072C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="info_script" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$R$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$D$2:$W$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="392">
   <si>
     <t>RCA2-GS3NA-I-10-2-50-A6-M-K1</t>
   </si>
@@ -1200,6 +1200,9 @@
   </si>
   <si>
     <t>波板送り軸</t>
+  </si>
+  <si>
+    <t>波板送り軸</t>
     <rPh sb="0" eb="2">
       <t>ナミイタ</t>
     </rPh>
@@ -1212,6 +1215,12 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>ワーク排出上下軸</t>
+  </si>
+  <si>
+    <t>溶接トーチ前後軸</t>
+  </si>
+  <si>
     <t>溶接トーチ前後軸</t>
     <rPh sb="0" eb="2">
       <t>ヨウセツ</t>
@@ -1223,6 +1232,9 @@
   </si>
   <si>
     <t>溶接トーチ上下軸</t>
+  </si>
+  <si>
+    <t>溶接トーチ上下軸</t>
     <rPh sb="0" eb="2">
       <t>ヨウセツ</t>
     </rPh>
@@ -1230,6 +1242,9 @@
       <t>ジョウゲ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>巻取り主軸</t>
   </si>
   <si>
     <t>ベース</t>
@@ -1525,6 +1540,211 @@
   </si>
   <si>
     <t>Workpiece Discharge F/B</t>
+  </si>
+  <si>
+    <t>緒言</t>
+    <rPh sb="0" eb="2">
+      <t>ショゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>短縮文字列制限[バイト]</t>
+    <rPh sb="0" eb="2">
+      <t>タンシュク</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セイゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>短縮機器名</t>
+  </si>
+  <si>
+    <t>短縮機器名(EN)</t>
+  </si>
+  <si>
+    <t>文字数オーバー</t>
+    <rPh sb="0" eb="3">
+      <t>モジスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文字数オーバー(EN)</t>
+    <rPh sb="0" eb="3">
+      <t>モジスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箔ロウリール軸</t>
+  </si>
+  <si>
+    <t>平板送り軸</t>
+  </si>
+  <si>
+    <t>箔ロウ送り軸</t>
+  </si>
+  <si>
+    <t>周長測定上下軸</t>
+  </si>
+  <si>
+    <t>排出チャック軸</t>
+  </si>
+  <si>
+    <t>バインダ供給ポンプM</t>
+  </si>
+  <si>
+    <t>波板リールM</t>
+  </si>
+  <si>
+    <t>平板リールM</t>
+  </si>
+  <si>
+    <t>ワーク幅調整軸</t>
+  </si>
+  <si>
+    <t>波板補助軸</t>
+  </si>
+  <si>
+    <t>平板張力軸</t>
+  </si>
+  <si>
+    <t>Flat Sheet Feed Ax</t>
+  </si>
+  <si>
+    <t>Brazing Foil Feed</t>
+  </si>
+  <si>
+    <t>Corr Sheet Feed Ax</t>
+  </si>
+  <si>
+    <t>Work Disch Lift</t>
+  </si>
+  <si>
+    <t>Circum Probe Lift</t>
+  </si>
+  <si>
+    <t>Discharge Chuck Ax</t>
+  </si>
+  <si>
+    <t>Weld Torch F/B Ax</t>
+  </si>
+  <si>
+    <t>Weld Torch U/D Ax</t>
+  </si>
+  <si>
+    <t>Binder Pump Motor</t>
+  </si>
+  <si>
+    <t>Corr Sheet Reel M</t>
+  </si>
+  <si>
+    <t>Flat Sheet Reel M</t>
+  </si>
+  <si>
+    <t>Work Width Adj Ax</t>
+  </si>
+  <si>
+    <t>Corr Sheet Aux Ax</t>
+  </si>
+  <si>
+    <t>Flat Sheet Tens Ax</t>
+  </si>
+  <si>
+    <t>Tロール糊下ロール</t>
+  </si>
+  <si>
+    <t>Tロール糊上ロール</t>
+  </si>
+  <si>
+    <t>平板チャック前後</t>
+  </si>
+  <si>
+    <t>平板刃押出し</t>
+  </si>
+  <si>
+    <t>平板刃開閉</t>
+  </si>
+  <si>
+    <t>波板刃押出し</t>
+  </si>
+  <si>
+    <t>波板刃開閉</t>
+  </si>
+  <si>
+    <t>Xロール左ロール</t>
+  </si>
+  <si>
+    <t>Xロール右ロール</t>
+  </si>
+  <si>
+    <t>Wind Shaft Ctr F/B</t>
+  </si>
+  <si>
+    <t>T-Roll Glue Lower</t>
+  </si>
+  <si>
+    <t>T-Roll Glue Upper</t>
+  </si>
+  <si>
+    <t>Flat Sheet Sup Plt</t>
+  </si>
+  <si>
+    <t>Flat Chuck F/B</t>
+  </si>
+  <si>
+    <t>Flat Chuck O/C</t>
+  </si>
+  <si>
+    <t>Flat Clamp U/D</t>
+  </si>
+  <si>
+    <t>Foil Clamp U/D</t>
+  </si>
+  <si>
+    <t>Brazing Foil Cut</t>
+  </si>
+  <si>
+    <t>Corr Sheet Clamp</t>
+  </si>
+  <si>
+    <t>Flat Cutter Extend</t>
+  </si>
+  <si>
+    <t>Flat Cutter O/C</t>
+  </si>
+  <si>
+    <t>Corr Cutter Extend</t>
+  </si>
+  <si>
+    <t>Corr Cutter O/C</t>
+  </si>
+  <si>
+    <t>Corr Cutter Support</t>
+  </si>
+  <si>
+    <t>Corr Cut Supp L</t>
+  </si>
+  <si>
+    <t>X-Roll Left Roll</t>
+  </si>
+  <si>
+    <t>X-Roll Right Roll</t>
+  </si>
+  <si>
+    <t>X-Roll Flat Press</t>
+  </si>
+  <si>
+    <t>Foil Reel Lock</t>
+  </si>
+  <si>
+    <t>Work Discharge F/B</t>
   </si>
 </sst>
 </file>
@@ -1816,7 +2036,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1946,23 +2166,14 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0099CC"/>
-      </font>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF7C80"/>
@@ -1981,6 +2192,18 @@
           <fgColor rgb="FF33CCCC"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0099CC"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2008,18 +2231,18 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>204304</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>496957</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$A$77">
+    <xdr:sp macro="" textlink="$D$78">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="正方形/長方形 1">
           <a:extLst>
@@ -2388,3452 +2611,4352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R101"/>
+  <dimension ref="A2:Z102"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="31.4140625" customWidth="1"/>
-    <col min="8" max="8" width="81" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="71.08203125" customWidth="1"/>
-    <col min="10" max="11" width="13.08203125" customWidth="1"/>
-    <col min="12" max="15" width="18.33203125" customWidth="1"/>
-    <col min="16" max="17" width="18.33203125" style="31" customWidth="1"/>
-    <col min="18" max="18" width="3.58203125" customWidth="1"/>
+    <col min="1" max="1" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="31.4140625" customWidth="1"/>
+    <col min="13" max="13" width="81" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="71.08203125" customWidth="1"/>
+    <col min="15" max="16" width="13.08203125" customWidth="1"/>
+    <col min="17" max="20" width="18.33203125" customWidth="1"/>
+    <col min="21" max="22" width="18.33203125" style="31" customWidth="1"/>
+    <col min="23" max="23" width="3.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="38" t="s">
+    <row r="2" spans="1:26" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="D2" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="E2" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="F2" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="G2" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="H2" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="I2" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="J2" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="H1" s="39" t="s">
+      <c r="K2" s="39" t="s">
+        <v>333</v>
+      </c>
+      <c r="L2" s="39" t="s">
+        <v>334</v>
+      </c>
+      <c r="M2" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="N2" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="39" t="s">
+      <c r="O2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="39" t="s">
+      <c r="P2" s="39" t="s">
         <v>154</v>
       </c>
-      <c r="L1" s="39" t="s">
+      <c r="Q2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="40" t="s">
+      <c r="R2" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="N1" s="40" t="s">
+      <c r="S2" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="O1" s="40" t="s">
+      <c r="T2" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="P1" s="41" t="s">
+      <c r="U2" s="41" t="s">
         <v>186</v>
       </c>
-      <c r="Q1" s="41" t="s">
+      <c r="V2" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="R1" s="40"/>
+      <c r="W2" s="40"/>
+      <c r="Y2" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>336</v>
+      </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="27">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D3" s="27">
         <v>38</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C2" s="5">
+      <c r="F3" s="5">
         <v>1</v>
       </c>
-      <c r="D2" s="28">
+      <c r="G3" s="28">
         <v>7</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="H3" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="I3" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="G2" s="28" t="s">
-        <v>283</v>
-      </c>
-      <c r="H2" s="28" t="s">
+      <c r="J3" s="28" t="s">
+        <v>288</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>337</v>
+      </c>
+      <c r="L3" s="28" t="s">
+        <v>232</v>
+      </c>
+      <c r="M3" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="28" t="s">
+      <c r="N3" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="O3" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="K2" s="28" t="s">
+      <c r="P3" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="L2" s="28">
+      <c r="Q3" s="28">
         <v>1</v>
       </c>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="32">
+      <c r="R3" s="29"/>
+      <c r="S3" s="29"/>
+      <c r="T3" s="29"/>
+      <c r="U3" s="32">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q2" s="32">
+      <c r="V3" s="32">
         <v>46226.618055555555</v>
       </c>
-      <c r="R2" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="Y3">
+        <f>LENB(K3)-$B$4</f>
+        <v>-4</v>
+      </c>
+      <c r="Z3">
+        <f>LENB(L3)-$B$4</f>
+        <v>-1</v>
+      </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="7">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B4">
+        <v>18</v>
+      </c>
+      <c r="D4" s="7">
         <v>35</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="7">
+      <c r="F4" s="7">
         <v>2</v>
       </c>
-      <c r="D3" s="12">
+      <c r="G4" s="12">
         <v>6</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="H4" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="I4" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="H3" s="12" t="s">
+      <c r="J4" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="M4" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="N4" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="O4" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="P4" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="L3" s="12">
+      <c r="Q4" s="12">
         <v>1</v>
       </c>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="33">
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="24"/>
+      <c r="U4" s="33">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q3" s="33">
+      <c r="V4" s="33">
         <v>46226.618055555555</v>
       </c>
-      <c r="R3" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="Y4">
+        <f t="shared" ref="Y4:Z67" si="0">LENB(K4)-$B$4</f>
+        <v>-8</v>
+      </c>
+      <c r="Z4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="7">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D5" s="7">
         <v>37</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="7">
+      <c r="F5" s="7">
         <v>3</v>
       </c>
-      <c r="D4" s="12">
+      <c r="G5" s="12">
         <v>7</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="H5" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="I5" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="G4" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="H4" s="12" t="s">
+      <c r="J5" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="M5" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="N5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="17" t="s">
+      <c r="O5" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="P5" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="L4" s="12">
+      <c r="Q5" s="12">
         <v>1</v>
       </c>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="33">
+      <c r="R5" s="24"/>
+      <c r="S5" s="24"/>
+      <c r="T5" s="24"/>
+      <c r="U5" s="33">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="V5" s="33">
         <v>46226.618055555555</v>
       </c>
-      <c r="R4" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="Y5">
+        <f t="shared" si="0"/>
+        <v>-6</v>
+      </c>
+      <c r="Z5">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="7">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D6" s="7">
         <v>36</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="7">
+      <c r="F6" s="7">
         <v>4</v>
       </c>
-      <c r="D5" s="12">
+      <c r="G6" s="12">
         <v>8</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="H6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="I6" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="K6" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="G5" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="H5" s="12" t="s">
+      <c r="L6" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="M6" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="N6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="17" t="s">
+      <c r="O6" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="P6" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="L5" s="12">
+      <c r="Q6" s="12">
         <v>1</v>
       </c>
-      <c r="M5" s="24"/>
-      <c r="N5" s="24"/>
-      <c r="O5" s="24"/>
-      <c r="P5" s="33">
+      <c r="R6" s="24"/>
+      <c r="S6" s="24"/>
+      <c r="T6" s="24"/>
+      <c r="U6" s="33">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q5" s="33">
+      <c r="V6" s="33">
         <v>46226.618055555555</v>
       </c>
-      <c r="R5" s="10"/>
+      <c r="W6" s="10"/>
+      <c r="Y6">
+        <f t="shared" si="0"/>
+        <v>-8</v>
+      </c>
+      <c r="Z6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="7">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D7" s="7">
         <v>19</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C6" s="7">
+      <c r="F7" s="7">
         <v>5</v>
       </c>
-      <c r="D6" s="8">
+      <c r="G7" s="8">
         <v>3</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="H7" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="I7" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="G6" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="H6" s="8" t="s">
+      <c r="J7" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="M7" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="N7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="O7" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="P7" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="L6" s="8">
+      <c r="Q7" s="8">
         <v>1</v>
       </c>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="34">
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q6" s="34">
+      <c r="V7" s="34">
         <v>46226.618055555555</v>
       </c>
-      <c r="R6" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="Y7">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="Z7">
+        <f t="shared" si="0"/>
+        <v>-3</v>
+      </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="7">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D8" s="7">
         <v>18</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="E8" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="7">
+      <c r="F8" s="7">
         <v>6</v>
       </c>
-      <c r="D7" s="8">
+      <c r="G8" s="8">
         <v>3</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="H8" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="I8" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="H7" s="8" t="s">
+      <c r="J8" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="M8" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="N8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="O8" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="P8" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="L7" s="8">
+      <c r="Q8" s="8">
         <v>1</v>
       </c>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="34">
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q7" s="34">
+      <c r="V8" s="34">
         <v>46226.618055555555</v>
       </c>
-      <c r="R7" s="10"/>
+      <c r="W8" s="10"/>
+      <c r="Y8">
+        <f t="shared" si="0"/>
+        <v>-4</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="7">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D9" s="7">
         <v>20</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="7">
+      <c r="F9" s="7">
         <v>7</v>
       </c>
-      <c r="D8" s="8">
+      <c r="G9" s="8">
         <v>1</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="H9" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="I9" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="G8" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="H8" s="8" t="s">
+      <c r="J9" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="M9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="N9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="O9" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="P9" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="L8" s="8">
+      <c r="Q9" s="8">
         <v>1</v>
       </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="34">
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q8" s="34">
+      <c r="V9" s="34">
         <v>46226.618055555555</v>
       </c>
-      <c r="R8" s="10"/>
+      <c r="W9" s="10"/>
+      <c r="Y9">
+        <f t="shared" si="0"/>
+        <v>-4</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="7">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D10" s="7">
         <v>22</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="E10" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="7">
+      <c r="F10" s="7">
         <v>8</v>
       </c>
-      <c r="D9" s="8">
+      <c r="G10" s="8">
         <v>10</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="H10" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="H9" s="8" t="s">
+      <c r="I10" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="M10" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="N10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="O10" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="P10" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="L9" s="8">
+      <c r="Q10" s="8">
         <v>1</v>
       </c>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="34">
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q9" s="34">
+      <c r="V10" s="34">
         <v>46226.618055555555</v>
       </c>
-      <c r="R9" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="Y10">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="7">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D11" s="7">
         <v>23</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C10" s="7">
+      <c r="F11" s="7">
         <v>9</v>
       </c>
-      <c r="D10" s="8">
+      <c r="G11" s="8">
         <v>10</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="H11" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="H10" s="8" t="s">
+      <c r="I11" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="M11" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="N11" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="O11" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="P11" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="L10" s="8">
+      <c r="Q11" s="8">
         <v>1</v>
       </c>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="34">
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q10" s="34">
+      <c r="V11" s="34">
         <v>46226.618055555555</v>
       </c>
-      <c r="R10" s="10"/>
+      <c r="W11" s="10"/>
+      <c r="Y11">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="7">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D12" s="7">
         <v>42</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="E12" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="7">
+      <c r="F12" s="7">
         <v>10</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8" t="s">
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="J12" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="34">
+      <c r="K12" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
+      <c r="U12" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q11" s="34">
+      <c r="V12" s="34">
         <v>46226.618055555555</v>
       </c>
-      <c r="R11" s="10"/>
+      <c r="W12" s="10"/>
+      <c r="Y12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Z12">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="7">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D13" s="7">
         <v>43</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="E13" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C12" s="7">
+      <c r="F13" s="7">
         <v>11</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8" t="s">
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="G12" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="34">
+      <c r="J13" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q12" s="34">
+      <c r="V13" s="34">
         <v>46226.618055555555</v>
       </c>
-      <c r="R12" s="10"/>
+      <c r="W13" s="10"/>
+      <c r="Y13">
+        <f t="shared" si="0"/>
+        <v>-7</v>
+      </c>
+      <c r="Z13">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="7">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D14" s="7">
         <v>44</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="E14" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C13" s="7">
+      <c r="F14" s="7">
         <v>12</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8" t="s">
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="G13" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="34">
+      <c r="J14" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q13" s="34">
+      <c r="V14" s="34">
         <v>46226.618055555555</v>
       </c>
-      <c r="R13" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="Y14">
+        <f t="shared" si="0"/>
+        <v>-7</v>
+      </c>
+      <c r="Z14">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="7">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D15" s="7">
         <v>32</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C14" s="7">
+      <c r="F15" s="7">
         <v>13</v>
       </c>
-      <c r="D14" s="8">
+      <c r="G15" s="8">
         <v>1</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="H15" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="I15" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="G14" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="H14" s="8" t="s">
+      <c r="J15" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="M15" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="N15" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="O15" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="P15" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="L14" s="8">
+      <c r="Q15" s="8">
         <v>1</v>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="34">
+      <c r="R15" s="10"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10"/>
+      <c r="U15" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q14" s="34">
+      <c r="V15" s="34">
         <v>46226.618055555555</v>
       </c>
-      <c r="R14" s="10"/>
+      <c r="W15" s="10"/>
+      <c r="Y15">
+        <f t="shared" si="0"/>
+        <v>-8</v>
+      </c>
+      <c r="Z15">
+        <f t="shared" si="0"/>
+        <v>-3</v>
+      </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="7">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D16" s="7">
         <v>33</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="E16" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="7">
+      <c r="F16" s="7">
         <v>14</v>
       </c>
-      <c r="D15" s="8">
+      <c r="G16" s="8">
         <v>1</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="H16" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="I16" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="G15" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="H15" s="8" t="s">
+      <c r="J16" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="M16" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="N16" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="O16" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="P16" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="L15" s="8">
+      <c r="Q16" s="8">
         <v>1</v>
       </c>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="34">
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+      <c r="U16" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q15" s="34">
+      <c r="V16" s="34">
         <v>46226.618055555555</v>
       </c>
-      <c r="R15" s="10"/>
+      <c r="W16" s="10"/>
+      <c r="Y16">
+        <f t="shared" si="0"/>
+        <v>-4</v>
+      </c>
+      <c r="Z16">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="7">
+    <row r="17" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D17" s="7">
         <v>41</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="7">
+      <c r="F17" s="7">
         <v>15</v>
       </c>
-      <c r="D16" s="8">
+      <c r="G17" s="8">
         <v>10</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="H17" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="I17" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="G16" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="H16" s="8" t="s">
+      <c r="J17" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="M17" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8" t="s">
+      <c r="N17" s="8"/>
+      <c r="O17" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="K16" s="8" t="s">
+      <c r="P17" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="L16" s="8"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="34">
+      <c r="Q17" s="8"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q16" s="34">
+      <c r="V17" s="34">
         <v>46226.618055555555</v>
       </c>
-      <c r="R16" s="10"/>
+      <c r="W17" s="10"/>
+      <c r="Y17">
+        <f t="shared" si="0"/>
+        <v>-8</v>
+      </c>
+      <c r="Z17">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="7">
+    <row r="18" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D18" s="7">
         <v>45</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="E18" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C17" s="7">
+      <c r="F18" s="7">
         <v>16</v>
       </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8" t="s">
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="G17" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="H17" s="8" t="s">
+      <c r="J18" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="M18" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="N18" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="O18" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="K17" s="8" t="s">
+      <c r="P18" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="L17" s="8"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="34">
+      <c r="Q18" s="8"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q17" s="34">
+      <c r="V18" s="34">
         <v>46226.618055555555</v>
       </c>
-      <c r="R17" s="10"/>
+      <c r="W18" s="10"/>
+      <c r="Y18">
+        <f t="shared" si="0"/>
+        <v>-8</v>
+      </c>
+      <c r="Z18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="7">
+    <row r="19" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D19" s="7">
         <v>59</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="E19" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C18" s="7">
+      <c r="F19" s="7">
         <v>17</v>
       </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8" t="s">
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="J19" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8" t="s">
+      <c r="N19" s="8"/>
+      <c r="O19" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="K18" s="8" t="s">
+      <c r="P19" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="L18" s="8"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="34">
+      <c r="Q19" s="8"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="34">
         <v>46170.415277777778</v>
       </c>
-      <c r="Q18" s="34">
+      <c r="V19" s="34">
         <v>46170.415277777778</v>
       </c>
-      <c r="R18" s="10"/>
+      <c r="W19" s="10"/>
+      <c r="Y19">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z19">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="7">
+    <row r="20" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D20" s="7">
         <v>66</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="E20" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C19" s="7">
+      <c r="F20" s="7">
         <v>18</v>
       </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8" t="s">
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="J20" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8" t="s">
+      <c r="N20" s="8"/>
+      <c r="O20" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="K19" s="8" t="s">
+      <c r="P20" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="L19" s="8"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="34">
+      <c r="Q20" s="8"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="10"/>
+      <c r="U20" s="34">
         <v>46170.415277777778</v>
       </c>
-      <c r="Q19" s="34">
+      <c r="V20" s="34">
         <v>46170.415277777778</v>
       </c>
-      <c r="R19" s="10"/>
+      <c r="W20" s="10"/>
+      <c r="Y20">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z20">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="7">
+    <row r="21" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D21" s="7">
         <v>67</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="E21" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C20" s="7">
+      <c r="F21" s="7">
         <v>19</v>
       </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8" t="s">
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="J21" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="H20" s="42" t="s">
+      <c r="K21" s="43"/>
+      <c r="L21" s="43"/>
+      <c r="M21" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="I20" s="8" t="s">
+      <c r="N21" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="O21" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="K20" s="8" t="s">
+      <c r="P21" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="L20" s="8">
+      <c r="Q21" s="8">
         <v>1</v>
       </c>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="34">
+      <c r="R21" s="10"/>
+      <c r="S21" s="10"/>
+      <c r="T21" s="10"/>
+      <c r="U21" s="34">
         <v>46139</v>
       </c>
-      <c r="Q20" s="34">
+      <c r="V21" s="34">
         <v>46196.622916666667</v>
       </c>
-      <c r="R20" s="10"/>
+      <c r="W21" s="10"/>
+      <c r="Y21">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z21">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="7">
+    <row r="22" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D22" s="7">
         <v>68</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="E22" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="7">
+      <c r="F22" s="7">
         <v>20</v>
       </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8" t="s">
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="J22" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="H21" s="42" t="s">
+      <c r="K22" s="43"/>
+      <c r="L22" s="43"/>
+      <c r="M22" s="42" t="s">
         <v>198</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="N22" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="O22" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="K21" s="8" t="s">
+      <c r="P22" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="L21" s="8">
+      <c r="Q22" s="8">
         <v>1</v>
       </c>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="34">
+      <c r="R22" s="10"/>
+      <c r="S22" s="10"/>
+      <c r="T22" s="10"/>
+      <c r="U22" s="34">
         <v>46139</v>
       </c>
-      <c r="Q21" s="34">
+      <c r="V22" s="34">
         <v>46139</v>
       </c>
-      <c r="R21" s="10"/>
+      <c r="W22" s="10"/>
+      <c r="Y22">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z22">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="7">
+    <row r="23" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D23" s="7">
         <v>69</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="E23" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C22" s="7">
+      <c r="F23" s="7">
         <v>21</v>
       </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8" t="s">
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="J23" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="H22" s="42" t="s">
+      <c r="K23" s="43"/>
+      <c r="L23" s="43"/>
+      <c r="M23" s="42" t="s">
         <v>200</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="N23" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="O23" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="K22" s="8" t="s">
+      <c r="P23" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="L22" s="8">
+      <c r="Q23" s="8">
         <v>1</v>
       </c>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="34">
+      <c r="R23" s="10"/>
+      <c r="S23" s="10"/>
+      <c r="T23" s="10"/>
+      <c r="U23" s="34">
         <v>46139</v>
       </c>
-      <c r="Q22" s="34">
+      <c r="V23" s="34">
         <v>46139</v>
       </c>
-      <c r="R22" s="10"/>
+      <c r="W23" s="10"/>
+      <c r="Y23">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z23">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="7">
+    <row r="24" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D24" s="7">
         <v>70</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="E24" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="7">
+      <c r="F24" s="7">
         <v>22</v>
       </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8" t="s">
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="J24" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="H23" s="42" t="s">
+      <c r="K24" s="43"/>
+      <c r="L24" s="43"/>
+      <c r="M24" s="42" t="s">
         <v>204</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="N24" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="J23" s="8" t="s">
+      <c r="O24" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="K23" s="8" t="s">
+      <c r="P24" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="L23" s="8">
+      <c r="Q24" s="8">
         <v>1</v>
       </c>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
-      <c r="P23" s="34">
+      <c r="R24" s="10"/>
+      <c r="S24" s="10"/>
+      <c r="T24" s="10"/>
+      <c r="U24" s="34">
         <v>46139</v>
       </c>
-      <c r="Q23" s="34">
+      <c r="V24" s="34">
         <v>46139</v>
       </c>
-      <c r="R23" s="10"/>
+      <c r="W24" s="10"/>
+      <c r="Y24">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z24">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="7">
+    <row r="25" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D25" s="7">
         <v>71</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="E25" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C24" s="7">
+      <c r="F25" s="7">
         <v>23</v>
       </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8" t="s">
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="J25" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="H24" s="42" t="s">
+      <c r="K25" s="43"/>
+      <c r="L25" s="43"/>
+      <c r="M25" s="42" t="s">
         <v>195</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="N25" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="O25" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="K24" s="8" t="s">
+      <c r="P25" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="L24" s="8">
+      <c r="Q25" s="8">
         <v>1</v>
       </c>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="34">
+      <c r="R25" s="10"/>
+      <c r="S25" s="10"/>
+      <c r="T25" s="10"/>
+      <c r="U25" s="34">
         <v>46139</v>
       </c>
-      <c r="Q24" s="34">
+      <c r="V25" s="34">
         <v>46139</v>
       </c>
-      <c r="R24" s="10"/>
+      <c r="W25" s="10"/>
+      <c r="Y25">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z25">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="7">
+    <row r="26" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D26" s="7">
         <v>72</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="E26" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C25" s="7">
+      <c r="F26" s="7">
         <v>24</v>
       </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8" t="s">
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="J26" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="H25" s="42" t="s">
+      <c r="K26" s="43"/>
+      <c r="L26" s="43"/>
+      <c r="M26" s="42" t="s">
         <v>208</v>
       </c>
-      <c r="I25" s="8" t="s">
+      <c r="N26" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="J25" s="8" t="s">
+      <c r="O26" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="K25" s="8" t="s">
+      <c r="P26" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="L25" s="8">
+      <c r="Q26" s="8">
         <v>1</v>
       </c>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="34">
+      <c r="R26" s="10"/>
+      <c r="S26" s="10"/>
+      <c r="T26" s="10"/>
+      <c r="U26" s="34">
         <v>46139</v>
       </c>
-      <c r="Q25" s="34">
+      <c r="V26" s="34">
         <v>46139</v>
       </c>
-      <c r="R25" s="10"/>
+      <c r="W26" s="10"/>
+      <c r="Y26">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z26">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="7">
+    <row r="27" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D27" s="7">
         <v>1</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="E27" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C26" s="7">
+      <c r="F27" s="7">
         <v>1</v>
       </c>
-      <c r="D26" s="8">
+      <c r="G27" s="8">
         <v>1</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="H26" s="42" t="s">
+      <c r="H27" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="K27" s="43" t="s">
+        <v>242</v>
+      </c>
+      <c r="L27" s="43" t="s">
+        <v>371</v>
+      </c>
+      <c r="M27" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="I26" s="8" t="s">
+      <c r="N27" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="J26" s="8" t="s">
+      <c r="O27" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="K26" s="8" t="s">
+      <c r="P27" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="L26" s="8">
+      <c r="Q27" s="8">
         <v>1</v>
       </c>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10">
+      <c r="R27" s="10"/>
+      <c r="S27" s="10">
         <v>0</v>
       </c>
-      <c r="O26" s="10">
+      <c r="T27" s="10">
         <v>0</v>
       </c>
-      <c r="P26" s="34">
+      <c r="U27" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q26" s="34">
+      <c r="V27" s="34">
         <v>46226.664583333331</v>
       </c>
-      <c r="R26" s="10"/>
+      <c r="W27" s="10"/>
+      <c r="Y27">
+        <f t="shared" si="0"/>
+        <v>-4</v>
+      </c>
+      <c r="Z27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="7">
+    <row r="28" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D28" s="7">
         <v>46</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="E28" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C27" s="7">
+      <c r="F28" s="7">
         <v>2</v>
       </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="G27" s="8" t="s">
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="J28" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="M28" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="10">
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="8"/>
+      <c r="Q28" s="8"/>
+      <c r="R28" s="10"/>
+      <c r="S28" s="10">
         <v>0</v>
       </c>
-      <c r="O27" s="10">
+      <c r="T28" s="10">
         <v>5</v>
       </c>
-      <c r="P27" s="34">
+      <c r="U28" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q27" s="34">
+      <c r="V28" s="34">
         <v>46226.664583333331</v>
       </c>
-      <c r="R27" s="10"/>
+      <c r="W28" s="10"/>
+      <c r="Y28">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="Z28">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="7">
+    <row r="29" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D29" s="7">
         <v>47</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="E29" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C28" s="7">
+      <c r="F29" s="7">
         <v>3</v>
       </c>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="G28" s="8" t="s">
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="J29" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="M29" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="10">
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
+      <c r="P29" s="8"/>
+      <c r="Q29" s="8"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="10">
         <v>0</v>
       </c>
-      <c r="O28" s="10">
+      <c r="T29" s="10">
         <v>6</v>
       </c>
-      <c r="P28" s="34">
+      <c r="U29" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q28" s="34">
+      <c r="V29" s="34">
         <v>46226.664583333331</v>
       </c>
-      <c r="R28" s="10"/>
+      <c r="W29" s="10"/>
+      <c r="Y29">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="Z29">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="7">
+    <row r="30" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D30" s="7">
         <v>2</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="E30" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C29" s="7">
+      <c r="F30" s="7">
         <v>4</v>
       </c>
-      <c r="D29" s="8">
+      <c r="G30" s="8">
         <v>2</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="H30" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="F29" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="G29" s="8" t="s">
+      <c r="I30" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="M30" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="N30" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="O30" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="P30" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q30" s="8">
+        <v>1</v>
+      </c>
+      <c r="R30" s="10"/>
+      <c r="S30" s="10">
+        <v>0</v>
+      </c>
+      <c r="T30" s="10">
+        <v>7</v>
+      </c>
+      <c r="U30" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V30" s="34">
+        <v>46226.664583333331</v>
+      </c>
+      <c r="W30" s="10"/>
+      <c r="Y30">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="Z30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D31" s="7">
+        <v>4</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F31" s="7">
+        <v>5</v>
+      </c>
+      <c r="G31" s="8">
+        <v>5</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="N31" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="O31" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="P31" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q31" s="8">
+        <v>1</v>
+      </c>
+      <c r="R31" s="10"/>
+      <c r="S31" s="10">
+        <v>0</v>
+      </c>
+      <c r="T31" s="10">
+        <v>1</v>
+      </c>
+      <c r="U31" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V31" s="34">
+        <v>46226.664583333331</v>
+      </c>
+      <c r="W31" s="10"/>
+      <c r="Y31">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="Z31">
+        <f t="shared" si="0"/>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="32" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D32" s="7">
+        <v>3</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F32" s="7">
+        <v>6</v>
+      </c>
+      <c r="G32" s="8">
+        <v>5</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="M32" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="N32" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="O32" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="P32" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q32" s="8">
+        <v>1</v>
+      </c>
+      <c r="R32" s="10"/>
+      <c r="S32" s="10">
+        <v>0</v>
+      </c>
+      <c r="T32" s="10">
+        <v>8</v>
+      </c>
+      <c r="U32" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V32" s="34">
+        <v>46226.664583333331</v>
+      </c>
+      <c r="W32" s="10"/>
+      <c r="Y32">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="Z32">
+        <f t="shared" si="0"/>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="33" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D33" s="7">
+        <v>8</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F33" s="7">
+        <v>7</v>
+      </c>
+      <c r="G33" s="8">
+        <v>6</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="M33" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="N33" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="O33" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="P33" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q33" s="8">
+        <v>1</v>
+      </c>
+      <c r="R33" s="10"/>
+      <c r="S33" s="10">
+        <v>0</v>
+      </c>
+      <c r="T33" s="10">
+        <v>9</v>
+      </c>
+      <c r="U33" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V33" s="34">
+        <v>46226.664583333331</v>
+      </c>
+      <c r="W33" s="10"/>
+      <c r="Y33">
+        <f t="shared" si="0"/>
+        <v>-6</v>
+      </c>
+      <c r="Z33">
+        <f t="shared" si="0"/>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="34" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D34" s="7">
+        <v>7</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F34" s="7">
+        <v>8</v>
+      </c>
+      <c r="G34" s="8">
+        <v>7</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="M34" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="N34" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="O34" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="P34" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q34" s="11">
+        <v>1</v>
+      </c>
+      <c r="R34" s="21"/>
+      <c r="S34" s="21">
+        <v>0</v>
+      </c>
+      <c r="T34" s="21">
+        <v>10</v>
+      </c>
+      <c r="U34" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V34" s="34">
+        <v>46226.664583333331</v>
+      </c>
+      <c r="W34" s="10"/>
+      <c r="Y34">
+        <f t="shared" si="0"/>
+        <v>-4</v>
+      </c>
+      <c r="Z34">
+        <f t="shared" si="0"/>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="35" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D35" s="7">
+        <v>6</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35" s="7">
+        <v>9</v>
+      </c>
+      <c r="G35" s="8">
+        <v>7</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="M35" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="N35" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="O35" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="P35" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q35" s="11">
+        <v>1</v>
+      </c>
+      <c r="R35" s="21"/>
+      <c r="S35" s="21">
+        <v>0</v>
+      </c>
+      <c r="T35" s="21">
+        <v>11</v>
+      </c>
+      <c r="U35" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V35" s="34">
+        <v>46226.664583333331</v>
+      </c>
+      <c r="W35" s="10"/>
+      <c r="Y35">
+        <f t="shared" si="0"/>
+        <v>-6</v>
+      </c>
+      <c r="Z35">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="36" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D36" s="7">
+        <v>5</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F36" s="7">
+        <v>10</v>
+      </c>
+      <c r="G36" s="8">
+        <v>8</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="M36" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="N36" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="O36" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="P36" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q36" s="11">
+        <v>1</v>
+      </c>
+      <c r="R36" s="21"/>
+      <c r="S36" s="21">
+        <v>0</v>
+      </c>
+      <c r="T36" s="21">
+        <v>12</v>
+      </c>
+      <c r="U36" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V36" s="34">
+        <v>46226.664583333331</v>
+      </c>
+      <c r="W36" s="10"/>
+      <c r="Y36">
+        <f t="shared" si="0"/>
+        <v>-10</v>
+      </c>
+      <c r="Z36">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="37" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D37" s="7">
+        <v>10</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F37" s="7">
+        <v>11</v>
+      </c>
+      <c r="G37" s="8">
+        <v>9</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="M37" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="N37" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="O37" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="P37" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q37" s="11">
+        <v>1</v>
+      </c>
+      <c r="R37" s="21"/>
+      <c r="S37" s="21">
+        <v>0</v>
+      </c>
+      <c r="T37" s="21">
+        <v>2</v>
+      </c>
+      <c r="U37" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V37" s="34">
+        <v>46226.664583333331</v>
+      </c>
+      <c r="W37" s="10"/>
+      <c r="Y37">
+        <f t="shared" si="0"/>
+        <v>-6</v>
+      </c>
+      <c r="Z37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D38" s="7">
+        <v>9</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F38" s="7">
+        <v>12</v>
+      </c>
+      <c r="G38" s="12">
+        <v>9</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="K38" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="L38" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="M38" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="N38" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="O38" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="P38" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q38" s="13">
+        <v>1</v>
+      </c>
+      <c r="R38" s="22"/>
+      <c r="S38" s="22">
+        <v>0</v>
+      </c>
+      <c r="T38" s="22">
+        <v>13</v>
+      </c>
+      <c r="U38" s="35">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V38" s="35">
+        <v>46226.664583333331</v>
+      </c>
+      <c r="W38" s="10"/>
+      <c r="Y38">
+        <f t="shared" si="0"/>
+        <v>-8</v>
+      </c>
+      <c r="Z38">
+        <f t="shared" si="0"/>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="39" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D39" s="7">
+        <v>11</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F39" s="7">
+        <v>13</v>
+      </c>
+      <c r="G39" s="8">
+        <v>11</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="M39" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="N39" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="O39" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="P39" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q39" s="11">
+        <v>1</v>
+      </c>
+      <c r="R39" s="21"/>
+      <c r="S39" s="21">
+        <v>0</v>
+      </c>
+      <c r="T39" s="21">
+        <v>3</v>
+      </c>
+      <c r="U39" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V39" s="34">
+        <v>46226.664583333331</v>
+      </c>
+      <c r="W39" s="10"/>
+      <c r="Y39">
+        <f t="shared" si="0"/>
+        <v>-6</v>
+      </c>
+      <c r="Z39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D40" s="7">
+        <v>13</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F40" s="7">
+        <v>14</v>
+      </c>
+      <c r="G40" s="12">
+        <v>11</v>
+      </c>
+      <c r="H40" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="I40" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="J40" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="K40" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="L40" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="M40" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="N40" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="O40" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="P40" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q40" s="13">
+        <v>1</v>
+      </c>
+      <c r="R40" s="22"/>
+      <c r="S40" s="22">
+        <v>0</v>
+      </c>
+      <c r="T40" s="22">
+        <v>4</v>
+      </c>
+      <c r="U40" s="35">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V40" s="35">
+        <v>46226.664583333331</v>
+      </c>
+      <c r="W40" s="10"/>
+      <c r="Y40">
+        <f t="shared" si="0"/>
+        <v>-8</v>
+      </c>
+      <c r="Z40">
+        <f t="shared" si="0"/>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="41" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D41" s="7">
+        <v>14</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F41" s="7">
+        <v>15</v>
+      </c>
+      <c r="G41" s="8">
+        <v>11</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="M41" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="N41" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="O41" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="P41" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q41" s="11">
+        <v>1</v>
+      </c>
+      <c r="R41" s="21"/>
+      <c r="S41" s="21">
+        <v>0</v>
+      </c>
+      <c r="T41" s="21">
+        <v>14</v>
+      </c>
+      <c r="U41" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V41" s="34">
+        <v>46226.664583333331</v>
+      </c>
+      <c r="W41" s="10"/>
+      <c r="Y41">
+        <f t="shared" si="0"/>
+        <v>-4</v>
+      </c>
+      <c r="Z41">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D42" s="7">
+        <v>15</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F42" s="7">
+        <v>16</v>
+      </c>
+      <c r="G42" s="12">
+        <v>11</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="J42" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="K42" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="L42" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="M42" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="N42" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="O42" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="P42" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q42" s="13">
+        <v>1</v>
+      </c>
+      <c r="R42" s="22"/>
+      <c r="S42" s="22">
+        <v>0</v>
+      </c>
+      <c r="T42" s="22">
+        <v>15</v>
+      </c>
+      <c r="U42" s="35">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V42" s="35">
+        <v>46226.664583333331</v>
+      </c>
+      <c r="W42" s="10"/>
+      <c r="Y42">
+        <f t="shared" si="0"/>
+        <v>-3</v>
+      </c>
+      <c r="Z42">
+        <f t="shared" si="0"/>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="43" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D43" s="7">
+        <v>48</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F43" s="7">
+        <v>17</v>
+      </c>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="H29" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J29" s="8" t="s">
+      <c r="J43" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="K43" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="L43" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="M43" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="N43" s="12"/>
+      <c r="O43" s="12"/>
+      <c r="P43" s="12"/>
+      <c r="Q43" s="13"/>
+      <c r="R43" s="22"/>
+      <c r="S43" s="22">
+        <v>1</v>
+      </c>
+      <c r="T43" s="22">
+        <v>0</v>
+      </c>
+      <c r="U43" s="35">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V43" s="35">
+        <v>46226.664583333331</v>
+      </c>
+      <c r="W43" s="10"/>
+      <c r="Y43">
+        <f t="shared" si="0"/>
+        <v>-3</v>
+      </c>
+      <c r="Z43">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="44" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D44" s="7">
+        <v>49</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F44" s="7">
+        <v>18</v>
+      </c>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="M44" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="N44" s="8"/>
+      <c r="O44" s="8"/>
+      <c r="P44" s="8"/>
+      <c r="Q44" s="8"/>
+      <c r="R44" s="10"/>
+      <c r="S44" s="10">
+        <v>1</v>
+      </c>
+      <c r="T44" s="10">
+        <v>1</v>
+      </c>
+      <c r="U44" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V44" s="34">
+        <v>46226.664583333331</v>
+      </c>
+      <c r="W44" s="10"/>
+      <c r="Y44">
+        <f t="shared" si="0"/>
+        <v>-3</v>
+      </c>
+      <c r="Z44">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="45" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D45" s="7">
+        <v>50</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F45" s="7">
+        <v>19</v>
+      </c>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="M45" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="N45" s="8"/>
+      <c r="O45" s="8"/>
+      <c r="P45" s="8"/>
+      <c r="Q45" s="8"/>
+      <c r="R45" s="10"/>
+      <c r="S45" s="10">
+        <v>1</v>
+      </c>
+      <c r="T45" s="10">
+        <v>2</v>
+      </c>
+      <c r="U45" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V45" s="34">
+        <v>46226.664583333331</v>
+      </c>
+      <c r="W45" s="10"/>
+      <c r="Y45">
+        <f t="shared" si="0"/>
+        <v>-3</v>
+      </c>
+      <c r="Z45">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="46" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D46" s="7">
+        <v>58</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F46" s="7">
+        <v>20</v>
+      </c>
+      <c r="G46" s="8">
+        <v>7</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="L46" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="M46" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="N46" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="O46" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="P46" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q46" s="8"/>
+      <c r="R46" s="10"/>
+      <c r="S46" s="10"/>
+      <c r="T46" s="10"/>
+      <c r="U46" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V46" s="34">
+        <v>46226.664583333331</v>
+      </c>
+      <c r="W46" s="10"/>
+      <c r="Y46">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="Z46">
+        <f t="shared" si="0"/>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="47" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D47" s="7">
+        <v>12</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F47" s="7"/>
+      <c r="G47" s="8">
+        <v>11</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="N47" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="O47" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="K29" s="8" t="s">
+      <c r="P47" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="L29" s="8">
+      <c r="Q47" s="8">
         <v>1</v>
       </c>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10">
+      <c r="R47" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="S47" s="10"/>
+      <c r="T47" s="10"/>
+      <c r="U47" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V47" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="W47" s="10"/>
+      <c r="Y47">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z47">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="48" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D48" s="26">
+        <v>16</v>
+      </c>
+      <c r="E48" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="F48" s="26"/>
+      <c r="G48" s="14">
+        <v>11</v>
+      </c>
+      <c r="H48" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="14"/>
+      <c r="L48" s="14"/>
+      <c r="M48" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="N48" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="O48" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="P48" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q48" s="15">
+        <v>1</v>
+      </c>
+      <c r="R48" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="S48" s="23"/>
+      <c r="T48" s="23"/>
+      <c r="U48" s="36">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V48" s="36">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="W48" s="10"/>
+      <c r="Y48">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z48">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="49" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D49" s="26">
+        <v>17</v>
+      </c>
+      <c r="E49" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="F49" s="26"/>
+      <c r="G49" s="14">
+        <v>11</v>
+      </c>
+      <c r="H49" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="14"/>
+      <c r="L49" s="14"/>
+      <c r="M49" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="N49" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="O49" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="P49" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q49" s="15">
+        <v>1</v>
+      </c>
+      <c r="R49" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="S49" s="23"/>
+      <c r="T49" s="23"/>
+      <c r="U49" s="36">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V49" s="36">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="W49" s="10"/>
+      <c r="Y49">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z49">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="50" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D50" s="26">
+        <v>21</v>
+      </c>
+      <c r="E50" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="F50" s="26">
+        <v>1</v>
+      </c>
+      <c r="G50" s="14">
+        <v>1</v>
+      </c>
+      <c r="H50" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="I50" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="J50" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="K50" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="L50" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="M50" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="N50" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="O50" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="P50" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q50" s="15">
+        <v>1</v>
+      </c>
+      <c r="R50" s="23"/>
+      <c r="S50" s="23"/>
+      <c r="T50" s="23"/>
+      <c r="U50" s="36">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V50" s="36">
+        <v>46226.664583333331</v>
+      </c>
+      <c r="W50" s="10"/>
+      <c r="Y50">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="Z50">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O29" s="10">
+    </row>
+    <row r="51" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D51" s="7">
+        <v>24</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="F51" s="7"/>
+      <c r="G51" s="8">
+        <v>3</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="N51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="O51" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="P51" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>1</v>
+      </c>
+      <c r="R51" s="10"/>
+      <c r="S51" s="10"/>
+      <c r="T51" s="10"/>
+      <c r="U51" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V51" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="W51" s="10"/>
+      <c r="Y51">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z51">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="52" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D52" s="7">
+        <v>25</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="F52" s="7"/>
+      <c r="G52" s="8">
+        <v>3</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="N52" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="O52" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="P52" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q52" s="8">
+        <v>1</v>
+      </c>
+      <c r="R52" s="10"/>
+      <c r="S52" s="10"/>
+      <c r="T52" s="10"/>
+      <c r="U52" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V52" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="W52" s="10"/>
+      <c r="Y52">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z52">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="53" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D53" s="7">
+        <v>29</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="F53" s="7"/>
+      <c r="G53" s="8">
         <v>7</v>
       </c>
-      <c r="P29" s="34">
+      <c r="H53" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="N53" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="O53" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="P53" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q53" s="8">
+        <v>3</v>
+      </c>
+      <c r="R53" s="10"/>
+      <c r="S53" s="10"/>
+      <c r="T53" s="10"/>
+      <c r="U53" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q29" s="34">
-        <v>46226.664583333331</v>
-      </c>
-      <c r="R29" s="10"/>
+      <c r="V53" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="W53" s="10"/>
+      <c r="Y53">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z53">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="7">
-        <v>4</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" s="7">
+    <row r="54" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D54" s="7">
+        <v>30</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="F54" s="7"/>
+      <c r="G54" s="8">
+        <v>1</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8"/>
+      <c r="M54" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="N54" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="O54" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="P54" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q54" s="8">
+        <v>1</v>
+      </c>
+      <c r="R54" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="S54" s="10"/>
+      <c r="T54" s="10"/>
+      <c r="U54" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V54" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="W54" s="10"/>
+      <c r="Y54">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z54">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="55" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D55" s="7">
+        <v>34</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="F55" s="7"/>
+      <c r="G55" s="8">
+        <v>1</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="J55" s="8"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="8"/>
+      <c r="M55" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="N55" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="O55" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="P55" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q55" s="8">
+        <v>1</v>
+      </c>
+      <c r="R55" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="S55" s="10"/>
+      <c r="T55" s="10"/>
+      <c r="U55" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V55" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="W55" s="10"/>
+      <c r="Y55">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z55">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="56" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D56" s="7">
+        <v>26</v>
+      </c>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="8">
+        <v>1</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="I56" s="8"/>
+      <c r="J56" s="8"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="8"/>
+      <c r="M56" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="N56" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="O56" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="P56" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q56" s="8">
+        <v>1</v>
+      </c>
+      <c r="R56" s="10"/>
+      <c r="S56" s="10"/>
+      <c r="T56" s="10"/>
+      <c r="U56" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V56" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="W56" s="10"/>
+      <c r="Y56">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z56">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="57" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D57" s="7">
+        <v>27</v>
+      </c>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="8">
         <v>5</v>
       </c>
-      <c r="D30" s="8">
+      <c r="H57" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="I57" s="8"/>
+      <c r="J57" s="8"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="8"/>
+      <c r="M57" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="N57" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="O57" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="P57" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q57" s="8">
+        <v>1</v>
+      </c>
+      <c r="R57" s="10"/>
+      <c r="S57" s="10"/>
+      <c r="T57" s="10"/>
+      <c r="U57" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V57" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="W57" s="10"/>
+      <c r="Y57">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z57">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="58" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D58" s="7">
+        <v>28</v>
+      </c>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="8">
         <v>5</v>
       </c>
-      <c r="E30" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="L30" s="8">
+      <c r="H58" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="I58" s="8"/>
+      <c r="J58" s="8"/>
+      <c r="K58" s="8"/>
+      <c r="L58" s="8"/>
+      <c r="M58" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="N58" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="O58" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="P58" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q58" s="8">
         <v>1</v>
       </c>
-      <c r="M30" s="10"/>
-      <c r="N30" s="10">
-        <v>0</v>
-      </c>
-      <c r="O30" s="10">
+      <c r="R58" s="10"/>
+      <c r="S58" s="10"/>
+      <c r="T58" s="10"/>
+      <c r="U58" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V58" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="W58" s="10"/>
+      <c r="Y58">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z58">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="59" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D59" s="7">
+        <v>31</v>
+      </c>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="8">
+        <v>3</v>
+      </c>
+      <c r="H59" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="I59" s="8"/>
+      <c r="J59" s="8"/>
+      <c r="K59" s="8"/>
+      <c r="L59" s="8"/>
+      <c r="M59" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N59" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="O59" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="P59" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q59" s="8">
         <v>1</v>
       </c>
-      <c r="P30" s="34">
+      <c r="R59" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="S59" s="10"/>
+      <c r="T59" s="10"/>
+      <c r="U59" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q30" s="34">
-        <v>46226.664583333331</v>
-      </c>
-      <c r="R30" s="10"/>
+      <c r="V59" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="W59" s="10"/>
+      <c r="Y59">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z59">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="7">
-        <v>3</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C31" s="7">
-        <v>6</v>
-      </c>
-      <c r="D31" s="8">
-        <v>5</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="I31" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K31" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="L31" s="8">
-        <v>1</v>
-      </c>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10">
-        <v>0</v>
-      </c>
-      <c r="O31" s="10">
-        <v>8</v>
-      </c>
-      <c r="P31" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q31" s="34">
-        <v>46226.664583333331</v>
-      </c>
-      <c r="R31" s="10"/>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="7">
-        <v>8</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C32" s="7">
+    <row r="60" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D60" s="7">
+        <v>39</v>
+      </c>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="8">
         <v>7</v>
       </c>
-      <c r="D32" s="8">
-        <v>6</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="L32" s="8">
-        <v>1</v>
-      </c>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10">
-        <v>0</v>
-      </c>
-      <c r="O32" s="10">
-        <v>9</v>
-      </c>
-      <c r="P32" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q32" s="34">
-        <v>46226.664583333331</v>
-      </c>
-      <c r="R32" s="10"/>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="7">
-        <v>7</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C33" s="7">
-        <v>8</v>
-      </c>
-      <c r="D33" s="8">
-        <v>7</v>
-      </c>
-      <c r="E33" s="8" t="s">
+      <c r="H60" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F33" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="L33" s="11">
-        <v>1</v>
-      </c>
-      <c r="M33" s="21"/>
-      <c r="N33" s="21">
-        <v>0</v>
-      </c>
-      <c r="O33" s="21">
-        <v>10</v>
-      </c>
-      <c r="P33" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q33" s="34">
-        <v>46226.664583333331</v>
-      </c>
-      <c r="R33" s="10"/>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="7">
-        <v>6</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C34" s="7">
-        <v>9</v>
-      </c>
-      <c r="D34" s="8">
-        <v>7</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K34" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="L34" s="11">
-        <v>1</v>
-      </c>
-      <c r="M34" s="21"/>
-      <c r="N34" s="21">
-        <v>0</v>
-      </c>
-      <c r="O34" s="21">
-        <v>11</v>
-      </c>
-      <c r="P34" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q34" s="34">
-        <v>46226.664583333331</v>
-      </c>
-      <c r="R34" s="10"/>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="7">
-        <v>5</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C35" s="7">
-        <v>10</v>
-      </c>
-      <c r="D35" s="8">
-        <v>8</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K35" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="L35" s="11">
-        <v>1</v>
-      </c>
-      <c r="M35" s="21"/>
-      <c r="N35" s="21">
-        <v>0</v>
-      </c>
-      <c r="O35" s="21">
-        <v>12</v>
-      </c>
-      <c r="P35" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q35" s="34">
-        <v>46226.664583333331</v>
-      </c>
-      <c r="R35" s="10"/>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="7">
-        <v>10</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C36" s="7">
-        <v>11</v>
-      </c>
-      <c r="D36" s="8">
-        <v>9</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K36" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="L36" s="11">
-        <v>1</v>
-      </c>
-      <c r="M36" s="21"/>
-      <c r="N36" s="21">
-        <v>0</v>
-      </c>
-      <c r="O36" s="21">
-        <v>2</v>
-      </c>
-      <c r="P36" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q36" s="34">
-        <v>46226.664583333331</v>
-      </c>
-      <c r="R36" s="10"/>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="7">
-        <v>9</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C37" s="7">
-        <v>12</v>
-      </c>
-      <c r="D37" s="12">
-        <v>9</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="F37" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G37" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="I37" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="J37" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="K37" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="L37" s="13">
-        <v>1</v>
-      </c>
-      <c r="M37" s="22"/>
-      <c r="N37" s="22">
-        <v>0</v>
-      </c>
-      <c r="O37" s="22">
-        <v>13</v>
-      </c>
-      <c r="P37" s="35">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q37" s="35">
-        <v>46226.664583333331</v>
-      </c>
-      <c r="R37" s="10"/>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="7">
-        <v>11</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C38" s="7">
-        <v>13</v>
-      </c>
-      <c r="D38" s="8">
-        <v>11</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="J38" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K38" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="L38" s="11">
-        <v>1</v>
-      </c>
-      <c r="M38" s="21"/>
-      <c r="N38" s="21">
-        <v>0</v>
-      </c>
-      <c r="O38" s="21">
-        <v>3</v>
-      </c>
-      <c r="P38" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q38" s="34">
-        <v>46226.664583333331</v>
-      </c>
-      <c r="R38" s="10"/>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="7">
-        <v>13</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C39" s="7">
-        <v>14</v>
-      </c>
-      <c r="D39" s="12">
-        <v>11</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="G39" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="H39" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="I39" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="J39" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="K39" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="L39" s="13">
-        <v>1</v>
-      </c>
-      <c r="M39" s="22"/>
-      <c r="N39" s="22">
-        <v>0</v>
-      </c>
-      <c r="O39" s="22">
-        <v>4</v>
-      </c>
-      <c r="P39" s="35">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q39" s="35">
-        <v>46226.664583333331</v>
-      </c>
-      <c r="R39" s="10"/>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="7">
-        <v>14</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C40" s="7">
-        <v>15</v>
-      </c>
-      <c r="D40" s="8">
-        <v>11</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I40" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="J40" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K40" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="L40" s="11">
-        <v>1</v>
-      </c>
-      <c r="M40" s="21"/>
-      <c r="N40" s="21">
-        <v>0</v>
-      </c>
-      <c r="O40" s="21">
-        <v>14</v>
-      </c>
-      <c r="P40" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q40" s="34">
-        <v>46226.664583333331</v>
-      </c>
-      <c r="R40" s="10"/>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="7">
-        <v>15</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C41" s="7">
-        <v>16</v>
-      </c>
-      <c r="D41" s="12">
-        <v>11</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="F41" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="G41" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="H41" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="I41" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="J41" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="K41" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="L41" s="13">
-        <v>1</v>
-      </c>
-      <c r="M41" s="22"/>
-      <c r="N41" s="22">
-        <v>0</v>
-      </c>
-      <c r="O41" s="22">
-        <v>15</v>
-      </c>
-      <c r="P41" s="35">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q41" s="35">
-        <v>46226.664583333331</v>
-      </c>
-      <c r="R41" s="10"/>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="7">
-        <v>48</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C42" s="7">
-        <v>17</v>
-      </c>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12" t="s">
-        <v>303</v>
-      </c>
-      <c r="G42" s="12" t="s">
-        <v>321</v>
-      </c>
-      <c r="H42" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="I42" s="12"/>
-      <c r="J42" s="12"/>
-      <c r="K42" s="12"/>
-      <c r="L42" s="13"/>
-      <c r="M42" s="22"/>
-      <c r="N42" s="22">
-        <v>1</v>
-      </c>
-      <c r="O42" s="22">
-        <v>0</v>
-      </c>
-      <c r="P42" s="35">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q42" s="35">
-        <v>46226.664583333331</v>
-      </c>
-      <c r="R42" s="10"/>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="7">
-        <v>49</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C43" s="7">
-        <v>18</v>
-      </c>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="10">
-        <v>1</v>
-      </c>
-      <c r="O43" s="10">
-        <v>1</v>
-      </c>
-      <c r="P43" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q43" s="34">
-        <v>46226.664583333331</v>
-      </c>
-      <c r="R43" s="10"/>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="7">
-        <v>50</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C44" s="7">
-        <v>19</v>
-      </c>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="I44" s="8"/>
-      <c r="J44" s="8"/>
-      <c r="K44" s="8"/>
-      <c r="L44" s="8"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="10">
-        <v>1</v>
-      </c>
-      <c r="O44" s="10">
-        <v>2</v>
-      </c>
-      <c r="P44" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q44" s="34">
-        <v>46226.664583333331</v>
-      </c>
-      <c r="R44" s="10"/>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="7">
-        <v>58</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C45" s="7">
-        <v>20</v>
-      </c>
-      <c r="D45" s="8">
-        <v>7</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="I45" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="J45" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="K45" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="L45" s="8"/>
-      <c r="M45" s="10"/>
-      <c r="N45" s="10"/>
-      <c r="O45" s="10"/>
-      <c r="P45" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q45" s="34">
-        <v>46226.664583333331</v>
-      </c>
-      <c r="R45" s="10"/>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="7">
-        <v>12</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8">
-        <v>11</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="J46" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K46" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="L46" s="8">
-        <v>1</v>
-      </c>
-      <c r="M46" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="N46" s="10"/>
-      <c r="O46" s="10"/>
-      <c r="P46" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q46" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="R46" s="10"/>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="26">
-        <v>16</v>
-      </c>
-      <c r="B47" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="C47" s="26"/>
-      <c r="D47" s="14">
-        <v>11</v>
-      </c>
-      <c r="E47" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="I47" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="J47" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="K47" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="L47" s="15">
-        <v>1</v>
-      </c>
-      <c r="M47" s="23" t="s">
-        <v>258</v>
-      </c>
-      <c r="N47" s="23"/>
-      <c r="O47" s="23"/>
-      <c r="P47" s="36">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q47" s="36">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="R47" s="10"/>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="26">
-        <v>17</v>
-      </c>
-      <c r="B48" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="C48" s="26"/>
-      <c r="D48" s="14">
-        <v>11</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="I48" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="J48" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="K48" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="L48" s="15">
-        <v>1</v>
-      </c>
-      <c r="M48" s="23" t="s">
-        <v>258</v>
-      </c>
-      <c r="N48" s="23"/>
-      <c r="O48" s="23"/>
-      <c r="P48" s="36">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q48" s="36">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="R48" s="10"/>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="26">
-        <v>21</v>
-      </c>
-      <c r="B49" s="26" t="s">
-        <v>259</v>
-      </c>
-      <c r="C49" s="26">
-        <v>1</v>
-      </c>
-      <c r="D49" s="14">
-        <v>1</v>
-      </c>
-      <c r="E49" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="F49" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="G49" s="14" t="s">
-        <v>325</v>
-      </c>
-      <c r="H49" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="I49" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="J49" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="K49" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="L49" s="15">
-        <v>1</v>
-      </c>
-      <c r="M49" s="23"/>
-      <c r="N49" s="23"/>
-      <c r="O49" s="23"/>
-      <c r="P49" s="36">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q49" s="36">
-        <v>46226.664583333331</v>
-      </c>
-      <c r="R49" s="10"/>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="7">
-        <v>24</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8">
-        <v>3</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="G50" s="8"/>
-      <c r="H50" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I50" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J50" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="K50" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="L50" s="8">
-        <v>1</v>
-      </c>
-      <c r="M50" s="10"/>
-      <c r="N50" s="10"/>
-      <c r="O50" s="10"/>
-      <c r="P50" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q50" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="R50" s="10"/>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="7">
-        <v>25</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8">
-        <v>3</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="F51" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="G51" s="8"/>
-      <c r="H51" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="I51" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="J51" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="K51" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="L51" s="8">
-        <v>1</v>
-      </c>
-      <c r="M51" s="10"/>
-      <c r="N51" s="10"/>
-      <c r="O51" s="10"/>
-      <c r="P51" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q51" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="R51" s="10"/>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="7">
-        <v>29</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8">
-        <v>7</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I52" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="J52" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="K52" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="L52" s="8">
-        <v>3</v>
-      </c>
-      <c r="M52" s="10"/>
-      <c r="N52" s="10"/>
-      <c r="O52" s="10"/>
-      <c r="P52" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q52" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="R52" s="10"/>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="7">
-        <v>30</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8">
-        <v>1</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I53" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="J53" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="K53" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="L53" s="8">
-        <v>1</v>
-      </c>
-      <c r="M53" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="N53" s="10"/>
-      <c r="O53" s="10"/>
-      <c r="P53" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q53" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="R53" s="10"/>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="7">
-        <v>34</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8">
-        <v>1</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="G54" s="8"/>
-      <c r="H54" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="I54" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="J54" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="K54" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="L54" s="8">
-        <v>1</v>
-      </c>
-      <c r="M54" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="N54" s="10"/>
-      <c r="O54" s="10"/>
-      <c r="P54" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q54" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="R54" s="10"/>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="7">
-        <v>26</v>
-      </c>
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8">
-        <v>1</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="I55" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="J55" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="K55" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="L55" s="8">
-        <v>1</v>
-      </c>
-      <c r="M55" s="10"/>
-      <c r="N55" s="10"/>
-      <c r="O55" s="10"/>
-      <c r="P55" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q55" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="R55" s="10"/>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="7">
-        <v>27</v>
-      </c>
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="8">
-        <v>5</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I56" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J56" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="K56" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="L56" s="8">
-        <v>1</v>
-      </c>
-      <c r="M56" s="10"/>
-      <c r="N56" s="10"/>
-      <c r="O56" s="10"/>
-      <c r="P56" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q56" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="R56" s="10"/>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="7">
-        <v>28</v>
-      </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="8">
-        <v>5</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8"/>
-      <c r="H57" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I57" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="J57" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="K57" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="L57" s="8">
-        <v>1</v>
-      </c>
-      <c r="M57" s="10"/>
-      <c r="N57" s="10"/>
-      <c r="O57" s="10"/>
-      <c r="P57" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q57" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="R57" s="10"/>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="7">
-        <v>31</v>
-      </c>
-      <c r="B58" s="7"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8">
-        <v>3</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I58" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="J58" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="K58" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="L58" s="8">
-        <v>1</v>
-      </c>
-      <c r="M58" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="N58" s="10"/>
-      <c r="O58" s="10"/>
-      <c r="P58" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q58" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="R58" s="10"/>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="7">
-        <v>39</v>
-      </c>
-      <c r="B59" s="7"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="8">
-        <v>7</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F59" s="8"/>
-      <c r="G59" s="8"/>
-      <c r="H59" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I59" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="J59" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="K59" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="L59" s="8">
-        <v>1</v>
-      </c>
-      <c r="M59" s="10"/>
-      <c r="N59" s="10"/>
-      <c r="O59" s="10"/>
-      <c r="P59" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q59" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="R59" s="10"/>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="7">
-        <v>51</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="C60" s="7">
-        <v>1</v>
-      </c>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="G60" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="H60" s="8"/>
       <c r="I60" s="8"/>
       <c r="J60" s="8"/>
       <c r="K60" s="8"/>
       <c r="L60" s="8"/>
-      <c r="M60" s="10"/>
-      <c r="N60" s="10"/>
-      <c r="O60" s="10"/>
-      <c r="P60" s="34">
+      <c r="M60" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N60" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="O60" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="P60" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q60" s="8">
+        <v>1</v>
+      </c>
+      <c r="R60" s="10"/>
+      <c r="S60" s="10"/>
+      <c r="T60" s="10"/>
+      <c r="U60" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q60" s="34">
-        <v>46226.584027777775</v>
-      </c>
-      <c r="R60" s="10"/>
+      <c r="V60" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="W60" s="10"/>
+      <c r="Y60">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z60">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="7">
-        <v>52</v>
-      </c>
-      <c r="B61" s="7" t="s">
+    <row r="61" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D61" s="7">
+        <v>51</v>
+      </c>
+      <c r="E61" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="C61" s="7">
-        <v>2</v>
-      </c>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="G61" s="8" t="s">
-        <v>224</v>
-      </c>
+      <c r="F61" s="7">
+        <v>1</v>
+      </c>
+      <c r="G61" s="8"/>
       <c r="H61" s="8"/>
-      <c r="I61" s="8"/>
-      <c r="J61" s="8"/>
+      <c r="I61" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="J61" s="8" t="s">
+        <v>223</v>
+      </c>
       <c r="K61" s="8"/>
       <c r="L61" s="8"/>
-      <c r="M61" s="10"/>
-      <c r="N61" s="10"/>
-      <c r="O61" s="10"/>
-      <c r="P61" s="34">
+      <c r="M61" s="8"/>
+      <c r="N61" s="8"/>
+      <c r="O61" s="8"/>
+      <c r="P61" s="8"/>
+      <c r="Q61" s="8"/>
+      <c r="R61" s="10"/>
+      <c r="S61" s="10"/>
+      <c r="T61" s="10"/>
+      <c r="U61" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q61" s="34">
+      <c r="V61" s="34">
         <v>46226.584027777775</v>
       </c>
-      <c r="R61" s="10"/>
+      <c r="W61" s="10"/>
+      <c r="Y61">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z61">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="7">
-        <v>53</v>
-      </c>
-      <c r="B62" s="7" t="s">
+    <row r="62" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D62" s="7">
+        <v>52</v>
+      </c>
+      <c r="E62" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="C62" s="7">
-        <v>3</v>
-      </c>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="G62" s="8" t="s">
-        <v>225</v>
-      </c>
+      <c r="F62" s="7">
+        <v>2</v>
+      </c>
+      <c r="G62" s="8"/>
       <c r="H62" s="8"/>
-      <c r="I62" s="8"/>
-      <c r="J62" s="8"/>
+      <c r="I62" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="J62" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="K62" s="8"/>
       <c r="L62" s="8"/>
-      <c r="M62" s="10"/>
-      <c r="N62" s="10"/>
-      <c r="O62" s="10"/>
-      <c r="P62" s="34">
+      <c r="M62" s="8"/>
+      <c r="N62" s="8"/>
+      <c r="O62" s="8"/>
+      <c r="P62" s="8"/>
+      <c r="Q62" s="8"/>
+      <c r="R62" s="10"/>
+      <c r="S62" s="10"/>
+      <c r="T62" s="10"/>
+      <c r="U62" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q62" s="34">
+      <c r="V62" s="34">
         <v>46226.584027777775</v>
       </c>
-      <c r="R62" s="10"/>
+      <c r="W62" s="10"/>
+      <c r="Y62">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z62">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="7">
-        <v>54</v>
-      </c>
-      <c r="B63" s="7" t="s">
+    <row r="63" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D63" s="7">
+        <v>53</v>
+      </c>
+      <c r="E63" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="C63" s="7">
-        <v>4</v>
-      </c>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="G63" s="8" t="s">
-        <v>226</v>
-      </c>
+      <c r="F63" s="7">
+        <v>3</v>
+      </c>
+      <c r="G63" s="8"/>
       <c r="H63" s="8"/>
-      <c r="I63" s="8"/>
-      <c r="J63" s="8"/>
+      <c r="I63" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="J63" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="K63" s="8"/>
       <c r="L63" s="8"/>
-      <c r="M63" s="10"/>
-      <c r="N63" s="10"/>
-      <c r="O63" s="10"/>
-      <c r="P63" s="34">
+      <c r="M63" s="8"/>
+      <c r="N63" s="8"/>
+      <c r="O63" s="8"/>
+      <c r="P63" s="8"/>
+      <c r="Q63" s="8"/>
+      <c r="R63" s="10"/>
+      <c r="S63" s="10"/>
+      <c r="T63" s="10"/>
+      <c r="U63" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q63" s="34">
+      <c r="V63" s="34">
         <v>46226.584027777775</v>
       </c>
-      <c r="R63" s="10"/>
+      <c r="W63" s="10"/>
+      <c r="Y63">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z63">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="7">
-        <v>55</v>
-      </c>
-      <c r="B64" s="7" t="s">
+    <row r="64" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D64" s="7">
+        <v>54</v>
+      </c>
+      <c r="E64" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="C64" s="7">
-        <v>5</v>
-      </c>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="G64" s="8" t="s">
-        <v>227</v>
-      </c>
+      <c r="F64" s="7">
+        <v>4</v>
+      </c>
+      <c r="G64" s="8"/>
       <c r="H64" s="8"/>
-      <c r="I64" s="8"/>
-      <c r="J64" s="8"/>
+      <c r="I64" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="J64" s="8" t="s">
+        <v>226</v>
+      </c>
       <c r="K64" s="8"/>
       <c r="L64" s="8"/>
-      <c r="M64" s="10"/>
-      <c r="N64" s="10"/>
-      <c r="O64" s="10"/>
-      <c r="P64" s="34">
+      <c r="M64" s="8"/>
+      <c r="N64" s="8"/>
+      <c r="O64" s="8"/>
+      <c r="P64" s="8"/>
+      <c r="Q64" s="8"/>
+      <c r="R64" s="10"/>
+      <c r="S64" s="10"/>
+      <c r="T64" s="10"/>
+      <c r="U64" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q64" s="34">
+      <c r="V64" s="34">
         <v>46226.584027777775</v>
       </c>
-      <c r="R64" s="10"/>
+      <c r="W64" s="10"/>
+      <c r="Y64">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z64">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="7">
-        <v>56</v>
-      </c>
-      <c r="B65" s="7" t="s">
+    <row r="65" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D65" s="7">
+        <v>55</v>
+      </c>
+      <c r="E65" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="7">
-        <v>6</v>
-      </c>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="G65" s="8" t="s">
-        <v>228</v>
-      </c>
+      <c r="F65" s="7">
+        <v>5</v>
+      </c>
+      <c r="G65" s="8"/>
       <c r="H65" s="8"/>
-      <c r="I65" s="8"/>
-      <c r="J65" s="8"/>
+      <c r="I65" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="K65" s="8"/>
       <c r="L65" s="8"/>
-      <c r="M65" s="10"/>
-      <c r="N65" s="10"/>
-      <c r="O65" s="10"/>
-      <c r="P65" s="34">
+      <c r="M65" s="8"/>
+      <c r="N65" s="8"/>
+      <c r="O65" s="8"/>
+      <c r="P65" s="8"/>
+      <c r="Q65" s="8"/>
+      <c r="R65" s="10"/>
+      <c r="S65" s="10"/>
+      <c r="T65" s="10"/>
+      <c r="U65" s="34">
         <v>46069.554861111108</v>
       </c>
-      <c r="Q65" s="34">
+      <c r="V65" s="34">
         <v>46226.584027777775</v>
       </c>
-      <c r="R65" s="10"/>
+      <c r="W65" s="10"/>
+      <c r="Y65">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z65">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="7">
-        <v>60</v>
-      </c>
-      <c r="B66" s="7" t="s">
+    <row r="66" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D66" s="7">
+        <v>56</v>
+      </c>
+      <c r="E66" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="C66" s="7">
-        <v>7</v>
-      </c>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="G66" s="8" t="s">
-        <v>230</v>
-      </c>
+      <c r="F66" s="7">
+        <v>6</v>
+      </c>
+      <c r="G66" s="8"/>
       <c r="H66" s="8"/>
-      <c r="I66" s="8"/>
-      <c r="J66" s="8"/>
+      <c r="I66" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="J66" s="8" t="s">
+        <v>228</v>
+      </c>
       <c r="K66" s="8"/>
       <c r="L66" s="8"/>
-      <c r="M66" s="10"/>
-      <c r="N66" s="10"/>
-      <c r="O66" s="10"/>
-      <c r="P66" s="34">
-        <v>46069.809027777781</v>
-      </c>
-      <c r="Q66" s="34">
+      <c r="M66" s="8"/>
+      <c r="N66" s="8"/>
+      <c r="O66" s="8"/>
+      <c r="P66" s="8"/>
+      <c r="Q66" s="8"/>
+      <c r="R66" s="10"/>
+      <c r="S66" s="10"/>
+      <c r="T66" s="10"/>
+      <c r="U66" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V66" s="34">
         <v>46226.584027777775</v>
       </c>
-      <c r="R66" s="10"/>
+      <c r="W66" s="10"/>
+      <c r="Y66">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z66">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="7">
-        <v>65</v>
-      </c>
-      <c r="B67" s="7" t="s">
+    <row r="67" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D67" s="7">
+        <v>60</v>
+      </c>
+      <c r="E67" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="C67" s="7">
-        <v>8</v>
-      </c>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="G67" s="8" t="s">
-        <v>232</v>
-      </c>
+      <c r="F67" s="7">
+        <v>7</v>
+      </c>
+      <c r="G67" s="8"/>
       <c r="H67" s="8"/>
-      <c r="I67" s="8"/>
-      <c r="J67" s="8"/>
+      <c r="I67" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="J67" s="8" t="s">
+        <v>230</v>
+      </c>
       <c r="K67" s="8"/>
       <c r="L67" s="8"/>
-      <c r="M67" s="10"/>
-      <c r="N67" s="10"/>
-      <c r="O67" s="10"/>
-      <c r="P67" s="34">
-        <v>46085.347222222219</v>
-      </c>
-      <c r="Q67" s="34">
+      <c r="M67" s="8"/>
+      <c r="N67" s="8"/>
+      <c r="O67" s="8"/>
+      <c r="P67" s="8"/>
+      <c r="Q67" s="8"/>
+      <c r="R67" s="10"/>
+      <c r="S67" s="10"/>
+      <c r="T67" s="10"/>
+      <c r="U67" s="34">
+        <v>46069.809027777781</v>
+      </c>
+      <c r="V67" s="34">
         <v>46226.584027777775</v>
       </c>
-      <c r="R67" s="10"/>
+      <c r="W67" s="10"/>
+      <c r="Y67">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
+      <c r="Z67">
+        <f t="shared" si="0"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="7">
-        <v>57</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C68" s="7">
-        <v>1</v>
-      </c>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="G68" s="8" t="s">
-        <v>278</v>
-      </c>
+    <row r="68" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D68" s="7">
+        <v>65</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="F68" s="7">
+        <v>8</v>
+      </c>
+      <c r="G68" s="8"/>
       <c r="H68" s="8"/>
-      <c r="I68" s="8"/>
-      <c r="J68" s="8"/>
+      <c r="I68" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="J68" s="8" t="s">
+        <v>232</v>
+      </c>
       <c r="K68" s="8"/>
       <c r="L68" s="8"/>
-      <c r="M68" s="10"/>
-      <c r="N68" s="10"/>
-      <c r="O68" s="10"/>
-      <c r="P68" s="34">
-        <v>46069.554861111108</v>
-      </c>
-      <c r="Q68" s="34">
-        <v>46077.372916666667</v>
-      </c>
+      <c r="M68" s="8"/>
+      <c r="N68" s="8"/>
+      <c r="O68" s="8"/>
+      <c r="P68" s="8"/>
+      <c r="Q68" s="8"/>
       <c r="R68" s="10"/>
+      <c r="S68" s="10"/>
+      <c r="T68" s="10"/>
+      <c r="U68" s="34">
+        <v>46085.347222222219</v>
+      </c>
+      <c r="V68" s="34">
+        <v>46226.584027777775</v>
+      </c>
+      <c r="W68" s="10"/>
+      <c r="Y68">
+        <f t="shared" ref="Y68:Z75" si="1">LENB(K68)-$B$4</f>
+        <v>-18</v>
+      </c>
+      <c r="Z68">
+        <f t="shared" si="1"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="7">
-        <v>61</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C69" s="7">
-        <v>2</v>
-      </c>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="G69" s="8" t="s">
-        <v>191</v>
-      </c>
+    <row r="69" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D69" s="7">
+        <v>57</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="F69" s="7">
+        <v>1</v>
+      </c>
+      <c r="G69" s="8"/>
       <c r="H69" s="8"/>
-      <c r="I69" s="8"/>
-      <c r="J69" s="8"/>
+      <c r="I69" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="J69" s="8" t="s">
+        <v>283</v>
+      </c>
       <c r="K69" s="8"/>
       <c r="L69" s="8"/>
-      <c r="M69" s="10"/>
-      <c r="N69" s="10"/>
-      <c r="O69" s="10"/>
-      <c r="P69" s="34">
+      <c r="M69" s="8"/>
+      <c r="N69" s="8"/>
+      <c r="O69" s="8"/>
+      <c r="P69" s="8"/>
+      <c r="Q69" s="8"/>
+      <c r="R69" s="10"/>
+      <c r="S69" s="10"/>
+      <c r="T69" s="10"/>
+      <c r="U69" s="34">
+        <v>46069.554861111108</v>
+      </c>
+      <c r="V69" s="34">
         <v>46077.372916666667</v>
       </c>
-      <c r="Q69" s="34">
-        <v>46077.372916666667</v>
-      </c>
-      <c r="R69" s="10"/>
+      <c r="W69" s="10"/>
+      <c r="Y69">
+        <f t="shared" si="1"/>
+        <v>-18</v>
+      </c>
+      <c r="Z69">
+        <f t="shared" si="1"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="7">
-        <v>62</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="C70" s="7">
-        <v>1</v>
-      </c>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8" t="s">
+    <row r="70" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D70" s="7">
+        <v>61</v>
+      </c>
+      <c r="E70" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="G70" s="8" t="s">
-        <v>194</v>
-      </c>
+      <c r="F70" s="7">
+        <v>2</v>
+      </c>
+      <c r="G70" s="8"/>
       <c r="H70" s="8"/>
-      <c r="I70" s="8"/>
-      <c r="J70" s="8"/>
+      <c r="I70" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="J70" s="8" t="s">
+        <v>191</v>
+      </c>
       <c r="K70" s="8"/>
       <c r="L70" s="8"/>
-      <c r="M70" s="10"/>
-      <c r="N70" s="10"/>
-      <c r="O70" s="10"/>
-      <c r="P70" s="34">
-        <v>46083.387499999997</v>
-      </c>
-      <c r="Q70" s="34">
-        <v>46083.387499999997</v>
-      </c>
+      <c r="M70" s="8"/>
+      <c r="N70" s="8"/>
+      <c r="O70" s="8"/>
+      <c r="P70" s="8"/>
+      <c r="Q70" s="8"/>
       <c r="R70" s="10"/>
+      <c r="S70" s="10"/>
+      <c r="T70" s="10"/>
+      <c r="U70" s="34">
+        <v>46077.372916666667</v>
+      </c>
+      <c r="V70" s="34">
+        <v>46077.372916666667</v>
+      </c>
+      <c r="W70" s="10"/>
+      <c r="Y70">
+        <f t="shared" si="1"/>
+        <v>-18</v>
+      </c>
+      <c r="Z70">
+        <f t="shared" si="1"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="7">
-        <v>63</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="C71" s="7">
-        <v>2</v>
-      </c>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="G71" s="8" t="s">
+    <row r="71" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D71" s="7">
+        <v>62</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="F71" s="7">
+        <v>1</v>
+      </c>
+      <c r="G71" s="8"/>
+      <c r="H71" s="8"/>
+      <c r="I71" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="J71" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="H71" s="8"/>
-      <c r="I71" s="8"/>
-      <c r="J71" s="8"/>
       <c r="K71" s="8"/>
       <c r="L71" s="8"/>
-      <c r="M71" s="10"/>
-      <c r="N71" s="10"/>
-      <c r="O71" s="10"/>
-      <c r="P71" s="34">
+      <c r="M71" s="8"/>
+      <c r="N71" s="8"/>
+      <c r="O71" s="8"/>
+      <c r="P71" s="8"/>
+      <c r="Q71" s="8"/>
+      <c r="R71" s="10"/>
+      <c r="S71" s="10"/>
+      <c r="T71" s="10"/>
+      <c r="U71" s="34">
         <v>46083.387499999997</v>
       </c>
-      <c r="Q71" s="34">
+      <c r="V71" s="34">
         <v>46083.387499999997</v>
       </c>
-      <c r="R71" s="10"/>
+      <c r="W71" s="10"/>
+      <c r="Y71">
+        <f t="shared" si="1"/>
+        <v>-18</v>
+      </c>
+      <c r="Z71">
+        <f t="shared" si="1"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="7">
-        <v>64</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="C72" s="7">
-        <v>3</v>
-      </c>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="G72" s="8" t="s">
-        <v>192</v>
-      </c>
+    <row r="72" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D72" s="7">
+        <v>63</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="F72" s="7">
+        <v>2</v>
+      </c>
+      <c r="G72" s="8"/>
       <c r="H72" s="8"/>
-      <c r="I72" s="8"/>
-      <c r="J72" s="8"/>
+      <c r="I72" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="J72" s="8" t="s">
+        <v>194</v>
+      </c>
       <c r="K72" s="8"/>
       <c r="L72" s="8"/>
-      <c r="M72" s="10"/>
-      <c r="N72" s="10"/>
-      <c r="O72" s="10"/>
-      <c r="P72" s="34">
-        <v>46083.363888888889</v>
-      </c>
-      <c r="Q72" s="34">
-        <v>46083.363888888889</v>
-      </c>
+      <c r="M72" s="8"/>
+      <c r="N72" s="8"/>
+      <c r="O72" s="8"/>
+      <c r="P72" s="8"/>
+      <c r="Q72" s="8"/>
       <c r="R72" s="10"/>
+      <c r="S72" s="10"/>
+      <c r="T72" s="10"/>
+      <c r="U72" s="34">
+        <v>46083.387499999997</v>
+      </c>
+      <c r="V72" s="34">
+        <v>46083.387499999997</v>
+      </c>
+      <c r="W72" s="10"/>
+      <c r="Y72">
+        <f t="shared" si="1"/>
+        <v>-18</v>
+      </c>
+      <c r="Z72">
+        <f t="shared" si="1"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="7"/>
-      <c r="B73" s="7"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
+    <row r="73" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D73" s="7">
+        <v>64</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="F73" s="7">
+        <v>3</v>
+      </c>
       <c r="G73" s="8"/>
       <c r="H73" s="8"/>
-      <c r="I73" s="8"/>
-      <c r="J73" s="8"/>
+      <c r="I73" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="J73" s="8" t="s">
+        <v>192</v>
+      </c>
       <c r="K73" s="8"/>
       <c r="L73" s="8"/>
-      <c r="M73" s="10"/>
-      <c r="N73" s="10"/>
-      <c r="O73" s="10"/>
-      <c r="P73" s="34"/>
-      <c r="Q73" s="34"/>
+      <c r="M73" s="8"/>
+      <c r="N73" s="8"/>
+      <c r="O73" s="8"/>
+      <c r="P73" s="8"/>
+      <c r="Q73" s="8"/>
       <c r="R73" s="10"/>
+      <c r="S73" s="10"/>
+      <c r="T73" s="10"/>
+      <c r="U73" s="34">
+        <v>46083.363888888889</v>
+      </c>
+      <c r="V73" s="34">
+        <v>46083.363888888889</v>
+      </c>
+      <c r="W73" s="10"/>
+      <c r="Y73">
+        <f t="shared" si="1"/>
+        <v>-18</v>
+      </c>
+      <c r="Z73">
+        <f t="shared" si="1"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" s="18"/>
-      <c r="B74" s="18"/>
-      <c r="C74" s="18"/>
-      <c r="D74" s="19"/>
-      <c r="E74" s="19"/>
-      <c r="F74" s="19"/>
-      <c r="G74" s="19"/>
-      <c r="H74" s="19"/>
-      <c r="I74" s="19"/>
-      <c r="J74" s="19"/>
-      <c r="K74" s="19"/>
-      <c r="L74" s="19"/>
-      <c r="M74" s="20"/>
-      <c r="N74" s="20"/>
-      <c r="O74" s="20"/>
-      <c r="P74" s="37"/>
-      <c r="Q74" s="37"/>
-      <c r="R74" s="20"/>
+    <row r="74" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="8"/>
+      <c r="J74" s="8"/>
+      <c r="K74" s="8"/>
+      <c r="L74" s="8"/>
+      <c r="M74" s="8"/>
+      <c r="N74" s="8"/>
+      <c r="O74" s="8"/>
+      <c r="P74" s="8"/>
+      <c r="Q74" s="8"/>
+      <c r="R74" s="10"/>
+      <c r="S74" s="10"/>
+      <c r="T74" s="10"/>
+      <c r="U74" s="34"/>
+      <c r="V74" s="34"/>
+      <c r="W74" s="10"/>
+      <c r="Y74">
+        <f t="shared" si="1"/>
+        <v>-18</v>
+      </c>
+      <c r="Z74">
+        <f t="shared" si="1"/>
+        <v>-18</v>
+      </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" t="s">
+    <row r="75" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D75" s="18"/>
+      <c r="E75" s="18"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="19"/>
+      <c r="H75" s="19"/>
+      <c r="I75" s="19"/>
+      <c r="J75" s="19"/>
+      <c r="K75" s="19"/>
+      <c r="L75" s="19"/>
+      <c r="M75" s="19"/>
+      <c r="N75" s="19"/>
+      <c r="O75" s="19"/>
+      <c r="P75" s="19"/>
+      <c r="Q75" s="19"/>
+      <c r="R75" s="20"/>
+      <c r="S75" s="20"/>
+      <c r="T75" s="20"/>
+      <c r="U75" s="37"/>
+      <c r="V75" s="37"/>
+      <c r="W75" s="20"/>
+      <c r="Y75">
+        <f t="shared" si="1"/>
+        <v>-18</v>
+      </c>
+      <c r="Z75">
+        <f t="shared" si="1"/>
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="77" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D77" t="s">
         <v>91</v>
       </c>
-      <c r="D76" t="s">
+      <c r="G77" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77">
-        <f>MAX(A$2:A$74)</f>
+    <row r="78" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D78">
+        <f>MAX(D$3:D$75)</f>
         <v>72</v>
       </c>
-      <c r="D77">
-        <f>MAX(D$2:D$74)</f>
+      <c r="G78">
+        <f>MAX(G$3:G$75)</f>
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" t="s">
+    <row r="79" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D79" t="s">
         <v>139</v>
       </c>
-      <c r="B78" t="s">
+      <c r="E79" t="s">
         <v>96</v>
       </c>
-      <c r="C78" t="s">
+      <c r="F79" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79">
-        <f>ROW(A75)-ROW(A1)-1</f>
+    <row r="80" spans="4:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="D80">
+        <f>ROW(D76)-ROW(D2)-1</f>
         <v>73</v>
       </c>
-      <c r="B79">
-        <f>COUNTIF(B$2:B$74,B78)</f>
+      <c r="E80">
+        <f>COUNTIF(E$3:E$75,E79)</f>
         <v>24</v>
       </c>
-      <c r="C79" s="25">
-        <f>_xlfn.MAXIFS(C$2:C$74,$B$2:$B$74,C78)</f>
+      <c r="F80" s="25">
+        <f>_xlfn.MAXIFS(F$3:F$75,$E$3:$E$75,F79)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" t="s">
+    <row r="81" spans="5:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="E81" t="s">
         <v>94</v>
       </c>
-      <c r="C80" t="s">
+      <c r="F81" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="81" spans="2:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81">
-        <f>COUNTIF(B$2:B$74,B80)</f>
+    <row r="82" spans="5:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="E82">
+        <f>COUNTIF(E$3:E$75,E81)</f>
         <v>23</v>
       </c>
-      <c r="C81" s="25">
-        <f>_xlfn.MAXIFS(C$2:C$74,$B$2:$B$74,C80)</f>
+      <c r="F82" s="25">
+        <f>_xlfn.MAXIFS(F$3:F$75,$E$3:$E$75,F81)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="2:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H84" s="2" t="s">
+    <row r="85" spans="5:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="M85" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="L84">
+      <c r="Q85">
         <v>1</v>
       </c>
-      <c r="R84" t="s">
+      <c r="W85" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="85" spans="2:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H85" t="s">
+    <row r="86" spans="5:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="M86" t="s">
         <v>49</v>
       </c>
-      <c r="I85" t="s">
+      <c r="N86" t="s">
         <v>46</v>
       </c>
-      <c r="J85" t="s">
+      <c r="O86" t="s">
         <v>45</v>
       </c>
-      <c r="L85">
+      <c r="Q86">
         <v>1</v>
       </c>
-      <c r="R85" t="s">
+      <c r="W86" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="87" spans="2:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H87" s="2" t="s">
+    <row r="88" spans="5:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="M88" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="2:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H88" t="s">
+    <row r="89" spans="5:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="M89" t="s">
         <v>69</v>
       </c>
-      <c r="I88" t="s">
+      <c r="N89" t="s">
         <v>71</v>
       </c>
-      <c r="J88" t="s">
+      <c r="O89" t="s">
         <v>67</v>
       </c>
-      <c r="L88">
+      <c r="Q89">
         <v>1</v>
       </c>
-      <c r="R88" t="s">
+      <c r="W89" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="90" spans="2:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H90" s="2" t="s">
+    <row r="91" spans="5:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="M91" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="91" spans="2:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H91" t="s">
+    <row r="92" spans="5:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="M92" t="s">
         <v>70</v>
       </c>
-      <c r="I91" t="s">
+      <c r="N92" t="s">
         <v>71</v>
       </c>
-      <c r="J91" t="s">
+      <c r="O92" t="s">
         <v>68</v>
       </c>
-      <c r="L91">
+      <c r="Q92">
         <v>1</v>
       </c>
-      <c r="R91" t="s">
+      <c r="W92" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="93" spans="2:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H93" s="2" t="s">
+    <row r="94" spans="5:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="M94" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="94" spans="2:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H94" t="s">
+    <row r="95" spans="5:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="M95" t="s">
         <v>35</v>
       </c>
-      <c r="I94" t="s">
+      <c r="N95" t="s">
         <v>36</v>
       </c>
-      <c r="J94" t="s">
+      <c r="O95" t="s">
         <v>11</v>
       </c>
-      <c r="L94">
+      <c r="Q95">
         <v>1</v>
       </c>
-      <c r="R94" t="s">
+      <c r="W95" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="95" spans="2:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H95" t="s">
+    <row r="96" spans="5:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="M96" t="s">
         <v>38</v>
       </c>
-      <c r="I95" s="1" t="s">
+      <c r="N96" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J95" t="s">
+      <c r="O96" t="s">
         <v>37</v>
       </c>
-      <c r="L95">
+      <c r="Q96">
         <v>2</v>
       </c>
-      <c r="R95" t="s">
+      <c r="W96" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="97" spans="8:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H97" s="2" t="s">
+    <row r="98" spans="13:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="M98" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="98" spans="8:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H98" t="s">
+    <row r="99" spans="13:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="M99" t="s">
         <v>39</v>
       </c>
-      <c r="I98" t="s">
+      <c r="N99" t="s">
         <v>40</v>
       </c>
-      <c r="J98" t="s">
+      <c r="O99" t="s">
         <v>11</v>
       </c>
-      <c r="L98">
+      <c r="Q99">
         <v>1</v>
       </c>
-      <c r="R98" t="s">
+      <c r="W99" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="8:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H99" t="s">
+    <row r="100" spans="13:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="M100" t="s">
         <v>43</v>
       </c>
-      <c r="I99" s="3" t="s">
+      <c r="N100" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="J99" t="s">
+      <c r="O100" t="s">
         <v>42</v>
       </c>
-      <c r="L99">
+      <c r="Q100">
         <v>1</v>
       </c>
-      <c r="R99" t="s">
+      <c r="W100" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="100" spans="8:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H100" t="s">
+    <row r="101" spans="13:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="M101" t="s">
         <v>44</v>
       </c>
-      <c r="I100" t="s">
+      <c r="N101" t="s">
         <v>48</v>
       </c>
-      <c r="J100" t="s">
+      <c r="O101" t="s">
         <v>4</v>
       </c>
-      <c r="L100">
+      <c r="Q101">
         <v>2</v>
       </c>
-      <c r="R100" t="s">
+      <c r="W101" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="101" spans="8:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="H101" t="s">
+    <row r="102" spans="13:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="M102" t="s">
         <v>72</v>
       </c>
-      <c r="I101" t="s">
+      <c r="N102" t="s">
         <v>73</v>
       </c>
-      <c r="J101" t="s">
+      <c r="O102" t="s">
         <v>75</v>
       </c>
-      <c r="L101">
+      <c r="Q102">
         <v>1</v>
       </c>
-      <c r="R101" t="s">
+      <c r="W102" t="s">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R60" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R60">
-      <sortCondition ref="B1:B60"/>
+  <autoFilter ref="D2:W61" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D3:W61">
+      <sortCondition ref="E2:E61"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A2:R74">
-    <cfRule type="expression" dxfId="1" priority="5">
-      <formula>INT($Q2)=TODAY()</formula>
+  <conditionalFormatting sqref="D3:W75">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>INT($V3)=TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="6">
-      <formula>MOD(ROW(A2),2)=1</formula>
+    <cfRule type="expression" dxfId="3" priority="6">
+      <formula>MOD(ROW(D3),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5861,7 +6984,7 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="S1" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.55000000000000004">
@@ -5943,7 +7066,7 @@
         <v>153</v>
       </c>
       <c r="S3" s="30" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="X3" s="30" t="s">
         <v>142</v>
@@ -5994,7 +7117,7 @@
       </c>
       <c r="B4" t="str" cm="1">
         <f t="array" aca="1" ref="B4" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\unit01\vt5-w10\[TP_メッセージ.xlsx]err</v>
+        <v>C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_index</v>
       </c>
       <c r="E4" t="s">
         <v>96</v>
@@ -6004,11 +7127,11 @@
         <v>1</v>
       </c>
       <c r="H4" cm="1">
-        <f t="array" ref="H4:H203">IFERROR(MATCH($E$4:$E$203&amp;$F$4:$F$203,info_index!$B$2:$B$74&amp;info_index!$C$2:$C$74,0),"")</f>
+        <f t="array" ref="H4:H203">IFERROR(MATCH($E$4:$E$203&amp;$F$4:$F$203,info_index!$E$3:$E$75&amp;info_index!$F$3:$F$75,0),"")</f>
         <v>1</v>
       </c>
       <c r="I4" t="str" cm="1">
-        <f t="array" aca="1" ref="I4:I203" ca="1">IF(LEN(_xlfn.ANCHORARRAY(H4)),INDEX(OFFSET(info_index!$F$2:$F$74,0,$B$24),MATCH($E$4:$E$203&amp;$F$4:$F$203,info_index!$B$2:$B$74&amp;info_index!$C$2:$C$74,0)&amp;"",1),"")</f>
+        <f t="array" aca="1" ref="I4:I203" ca="1">IF(LEN(_xlfn.ANCHORARRAY(H4)),INDEX(OFFSET(info_index!$I$3:$I$75,0,$B$24),MATCH($E$4:$E$203&amp;$F$4:$F$203,info_index!$E$3:$E$75&amp;info_index!$F$3:$F$75,0)&amp;"",1),"")</f>
         <v>Brazing Foil Reel Axis</v>
       </c>
       <c r="J4" t="str" cm="1">
@@ -6020,7 +7143,7 @@
         <v>【axis1】 Brazing Foil Reel Axis</v>
       </c>
       <c r="M4" t="str" cm="1">
-        <f t="array" ref="M4:M203">IFERROR(INDEX(info_index!$H$2:$H$74,MATCH($E$4:$E$203&amp;$F$4:$F$203,info_index!$B$2:$B$74&amp;info_index!$C$2:$C$74,0),1)&amp;"","")</f>
+        <f t="array" ref="M4:M203">IFERROR(INDEX(info_index!$M$3:$M$75,MATCH($E$4:$E$203&amp;$F$4:$F$203,info_index!$E$3:$E$75&amp;info_index!$F$3:$F$75,0),1)&amp;"","")</f>
         <v>5TK20GN-CW2J+5GN180K</v>
       </c>
       <c r="N4" t="str" cm="1">
@@ -6028,7 +7151,7 @@
         <v>5TK20GN-CW2J+5GN180K</v>
       </c>
       <c r="O4" t="str" cm="1">
-        <f t="array" aca="1" ref="O4:O203" ca="1">IF(LEN(_xlfn.ANCHORARRAY(H4)),INDEX(OFFSET(info_index!$J$2:$J$74,0,$B$24),MATCH($E$4:$E$203&amp;$F$4:$F$203,info_index!$B$2:$B$74&amp;info_index!$C$2:$C$74,0),1)&amp;"","")</f>
+        <f t="array" aca="1" ref="O4:O203" ca="1">IF(LEN(_xlfn.ANCHORARRAY(H4)),INDEX(OFFSET(info_index!$O$3:$O$75,0,$B$24),MATCH($E$4:$E$203&amp;$F$4:$F$203,info_index!$E$3:$E$75&amp;info_index!$F$3:$F$75,0),1)&amp;"","")</f>
         <v>OrientalMotor</v>
       </c>
       <c r="P4" t="str" cm="1">
@@ -6406,7 +7529,7 @@
       </c>
       <c r="B6" t="str">
         <f ca="1">"このスクリプトは "&amp;B4&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\vt5-w10\[TP_メッセージ.xlsx]err によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" ref="E6:E69" si="1">E5</f>
@@ -8013,7 +9136,7 @@
       </c>
       <c r="B14" t="str">
         <f ca="1">$AK$206</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\vt5-w10\[TP_メッセージ.xlsx]err によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//Brazing Foil Reel Axis
@@ -13247,7 +14370,7 @@
     </row>
     <row r="44" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B44">
         <v>64</v>
@@ -32954,7 +34077,7 @@
     <row r="206" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="AK206" t="str">
         <f ca="1">IF(LENB($B$6),$B$8&amp;$B$6,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AK$4:AK$203)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$30&amp;CHAR(9)&amp;$B$9&amp;" 1"&amp;$B$10&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$7),CHAR(10)&amp;$B$8&amp;$B$7,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\vt5-w10\[TP_メッセージ.xlsx]err によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//Brazing Foil Reel Axis
@@ -33748,17 +34871,17 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4:L203">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>0&lt;$S4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>0&lt;S$2</formula>
     </cfRule>
   </conditionalFormatting>

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D03C12-83C7-4D86-8C0C-11CBA904BAF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762EFF3B-07A8-4E78-B9B2-7005326DA58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
   <sheets>
     <sheet name="info_index" sheetId="1" r:id="rId1"/>
     <sheet name="info_script" sheetId="3" r:id="rId2"/>
+    <sheet name="Additional Terms" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$D$2:$W$61</definedName>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="431">
   <si>
     <t>RCA2-GS3NA-I-10-2-50-A6-M-K1</t>
   </si>
@@ -1032,12 +1033,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>X-roll electromagnetic clutch</t>
-  </si>
-  <si>
-    <t>T-roll gluing shaft</t>
-  </si>
-  <si>
     <t>OTHC</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1138,18 +1133,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Flat plate chuck front and rear shafts</t>
-  </si>
-  <si>
     <t>RCP4-GRSWL-I-42P-28-30-P3-M-AC1</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>RCP6-TA6C-WA-42P-12-125-P3-X07-CJB-1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Flat plate chuck shaft</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1166,9 +1154,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Corrugated sheet tensioning shaft</t>
-  </si>
-  <si>
     <t>Flat Sheet Feeder</t>
   </si>
   <si>
@@ -1367,9 +1352,6 @@
     <t>溶接機</t>
   </si>
   <si>
-    <t>welding machine</t>
-  </si>
-  <si>
     <t>Xロール電磁クラッチ</t>
   </si>
   <si>
@@ -1554,15 +1536,9 @@
     <t>箔ロウ送り軸</t>
   </si>
   <si>
-    <t>周長測定上下軸</t>
-  </si>
-  <si>
     <t>排出チャック軸</t>
   </si>
   <si>
-    <t>バインダ供給ポンプM</t>
-  </si>
-  <si>
     <t>波板リールM</t>
   </si>
   <si>
@@ -1684,9 +1660,6 @@
   </si>
   <si>
     <t>Corr Cutter O/C</t>
-  </si>
-  <si>
-    <t>Corr Cutter Support</t>
   </si>
   <si>
     <t>Corr Cut Supp L</t>
@@ -1791,6 +1764,146 @@
   </si>
   <si>
     <t>文字数オーバー(EN)</t>
+  </si>
+  <si>
+    <t>Corr Cut Support</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>意味</t>
+  </si>
+  <si>
+    <t>推奨略語</t>
+  </si>
+  <si>
+    <t>Axis</t>
+  </si>
+  <si>
+    <t>Ax</t>
+  </si>
+  <si>
+    <t>Workpiece</t>
+  </si>
+  <si>
+    <t>Work</t>
+  </si>
+  <si>
+    <t>Discharge</t>
+  </si>
+  <si>
+    <t>Disch</t>
+  </si>
+  <si>
+    <t>Corrugated Sheet</t>
+  </si>
+  <si>
+    <t>Corr</t>
+  </si>
+  <si>
+    <t>Adjustment</t>
+  </si>
+  <si>
+    <t>Adj</t>
+  </si>
+  <si>
+    <t>Auxiliary</t>
+  </si>
+  <si>
+    <t>Aux</t>
+  </si>
+  <si>
+    <t>Center</t>
+  </si>
+  <si>
+    <t>Ctr</t>
+  </si>
+  <si>
+    <t>Support</t>
+  </si>
+  <si>
+    <t>Supp</t>
+  </si>
+  <si>
+    <t>Open/Close</t>
+  </si>
+  <si>
+    <t>O/C</t>
+  </si>
+  <si>
+    <t>Forward/Backward</t>
+  </si>
+  <si>
+    <t>F/B</t>
+  </si>
+  <si>
+    <t>Up/Down</t>
+  </si>
+  <si>
+    <t>U/D</t>
+  </si>
+  <si>
+    <t>Motor</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Extend</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(FAにおける)押出し動作。(例)Cutter Blade Extend.</t>
+    <rPh sb="15" eb="16">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>平板チャック開閉</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Welding Machine</t>
+  </si>
+  <si>
+    <t>X-Roll Electromagnetic Clutch</t>
+  </si>
+  <si>
+    <t>T-Roll Gluing Axis</t>
+  </si>
+  <si>
+    <t>Weld Machine</t>
+  </si>
+  <si>
+    <t>X-Roll EM Clutch</t>
+  </si>
+  <si>
+    <t>Unassigned</t>
+  </si>
+  <si>
+    <t>T-Roll Glue Axis</t>
+  </si>
+  <si>
+    <t>ワーク排出前後軸</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Flat Sheet Chuck Forward/Backward Axis</t>
+  </si>
+  <si>
+    <t>Flat Chuck Axis</t>
+  </si>
+  <si>
+    <t>Corr Tension Axis</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Flat Chuck F/B Ax</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バインダ供給ポンプ</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -2137,7 +2250,71 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <color rgb="FFFF5050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF5050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF5050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF5050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0099CC"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF5050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF5050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF5050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF5050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0099CC"/>
+      </font>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2157,22 +2334,11 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0099CC"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF5050"/>
       <color rgb="FFFF7C80"/>
       <color rgb="FFFF9999"/>
       <color rgb="FFFFCCCC"/>
@@ -2598,15 +2764,15 @@
         <v>115</v>
       </c>
       <c r="K1" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="L1" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2" spans="1:28" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="4" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="D2" s="19" t="s">
         <v>84</v>
@@ -2671,21 +2837,21 @@
       </c>
       <c r="W2" s="21"/>
       <c r="Y2" s="4" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="AA2" s="4" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="AB2" s="4" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B3">
         <v>64</v>
@@ -2709,13 +2875,13 @@
         <v>107</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="K3" s="16" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="L3" s="16" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="M3" s="16" t="s">
         <v>18</v>
@@ -2761,7 +2927,7 @@
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B4">
         <v>18</v>
@@ -2785,13 +2951,13 @@
         <v>101</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="M4" s="10" t="s">
         <v>13</v>
@@ -2855,13 +3021,13 @@
         <v>100</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="M5" s="10" t="s">
         <v>13</v>
@@ -2922,16 +3088,16 @@
         <v>82</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="M6" s="10" t="s">
         <v>13</v>
@@ -2995,13 +3161,13 @@
         <v>175</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>1</v>
@@ -3065,13 +3231,13 @@
         <v>105</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>331</v>
+        <v>105</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="M8" s="10" t="s">
         <v>0</v>
@@ -3108,7 +3274,7 @@
       </c>
       <c r="AA8">
         <f>LENB(K8)-$B$4</f>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AB8">
         <f>LENB(L8)-$B$4</f>
@@ -3135,13 +3301,13 @@
         <v>104</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="M9" s="10" t="s">
         <v>24</v>
@@ -3202,16 +3368,16 @@
         <v>83</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="M10" s="10" t="s">
         <v>88</v>
@@ -3272,16 +3438,16 @@
         <v>83</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="M11" s="10" t="s">
         <v>89</v>
@@ -3341,13 +3507,13 @@
         <v>106</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10"/>
@@ -3361,7 +3527,7 @@
         <v>46069.554861111108</v>
       </c>
       <c r="V12" s="26">
-        <v>46226.618055555555</v>
+        <v>46227.401388888888</v>
       </c>
       <c r="W12" s="8"/>
       <c r="Y12">
@@ -3374,7 +3540,7 @@
       </c>
       <c r="AA12">
         <f>LENB(K12)-$B$4</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB12">
         <f>LENB(L12)-$B$4</f>
@@ -3397,13 +3563,13 @@
         <v>108</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="10"/>
@@ -3453,13 +3619,13 @@
         <v>109</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="10"/>
@@ -3513,13 +3679,13 @@
         <v>102</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="M15" s="10" t="s">
         <v>26</v>
@@ -3583,13 +3749,13 @@
         <v>103</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="M16" s="10" t="s">
         <v>28</v>
@@ -3653,13 +3819,13 @@
         <v>184</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="M17" s="10" t="s">
         <v>185</v>
@@ -3712,22 +3878,22 @@
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
       <c r="I18" s="10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="M18" s="10" t="s">
         <v>28</v>
       </c>
       <c r="N18" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="O18" s="10" t="s">
         <v>157</v>
@@ -3743,7 +3909,7 @@
         <v>46069.554861111108</v>
       </c>
       <c r="V18" s="26">
-        <v>46226.618055555555</v>
+        <v>46227.401388888888</v>
       </c>
       <c r="W18" s="8"/>
       <c r="Y18">
@@ -3776,15 +3942,17 @@
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
       <c r="I19" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="M19" s="10" t="s">
         <v>215</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10" t="s">
-        <v>218</v>
       </c>
       <c r="N19" s="10"/>
       <c r="O19" s="10" t="s">
@@ -3801,7 +3969,7 @@
         <v>46170.415277777778</v>
       </c>
       <c r="V19" s="26">
-        <v>46170.415277777778</v>
+        <v>46227.401388888888</v>
       </c>
       <c r="W19" s="8"/>
       <c r="Y19">
@@ -3810,7 +3978,7 @@
       </c>
       <c r="Z19">
         <f t="shared" si="1"/>
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="AA19">
         <f>LENB(K19)-$B$4</f>
@@ -3818,7 +3986,7 @@
       </c>
       <c r="AB19">
         <f>LENB(L19)-$B$4</f>
-        <v>-18</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="20" spans="4:28" x14ac:dyDescent="0.55000000000000004">
@@ -3834,15 +4002,17 @@
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
       <c r="I20" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="M20" s="10" t="s">
         <v>216</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10" t="s">
-        <v>219</v>
       </c>
       <c r="N20" s="10"/>
       <c r="O20" s="10" t="s">
@@ -3859,7 +4029,7 @@
         <v>46170.415277777778</v>
       </c>
       <c r="V20" s="26">
-        <v>46170.415277777778</v>
+        <v>46227.401388888888</v>
       </c>
       <c r="W20" s="8"/>
       <c r="Y20">
@@ -3876,7 +4046,7 @@
       </c>
       <c r="AB20">
         <f>LENB(L20)-$B$4</f>
-        <v>-18</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="21" spans="4:28" x14ac:dyDescent="0.55000000000000004">
@@ -3892,18 +4062,20 @@
       <c r="G21" s="10"/>
       <c r="H21" s="10"/>
       <c r="I21" s="10" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>222</v>
+        <v>294</v>
       </c>
       <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
+      <c r="L21" s="10" t="s">
+        <v>428</v>
+      </c>
       <c r="M21" s="10" t="s">
         <v>28</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="O21" s="10" t="s">
         <v>159</v>
@@ -3930,7 +4102,7 @@
       </c>
       <c r="Z21">
         <f t="shared" si="1"/>
-        <v>-31</v>
+        <v>-35</v>
       </c>
       <c r="AA21">
         <f>LENB(K21)-$B$4</f>
@@ -3938,7 +4110,7 @@
       </c>
       <c r="AB21">
         <f>LENB(L21)-$B$4</f>
-        <v>-18</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22" spans="4:28" x14ac:dyDescent="0.55000000000000004">
@@ -3954,18 +4126,18 @@
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
       <c r="I22" s="10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
       <c r="M22" s="10" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="O22" s="10" t="s">
         <v>159</v>
@@ -4016,18 +4188,18 @@
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
       <c r="I23" s="10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K23" s="10"/>
       <c r="L23" s="10"/>
       <c r="M23" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>159</v>
@@ -4078,18 +4250,18 @@
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
       <c r="I24" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K24" s="10"/>
       <c r="L24" s="10"/>
       <c r="M24" s="10" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="N24" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="O24" s="10" t="s">
         <v>159</v>
@@ -4140,18 +4312,18 @@
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
       <c r="I25" s="10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K25" s="10"/>
       <c r="L25" s="10"/>
       <c r="M25" s="10" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>159</v>
@@ -4202,18 +4374,18 @@
       <c r="G26" s="10"/>
       <c r="H26" s="10"/>
       <c r="I26" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="K26" s="10"/>
       <c r="L26" s="10"/>
       <c r="M26" s="10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N26" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="O26" s="10" t="s">
         <v>159</v>
@@ -4265,19 +4437,19 @@
         <v>1</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="M27" s="10" t="s">
         <v>51</v>
@@ -4338,16 +4510,16 @@
       <c r="G28" s="10"/>
       <c r="H28" s="10"/>
       <c r="I28" s="10" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="M28" s="10" t="s">
         <v>145</v>
@@ -4400,16 +4572,16 @@
       <c r="G29" s="10"/>
       <c r="H29" s="10"/>
       <c r="I29" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="M29" s="10" t="s">
         <v>145</v>
@@ -4466,16 +4638,16 @@
         <v>110</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="M30" s="10" t="s">
         <v>53</v>
@@ -4537,25 +4709,25 @@
         <v>5</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="L31" s="10" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="M31" s="10" t="s">
         <v>56</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="O31" s="10" t="s">
         <v>160</v>
@@ -4611,25 +4783,25 @@
         <v>5</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I32" s="10" t="s">
         <v>114</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>114</v>
+        <v>417</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="M32" s="10" t="s">
         <v>55</v>
       </c>
       <c r="N32" s="10" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="O32" s="10" t="s">
         <v>160</v>
@@ -4685,25 +4857,25 @@
         <v>6</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="L33" s="10" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="M33" s="10" t="s">
         <v>57</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>160</v>
@@ -4765,19 +4937,19 @@
         <v>113</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="K34" s="10" t="s">
         <v>113</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="M34" s="10" t="s">
         <v>60</v>
       </c>
       <c r="N34" s="10" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="O34" s="10" t="s">
         <v>160</v>
@@ -4836,16 +5008,16 @@
         <v>76</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="M35" s="10" t="s">
         <v>58</v>
@@ -4910,22 +5082,22 @@
         <v>188</v>
       </c>
       <c r="I36" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="J36" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="J36" s="10" t="s">
-        <v>391</v>
-      </c>
       <c r="K36" s="10" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="L36" s="10" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="M36" s="10" t="s">
         <v>57</v>
       </c>
       <c r="N36" s="10" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="O36" s="10" t="s">
         <v>160</v>
@@ -4981,25 +5153,25 @@
         <v>9</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="L37" s="10" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="M37" s="10" t="s">
         <v>62</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>160</v>
@@ -5055,25 +5227,25 @@
         <v>9</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="I38" s="10" t="s">
         <v>111</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="L38" s="10" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="M38" s="10" t="s">
         <v>61</v>
       </c>
       <c r="N38" s="10" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="O38" s="10" t="s">
         <v>160</v>
@@ -5132,22 +5304,22 @@
         <v>79</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="L39" s="10" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="M39" s="10" t="s">
         <v>62</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>160</v>
@@ -5209,19 +5381,19 @@
         <v>112</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="K40" s="10" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="L40" s="10" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="M40" s="10" t="s">
         <v>63</v>
       </c>
       <c r="N40" s="10" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="O40" s="10" t="s">
         <v>160</v>
@@ -5280,16 +5452,16 @@
         <v>79</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="L41" s="10" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="M41" s="10" t="s">
         <v>64</v>
@@ -5334,7 +5506,7 @@
       </c>
       <c r="AB41">
         <f>LENB(L41)-$B$4</f>
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="42" spans="4:28" x14ac:dyDescent="0.55000000000000004">
@@ -5354,16 +5526,16 @@
         <v>79</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="L42" s="10" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="M42" s="10" t="s">
         <v>64</v>
@@ -5424,16 +5596,16 @@
       <c r="G43" s="10"/>
       <c r="H43" s="10"/>
       <c r="I43" s="10" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="K43" s="10" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="L43" s="10" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="M43" s="10" t="s">
         <v>44</v>
@@ -5486,16 +5658,16 @@
       <c r="G44" s="10"/>
       <c r="H44" s="10"/>
       <c r="I44" s="10" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="K44" s="10" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="L44" s="10" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="M44" s="10" t="s">
         <v>44</v>
@@ -5548,19 +5720,19 @@
       <c r="G45" s="10"/>
       <c r="H45" s="10"/>
       <c r="I45" s="10" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="K45" s="10" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="L45" s="10" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="M45" s="10" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="N45" s="10"/>
       <c r="O45" s="10"/>
@@ -5614,28 +5786,28 @@
         <v>76</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="K46" s="10" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="L46" s="10" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="M46" s="10" t="s">
         <v>183</v>
       </c>
       <c r="N46" s="10" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="O46" s="10" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="P46" s="10" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="Q46" s="10"/>
       <c r="R46" s="10"/>
@@ -5687,7 +5859,7 @@
         <v>62</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>160</v>
@@ -5699,7 +5871,7 @@
         <v>1</v>
       </c>
       <c r="R47" s="27" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="S47" s="10"/>
       <c r="T47" s="10"/>
@@ -5761,7 +5933,7 @@
         <v>1</v>
       </c>
       <c r="R48" s="27" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="S48" s="24"/>
       <c r="T48" s="24"/>
@@ -5823,7 +5995,7 @@
         <v>1</v>
       </c>
       <c r="R49" s="27" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="S49" s="24"/>
       <c r="T49" s="24"/>
@@ -5856,7 +6028,7 @@
         <v>21</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="F50" s="10">
         <v>1</v>
@@ -5865,25 +6037,25 @@
         <v>1</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="K50" s="10" t="s">
-        <v>263</v>
+        <v>425</v>
       </c>
       <c r="L50" s="10" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="M50" s="10" t="s">
         <v>25</v>
       </c>
       <c r="N50" s="10" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="O50" s="10" t="s">
         <v>159</v>
@@ -5926,17 +6098,17 @@
         <v>24</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F51" s="10"/>
       <c r="G51" s="10">
         <v>3</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="J51" s="10"/>
       <c r="K51" s="10"/>
@@ -5988,26 +6160,26 @@
         <v>25</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="7">
         <v>3</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="J52" s="7"/>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
       <c r="M52" s="7" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="N52" s="7" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="O52" s="7" t="s">
         <v>157</v>
@@ -6050,7 +6222,7 @@
         <v>29</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F53" s="7"/>
       <c r="G53" s="7">
@@ -6067,7 +6239,7 @@
         <v>20</v>
       </c>
       <c r="N53" s="7" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="O53" s="7" t="s">
         <v>157</v>
@@ -6110,17 +6282,17 @@
         <v>30</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F54" s="7"/>
       <c r="G54" s="7">
         <v>1</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="J54" s="7"/>
       <c r="K54" s="7"/>
@@ -6129,7 +6301,7 @@
         <v>21</v>
       </c>
       <c r="N54" s="7" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="O54" s="7" t="s">
         <v>157</v>
@@ -6141,7 +6313,7 @@
         <v>1</v>
       </c>
       <c r="R54" s="7" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="S54" s="7"/>
       <c r="T54" s="7"/>
@@ -6174,17 +6346,17 @@
         <v>34</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="7">
         <v>1</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="J55" s="7"/>
       <c r="K55" s="7"/>
@@ -6193,7 +6365,7 @@
         <v>29</v>
       </c>
       <c r="N55" s="7" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="O55" s="7" t="s">
         <v>157</v>
@@ -6205,7 +6377,7 @@
         <v>1</v>
       </c>
       <c r="R55" s="7" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="S55" s="7"/>
       <c r="T55" s="7"/>
@@ -6243,14 +6415,14 @@
         <v>1</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="I56" s="7"/>
       <c r="J56" s="7"/>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
       <c r="M56" s="7" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="N56" s="9" t="s">
         <v>50</v>
@@ -6301,7 +6473,7 @@
         <v>5</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I57" s="7"/>
       <c r="J57" s="7"/>
@@ -6359,7 +6531,7 @@
         <v>5</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I58" s="7"/>
       <c r="J58" s="7"/>
@@ -6369,7 +6541,7 @@
         <v>15</v>
       </c>
       <c r="N58" s="7" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="O58" s="7" t="s">
         <v>157</v>
@@ -6417,7 +6589,7 @@
         <v>3</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="I59" s="7"/>
       <c r="J59" s="7"/>
@@ -6439,7 +6611,7 @@
         <v>1</v>
       </c>
       <c r="R59" s="7" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="S59" s="7"/>
       <c r="T59" s="7"/>
@@ -6541,7 +6713,7 @@
         <v>176</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -6593,7 +6765,7 @@
         <v>177</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -6645,7 +6817,7 @@
         <v>178</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -6697,7 +6869,7 @@
         <v>179</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -6749,7 +6921,7 @@
         <v>180</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
@@ -6801,7 +6973,7 @@
         <v>181</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -6850,10 +7022,10 @@
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
       <c r="I67" s="7" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -6902,10 +7074,10 @@
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
       <c r="I68" s="7" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -6946,7 +7118,7 @@
         <v>57</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F69" s="7">
         <v>1</v>
@@ -6954,13 +7126,17 @@
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
       <c r="I69" s="7" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="K69" s="7"/>
-      <c r="L69" s="7"/>
+        <v>418</v>
+      </c>
+      <c r="K69" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="L69" s="7" t="s">
+        <v>421</v>
+      </c>
       <c r="M69" s="7"/>
       <c r="N69" s="7"/>
       <c r="O69" s="7"/>
@@ -6986,11 +7162,11 @@
       </c>
       <c r="AA69">
         <f>LENB(K69)-$B$4</f>
-        <v>-18</v>
+        <v>-12</v>
       </c>
       <c r="AB69">
         <f>LENB(L69)-$B$4</f>
-        <v>-18</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="70" spans="4:28" x14ac:dyDescent="0.55000000000000004">
@@ -6998,7 +7174,7 @@
         <v>61</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F70" s="7">
         <v>2</v>
@@ -7006,13 +7182,17 @@
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
       <c r="I70" s="7" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="K70" s="7"/>
-      <c r="L70" s="7"/>
+        <v>419</v>
+      </c>
+      <c r="K70" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="L70" s="7" t="s">
+        <v>422</v>
+      </c>
       <c r="M70" s="7"/>
       <c r="N70" s="7"/>
       <c r="O70" s="7"/>
@@ -7038,11 +7218,11 @@
       </c>
       <c r="AA70">
         <f>LENB(K70)-$B$4</f>
-        <v>-18</v>
+        <v>1</v>
       </c>
       <c r="AB70">
         <f>LENB(L70)-$B$4</f>
-        <v>-18</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="71" spans="4:28" x14ac:dyDescent="0.55000000000000004">
@@ -7050,7 +7230,7 @@
         <v>62</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F71" s="7">
         <v>1</v>
@@ -7058,13 +7238,17 @@
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
       <c r="I71" s="7" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="K71" s="7"/>
-      <c r="L71" s="7"/>
+        <v>192</v>
+      </c>
+      <c r="K71" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="L71" s="7" t="s">
+        <v>423</v>
+      </c>
       <c r="M71" s="7"/>
       <c r="N71" s="7"/>
       <c r="O71" s="7"/>
@@ -7090,11 +7274,11 @@
       </c>
       <c r="AA71">
         <f>LENB(K71)-$B$4</f>
-        <v>-18</v>
+        <v>-8</v>
       </c>
       <c r="AB71">
         <f>LENB(L71)-$B$4</f>
-        <v>-18</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="72" spans="4:28" x14ac:dyDescent="0.55000000000000004">
@@ -7102,7 +7286,7 @@
         <v>63</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F72" s="7">
         <v>2</v>
@@ -7110,13 +7294,17 @@
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
       <c r="I72" s="7" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="K72" s="7"/>
-      <c r="L72" s="7"/>
+        <v>192</v>
+      </c>
+      <c r="K72" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="L72" s="7" t="s">
+        <v>423</v>
+      </c>
       <c r="M72" s="7"/>
       <c r="N72" s="7"/>
       <c r="O72" s="7"/>
@@ -7142,11 +7330,11 @@
       </c>
       <c r="AA72">
         <f>LENB(K72)-$B$4</f>
-        <v>-18</v>
+        <v>-8</v>
       </c>
       <c r="AB72">
         <f>LENB(L72)-$B$4</f>
-        <v>-18</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="73" spans="4:28" x14ac:dyDescent="0.55000000000000004">
@@ -7154,7 +7342,7 @@
         <v>64</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F73" s="12">
         <v>3</v>
@@ -7162,13 +7350,17 @@
       <c r="G73" s="12"/>
       <c r="H73" s="12"/>
       <c r="I73" s="12" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="J73" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="K73" s="12"/>
-      <c r="L73" s="12"/>
+        <v>420</v>
+      </c>
+      <c r="K73" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="L73" s="12" t="s">
+        <v>424</v>
+      </c>
       <c r="M73" s="12"/>
       <c r="N73" s="12"/>
       <c r="O73" s="12"/>
@@ -7190,15 +7382,15 @@
       </c>
       <c r="Z73">
         <f t="shared" si="3"/>
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="AA73">
         <f>LENB(K73)-$B$4</f>
-        <v>-18</v>
+        <v>-3</v>
       </c>
       <c r="AB73">
         <f>LENB(L73)-$B$4</f>
-        <v>-18</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="75" spans="4:28" x14ac:dyDescent="0.55000000000000004">
@@ -7454,11 +7646,31 @@
   </autoFilter>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="D3:W73">
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="11" priority="9">
       <formula>INT($V3)=TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="6">
+    <cfRule type="expression" dxfId="10" priority="10">
       <formula>MOD(ROW(D3),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I73">
+    <cfRule type="expression" dxfId="9" priority="4" stopIfTrue="1">
+      <formula>0&lt;Y3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:J73">
+    <cfRule type="expression" dxfId="8" priority="3" stopIfTrue="1">
+      <formula>0&lt;Z3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3:K73">
+    <cfRule type="expression" dxfId="7" priority="2" stopIfTrue="1">
+      <formula>0&lt;AA3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L3:L73">
+    <cfRule type="expression" dxfId="6" priority="1" stopIfTrue="1">
+      <formula>0&lt;AB3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7486,7 +7698,7 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="S1" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.55000000000000004">
@@ -7568,7 +7780,7 @@
         <v>153</v>
       </c>
       <c r="S3" s="17" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="X3" s="17" t="s">
         <v>142</v>
@@ -7619,7 +7831,7 @@
       </c>
       <c r="B4" t="str" cm="1">
         <f t="array" aca="1" ref="B4" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_script</v>
+        <v>C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_index</v>
       </c>
       <c r="E4" t="s">
         <v>96</v>
@@ -8031,7 +8243,7 @@
       </c>
       <c r="B6" t="str">
         <f ca="1">"このスクリプトは "&amp;B4&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" ref="E6:E69" si="1">E5</f>
@@ -9638,7 +9850,7 @@
       </c>
       <c r="B14" t="str">
         <f ca="1">$AK$206</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸
@@ -14872,7 +15084,7 @@
     </row>
     <row r="44" spans="1:37" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B44">
         <f>info_index!B3</f>
@@ -22560,7 +22772,7 @@
     </row>
     <row r="97" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="E97" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F97">
         <f>COUNTIF(E$4:E97,E97)</f>
@@ -34580,7 +34792,7 @@
     <row r="206" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="AK206" t="str">
         <f ca="1">IF(LENB($B$6),$B$8&amp;$B$6,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AK$4:AK$203)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$30&amp;CHAR(9)&amp;$B$9&amp;" 1"&amp;$B$10&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$7),CHAR(10)&amp;$B$8&amp;$B$7,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\[kv_script_conv_info.xlsx]info_index によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸
@@ -35374,21 +35586,148 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="14" priority="3">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>0&lt;S$2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4:L203">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="12" priority="2">
       <formula>0&lt;$S4</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7499C32C-6D41-458C-8FAE-4571C9EC5428}">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.58203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>396</v>
+      </c>
+      <c r="B4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>398</v>
+      </c>
+      <c r="B5" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>400</v>
+      </c>
+      <c r="B6" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>402</v>
+      </c>
+      <c r="B7" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>404</v>
+      </c>
+      <c r="B8" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>406</v>
+      </c>
+      <c r="B9" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>408</v>
+      </c>
+      <c r="B10" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>410</v>
+      </c>
+      <c r="B11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>412</v>
+      </c>
+      <c r="B12" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>414</v>
+      </c>
+      <c r="B13" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>415</v>
+      </c>
+      <c r="B14" t="s">
+        <v>416</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762EFF3B-07A8-4E78-B9B2-7005326DA58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2654CB0-DBA7-410D-8A7C-0BEE6882D8F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="432">
   <si>
     <t>RCA2-GS3NA-I-10-2-50-A6-M-K1</t>
   </si>
@@ -1903,6 +1903,10 @@
   </si>
   <si>
     <t>バインダ供給ポンプ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Xロールクラッチ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3947,7 +3951,9 @@
       <c r="J19" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="K19" s="10"/>
+      <c r="K19" s="10" t="s">
+        <v>213</v>
+      </c>
       <c r="L19" s="10" t="s">
         <v>427</v>
       </c>
@@ -3982,7 +3988,7 @@
       </c>
       <c r="AA19">
         <f>LENB(K19)-$B$4</f>
-        <v>-18</v>
+        <v>-4</v>
       </c>
       <c r="AB19">
         <f>LENB(L19)-$B$4</f>
@@ -4007,7 +4013,9 @@
       <c r="J20" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="K20" s="10"/>
+      <c r="K20" s="10" t="s">
+        <v>214</v>
+      </c>
       <c r="L20" s="10" t="s">
         <v>429</v>
       </c>
@@ -4042,7 +4050,7 @@
       </c>
       <c r="AA20">
         <f>LENB(K20)-$B$4</f>
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="AB20">
         <f>LENB(L20)-$B$4</f>
@@ -4067,7 +4075,9 @@
       <c r="J21" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="K21" s="10"/>
+      <c r="K21" s="10" t="s">
+        <v>217</v>
+      </c>
       <c r="L21" s="10" t="s">
         <v>428</v>
       </c>
@@ -4093,7 +4103,7 @@
         <v>46139</v>
       </c>
       <c r="V21" s="26">
-        <v>46196.622916666667</v>
+        <v>46227.413888888892</v>
       </c>
       <c r="W21" s="8"/>
       <c r="Y21">
@@ -4106,7 +4116,7 @@
       </c>
       <c r="AA21">
         <f>LENB(K21)-$B$4</f>
-        <v>-18</v>
+        <v>-8</v>
       </c>
       <c r="AB21">
         <f>LENB(L21)-$B$4</f>
@@ -7149,7 +7159,7 @@
         <v>46069.554861111108</v>
       </c>
       <c r="V69" s="28">
-        <v>46077.372916666667</v>
+        <v>46227.4375</v>
       </c>
       <c r="W69" s="8"/>
       <c r="Y69">
@@ -7188,7 +7198,7 @@
         <v>419</v>
       </c>
       <c r="K70" s="7" t="s">
-        <v>276</v>
+        <v>431</v>
       </c>
       <c r="L70" s="7" t="s">
         <v>422</v>
@@ -7205,7 +7215,7 @@
         <v>46077.372916666667</v>
       </c>
       <c r="V70" s="28">
-        <v>46077.372916666667</v>
+        <v>46227.4375</v>
       </c>
       <c r="W70" s="8"/>
       <c r="Y70">
@@ -7218,7 +7228,7 @@
       </c>
       <c r="AA70">
         <f>LENB(K70)-$B$4</f>
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="AB70">
         <f>LENB(L70)-$B$4</f>
@@ -7261,7 +7271,7 @@
         <v>46083.387499999997</v>
       </c>
       <c r="V71" s="28">
-        <v>46083.387499999997</v>
+        <v>46227.4375</v>
       </c>
       <c r="W71" s="8"/>
       <c r="Y71">
@@ -7317,7 +7327,7 @@
         <v>46083.387499999997</v>
       </c>
       <c r="V72" s="28">
-        <v>46083.387499999997</v>
+        <v>46227.4375</v>
       </c>
       <c r="W72" s="8"/>
       <c r="Y72">
@@ -7373,7 +7383,7 @@
         <v>46083.363888888889</v>
       </c>
       <c r="V73" s="29">
-        <v>46083.363888888889</v>
+        <v>46227.4375</v>
       </c>
       <c r="W73" s="13"/>
       <c r="Y73">

--- a/doc/kv_script_conv_info.xlsx
+++ b/doc/kv_script_conv_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\unit01\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75437E9C-D700-4234-AD61-1DF930D3C808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{459A2834-1346-4A16-8C5D-65AED61C45ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="461">
   <si>
     <t>RCA2-GS3NA-I-10-2-50-A6-M-K1</t>
   </si>
@@ -2026,6 +2026,12 @@
   <si>
     <t>●</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>X-Roll Tower Unit</t>
+  </si>
+  <si>
+    <t>Brazing Foil Reel Unit</t>
   </si>
 </sst>
 </file>
@@ -2375,7 +2381,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill>
@@ -2394,48 +2400,6 @@
           <fgColor rgb="FF33CCCC"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF5050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF5050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF5050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF5050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0099CC"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF5050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF5050"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2865,7 +2829,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
-  <sheetPr codeName="Sheet1" filterMode="1"/>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AE100"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -2993,7 +2957,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="3" spans="1:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>384</v>
       </c>
@@ -3684,7 +3648,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="1:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D12" s="20">
         <v>42</v>
       </c>
@@ -3743,7 +3707,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="13" spans="1:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D13" s="20">
         <v>43</v>
       </c>
@@ -3802,7 +3766,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="14" spans="1:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D14" s="20">
         <v>44</v>
       </c>
@@ -4285,7 +4249,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="21" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D21" s="20">
         <v>67</v>
       </c>
@@ -4354,7 +4318,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D22" s="20">
         <v>68</v>
       </c>
@@ -4419,7 +4383,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="23" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D23" s="20">
         <v>69</v>
       </c>
@@ -4484,7 +4448,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="24" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D24" s="20">
         <v>70</v>
       </c>
@@ -4549,7 +4513,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="25" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D25" s="20">
         <v>71</v>
       </c>
@@ -4614,7 +4578,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="26" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D26" s="20">
         <v>72</v>
       </c>
@@ -5840,7 +5804,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="42" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D42" s="20">
         <v>15</v>
       </c>
@@ -6191,7 +6155,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="47" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D47" s="20">
         <v>12</v>
       </c>
@@ -6256,7 +6220,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="48" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D48" s="20">
         <v>16</v>
       </c>
@@ -6321,7 +6285,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="49" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D49" s="20">
         <v>17</v>
       </c>
@@ -6386,7 +6350,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="50" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D50" s="20">
         <v>21</v>
       </c>
@@ -6459,7 +6423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D51" s="20">
         <v>24</v>
       </c>
@@ -6524,7 +6488,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="52" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D52" s="6">
         <v>25</v>
       </c>
@@ -6589,7 +6553,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="53" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D53" s="6">
         <v>29</v>
       </c>
@@ -6652,7 +6616,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="54" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D54" s="6">
         <v>30</v>
       </c>
@@ -6719,7 +6683,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="55" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D55" s="6">
         <v>34</v>
       </c>
@@ -6786,7 +6750,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="56" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D56" s="6">
         <v>26</v>
       </c>
@@ -6847,7 +6811,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="57" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D57" s="6">
         <v>27</v>
       </c>
@@ -6908,7 +6872,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="58" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D58" s="6">
         <v>28</v>
       </c>
@@ -6969,7 +6933,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="59" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D59" s="6">
         <v>31</v>
       </c>
@@ -7032,7 +6996,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="60" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D60" s="6">
         <v>39</v>
       </c>
@@ -7483,7 +7447,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="67" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D67" s="6">
         <v>60</v>
       </c>
@@ -7499,7 +7463,7 @@
         <v>223</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>224</v>
+        <v>459</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7" t="s">
@@ -7523,7 +7487,7 @@
         <v>46069.809027777781</v>
       </c>
       <c r="X67" s="25">
-        <v>46226.584027777775</v>
+        <v>46227.67291666667</v>
       </c>
       <c r="Y67" s="7"/>
       <c r="Z67" s="8"/>
@@ -7533,7 +7497,7 @@
       </c>
       <c r="AC67">
         <f t="shared" si="1"/>
-        <v>-53</v>
+        <v>-47</v>
       </c>
       <c r="AD67">
         <f>LENB(K67)-$B$4</f>
@@ -7544,7 +7508,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="68" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D68" s="6">
         <v>65</v>
       </c>
@@ -7560,7 +7524,7 @@
         <v>225</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>226</v>
+        <v>460</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7" t="s">
@@ -7584,7 +7548,7 @@
         <v>46085.347222222219</v>
       </c>
       <c r="X68" s="25">
-        <v>46226.584027777775</v>
+        <v>46227.67291666667</v>
       </c>
       <c r="Y68" s="7"/>
       <c r="Z68" s="8"/>
@@ -7594,7 +7558,7 @@
       </c>
       <c r="AC68">
         <f t="shared" ref="AC68:AC73" si="3">LENB(J68)-$B$3</f>
-        <v>-47</v>
+        <v>-42</v>
       </c>
       <c r="AD68">
         <f>LENB(K68)-$B$4</f>
@@ -7727,7 +7691,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="71" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D71" s="6">
         <v>62</v>
       </c>
@@ -7786,7 +7750,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="72" spans="4:31" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="4:31" x14ac:dyDescent="0.55000000000000004">
       <c r="D72" s="6">
         <v>63</v>
       </c>
@@ -8152,38 +8116,19 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="D2:Z73" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
-    <filterColumn colId="21">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D3:Z61">
-      <sortCondition ref="E2:E61"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="D2:Z73" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}"/>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="D3:Z73">
-    <cfRule type="expression" dxfId="8" priority="9">
+    <cfRule type="expression" dxfId="6" priority="9">
       <formula>INT($X3)=TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="10">
+    <cfRule type="expression" dxfId="5" priority="10">
       <formula>MOD(ROW(D3),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I73 L3:M73">
-    <cfRule type="expression" dxfId="6" priority="4" stopIfTrue="1">
+  <conditionalFormatting sqref="I3:M73">
+    <cfRule type="expression" dxfId="4" priority="4" stopIfTrue="1">
       <formula>0&lt;AB3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J3:J73">
-    <cfRule type="expression" dxfId="5" priority="3" stopIfTrue="1">
-      <formula>0&lt;AC3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K3:K73">
-    <cfRule type="expression" dxfId="4" priority="2" stopIfTrue="1">
-      <formula>0&lt;AD3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3:N73">
@@ -11124,12 +11069,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//X-Roll Unit
+	//X-Roll Tower Unit
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-Roll Unit';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit7】 X-Roll Unit';
+			strRt	:= 'X-Roll Tower Unit';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit7】 X-Roll Tower Unit';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11137,12 +11082,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Brazing Foil Reel
+	//Brazing Foil Reel Unit
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Brazing Foil Reel';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit8】 Brazing Foil Reel';
+			strRt	:= 'Brazing Foil Reel Unit';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit8】 Brazing Foil Reel Unit';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -25846,15 +25791,15 @@
       </c>
       <c r="I113" t="str">
         <f ca="1"/>
-        <v>X-Roll Unit</v>
+        <v>X-Roll Tower Unit</v>
       </c>
       <c r="J113" t="str">
         <f ca="1"/>
-        <v>X-Roll Unit</v>
+        <v>X-Roll Tower Unit</v>
       </c>
       <c r="L113" t="str">
         <f ca="1"/>
-        <v>【unit7】 X-Roll Unit</v>
+        <v>【unit7】 X-Roll Tower Unit</v>
       </c>
       <c r="M113" t="str">
         <v/>
@@ -25872,7 +25817,7 @@
       </c>
       <c r="S113">
         <f t="shared" ca="1" si="2"/>
-        <v>-43</v>
+        <v>-37</v>
       </c>
       <c r="X113" t="str">
         <f ca="1"/>
@@ -25887,75 +25832,75 @@
       <c r="Z113" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-Roll Unit
+	//X-Roll Tower Unit
 	ELSIF uiInfoIdx = 7 THEN</v>
       </c>
       <c r="AA113" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-Roll Unit
+	//X-Roll Tower Unit
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB113" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-Roll Unit
+	//X-Roll Tower Unit
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-Roll Unit';</v>
+			strRt	:= 'X-Roll Tower Unit';</v>
       </c>
       <c r="AC113" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-Roll Unit
+	//X-Roll Tower Unit
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-Roll Unit';
+			strRt	:= 'X-Roll Tower Unit';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD113" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-Roll Unit
+	//X-Roll Tower Unit
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-Roll Unit';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit7】 X-Roll Unit';</v>
+			strRt	:= 'X-Roll Tower Unit';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit7】 X-Roll Tower Unit';</v>
       </c>
       <c r="AE113" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-Roll Unit
+	//X-Roll Tower Unit
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-Roll Unit';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit7】 X-Roll Unit';
+			strRt	:= 'X-Roll Tower Unit';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit7】 X-Roll Tower Unit';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF113" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-Roll Unit
+	//X-Roll Tower Unit
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-Roll Unit';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit7】 X-Roll Unit';
+			strRt	:= 'X-Roll Tower Unit';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit7】 X-Roll Tower Unit';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AG113" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-Roll Unit
+	//X-Roll Tower Unit
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-Roll Unit';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit7】 X-Roll Unit';
+			strRt	:= 'X-Roll Tower Unit';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit7】 X-Roll Tower Unit';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -25963,12 +25908,12 @@
       <c r="AH113" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-Roll Unit
+	//X-Roll Tower Unit
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-Roll Unit';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit7】 X-Roll Unit';
+			strRt	:= 'X-Roll Tower Unit';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit7】 X-Roll Tower Unit';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -25977,12 +25922,12 @@
       <c r="AI113" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-Roll Unit
+	//X-Roll Tower Unit
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-Roll Unit';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit7】 X-Roll Unit';
+			strRt	:= 'X-Roll Tower Unit';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit7】 X-Roll Tower Unit';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -25994,12 +25939,12 @@
       <c r="AJ113" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-Roll Unit
+	//X-Roll Tower Unit
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-Roll Unit';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit7】 X-Roll Unit';
+			strRt	:= 'X-Roll Tower Unit';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit7】 X-Roll Tower Unit';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -26011,12 +25956,12 @@
       <c r="AK113" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//X-Roll Unit
+	//X-Roll Tower Unit
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-Roll Unit';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit7】 X-Roll Unit';
+			strRt	:= 'X-Roll Tower Unit';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit7】 X-Roll Tower Unit';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -26043,15 +25988,15 @@
       </c>
       <c r="I114" t="str">
         <f ca="1"/>
-        <v>Brazing Foil Reel</v>
+        <v>Brazing Foil Reel Unit</v>
       </c>
       <c r="J114" t="str">
         <f ca="1"/>
-        <v>Brazing Foil Reel</v>
+        <v>Brazing Foil Reel Unit</v>
       </c>
       <c r="L114" t="str">
         <f ca="1"/>
-        <v>【unit8】 Brazing Foil Reel</v>
+        <v>【unit8】 Brazing Foil Reel Unit</v>
       </c>
       <c r="M114" t="str">
         <v/>
@@ -26069,7 +26014,7 @@
       </c>
       <c r="S114">
         <f t="shared" ca="1" si="2"/>
-        <v>-37</v>
+        <v>-32</v>
       </c>
       <c r="X114" t="str">
         <f ca="1"/>
@@ -26084,75 +26029,75 @@
       <c r="Z114" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Brazing Foil Reel
+	//Brazing Foil Reel Unit
 	ELSIF uiInfoIdx = 8 THEN</v>
       </c>
       <c r="AA114" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Brazing Foil Reel
+	//Brazing Foil Reel Unit
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AB114" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Brazing Foil Reel
+	//Brazing Foil Reel Unit
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Brazing Foil Reel';</v>
+			strRt	:= 'Brazing Foil Reel Unit';</v>
       </c>
       <c r="AC114" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Brazing Foil Reel
+	//Brazing Foil Reel Unit
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Brazing Foil Reel';
+			strRt	:= 'Brazing Foil Reel Unit';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AD114" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Brazing Foil Reel
+	//Brazing Foil Reel Unit
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Brazing Foil Reel';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit8】 Brazing Foil Reel';</v>
+			strRt	:= 'Brazing Foil Reel Unit';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit8】 Brazing Foil Reel Unit';</v>
       </c>
       <c r="AE114" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Brazing Foil Reel
+	//Brazing Foil Reel Unit
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Brazing Foil Reel';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit8】 Brazing Foil Reel';
+			strRt	:= 'Brazing Foil Reel Unit';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit8】 Brazing Foil Reel Unit';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AF114" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Brazing Foil Reel
+	//Brazing Foil Reel Unit
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Brazing Foil Reel';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit8】 Brazing Foil Reel';
+			strRt	:= 'Brazing Foil Reel Unit';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit8】 Brazing Foil Reel Unit';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AG114" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Brazing Foil Reel
+	//Brazing Foil Reel Unit
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Brazing Foil Reel';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit8】 Brazing Foil Reel';
+			strRt	:= 'Brazing Foil Reel Unit';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit8】 Brazing Foil Reel Unit';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -26160,12 +26105,12 @@
       <c r="AH114" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Brazing Foil Reel
+	//Brazing Foil Reel Unit
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Brazing Foil Reel';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit8】 Brazing Foil Reel';
+			strRt	:= 'Brazing Foil Reel Unit';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit8】 Brazing Foil Reel Unit';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -26174,12 +26119,12 @@
       <c r="AI114" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Brazing Foil Reel
+	//Brazing Foil Reel Unit
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Brazing Foil Reel';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit8】 Brazing Foil Reel';
+			strRt	:= 'Brazing Foil Reel Unit';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit8】 Brazing Foil Reel Unit';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -26191,12 +26136,12 @@
       <c r="AJ114" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Brazing Foil Reel
+	//Brazing Foil Reel Unit
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Brazing Foil Reel';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit8】 Brazing Foil Reel';
+			strRt	:= 'Brazing Foil Reel Unit';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit8】 Brazing Foil Reel Unit';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -26208,12 +26153,12 @@
       <c r="AK114" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Brazing Foil Reel
+	//Brazing Foil Reel Unit
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Brazing Foil Reel';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit8】 Brazing Foil Reel';
+			strRt	:= 'Brazing Foil Reel Unit';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit8】 Brazing Foil Reel Unit';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -36066,12 +36011,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//X-Roll Unit
+	//X-Roll Tower Unit
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'X-Roll Unit';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit7】 X-Roll Unit';
+			strRt	:= 'X-Roll Tower Unit';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit7】 X-Roll Tower Unit';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -36079,12 +36024,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Brazing Foil Reel
+	//Brazing Foil Reel Unit
 	ELSIF uiInfoIdx = 8 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Brazing Foil Reel';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【unit8】 Brazing Foil Reel';
+			strRt	:= 'Brazing Foil Reel Unit';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【unit8】 Brazing Foil Reel Unit';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
